--- a/DECEMBER/DECEMBER BAR.xlsx
+++ b/DECEMBER/DECEMBER BAR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500" firstSheet="4" activeTab="7"/>
+    <workbookView windowWidth="19635" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="BUK BUNGA (Groceries)" sheetId="28" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="86">
   <si>
     <t>DATE</t>
   </si>
@@ -153,6 +153,24 @@
     <t>ROSEMARY</t>
   </si>
   <si>
+    <t>WATERMELON</t>
+  </si>
+  <si>
+    <t>GINGER</t>
+  </si>
+  <si>
+    <t>CHILI</t>
+  </si>
+  <si>
+    <t>TRASH BAG</t>
+  </si>
+  <si>
+    <t>OATSIDE</t>
+  </si>
+  <si>
+    <t>SARIWANGI</t>
+  </si>
+  <si>
     <t>INV NO</t>
   </si>
   <si>
@@ -208,9 +226,6 @@
   </si>
   <si>
     <t>MALANG APPLE</t>
-  </si>
-  <si>
-    <t>WATERMELON</t>
   </si>
   <si>
     <t>LYCHEE CAN</t>
@@ -1344,7 +1359,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="307">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2140,24 +2155,6 @@
     <xf numFmtId="178" fontId="27" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2224,18 +2221,6 @@
     <xf numFmtId="179" fontId="30" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="30" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="30" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2244,6 +2229,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="30" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2950,18 +2947,18 @@
       <c r="E1" s="252" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="285" t="s">
+      <c r="F1" s="279" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A2" s="286">
+      <c r="A2" s="280">
         <v>45995</v>
       </c>
-      <c r="B2" s="287" t="s">
+      <c r="B2" s="281" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="288">
+      <c r="C2" s="282">
         <v>5</v>
       </c>
       <c r="D2" s="7">
@@ -2971,17 +2968,17 @@
         <f t="shared" ref="E2:E7" si="0">SUM(C2*D2)</f>
         <v>100000</v>
       </c>
-      <c r="F2" s="289">
+      <c r="F2" s="283">
         <f>SUM(E2:E13)</f>
         <v>652000</v>
       </c>
     </row>
     <row r="3" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A3" s="290"/>
-      <c r="B3" s="287" t="s">
+      <c r="A3" s="284"/>
+      <c r="B3" s="281" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="288">
+      <c r="C3" s="282">
         <v>2</v>
       </c>
       <c r="D3" s="7">
@@ -2991,14 +2988,14 @@
         <f t="shared" si="0"/>
         <v>140000</v>
       </c>
-      <c r="F3" s="291"/>
+      <c r="F3" s="285"/>
     </row>
     <row r="4" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A4" s="290"/>
-      <c r="B4" s="287" t="s">
+      <c r="A4" s="284"/>
+      <c r="B4" s="281" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="288">
+      <c r="C4" s="282">
         <v>6</v>
       </c>
       <c r="D4" s="7">
@@ -3008,14 +3005,14 @@
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
-      <c r="F4" s="291"/>
+      <c r="F4" s="285"/>
     </row>
     <row r="5" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A5" s="290"/>
-      <c r="B5" s="287" t="s">
+      <c r="A5" s="284"/>
+      <c r="B5" s="281" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="288">
+      <c r="C5" s="282">
         <v>1</v>
       </c>
       <c r="D5" s="7">
@@ -3025,14 +3022,14 @@
         <f t="shared" ref="E5:E68" si="1">SUM(C5*D5)</f>
         <v>38000</v>
       </c>
-      <c r="F5" s="291"/>
+      <c r="F5" s="285"/>
     </row>
     <row r="6" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A6" s="290"/>
-      <c r="B6" s="287" t="s">
+      <c r="A6" s="284"/>
+      <c r="B6" s="281" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="288">
+      <c r="C6" s="282">
         <v>0.3</v>
       </c>
       <c r="D6" s="7">
@@ -3042,14 +3039,14 @@
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
-      <c r="F6" s="291"/>
+      <c r="F6" s="285"/>
     </row>
     <row r="7" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A7" s="290"/>
-      <c r="B7" s="287" t="s">
+      <c r="A7" s="284"/>
+      <c r="B7" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="288">
+      <c r="C7" s="282">
         <v>1</v>
       </c>
       <c r="D7" s="7">
@@ -3059,14 +3056,14 @@
         <f t="shared" si="1"/>
         <v>25000</v>
       </c>
-      <c r="F7" s="291"/>
+      <c r="F7" s="285"/>
     </row>
     <row r="8" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A8" s="290"/>
-      <c r="B8" s="287" t="s">
+      <c r="A8" s="284"/>
+      <c r="B8" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="288">
+      <c r="C8" s="282">
         <v>1</v>
       </c>
       <c r="D8" s="7">
@@ -3076,14 +3073,14 @@
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="F8" s="291"/>
+      <c r="F8" s="285"/>
     </row>
     <row r="9" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A9" s="290"/>
-      <c r="B9" s="287" t="s">
+      <c r="A9" s="284"/>
+      <c r="B9" s="281" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="288">
+      <c r="C9" s="282">
         <v>1</v>
       </c>
       <c r="D9" s="7">
@@ -3093,14 +3090,14 @@
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
-      <c r="F9" s="291"/>
+      <c r="F9" s="285"/>
     </row>
     <row r="10" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A10" s="290"/>
-      <c r="B10" s="287" t="s">
+      <c r="A10" s="284"/>
+      <c r="B10" s="281" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="288">
+      <c r="C10" s="282">
         <v>3</v>
       </c>
       <c r="D10" s="7">
@@ -3110,14 +3107,14 @@
         <f t="shared" si="1"/>
         <v>72000</v>
       </c>
-      <c r="F10" s="291"/>
+      <c r="F10" s="285"/>
     </row>
     <row r="11" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A11" s="290"/>
-      <c r="B11" s="287" t="s">
+      <c r="A11" s="284"/>
+      <c r="B11" s="281" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="288">
+      <c r="C11" s="282">
         <v>1</v>
       </c>
       <c r="D11" s="7">
@@ -3127,14 +3124,14 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F11" s="291"/>
+      <c r="F11" s="285"/>
     </row>
     <row r="12" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A12" s="292"/>
-      <c r="B12" s="287" t="s">
+      <c r="A12" s="286"/>
+      <c r="B12" s="281" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="288">
+      <c r="C12" s="282">
         <v>1</v>
       </c>
       <c r="D12" s="7">
@@ -3144,16 +3141,16 @@
         <f t="shared" si="1"/>
         <v>49000</v>
       </c>
-      <c r="F12" s="273"/>
+      <c r="F12" s="267"/>
     </row>
     <row r="13" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A13" s="293">
+      <c r="A13" s="280">
         <v>45996</v>
       </c>
-      <c r="B13" s="287" t="s">
+      <c r="B13" s="281" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="288">
+      <c r="C13" s="282">
         <v>8</v>
       </c>
       <c r="D13" s="7">
@@ -3163,17 +3160,17 @@
         <f t="shared" si="1"/>
         <v>80000</v>
       </c>
-      <c r="F13" s="294">
+      <c r="F13" s="283">
         <f>SUM(E13:E25)</f>
         <v>730000</v>
       </c>
     </row>
     <row r="14" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A14" s="295"/>
-      <c r="B14" s="287" t="s">
+      <c r="A14" s="284"/>
+      <c r="B14" s="281" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="288">
+      <c r="C14" s="282">
         <v>2</v>
       </c>
       <c r="D14" s="7">
@@ -3183,14 +3180,14 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F14" s="296"/>
+      <c r="F14" s="285"/>
     </row>
     <row r="15" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A15" s="295"/>
-      <c r="B15" s="287" t="s">
+      <c r="A15" s="284"/>
+      <c r="B15" s="281" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="288">
+      <c r="C15" s="282">
         <v>2</v>
       </c>
       <c r="D15" s="7">
@@ -3200,14 +3197,14 @@
         <f t="shared" si="1"/>
         <v>70000</v>
       </c>
-      <c r="F15" s="296"/>
+      <c r="F15" s="285"/>
     </row>
     <row r="16" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A16" s="295"/>
-      <c r="B16" s="287" t="s">
+      <c r="A16" s="284"/>
+      <c r="B16" s="281" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="288">
+      <c r="C16" s="282">
         <v>0.5</v>
       </c>
       <c r="D16" s="7">
@@ -3216,14 +3213,14 @@
       <c r="E16" s="7">
         <v>48000</v>
       </c>
-      <c r="F16" s="296"/>
+      <c r="F16" s="285"/>
     </row>
     <row r="17" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A17" s="295"/>
-      <c r="B17" s="287" t="s">
+      <c r="A17" s="284"/>
+      <c r="B17" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="288">
+      <c r="C17" s="282">
         <v>1.1</v>
       </c>
       <c r="D17" s="7">
@@ -3232,14 +3229,14 @@
       <c r="E17" s="7">
         <v>42000</v>
       </c>
-      <c r="F17" s="296"/>
+      <c r="F17" s="285"/>
     </row>
     <row r="18" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A18" s="295"/>
-      <c r="B18" s="287" t="s">
+      <c r="A18" s="284"/>
+      <c r="B18" s="281" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="282">
         <v>5</v>
       </c>
       <c r="D18" s="7">
@@ -3249,32 +3246,32 @@
         <f t="shared" si="1"/>
         <v>120000</v>
       </c>
-      <c r="F18" s="296"/>
+      <c r="F18" s="285"/>
     </row>
     <row r="19" s="244" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A19" s="295"/>
-      <c r="B19" s="297" t="s">
+      <c r="A19" s="284"/>
+      <c r="B19" s="287" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="298">
+      <c r="C19" s="288">
         <v>3</v>
       </c>
-      <c r="D19" s="289">
+      <c r="D19" s="283">
         <v>40000</v>
       </c>
       <c r="E19" s="7">
         <f t="shared" si="1"/>
         <v>120000</v>
       </c>
-      <c r="F19" s="296"/>
-      <c r="G19" s="274"/>
+      <c r="F19" s="285"/>
+      <c r="G19" s="268"/>
     </row>
     <row r="20" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A20" s="295"/>
-      <c r="B20" s="299" t="s">
+      <c r="A20" s="284"/>
+      <c r="B20" s="289" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="288">
+      <c r="C20" s="282">
         <v>1</v>
       </c>
       <c r="D20" s="256">
@@ -3284,14 +3281,14 @@
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F20" s="296"/>
+      <c r="F20" s="285"/>
     </row>
     <row r="21" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A21" s="295"/>
-      <c r="B21" s="299" t="s">
+      <c r="A21" s="284"/>
+      <c r="B21" s="289" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="288">
+      <c r="C21" s="282">
         <v>2</v>
       </c>
       <c r="D21" s="256">
@@ -3301,14 +3298,14 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F21" s="296"/>
+      <c r="F21" s="285"/>
     </row>
     <row r="22" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A22" s="295"/>
-      <c r="B22" s="299" t="s">
+      <c r="A22" s="284"/>
+      <c r="B22" s="289" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="288">
+      <c r="C22" s="282">
         <v>0.5</v>
       </c>
       <c r="D22" s="256">
@@ -3318,14 +3315,14 @@
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
-      <c r="F22" s="296"/>
+      <c r="F22" s="285"/>
     </row>
     <row r="23" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A23" s="295"/>
-      <c r="B23" s="299" t="s">
+      <c r="A23" s="284"/>
+      <c r="B23" s="289" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="288">
+      <c r="C23" s="282">
         <v>1</v>
       </c>
       <c r="D23" s="256">
@@ -3335,14 +3332,14 @@
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="F23" s="296"/>
+      <c r="F23" s="285"/>
     </row>
     <row r="24" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A24" s="295"/>
-      <c r="B24" s="299" t="s">
+      <c r="A24" s="284"/>
+      <c r="B24" s="289" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="288">
+      <c r="C24" s="282">
         <v>0.3</v>
       </c>
       <c r="D24" s="256">
@@ -3352,14 +3349,14 @@
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F24" s="296"/>
+      <c r="F24" s="285"/>
     </row>
     <row r="25" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A25" s="300"/>
-      <c r="B25" s="299" t="s">
+      <c r="A25" s="286"/>
+      <c r="B25" s="289" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="288">
+      <c r="C25" s="282">
         <v>1</v>
       </c>
       <c r="D25" s="256">
@@ -3369,111 +3366,168 @@
         <f t="shared" si="1"/>
         <v>35000</v>
       </c>
-      <c r="F25" s="301"/>
+      <c r="F25" s="267"/>
     </row>
     <row r="26" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A26" s="302"/>
-      <c r="B26" s="299"/>
-      <c r="C26" s="288"/>
-      <c r="D26" s="256"/>
+      <c r="A26" s="290">
+        <v>45997</v>
+      </c>
+      <c r="B26" s="289" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="282">
+        <v>3.995</v>
+      </c>
+      <c r="D26" s="256">
+        <v>15000</v>
+      </c>
       <c r="E26" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="256"/>
+        <v>60000</v>
+      </c>
+      <c r="F26" s="291">
+        <f>SUM(E26:E34)</f>
+        <v>422000</v>
+      </c>
     </row>
     <row r="27" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A27" s="302"/>
-      <c r="B27" s="299"/>
-      <c r="C27" s="288"/>
-      <c r="D27" s="256"/>
+      <c r="A27" s="292"/>
+      <c r="B27" s="289" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="282">
+        <v>2</v>
+      </c>
+      <c r="D27" s="256">
+        <v>20000</v>
+      </c>
       <c r="E27" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F27" s="256"/>
+        <v>40000</v>
+      </c>
+      <c r="F27" s="293"/>
     </row>
     <row r="28" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A28" s="302"/>
-      <c r="B28" s="299"/>
-      <c r="C28" s="288"/>
-      <c r="D28" s="256"/>
+      <c r="A28" s="292"/>
+      <c r="B28" s="289" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="282">
+        <v>0.5</v>
+      </c>
+      <c r="D28" s="256">
+        <v>35000</v>
+      </c>
       <c r="E28" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="256"/>
+        <v>18000</v>
+      </c>
+      <c r="F28" s="293"/>
     </row>
     <row r="29" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A29" s="302"/>
-      <c r="B29" s="299"/>
-      <c r="C29" s="288"/>
-      <c r="D29" s="256"/>
+      <c r="A29" s="292"/>
+      <c r="B29" s="289" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="282">
+        <v>0.1</v>
+      </c>
+      <c r="D29" s="256">
+        <v>80000</v>
+      </c>
       <c r="E29" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="256"/>
+        <v>8000</v>
+      </c>
+      <c r="F29" s="293"/>
     </row>
     <row r="30" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A30" s="302"/>
-      <c r="B30" s="299"/>
-      <c r="C30" s="288"/>
-      <c r="D30" s="256"/>
+      <c r="A30" s="292"/>
+      <c r="B30" s="289" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="282">
+        <v>0.5</v>
+      </c>
+      <c r="D30" s="256">
+        <v>30000</v>
+      </c>
       <c r="E30" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="256"/>
+        <v>15000</v>
+      </c>
+      <c r="F30" s="293"/>
     </row>
     <row r="31" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A31" s="302"/>
-      <c r="B31" s="299"/>
-      <c r="C31" s="288"/>
-      <c r="D31" s="256"/>
+      <c r="A31" s="292"/>
+      <c r="B31" s="289" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="282">
+        <v>4</v>
+      </c>
+      <c r="D31" s="256">
+        <v>20000</v>
+      </c>
       <c r="E31" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F31" s="256"/>
+        <v>80000</v>
+      </c>
+      <c r="F31" s="293"/>
     </row>
     <row r="32" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A32" s="302"/>
-      <c r="B32" s="287"/>
-      <c r="C32" s="288"/>
-      <c r="D32" s="7"/>
+      <c r="A32" s="292"/>
+      <c r="B32" s="281" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="282">
+        <v>4</v>
+      </c>
+      <c r="D32" s="7">
+        <v>24000</v>
+      </c>
       <c r="E32" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F32" s="256"/>
+        <v>96000</v>
+      </c>
+      <c r="F32" s="293"/>
     </row>
     <row r="33" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A33" s="302"/>
-      <c r="B33" s="287"/>
-      <c r="C33" s="288"/>
-      <c r="D33" s="7"/>
+      <c r="A33" s="292"/>
+      <c r="B33" s="281" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="282">
+        <v>2</v>
+      </c>
+      <c r="D33" s="7">
+        <v>40000</v>
+      </c>
       <c r="E33" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="256"/>
+        <v>80000</v>
+      </c>
+      <c r="F33" s="293"/>
     </row>
     <row r="34" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A34" s="302"/>
-      <c r="B34" s="287"/>
-      <c r="C34" s="288"/>
-      <c r="D34" s="7"/>
+      <c r="A34" s="294"/>
+      <c r="B34" s="281" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="282">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7">
+        <v>25000</v>
+      </c>
       <c r="E34" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="256"/>
+        <v>25000</v>
+      </c>
+      <c r="F34" s="295"/>
     </row>
     <row r="35" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A35" s="302"/>
-      <c r="B35" s="287"/>
-      <c r="C35" s="288"/>
+      <c r="A35" s="296"/>
+      <c r="B35" s="281"/>
+      <c r="C35" s="282"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7">
         <f t="shared" si="1"/>
@@ -3482,980 +3536,980 @@
       <c r="F35" s="256"/>
     </row>
     <row r="36" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A36" s="286"/>
-      <c r="B36" s="287"/>
-      <c r="C36" s="288"/>
+      <c r="A36" s="280"/>
+      <c r="B36" s="281"/>
+      <c r="C36" s="282"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F36" s="289">
+      <c r="F36" s="283">
         <f>SUM(E36:E41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A37" s="290"/>
-      <c r="B37" s="287"/>
-      <c r="C37" s="288"/>
+      <c r="A37" s="284"/>
+      <c r="B37" s="281"/>
+      <c r="C37" s="282"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F37" s="291"/>
+      <c r="F37" s="285"/>
     </row>
     <row r="38" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A38" s="290"/>
-      <c r="B38" s="287"/>
-      <c r="C38" s="288"/>
+      <c r="A38" s="284"/>
+      <c r="B38" s="281"/>
+      <c r="C38" s="282"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F38" s="291"/>
+      <c r="F38" s="285"/>
     </row>
     <row r="39" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A39" s="290"/>
-      <c r="B39" s="287"/>
-      <c r="C39" s="288"/>
+      <c r="A39" s="284"/>
+      <c r="B39" s="281"/>
+      <c r="C39" s="282"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F39" s="291"/>
+      <c r="F39" s="285"/>
     </row>
     <row r="40" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A40" s="290"/>
-      <c r="B40" s="287"/>
-      <c r="C40" s="288"/>
+      <c r="A40" s="284"/>
+      <c r="B40" s="281"/>
+      <c r="C40" s="282"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F40" s="291"/>
+      <c r="F40" s="285"/>
     </row>
     <row r="41" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A41" s="292"/>
-      <c r="B41" s="287"/>
-      <c r="C41" s="288"/>
+      <c r="A41" s="286"/>
+      <c r="B41" s="281"/>
+      <c r="C41" s="282"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F41" s="273"/>
+      <c r="F41" s="267"/>
     </row>
     <row r="42" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A42" s="286"/>
-      <c r="B42" s="287"/>
-      <c r="C42" s="288"/>
+      <c r="A42" s="280"/>
+      <c r="B42" s="281"/>
+      <c r="C42" s="282"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F42" s="289">
+      <c r="F42" s="283">
         <f>SUM(E42:E47)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A43" s="290"/>
-      <c r="B43" s="287"/>
-      <c r="C43" s="288"/>
+      <c r="A43" s="284"/>
+      <c r="B43" s="281"/>
+      <c r="C43" s="282"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F43" s="291"/>
+      <c r="F43" s="285"/>
     </row>
     <row r="44" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A44" s="290"/>
-      <c r="B44" s="287"/>
-      <c r="C44" s="288"/>
+      <c r="A44" s="284"/>
+      <c r="B44" s="281"/>
+      <c r="C44" s="282"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F44" s="291"/>
+      <c r="F44" s="285"/>
     </row>
     <row r="45" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A45" s="290"/>
-      <c r="B45" s="287"/>
-      <c r="C45" s="288"/>
+      <c r="A45" s="284"/>
+      <c r="B45" s="281"/>
+      <c r="C45" s="282"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F45" s="291"/>
+      <c r="F45" s="285"/>
     </row>
     <row r="46" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A46" s="290"/>
-      <c r="B46" s="287"/>
-      <c r="C46" s="288"/>
+      <c r="A46" s="284"/>
+      <c r="B46" s="281"/>
+      <c r="C46" s="282"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F46" s="291"/>
+      <c r="F46" s="285"/>
     </row>
     <row r="47" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A47" s="292"/>
-      <c r="B47" s="287"/>
-      <c r="C47" s="288"/>
+      <c r="A47" s="286"/>
+      <c r="B47" s="281"/>
+      <c r="C47" s="282"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F47" s="273"/>
+      <c r="F47" s="267"/>
     </row>
     <row r="48" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A48" s="286"/>
-      <c r="B48" s="287"/>
-      <c r="C48" s="288"/>
+      <c r="A48" s="280"/>
+      <c r="B48" s="281"/>
+      <c r="C48" s="282"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F48" s="289">
+      <c r="F48" s="283">
         <f>SUM(E48:E56)</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A49" s="290"/>
-      <c r="B49" s="287"/>
-      <c r="C49" s="288"/>
+      <c r="A49" s="284"/>
+      <c r="B49" s="281"/>
+      <c r="C49" s="282"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F49" s="291"/>
+      <c r="F49" s="285"/>
     </row>
     <row r="50" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A50" s="290"/>
-      <c r="B50" s="287"/>
-      <c r="C50" s="288"/>
+      <c r="A50" s="284"/>
+      <c r="B50" s="281"/>
+      <c r="C50" s="282"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F50" s="291"/>
+      <c r="F50" s="285"/>
     </row>
     <row r="51" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A51" s="290"/>
-      <c r="B51" s="287"/>
-      <c r="C51" s="288"/>
+      <c r="A51" s="284"/>
+      <c r="B51" s="281"/>
+      <c r="C51" s="282"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F51" s="291"/>
+      <c r="F51" s="285"/>
     </row>
     <row r="52" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A52" s="290"/>
-      <c r="B52" s="287"/>
-      <c r="C52" s="288"/>
+      <c r="A52" s="284"/>
+      <c r="B52" s="281"/>
+      <c r="C52" s="282"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F52" s="291"/>
+      <c r="F52" s="285"/>
     </row>
     <row r="53" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A53" s="290"/>
-      <c r="B53" s="287"/>
-      <c r="C53" s="288"/>
+      <c r="A53" s="284"/>
+      <c r="B53" s="281"/>
+      <c r="C53" s="282"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F53" s="291"/>
+      <c r="F53" s="285"/>
     </row>
     <row r="54" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A54" s="290"/>
-      <c r="B54" s="287"/>
-      <c r="C54" s="288"/>
+      <c r="A54" s="284"/>
+      <c r="B54" s="281"/>
+      <c r="C54" s="282"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F54" s="291"/>
+      <c r="F54" s="285"/>
     </row>
     <row r="55" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A55" s="290"/>
-      <c r="B55" s="287"/>
-      <c r="C55" s="288"/>
+      <c r="A55" s="284"/>
+      <c r="B55" s="281"/>
+      <c r="C55" s="282"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F55" s="291"/>
+      <c r="F55" s="285"/>
     </row>
     <row r="56" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A56" s="292"/>
-      <c r="B56" s="287"/>
-      <c r="C56" s="288"/>
+      <c r="A56" s="286"/>
+      <c r="B56" s="281"/>
+      <c r="C56" s="282"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F56" s="273"/>
+      <c r="F56" s="267"/>
     </row>
     <row r="57" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A57" s="286"/>
-      <c r="B57" s="287"/>
-      <c r="C57" s="288"/>
+      <c r="A57" s="280"/>
+      <c r="B57" s="281"/>
+      <c r="C57" s="282"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F57" s="289">
+      <c r="F57" s="283">
         <f>SUM(E57:E71)</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A58" s="290"/>
-      <c r="B58" s="287"/>
-      <c r="C58" s="288"/>
+      <c r="A58" s="284"/>
+      <c r="B58" s="281"/>
+      <c r="C58" s="282"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F58" s="291"/>
+      <c r="F58" s="285"/>
     </row>
     <row r="59" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A59" s="290"/>
-      <c r="B59" s="287"/>
-      <c r="C59" s="288"/>
+      <c r="A59" s="284"/>
+      <c r="B59" s="281"/>
+      <c r="C59" s="282"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F59" s="291"/>
+      <c r="F59" s="285"/>
     </row>
     <row r="60" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A60" s="290"/>
-      <c r="B60" s="287"/>
-      <c r="C60" s="288"/>
+      <c r="A60" s="284"/>
+      <c r="B60" s="281"/>
+      <c r="C60" s="282"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F60" s="291"/>
+      <c r="F60" s="285"/>
     </row>
     <row r="61" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A61" s="290"/>
-      <c r="B61" s="287"/>
-      <c r="C61" s="288"/>
+      <c r="A61" s="284"/>
+      <c r="B61" s="281"/>
+      <c r="C61" s="282"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F61" s="291"/>
+      <c r="F61" s="285"/>
     </row>
     <row r="62" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A62" s="290"/>
-      <c r="B62" s="287"/>
-      <c r="C62" s="288"/>
+      <c r="A62" s="284"/>
+      <c r="B62" s="281"/>
+      <c r="C62" s="282"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F62" s="291"/>
+      <c r="F62" s="285"/>
     </row>
     <row r="63" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A63" s="290"/>
-      <c r="B63" s="287"/>
-      <c r="C63" s="288"/>
+      <c r="A63" s="284"/>
+      <c r="B63" s="281"/>
+      <c r="C63" s="282"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F63" s="291"/>
+      <c r="F63" s="285"/>
     </row>
     <row r="64" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A64" s="290"/>
-      <c r="B64" s="287"/>
-      <c r="C64" s="288"/>
+      <c r="A64" s="284"/>
+      <c r="B64" s="281"/>
+      <c r="C64" s="282"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F64" s="291"/>
+      <c r="F64" s="285"/>
     </row>
     <row r="65" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A65" s="290"/>
-      <c r="B65" s="287"/>
-      <c r="C65" s="288"/>
+      <c r="A65" s="284"/>
+      <c r="B65" s="281"/>
+      <c r="C65" s="282"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F65" s="291"/>
+      <c r="F65" s="285"/>
     </row>
     <row r="66" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A66" s="290"/>
-      <c r="B66" s="287"/>
-      <c r="C66" s="288"/>
+      <c r="A66" s="284"/>
+      <c r="B66" s="281"/>
+      <c r="C66" s="282"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F66" s="291"/>
+      <c r="F66" s="285"/>
     </row>
     <row r="67" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A67" s="290"/>
-      <c r="B67" s="287"/>
-      <c r="C67" s="288"/>
+      <c r="A67" s="284"/>
+      <c r="B67" s="281"/>
+      <c r="C67" s="282"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F67" s="291"/>
+      <c r="F67" s="285"/>
     </row>
     <row r="68" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A68" s="290"/>
-      <c r="B68" s="287"/>
-      <c r="C68" s="288"/>
+      <c r="A68" s="284"/>
+      <c r="B68" s="281"/>
+      <c r="C68" s="282"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F68" s="291"/>
+      <c r="F68" s="285"/>
     </row>
     <row r="69" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A69" s="290"/>
-      <c r="B69" s="287"/>
-      <c r="C69" s="288"/>
+      <c r="A69" s="284"/>
+      <c r="B69" s="281"/>
+      <c r="C69" s="282"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7">
         <f t="shared" ref="E69:E132" si="2">SUM(C69*D69)</f>
         <v>0</v>
       </c>
-      <c r="F69" s="291"/>
+      <c r="F69" s="285"/>
     </row>
     <row r="70" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A70" s="290"/>
-      <c r="B70" s="287"/>
-      <c r="C70" s="288"/>
+      <c r="A70" s="284"/>
+      <c r="B70" s="281"/>
+      <c r="C70" s="282"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F70" s="291"/>
+      <c r="F70" s="285"/>
     </row>
     <row r="71" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A71" s="292"/>
-      <c r="B71" s="287"/>
-      <c r="C71" s="288"/>
+      <c r="A71" s="286"/>
+      <c r="B71" s="281"/>
+      <c r="C71" s="282"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F71" s="273"/>
+      <c r="F71" s="267"/>
     </row>
     <row r="72" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A72" s="286"/>
-      <c r="B72" s="287"/>
-      <c r="C72" s="288"/>
+      <c r="A72" s="280"/>
+      <c r="B72" s="281"/>
+      <c r="C72" s="282"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F72" s="289">
+      <c r="F72" s="283">
         <f>-SUM(E72:E83)</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A73" s="290"/>
-      <c r="B73" s="287"/>
-      <c r="C73" s="288"/>
+      <c r="A73" s="284"/>
+      <c r="B73" s="281"/>
+      <c r="C73" s="282"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F73" s="291"/>
+      <c r="F73" s="285"/>
     </row>
     <row r="74" s="244" customFormat="1" ht="14" customHeight="1" spans="1:8">
-      <c r="A74" s="290"/>
-      <c r="B74" s="287"/>
-      <c r="C74" s="288"/>
+      <c r="A74" s="284"/>
+      <c r="B74" s="281"/>
+      <c r="C74" s="282"/>
       <c r="D74" s="7"/>
       <c r="E74" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F74" s="291"/>
-      <c r="H74" s="274"/>
+      <c r="F74" s="285"/>
+      <c r="H74" s="268"/>
     </row>
     <row r="75" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A75" s="290"/>
-      <c r="B75" s="287"/>
-      <c r="C75" s="288"/>
+      <c r="A75" s="284"/>
+      <c r="B75" s="281"/>
+      <c r="C75" s="282"/>
       <c r="D75" s="7"/>
       <c r="E75" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F75" s="291"/>
+      <c r="F75" s="285"/>
     </row>
     <row r="76" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A76" s="290"/>
-      <c r="B76" s="287"/>
-      <c r="C76" s="288"/>
+      <c r="A76" s="284"/>
+      <c r="B76" s="281"/>
+      <c r="C76" s="282"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F76" s="291"/>
+      <c r="F76" s="285"/>
     </row>
     <row r="77" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A77" s="290"/>
-      <c r="B77" s="287"/>
-      <c r="C77" s="288"/>
+      <c r="A77" s="284"/>
+      <c r="B77" s="281"/>
+      <c r="C77" s="282"/>
       <c r="D77" s="7"/>
       <c r="E77" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F77" s="291"/>
+      <c r="F77" s="285"/>
     </row>
     <row r="78" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A78" s="290"/>
-      <c r="B78" s="287"/>
-      <c r="C78" s="288"/>
+      <c r="A78" s="284"/>
+      <c r="B78" s="281"/>
+      <c r="C78" s="282"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F78" s="291"/>
+      <c r="F78" s="285"/>
     </row>
     <row r="79" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A79" s="290"/>
-      <c r="B79" s="287"/>
-      <c r="C79" s="288"/>
+      <c r="A79" s="284"/>
+      <c r="B79" s="281"/>
+      <c r="C79" s="282"/>
       <c r="D79" s="7"/>
       <c r="E79" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F79" s="291"/>
+      <c r="F79" s="285"/>
     </row>
     <row r="80" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A80" s="290"/>
-      <c r="B80" s="287"/>
-      <c r="C80" s="288"/>
+      <c r="A80" s="284"/>
+      <c r="B80" s="281"/>
+      <c r="C80" s="282"/>
       <c r="D80" s="7"/>
       <c r="E80" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F80" s="291"/>
+      <c r="F80" s="285"/>
     </row>
     <row r="81" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A81" s="290"/>
-      <c r="B81" s="299"/>
-      <c r="C81" s="303"/>
+      <c r="A81" s="284"/>
+      <c r="B81" s="289"/>
+      <c r="C81" s="297"/>
       <c r="D81" s="7"/>
       <c r="E81" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F81" s="291"/>
+      <c r="F81" s="285"/>
     </row>
     <row r="82" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A82" s="290"/>
-      <c r="B82" s="299"/>
-      <c r="C82" s="303"/>
+      <c r="A82" s="284"/>
+      <c r="B82" s="289"/>
+      <c r="C82" s="297"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F82" s="291"/>
+      <c r="F82" s="285"/>
     </row>
     <row r="83" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A83" s="292"/>
-      <c r="B83" s="299"/>
-      <c r="C83" s="303"/>
+      <c r="A83" s="286"/>
+      <c r="B83" s="289"/>
+      <c r="C83" s="297"/>
       <c r="D83" s="7"/>
       <c r="E83" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F83" s="273"/>
+      <c r="F83" s="267"/>
     </row>
     <row r="84" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A84" s="286"/>
-      <c r="B84" s="299"/>
-      <c r="C84" s="303"/>
+      <c r="A84" s="280"/>
+      <c r="B84" s="289"/>
+      <c r="C84" s="297"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F84" s="289">
+      <c r="F84" s="283">
         <f>SUM(E84:E90)</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A85" s="290"/>
-      <c r="B85" s="299"/>
-      <c r="C85" s="303"/>
+      <c r="A85" s="284"/>
+      <c r="B85" s="289"/>
+      <c r="C85" s="297"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F85" s="291"/>
+      <c r="F85" s="285"/>
     </row>
     <row r="86" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A86" s="290"/>
-      <c r="B86" s="299"/>
-      <c r="C86" s="303"/>
+      <c r="A86" s="284"/>
+      <c r="B86" s="289"/>
+      <c r="C86" s="297"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F86" s="291"/>
+      <c r="F86" s="285"/>
     </row>
     <row r="87" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A87" s="290"/>
-      <c r="B87" s="299"/>
-      <c r="C87" s="303"/>
+      <c r="A87" s="284"/>
+      <c r="B87" s="289"/>
+      <c r="C87" s="297"/>
       <c r="D87" s="7"/>
       <c r="E87" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F87" s="291"/>
+      <c r="F87" s="285"/>
     </row>
     <row r="88" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A88" s="290"/>
-      <c r="B88" s="299"/>
-      <c r="C88" s="303"/>
+      <c r="A88" s="284"/>
+      <c r="B88" s="289"/>
+      <c r="C88" s="297"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F88" s="291"/>
+      <c r="F88" s="285"/>
     </row>
     <row r="89" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A89" s="290"/>
-      <c r="B89" s="299"/>
-      <c r="C89" s="303"/>
+      <c r="A89" s="284"/>
+      <c r="B89" s="289"/>
+      <c r="C89" s="297"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F89" s="291"/>
+      <c r="F89" s="285"/>
     </row>
     <row r="90" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A90" s="292"/>
-      <c r="B90" s="299"/>
-      <c r="C90" s="303"/>
+      <c r="A90" s="286"/>
+      <c r="B90" s="289"/>
+      <c r="C90" s="297"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F90" s="273"/>
+      <c r="F90" s="267"/>
     </row>
     <row r="91" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A91" s="286"/>
-      <c r="B91" s="299"/>
-      <c r="C91" s="303"/>
+      <c r="A91" s="280"/>
+      <c r="B91" s="289"/>
+      <c r="C91" s="297"/>
       <c r="D91" s="7"/>
       <c r="E91" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F91" s="289">
+      <c r="F91" s="283">
         <f>SUM(E91:E105)</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A92" s="290"/>
-      <c r="B92" s="299"/>
-      <c r="C92" s="303"/>
+      <c r="A92" s="284"/>
+      <c r="B92" s="289"/>
+      <c r="C92" s="297"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F92" s="291"/>
+      <c r="F92" s="285"/>
     </row>
     <row r="93" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A93" s="290"/>
-      <c r="B93" s="299"/>
-      <c r="C93" s="303"/>
+      <c r="A93" s="284"/>
+      <c r="B93" s="289"/>
+      <c r="C93" s="297"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F93" s="291"/>
+      <c r="F93" s="285"/>
     </row>
     <row r="94" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A94" s="290"/>
-      <c r="B94" s="299"/>
-      <c r="C94" s="303"/>
+      <c r="A94" s="284"/>
+      <c r="B94" s="289"/>
+      <c r="C94" s="297"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F94" s="291"/>
+      <c r="F94" s="285"/>
     </row>
     <row r="95" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A95" s="290"/>
-      <c r="B95" s="299"/>
-      <c r="C95" s="303"/>
+      <c r="A95" s="284"/>
+      <c r="B95" s="289"/>
+      <c r="C95" s="297"/>
       <c r="D95" s="7"/>
       <c r="E95" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F95" s="291"/>
+      <c r="F95" s="285"/>
     </row>
     <row r="96" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A96" s="290"/>
-      <c r="B96" s="299"/>
-      <c r="C96" s="303"/>
+      <c r="A96" s="284"/>
+      <c r="B96" s="289"/>
+      <c r="C96" s="297"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F96" s="291"/>
+      <c r="F96" s="285"/>
     </row>
     <row r="97" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A97" s="290"/>
-      <c r="B97" s="299"/>
-      <c r="C97" s="303"/>
+      <c r="A97" s="284"/>
+      <c r="B97" s="289"/>
+      <c r="C97" s="297"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F97" s="291"/>
+      <c r="F97" s="285"/>
     </row>
     <row r="98" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A98" s="290"/>
-      <c r="B98" s="299"/>
-      <c r="C98" s="303"/>
+      <c r="A98" s="284"/>
+      <c r="B98" s="289"/>
+      <c r="C98" s="297"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F98" s="291"/>
+      <c r="F98" s="285"/>
     </row>
     <row r="99" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A99" s="290"/>
-      <c r="B99" s="299"/>
-      <c r="C99" s="303"/>
+      <c r="A99" s="284"/>
+      <c r="B99" s="289"/>
+      <c r="C99" s="297"/>
       <c r="D99" s="7"/>
       <c r="E99" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F99" s="291"/>
+      <c r="F99" s="285"/>
     </row>
     <row r="100" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A100" s="290"/>
-      <c r="B100" s="299"/>
-      <c r="C100" s="303"/>
+      <c r="A100" s="284"/>
+      <c r="B100" s="289"/>
+      <c r="C100" s="297"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F100" s="291"/>
+      <c r="F100" s="285"/>
     </row>
     <row r="101" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A101" s="290"/>
-      <c r="B101" s="299"/>
-      <c r="C101" s="303"/>
+      <c r="A101" s="284"/>
+      <c r="B101" s="289"/>
+      <c r="C101" s="297"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F101" s="291"/>
+      <c r="F101" s="285"/>
     </row>
     <row r="102" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A102" s="290"/>
-      <c r="B102" s="299"/>
-      <c r="C102" s="303"/>
+      <c r="A102" s="284"/>
+      <c r="B102" s="289"/>
+      <c r="C102" s="297"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F102" s="291"/>
+      <c r="F102" s="285"/>
     </row>
     <row r="103" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A103" s="290"/>
-      <c r="B103" s="299"/>
-      <c r="C103" s="303"/>
+      <c r="A103" s="284"/>
+      <c r="B103" s="289"/>
+      <c r="C103" s="297"/>
       <c r="D103" s="7"/>
       <c r="E103" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F103" s="291"/>
+      <c r="F103" s="285"/>
     </row>
     <row r="104" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A104" s="290"/>
-      <c r="B104" s="299"/>
-      <c r="C104" s="303"/>
+      <c r="A104" s="284"/>
+      <c r="B104" s="289"/>
+      <c r="C104" s="297"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F104" s="291"/>
+      <c r="F104" s="285"/>
     </row>
     <row r="105" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A105" s="292"/>
-      <c r="B105" s="299"/>
-      <c r="C105" s="303"/>
+      <c r="A105" s="286"/>
+      <c r="B105" s="289"/>
+      <c r="C105" s="297"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F105" s="273"/>
+      <c r="F105" s="267"/>
     </row>
     <row r="106" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A106" s="286"/>
-      <c r="B106" s="299"/>
-      <c r="C106" s="303"/>
+      <c r="A106" s="280"/>
+      <c r="B106" s="289"/>
+      <c r="C106" s="297"/>
       <c r="D106" s="7"/>
       <c r="E106" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F106" s="289">
+      <c r="F106" s="283">
         <f>SUM(E106:E121)</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A107" s="290"/>
-      <c r="B107" s="299"/>
-      <c r="C107" s="303"/>
+      <c r="A107" s="284"/>
+      <c r="B107" s="289"/>
+      <c r="C107" s="297"/>
       <c r="D107" s="7"/>
       <c r="E107" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F107" s="291"/>
+      <c r="F107" s="285"/>
     </row>
     <row r="108" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A108" s="290"/>
-      <c r="B108" s="299"/>
-      <c r="C108" s="303"/>
+      <c r="A108" s="284"/>
+      <c r="B108" s="289"/>
+      <c r="C108" s="297"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F108" s="291"/>
+      <c r="F108" s="285"/>
     </row>
     <row r="109" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A109" s="290"/>
-      <c r="B109" s="299"/>
-      <c r="C109" s="303"/>
+      <c r="A109" s="284"/>
+      <c r="B109" s="289"/>
+      <c r="C109" s="297"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F109" s="291"/>
+      <c r="F109" s="285"/>
     </row>
     <row r="110" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A110" s="290"/>
-      <c r="B110" s="299"/>
-      <c r="C110" s="303"/>
+      <c r="A110" s="284"/>
+      <c r="B110" s="289"/>
+      <c r="C110" s="297"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F110" s="291"/>
+      <c r="F110" s="285"/>
     </row>
     <row r="111" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A111" s="290"/>
-      <c r="B111" s="299"/>
-      <c r="C111" s="303"/>
+      <c r="A111" s="284"/>
+      <c r="B111" s="289"/>
+      <c r="C111" s="297"/>
       <c r="D111" s="7"/>
       <c r="E111" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F111" s="291"/>
+      <c r="F111" s="285"/>
     </row>
     <row r="112" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A112" s="290"/>
-      <c r="B112" s="299"/>
-      <c r="C112" s="303"/>
+      <c r="A112" s="284"/>
+      <c r="B112" s="289"/>
+      <c r="C112" s="297"/>
       <c r="D112" s="7"/>
       <c r="E112" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F112" s="291"/>
+      <c r="F112" s="285"/>
     </row>
     <row r="113" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A113" s="290"/>
-      <c r="B113" s="299"/>
-      <c r="C113" s="303"/>
+      <c r="A113" s="284"/>
+      <c r="B113" s="289"/>
+      <c r="C113" s="297"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F113" s="291"/>
+      <c r="F113" s="285"/>
     </row>
     <row r="114" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A114" s="290"/>
-      <c r="B114" s="299"/>
-      <c r="C114" s="303"/>
+      <c r="A114" s="284"/>
+      <c r="B114" s="289"/>
+      <c r="C114" s="297"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F114" s="291"/>
+      <c r="F114" s="285"/>
     </row>
     <row r="115" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A115" s="290"/>
-      <c r="B115" s="299"/>
-      <c r="C115" s="303"/>
+      <c r="A115" s="284"/>
+      <c r="B115" s="289"/>
+      <c r="C115" s="297"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F115" s="291"/>
+      <c r="F115" s="285"/>
     </row>
     <row r="116" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A116" s="290"/>
-      <c r="B116" s="299"/>
-      <c r="C116" s="303"/>
+      <c r="A116" s="284"/>
+      <c r="B116" s="289"/>
+      <c r="C116" s="297"/>
       <c r="D116" s="7"/>
       <c r="E116" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F116" s="291"/>
+      <c r="F116" s="285"/>
     </row>
     <row r="117" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A117" s="290"/>
-      <c r="B117" s="299"/>
-      <c r="C117" s="303"/>
+      <c r="A117" s="284"/>
+      <c r="B117" s="289"/>
+      <c r="C117" s="297"/>
       <c r="D117" s="7"/>
       <c r="E117" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F117" s="291"/>
+      <c r="F117" s="285"/>
     </row>
     <row r="118" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A118" s="290"/>
-      <c r="B118" s="299"/>
-      <c r="C118" s="303"/>
+      <c r="A118" s="284"/>
+      <c r="B118" s="289"/>
+      <c r="C118" s="297"/>
       <c r="D118" s="7"/>
       <c r="E118" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F118" s="291"/>
+      <c r="F118" s="285"/>
     </row>
     <row r="119" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A119" s="290"/>
-      <c r="B119" s="299"/>
-      <c r="C119" s="303"/>
+      <c r="A119" s="284"/>
+      <c r="B119" s="289"/>
+      <c r="C119" s="297"/>
       <c r="D119" s="7"/>
       <c r="E119" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F119" s="291"/>
+      <c r="F119" s="285"/>
     </row>
     <row r="120" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A120" s="290"/>
-      <c r="B120" s="299"/>
-      <c r="C120" s="303"/>
+      <c r="A120" s="284"/>
+      <c r="B120" s="289"/>
+      <c r="C120" s="297"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F120" s="291"/>
+      <c r="F120" s="285"/>
     </row>
     <row r="121" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A121" s="292"/>
-      <c r="B121" s="299"/>
-      <c r="C121" s="303"/>
+      <c r="A121" s="286"/>
+      <c r="B121" s="289"/>
+      <c r="C121" s="297"/>
       <c r="D121" s="7"/>
       <c r="E121" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F121" s="273"/>
+      <c r="F121" s="267"/>
     </row>
     <row r="122" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A122" s="304"/>
-      <c r="B122" s="299"/>
-      <c r="C122" s="303"/>
+      <c r="A122" s="298"/>
+      <c r="B122" s="289"/>
+      <c r="C122" s="297"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7">
         <f t="shared" si="2"/>
@@ -4467,9 +4521,9 @@
       </c>
     </row>
     <row r="123" s="244" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A123" s="304"/>
-      <c r="B123" s="299"/>
-      <c r="C123" s="303"/>
+      <c r="A123" s="298"/>
+      <c r="B123" s="289"/>
+      <c r="C123" s="297"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7">
         <f t="shared" si="2"/>
@@ -4479,12 +4533,12 @@
         <f>SUM(E123:E127)</f>
         <v>0</v>
       </c>
-      <c r="G123" s="274"/>
+      <c r="G123" s="268"/>
     </row>
     <row r="124" s="244" customFormat="1" spans="1:6">
-      <c r="A124" s="304"/>
-      <c r="B124" s="299"/>
-      <c r="C124" s="303"/>
+      <c r="A124" s="298"/>
+      <c r="B124" s="289"/>
+      <c r="C124" s="297"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7">
         <f t="shared" si="2"/>
@@ -4493,9 +4547,9 @@
       <c r="F124" s="7"/>
     </row>
     <row r="125" s="244" customFormat="1" spans="1:6">
-      <c r="A125" s="304"/>
-      <c r="B125" s="299"/>
-      <c r="C125" s="303"/>
+      <c r="A125" s="298"/>
+      <c r="B125" s="289"/>
+      <c r="C125" s="297"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7">
         <f t="shared" si="2"/>
@@ -4504,9 +4558,9 @@
       <c r="F125" s="7"/>
     </row>
     <row r="126" s="244" customFormat="1" spans="1:6">
-      <c r="A126" s="304"/>
-      <c r="B126" s="299"/>
-      <c r="C126" s="303"/>
+      <c r="A126" s="298"/>
+      <c r="B126" s="289"/>
+      <c r="C126" s="297"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7">
         <f t="shared" si="2"/>
@@ -4515,9 +4569,9 @@
       <c r="F126" s="7"/>
     </row>
     <row r="127" s="244" customFormat="1" spans="1:6">
-      <c r="A127" s="304"/>
-      <c r="B127" s="299"/>
-      <c r="C127" s="303"/>
+      <c r="A127" s="298"/>
+      <c r="B127" s="289"/>
+      <c r="C127" s="297"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7">
         <f t="shared" si="2"/>
@@ -4526,1536 +4580,1536 @@
       <c r="F127" s="7"/>
     </row>
     <row r="128" s="244" customFormat="1" spans="1:6">
-      <c r="A128" s="290"/>
-      <c r="B128" s="305"/>
-      <c r="C128" s="306"/>
-      <c r="D128" s="273"/>
+      <c r="A128" s="284"/>
+      <c r="B128" s="299"/>
+      <c r="C128" s="300"/>
+      <c r="D128" s="267"/>
       <c r="E128" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F128" s="289">
+      <c r="F128" s="283">
         <f>SUM(E128:E134)</f>
         <v>0</v>
       </c>
     </row>
     <row r="129" s="244" customFormat="1" spans="1:6">
-      <c r="A129" s="290"/>
-      <c r="B129" s="299"/>
-      <c r="C129" s="303"/>
+      <c r="A129" s="284"/>
+      <c r="B129" s="289"/>
+      <c r="C129" s="297"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F129" s="291"/>
+      <c r="F129" s="285"/>
     </row>
     <row r="130" s="244" customFormat="1" spans="1:6">
-      <c r="A130" s="290"/>
-      <c r="B130" s="299"/>
-      <c r="C130" s="303"/>
+      <c r="A130" s="284"/>
+      <c r="B130" s="289"/>
+      <c r="C130" s="297"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F130" s="291"/>
+      <c r="F130" s="285"/>
     </row>
     <row r="131" s="244" customFormat="1" spans="1:6">
-      <c r="A131" s="290"/>
-      <c r="B131" s="299"/>
-      <c r="C131" s="303"/>
+      <c r="A131" s="284"/>
+      <c r="B131" s="289"/>
+      <c r="C131" s="297"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F131" s="291"/>
+      <c r="F131" s="285"/>
     </row>
     <row r="132" s="244" customFormat="1" spans="1:6">
-      <c r="A132" s="290"/>
-      <c r="B132" s="299"/>
-      <c r="C132" s="303"/>
+      <c r="A132" s="284"/>
+      <c r="B132" s="289"/>
+      <c r="C132" s="297"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F132" s="291"/>
+      <c r="F132" s="285"/>
     </row>
     <row r="133" s="244" customFormat="1" spans="1:6">
-      <c r="A133" s="290"/>
-      <c r="B133" s="299"/>
-      <c r="C133" s="303"/>
+      <c r="A133" s="284"/>
+      <c r="B133" s="289"/>
+      <c r="C133" s="297"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7">
         <f t="shared" ref="E133:E196" si="3">SUM(C133*D133)</f>
         <v>0</v>
       </c>
-      <c r="F133" s="291"/>
+      <c r="F133" s="285"/>
     </row>
     <row r="134" s="244" customFormat="1" spans="1:6">
-      <c r="A134" s="292"/>
-      <c r="B134" s="299"/>
-      <c r="C134" s="303"/>
+      <c r="A134" s="286"/>
+      <c r="B134" s="289"/>
+      <c r="C134" s="297"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F134" s="273"/>
+      <c r="F134" s="267"/>
     </row>
     <row r="135" s="244" customFormat="1" spans="1:6">
-      <c r="A135" s="286"/>
-      <c r="B135" s="299"/>
-      <c r="C135" s="303"/>
+      <c r="A135" s="280"/>
+      <c r="B135" s="289"/>
+      <c r="C135" s="297"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F135" s="289">
+      <c r="F135" s="283">
         <f>SUM(E135:E142)</f>
         <v>0</v>
       </c>
     </row>
     <row r="136" s="244" customFormat="1" spans="1:6">
-      <c r="A136" s="290"/>
-      <c r="B136" s="299"/>
-      <c r="C136" s="303"/>
+      <c r="A136" s="284"/>
+      <c r="B136" s="289"/>
+      <c r="C136" s="297"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F136" s="291"/>
+      <c r="F136" s="285"/>
     </row>
     <row r="137" s="244" customFormat="1" spans="1:6">
-      <c r="A137" s="290"/>
-      <c r="B137" s="299"/>
-      <c r="C137" s="303"/>
+      <c r="A137" s="284"/>
+      <c r="B137" s="289"/>
+      <c r="C137" s="297"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F137" s="291"/>
+      <c r="F137" s="285"/>
     </row>
     <row r="138" s="244" customFormat="1" spans="1:6">
-      <c r="A138" s="290"/>
-      <c r="B138" s="299"/>
-      <c r="C138" s="303"/>
+      <c r="A138" s="284"/>
+      <c r="B138" s="289"/>
+      <c r="C138" s="297"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F138" s="291"/>
+      <c r="F138" s="285"/>
     </row>
     <row r="139" s="244" customFormat="1" spans="1:6">
-      <c r="A139" s="290"/>
-      <c r="B139" s="299"/>
-      <c r="C139" s="303"/>
+      <c r="A139" s="284"/>
+      <c r="B139" s="289"/>
+      <c r="C139" s="297"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F139" s="291"/>
+      <c r="F139" s="285"/>
     </row>
     <row r="140" s="244" customFormat="1" spans="1:6">
-      <c r="A140" s="290"/>
-      <c r="B140" s="299"/>
-      <c r="C140" s="303"/>
+      <c r="A140" s="284"/>
+      <c r="B140" s="289"/>
+      <c r="C140" s="297"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F140" s="291"/>
+      <c r="F140" s="285"/>
     </row>
     <row r="141" s="244" customFormat="1" spans="1:6">
-      <c r="A141" s="290"/>
-      <c r="B141" s="299"/>
-      <c r="C141" s="303"/>
+      <c r="A141" s="284"/>
+      <c r="B141" s="289"/>
+      <c r="C141" s="297"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F141" s="291"/>
+      <c r="F141" s="285"/>
     </row>
     <row r="142" s="244" customFormat="1" spans="1:6">
-      <c r="A142" s="292"/>
-      <c r="B142" s="299"/>
-      <c r="C142" s="303"/>
+      <c r="A142" s="286"/>
+      <c r="B142" s="289"/>
+      <c r="C142" s="297"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F142" s="273"/>
+      <c r="F142" s="267"/>
     </row>
     <row r="143" s="244" customFormat="1" spans="1:6">
-      <c r="A143" s="286"/>
-      <c r="B143" s="299"/>
-      <c r="C143" s="303"/>
+      <c r="A143" s="280"/>
+      <c r="B143" s="289"/>
+      <c r="C143" s="297"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F143" s="289">
+      <c r="F143" s="283">
         <f>SUM(E143:E149)</f>
         <v>0</v>
       </c>
     </row>
     <row r="144" s="244" customFormat="1" spans="1:6">
-      <c r="A144" s="290"/>
-      <c r="B144" s="299"/>
-      <c r="C144" s="303"/>
+      <c r="A144" s="284"/>
+      <c r="B144" s="289"/>
+      <c r="C144" s="297"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F144" s="291"/>
+      <c r="F144" s="285"/>
     </row>
     <row r="145" s="244" customFormat="1" spans="1:6">
-      <c r="A145" s="290"/>
-      <c r="B145" s="299"/>
-      <c r="C145" s="303"/>
+      <c r="A145" s="284"/>
+      <c r="B145" s="289"/>
+      <c r="C145" s="297"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F145" s="291"/>
+      <c r="F145" s="285"/>
     </row>
     <row r="146" s="244" customFormat="1" spans="1:6">
-      <c r="A146" s="290"/>
-      <c r="B146" s="299"/>
-      <c r="C146" s="303"/>
+      <c r="A146" s="284"/>
+      <c r="B146" s="289"/>
+      <c r="C146" s="297"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F146" s="291"/>
+      <c r="F146" s="285"/>
     </row>
     <row r="147" s="244" customFormat="1" spans="1:6">
-      <c r="A147" s="290"/>
-      <c r="B147" s="299"/>
-      <c r="C147" s="303"/>
+      <c r="A147" s="284"/>
+      <c r="B147" s="289"/>
+      <c r="C147" s="297"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F147" s="291"/>
+      <c r="F147" s="285"/>
     </row>
     <row r="148" s="244" customFormat="1" spans="1:6">
-      <c r="A148" s="290"/>
-      <c r="B148" s="299"/>
-      <c r="C148" s="303"/>
+      <c r="A148" s="284"/>
+      <c r="B148" s="289"/>
+      <c r="C148" s="297"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F148" s="291"/>
+      <c r="F148" s="285"/>
     </row>
     <row r="149" s="244" customFormat="1" spans="1:6">
-      <c r="A149" s="292"/>
-      <c r="B149" s="299"/>
-      <c r="C149" s="303"/>
+      <c r="A149" s="286"/>
+      <c r="B149" s="289"/>
+      <c r="C149" s="297"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F149" s="273"/>
+      <c r="F149" s="267"/>
     </row>
     <row r="150" s="244" customFormat="1" spans="1:6">
-      <c r="A150" s="286"/>
-      <c r="B150" s="299"/>
-      <c r="C150" s="303"/>
+      <c r="A150" s="280"/>
+      <c r="B150" s="289"/>
+      <c r="C150" s="297"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F150" s="289">
+      <c r="F150" s="283">
         <f>SUM(E150:E159)</f>
         <v>0</v>
       </c>
     </row>
     <row r="151" s="244" customFormat="1" spans="1:6">
-      <c r="A151" s="290"/>
-      <c r="B151" s="299"/>
-      <c r="C151" s="303"/>
+      <c r="A151" s="284"/>
+      <c r="B151" s="289"/>
+      <c r="C151" s="297"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F151" s="291"/>
+      <c r="F151" s="285"/>
     </row>
     <row r="152" s="244" customFormat="1" spans="1:6">
-      <c r="A152" s="290"/>
-      <c r="B152" s="299"/>
-      <c r="C152" s="303"/>
+      <c r="A152" s="284"/>
+      <c r="B152" s="289"/>
+      <c r="C152" s="297"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F152" s="291"/>
+      <c r="F152" s="285"/>
     </row>
     <row r="153" s="244" customFormat="1" spans="1:6">
-      <c r="A153" s="290"/>
-      <c r="B153" s="299"/>
-      <c r="C153" s="303"/>
+      <c r="A153" s="284"/>
+      <c r="B153" s="289"/>
+      <c r="C153" s="297"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F153" s="291"/>
+      <c r="F153" s="285"/>
     </row>
     <row r="154" s="244" customFormat="1" spans="1:6">
-      <c r="A154" s="290"/>
-      <c r="B154" s="299"/>
-      <c r="C154" s="303"/>
+      <c r="A154" s="284"/>
+      <c r="B154" s="289"/>
+      <c r="C154" s="297"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F154" s="291"/>
+      <c r="F154" s="285"/>
     </row>
     <row r="155" s="244" customFormat="1" spans="1:6">
-      <c r="A155" s="290"/>
-      <c r="B155" s="299"/>
-      <c r="C155" s="303"/>
+      <c r="A155" s="284"/>
+      <c r="B155" s="289"/>
+      <c r="C155" s="297"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F155" s="291"/>
+      <c r="F155" s="285"/>
     </row>
     <row r="156" s="244" customFormat="1" spans="1:6">
-      <c r="A156" s="290"/>
-      <c r="B156" s="299"/>
-      <c r="C156" s="303"/>
+      <c r="A156" s="284"/>
+      <c r="B156" s="289"/>
+      <c r="C156" s="297"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F156" s="291"/>
+      <c r="F156" s="285"/>
     </row>
     <row r="157" s="244" customFormat="1" spans="1:6">
-      <c r="A157" s="290"/>
-      <c r="B157" s="299"/>
-      <c r="C157" s="303"/>
+      <c r="A157" s="284"/>
+      <c r="B157" s="289"/>
+      <c r="C157" s="297"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F157" s="291"/>
+      <c r="F157" s="285"/>
     </row>
     <row r="158" s="244" customFormat="1" spans="1:6">
-      <c r="A158" s="290"/>
-      <c r="B158" s="299"/>
-      <c r="C158" s="303"/>
+      <c r="A158" s="284"/>
+      <c r="B158" s="289"/>
+      <c r="C158" s="297"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F158" s="291"/>
+      <c r="F158" s="285"/>
     </row>
     <row r="159" s="244" customFormat="1" spans="1:6">
-      <c r="A159" s="292"/>
-      <c r="B159" s="299"/>
-      <c r="C159" s="303"/>
+      <c r="A159" s="286"/>
+      <c r="B159" s="289"/>
+      <c r="C159" s="297"/>
       <c r="D159" s="7"/>
       <c r="E159" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F159" s="273"/>
+      <c r="F159" s="267"/>
     </row>
     <row r="160" s="244" customFormat="1" spans="1:6">
-      <c r="A160" s="286"/>
-      <c r="B160" s="299"/>
-      <c r="C160" s="303"/>
+      <c r="A160" s="280"/>
+      <c r="B160" s="289"/>
+      <c r="C160" s="297"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F160" s="289">
+      <c r="F160" s="283">
         <f>SUM(E160:E173)</f>
         <v>0</v>
       </c>
     </row>
     <row r="161" s="244" customFormat="1" spans="1:6">
-      <c r="A161" s="290"/>
-      <c r="B161" s="299"/>
-      <c r="C161" s="303"/>
+      <c r="A161" s="284"/>
+      <c r="B161" s="289"/>
+      <c r="C161" s="297"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F161" s="291"/>
+      <c r="F161" s="285"/>
     </row>
     <row r="162" s="244" customFormat="1" spans="1:6">
-      <c r="A162" s="290"/>
-      <c r="B162" s="299"/>
-      <c r="C162" s="303"/>
+      <c r="A162" s="284"/>
+      <c r="B162" s="289"/>
+      <c r="C162" s="297"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F162" s="291"/>
+      <c r="F162" s="285"/>
     </row>
     <row r="163" s="244" customFormat="1" spans="1:6">
-      <c r="A163" s="290"/>
-      <c r="B163" s="299"/>
-      <c r="C163" s="303"/>
+      <c r="A163" s="284"/>
+      <c r="B163" s="289"/>
+      <c r="C163" s="297"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F163" s="291"/>
+      <c r="F163" s="285"/>
     </row>
     <row r="164" s="244" customFormat="1" spans="1:6">
-      <c r="A164" s="290"/>
-      <c r="B164" s="299"/>
-      <c r="C164" s="303"/>
+      <c r="A164" s="284"/>
+      <c r="B164" s="289"/>
+      <c r="C164" s="297"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F164" s="291"/>
+      <c r="F164" s="285"/>
     </row>
     <row r="165" s="244" customFormat="1" spans="1:6">
-      <c r="A165" s="290"/>
-      <c r="B165" s="299"/>
-      <c r="C165" s="303"/>
+      <c r="A165" s="284"/>
+      <c r="B165" s="289"/>
+      <c r="C165" s="297"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F165" s="291"/>
+      <c r="F165" s="285"/>
     </row>
     <row r="166" s="244" customFormat="1" spans="1:6">
-      <c r="A166" s="290"/>
-      <c r="B166" s="299"/>
-      <c r="C166" s="303"/>
+      <c r="A166" s="284"/>
+      <c r="B166" s="289"/>
+      <c r="C166" s="297"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F166" s="291"/>
+      <c r="F166" s="285"/>
     </row>
     <row r="167" s="244" customFormat="1" spans="1:6">
-      <c r="A167" s="290"/>
-      <c r="B167" s="299"/>
-      <c r="C167" s="303"/>
+      <c r="A167" s="284"/>
+      <c r="B167" s="289"/>
+      <c r="C167" s="297"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F167" s="291"/>
+      <c r="F167" s="285"/>
     </row>
     <row r="168" s="244" customFormat="1" spans="1:6">
-      <c r="A168" s="290"/>
-      <c r="B168" s="299"/>
-      <c r="C168" s="303"/>
+      <c r="A168" s="284"/>
+      <c r="B168" s="289"/>
+      <c r="C168" s="297"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F168" s="291"/>
+      <c r="F168" s="285"/>
     </row>
     <row r="169" s="244" customFormat="1" spans="1:6">
-      <c r="A169" s="290"/>
-      <c r="B169" s="299"/>
-      <c r="C169" s="303"/>
+      <c r="A169" s="284"/>
+      <c r="B169" s="289"/>
+      <c r="C169" s="297"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F169" s="291"/>
+      <c r="F169" s="285"/>
     </row>
     <row r="170" s="244" customFormat="1" spans="1:6">
-      <c r="A170" s="290"/>
-      <c r="B170" s="299"/>
-      <c r="C170" s="303"/>
+      <c r="A170" s="284"/>
+      <c r="B170" s="289"/>
+      <c r="C170" s="297"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F170" s="291"/>
+      <c r="F170" s="285"/>
     </row>
     <row r="171" s="244" customFormat="1" spans="1:6">
-      <c r="A171" s="290"/>
-      <c r="B171" s="299"/>
-      <c r="C171" s="303"/>
+      <c r="A171" s="284"/>
+      <c r="B171" s="289"/>
+      <c r="C171" s="297"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F171" s="291"/>
+      <c r="F171" s="285"/>
     </row>
     <row r="172" s="244" customFormat="1" spans="1:6">
-      <c r="A172" s="290"/>
-      <c r="B172" s="299"/>
-      <c r="C172" s="303"/>
+      <c r="A172" s="284"/>
+      <c r="B172" s="289"/>
+      <c r="C172" s="297"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F172" s="291"/>
+      <c r="F172" s="285"/>
     </row>
     <row r="173" s="244" customFormat="1" spans="1:6">
-      <c r="A173" s="292"/>
-      <c r="B173" s="299"/>
-      <c r="C173" s="303"/>
+      <c r="A173" s="286"/>
+      <c r="B173" s="289"/>
+      <c r="C173" s="297"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F173" s="273"/>
+      <c r="F173" s="267"/>
     </row>
     <row r="174" s="244" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A174" s="290"/>
-      <c r="B174" s="299"/>
-      <c r="C174" s="303"/>
+      <c r="A174" s="284"/>
+      <c r="B174" s="289"/>
+      <c r="C174" s="297"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F174" s="291">
+      <c r="F174" s="285">
         <f>SUM(E174)</f>
         <v>0</v>
       </c>
     </row>
     <row r="175" s="244" customFormat="1" spans="1:6">
-      <c r="A175" s="286"/>
-      <c r="B175" s="299"/>
-      <c r="C175" s="303"/>
+      <c r="A175" s="280"/>
+      <c r="B175" s="289"/>
+      <c r="C175" s="297"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F175" s="289">
+      <c r="F175" s="283">
         <f>SUM(E175:E190)</f>
         <v>0</v>
       </c>
     </row>
     <row r="176" s="244" customFormat="1" spans="1:6">
-      <c r="A176" s="290"/>
-      <c r="B176" s="299"/>
-      <c r="C176" s="303"/>
+      <c r="A176" s="284"/>
+      <c r="B176" s="289"/>
+      <c r="C176" s="297"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F176" s="291"/>
+      <c r="F176" s="285"/>
     </row>
     <row r="177" s="244" customFormat="1" spans="1:6">
-      <c r="A177" s="290"/>
-      <c r="B177" s="299"/>
-      <c r="C177" s="303"/>
+      <c r="A177" s="284"/>
+      <c r="B177" s="289"/>
+      <c r="C177" s="297"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F177" s="291"/>
+      <c r="F177" s="285"/>
     </row>
     <row r="178" s="244" customFormat="1" spans="1:6">
-      <c r="A178" s="290"/>
-      <c r="B178" s="299"/>
-      <c r="C178" s="303"/>
+      <c r="A178" s="284"/>
+      <c r="B178" s="289"/>
+      <c r="C178" s="297"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F178" s="291"/>
+      <c r="F178" s="285"/>
     </row>
     <row r="179" s="244" customFormat="1" spans="1:6">
-      <c r="A179" s="290"/>
-      <c r="B179" s="299"/>
-      <c r="C179" s="303"/>
+      <c r="A179" s="284"/>
+      <c r="B179" s="289"/>
+      <c r="C179" s="297"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F179" s="291"/>
+      <c r="F179" s="285"/>
     </row>
     <row r="180" s="244" customFormat="1" spans="1:6">
-      <c r="A180" s="290"/>
-      <c r="B180" s="299"/>
-      <c r="C180" s="303"/>
+      <c r="A180" s="284"/>
+      <c r="B180" s="289"/>
+      <c r="C180" s="297"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F180" s="291"/>
+      <c r="F180" s="285"/>
     </row>
     <row r="181" s="244" customFormat="1" spans="1:6">
-      <c r="A181" s="290"/>
-      <c r="B181" s="299"/>
-      <c r="C181" s="303"/>
+      <c r="A181" s="284"/>
+      <c r="B181" s="289"/>
+      <c r="C181" s="297"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F181" s="291"/>
+      <c r="F181" s="285"/>
     </row>
     <row r="182" s="244" customFormat="1" spans="1:6">
-      <c r="A182" s="290"/>
-      <c r="B182" s="299"/>
-      <c r="C182" s="303"/>
+      <c r="A182" s="284"/>
+      <c r="B182" s="289"/>
+      <c r="C182" s="297"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F182" s="291"/>
+      <c r="F182" s="285"/>
     </row>
     <row r="183" s="244" customFormat="1" spans="1:6">
-      <c r="A183" s="290"/>
-      <c r="B183" s="299"/>
-      <c r="C183" s="303"/>
+      <c r="A183" s="284"/>
+      <c r="B183" s="289"/>
+      <c r="C183" s="297"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F183" s="291"/>
+      <c r="F183" s="285"/>
     </row>
     <row r="184" s="244" customFormat="1" spans="1:6">
-      <c r="A184" s="290"/>
-      <c r="B184" s="299"/>
-      <c r="C184" s="303"/>
+      <c r="A184" s="284"/>
+      <c r="B184" s="289"/>
+      <c r="C184" s="297"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F184" s="291"/>
+      <c r="F184" s="285"/>
     </row>
     <row r="185" s="244" customFormat="1" spans="1:6">
-      <c r="A185" s="290"/>
-      <c r="B185" s="299"/>
-      <c r="C185" s="303"/>
+      <c r="A185" s="284"/>
+      <c r="B185" s="289"/>
+      <c r="C185" s="297"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F185" s="291"/>
+      <c r="F185" s="285"/>
     </row>
     <row r="186" s="244" customFormat="1" spans="1:6">
-      <c r="A186" s="290"/>
-      <c r="B186" s="299"/>
-      <c r="C186" s="303"/>
+      <c r="A186" s="284"/>
+      <c r="B186" s="289"/>
+      <c r="C186" s="297"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F186" s="291"/>
+      <c r="F186" s="285"/>
     </row>
     <row r="187" s="244" customFormat="1" spans="1:6">
-      <c r="A187" s="290"/>
-      <c r="B187" s="299"/>
-      <c r="C187" s="303"/>
+      <c r="A187" s="284"/>
+      <c r="B187" s="289"/>
+      <c r="C187" s="297"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F187" s="291"/>
+      <c r="F187" s="285"/>
     </row>
     <row r="188" s="244" customFormat="1" spans="1:6">
-      <c r="A188" s="290"/>
-      <c r="B188" s="299"/>
-      <c r="C188" s="303"/>
+      <c r="A188" s="284"/>
+      <c r="B188" s="289"/>
+      <c r="C188" s="297"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F188" s="291"/>
+      <c r="F188" s="285"/>
     </row>
     <row r="189" s="244" customFormat="1" spans="1:6">
-      <c r="A189" s="290"/>
-      <c r="B189" s="305"/>
-      <c r="C189" s="306"/>
-      <c r="D189" s="273"/>
+      <c r="A189" s="284"/>
+      <c r="B189" s="299"/>
+      <c r="C189" s="300"/>
+      <c r="D189" s="267"/>
       <c r="E189" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F189" s="291"/>
+      <c r="F189" s="285"/>
     </row>
     <row r="190" s="244" customFormat="1" spans="1:6">
-      <c r="A190" s="290"/>
-      <c r="B190" s="299"/>
-      <c r="C190" s="303"/>
+      <c r="A190" s="284"/>
+      <c r="B190" s="289"/>
+      <c r="C190" s="297"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F190" s="273"/>
+      <c r="F190" s="267"/>
     </row>
     <row r="191" s="244" customFormat="1" spans="1:6">
-      <c r="A191" s="286"/>
-      <c r="B191" s="299"/>
-      <c r="C191" s="303"/>
+      <c r="A191" s="280"/>
+      <c r="B191" s="289"/>
+      <c r="C191" s="297"/>
       <c r="D191" s="7"/>
       <c r="E191" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F191" s="289">
+      <c r="F191" s="283">
         <f>SUM(E191:E198)</f>
         <v>0</v>
       </c>
     </row>
     <row r="192" s="244" customFormat="1" spans="1:6">
-      <c r="A192" s="290"/>
-      <c r="B192" s="299"/>
-      <c r="C192" s="303"/>
+      <c r="A192" s="284"/>
+      <c r="B192" s="289"/>
+      <c r="C192" s="297"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F192" s="291"/>
+      <c r="F192" s="285"/>
     </row>
     <row r="193" s="244" customFormat="1" spans="1:6">
-      <c r="A193" s="290"/>
-      <c r="B193" s="299"/>
-      <c r="C193" s="303"/>
+      <c r="A193" s="284"/>
+      <c r="B193" s="289"/>
+      <c r="C193" s="297"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F193" s="291"/>
+      <c r="F193" s="285"/>
     </row>
     <row r="194" s="244" customFormat="1" spans="1:6">
-      <c r="A194" s="290"/>
-      <c r="B194" s="299"/>
-      <c r="C194" s="303"/>
+      <c r="A194" s="284"/>
+      <c r="B194" s="289"/>
+      <c r="C194" s="297"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F194" s="291"/>
+      <c r="F194" s="285"/>
     </row>
     <row r="195" s="244" customFormat="1" spans="1:6">
-      <c r="A195" s="290"/>
-      <c r="B195" s="299"/>
-      <c r="C195" s="303"/>
+      <c r="A195" s="284"/>
+      <c r="B195" s="289"/>
+      <c r="C195" s="297"/>
       <c r="D195" s="7"/>
       <c r="E195" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F195" s="291"/>
+      <c r="F195" s="285"/>
     </row>
     <row r="196" s="244" customFormat="1" spans="1:6">
-      <c r="A196" s="290"/>
-      <c r="B196" s="299"/>
-      <c r="C196" s="303"/>
+      <c r="A196" s="284"/>
+      <c r="B196" s="289"/>
+      <c r="C196" s="297"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F196" s="291"/>
+      <c r="F196" s="285"/>
     </row>
     <row r="197" s="244" customFormat="1" spans="1:6">
-      <c r="A197" s="290"/>
-      <c r="B197" s="299"/>
-      <c r="C197" s="303"/>
+      <c r="A197" s="284"/>
+      <c r="B197" s="289"/>
+      <c r="C197" s="297"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7">
         <f t="shared" ref="E197:E260" si="4">SUM(C197*D197)</f>
         <v>0</v>
       </c>
-      <c r="F197" s="291"/>
+      <c r="F197" s="285"/>
     </row>
     <row r="198" s="244" customFormat="1" spans="1:6">
-      <c r="A198" s="292"/>
-      <c r="B198" s="299"/>
-      <c r="C198" s="303"/>
+      <c r="A198" s="286"/>
+      <c r="B198" s="289"/>
+      <c r="C198" s="297"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F198" s="273"/>
+      <c r="F198" s="267"/>
     </row>
     <row r="199" s="244" customFormat="1" spans="1:6">
-      <c r="A199" s="286"/>
-      <c r="B199" s="299"/>
-      <c r="C199" s="303"/>
+      <c r="A199" s="280"/>
+      <c r="B199" s="289"/>
+      <c r="C199" s="297"/>
       <c r="D199" s="7"/>
       <c r="E199" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F199" s="289">
+      <c r="F199" s="283">
         <f>SUM(E199:E210)</f>
         <v>0</v>
       </c>
     </row>
     <row r="200" s="244" customFormat="1" spans="1:6">
-      <c r="A200" s="290"/>
-      <c r="B200" s="299"/>
-      <c r="C200" s="303"/>
+      <c r="A200" s="284"/>
+      <c r="B200" s="289"/>
+      <c r="C200" s="297"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F200" s="291"/>
+      <c r="F200" s="285"/>
     </row>
     <row r="201" s="244" customFormat="1" spans="1:6">
-      <c r="A201" s="290"/>
-      <c r="B201" s="299"/>
-      <c r="C201" s="303"/>
+      <c r="A201" s="284"/>
+      <c r="B201" s="289"/>
+      <c r="C201" s="297"/>
       <c r="D201" s="7"/>
       <c r="E201" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F201" s="291"/>
+      <c r="F201" s="285"/>
     </row>
     <row r="202" s="244" customFormat="1" spans="1:6">
-      <c r="A202" s="290"/>
-      <c r="B202" s="299"/>
-      <c r="C202" s="303"/>
+      <c r="A202" s="284"/>
+      <c r="B202" s="289"/>
+      <c r="C202" s="297"/>
       <c r="D202" s="7"/>
       <c r="E202" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F202" s="291"/>
+      <c r="F202" s="285"/>
     </row>
     <row r="203" s="244" customFormat="1" spans="1:6">
-      <c r="A203" s="290"/>
-      <c r="B203" s="299"/>
-      <c r="C203" s="303"/>
+      <c r="A203" s="284"/>
+      <c r="B203" s="289"/>
+      <c r="C203" s="297"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F203" s="291"/>
+      <c r="F203" s="285"/>
     </row>
     <row r="204" s="244" customFormat="1" spans="1:6">
-      <c r="A204" s="290"/>
-      <c r="B204" s="299"/>
-      <c r="C204" s="303"/>
+      <c r="A204" s="284"/>
+      <c r="B204" s="289"/>
+      <c r="C204" s="297"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F204" s="291"/>
+      <c r="F204" s="285"/>
     </row>
     <row r="205" s="244" customFormat="1" spans="1:6">
-      <c r="A205" s="290"/>
-      <c r="B205" s="299"/>
-      <c r="C205" s="303"/>
+      <c r="A205" s="284"/>
+      <c r="B205" s="289"/>
+      <c r="C205" s="297"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F205" s="291"/>
+      <c r="F205" s="285"/>
     </row>
     <row r="206" s="244" customFormat="1" spans="1:6">
-      <c r="A206" s="290"/>
-      <c r="B206" s="299"/>
-      <c r="C206" s="303"/>
+      <c r="A206" s="284"/>
+      <c r="B206" s="289"/>
+      <c r="C206" s="297"/>
       <c r="D206" s="7"/>
       <c r="E206" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F206" s="291"/>
+      <c r="F206" s="285"/>
     </row>
     <row r="207" s="244" customFormat="1" spans="1:6">
-      <c r="A207" s="290"/>
-      <c r="B207" s="299"/>
-      <c r="C207" s="303"/>
+      <c r="A207" s="284"/>
+      <c r="B207" s="289"/>
+      <c r="C207" s="297"/>
       <c r="D207" s="7"/>
       <c r="E207" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F207" s="291"/>
+      <c r="F207" s="285"/>
     </row>
     <row r="208" s="244" customFormat="1" spans="1:6">
-      <c r="A208" s="290"/>
-      <c r="B208" s="299"/>
-      <c r="C208" s="303"/>
+      <c r="A208" s="284"/>
+      <c r="B208" s="289"/>
+      <c r="C208" s="297"/>
       <c r="D208" s="7"/>
       <c r="E208" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F208" s="291"/>
+      <c r="F208" s="285"/>
     </row>
     <row r="209" s="244" customFormat="1" spans="1:6">
-      <c r="A209" s="290"/>
-      <c r="B209" s="299"/>
-      <c r="C209" s="303"/>
+      <c r="A209" s="284"/>
+      <c r="B209" s="289"/>
+      <c r="C209" s="297"/>
       <c r="D209" s="7"/>
       <c r="E209" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F209" s="291"/>
+      <c r="F209" s="285"/>
     </row>
     <row r="210" s="244" customFormat="1" spans="1:6">
-      <c r="A210" s="292"/>
-      <c r="B210" s="299"/>
-      <c r="C210" s="303"/>
+      <c r="A210" s="286"/>
+      <c r="B210" s="289"/>
+      <c r="C210" s="297"/>
       <c r="D210" s="7"/>
       <c r="E210" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F210" s="273"/>
+      <c r="F210" s="267"/>
     </row>
     <row r="211" s="244" customFormat="1" spans="1:6">
-      <c r="A211" s="286"/>
-      <c r="B211" s="299"/>
-      <c r="C211" s="303"/>
+      <c r="A211" s="280"/>
+      <c r="B211" s="289"/>
+      <c r="C211" s="297"/>
       <c r="D211" s="7"/>
       <c r="E211" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F211" s="289">
+      <c r="F211" s="283">
         <f>SUM(E211:E219)</f>
         <v>0</v>
       </c>
     </row>
     <row r="212" s="244" customFormat="1" spans="1:6">
-      <c r="A212" s="290"/>
-      <c r="B212" s="299"/>
-      <c r="C212" s="303"/>
+      <c r="A212" s="284"/>
+      <c r="B212" s="289"/>
+      <c r="C212" s="297"/>
       <c r="D212" s="7"/>
       <c r="E212" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F212" s="291"/>
+      <c r="F212" s="285"/>
     </row>
     <row r="213" s="244" customFormat="1" spans="1:6">
-      <c r="A213" s="290"/>
-      <c r="B213" s="299"/>
-      <c r="C213" s="303"/>
+      <c r="A213" s="284"/>
+      <c r="B213" s="289"/>
+      <c r="C213" s="297"/>
       <c r="D213" s="7"/>
       <c r="E213" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F213" s="291"/>
+      <c r="F213" s="285"/>
     </row>
     <row r="214" s="244" customFormat="1" spans="1:6">
-      <c r="A214" s="290"/>
-      <c r="B214" s="299"/>
-      <c r="C214" s="303"/>
+      <c r="A214" s="284"/>
+      <c r="B214" s="289"/>
+      <c r="C214" s="297"/>
       <c r="D214" s="7"/>
       <c r="E214" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F214" s="291"/>
+      <c r="F214" s="285"/>
     </row>
     <row r="215" s="244" customFormat="1" spans="1:6">
-      <c r="A215" s="290"/>
-      <c r="B215" s="299"/>
-      <c r="C215" s="303"/>
+      <c r="A215" s="284"/>
+      <c r="B215" s="289"/>
+      <c r="C215" s="297"/>
       <c r="D215" s="7"/>
       <c r="E215" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F215" s="291"/>
+      <c r="F215" s="285"/>
     </row>
     <row r="216" s="244" customFormat="1" spans="1:6">
-      <c r="A216" s="290"/>
-      <c r="B216" s="299"/>
-      <c r="C216" s="303"/>
+      <c r="A216" s="284"/>
+      <c r="B216" s="289"/>
+      <c r="C216" s="297"/>
       <c r="D216" s="7"/>
       <c r="E216" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F216" s="291"/>
+      <c r="F216" s="285"/>
     </row>
     <row r="217" s="244" customFormat="1" spans="1:6">
-      <c r="A217" s="290"/>
-      <c r="B217" s="299"/>
-      <c r="C217" s="303"/>
+      <c r="A217" s="284"/>
+      <c r="B217" s="289"/>
+      <c r="C217" s="297"/>
       <c r="D217" s="7"/>
       <c r="E217" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F217" s="291"/>
+      <c r="F217" s="285"/>
     </row>
     <row r="218" s="244" customFormat="1" spans="1:6">
-      <c r="A218" s="290"/>
-      <c r="B218" s="299"/>
-      <c r="C218" s="303"/>
+      <c r="A218" s="284"/>
+      <c r="B218" s="289"/>
+      <c r="C218" s="297"/>
       <c r="D218" s="7"/>
       <c r="E218" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F218" s="291"/>
+      <c r="F218" s="285"/>
     </row>
     <row r="219" s="244" customFormat="1" spans="1:6">
-      <c r="A219" s="292"/>
-      <c r="B219" s="299"/>
-      <c r="C219" s="303"/>
+      <c r="A219" s="286"/>
+      <c r="B219" s="289"/>
+      <c r="C219" s="297"/>
       <c r="D219" s="7"/>
       <c r="E219" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F219" s="273"/>
+      <c r="F219" s="267"/>
     </row>
     <row r="220" s="244" customFormat="1" spans="1:6">
-      <c r="A220" s="286"/>
-      <c r="B220" s="299"/>
-      <c r="C220" s="303"/>
+      <c r="A220" s="280"/>
+      <c r="B220" s="289"/>
+      <c r="C220" s="297"/>
       <c r="D220" s="7"/>
       <c r="E220" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F220" s="289">
+      <c r="F220" s="283">
         <f>SUM(E220:E230)</f>
         <v>0</v>
       </c>
     </row>
     <row r="221" s="244" customFormat="1" spans="1:6">
-      <c r="A221" s="290"/>
-      <c r="B221" s="299"/>
-      <c r="C221" s="303"/>
+      <c r="A221" s="284"/>
+      <c r="B221" s="289"/>
+      <c r="C221" s="297"/>
       <c r="D221" s="7"/>
       <c r="E221" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F221" s="291"/>
+      <c r="F221" s="285"/>
     </row>
     <row r="222" s="244" customFormat="1" spans="1:6">
-      <c r="A222" s="290"/>
-      <c r="B222" s="299"/>
-      <c r="C222" s="303"/>
+      <c r="A222" s="284"/>
+      <c r="B222" s="289"/>
+      <c r="C222" s="297"/>
       <c r="D222" s="7"/>
       <c r="E222" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F222" s="291"/>
+      <c r="F222" s="285"/>
     </row>
     <row r="223" s="244" customFormat="1" spans="1:6">
-      <c r="A223" s="290"/>
-      <c r="B223" s="299"/>
-      <c r="C223" s="303"/>
+      <c r="A223" s="284"/>
+      <c r="B223" s="289"/>
+      <c r="C223" s="297"/>
       <c r="D223" s="7"/>
       <c r="E223" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F223" s="291"/>
+      <c r="F223" s="285"/>
     </row>
     <row r="224" s="244" customFormat="1" spans="1:6">
-      <c r="A224" s="290"/>
-      <c r="B224" s="299"/>
-      <c r="C224" s="303"/>
+      <c r="A224" s="284"/>
+      <c r="B224" s="289"/>
+      <c r="C224" s="297"/>
       <c r="D224" s="7"/>
       <c r="E224" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F224" s="291"/>
+      <c r="F224" s="285"/>
     </row>
     <row r="225" s="244" customFormat="1" spans="1:6">
-      <c r="A225" s="290"/>
-      <c r="B225" s="299"/>
-      <c r="C225" s="303"/>
+      <c r="A225" s="284"/>
+      <c r="B225" s="289"/>
+      <c r="C225" s="297"/>
       <c r="D225" s="7"/>
       <c r="E225" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F225" s="291"/>
+      <c r="F225" s="285"/>
     </row>
     <row r="226" s="244" customFormat="1" spans="1:6">
-      <c r="A226" s="290"/>
-      <c r="B226" s="299"/>
-      <c r="C226" s="303"/>
+      <c r="A226" s="284"/>
+      <c r="B226" s="289"/>
+      <c r="C226" s="297"/>
       <c r="D226" s="7"/>
       <c r="E226" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F226" s="291"/>
+      <c r="F226" s="285"/>
     </row>
     <row r="227" s="244" customFormat="1" spans="1:6">
-      <c r="A227" s="290"/>
-      <c r="B227" s="299"/>
-      <c r="C227" s="303"/>
+      <c r="A227" s="284"/>
+      <c r="B227" s="289"/>
+      <c r="C227" s="297"/>
       <c r="D227" s="7"/>
       <c r="E227" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F227" s="291"/>
+      <c r="F227" s="285"/>
     </row>
     <row r="228" s="244" customFormat="1" spans="1:6">
-      <c r="A228" s="290"/>
-      <c r="B228" s="299"/>
-      <c r="C228" s="303"/>
+      <c r="A228" s="284"/>
+      <c r="B228" s="289"/>
+      <c r="C228" s="297"/>
       <c r="D228" s="7"/>
       <c r="E228" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F228" s="291"/>
+      <c r="F228" s="285"/>
     </row>
     <row r="229" s="244" customFormat="1" spans="1:6">
-      <c r="A229" s="290"/>
-      <c r="B229" s="299"/>
-      <c r="C229" s="303"/>
+      <c r="A229" s="284"/>
+      <c r="B229" s="289"/>
+      <c r="C229" s="297"/>
       <c r="D229" s="7"/>
       <c r="E229" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F229" s="291"/>
+      <c r="F229" s="285"/>
     </row>
     <row r="230" s="244" customFormat="1" spans="1:6">
-      <c r="A230" s="292"/>
-      <c r="B230" s="299"/>
-      <c r="C230" s="303"/>
+      <c r="A230" s="286"/>
+      <c r="B230" s="289"/>
+      <c r="C230" s="297"/>
       <c r="D230" s="7"/>
       <c r="E230" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F230" s="273"/>
+      <c r="F230" s="267"/>
     </row>
     <row r="231" s="244" customFormat="1" spans="1:6">
-      <c r="A231" s="286"/>
-      <c r="B231" s="299"/>
-      <c r="C231" s="303"/>
+      <c r="A231" s="280"/>
+      <c r="B231" s="289"/>
+      <c r="C231" s="297"/>
       <c r="D231" s="7"/>
       <c r="E231" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F231" s="289">
+      <c r="F231" s="283">
         <f>SUM(E231:E241)</f>
         <v>0</v>
       </c>
     </row>
     <row r="232" s="244" customFormat="1" spans="1:6">
-      <c r="A232" s="290"/>
-      <c r="B232" s="299"/>
-      <c r="C232" s="303"/>
+      <c r="A232" s="284"/>
+      <c r="B232" s="289"/>
+      <c r="C232" s="297"/>
       <c r="D232" s="7"/>
       <c r="E232" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F232" s="291"/>
+      <c r="F232" s="285"/>
     </row>
     <row r="233" s="244" customFormat="1" spans="1:6">
-      <c r="A233" s="290"/>
-      <c r="B233" s="299"/>
-      <c r="C233" s="303"/>
+      <c r="A233" s="284"/>
+      <c r="B233" s="289"/>
+      <c r="C233" s="297"/>
       <c r="D233" s="7"/>
       <c r="E233" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F233" s="291"/>
+      <c r="F233" s="285"/>
     </row>
     <row r="234" s="244" customFormat="1" spans="1:6">
-      <c r="A234" s="290"/>
-      <c r="B234" s="299"/>
-      <c r="C234" s="303"/>
+      <c r="A234" s="284"/>
+      <c r="B234" s="289"/>
+      <c r="C234" s="297"/>
       <c r="D234" s="7"/>
       <c r="E234" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F234" s="291"/>
+      <c r="F234" s="285"/>
     </row>
     <row r="235" s="244" customFormat="1" spans="1:6">
-      <c r="A235" s="290"/>
-      <c r="B235" s="299"/>
-      <c r="C235" s="303"/>
+      <c r="A235" s="284"/>
+      <c r="B235" s="289"/>
+      <c r="C235" s="297"/>
       <c r="D235" s="7"/>
       <c r="E235" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F235" s="291"/>
+      <c r="F235" s="285"/>
     </row>
     <row r="236" s="244" customFormat="1" spans="1:6">
-      <c r="A236" s="290"/>
-      <c r="B236" s="299"/>
-      <c r="C236" s="303"/>
+      <c r="A236" s="284"/>
+      <c r="B236" s="289"/>
+      <c r="C236" s="297"/>
       <c r="D236" s="7"/>
       <c r="E236" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F236" s="291"/>
+      <c r="F236" s="285"/>
     </row>
     <row r="237" s="244" customFormat="1" spans="1:6">
-      <c r="A237" s="290"/>
-      <c r="B237" s="299"/>
-      <c r="C237" s="303"/>
+      <c r="A237" s="284"/>
+      <c r="B237" s="289"/>
+      <c r="C237" s="297"/>
       <c r="D237" s="7"/>
       <c r="E237" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F237" s="291"/>
+      <c r="F237" s="285"/>
     </row>
     <row r="238" s="244" customFormat="1" spans="1:6">
-      <c r="A238" s="290"/>
-      <c r="B238" s="299"/>
-      <c r="C238" s="303"/>
+      <c r="A238" s="284"/>
+      <c r="B238" s="289"/>
+      <c r="C238" s="297"/>
       <c r="D238" s="7"/>
       <c r="E238" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F238" s="291"/>
+      <c r="F238" s="285"/>
     </row>
     <row r="239" s="244" customFormat="1" spans="1:6">
-      <c r="A239" s="290"/>
-      <c r="B239" s="299"/>
-      <c r="C239" s="303"/>
+      <c r="A239" s="284"/>
+      <c r="B239" s="289"/>
+      <c r="C239" s="297"/>
       <c r="D239" s="7"/>
       <c r="E239" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F239" s="291"/>
+      <c r="F239" s="285"/>
     </row>
     <row r="240" s="244" customFormat="1" spans="1:6">
-      <c r="A240" s="290"/>
-      <c r="B240" s="299"/>
-      <c r="C240" s="303"/>
+      <c r="A240" s="284"/>
+      <c r="B240" s="289"/>
+      <c r="C240" s="297"/>
       <c r="D240" s="7"/>
       <c r="E240" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F240" s="291"/>
+      <c r="F240" s="285"/>
     </row>
     <row r="241" s="244" customFormat="1" spans="1:6">
-      <c r="A241" s="292"/>
-      <c r="B241" s="299"/>
-      <c r="C241" s="303"/>
+      <c r="A241" s="286"/>
+      <c r="B241" s="289"/>
+      <c r="C241" s="297"/>
       <c r="D241" s="7"/>
       <c r="E241" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F241" s="273"/>
+      <c r="F241" s="267"/>
     </row>
     <row r="242" s="244" customFormat="1" spans="1:6">
-      <c r="A242" s="286"/>
-      <c r="B242" s="299"/>
-      <c r="C242" s="303"/>
+      <c r="A242" s="280"/>
+      <c r="B242" s="289"/>
+      <c r="C242" s="297"/>
       <c r="D242" s="7"/>
       <c r="E242" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F242" s="289">
+      <c r="F242" s="283">
         <f>SUM(E242:E252)</f>
         <v>0</v>
       </c>
     </row>
     <row r="243" s="244" customFormat="1" spans="1:6">
-      <c r="A243" s="290"/>
-      <c r="B243" s="299"/>
-      <c r="C243" s="303"/>
+      <c r="A243" s="284"/>
+      <c r="B243" s="289"/>
+      <c r="C243" s="297"/>
       <c r="D243" s="7"/>
       <c r="E243" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F243" s="291"/>
+      <c r="F243" s="285"/>
     </row>
     <row r="244" s="244" customFormat="1" spans="1:6">
-      <c r="A244" s="290"/>
-      <c r="B244" s="299"/>
-      <c r="C244" s="303"/>
+      <c r="A244" s="284"/>
+      <c r="B244" s="289"/>
+      <c r="C244" s="297"/>
       <c r="D244" s="7"/>
       <c r="E244" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F244" s="291"/>
+      <c r="F244" s="285"/>
     </row>
     <row r="245" s="244" customFormat="1" spans="1:6">
-      <c r="A245" s="290"/>
-      <c r="B245" s="299"/>
-      <c r="C245" s="303"/>
+      <c r="A245" s="284"/>
+      <c r="B245" s="289"/>
+      <c r="C245" s="297"/>
       <c r="D245" s="7"/>
       <c r="E245" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F245" s="291"/>
+      <c r="F245" s="285"/>
     </row>
     <row r="246" s="244" customFormat="1" spans="1:6">
-      <c r="A246" s="290"/>
-      <c r="B246" s="299"/>
-      <c r="C246" s="303"/>
+      <c r="A246" s="284"/>
+      <c r="B246" s="289"/>
+      <c r="C246" s="297"/>
       <c r="D246" s="7"/>
       <c r="E246" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F246" s="291"/>
+      <c r="F246" s="285"/>
     </row>
     <row r="247" s="244" customFormat="1" spans="1:6">
-      <c r="A247" s="290"/>
-      <c r="B247" s="299"/>
-      <c r="C247" s="303"/>
+      <c r="A247" s="284"/>
+      <c r="B247" s="289"/>
+      <c r="C247" s="297"/>
       <c r="D247" s="7"/>
       <c r="E247" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F247" s="291"/>
+      <c r="F247" s="285"/>
     </row>
     <row r="248" s="244" customFormat="1" spans="1:6">
-      <c r="A248" s="290"/>
-      <c r="B248" s="299"/>
-      <c r="C248" s="303"/>
+      <c r="A248" s="284"/>
+      <c r="B248" s="289"/>
+      <c r="C248" s="297"/>
       <c r="D248" s="7"/>
       <c r="E248" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F248" s="291"/>
+      <c r="F248" s="285"/>
     </row>
     <row r="249" s="244" customFormat="1" spans="1:6">
-      <c r="A249" s="290"/>
-      <c r="B249" s="299"/>
-      <c r="C249" s="303"/>
+      <c r="A249" s="284"/>
+      <c r="B249" s="289"/>
+      <c r="C249" s="297"/>
       <c r="D249" s="7"/>
       <c r="E249" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F249" s="291"/>
+      <c r="F249" s="285"/>
     </row>
     <row r="250" s="244" customFormat="1" spans="1:6">
-      <c r="A250" s="290"/>
-      <c r="B250" s="299"/>
-      <c r="C250" s="303"/>
+      <c r="A250" s="284"/>
+      <c r="B250" s="289"/>
+      <c r="C250" s="297"/>
       <c r="D250" s="7"/>
       <c r="E250" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F250" s="291"/>
+      <c r="F250" s="285"/>
     </row>
     <row r="251" s="244" customFormat="1" spans="1:6">
-      <c r="A251" s="290"/>
-      <c r="B251" s="299"/>
-      <c r="C251" s="303"/>
+      <c r="A251" s="284"/>
+      <c r="B251" s="289"/>
+      <c r="C251" s="297"/>
       <c r="D251" s="7"/>
       <c r="E251" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F251" s="291"/>
+      <c r="F251" s="285"/>
     </row>
     <row r="252" s="244" customFormat="1" spans="1:6">
-      <c r="A252" s="292"/>
-      <c r="B252" s="299"/>
-      <c r="C252" s="303"/>
+      <c r="A252" s="286"/>
+      <c r="B252" s="289"/>
+      <c r="C252" s="297"/>
       <c r="D252" s="7"/>
       <c r="E252" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F252" s="273"/>
+      <c r="F252" s="267"/>
     </row>
     <row r="253" s="244" customFormat="1" spans="1:6">
-      <c r="A253" s="286"/>
-      <c r="B253" s="299"/>
-      <c r="C253" s="303"/>
+      <c r="A253" s="280"/>
+      <c r="B253" s="289"/>
+      <c r="C253" s="297"/>
       <c r="D253" s="7"/>
       <c r="E253" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F253" s="289">
+      <c r="F253" s="283">
         <f>SUM(E253:E262)</f>
         <v>0</v>
       </c>
     </row>
     <row r="254" s="244" customFormat="1" spans="1:6">
-      <c r="A254" s="290"/>
-      <c r="B254" s="299"/>
-      <c r="C254" s="303"/>
+      <c r="A254" s="284"/>
+      <c r="B254" s="289"/>
+      <c r="C254" s="297"/>
       <c r="D254" s="7"/>
       <c r="E254" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F254" s="291"/>
+      <c r="F254" s="285"/>
     </row>
     <row r="255" s="244" customFormat="1" spans="1:6">
-      <c r="A255" s="290"/>
-      <c r="B255" s="299"/>
-      <c r="C255" s="303"/>
+      <c r="A255" s="284"/>
+      <c r="B255" s="289"/>
+      <c r="C255" s="297"/>
       <c r="D255" s="7"/>
       <c r="E255" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F255" s="291"/>
+      <c r="F255" s="285"/>
     </row>
     <row r="256" s="244" customFormat="1" spans="1:6">
-      <c r="A256" s="290"/>
-      <c r="B256" s="299"/>
-      <c r="C256" s="303"/>
+      <c r="A256" s="284"/>
+      <c r="B256" s="289"/>
+      <c r="C256" s="297"/>
       <c r="D256" s="7"/>
       <c r="E256" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F256" s="291"/>
+      <c r="F256" s="285"/>
     </row>
     <row r="257" s="244" customFormat="1" spans="1:6">
-      <c r="A257" s="290"/>
-      <c r="B257" s="299"/>
-      <c r="C257" s="303"/>
+      <c r="A257" s="284"/>
+      <c r="B257" s="289"/>
+      <c r="C257" s="297"/>
       <c r="D257" s="7"/>
       <c r="E257" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F257" s="291"/>
+      <c r="F257" s="285"/>
     </row>
     <row r="258" s="244" customFormat="1" spans="1:6">
-      <c r="A258" s="290"/>
-      <c r="B258" s="299"/>
-      <c r="C258" s="303"/>
+      <c r="A258" s="284"/>
+      <c r="B258" s="289"/>
+      <c r="C258" s="297"/>
       <c r="D258" s="7"/>
       <c r="E258" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F258" s="291"/>
+      <c r="F258" s="285"/>
     </row>
     <row r="259" s="244" customFormat="1" spans="1:6">
-      <c r="A259" s="290"/>
-      <c r="B259" s="299"/>
-      <c r="C259" s="303"/>
+      <c r="A259" s="284"/>
+      <c r="B259" s="289"/>
+      <c r="C259" s="297"/>
       <c r="D259" s="7"/>
       <c r="E259" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F259" s="291"/>
+      <c r="F259" s="285"/>
     </row>
     <row r="260" s="244" customFormat="1" spans="1:6">
-      <c r="A260" s="290"/>
-      <c r="B260" s="299"/>
-      <c r="C260" s="303"/>
+      <c r="A260" s="284"/>
+      <c r="B260" s="289"/>
+      <c r="C260" s="297"/>
       <c r="D260" s="7"/>
       <c r="E260" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F260" s="291"/>
+      <c r="F260" s="285"/>
     </row>
     <row r="261" s="244" customFormat="1" spans="1:6">
-      <c r="A261" s="290"/>
-      <c r="B261" s="299"/>
-      <c r="C261" s="303"/>
+      <c r="A261" s="284"/>
+      <c r="B261" s="289"/>
+      <c r="C261" s="297"/>
       <c r="D261" s="7"/>
       <c r="E261" s="7">
         <f t="shared" ref="E261:E274" si="5">SUM(C261*D261)</f>
         <v>0</v>
       </c>
-      <c r="F261" s="291"/>
+      <c r="F261" s="285"/>
     </row>
     <row r="262" s="244" customFormat="1" spans="1:6">
-      <c r="A262" s="292"/>
-      <c r="B262" s="299"/>
-      <c r="C262" s="303"/>
+      <c r="A262" s="286"/>
+      <c r="B262" s="289"/>
+      <c r="C262" s="297"/>
       <c r="D262" s="7"/>
       <c r="E262" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F262" s="273"/>
+      <c r="F262" s="267"/>
     </row>
     <row r="263" s="244" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A263" s="304"/>
-      <c r="B263" s="299"/>
-      <c r="C263" s="303"/>
+      <c r="A263" s="298"/>
+      <c r="B263" s="289"/>
+      <c r="C263" s="297"/>
       <c r="D263" s="7"/>
       <c r="E263" s="7">
         <f t="shared" si="5"/>
@@ -6067,128 +6121,128 @@
       </c>
     </row>
     <row r="264" s="244" customFormat="1" spans="1:6">
-      <c r="A264" s="286"/>
-      <c r="B264" s="299"/>
-      <c r="C264" s="303"/>
+      <c r="A264" s="280"/>
+      <c r="B264" s="289"/>
+      <c r="C264" s="297"/>
       <c r="D264" s="7"/>
       <c r="E264" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F264" s="289">
+      <c r="F264" s="283">
         <f>SUM(E264:E274)</f>
         <v>0</v>
       </c>
     </row>
     <row r="265" s="244" customFormat="1" spans="1:6">
-      <c r="A265" s="290"/>
-      <c r="B265" s="299"/>
-      <c r="C265" s="303"/>
+      <c r="A265" s="284"/>
+      <c r="B265" s="289"/>
+      <c r="C265" s="297"/>
       <c r="D265" s="7"/>
       <c r="E265" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F265" s="291"/>
+      <c r="F265" s="285"/>
     </row>
     <row r="266" s="244" customFormat="1" spans="1:6">
-      <c r="A266" s="290"/>
-      <c r="B266" s="299"/>
-      <c r="C266" s="303"/>
+      <c r="A266" s="284"/>
+      <c r="B266" s="289"/>
+      <c r="C266" s="297"/>
       <c r="D266" s="7"/>
       <c r="E266" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F266" s="291"/>
+      <c r="F266" s="285"/>
     </row>
     <row r="267" s="244" customFormat="1" spans="1:6">
-      <c r="A267" s="290"/>
-      <c r="B267" s="299"/>
-      <c r="C267" s="303"/>
+      <c r="A267" s="284"/>
+      <c r="B267" s="289"/>
+      <c r="C267" s="297"/>
       <c r="D267" s="7"/>
       <c r="E267" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F267" s="291"/>
+      <c r="F267" s="285"/>
     </row>
     <row r="268" s="244" customFormat="1" spans="1:6">
-      <c r="A268" s="290"/>
-      <c r="B268" s="299"/>
-      <c r="C268" s="303"/>
+      <c r="A268" s="284"/>
+      <c r="B268" s="289"/>
+      <c r="C268" s="297"/>
       <c r="D268" s="7"/>
       <c r="E268" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F268" s="291"/>
+      <c r="F268" s="285"/>
     </row>
     <row r="269" s="244" customFormat="1" spans="1:6">
-      <c r="A269" s="290"/>
-      <c r="B269" s="299"/>
-      <c r="C269" s="303"/>
+      <c r="A269" s="284"/>
+      <c r="B269" s="289"/>
+      <c r="C269" s="297"/>
       <c r="D269" s="7"/>
       <c r="E269" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F269" s="291"/>
+      <c r="F269" s="285"/>
     </row>
     <row r="270" s="244" customFormat="1" spans="1:6">
-      <c r="A270" s="290"/>
-      <c r="B270" s="299"/>
-      <c r="C270" s="303"/>
+      <c r="A270" s="284"/>
+      <c r="B270" s="289"/>
+      <c r="C270" s="297"/>
       <c r="D270" s="7"/>
       <c r="E270" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F270" s="291"/>
+      <c r="F270" s="285"/>
     </row>
     <row r="271" s="244" customFormat="1" spans="1:6">
-      <c r="A271" s="290"/>
-      <c r="B271" s="299"/>
-      <c r="C271" s="303"/>
+      <c r="A271" s="284"/>
+      <c r="B271" s="289"/>
+      <c r="C271" s="297"/>
       <c r="D271" s="7"/>
       <c r="E271" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F271" s="291"/>
+      <c r="F271" s="285"/>
     </row>
     <row r="272" s="244" customFormat="1" spans="1:6">
-      <c r="A272" s="290"/>
-      <c r="B272" s="299"/>
-      <c r="C272" s="303"/>
+      <c r="A272" s="284"/>
+      <c r="B272" s="289"/>
+      <c r="C272" s="297"/>
       <c r="D272" s="7"/>
       <c r="E272" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F272" s="291"/>
+      <c r="F272" s="285"/>
     </row>
     <row r="273" s="244" customFormat="1" spans="1:6">
-      <c r="A273" s="290"/>
-      <c r="B273" s="299"/>
-      <c r="C273" s="303"/>
+      <c r="A273" s="284"/>
+      <c r="B273" s="289"/>
+      <c r="C273" s="297"/>
       <c r="D273" s="7"/>
       <c r="E273" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F273" s="291"/>
+      <c r="F273" s="285"/>
     </row>
     <row r="274" s="244" customFormat="1" spans="1:6">
-      <c r="A274" s="292"/>
-      <c r="B274" s="299"/>
-      <c r="C274" s="303"/>
+      <c r="A274" s="286"/>
+      <c r="B274" s="289"/>
+      <c r="C274" s="297"/>
       <c r="D274" s="7"/>
       <c r="E274" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F274" s="273"/>
+      <c r="F274" s="267"/>
     </row>
     <row r="275" s="244" customFormat="1" spans="1:6">
       <c r="A275" s="246"/>
@@ -6196,7 +6250,7 @@
       <c r="E275" s="7"/>
       <c r="F275" s="256">
         <f>SUM(F2:F274)</f>
-        <v>1382000</v>
+        <v>1804000</v>
       </c>
     </row>
     <row r="276" s="244" customFormat="1" spans="1:3">
@@ -6610,12 +6664,13 @@
     <row r="378" s="244" customFormat="1" spans="1:7">
       <c r="A378" s="246"/>
       <c r="C378" s="245"/>
-      <c r="G378" s="274"/>
+      <c r="G378" s="268"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="52">
     <mergeCell ref="A2:A12"/>
     <mergeCell ref="A13:A25"/>
+    <mergeCell ref="A26:A34"/>
     <mergeCell ref="A36:A41"/>
     <mergeCell ref="A42:A47"/>
     <mergeCell ref="A48:A56"/>
@@ -6641,6 +6696,7 @@
     <mergeCell ref="A264:A274"/>
     <mergeCell ref="F2:F12"/>
     <mergeCell ref="F13:F25"/>
+    <mergeCell ref="F26:F34"/>
     <mergeCell ref="F36:F41"/>
     <mergeCell ref="F42:F47"/>
     <mergeCell ref="F48:F56"/>
@@ -6690,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -6729,7 +6785,7 @@
       <c r="D3" s="27"/>
       <c r="E3" s="17"/>
       <c r="F3" s="118" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G3" s="41">
         <f>G2*11%</f>
@@ -6771,7 +6827,7 @@
       <c r="D6" s="125"/>
       <c r="E6" s="7"/>
       <c r="F6" s="126" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G6" s="7">
         <f>G5*11%</f>
@@ -6853,7 +6909,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="87" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B14" s="88"/>
       <c r="C14" s="88"/>
@@ -6907,16 +6963,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -7055,7 +7111,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="87" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B14" s="88"/>
       <c r="C14" s="88"/>
@@ -7109,16 +7165,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -7127,7 +7183,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" ht="138.55" customHeight="1" spans="1:8">
@@ -7155,7 +7211,7 @@
       </c>
       <c r="E3" s="101"/>
       <c r="F3" s="82" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G3" s="102">
         <f>G2*11%</f>
@@ -7203,7 +7259,7 @@
       </c>
       <c r="E6" s="81"/>
       <c r="F6" s="82" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G6" s="102">
         <f>G5*11%</f>
@@ -7248,7 +7304,7 @@
       <c r="D9" s="104"/>
       <c r="E9" s="81"/>
       <c r="F9" s="82" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G9" s="102">
         <f>G8*11%</f>
@@ -7293,7 +7349,7 @@
       <c r="D12" s="104"/>
       <c r="E12" s="81"/>
       <c r="F12" s="82" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G12" s="102">
         <f>G11*11%</f>
@@ -7335,7 +7391,7 @@
       <c r="D15" s="104"/>
       <c r="E15" s="81"/>
       <c r="F15" s="82" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G15" s="102">
         <f>G14*11%</f>
@@ -7360,7 +7416,7 @@
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:8">
       <c r="A17" s="87" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B17" s="88"/>
       <c r="C17" s="88"/>
@@ -7418,19 +7474,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E1" s="35" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>5</v>
@@ -7462,7 +7518,7 @@
     </row>
     <row r="4" ht="23" customHeight="1" spans="1:7">
       <c r="A4" s="94" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B4" s="95"/>
       <c r="C4" s="95"/>
@@ -7503,16 +7559,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -7535,7 +7591,7 @@
     </row>
     <row r="3" ht="23.25" spans="1:7">
       <c r="A3" s="29" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="79"/>
@@ -7545,7 +7601,7 @@
       </c>
       <c r="E3" s="81"/>
       <c r="F3" s="81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G3" s="82">
         <f>G2*11%</f>
@@ -7600,7 +7656,7 @@
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:7">
       <c r="A8" s="87" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B8" s="88"/>
       <c r="C8" s="88"/>
@@ -7647,19 +7703,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" ht="321" customHeight="1" spans="1:6">
@@ -7722,16 +7778,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -7832,7 +7888,7 @@
     </row>
     <row r="12" ht="27" customHeight="1" spans="1:7">
       <c r="A12" s="61" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B12" s="62"/>
       <c r="C12" s="62"/>
@@ -7885,13 +7941,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>3</v>
@@ -7900,7 +7956,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" ht="324.4" customHeight="1" spans="1:7">
@@ -7959,22 +8015,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" ht="177" customHeight="1" spans="1:7">
@@ -8035,10 +8091,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>5</v>
@@ -8049,11 +8105,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C2" s="5">
         <f>'BUK BUNGA (Groceries)'!F275</f>
-        <v>1382000</v>
+        <v>1804000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8061,7 +8117,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C3" s="5">
         <f>'WARUNG EKA (Drinks, Etc)'!G118</f>
@@ -8073,7 +8129,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C4" s="5">
         <f>'DEWATA COCONUT (Coconut)'!E10</f>
@@ -8085,7 +8141,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C5" s="5">
         <f>'SEDANA JAYA'!F37</f>
@@ -8097,7 +8153,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C6" s="5">
         <f>'PNB (Alcohol)'!H7</f>
@@ -8109,7 +8165,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C7" s="5">
         <f>'DSP (Alcohol)'!F16</f>
@@ -8121,7 +8177,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C8" s="5">
         <f>'DSP ARYA BIMA (Alcohol)'!E3</f>
@@ -8133,7 +8189,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C9" s="5">
         <f>'SELERA OR STIR UP (Syrup)'!F9</f>
@@ -8145,7 +8201,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C10" s="5">
         <f>'DW BALI (Alcohol)'!E4</f>
@@ -8157,7 +8213,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C11" s="5">
         <f>'DDB (Alcohol)'!E14</f>
@@ -8169,7 +8225,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C12" s="5">
         <f>'NANO DEWATA (Alcohol)'!E14</f>
@@ -8181,7 +8237,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C13" s="5">
         <f>'BALI PERMATA JAYA (Corona Beer)'!E17</f>
@@ -8193,7 +8249,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C14" s="7">
         <f>'BLACK COFFEE ROASTERS (Coffee)'!F4</f>
@@ -8205,7 +8261,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C15" s="5">
         <f>'PT. PRASIDA LANTUR MAJU (Wine)'!E8</f>
@@ -8217,7 +8273,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C16" s="8">
         <f>'PT LOVINA BEACH BREWERY'!D3</f>
@@ -8229,7 +8285,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C17" s="5">
         <f>'CHAI CHITAI (Tea Leaf,etc)'!E12</f>
@@ -8241,7 +8297,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C18" s="5">
         <f>'MULIA JAYA (Passion Fruit)'!D3</f>
@@ -8253,7 +8309,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C19" s="5">
         <f>'Dewata Kencana Distribusi (Vdka'!E3</f>
@@ -8267,7 +8323,7 @@
       <c r="B20" s="9"/>
       <c r="C20" s="10">
         <f>SUM(C2:C13)</f>
-        <v>6711100</v>
+        <v>7133100</v>
       </c>
     </row>
   </sheetData>
@@ -8303,7 +8359,7 @@
   <sheetData>
     <row r="1" s="244" customFormat="1" ht="21" customHeight="1" spans="1:7">
       <c r="A1" s="250" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B1" s="251" t="s">
         <v>0</v>
@@ -8318,10 +8374,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="252" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G1" s="252" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
@@ -8332,7 +8388,7 @@
         <v>45992</v>
       </c>
       <c r="C2" s="255" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D2" s="114">
         <v>5</v>
@@ -8353,7 +8409,7 @@
       <c r="A3" s="43"/>
       <c r="B3" s="42"/>
       <c r="C3" s="255" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D3" s="114">
         <v>1</v>
@@ -8371,7 +8427,7 @@
       <c r="A4" s="259"/>
       <c r="B4" s="260"/>
       <c r="C4" s="255" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D4" s="114">
         <v>1</v>
@@ -8393,7 +8449,7 @@
         <v>45993</v>
       </c>
       <c r="C5" s="255" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D5" s="114">
         <v>5</v>
@@ -8414,7 +8470,7 @@
       <c r="A6" s="204"/>
       <c r="B6" s="42"/>
       <c r="C6" s="255" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D6" s="114">
         <v>1</v>
@@ -8432,7 +8488,7 @@
       <c r="A7" s="262"/>
       <c r="B7" s="260"/>
       <c r="C7" s="255" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D7" s="114">
         <v>1</v>
@@ -8454,7 +8510,7 @@
         <v>45994</v>
       </c>
       <c r="C8" s="255" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D8" s="114">
         <v>6</v>
@@ -8475,7 +8531,7 @@
       <c r="A9" s="204"/>
       <c r="B9" s="42"/>
       <c r="C9" s="255" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D9" s="114">
         <v>1</v>
@@ -8493,7 +8549,7 @@
       <c r="A10" s="204"/>
       <c r="B10" s="42"/>
       <c r="C10" s="255" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D10" s="114">
         <v>1</v>
@@ -8511,7 +8567,7 @@
       <c r="A11" s="204"/>
       <c r="B11" s="42"/>
       <c r="C11" s="255" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D11" s="114">
         <v>1</v>
@@ -8529,7 +8585,7 @@
       <c r="A12" s="204"/>
       <c r="B12" s="42"/>
       <c r="C12" s="264" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D12" s="114">
         <v>2</v>
@@ -8547,7 +8603,7 @@
       <c r="A13" s="262"/>
       <c r="B13" s="260"/>
       <c r="C13" s="255" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D13" s="114">
         <v>1</v>
@@ -8562,14 +8618,14 @@
       <c r="G13" s="261"/>
     </row>
     <row r="14" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A14" s="265">
+      <c r="A14" s="202">
         <v>74191</v>
       </c>
-      <c r="B14" s="266">
+      <c r="B14" s="36">
         <v>45995</v>
       </c>
       <c r="C14" s="255" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D14" s="114">
         <v>6</v>
@@ -8581,16 +8637,16 @@
         <f t="shared" si="1"/>
         <v>48000</v>
       </c>
-      <c r="G14" s="267">
+      <c r="G14" s="257">
         <f>SUM(F14:F15)</f>
         <v>92000</v>
       </c>
     </row>
     <row r="15" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A15" s="268"/>
-      <c r="B15" s="269"/>
+      <c r="A15" s="262"/>
+      <c r="B15" s="260"/>
       <c r="C15" s="264" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D15" s="114">
         <v>2</v>
@@ -8602,7 +8658,7 @@
         <f t="shared" si="1"/>
         <v>44000</v>
       </c>
-      <c r="G15" s="270"/>
+      <c r="G15" s="261"/>
     </row>
     <row r="16" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A16" s="202"/>
@@ -8614,7 +8670,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="271"/>
+      <c r="G16" s="265"/>
     </row>
     <row r="17" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A17" s="204"/>
@@ -8626,7 +8682,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="271"/>
+      <c r="G17" s="265"/>
     </row>
     <row r="18" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A18" s="262"/>
@@ -8638,7 +8694,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G18" s="271"/>
+      <c r="G18" s="265"/>
     </row>
     <row r="19" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A19" s="49"/>
@@ -8650,7 +8706,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G19" s="271">
+      <c r="G19" s="265">
         <f>SUM(F19:F20)</f>
         <v>0</v>
       </c>
@@ -8665,7 +8721,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="271"/>
+      <c r="G20" s="265"/>
     </row>
     <row r="21" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A21" s="202"/>
@@ -8677,7 +8733,7 @@
         <f t="shared" ref="F21:F45" si="2">SUM(D21*E21)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="271">
+      <c r="G21" s="265">
         <f>SUM(F21:F25)</f>
         <v>0</v>
       </c>
@@ -8692,7 +8748,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G22" s="271"/>
+      <c r="G22" s="265"/>
     </row>
     <row r="23" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A23" s="204"/>
@@ -8704,7 +8760,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G23" s="271"/>
+      <c r="G23" s="265"/>
     </row>
     <row r="24" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A24" s="204"/>
@@ -8716,7 +8772,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G24" s="271"/>
+      <c r="G24" s="265"/>
     </row>
     <row r="25" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A25" s="262"/>
@@ -8728,7 +8784,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G25" s="271"/>
+      <c r="G25" s="265"/>
     </row>
     <row r="26" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A26" s="202"/>
@@ -8740,7 +8796,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G26" s="271">
+      <c r="G26" s="265">
         <f>SUM(F26:F28)</f>
         <v>0</v>
       </c>
@@ -8755,7 +8811,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G27" s="271"/>
+      <c r="G27" s="265"/>
     </row>
     <row r="28" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A28" s="262"/>
@@ -8767,7 +8823,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G28" s="271"/>
+      <c r="G28" s="265"/>
     </row>
     <row r="29" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A29" s="202"/>
@@ -8779,7 +8835,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G29" s="271">
+      <c r="G29" s="265">
         <f>SUM(F29:F32)</f>
         <v>0</v>
       </c>
@@ -8794,7 +8850,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G30" s="271"/>
+      <c r="G30" s="265"/>
     </row>
     <row r="31" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A31" s="204"/>
@@ -8806,7 +8862,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G31" s="271"/>
+      <c r="G31" s="265"/>
     </row>
     <row r="32" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A32" s="262"/>
@@ -8818,7 +8874,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G32" s="271"/>
+      <c r="G32" s="265"/>
     </row>
     <row r="33" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A33" s="202"/>
@@ -8830,7 +8886,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G33" s="271">
+      <c r="G33" s="265">
         <f>SUM(F33:F37)</f>
         <v>0</v>
       </c>
@@ -8845,7 +8901,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G34" s="271"/>
+      <c r="G34" s="265"/>
     </row>
     <row r="35" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A35" s="204"/>
@@ -8857,7 +8913,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G35" s="271"/>
+      <c r="G35" s="265"/>
     </row>
     <row r="36" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A36" s="204"/>
@@ -8869,7 +8925,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G36" s="271"/>
+      <c r="G36" s="265"/>
     </row>
     <row r="37" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A37" s="262"/>
@@ -8881,7 +8937,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G37" s="271"/>
+      <c r="G37" s="265"/>
     </row>
     <row r="38" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A38" s="202"/>
@@ -8893,7 +8949,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G38" s="271">
+      <c r="G38" s="265">
         <f>SUM(F38:F41)</f>
         <v>0</v>
       </c>
@@ -8908,7 +8964,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G39" s="271"/>
+      <c r="G39" s="265"/>
     </row>
     <row r="40" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A40" s="204"/>
@@ -8920,7 +8976,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G40" s="271"/>
+      <c r="G40" s="265"/>
     </row>
     <row r="41" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A41" s="262"/>
@@ -8932,7 +8988,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G41" s="271"/>
+      <c r="G41" s="265"/>
     </row>
     <row r="42" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A42" s="49"/>
@@ -8944,7 +9000,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G42" s="271">
+      <c r="G42" s="265">
         <f>SUM(F42:F43)</f>
         <v>0</v>
       </c>
@@ -8959,7 +9015,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G43" s="271"/>
+      <c r="G43" s="265"/>
     </row>
     <row r="44" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A44" s="202"/>
@@ -8971,7 +9027,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G44" s="271">
+      <c r="G44" s="265">
         <f>SUM(F44:F45)</f>
         <v>0</v>
       </c>
@@ -8986,7 +9042,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G45" s="271"/>
+      <c r="G45" s="265"/>
     </row>
     <row r="46" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A46" s="202"/>
@@ -8998,7 +9054,7 @@
         <f t="shared" ref="F46:F72" si="3">SUM(D46*E46)</f>
         <v>0</v>
       </c>
-      <c r="G46" s="271">
+      <c r="G46" s="265">
         <f>SUM(F46:F54)</f>
         <v>0</v>
       </c>
@@ -9013,7 +9069,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G47" s="271"/>
+      <c r="G47" s="265"/>
     </row>
     <row r="48" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A48" s="204"/>
@@ -9025,7 +9081,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G48" s="271"/>
+      <c r="G48" s="265"/>
     </row>
     <row r="49" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A49" s="204"/>
@@ -9037,7 +9093,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G49" s="271"/>
+      <c r="G49" s="265"/>
     </row>
     <row r="50" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A50" s="204"/>
@@ -9049,7 +9105,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G50" s="271"/>
+      <c r="G50" s="265"/>
     </row>
     <row r="51" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A51" s="204"/>
@@ -9061,7 +9117,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G51" s="271"/>
+      <c r="G51" s="265"/>
     </row>
     <row r="52" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A52" s="204"/>
@@ -9073,7 +9129,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G52" s="271"/>
+      <c r="G52" s="265"/>
     </row>
     <row r="53" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A53" s="204"/>
@@ -9085,7 +9141,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G53" s="271"/>
+      <c r="G53" s="265"/>
     </row>
     <row r="54" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A54" s="262"/>
@@ -9097,7 +9153,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G54" s="271"/>
+      <c r="G54" s="265"/>
     </row>
     <row r="55" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A55" s="49"/>
@@ -9109,7 +9165,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G55" s="271">
+      <c r="G55" s="265">
         <f>SUM(F55:F58)</f>
         <v>0</v>
       </c>
@@ -9117,14 +9173,14 @@
     <row r="56" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A56" s="49"/>
       <c r="B56" s="25"/>
-      <c r="C56" s="272"/>
+      <c r="C56" s="266"/>
       <c r="D56" s="259"/>
-      <c r="E56" s="273"/>
+      <c r="E56" s="267"/>
       <c r="F56" s="256">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G56" s="271"/>
+      <c r="G56" s="265"/>
     </row>
     <row r="57" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A57" s="49"/>
@@ -9136,7 +9192,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G57" s="271"/>
+      <c r="G57" s="265"/>
     </row>
     <row r="58" s="244" customFormat="1" spans="1:7">
       <c r="A58" s="49"/>
@@ -9148,7 +9204,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G58" s="271"/>
+      <c r="G58" s="265"/>
     </row>
     <row r="59" s="244" customFormat="1" spans="1:7">
       <c r="A59" s="204"/>
@@ -9160,7 +9216,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G59" s="271">
+      <c r="G59" s="265">
         <f>SUM(F59:F60)</f>
         <v>0</v>
       </c>
@@ -9175,7 +9231,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G60" s="271"/>
+      <c r="G60" s="265"/>
     </row>
     <row r="61" s="244" customFormat="1" spans="1:7">
       <c r="A61" s="202"/>
@@ -9187,7 +9243,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G61" s="271">
+      <c r="G61" s="265">
         <f>SUM(F61:F63)</f>
         <v>0</v>
       </c>
@@ -9202,7 +9258,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G62" s="271"/>
+      <c r="G62" s="265"/>
     </row>
     <row r="63" s="244" customFormat="1" spans="1:7">
       <c r="A63" s="262"/>
@@ -9214,7 +9270,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G63" s="271"/>
+      <c r="G63" s="265"/>
     </row>
     <row r="64" s="244" customFormat="1" spans="1:7">
       <c r="A64" s="49"/>
@@ -9226,7 +9282,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G64" s="271">
+      <c r="G64" s="265">
         <f>SUM(F64:F68)</f>
         <v>0</v>
       </c>
@@ -9241,7 +9297,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G65" s="271"/>
+      <c r="G65" s="265"/>
     </row>
     <row r="66" s="244" customFormat="1" spans="1:7">
       <c r="A66" s="49"/>
@@ -9253,7 +9309,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G66" s="271"/>
+      <c r="G66" s="265"/>
     </row>
     <row r="67" s="244" customFormat="1" spans="1:7">
       <c r="A67" s="49"/>
@@ -9265,7 +9321,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G67" s="271"/>
+      <c r="G67" s="265"/>
     </row>
     <row r="68" s="244" customFormat="1" spans="1:8">
       <c r="A68" s="49"/>
@@ -9277,8 +9333,8 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G68" s="271"/>
-      <c r="H68" s="274"/>
+      <c r="G68" s="265"/>
+      <c r="H68" s="268"/>
     </row>
     <row r="69" s="244" customFormat="1" ht="15.75" spans="1:14">
       <c r="A69" s="49"/>
@@ -9290,17 +9346,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G69" s="271">
+      <c r="G69" s="265">
         <f>SUM(F69)</f>
         <v>0</v>
       </c>
-      <c r="H69" s="274"/>
-      <c r="I69" s="279"/>
-      <c r="J69" s="280"/>
-      <c r="K69" s="281"/>
-      <c r="L69" s="282"/>
-      <c r="M69" s="282"/>
-      <c r="N69" s="283"/>
+      <c r="H69" s="268"/>
+      <c r="I69" s="273"/>
+      <c r="J69" s="274"/>
+      <c r="K69" s="275"/>
+      <c r="L69" s="276"/>
+      <c r="M69" s="276"/>
+      <c r="N69" s="277"/>
     </row>
     <row r="70" s="244" customFormat="1" ht="15.75" spans="1:14">
       <c r="A70" s="202"/>
@@ -9312,16 +9368,16 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G70" s="271">
+      <c r="G70" s="265">
         <f>SUM(F70:F72)</f>
         <v>0</v>
       </c>
-      <c r="I70" s="284"/>
-      <c r="J70" s="280"/>
-      <c r="K70" s="281"/>
-      <c r="L70" s="282"/>
-      <c r="M70" s="282"/>
-      <c r="N70" s="282"/>
+      <c r="I70" s="278"/>
+      <c r="J70" s="274"/>
+      <c r="K70" s="275"/>
+      <c r="L70" s="276"/>
+      <c r="M70" s="276"/>
+      <c r="N70" s="276"/>
     </row>
     <row r="71" s="244" customFormat="1" ht="15.75" spans="1:14">
       <c r="A71" s="204"/>
@@ -9333,13 +9389,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G71" s="271"/>
-      <c r="I71" s="284"/>
-      <c r="J71" s="280"/>
-      <c r="K71" s="281"/>
-      <c r="L71" s="282"/>
-      <c r="M71" s="282"/>
-      <c r="N71" s="282"/>
+      <c r="G71" s="265"/>
+      <c r="I71" s="278"/>
+      <c r="J71" s="274"/>
+      <c r="K71" s="275"/>
+      <c r="L71" s="276"/>
+      <c r="M71" s="276"/>
+      <c r="N71" s="276"/>
     </row>
     <row r="72" s="244" customFormat="1" ht="15.75" spans="1:14">
       <c r="A72" s="262"/>
@@ -9351,25 +9407,25 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G72" s="271"/>
-      <c r="I72" s="284"/>
-      <c r="J72" s="280"/>
-      <c r="K72" s="281"/>
-      <c r="L72" s="282"/>
-      <c r="M72" s="282"/>
-      <c r="N72" s="282"/>
+      <c r="G72" s="265"/>
+      <c r="I72" s="278"/>
+      <c r="J72" s="274"/>
+      <c r="K72" s="275"/>
+      <c r="L72" s="276"/>
+      <c r="M72" s="276"/>
+      <c r="N72" s="276"/>
     </row>
     <row r="73" s="244" customFormat="1" spans="1:7">
       <c r="A73" s="202"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="275"/>
+      <c r="C73" s="269"/>
       <c r="D73" s="114"/>
       <c r="E73" s="256"/>
       <c r="F73" s="256">
         <f t="shared" ref="F73:F84" si="4">D73*E73</f>
         <v>0</v>
       </c>
-      <c r="G73" s="271">
+      <c r="G73" s="265">
         <f>SUM(F73:F79)</f>
         <v>0</v>
       </c>
@@ -9377,86 +9433,86 @@
     <row r="74" s="244" customFormat="1" spans="1:7">
       <c r="A74" s="204"/>
       <c r="B74" s="42"/>
-      <c r="C74" s="275"/>
+      <c r="C74" s="269"/>
       <c r="D74" s="114"/>
       <c r="E74" s="256"/>
       <c r="F74" s="256">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G74" s="271"/>
+      <c r="G74" s="265"/>
     </row>
     <row r="75" s="244" customFormat="1" spans="1:7">
       <c r="A75" s="204"/>
       <c r="B75" s="42"/>
-      <c r="C75" s="275"/>
+      <c r="C75" s="269"/>
       <c r="D75" s="114"/>
       <c r="E75" s="256"/>
       <c r="F75" s="256">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G75" s="271"/>
+      <c r="G75" s="265"/>
     </row>
     <row r="76" s="244" customFormat="1" spans="1:7">
       <c r="A76" s="204"/>
       <c r="B76" s="42"/>
-      <c r="C76" s="275"/>
+      <c r="C76" s="269"/>
       <c r="D76" s="114"/>
       <c r="E76" s="256"/>
       <c r="F76" s="256">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G76" s="271"/>
+      <c r="G76" s="265"/>
     </row>
     <row r="77" s="244" customFormat="1" spans="1:7">
       <c r="A77" s="204"/>
       <c r="B77" s="42"/>
-      <c r="C77" s="275"/>
+      <c r="C77" s="269"/>
       <c r="D77" s="114"/>
       <c r="E77" s="256"/>
       <c r="F77" s="256">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G77" s="271"/>
+      <c r="G77" s="265"/>
     </row>
     <row r="78" s="244" customFormat="1" spans="1:7">
       <c r="A78" s="204"/>
       <c r="B78" s="42"/>
-      <c r="C78" s="275"/>
+      <c r="C78" s="269"/>
       <c r="D78" s="114"/>
       <c r="E78" s="256"/>
       <c r="F78" s="256">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G78" s="271"/>
+      <c r="G78" s="265"/>
     </row>
     <row r="79" s="244" customFormat="1" spans="1:7">
       <c r="A79" s="262"/>
       <c r="B79" s="260"/>
-      <c r="C79" s="275"/>
+      <c r="C79" s="269"/>
       <c r="D79" s="114"/>
       <c r="E79" s="256"/>
       <c r="F79" s="256">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G79" s="271"/>
+      <c r="G79" s="265"/>
     </row>
     <row r="80" s="244" customFormat="1" spans="1:7">
       <c r="A80" s="202"/>
       <c r="B80" s="36"/>
-      <c r="C80" s="275"/>
+      <c r="C80" s="269"/>
       <c r="D80" s="114"/>
       <c r="E80" s="256"/>
       <c r="F80" s="256">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G80" s="271">
+      <c r="G80" s="265">
         <f>SUM(F80:F84)</f>
         <v>0</v>
       </c>
@@ -9464,62 +9520,62 @@
     <row r="81" s="244" customFormat="1" spans="1:7">
       <c r="A81" s="204"/>
       <c r="B81" s="42"/>
-      <c r="C81" s="275"/>
+      <c r="C81" s="269"/>
       <c r="D81" s="114"/>
       <c r="E81" s="256"/>
       <c r="F81" s="256">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G81" s="271"/>
+      <c r="G81" s="265"/>
     </row>
     <row r="82" s="244" customFormat="1" spans="1:7">
       <c r="A82" s="204"/>
       <c r="B82" s="42"/>
-      <c r="C82" s="275"/>
+      <c r="C82" s="269"/>
       <c r="D82" s="114"/>
       <c r="E82" s="256"/>
       <c r="F82" s="256">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G82" s="271"/>
+      <c r="G82" s="265"/>
     </row>
     <row r="83" s="244" customFormat="1" spans="1:7">
       <c r="A83" s="204"/>
       <c r="B83" s="42"/>
-      <c r="C83" s="275"/>
+      <c r="C83" s="269"/>
       <c r="D83" s="114"/>
       <c r="E83" s="256"/>
       <c r="F83" s="256">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G83" s="271"/>
+      <c r="G83" s="265"/>
     </row>
     <row r="84" s="244" customFormat="1" spans="1:7">
       <c r="A84" s="262"/>
       <c r="B84" s="260"/>
-      <c r="C84" s="275"/>
+      <c r="C84" s="269"/>
       <c r="D84" s="114"/>
       <c r="E84" s="256"/>
       <c r="F84" s="256">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G84" s="271"/>
+      <c r="G84" s="265"/>
     </row>
     <row r="85" s="244" customFormat="1" spans="1:7">
       <c r="A85" s="202"/>
       <c r="B85" s="36"/>
-      <c r="C85" s="275"/>
+      <c r="C85" s="269"/>
       <c r="D85" s="114"/>
       <c r="E85" s="256"/>
       <c r="F85" s="256">
         <f t="shared" ref="F85:F93" si="5">D85*E85</f>
         <v>0</v>
       </c>
-      <c r="G85" s="271">
+      <c r="G85" s="265">
         <f>SUM(F85:F90)</f>
         <v>0</v>
       </c>
@@ -9527,74 +9583,74 @@
     <row r="86" s="244" customFormat="1" spans="1:7">
       <c r="A86" s="204"/>
       <c r="B86" s="42"/>
-      <c r="C86" s="275"/>
+      <c r="C86" s="269"/>
       <c r="D86" s="114"/>
       <c r="E86" s="256"/>
       <c r="F86" s="256">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G86" s="271"/>
+      <c r="G86" s="265"/>
     </row>
     <row r="87" s="244" customFormat="1" spans="1:7">
       <c r="A87" s="204"/>
       <c r="B87" s="42"/>
-      <c r="C87" s="275"/>
+      <c r="C87" s="269"/>
       <c r="D87" s="114"/>
       <c r="E87" s="256"/>
       <c r="F87" s="256">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G87" s="271"/>
+      <c r="G87" s="265"/>
     </row>
     <row r="88" s="244" customFormat="1" spans="1:7">
       <c r="A88" s="204"/>
       <c r="B88" s="42"/>
-      <c r="C88" s="275"/>
+      <c r="C88" s="269"/>
       <c r="D88" s="114"/>
       <c r="E88" s="256"/>
       <c r="F88" s="256">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G88" s="271"/>
+      <c r="G88" s="265"/>
     </row>
     <row r="89" s="244" customFormat="1" spans="1:7">
       <c r="A89" s="204"/>
       <c r="B89" s="42"/>
-      <c r="C89" s="275"/>
+      <c r="C89" s="269"/>
       <c r="D89" s="114"/>
       <c r="E89" s="256"/>
       <c r="F89" s="256">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G89" s="271"/>
+      <c r="G89" s="265"/>
     </row>
     <row r="90" s="244" customFormat="1" spans="1:7">
       <c r="A90" s="262"/>
       <c r="B90" s="260"/>
-      <c r="C90" s="275"/>
+      <c r="C90" s="269"/>
       <c r="D90" s="114"/>
       <c r="E90" s="256"/>
       <c r="F90" s="256">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G90" s="271"/>
+      <c r="G90" s="265"/>
     </row>
     <row r="91" s="244" customFormat="1" spans="1:7">
       <c r="A91" s="202"/>
       <c r="B91" s="36"/>
-      <c r="C91" s="275"/>
+      <c r="C91" s="269"/>
       <c r="D91" s="114"/>
       <c r="E91" s="256"/>
       <c r="F91" s="256">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G91" s="271">
+      <c r="G91" s="265">
         <f>SUM(F91:F93)</f>
         <v>0</v>
       </c>
@@ -9602,38 +9658,38 @@
     <row r="92" s="244" customFormat="1" spans="1:7">
       <c r="A92" s="204"/>
       <c r="B92" s="42"/>
-      <c r="C92" s="275"/>
+      <c r="C92" s="269"/>
       <c r="D92" s="114"/>
       <c r="E92" s="256"/>
       <c r="F92" s="256">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G92" s="271"/>
+      <c r="G92" s="265"/>
     </row>
     <row r="93" s="244" customFormat="1" spans="1:7">
       <c r="A93" s="262"/>
       <c r="B93" s="260"/>
-      <c r="C93" s="275"/>
+      <c r="C93" s="269"/>
       <c r="D93" s="114"/>
       <c r="E93" s="256"/>
       <c r="F93" s="256">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G93" s="271"/>
+      <c r="G93" s="265"/>
     </row>
     <row r="94" s="244" customFormat="1" spans="1:7">
       <c r="A94" s="202"/>
       <c r="B94" s="36"/>
-      <c r="C94" s="275"/>
+      <c r="C94" s="269"/>
       <c r="D94" s="114"/>
       <c r="E94" s="256"/>
       <c r="F94" s="256">
         <f t="shared" ref="F94:F114" si="6">D94*E94</f>
         <v>0</v>
       </c>
-      <c r="G94" s="271">
+      <c r="G94" s="265">
         <f>SUM(F94:F99)</f>
         <v>0</v>
       </c>
@@ -9641,74 +9697,74 @@
     <row r="95" s="244" customFormat="1" spans="1:7">
       <c r="A95" s="204"/>
       <c r="B95" s="42"/>
-      <c r="C95" s="275"/>
+      <c r="C95" s="269"/>
       <c r="D95" s="114"/>
       <c r="E95" s="256"/>
       <c r="F95" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G95" s="271"/>
+      <c r="G95" s="265"/>
     </row>
     <row r="96" s="244" customFormat="1" spans="1:7">
       <c r="A96" s="204"/>
       <c r="B96" s="42"/>
-      <c r="C96" s="275"/>
+      <c r="C96" s="269"/>
       <c r="D96" s="114"/>
       <c r="E96" s="256"/>
       <c r="F96" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G96" s="271"/>
+      <c r="G96" s="265"/>
     </row>
     <row r="97" s="244" customFormat="1" spans="1:7">
       <c r="A97" s="204"/>
       <c r="B97" s="42"/>
-      <c r="C97" s="275"/>
+      <c r="C97" s="269"/>
       <c r="D97" s="114"/>
       <c r="E97" s="256"/>
       <c r="F97" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G97" s="271"/>
+      <c r="G97" s="265"/>
     </row>
     <row r="98" s="244" customFormat="1" spans="1:7">
       <c r="A98" s="204"/>
       <c r="B98" s="42"/>
-      <c r="C98" s="275"/>
+      <c r="C98" s="269"/>
       <c r="D98" s="114"/>
       <c r="E98" s="256"/>
       <c r="F98" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G98" s="271"/>
+      <c r="G98" s="265"/>
     </row>
     <row r="99" s="244" customFormat="1" spans="1:7">
       <c r="A99" s="262"/>
       <c r="B99" s="260"/>
-      <c r="C99" s="275"/>
+      <c r="C99" s="269"/>
       <c r="D99" s="114"/>
       <c r="E99" s="256"/>
       <c r="F99" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G99" s="271"/>
+      <c r="G99" s="265"/>
     </row>
     <row r="100" s="244" customFormat="1" spans="1:7">
       <c r="A100" s="202"/>
       <c r="B100" s="36"/>
-      <c r="C100" s="275"/>
+      <c r="C100" s="269"/>
       <c r="D100" s="114"/>
       <c r="E100" s="256"/>
       <c r="F100" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G100" s="271">
+      <c r="G100" s="265">
         <f>SUM(F100:F104)</f>
         <v>0</v>
       </c>
@@ -9716,62 +9772,62 @@
     <row r="101" s="244" customFormat="1" spans="1:7">
       <c r="A101" s="204"/>
       <c r="B101" s="42"/>
-      <c r="C101" s="275"/>
+      <c r="C101" s="269"/>
       <c r="D101" s="114"/>
       <c r="E101" s="256"/>
       <c r="F101" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G101" s="271"/>
+      <c r="G101" s="265"/>
     </row>
     <row r="102" s="244" customFormat="1" spans="1:7">
       <c r="A102" s="204"/>
       <c r="B102" s="42"/>
-      <c r="C102" s="275"/>
+      <c r="C102" s="269"/>
       <c r="D102" s="114"/>
       <c r="E102" s="256"/>
       <c r="F102" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G102" s="271"/>
+      <c r="G102" s="265"/>
     </row>
     <row r="103" s="244" customFormat="1" spans="1:7">
       <c r="A103" s="204"/>
       <c r="B103" s="42"/>
-      <c r="C103" s="275"/>
+      <c r="C103" s="269"/>
       <c r="D103" s="114"/>
       <c r="E103" s="256"/>
       <c r="F103" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G103" s="271"/>
+      <c r="G103" s="265"/>
     </row>
     <row r="104" s="244" customFormat="1" spans="1:7">
       <c r="A104" s="262"/>
       <c r="B104" s="260"/>
-      <c r="C104" s="275"/>
+      <c r="C104" s="269"/>
       <c r="D104" s="114"/>
       <c r="E104" s="256"/>
       <c r="F104" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G104" s="271"/>
+      <c r="G104" s="265"/>
     </row>
     <row r="105" s="244" customFormat="1" spans="1:7">
       <c r="A105" s="202"/>
       <c r="B105" s="36"/>
-      <c r="C105" s="275"/>
+      <c r="C105" s="269"/>
       <c r="D105" s="114"/>
       <c r="E105" s="256"/>
       <c r="F105" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G105" s="271">
+      <c r="G105" s="265">
         <f>SUM(F105:F110)</f>
         <v>0</v>
       </c>
@@ -9779,74 +9835,74 @@
     <row r="106" s="244" customFormat="1" spans="1:7">
       <c r="A106" s="204"/>
       <c r="B106" s="42"/>
-      <c r="C106" s="275"/>
+      <c r="C106" s="269"/>
       <c r="D106" s="114"/>
       <c r="E106" s="256"/>
       <c r="F106" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G106" s="271"/>
+      <c r="G106" s="265"/>
     </row>
     <row r="107" s="244" customFormat="1" spans="1:7">
       <c r="A107" s="204"/>
       <c r="B107" s="42"/>
-      <c r="C107" s="275"/>
+      <c r="C107" s="269"/>
       <c r="D107" s="114"/>
       <c r="E107" s="256"/>
       <c r="F107" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G107" s="271"/>
+      <c r="G107" s="265"/>
     </row>
     <row r="108" s="244" customFormat="1" spans="1:7">
       <c r="A108" s="204"/>
       <c r="B108" s="42"/>
-      <c r="C108" s="275"/>
+      <c r="C108" s="269"/>
       <c r="D108" s="114"/>
       <c r="E108" s="256"/>
       <c r="F108" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G108" s="271"/>
+      <c r="G108" s="265"/>
     </row>
     <row r="109" s="244" customFormat="1" spans="1:7">
       <c r="A109" s="204"/>
       <c r="B109" s="42"/>
-      <c r="C109" s="275"/>
+      <c r="C109" s="269"/>
       <c r="D109" s="114"/>
       <c r="E109" s="256"/>
       <c r="F109" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G109" s="271"/>
+      <c r="G109" s="265"/>
     </row>
     <row r="110" s="244" customFormat="1" spans="1:7">
       <c r="A110" s="262"/>
       <c r="B110" s="260"/>
-      <c r="C110" s="275"/>
+      <c r="C110" s="269"/>
       <c r="D110" s="114"/>
       <c r="E110" s="256"/>
       <c r="F110" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G110" s="271"/>
+      <c r="G110" s="265"/>
     </row>
     <row r="111" s="244" customFormat="1" spans="1:7">
       <c r="A111" s="202"/>
       <c r="B111" s="36"/>
-      <c r="C111" s="275"/>
+      <c r="C111" s="269"/>
       <c r="D111" s="114"/>
       <c r="E111" s="256"/>
       <c r="F111" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G111" s="271">
+      <c r="G111" s="265">
         <f>SUM(F111:F114)</f>
         <v>0</v>
       </c>
@@ -9854,50 +9910,50 @@
     <row r="112" s="244" customFormat="1" spans="1:7">
       <c r="A112" s="204"/>
       <c r="B112" s="42"/>
-      <c r="C112" s="275"/>
+      <c r="C112" s="269"/>
       <c r="D112" s="114"/>
       <c r="E112" s="256"/>
       <c r="F112" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G112" s="271"/>
+      <c r="G112" s="265"/>
     </row>
     <row r="113" s="244" customFormat="1" spans="1:7">
       <c r="A113" s="204"/>
       <c r="B113" s="42"/>
-      <c r="C113" s="275"/>
+      <c r="C113" s="269"/>
       <c r="D113" s="114"/>
       <c r="E113" s="256"/>
       <c r="F113" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G113" s="271"/>
+      <c r="G113" s="265"/>
     </row>
     <row r="114" s="244" customFormat="1" spans="1:7">
       <c r="A114" s="204"/>
       <c r="B114" s="42"/>
-      <c r="C114" s="275"/>
+      <c r="C114" s="269"/>
       <c r="D114" s="114"/>
       <c r="E114" s="256"/>
       <c r="F114" s="256">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G114" s="271"/>
+      <c r="G114" s="265"/>
     </row>
     <row r="115" s="244" customFormat="1" spans="1:7">
       <c r="A115" s="202"/>
       <c r="B115" s="36"/>
-      <c r="C115" s="275"/>
+      <c r="C115" s="269"/>
       <c r="D115" s="114"/>
       <c r="E115" s="256"/>
       <c r="F115" s="256">
         <f t="shared" ref="F115:F117" si="7">D115*E115</f>
         <v>0</v>
       </c>
-      <c r="G115" s="271">
+      <c r="G115" s="265">
         <f>SUM(F115:F117)</f>
         <v>0</v>
       </c>
@@ -9905,36 +9961,36 @@
     <row r="116" s="244" customFormat="1" spans="1:7">
       <c r="A116" s="204"/>
       <c r="B116" s="42"/>
-      <c r="C116" s="275"/>
+      <c r="C116" s="269"/>
       <c r="D116" s="114"/>
       <c r="E116" s="256"/>
       <c r="F116" s="256">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G116" s="271"/>
+      <c r="G116" s="265"/>
     </row>
     <row r="117" s="244" customFormat="1" spans="1:7">
       <c r="A117" s="262"/>
       <c r="B117" s="260"/>
-      <c r="C117" s="275"/>
+      <c r="C117" s="269"/>
       <c r="D117" s="114"/>
       <c r="E117" s="256"/>
       <c r="F117" s="256">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G117" s="271"/>
+      <c r="G117" s="265"/>
     </row>
     <row r="118" s="244" customFormat="1" spans="1:7">
-      <c r="A118" s="276" t="s">
-        <v>34</v>
+      <c r="A118" s="270" t="s">
+        <v>40</v>
       </c>
       <c r="B118" s="125"/>
-      <c r="C118" s="277"/>
+      <c r="C118" s="271"/>
       <c r="D118" s="125"/>
       <c r="E118" s="125"/>
-      <c r="F118" s="278"/>
+      <c r="F118" s="272"/>
       <c r="G118" s="60">
         <f>SUM(G2:G117)</f>
         <v>959000</v>
@@ -10219,7 +10275,7 @@
       <c r="D153" s="248"/>
       <c r="E153" s="249"/>
       <c r="G153" s="245"/>
-      <c r="H153" s="274"/>
+      <c r="H153" s="268"/>
     </row>
   </sheetData>
   <mergeCells count="62">
@@ -10309,16 +10365,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>3</v>
@@ -10335,7 +10391,7 @@
         <v>12340</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D2" s="16">
         <v>20</v>
@@ -10357,7 +10413,7 @@
         <v>12357</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D3" s="16">
         <v>20</v>
@@ -10379,7 +10435,7 @@
         <v>11374</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D4" s="16">
         <v>20</v>
@@ -10511,7 +10567,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="224" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F1" s="224" t="s">
         <v>5</v>
@@ -10559,7 +10615,7 @@
     <row r="4" s="217" customFormat="1" spans="1:7">
       <c r="A4" s="230"/>
       <c r="B4" s="226" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C4" s="227">
         <v>0.3</v>
@@ -10577,7 +10633,7 @@
     <row r="5" s="217" customFormat="1" spans="1:6">
       <c r="A5" s="230"/>
       <c r="B5" s="226" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C5" s="227">
         <v>1</v>
@@ -10629,7 +10685,7 @@
     <row r="8" s="217" customFormat="1" spans="1:6">
       <c r="A8" s="230"/>
       <c r="B8" s="226" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C8" s="227">
         <v>8</v>
@@ -10663,7 +10719,7 @@
     <row r="10" s="217" customFormat="1" spans="1:6">
       <c r="A10" s="233"/>
       <c r="B10" s="226" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C10" s="227">
         <v>2</v>
@@ -10720,7 +10776,7 @@
     <row r="13" s="217" customFormat="1" spans="1:6">
       <c r="A13" s="230"/>
       <c r="B13" s="226" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C13" s="227">
         <v>8</v>
@@ -10771,7 +10827,7 @@
     <row r="16" s="217" customFormat="1" spans="1:6">
       <c r="A16" s="230"/>
       <c r="B16" s="226" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C16" s="227">
         <v>2</v>
@@ -10805,7 +10861,7 @@
     <row r="18" s="217" customFormat="1" spans="1:6">
       <c r="A18" s="230"/>
       <c r="B18" s="226" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C18" s="227">
         <v>1</v>
@@ -10839,7 +10895,7 @@
     <row r="20" s="217" customFormat="1" spans="1:6">
       <c r="A20" s="233"/>
       <c r="B20" s="226" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C20" s="227">
         <v>1</v>
@@ -12859,19 +12915,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>4</v>
@@ -12885,10 +12941,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="211" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D2" s="16">
         <v>3</v>
@@ -13029,31 +13085,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="176" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="176" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E1" s="176" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="176" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G1" s="176" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H1" s="176" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I1" s="176" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="176" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" ht="160" customHeight="1" spans="1:10">
@@ -13431,16 +13487,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="166" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="166" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="166" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E1" s="166" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" s="166" t="s">
         <v>3</v>
@@ -13502,22 +13558,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="135" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="135" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="135" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E1" s="135" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" s="135" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="135" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H1" s="136" t="s">
         <v>5</v>
@@ -13528,10 +13584,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="137" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C2" s="138" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D2" s="139">
         <v>5</v>
@@ -13604,7 +13660,7 @@
       </c>
       <c r="E7" s="153"/>
       <c r="F7" s="154" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G7" s="154"/>
       <c r="H7" s="154">
@@ -13633,7 +13689,7 @@
       <c r="C9" s="160"/>
       <c r="D9" s="160"/>
       <c r="E9" s="161" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F9" s="162">
         <f>SUM(E8)</f>
@@ -13709,16 +13765,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -13753,7 +13809,7 @@
     </row>
     <row r="4" ht="23.25" spans="1:7">
       <c r="A4" s="87" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B4" s="88"/>
       <c r="C4" s="88"/>

--- a/DECEMBER/DECEMBER BAR.xlsx
+++ b/DECEMBER/DECEMBER BAR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500"/>
+    <workbookView windowWidth="19635" windowHeight="7500" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="BUK BUNGA (Groceries)" sheetId="28" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="89">
   <si>
     <t>DATE</t>
   </si>
@@ -169,6 +169,15 @@
   </si>
   <si>
     <t>SARIWANGI</t>
+  </si>
+  <si>
+    <t>ALMOND MILK</t>
+  </si>
+  <si>
+    <t>CHERRY (BOTTLE)</t>
+  </si>
+  <si>
+    <t>CITRUN</t>
   </si>
   <si>
     <t>INV NO</t>
@@ -1359,7 +1368,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="301">
+  <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2197,10 +2206,16 @@
     <xf numFmtId="179" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="30" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2209,16 +2224,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="30" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="30" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2227,40 +2245,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="30" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="30" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="30" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="30" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="30" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2921,12 +2948,12 @@
   <dimension ref="A1:H378"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.5714285714286" style="246" customWidth="1"/>
+    <col min="1" max="1" width="17.5714285714286" style="279" customWidth="1"/>
     <col min="2" max="2" width="30.5714285714286" style="244" customWidth="1"/>
     <col min="3" max="3" width="9.14285714285714" style="245"/>
     <col min="4" max="4" width="15.8571428571429" style="244" customWidth="1"/>
     <col min="5" max="5" width="13.7142857142857" style="244" customWidth="1"/>
-    <col min="6" max="6" width="25.8666666666667" style="244" customWidth="1"/>
+    <col min="6" max="6" width="25.8666666666667" style="280" customWidth="1"/>
     <col min="7" max="8" width="13.1428571428571" style="244"/>
     <col min="9" max="16384" width="9.14285714285714" style="244"/>
   </cols>
@@ -2947,18 +2974,18 @@
       <c r="E1" s="252" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="279" t="s">
+      <c r="F1" s="281" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A2" s="280">
+      <c r="A2" s="282">
         <v>45995</v>
       </c>
-      <c r="B2" s="281" t="s">
+      <c r="B2" s="283" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="282">
+      <c r="C2" s="284">
         <v>5</v>
       </c>
       <c r="D2" s="7">
@@ -2968,17 +2995,17 @@
         <f t="shared" ref="E2:E7" si="0">SUM(C2*D2)</f>
         <v>100000</v>
       </c>
-      <c r="F2" s="283">
-        <f>SUM(E2:E13)</f>
-        <v>652000</v>
+      <c r="F2" s="285">
+        <f>SUM(E2:E12)</f>
+        <v>572000</v>
       </c>
     </row>
     <row r="3" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A3" s="284"/>
-      <c r="B3" s="281" t="s">
+      <c r="A3" s="286"/>
+      <c r="B3" s="283" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="282">
+      <c r="C3" s="284">
         <v>2</v>
       </c>
       <c r="D3" s="7">
@@ -2988,14 +3015,14 @@
         <f t="shared" si="0"/>
         <v>140000</v>
       </c>
-      <c r="F3" s="285"/>
+      <c r="F3" s="287"/>
     </row>
     <row r="4" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A4" s="284"/>
-      <c r="B4" s="281" t="s">
+      <c r="A4" s="286"/>
+      <c r="B4" s="283" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="282">
+      <c r="C4" s="284">
         <v>6</v>
       </c>
       <c r="D4" s="7">
@@ -3005,14 +3032,14 @@
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
-      <c r="F4" s="285"/>
+      <c r="F4" s="287"/>
     </row>
     <row r="5" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A5" s="284"/>
-      <c r="B5" s="281" t="s">
+      <c r="A5" s="286"/>
+      <c r="B5" s="283" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="282">
+      <c r="C5" s="284">
         <v>1</v>
       </c>
       <c r="D5" s="7">
@@ -3022,14 +3049,14 @@
         <f t="shared" ref="E5:E68" si="1">SUM(C5*D5)</f>
         <v>38000</v>
       </c>
-      <c r="F5" s="285"/>
+      <c r="F5" s="287"/>
     </row>
     <row r="6" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A6" s="284"/>
-      <c r="B6" s="281" t="s">
+      <c r="A6" s="286"/>
+      <c r="B6" s="283" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="282">
+      <c r="C6" s="284">
         <v>0.3</v>
       </c>
       <c r="D6" s="7">
@@ -3039,14 +3066,14 @@
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="287"/>
     </row>
     <row r="7" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A7" s="284"/>
-      <c r="B7" s="281" t="s">
+      <c r="A7" s="286"/>
+      <c r="B7" s="283" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="282">
+      <c r="C7" s="284">
         <v>1</v>
       </c>
       <c r="D7" s="7">
@@ -3056,14 +3083,14 @@
         <f t="shared" si="1"/>
         <v>25000</v>
       </c>
-      <c r="F7" s="285"/>
+      <c r="F7" s="287"/>
     </row>
     <row r="8" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A8" s="284"/>
-      <c r="B8" s="281" t="s">
+      <c r="A8" s="286"/>
+      <c r="B8" s="283" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="282">
+      <c r="C8" s="284">
         <v>1</v>
       </c>
       <c r="D8" s="7">
@@ -3073,14 +3100,14 @@
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="F8" s="285"/>
+      <c r="F8" s="287"/>
     </row>
     <row r="9" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A9" s="284"/>
-      <c r="B9" s="281" t="s">
+      <c r="A9" s="286"/>
+      <c r="B9" s="283" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="282">
+      <c r="C9" s="284">
         <v>1</v>
       </c>
       <c r="D9" s="7">
@@ -3090,14 +3117,14 @@
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
-      <c r="F9" s="285"/>
+      <c r="F9" s="287"/>
     </row>
     <row r="10" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A10" s="284"/>
-      <c r="B10" s="281" t="s">
+      <c r="A10" s="286"/>
+      <c r="B10" s="283" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="282">
+      <c r="C10" s="284">
         <v>3</v>
       </c>
       <c r="D10" s="7">
@@ -3107,14 +3134,14 @@
         <f t="shared" si="1"/>
         <v>72000</v>
       </c>
-      <c r="F10" s="285"/>
+      <c r="F10" s="287"/>
     </row>
     <row r="11" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A11" s="284"/>
-      <c r="B11" s="281" t="s">
+      <c r="A11" s="286"/>
+      <c r="B11" s="283" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="282">
+      <c r="C11" s="284">
         <v>1</v>
       </c>
       <c r="D11" s="7">
@@ -3124,14 +3151,14 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F11" s="285"/>
+      <c r="F11" s="287"/>
     </row>
     <row r="12" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A12" s="286"/>
-      <c r="B12" s="281" t="s">
+      <c r="A12" s="288"/>
+      <c r="B12" s="283" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="282">
+      <c r="C12" s="284">
         <v>1</v>
       </c>
       <c r="D12" s="7">
@@ -3141,16 +3168,16 @@
         <f t="shared" si="1"/>
         <v>49000</v>
       </c>
-      <c r="F12" s="267"/>
+      <c r="F12" s="289"/>
     </row>
     <row r="13" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A13" s="280">
+      <c r="A13" s="282">
         <v>45996</v>
       </c>
-      <c r="B13" s="281" t="s">
+      <c r="B13" s="283" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="282">
+      <c r="C13" s="284">
         <v>8</v>
       </c>
       <c r="D13" s="7">
@@ -3160,17 +3187,17 @@
         <f t="shared" si="1"/>
         <v>80000</v>
       </c>
-      <c r="F13" s="283">
+      <c r="F13" s="285">
         <f>SUM(E13:E25)</f>
         <v>730000</v>
       </c>
     </row>
     <row r="14" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A14" s="284"/>
-      <c r="B14" s="281" t="s">
+      <c r="A14" s="286"/>
+      <c r="B14" s="283" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="282">
+      <c r="C14" s="284">
         <v>2</v>
       </c>
       <c r="D14" s="7">
@@ -3180,14 +3207,14 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F14" s="285"/>
+      <c r="F14" s="287"/>
     </row>
     <row r="15" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A15" s="284"/>
-      <c r="B15" s="281" t="s">
+      <c r="A15" s="286"/>
+      <c r="B15" s="283" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="282">
+      <c r="C15" s="284">
         <v>2</v>
       </c>
       <c r="D15" s="7">
@@ -3197,14 +3224,14 @@
         <f t="shared" si="1"/>
         <v>70000</v>
       </c>
-      <c r="F15" s="285"/>
+      <c r="F15" s="287"/>
     </row>
     <row r="16" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A16" s="284"/>
-      <c r="B16" s="281" t="s">
+      <c r="A16" s="286"/>
+      <c r="B16" s="283" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="282">
+      <c r="C16" s="284">
         <v>0.5</v>
       </c>
       <c r="D16" s="7">
@@ -3213,14 +3240,14 @@
       <c r="E16" s="7">
         <v>48000</v>
       </c>
-      <c r="F16" s="285"/>
+      <c r="F16" s="287"/>
     </row>
     <row r="17" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A17" s="284"/>
-      <c r="B17" s="281" t="s">
+      <c r="A17" s="286"/>
+      <c r="B17" s="283" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="282">
+      <c r="C17" s="284">
         <v>1.1</v>
       </c>
       <c r="D17" s="7">
@@ -3229,14 +3256,14 @@
       <c r="E17" s="7">
         <v>42000</v>
       </c>
-      <c r="F17" s="285"/>
+      <c r="F17" s="287"/>
     </row>
     <row r="18" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A18" s="284"/>
-      <c r="B18" s="281" t="s">
+      <c r="A18" s="286"/>
+      <c r="B18" s="283" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="282">
+      <c r="C18" s="284">
         <v>5</v>
       </c>
       <c r="D18" s="7">
@@ -3246,32 +3273,32 @@
         <f t="shared" si="1"/>
         <v>120000</v>
       </c>
-      <c r="F18" s="285"/>
+      <c r="F18" s="287"/>
     </row>
     <row r="19" s="244" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A19" s="284"/>
-      <c r="B19" s="287" t="s">
+      <c r="A19" s="286"/>
+      <c r="B19" s="290" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="288">
+      <c r="C19" s="291">
         <v>3</v>
       </c>
-      <c r="D19" s="283">
+      <c r="D19" s="292">
         <v>40000</v>
       </c>
       <c r="E19" s="7">
         <f t="shared" si="1"/>
         <v>120000</v>
       </c>
-      <c r="F19" s="285"/>
+      <c r="F19" s="287"/>
       <c r="G19" s="268"/>
     </row>
     <row r="20" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A20" s="284"/>
-      <c r="B20" s="289" t="s">
+      <c r="A20" s="286"/>
+      <c r="B20" s="293" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="282">
+      <c r="C20" s="284">
         <v>1</v>
       </c>
       <c r="D20" s="256">
@@ -3281,14 +3308,14 @@
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F20" s="285"/>
+      <c r="F20" s="287"/>
     </row>
     <row r="21" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A21" s="284"/>
-      <c r="B21" s="289" t="s">
+      <c r="A21" s="286"/>
+      <c r="B21" s="293" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="282">
+      <c r="C21" s="284">
         <v>2</v>
       </c>
       <c r="D21" s="256">
@@ -3298,14 +3325,14 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F21" s="285"/>
+      <c r="F21" s="287"/>
     </row>
     <row r="22" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A22" s="284"/>
-      <c r="B22" s="289" t="s">
+      <c r="A22" s="286"/>
+      <c r="B22" s="293" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="282">
+      <c r="C22" s="284">
         <v>0.5</v>
       </c>
       <c r="D22" s="256">
@@ -3315,14 +3342,14 @@
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
-      <c r="F22" s="285"/>
+      <c r="F22" s="287"/>
     </row>
     <row r="23" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A23" s="284"/>
-      <c r="B23" s="289" t="s">
+      <c r="A23" s="286"/>
+      <c r="B23" s="293" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="282">
+      <c r="C23" s="284">
         <v>1</v>
       </c>
       <c r="D23" s="256">
@@ -3332,14 +3359,14 @@
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="F23" s="285"/>
+      <c r="F23" s="287"/>
     </row>
     <row r="24" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A24" s="284"/>
-      <c r="B24" s="289" t="s">
+      <c r="A24" s="286"/>
+      <c r="B24" s="293" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="282">
+      <c r="C24" s="284">
         <v>0.3</v>
       </c>
       <c r="D24" s="256">
@@ -3349,14 +3376,14 @@
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F24" s="285"/>
+      <c r="F24" s="287"/>
     </row>
     <row r="25" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A25" s="286"/>
-      <c r="B25" s="289" t="s">
+      <c r="A25" s="288"/>
+      <c r="B25" s="293" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="282">
+      <c r="C25" s="284">
         <v>1</v>
       </c>
       <c r="D25" s="256">
@@ -3366,16 +3393,16 @@
         <f t="shared" si="1"/>
         <v>35000</v>
       </c>
-      <c r="F25" s="267"/>
+      <c r="F25" s="289"/>
     </row>
     <row r="26" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A26" s="290">
+      <c r="A26" s="282">
         <v>45997</v>
       </c>
-      <c r="B26" s="289" t="s">
+      <c r="B26" s="293" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="282">
+      <c r="C26" s="284">
         <v>3.995</v>
       </c>
       <c r="D26" s="256">
@@ -3384,17 +3411,17 @@
       <c r="E26" s="7">
         <v>60000</v>
       </c>
-      <c r="F26" s="291">
+      <c r="F26" s="285">
         <f>SUM(E26:E34)</f>
         <v>422000</v>
       </c>
     </row>
     <row r="27" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A27" s="292"/>
-      <c r="B27" s="289" t="s">
+      <c r="A27" s="286"/>
+      <c r="B27" s="293" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="282">
+      <c r="C27" s="284">
         <v>2</v>
       </c>
       <c r="D27" s="256">
@@ -3404,14 +3431,14 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F27" s="293"/>
+      <c r="F27" s="287"/>
     </row>
     <row r="28" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A28" s="292"/>
-      <c r="B28" s="289" t="s">
+      <c r="A28" s="286"/>
+      <c r="B28" s="293" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="282">
+      <c r="C28" s="284">
         <v>0.5</v>
       </c>
       <c r="D28" s="256">
@@ -3420,14 +3447,14 @@
       <c r="E28" s="7">
         <v>18000</v>
       </c>
-      <c r="F28" s="293"/>
+      <c r="F28" s="287"/>
     </row>
     <row r="29" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A29" s="292"/>
-      <c r="B29" s="289" t="s">
+      <c r="A29" s="286"/>
+      <c r="B29" s="293" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="282">
+      <c r="C29" s="284">
         <v>0.1</v>
       </c>
       <c r="D29" s="256">
@@ -3437,14 +3464,14 @@
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
-      <c r="F29" s="293"/>
+      <c r="F29" s="287"/>
     </row>
     <row r="30" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A30" s="292"/>
-      <c r="B30" s="289" t="s">
+      <c r="A30" s="286"/>
+      <c r="B30" s="293" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="282">
+      <c r="C30" s="284">
         <v>0.5</v>
       </c>
       <c r="D30" s="256">
@@ -3454,14 +3481,14 @@
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
-      <c r="F30" s="293"/>
+      <c r="F30" s="287"/>
     </row>
     <row r="31" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A31" s="292"/>
-      <c r="B31" s="289" t="s">
+      <c r="A31" s="286"/>
+      <c r="B31" s="293" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="282">
+      <c r="C31" s="284">
         <v>4</v>
       </c>
       <c r="D31" s="256">
@@ -3471,14 +3498,14 @@
         <f t="shared" si="1"/>
         <v>80000</v>
       </c>
-      <c r="F31" s="293"/>
+      <c r="F31" s="287"/>
     </row>
     <row r="32" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A32" s="292"/>
-      <c r="B32" s="281" t="s">
+      <c r="A32" s="286"/>
+      <c r="B32" s="283" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="282">
+      <c r="C32" s="284">
         <v>4</v>
       </c>
       <c r="D32" s="7">
@@ -3488,14 +3515,14 @@
         <f t="shared" si="1"/>
         <v>96000</v>
       </c>
-      <c r="F32" s="293"/>
+      <c r="F32" s="287"/>
     </row>
     <row r="33" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A33" s="292"/>
-      <c r="B33" s="281" t="s">
+      <c r="A33" s="286"/>
+      <c r="B33" s="283" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="282">
+      <c r="C33" s="284">
         <v>2</v>
       </c>
       <c r="D33" s="7">
@@ -3505,14 +3532,14 @@
         <f t="shared" si="1"/>
         <v>80000</v>
       </c>
-      <c r="F33" s="293"/>
+      <c r="F33" s="287"/>
     </row>
     <row r="34" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A34" s="294"/>
-      <c r="B34" s="281" t="s">
+      <c r="A34" s="288"/>
+      <c r="B34" s="283" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="282">
+      <c r="C34" s="284">
         <v>1</v>
       </c>
       <c r="D34" s="7">
@@ -3522,3170 +3549,3323 @@
         <f t="shared" si="1"/>
         <v>25000</v>
       </c>
-      <c r="F34" s="295"/>
+      <c r="F34" s="289"/>
     </row>
     <row r="35" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A35" s="296"/>
-      <c r="B35" s="281"/>
-      <c r="C35" s="282"/>
-      <c r="D35" s="7"/>
+      <c r="A35" s="294">
+        <v>46000</v>
+      </c>
+      <c r="B35" s="293" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="284">
+        <v>2</v>
+      </c>
+      <c r="D35" s="7">
+        <v>20000</v>
+      </c>
       <c r="E35" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="256"/>
+        <v>40000</v>
+      </c>
+      <c r="F35" s="295">
+        <f>SUM(E36:E45)</f>
+        <v>572000</v>
+      </c>
     </row>
     <row r="36" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A36" s="280"/>
-      <c r="B36" s="281"/>
-      <c r="C36" s="282"/>
-      <c r="D36" s="7"/>
+      <c r="A36" s="296"/>
+      <c r="B36" s="293" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="284">
+        <v>2</v>
+      </c>
+      <c r="D36" s="7">
+        <v>35000</v>
+      </c>
       <c r="E36" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="283">
-        <f>SUM(E36:E41)</f>
-        <v>0</v>
-      </c>
+        <v>70000</v>
+      </c>
+      <c r="F36" s="297"/>
     </row>
     <row r="37" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A37" s="284"/>
-      <c r="B37" s="281"/>
-      <c r="C37" s="282"/>
-      <c r="D37" s="7"/>
+      <c r="A37" s="296"/>
+      <c r="B37" s="293" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="284">
+        <v>5</v>
+      </c>
+      <c r="D37" s="7">
+        <v>24000</v>
+      </c>
       <c r="E37" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="285"/>
+        <v>120000</v>
+      </c>
+      <c r="F37" s="297"/>
     </row>
     <row r="38" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A38" s="284"/>
-      <c r="B38" s="281"/>
-      <c r="C38" s="282"/>
-      <c r="D38" s="7"/>
+      <c r="A38" s="296"/>
+      <c r="B38" s="293" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="284">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7">
+        <v>49000</v>
+      </c>
       <c r="E38" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="285"/>
+        <v>49000</v>
+      </c>
+      <c r="F38" s="297"/>
     </row>
     <row r="39" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A39" s="284"/>
-      <c r="B39" s="281"/>
-      <c r="C39" s="282"/>
-      <c r="D39" s="7"/>
+      <c r="A39" s="296"/>
+      <c r="B39" s="293" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="284">
+        <v>1</v>
+      </c>
+      <c r="D39" s="7">
+        <v>65000</v>
+      </c>
       <c r="E39" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F39" s="285"/>
+        <v>65000</v>
+      </c>
+      <c r="F39" s="297"/>
     </row>
     <row r="40" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A40" s="284"/>
-      <c r="B40" s="281"/>
-      <c r="C40" s="282"/>
-      <c r="D40" s="7"/>
+      <c r="A40" s="296"/>
+      <c r="B40" s="293" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="284">
+        <v>0.5</v>
+      </c>
+      <c r="D40" s="7">
+        <v>95000</v>
+      </c>
       <c r="E40" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="285"/>
+        <v>48000</v>
+      </c>
+      <c r="F40" s="297"/>
     </row>
     <row r="41" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A41" s="286"/>
-      <c r="B41" s="281"/>
-      <c r="C41" s="282"/>
-      <c r="D41" s="7"/>
+      <c r="A41" s="296"/>
+      <c r="B41" s="293" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="284">
+        <v>1</v>
+      </c>
+      <c r="D41" s="7">
+        <v>15000</v>
+      </c>
       <c r="E41" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F41" s="267"/>
+        <v>15000</v>
+      </c>
+      <c r="F41" s="297"/>
     </row>
     <row r="42" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A42" s="280"/>
-      <c r="B42" s="281"/>
-      <c r="C42" s="282"/>
-      <c r="D42" s="7"/>
+      <c r="A42" s="296"/>
+      <c r="B42" s="293" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="284">
+        <v>9</v>
+      </c>
+      <c r="D42" s="7">
+        <v>10000</v>
+      </c>
       <c r="E42" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="283">
-        <f>SUM(E42:E47)</f>
-        <v>0</v>
-      </c>
+        <v>90000</v>
+      </c>
+      <c r="F42" s="297"/>
     </row>
     <row r="43" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A43" s="284"/>
-      <c r="B43" s="281"/>
-      <c r="C43" s="282"/>
-      <c r="D43" s="7"/>
+      <c r="A43" s="298"/>
+      <c r="B43" s="283" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="284">
+        <v>1</v>
+      </c>
+      <c r="D43" s="7">
+        <v>70000</v>
+      </c>
       <c r="E43" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="285"/>
+        <v>70000</v>
+      </c>
+      <c r="F43" s="297"/>
     </row>
     <row r="44" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A44" s="284"/>
-      <c r="B44" s="281"/>
-      <c r="C44" s="282"/>
-      <c r="D44" s="7"/>
+      <c r="A44" s="298"/>
+      <c r="B44" s="283" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="284">
+        <v>2</v>
+      </c>
+      <c r="D44" s="7">
+        <v>20000</v>
+      </c>
       <c r="E44" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F44" s="285"/>
+        <v>40000</v>
+      </c>
+      <c r="F44" s="297"/>
     </row>
     <row r="45" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A45" s="284"/>
-      <c r="B45" s="281"/>
-      <c r="C45" s="282"/>
-      <c r="D45" s="7"/>
+      <c r="A45" s="299"/>
+      <c r="B45" s="283" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="284">
+        <v>1</v>
+      </c>
+      <c r="D45" s="7">
+        <v>5000</v>
+      </c>
       <c r="E45" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F45" s="285"/>
+        <v>5000</v>
+      </c>
+      <c r="F45" s="300"/>
     </row>
     <row r="46" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A46" s="284"/>
-      <c r="B46" s="281"/>
-      <c r="C46" s="282"/>
+      <c r="A46" s="301"/>
+      <c r="B46" s="283"/>
+      <c r="C46" s="284"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F46" s="285"/>
+      <c r="F46" s="302"/>
     </row>
     <row r="47" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A47" s="286"/>
-      <c r="B47" s="281"/>
-      <c r="C47" s="282"/>
+      <c r="A47" s="301"/>
+      <c r="B47" s="283"/>
+      <c r="C47" s="284"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F47" s="267"/>
+      <c r="F47" s="302"/>
     </row>
     <row r="48" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A48" s="280"/>
-      <c r="B48" s="281"/>
-      <c r="C48" s="282"/>
+      <c r="A48" s="301"/>
+      <c r="B48" s="283"/>
+      <c r="C48" s="284"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F48" s="283">
+      <c r="F48" s="302">
         <f>SUM(E48:E56)</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A49" s="284"/>
-      <c r="B49" s="281"/>
-      <c r="C49" s="282"/>
+      <c r="A49" s="301"/>
+      <c r="B49" s="283"/>
+      <c r="C49" s="284"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F49" s="285"/>
+      <c r="F49" s="302"/>
     </row>
     <row r="50" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A50" s="284"/>
-      <c r="B50" s="281"/>
-      <c r="C50" s="282"/>
+      <c r="A50" s="301"/>
+      <c r="B50" s="283"/>
+      <c r="C50" s="284"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F50" s="285"/>
+      <c r="F50" s="302"/>
     </row>
     <row r="51" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A51" s="284"/>
-      <c r="B51" s="281"/>
-      <c r="C51" s="282"/>
+      <c r="A51" s="301"/>
+      <c r="B51" s="283"/>
+      <c r="C51" s="284"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F51" s="285"/>
+      <c r="F51" s="302"/>
     </row>
     <row r="52" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A52" s="284"/>
-      <c r="B52" s="281"/>
-      <c r="C52" s="282"/>
+      <c r="A52" s="301"/>
+      <c r="B52" s="283"/>
+      <c r="C52" s="284"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F52" s="285"/>
+      <c r="F52" s="302"/>
     </row>
     <row r="53" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A53" s="284"/>
-      <c r="B53" s="281"/>
-      <c r="C53" s="282"/>
+      <c r="A53" s="301"/>
+      <c r="B53" s="283"/>
+      <c r="C53" s="284"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F53" s="285"/>
+      <c r="F53" s="302"/>
     </row>
     <row r="54" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A54" s="284"/>
-      <c r="B54" s="281"/>
-      <c r="C54" s="282"/>
+      <c r="A54" s="301"/>
+      <c r="B54" s="283"/>
+      <c r="C54" s="284"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F54" s="285"/>
+      <c r="F54" s="302"/>
     </row>
     <row r="55" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A55" s="284"/>
-      <c r="B55" s="281"/>
-      <c r="C55" s="282"/>
+      <c r="A55" s="301"/>
+      <c r="B55" s="283"/>
+      <c r="C55" s="284"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F55" s="285"/>
+      <c r="F55" s="302"/>
     </row>
     <row r="56" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A56" s="286"/>
-      <c r="B56" s="281"/>
-      <c r="C56" s="282"/>
+      <c r="A56" s="301"/>
+      <c r="B56" s="283"/>
+      <c r="C56" s="284"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F56" s="267"/>
+      <c r="F56" s="302"/>
     </row>
     <row r="57" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A57" s="280"/>
-      <c r="B57" s="281"/>
-      <c r="C57" s="282"/>
+      <c r="A57" s="301"/>
+      <c r="B57" s="283"/>
+      <c r="C57" s="284"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F57" s="283">
+      <c r="F57" s="302">
         <f>SUM(E57:E71)</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A58" s="284"/>
-      <c r="B58" s="281"/>
-      <c r="C58" s="282"/>
+      <c r="A58" s="301"/>
+      <c r="B58" s="283"/>
+      <c r="C58" s="284"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F58" s="285"/>
+      <c r="F58" s="302"/>
     </row>
     <row r="59" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A59" s="284"/>
-      <c r="B59" s="281"/>
-      <c r="C59" s="282"/>
+      <c r="A59" s="301"/>
+      <c r="B59" s="283"/>
+      <c r="C59" s="284"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F59" s="285"/>
+      <c r="F59" s="302"/>
     </row>
     <row r="60" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A60" s="284"/>
-      <c r="B60" s="281"/>
-      <c r="C60" s="282"/>
+      <c r="A60" s="301"/>
+      <c r="B60" s="283"/>
+      <c r="C60" s="284"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F60" s="285"/>
+      <c r="F60" s="302"/>
     </row>
     <row r="61" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A61" s="284"/>
-      <c r="B61" s="281"/>
-      <c r="C61" s="282"/>
+      <c r="A61" s="301"/>
+      <c r="B61" s="283"/>
+      <c r="C61" s="284"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F61" s="285"/>
+      <c r="F61" s="302"/>
     </row>
     <row r="62" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A62" s="284"/>
-      <c r="B62" s="281"/>
-      <c r="C62" s="282"/>
+      <c r="A62" s="301"/>
+      <c r="B62" s="283"/>
+      <c r="C62" s="284"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F62" s="285"/>
+      <c r="F62" s="302"/>
     </row>
     <row r="63" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A63" s="284"/>
-      <c r="B63" s="281"/>
-      <c r="C63" s="282"/>
+      <c r="A63" s="301"/>
+      <c r="B63" s="283"/>
+      <c r="C63" s="284"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F63" s="285"/>
+      <c r="F63" s="302"/>
     </row>
     <row r="64" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A64" s="284"/>
-      <c r="B64" s="281"/>
-      <c r="C64" s="282"/>
+      <c r="A64" s="301"/>
+      <c r="B64" s="283"/>
+      <c r="C64" s="284"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F64" s="285"/>
+      <c r="F64" s="302"/>
     </row>
     <row r="65" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A65" s="284"/>
-      <c r="B65" s="281"/>
-      <c r="C65" s="282"/>
+      <c r="A65" s="301"/>
+      <c r="B65" s="283"/>
+      <c r="C65" s="284"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F65" s="285"/>
+      <c r="F65" s="302"/>
     </row>
     <row r="66" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A66" s="284"/>
-      <c r="B66" s="281"/>
-      <c r="C66" s="282"/>
+      <c r="A66" s="301"/>
+      <c r="B66" s="283"/>
+      <c r="C66" s="284"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F66" s="285"/>
+      <c r="F66" s="302"/>
     </row>
     <row r="67" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A67" s="284"/>
-      <c r="B67" s="281"/>
-      <c r="C67" s="282"/>
+      <c r="A67" s="301"/>
+      <c r="B67" s="283"/>
+      <c r="C67" s="284"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F67" s="285"/>
+      <c r="F67" s="302"/>
     </row>
     <row r="68" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A68" s="284"/>
-      <c r="B68" s="281"/>
-      <c r="C68" s="282"/>
+      <c r="A68" s="301"/>
+      <c r="B68" s="283"/>
+      <c r="C68" s="284"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F68" s="285"/>
+      <c r="F68" s="302"/>
     </row>
     <row r="69" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A69" s="284"/>
-      <c r="B69" s="281"/>
-      <c r="C69" s="282"/>
+      <c r="A69" s="301"/>
+      <c r="B69" s="283"/>
+      <c r="C69" s="284"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7">
         <f t="shared" ref="E69:E132" si="2">SUM(C69*D69)</f>
         <v>0</v>
       </c>
-      <c r="F69" s="285"/>
+      <c r="F69" s="302"/>
     </row>
     <row r="70" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A70" s="284"/>
-      <c r="B70" s="281"/>
-      <c r="C70" s="282"/>
+      <c r="A70" s="301"/>
+      <c r="B70" s="283"/>
+      <c r="C70" s="284"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F70" s="285"/>
+      <c r="F70" s="302"/>
     </row>
     <row r="71" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A71" s="286"/>
-      <c r="B71" s="281"/>
-      <c r="C71" s="282"/>
+      <c r="A71" s="301"/>
+      <c r="B71" s="283"/>
+      <c r="C71" s="284"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F71" s="267"/>
+      <c r="F71" s="302"/>
     </row>
     <row r="72" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A72" s="280"/>
-      <c r="B72" s="281"/>
-      <c r="C72" s="282"/>
+      <c r="A72" s="301"/>
+      <c r="B72" s="283"/>
+      <c r="C72" s="284"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F72" s="283">
+      <c r="F72" s="302">
         <f>-SUM(E72:E83)</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A73" s="284"/>
-      <c r="B73" s="281"/>
-      <c r="C73" s="282"/>
+      <c r="A73" s="301"/>
+      <c r="B73" s="283"/>
+      <c r="C73" s="284"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F73" s="285"/>
+      <c r="F73" s="302"/>
     </row>
     <row r="74" s="244" customFormat="1" ht="14" customHeight="1" spans="1:8">
-      <c r="A74" s="284"/>
-      <c r="B74" s="281"/>
-      <c r="C74" s="282"/>
+      <c r="A74" s="301"/>
+      <c r="B74" s="283"/>
+      <c r="C74" s="284"/>
       <c r="D74" s="7"/>
       <c r="E74" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F74" s="285"/>
+      <c r="F74" s="302"/>
       <c r="H74" s="268"/>
     </row>
     <row r="75" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A75" s="284"/>
-      <c r="B75" s="281"/>
-      <c r="C75" s="282"/>
+      <c r="A75" s="301"/>
+      <c r="B75" s="283"/>
+      <c r="C75" s="284"/>
       <c r="D75" s="7"/>
       <c r="E75" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F75" s="285"/>
+      <c r="F75" s="302"/>
     </row>
     <row r="76" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A76" s="284"/>
-      <c r="B76" s="281"/>
-      <c r="C76" s="282"/>
+      <c r="A76" s="301"/>
+      <c r="B76" s="283"/>
+      <c r="C76" s="284"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F76" s="285"/>
+      <c r="F76" s="302"/>
     </row>
     <row r="77" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A77" s="284"/>
-      <c r="B77" s="281"/>
-      <c r="C77" s="282"/>
+      <c r="A77" s="301"/>
+      <c r="B77" s="283"/>
+      <c r="C77" s="284"/>
       <c r="D77" s="7"/>
       <c r="E77" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F77" s="285"/>
+      <c r="F77" s="302"/>
     </row>
     <row r="78" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A78" s="284"/>
-      <c r="B78" s="281"/>
-      <c r="C78" s="282"/>
+      <c r="A78" s="301"/>
+      <c r="B78" s="283"/>
+      <c r="C78" s="284"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F78" s="285"/>
+      <c r="F78" s="302"/>
     </row>
     <row r="79" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A79" s="284"/>
-      <c r="B79" s="281"/>
-      <c r="C79" s="282"/>
+      <c r="A79" s="301"/>
+      <c r="B79" s="283"/>
+      <c r="C79" s="284"/>
       <c r="D79" s="7"/>
       <c r="E79" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F79" s="285"/>
+      <c r="F79" s="302"/>
     </row>
     <row r="80" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A80" s="284"/>
-      <c r="B80" s="281"/>
-      <c r="C80" s="282"/>
+      <c r="A80" s="301"/>
+      <c r="B80" s="283"/>
+      <c r="C80" s="284"/>
       <c r="D80" s="7"/>
       <c r="E80" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F80" s="285"/>
+      <c r="F80" s="302"/>
     </row>
     <row r="81" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A81" s="284"/>
-      <c r="B81" s="289"/>
-      <c r="C81" s="297"/>
+      <c r="A81" s="301"/>
+      <c r="B81" s="293"/>
+      <c r="C81" s="303"/>
       <c r="D81" s="7"/>
       <c r="E81" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F81" s="285"/>
+      <c r="F81" s="302"/>
     </row>
     <row r="82" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A82" s="284"/>
-      <c r="B82" s="289"/>
-      <c r="C82" s="297"/>
+      <c r="A82" s="301"/>
+      <c r="B82" s="293"/>
+      <c r="C82" s="303"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F82" s="285"/>
+      <c r="F82" s="302"/>
     </row>
     <row r="83" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A83" s="286"/>
-      <c r="B83" s="289"/>
-      <c r="C83" s="297"/>
+      <c r="A83" s="301"/>
+      <c r="B83" s="293"/>
+      <c r="C83" s="303"/>
       <c r="D83" s="7"/>
       <c r="E83" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F83" s="267"/>
+      <c r="F83" s="302"/>
     </row>
     <row r="84" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A84" s="280"/>
-      <c r="B84" s="289"/>
-      <c r="C84" s="297"/>
+      <c r="A84" s="301"/>
+      <c r="B84" s="293"/>
+      <c r="C84" s="303"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F84" s="283">
+      <c r="F84" s="302">
         <f>SUM(E84:E90)</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A85" s="284"/>
-      <c r="B85" s="289"/>
-      <c r="C85" s="297"/>
+      <c r="A85" s="301"/>
+      <c r="B85" s="293"/>
+      <c r="C85" s="303"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F85" s="285"/>
+      <c r="F85" s="302"/>
     </row>
     <row r="86" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A86" s="284"/>
-      <c r="B86" s="289"/>
-      <c r="C86" s="297"/>
+      <c r="A86" s="301"/>
+      <c r="B86" s="293"/>
+      <c r="C86" s="303"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F86" s="285"/>
+      <c r="F86" s="302"/>
     </row>
     <row r="87" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A87" s="284"/>
-      <c r="B87" s="289"/>
-      <c r="C87" s="297"/>
+      <c r="A87" s="301"/>
+      <c r="B87" s="293"/>
+      <c r="C87" s="303"/>
       <c r="D87" s="7"/>
       <c r="E87" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F87" s="285"/>
+      <c r="F87" s="302"/>
     </row>
     <row r="88" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A88" s="284"/>
-      <c r="B88" s="289"/>
-      <c r="C88" s="297"/>
+      <c r="A88" s="301"/>
+      <c r="B88" s="293"/>
+      <c r="C88" s="303"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F88" s="285"/>
+      <c r="F88" s="302"/>
     </row>
     <row r="89" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A89" s="284"/>
-      <c r="B89" s="289"/>
-      <c r="C89" s="297"/>
+      <c r="A89" s="301"/>
+      <c r="B89" s="293"/>
+      <c r="C89" s="303"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F89" s="285"/>
+      <c r="F89" s="302"/>
     </row>
     <row r="90" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A90" s="286"/>
-      <c r="B90" s="289"/>
-      <c r="C90" s="297"/>
+      <c r="A90" s="301"/>
+      <c r="B90" s="293"/>
+      <c r="C90" s="303"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F90" s="267"/>
+      <c r="F90" s="302"/>
     </row>
     <row r="91" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A91" s="280"/>
-      <c r="B91" s="289"/>
-      <c r="C91" s="297"/>
+      <c r="A91" s="301"/>
+      <c r="B91" s="293"/>
+      <c r="C91" s="303"/>
       <c r="D91" s="7"/>
       <c r="E91" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F91" s="283">
+      <c r="F91" s="302">
         <f>SUM(E91:E105)</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A92" s="284"/>
-      <c r="B92" s="289"/>
-      <c r="C92" s="297"/>
+      <c r="A92" s="301"/>
+      <c r="B92" s="293"/>
+      <c r="C92" s="303"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F92" s="285"/>
+      <c r="F92" s="302"/>
     </row>
     <row r="93" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A93" s="284"/>
-      <c r="B93" s="289"/>
-      <c r="C93" s="297"/>
+      <c r="A93" s="301"/>
+      <c r="B93" s="293"/>
+      <c r="C93" s="303"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F93" s="285"/>
+      <c r="F93" s="302"/>
     </row>
     <row r="94" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A94" s="284"/>
-      <c r="B94" s="289"/>
-      <c r="C94" s="297"/>
+      <c r="A94" s="301"/>
+      <c r="B94" s="293"/>
+      <c r="C94" s="303"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F94" s="285"/>
+      <c r="F94" s="302"/>
     </row>
     <row r="95" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A95" s="284"/>
-      <c r="B95" s="289"/>
-      <c r="C95" s="297"/>
+      <c r="A95" s="301"/>
+      <c r="B95" s="293"/>
+      <c r="C95" s="303"/>
       <c r="D95" s="7"/>
       <c r="E95" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F95" s="285"/>
+      <c r="F95" s="302"/>
     </row>
     <row r="96" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A96" s="284"/>
-      <c r="B96" s="289"/>
-      <c r="C96" s="297"/>
+      <c r="A96" s="301"/>
+      <c r="B96" s="293"/>
+      <c r="C96" s="303"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F96" s="285"/>
+      <c r="F96" s="302"/>
     </row>
     <row r="97" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A97" s="284"/>
-      <c r="B97" s="289"/>
-      <c r="C97" s="297"/>
+      <c r="A97" s="301"/>
+      <c r="B97" s="293"/>
+      <c r="C97" s="303"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F97" s="285"/>
+      <c r="F97" s="302"/>
     </row>
     <row r="98" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A98" s="284"/>
-      <c r="B98" s="289"/>
-      <c r="C98" s="297"/>
+      <c r="A98" s="301"/>
+      <c r="B98" s="293"/>
+      <c r="C98" s="303"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F98" s="285"/>
+      <c r="F98" s="302"/>
     </row>
     <row r="99" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A99" s="284"/>
-      <c r="B99" s="289"/>
-      <c r="C99" s="297"/>
+      <c r="A99" s="301"/>
+      <c r="B99" s="293"/>
+      <c r="C99" s="303"/>
       <c r="D99" s="7"/>
       <c r="E99" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F99" s="285"/>
+      <c r="F99" s="302"/>
     </row>
     <row r="100" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A100" s="284"/>
-      <c r="B100" s="289"/>
-      <c r="C100" s="297"/>
+      <c r="A100" s="301"/>
+      <c r="B100" s="293"/>
+      <c r="C100" s="303"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F100" s="285"/>
+      <c r="F100" s="302"/>
     </row>
     <row r="101" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A101" s="284"/>
-      <c r="B101" s="289"/>
-      <c r="C101" s="297"/>
+      <c r="A101" s="301"/>
+      <c r="B101" s="293"/>
+      <c r="C101" s="303"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F101" s="285"/>
+      <c r="F101" s="302"/>
     </row>
     <row r="102" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A102" s="284"/>
-      <c r="B102" s="289"/>
-      <c r="C102" s="297"/>
+      <c r="A102" s="301"/>
+      <c r="B102" s="293"/>
+      <c r="C102" s="303"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F102" s="285"/>
+      <c r="F102" s="302"/>
     </row>
     <row r="103" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A103" s="284"/>
-      <c r="B103" s="289"/>
-      <c r="C103" s="297"/>
+      <c r="A103" s="301"/>
+      <c r="B103" s="293"/>
+      <c r="C103" s="303"/>
       <c r="D103" s="7"/>
       <c r="E103" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F103" s="285"/>
+      <c r="F103" s="302"/>
     </row>
     <row r="104" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A104" s="284"/>
-      <c r="B104" s="289"/>
-      <c r="C104" s="297"/>
+      <c r="A104" s="301"/>
+      <c r="B104" s="293"/>
+      <c r="C104" s="303"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F104" s="285"/>
+      <c r="F104" s="302"/>
     </row>
     <row r="105" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A105" s="286"/>
-      <c r="B105" s="289"/>
-      <c r="C105" s="297"/>
+      <c r="A105" s="301"/>
+      <c r="B105" s="293"/>
+      <c r="C105" s="303"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F105" s="267"/>
+      <c r="F105" s="302"/>
     </row>
     <row r="106" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A106" s="280"/>
-      <c r="B106" s="289"/>
-      <c r="C106" s="297"/>
+      <c r="A106" s="301"/>
+      <c r="B106" s="293"/>
+      <c r="C106" s="303"/>
       <c r="D106" s="7"/>
       <c r="E106" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F106" s="283">
+      <c r="F106" s="302">
         <f>SUM(E106:E121)</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A107" s="284"/>
-      <c r="B107" s="289"/>
-      <c r="C107" s="297"/>
+      <c r="A107" s="301"/>
+      <c r="B107" s="293"/>
+      <c r="C107" s="303"/>
       <c r="D107" s="7"/>
       <c r="E107" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F107" s="285"/>
+      <c r="F107" s="302"/>
     </row>
     <row r="108" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A108" s="284"/>
-      <c r="B108" s="289"/>
-      <c r="C108" s="297"/>
+      <c r="A108" s="301"/>
+      <c r="B108" s="293"/>
+      <c r="C108" s="303"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F108" s="285"/>
+      <c r="F108" s="302"/>
     </row>
     <row r="109" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A109" s="284"/>
-      <c r="B109" s="289"/>
-      <c r="C109" s="297"/>
+      <c r="A109" s="301"/>
+      <c r="B109" s="293"/>
+      <c r="C109" s="303"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F109" s="285"/>
+      <c r="F109" s="302"/>
     </row>
     <row r="110" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A110" s="284"/>
-      <c r="B110" s="289"/>
-      <c r="C110" s="297"/>
+      <c r="A110" s="301"/>
+      <c r="B110" s="293"/>
+      <c r="C110" s="303"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F110" s="285"/>
+      <c r="F110" s="302"/>
     </row>
     <row r="111" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A111" s="284"/>
-      <c r="B111" s="289"/>
-      <c r="C111" s="297"/>
+      <c r="A111" s="301"/>
+      <c r="B111" s="293"/>
+      <c r="C111" s="303"/>
       <c r="D111" s="7"/>
       <c r="E111" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F111" s="285"/>
+      <c r="F111" s="302"/>
     </row>
     <row r="112" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A112" s="284"/>
-      <c r="B112" s="289"/>
-      <c r="C112" s="297"/>
+      <c r="A112" s="301"/>
+      <c r="B112" s="293"/>
+      <c r="C112" s="303"/>
       <c r="D112" s="7"/>
       <c r="E112" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F112" s="285"/>
+      <c r="F112" s="302"/>
     </row>
     <row r="113" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A113" s="284"/>
-      <c r="B113" s="289"/>
-      <c r="C113" s="297"/>
+      <c r="A113" s="301"/>
+      <c r="B113" s="293"/>
+      <c r="C113" s="303"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F113" s="285"/>
+      <c r="F113" s="302"/>
     </row>
     <row r="114" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A114" s="284"/>
-      <c r="B114" s="289"/>
-      <c r="C114" s="297"/>
+      <c r="A114" s="301"/>
+      <c r="B114" s="293"/>
+      <c r="C114" s="303"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F114" s="285"/>
+      <c r="F114" s="302"/>
     </row>
     <row r="115" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A115" s="284"/>
-      <c r="B115" s="289"/>
-      <c r="C115" s="297"/>
+      <c r="A115" s="301"/>
+      <c r="B115" s="293"/>
+      <c r="C115" s="303"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F115" s="285"/>
+      <c r="F115" s="302"/>
     </row>
     <row r="116" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A116" s="284"/>
-      <c r="B116" s="289"/>
-      <c r="C116" s="297"/>
+      <c r="A116" s="301"/>
+      <c r="B116" s="293"/>
+      <c r="C116" s="303"/>
       <c r="D116" s="7"/>
       <c r="E116" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F116" s="285"/>
+      <c r="F116" s="302"/>
     </row>
     <row r="117" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A117" s="284"/>
-      <c r="B117" s="289"/>
-      <c r="C117" s="297"/>
+      <c r="A117" s="301"/>
+      <c r="B117" s="293"/>
+      <c r="C117" s="303"/>
       <c r="D117" s="7"/>
       <c r="E117" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F117" s="285"/>
+      <c r="F117" s="302"/>
     </row>
     <row r="118" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A118" s="284"/>
-      <c r="B118" s="289"/>
-      <c r="C118" s="297"/>
+      <c r="A118" s="301"/>
+      <c r="B118" s="293"/>
+      <c r="C118" s="303"/>
       <c r="D118" s="7"/>
       <c r="E118" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F118" s="285"/>
+      <c r="F118" s="302"/>
     </row>
     <row r="119" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A119" s="284"/>
-      <c r="B119" s="289"/>
-      <c r="C119" s="297"/>
+      <c r="A119" s="301"/>
+      <c r="B119" s="293"/>
+      <c r="C119" s="303"/>
       <c r="D119" s="7"/>
       <c r="E119" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F119" s="285"/>
+      <c r="F119" s="302"/>
     </row>
     <row r="120" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A120" s="284"/>
-      <c r="B120" s="289"/>
-      <c r="C120" s="297"/>
+      <c r="A120" s="301"/>
+      <c r="B120" s="293"/>
+      <c r="C120" s="303"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F120" s="285"/>
+      <c r="F120" s="302"/>
     </row>
     <row r="121" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A121" s="286"/>
-      <c r="B121" s="289"/>
-      <c r="C121" s="297"/>
+      <c r="A121" s="301"/>
+      <c r="B121" s="293"/>
+      <c r="C121" s="303"/>
       <c r="D121" s="7"/>
       <c r="E121" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F121" s="267"/>
+      <c r="F121" s="302"/>
     </row>
     <row r="122" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A122" s="298"/>
-      <c r="B122" s="289"/>
-      <c r="C122" s="297"/>
+      <c r="A122" s="301"/>
+      <c r="B122" s="293"/>
+      <c r="C122" s="303"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F122" s="256">
+      <c r="F122" s="302">
         <f>SUM(E122)</f>
         <v>0</v>
       </c>
     </row>
     <row r="123" s="244" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A123" s="298"/>
-      <c r="B123" s="289"/>
-      <c r="C123" s="297"/>
+      <c r="A123" s="301"/>
+      <c r="B123" s="293"/>
+      <c r="C123" s="303"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F123" s="7">
+      <c r="F123" s="302">
         <f>SUM(E123:E127)</f>
         <v>0</v>
       </c>
       <c r="G123" s="268"/>
     </row>
     <row r="124" s="244" customFormat="1" spans="1:6">
-      <c r="A124" s="298"/>
-      <c r="B124" s="289"/>
-      <c r="C124" s="297"/>
+      <c r="A124" s="301"/>
+      <c r="B124" s="293"/>
+      <c r="C124" s="303"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F124" s="7"/>
+      <c r="F124" s="302"/>
     </row>
     <row r="125" s="244" customFormat="1" spans="1:6">
-      <c r="A125" s="298"/>
-      <c r="B125" s="289"/>
-      <c r="C125" s="297"/>
+      <c r="A125" s="301"/>
+      <c r="B125" s="293"/>
+      <c r="C125" s="303"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F125" s="7"/>
+      <c r="F125" s="302"/>
     </row>
     <row r="126" s="244" customFormat="1" spans="1:6">
-      <c r="A126" s="298"/>
-      <c r="B126" s="289"/>
-      <c r="C126" s="297"/>
+      <c r="A126" s="301"/>
+      <c r="B126" s="293"/>
+      <c r="C126" s="303"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F126" s="7"/>
+      <c r="F126" s="302"/>
     </row>
     <row r="127" s="244" customFormat="1" spans="1:6">
-      <c r="A127" s="298"/>
-      <c r="B127" s="289"/>
-      <c r="C127" s="297"/>
+      <c r="A127" s="301"/>
+      <c r="B127" s="293"/>
+      <c r="C127" s="303"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F127" s="7"/>
+      <c r="F127" s="302"/>
     </row>
     <row r="128" s="244" customFormat="1" spans="1:6">
-      <c r="A128" s="284"/>
-      <c r="B128" s="299"/>
-      <c r="C128" s="300"/>
+      <c r="A128" s="301"/>
+      <c r="B128" s="304"/>
+      <c r="C128" s="305"/>
       <c r="D128" s="267"/>
       <c r="E128" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F128" s="283">
+      <c r="F128" s="302">
         <f>SUM(E128:E134)</f>
         <v>0</v>
       </c>
     </row>
     <row r="129" s="244" customFormat="1" spans="1:6">
-      <c r="A129" s="284"/>
-      <c r="B129" s="289"/>
-      <c r="C129" s="297"/>
+      <c r="A129" s="301"/>
+      <c r="B129" s="293"/>
+      <c r="C129" s="303"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F129" s="285"/>
+      <c r="F129" s="302"/>
     </row>
     <row r="130" s="244" customFormat="1" spans="1:6">
-      <c r="A130" s="284"/>
-      <c r="B130" s="289"/>
-      <c r="C130" s="297"/>
+      <c r="A130" s="301"/>
+      <c r="B130" s="293"/>
+      <c r="C130" s="303"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F130" s="285"/>
+      <c r="F130" s="302"/>
     </row>
     <row r="131" s="244" customFormat="1" spans="1:6">
-      <c r="A131" s="284"/>
-      <c r="B131" s="289"/>
-      <c r="C131" s="297"/>
+      <c r="A131" s="301"/>
+      <c r="B131" s="293"/>
+      <c r="C131" s="303"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F131" s="285"/>
+      <c r="F131" s="302"/>
     </row>
     <row r="132" s="244" customFormat="1" spans="1:6">
-      <c r="A132" s="284"/>
-      <c r="B132" s="289"/>
-      <c r="C132" s="297"/>
+      <c r="A132" s="301"/>
+      <c r="B132" s="293"/>
+      <c r="C132" s="303"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F132" s="285"/>
+      <c r="F132" s="302"/>
     </row>
     <row r="133" s="244" customFormat="1" spans="1:6">
-      <c r="A133" s="284"/>
-      <c r="B133" s="289"/>
-      <c r="C133" s="297"/>
+      <c r="A133" s="301"/>
+      <c r="B133" s="293"/>
+      <c r="C133" s="303"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7">
         <f t="shared" ref="E133:E196" si="3">SUM(C133*D133)</f>
         <v>0</v>
       </c>
-      <c r="F133" s="285"/>
+      <c r="F133" s="302"/>
     </row>
     <row r="134" s="244" customFormat="1" spans="1:6">
-      <c r="A134" s="286"/>
-      <c r="B134" s="289"/>
-      <c r="C134" s="297"/>
-      <c r="D134" s="7"/>
+      <c r="A134" s="301"/>
+      <c r="B134" s="293"/>
+      <c r="C134" s="303"/>
+      <c r="D134" s="256"/>
       <c r="E134" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F134" s="267"/>
+      <c r="F134" s="302"/>
     </row>
     <row r="135" s="244" customFormat="1" spans="1:6">
-      <c r="A135" s="280"/>
-      <c r="B135" s="289"/>
-      <c r="C135" s="297"/>
+      <c r="A135" s="301"/>
+      <c r="B135" s="293"/>
+      <c r="C135" s="303"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F135" s="283">
+      <c r="F135" s="302">
         <f>SUM(E135:E142)</f>
         <v>0</v>
       </c>
     </row>
     <row r="136" s="244" customFormat="1" spans="1:6">
-      <c r="A136" s="284"/>
-      <c r="B136" s="289"/>
-      <c r="C136" s="297"/>
+      <c r="A136" s="301"/>
+      <c r="B136" s="293"/>
+      <c r="C136" s="303"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F136" s="285"/>
+      <c r="F136" s="302"/>
     </row>
     <row r="137" s="244" customFormat="1" spans="1:6">
-      <c r="A137" s="284"/>
-      <c r="B137" s="289"/>
-      <c r="C137" s="297"/>
+      <c r="A137" s="301"/>
+      <c r="B137" s="293"/>
+      <c r="C137" s="303"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F137" s="285"/>
+      <c r="F137" s="302"/>
     </row>
     <row r="138" s="244" customFormat="1" spans="1:6">
-      <c r="A138" s="284"/>
-      <c r="B138" s="289"/>
-      <c r="C138" s="297"/>
+      <c r="A138" s="301"/>
+      <c r="B138" s="293"/>
+      <c r="C138" s="303"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F138" s="285"/>
+      <c r="F138" s="302"/>
     </row>
     <row r="139" s="244" customFormat="1" spans="1:6">
-      <c r="A139" s="284"/>
-      <c r="B139" s="289"/>
-      <c r="C139" s="297"/>
+      <c r="A139" s="301"/>
+      <c r="B139" s="293"/>
+      <c r="C139" s="303"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F139" s="285"/>
+      <c r="F139" s="302"/>
     </row>
     <row r="140" s="244" customFormat="1" spans="1:6">
-      <c r="A140" s="284"/>
-      <c r="B140" s="289"/>
-      <c r="C140" s="297"/>
+      <c r="A140" s="301"/>
+      <c r="B140" s="293"/>
+      <c r="C140" s="303"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F140" s="285"/>
+      <c r="F140" s="302"/>
     </row>
     <row r="141" s="244" customFormat="1" spans="1:6">
-      <c r="A141" s="284"/>
-      <c r="B141" s="289"/>
-      <c r="C141" s="297"/>
+      <c r="A141" s="301"/>
+      <c r="B141" s="293"/>
+      <c r="C141" s="303"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F141" s="285"/>
+      <c r="F141" s="302"/>
     </row>
     <row r="142" s="244" customFormat="1" spans="1:6">
-      <c r="A142" s="286"/>
-      <c r="B142" s="289"/>
-      <c r="C142" s="297"/>
+      <c r="A142" s="301"/>
+      <c r="B142" s="293"/>
+      <c r="C142" s="303"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F142" s="267"/>
+      <c r="F142" s="302"/>
     </row>
     <row r="143" s="244" customFormat="1" spans="1:6">
-      <c r="A143" s="280"/>
-      <c r="B143" s="289"/>
-      <c r="C143" s="297"/>
+      <c r="A143" s="301"/>
+      <c r="B143" s="293"/>
+      <c r="C143" s="303"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F143" s="283">
+      <c r="F143" s="302">
         <f>SUM(E143:E149)</f>
         <v>0</v>
       </c>
     </row>
     <row r="144" s="244" customFormat="1" spans="1:6">
-      <c r="A144" s="284"/>
-      <c r="B144" s="289"/>
-      <c r="C144" s="297"/>
+      <c r="A144" s="301"/>
+      <c r="B144" s="293"/>
+      <c r="C144" s="303"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F144" s="285"/>
+      <c r="F144" s="302"/>
     </row>
     <row r="145" s="244" customFormat="1" spans="1:6">
-      <c r="A145" s="284"/>
-      <c r="B145" s="289"/>
-      <c r="C145" s="297"/>
+      <c r="A145" s="301"/>
+      <c r="B145" s="293"/>
+      <c r="C145" s="303"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F145" s="285"/>
+      <c r="F145" s="302"/>
     </row>
     <row r="146" s="244" customFormat="1" spans="1:6">
-      <c r="A146" s="284"/>
-      <c r="B146" s="289"/>
-      <c r="C146" s="297"/>
+      <c r="A146" s="301"/>
+      <c r="B146" s="293"/>
+      <c r="C146" s="303"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F146" s="285"/>
+      <c r="F146" s="302"/>
     </row>
     <row r="147" s="244" customFormat="1" spans="1:6">
-      <c r="A147" s="284"/>
-      <c r="B147" s="289"/>
-      <c r="C147" s="297"/>
+      <c r="A147" s="301"/>
+      <c r="B147" s="293"/>
+      <c r="C147" s="303"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F147" s="285"/>
+      <c r="F147" s="302"/>
     </row>
     <row r="148" s="244" customFormat="1" spans="1:6">
-      <c r="A148" s="284"/>
-      <c r="B148" s="289"/>
-      <c r="C148" s="297"/>
+      <c r="A148" s="301"/>
+      <c r="B148" s="293"/>
+      <c r="C148" s="303"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F148" s="285"/>
+      <c r="F148" s="302"/>
     </row>
     <row r="149" s="244" customFormat="1" spans="1:6">
-      <c r="A149" s="286"/>
-      <c r="B149" s="289"/>
-      <c r="C149" s="297"/>
+      <c r="A149" s="301"/>
+      <c r="B149" s="293"/>
+      <c r="C149" s="303"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F149" s="267"/>
+      <c r="F149" s="302"/>
     </row>
     <row r="150" s="244" customFormat="1" spans="1:6">
-      <c r="A150" s="280"/>
-      <c r="B150" s="289"/>
-      <c r="C150" s="297"/>
+      <c r="A150" s="301"/>
+      <c r="B150" s="293"/>
+      <c r="C150" s="303"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F150" s="283">
+      <c r="F150" s="302">
         <f>SUM(E150:E159)</f>
         <v>0</v>
       </c>
     </row>
     <row r="151" s="244" customFormat="1" spans="1:6">
-      <c r="A151" s="284"/>
-      <c r="B151" s="289"/>
-      <c r="C151" s="297"/>
+      <c r="A151" s="301"/>
+      <c r="B151" s="293"/>
+      <c r="C151" s="303"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F151" s="285"/>
+      <c r="F151" s="302"/>
     </row>
     <row r="152" s="244" customFormat="1" spans="1:6">
-      <c r="A152" s="284"/>
-      <c r="B152" s="289"/>
-      <c r="C152" s="297"/>
+      <c r="A152" s="301"/>
+      <c r="B152" s="293"/>
+      <c r="C152" s="303"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F152" s="285"/>
+      <c r="F152" s="302"/>
     </row>
     <row r="153" s="244" customFormat="1" spans="1:6">
-      <c r="A153" s="284"/>
-      <c r="B153" s="289"/>
-      <c r="C153" s="297"/>
+      <c r="A153" s="301"/>
+      <c r="B153" s="293"/>
+      <c r="C153" s="303"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F153" s="285"/>
+      <c r="F153" s="302"/>
     </row>
     <row r="154" s="244" customFormat="1" spans="1:6">
-      <c r="A154" s="284"/>
-      <c r="B154" s="289"/>
-      <c r="C154" s="297"/>
+      <c r="A154" s="301"/>
+      <c r="B154" s="293"/>
+      <c r="C154" s="303"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F154" s="285"/>
+      <c r="F154" s="302"/>
     </row>
     <row r="155" s="244" customFormat="1" spans="1:6">
-      <c r="A155" s="284"/>
-      <c r="B155" s="289"/>
-      <c r="C155" s="297"/>
+      <c r="A155" s="301"/>
+      <c r="B155" s="293"/>
+      <c r="C155" s="303"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F155" s="285"/>
+      <c r="F155" s="302"/>
     </row>
     <row r="156" s="244" customFormat="1" spans="1:6">
-      <c r="A156" s="284"/>
-      <c r="B156" s="289"/>
-      <c r="C156" s="297"/>
+      <c r="A156" s="301"/>
+      <c r="B156" s="293"/>
+      <c r="C156" s="303"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F156" s="285"/>
+      <c r="F156" s="302"/>
     </row>
     <row r="157" s="244" customFormat="1" spans="1:6">
-      <c r="A157" s="284"/>
-      <c r="B157" s="289"/>
-      <c r="C157" s="297"/>
+      <c r="A157" s="301"/>
+      <c r="B157" s="293"/>
+      <c r="C157" s="303"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F157" s="285"/>
+      <c r="F157" s="302"/>
     </row>
     <row r="158" s="244" customFormat="1" spans="1:6">
-      <c r="A158" s="284"/>
-      <c r="B158" s="289"/>
-      <c r="C158" s="297"/>
+      <c r="A158" s="301"/>
+      <c r="B158" s="293"/>
+      <c r="C158" s="303"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F158" s="285"/>
+      <c r="F158" s="302"/>
     </row>
     <row r="159" s="244" customFormat="1" spans="1:6">
-      <c r="A159" s="286"/>
-      <c r="B159" s="289"/>
-      <c r="C159" s="297"/>
+      <c r="A159" s="301"/>
+      <c r="B159" s="293"/>
+      <c r="C159" s="303"/>
       <c r="D159" s="7"/>
       <c r="E159" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F159" s="267"/>
+      <c r="F159" s="302"/>
     </row>
     <row r="160" s="244" customFormat="1" spans="1:6">
-      <c r="A160" s="280"/>
-      <c r="B160" s="289"/>
-      <c r="C160" s="297"/>
+      <c r="A160" s="301"/>
+      <c r="B160" s="293"/>
+      <c r="C160" s="303"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F160" s="283">
+      <c r="F160" s="302">
         <f>SUM(E160:E173)</f>
         <v>0</v>
       </c>
     </row>
     <row r="161" s="244" customFormat="1" spans="1:6">
-      <c r="A161" s="284"/>
-      <c r="B161" s="289"/>
-      <c r="C161" s="297"/>
+      <c r="A161" s="301"/>
+      <c r="B161" s="293"/>
+      <c r="C161" s="303"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F161" s="285"/>
+      <c r="F161" s="302"/>
     </row>
     <row r="162" s="244" customFormat="1" spans="1:6">
-      <c r="A162" s="284"/>
-      <c r="B162" s="289"/>
-      <c r="C162" s="297"/>
+      <c r="A162" s="301"/>
+      <c r="B162" s="293"/>
+      <c r="C162" s="303"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F162" s="285"/>
+      <c r="F162" s="302"/>
     </row>
     <row r="163" s="244" customFormat="1" spans="1:6">
-      <c r="A163" s="284"/>
-      <c r="B163" s="289"/>
-      <c r="C163" s="297"/>
+      <c r="A163" s="301"/>
+      <c r="B163" s="293"/>
+      <c r="C163" s="303"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F163" s="285"/>
+      <c r="F163" s="302"/>
     </row>
     <row r="164" s="244" customFormat="1" spans="1:6">
-      <c r="A164" s="284"/>
-      <c r="B164" s="289"/>
-      <c r="C164" s="297"/>
+      <c r="A164" s="301"/>
+      <c r="B164" s="293"/>
+      <c r="C164" s="303"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F164" s="285"/>
+      <c r="F164" s="302"/>
     </row>
     <row r="165" s="244" customFormat="1" spans="1:6">
-      <c r="A165" s="284"/>
-      <c r="B165" s="289"/>
-      <c r="C165" s="297"/>
+      <c r="A165" s="301"/>
+      <c r="B165" s="293"/>
+      <c r="C165" s="303"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F165" s="285"/>
+      <c r="F165" s="302"/>
     </row>
     <row r="166" s="244" customFormat="1" spans="1:6">
-      <c r="A166" s="284"/>
-      <c r="B166" s="289"/>
-      <c r="C166" s="297"/>
+      <c r="A166" s="301"/>
+      <c r="B166" s="293"/>
+      <c r="C166" s="303"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F166" s="285"/>
+      <c r="F166" s="302"/>
     </row>
     <row r="167" s="244" customFormat="1" spans="1:6">
-      <c r="A167" s="284"/>
-      <c r="B167" s="289"/>
-      <c r="C167" s="297"/>
+      <c r="A167" s="301"/>
+      <c r="B167" s="293"/>
+      <c r="C167" s="303"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F167" s="285"/>
+      <c r="F167" s="302"/>
     </row>
     <row r="168" s="244" customFormat="1" spans="1:6">
-      <c r="A168" s="284"/>
-      <c r="B168" s="289"/>
-      <c r="C168" s="297"/>
+      <c r="A168" s="301"/>
+      <c r="B168" s="293"/>
+      <c r="C168" s="303"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F168" s="285"/>
+      <c r="F168" s="302"/>
     </row>
     <row r="169" s="244" customFormat="1" spans="1:6">
-      <c r="A169" s="284"/>
-      <c r="B169" s="289"/>
-      <c r="C169" s="297"/>
+      <c r="A169" s="301"/>
+      <c r="B169" s="293"/>
+      <c r="C169" s="303"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F169" s="285"/>
+      <c r="F169" s="302"/>
     </row>
     <row r="170" s="244" customFormat="1" spans="1:6">
-      <c r="A170" s="284"/>
-      <c r="B170" s="289"/>
-      <c r="C170" s="297"/>
+      <c r="A170" s="301"/>
+      <c r="B170" s="293"/>
+      <c r="C170" s="303"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F170" s="285"/>
+      <c r="F170" s="302"/>
     </row>
     <row r="171" s="244" customFormat="1" spans="1:6">
-      <c r="A171" s="284"/>
-      <c r="B171" s="289"/>
-      <c r="C171" s="297"/>
+      <c r="A171" s="301"/>
+      <c r="B171" s="293"/>
+      <c r="C171" s="303"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F171" s="285"/>
+      <c r="F171" s="302"/>
     </row>
     <row r="172" s="244" customFormat="1" spans="1:6">
-      <c r="A172" s="284"/>
-      <c r="B172" s="289"/>
-      <c r="C172" s="297"/>
+      <c r="A172" s="301"/>
+      <c r="B172" s="293"/>
+      <c r="C172" s="303"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F172" s="285"/>
+      <c r="F172" s="302"/>
     </row>
     <row r="173" s="244" customFormat="1" spans="1:6">
-      <c r="A173" s="286"/>
-      <c r="B173" s="289"/>
-      <c r="C173" s="297"/>
+      <c r="A173" s="301"/>
+      <c r="B173" s="293"/>
+      <c r="C173" s="303"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F173" s="267"/>
+      <c r="F173" s="302"/>
     </row>
     <row r="174" s="244" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A174" s="284"/>
-      <c r="B174" s="289"/>
-      <c r="C174" s="297"/>
+      <c r="A174" s="301"/>
+      <c r="B174" s="293"/>
+      <c r="C174" s="303"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F174" s="285">
+      <c r="F174" s="302">
         <f>SUM(E174)</f>
         <v>0</v>
       </c>
     </row>
     <row r="175" s="244" customFormat="1" spans="1:6">
-      <c r="A175" s="280"/>
-      <c r="B175" s="289"/>
-      <c r="C175" s="297"/>
+      <c r="A175" s="301"/>
+      <c r="B175" s="293"/>
+      <c r="C175" s="303"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F175" s="283">
+      <c r="F175" s="302">
         <f>SUM(E175:E190)</f>
         <v>0</v>
       </c>
     </row>
     <row r="176" s="244" customFormat="1" spans="1:6">
-      <c r="A176" s="284"/>
-      <c r="B176" s="289"/>
-      <c r="C176" s="297"/>
+      <c r="A176" s="301"/>
+      <c r="B176" s="293"/>
+      <c r="C176" s="303"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F176" s="285"/>
+      <c r="F176" s="302"/>
     </row>
     <row r="177" s="244" customFormat="1" spans="1:6">
-      <c r="A177" s="284"/>
-      <c r="B177" s="289"/>
-      <c r="C177" s="297"/>
+      <c r="A177" s="301"/>
+      <c r="B177" s="293"/>
+      <c r="C177" s="303"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F177" s="285"/>
+      <c r="F177" s="302"/>
     </row>
     <row r="178" s="244" customFormat="1" spans="1:6">
-      <c r="A178" s="284"/>
-      <c r="B178" s="289"/>
-      <c r="C178" s="297"/>
+      <c r="A178" s="301"/>
+      <c r="B178" s="293"/>
+      <c r="C178" s="303"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F178" s="285"/>
+      <c r="F178" s="302"/>
     </row>
     <row r="179" s="244" customFormat="1" spans="1:6">
-      <c r="A179" s="284"/>
-      <c r="B179" s="289"/>
-      <c r="C179" s="297"/>
+      <c r="A179" s="301"/>
+      <c r="B179" s="293"/>
+      <c r="C179" s="303"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F179" s="285"/>
+      <c r="F179" s="302"/>
     </row>
     <row r="180" s="244" customFormat="1" spans="1:6">
-      <c r="A180" s="284"/>
-      <c r="B180" s="289"/>
-      <c r="C180" s="297"/>
+      <c r="A180" s="301"/>
+      <c r="B180" s="293"/>
+      <c r="C180" s="303"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F180" s="285"/>
+      <c r="F180" s="302"/>
     </row>
     <row r="181" s="244" customFormat="1" spans="1:6">
-      <c r="A181" s="284"/>
-      <c r="B181" s="289"/>
-      <c r="C181" s="297"/>
+      <c r="A181" s="301"/>
+      <c r="B181" s="293"/>
+      <c r="C181" s="303"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F181" s="285"/>
+      <c r="F181" s="302"/>
     </row>
     <row r="182" s="244" customFormat="1" spans="1:6">
-      <c r="A182" s="284"/>
-      <c r="B182" s="289"/>
-      <c r="C182" s="297"/>
+      <c r="A182" s="301"/>
+      <c r="B182" s="293"/>
+      <c r="C182" s="303"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F182" s="285"/>
+      <c r="F182" s="302"/>
     </row>
     <row r="183" s="244" customFormat="1" spans="1:6">
-      <c r="A183" s="284"/>
-      <c r="B183" s="289"/>
-      <c r="C183" s="297"/>
+      <c r="A183" s="301"/>
+      <c r="B183" s="293"/>
+      <c r="C183" s="303"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F183" s="285"/>
+      <c r="F183" s="302"/>
     </row>
     <row r="184" s="244" customFormat="1" spans="1:6">
-      <c r="A184" s="284"/>
-      <c r="B184" s="289"/>
-      <c r="C184" s="297"/>
+      <c r="A184" s="301"/>
+      <c r="B184" s="293"/>
+      <c r="C184" s="303"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F184" s="285"/>
+      <c r="F184" s="302"/>
     </row>
     <row r="185" s="244" customFormat="1" spans="1:6">
-      <c r="A185" s="284"/>
-      <c r="B185" s="289"/>
-      <c r="C185" s="297"/>
+      <c r="A185" s="301"/>
+      <c r="B185" s="293"/>
+      <c r="C185" s="303"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F185" s="285"/>
+      <c r="F185" s="302"/>
     </row>
     <row r="186" s="244" customFormat="1" spans="1:6">
-      <c r="A186" s="284"/>
-      <c r="B186" s="289"/>
-      <c r="C186" s="297"/>
+      <c r="A186" s="301"/>
+      <c r="B186" s="293"/>
+      <c r="C186" s="303"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F186" s="285"/>
+      <c r="F186" s="302"/>
     </row>
     <row r="187" s="244" customFormat="1" spans="1:6">
-      <c r="A187" s="284"/>
-      <c r="B187" s="289"/>
-      <c r="C187" s="297"/>
+      <c r="A187" s="301"/>
+      <c r="B187" s="293"/>
+      <c r="C187" s="303"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F187" s="285"/>
+      <c r="F187" s="302"/>
     </row>
     <row r="188" s="244" customFormat="1" spans="1:6">
-      <c r="A188" s="284"/>
-      <c r="B188" s="289"/>
-      <c r="C188" s="297"/>
+      <c r="A188" s="301"/>
+      <c r="B188" s="293"/>
+      <c r="C188" s="303"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F188" s="285"/>
+      <c r="F188" s="302"/>
     </row>
     <row r="189" s="244" customFormat="1" spans="1:6">
-      <c r="A189" s="284"/>
-      <c r="B189" s="299"/>
-      <c r="C189" s="300"/>
+      <c r="A189" s="301"/>
+      <c r="B189" s="304"/>
+      <c r="C189" s="305"/>
       <c r="D189" s="267"/>
       <c r="E189" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F189" s="285"/>
+      <c r="F189" s="302"/>
     </row>
     <row r="190" s="244" customFormat="1" spans="1:6">
-      <c r="A190" s="284"/>
-      <c r="B190" s="289"/>
-      <c r="C190" s="297"/>
+      <c r="A190" s="301"/>
+      <c r="B190" s="293"/>
+      <c r="C190" s="303"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F190" s="267"/>
+      <c r="F190" s="302"/>
     </row>
     <row r="191" s="244" customFormat="1" spans="1:6">
-      <c r="A191" s="280"/>
-      <c r="B191" s="289"/>
-      <c r="C191" s="297"/>
+      <c r="A191" s="282"/>
+      <c r="B191" s="293"/>
+      <c r="C191" s="303"/>
       <c r="D191" s="7"/>
       <c r="E191" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F191" s="283">
+      <c r="F191" s="285">
         <f>SUM(E191:E198)</f>
         <v>0</v>
       </c>
     </row>
     <row r="192" s="244" customFormat="1" spans="1:6">
-      <c r="A192" s="284"/>
-      <c r="B192" s="289"/>
-      <c r="C192" s="297"/>
+      <c r="A192" s="286"/>
+      <c r="B192" s="293"/>
+      <c r="C192" s="303"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F192" s="285"/>
+      <c r="F192" s="287"/>
     </row>
     <row r="193" s="244" customFormat="1" spans="1:6">
-      <c r="A193" s="284"/>
-      <c r="B193" s="289"/>
-      <c r="C193" s="297"/>
+      <c r="A193" s="286"/>
+      <c r="B193" s="293"/>
+      <c r="C193" s="303"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F193" s="285"/>
+      <c r="F193" s="287"/>
     </row>
     <row r="194" s="244" customFormat="1" spans="1:6">
-      <c r="A194" s="284"/>
-      <c r="B194" s="289"/>
-      <c r="C194" s="297"/>
+      <c r="A194" s="286"/>
+      <c r="B194" s="293"/>
+      <c r="C194" s="303"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F194" s="285"/>
+      <c r="F194" s="287"/>
     </row>
     <row r="195" s="244" customFormat="1" spans="1:6">
-      <c r="A195" s="284"/>
-      <c r="B195" s="289"/>
-      <c r="C195" s="297"/>
+      <c r="A195" s="286"/>
+      <c r="B195" s="293"/>
+      <c r="C195" s="303"/>
       <c r="D195" s="7"/>
       <c r="E195" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F195" s="285"/>
+      <c r="F195" s="287"/>
     </row>
     <row r="196" s="244" customFormat="1" spans="1:6">
-      <c r="A196" s="284"/>
-      <c r="B196" s="289"/>
-      <c r="C196" s="297"/>
+      <c r="A196" s="286"/>
+      <c r="B196" s="293"/>
+      <c r="C196" s="303"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F196" s="285"/>
+      <c r="F196" s="287"/>
     </row>
     <row r="197" s="244" customFormat="1" spans="1:6">
-      <c r="A197" s="284"/>
-      <c r="B197" s="289"/>
-      <c r="C197" s="297"/>
+      <c r="A197" s="286"/>
+      <c r="B197" s="293"/>
+      <c r="C197" s="303"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7">
         <f t="shared" ref="E197:E260" si="4">SUM(C197*D197)</f>
         <v>0</v>
       </c>
-      <c r="F197" s="285"/>
+      <c r="F197" s="287"/>
     </row>
     <row r="198" s="244" customFormat="1" spans="1:6">
-      <c r="A198" s="286"/>
-      <c r="B198" s="289"/>
-      <c r="C198" s="297"/>
+      <c r="A198" s="288"/>
+      <c r="B198" s="293"/>
+      <c r="C198" s="303"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F198" s="267"/>
+      <c r="F198" s="289"/>
     </row>
     <row r="199" s="244" customFormat="1" spans="1:6">
-      <c r="A199" s="280"/>
-      <c r="B199" s="289"/>
-      <c r="C199" s="297"/>
+      <c r="A199" s="282"/>
+      <c r="B199" s="293"/>
+      <c r="C199" s="303"/>
       <c r="D199" s="7"/>
       <c r="E199" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F199" s="283">
+      <c r="F199" s="285">
         <f>SUM(E199:E210)</f>
         <v>0</v>
       </c>
     </row>
     <row r="200" s="244" customFormat="1" spans="1:6">
-      <c r="A200" s="284"/>
-      <c r="B200" s="289"/>
-      <c r="C200" s="297"/>
+      <c r="A200" s="286"/>
+      <c r="B200" s="293"/>
+      <c r="C200" s="303"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F200" s="285"/>
+      <c r="F200" s="287"/>
     </row>
     <row r="201" s="244" customFormat="1" spans="1:6">
-      <c r="A201" s="284"/>
-      <c r="B201" s="289"/>
-      <c r="C201" s="297"/>
+      <c r="A201" s="286"/>
+      <c r="B201" s="293"/>
+      <c r="C201" s="303"/>
       <c r="D201" s="7"/>
       <c r="E201" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F201" s="285"/>
+      <c r="F201" s="287"/>
     </row>
     <row r="202" s="244" customFormat="1" spans="1:6">
-      <c r="A202" s="284"/>
-      <c r="B202" s="289"/>
-      <c r="C202" s="297"/>
+      <c r="A202" s="286"/>
+      <c r="B202" s="293"/>
+      <c r="C202" s="303"/>
       <c r="D202" s="7"/>
       <c r="E202" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F202" s="285"/>
+      <c r="F202" s="287"/>
     </row>
     <row r="203" s="244" customFormat="1" spans="1:6">
-      <c r="A203" s="284"/>
-      <c r="B203" s="289"/>
-      <c r="C203" s="297"/>
+      <c r="A203" s="286"/>
+      <c r="B203" s="293"/>
+      <c r="C203" s="303"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F203" s="285"/>
+      <c r="F203" s="287"/>
     </row>
     <row r="204" s="244" customFormat="1" spans="1:6">
-      <c r="A204" s="284"/>
-      <c r="B204" s="289"/>
-      <c r="C204" s="297"/>
+      <c r="A204" s="286"/>
+      <c r="B204" s="293"/>
+      <c r="C204" s="303"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F204" s="285"/>
+      <c r="F204" s="287"/>
     </row>
     <row r="205" s="244" customFormat="1" spans="1:6">
-      <c r="A205" s="284"/>
-      <c r="B205" s="289"/>
-      <c r="C205" s="297"/>
+      <c r="A205" s="286"/>
+      <c r="B205" s="293"/>
+      <c r="C205" s="303"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F205" s="285"/>
+      <c r="F205" s="287"/>
     </row>
     <row r="206" s="244" customFormat="1" spans="1:6">
-      <c r="A206" s="284"/>
-      <c r="B206" s="289"/>
-      <c r="C206" s="297"/>
+      <c r="A206" s="286"/>
+      <c r="B206" s="293"/>
+      <c r="C206" s="303"/>
       <c r="D206" s="7"/>
       <c r="E206" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F206" s="285"/>
+      <c r="F206" s="287"/>
     </row>
     <row r="207" s="244" customFormat="1" spans="1:6">
-      <c r="A207" s="284"/>
-      <c r="B207" s="289"/>
-      <c r="C207" s="297"/>
+      <c r="A207" s="286"/>
+      <c r="B207" s="293"/>
+      <c r="C207" s="303"/>
       <c r="D207" s="7"/>
       <c r="E207" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F207" s="285"/>
+      <c r="F207" s="287"/>
     </row>
     <row r="208" s="244" customFormat="1" spans="1:6">
-      <c r="A208" s="284"/>
-      <c r="B208" s="289"/>
-      <c r="C208" s="297"/>
+      <c r="A208" s="286"/>
+      <c r="B208" s="293"/>
+      <c r="C208" s="303"/>
       <c r="D208" s="7"/>
       <c r="E208" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F208" s="285"/>
+      <c r="F208" s="287"/>
     </row>
     <row r="209" s="244" customFormat="1" spans="1:6">
-      <c r="A209" s="284"/>
-      <c r="B209" s="289"/>
-      <c r="C209" s="297"/>
+      <c r="A209" s="286"/>
+      <c r="B209" s="293"/>
+      <c r="C209" s="303"/>
       <c r="D209" s="7"/>
       <c r="E209" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F209" s="285"/>
+      <c r="F209" s="287"/>
     </row>
     <row r="210" s="244" customFormat="1" spans="1:6">
-      <c r="A210" s="286"/>
-      <c r="B210" s="289"/>
-      <c r="C210" s="297"/>
+      <c r="A210" s="288"/>
+      <c r="B210" s="293"/>
+      <c r="C210" s="303"/>
       <c r="D210" s="7"/>
       <c r="E210" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F210" s="267"/>
+      <c r="F210" s="289"/>
     </row>
     <row r="211" s="244" customFormat="1" spans="1:6">
-      <c r="A211" s="280"/>
-      <c r="B211" s="289"/>
-      <c r="C211" s="297"/>
+      <c r="A211" s="282"/>
+      <c r="B211" s="293"/>
+      <c r="C211" s="303"/>
       <c r="D211" s="7"/>
       <c r="E211" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F211" s="283">
+      <c r="F211" s="285">
         <f>SUM(E211:E219)</f>
         <v>0</v>
       </c>
     </row>
     <row r="212" s="244" customFormat="1" spans="1:6">
-      <c r="A212" s="284"/>
-      <c r="B212" s="289"/>
-      <c r="C212" s="297"/>
+      <c r="A212" s="286"/>
+      <c r="B212" s="293"/>
+      <c r="C212" s="303"/>
       <c r="D212" s="7"/>
       <c r="E212" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F212" s="285"/>
+      <c r="F212" s="287"/>
     </row>
     <row r="213" s="244" customFormat="1" spans="1:6">
-      <c r="A213" s="284"/>
-      <c r="B213" s="289"/>
-      <c r="C213" s="297"/>
+      <c r="A213" s="286"/>
+      <c r="B213" s="293"/>
+      <c r="C213" s="303"/>
       <c r="D213" s="7"/>
       <c r="E213" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F213" s="285"/>
+      <c r="F213" s="287"/>
     </row>
     <row r="214" s="244" customFormat="1" spans="1:6">
-      <c r="A214" s="284"/>
-      <c r="B214" s="289"/>
-      <c r="C214" s="297"/>
+      <c r="A214" s="286"/>
+      <c r="B214" s="293"/>
+      <c r="C214" s="303"/>
       <c r="D214" s="7"/>
       <c r="E214" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F214" s="285"/>
+      <c r="F214" s="287"/>
     </row>
     <row r="215" s="244" customFormat="1" spans="1:6">
-      <c r="A215" s="284"/>
-      <c r="B215" s="289"/>
-      <c r="C215" s="297"/>
+      <c r="A215" s="286"/>
+      <c r="B215" s="293"/>
+      <c r="C215" s="303"/>
       <c r="D215" s="7"/>
       <c r="E215" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F215" s="285"/>
+      <c r="F215" s="287"/>
     </row>
     <row r="216" s="244" customFormat="1" spans="1:6">
-      <c r="A216" s="284"/>
-      <c r="B216" s="289"/>
-      <c r="C216" s="297"/>
+      <c r="A216" s="286"/>
+      <c r="B216" s="293"/>
+      <c r="C216" s="303"/>
       <c r="D216" s="7"/>
       <c r="E216" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F216" s="285"/>
+      <c r="F216" s="287"/>
     </row>
     <row r="217" s="244" customFormat="1" spans="1:6">
-      <c r="A217" s="284"/>
-      <c r="B217" s="289"/>
-      <c r="C217" s="297"/>
+      <c r="A217" s="286"/>
+      <c r="B217" s="293"/>
+      <c r="C217" s="303"/>
       <c r="D217" s="7"/>
       <c r="E217" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F217" s="285"/>
+      <c r="F217" s="287"/>
     </row>
     <row r="218" s="244" customFormat="1" spans="1:6">
-      <c r="A218" s="284"/>
-      <c r="B218" s="289"/>
-      <c r="C218" s="297"/>
+      <c r="A218" s="286"/>
+      <c r="B218" s="293"/>
+      <c r="C218" s="303"/>
       <c r="D218" s="7"/>
       <c r="E218" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F218" s="285"/>
+      <c r="F218" s="287"/>
     </row>
     <row r="219" s="244" customFormat="1" spans="1:6">
-      <c r="A219" s="286"/>
-      <c r="B219" s="289"/>
-      <c r="C219" s="297"/>
+      <c r="A219" s="288"/>
+      <c r="B219" s="293"/>
+      <c r="C219" s="303"/>
       <c r="D219" s="7"/>
       <c r="E219" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F219" s="267"/>
+      <c r="F219" s="289"/>
     </row>
     <row r="220" s="244" customFormat="1" spans="1:6">
-      <c r="A220" s="280"/>
-      <c r="B220" s="289"/>
-      <c r="C220" s="297"/>
+      <c r="A220" s="282"/>
+      <c r="B220" s="293"/>
+      <c r="C220" s="303"/>
       <c r="D220" s="7"/>
       <c r="E220" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F220" s="283">
+      <c r="F220" s="285">
         <f>SUM(E220:E230)</f>
         <v>0</v>
       </c>
     </row>
     <row r="221" s="244" customFormat="1" spans="1:6">
-      <c r="A221" s="284"/>
-      <c r="B221" s="289"/>
-      <c r="C221" s="297"/>
+      <c r="A221" s="286"/>
+      <c r="B221" s="293"/>
+      <c r="C221" s="303"/>
       <c r="D221" s="7"/>
       <c r="E221" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F221" s="285"/>
+      <c r="F221" s="287"/>
     </row>
     <row r="222" s="244" customFormat="1" spans="1:6">
-      <c r="A222" s="284"/>
-      <c r="B222" s="289"/>
-      <c r="C222" s="297"/>
+      <c r="A222" s="286"/>
+      <c r="B222" s="293"/>
+      <c r="C222" s="303"/>
       <c r="D222" s="7"/>
       <c r="E222" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F222" s="285"/>
+      <c r="F222" s="287"/>
     </row>
     <row r="223" s="244" customFormat="1" spans="1:6">
-      <c r="A223" s="284"/>
-      <c r="B223" s="289"/>
-      <c r="C223" s="297"/>
+      <c r="A223" s="286"/>
+      <c r="B223" s="293"/>
+      <c r="C223" s="303"/>
       <c r="D223" s="7"/>
       <c r="E223" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F223" s="285"/>
+      <c r="F223" s="287"/>
     </row>
     <row r="224" s="244" customFormat="1" spans="1:6">
-      <c r="A224" s="284"/>
-      <c r="B224" s="289"/>
-      <c r="C224" s="297"/>
+      <c r="A224" s="286"/>
+      <c r="B224" s="293"/>
+      <c r="C224" s="303"/>
       <c r="D224" s="7"/>
       <c r="E224" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F224" s="285"/>
+      <c r="F224" s="287"/>
     </row>
     <row r="225" s="244" customFormat="1" spans="1:6">
-      <c r="A225" s="284"/>
-      <c r="B225" s="289"/>
-      <c r="C225" s="297"/>
+      <c r="A225" s="286"/>
+      <c r="B225" s="293"/>
+      <c r="C225" s="303"/>
       <c r="D225" s="7"/>
       <c r="E225" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F225" s="285"/>
+      <c r="F225" s="287"/>
     </row>
     <row r="226" s="244" customFormat="1" spans="1:6">
-      <c r="A226" s="284"/>
-      <c r="B226" s="289"/>
-      <c r="C226" s="297"/>
+      <c r="A226" s="286"/>
+      <c r="B226" s="293"/>
+      <c r="C226" s="303"/>
       <c r="D226" s="7"/>
       <c r="E226" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F226" s="285"/>
+      <c r="F226" s="287"/>
     </row>
     <row r="227" s="244" customFormat="1" spans="1:6">
-      <c r="A227" s="284"/>
-      <c r="B227" s="289"/>
-      <c r="C227" s="297"/>
+      <c r="A227" s="286"/>
+      <c r="B227" s="293"/>
+      <c r="C227" s="303"/>
       <c r="D227" s="7"/>
       <c r="E227" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F227" s="285"/>
+      <c r="F227" s="287"/>
     </row>
     <row r="228" s="244" customFormat="1" spans="1:6">
-      <c r="A228" s="284"/>
-      <c r="B228" s="289"/>
-      <c r="C228" s="297"/>
+      <c r="A228" s="286"/>
+      <c r="B228" s="293"/>
+      <c r="C228" s="303"/>
       <c r="D228" s="7"/>
       <c r="E228" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F228" s="285"/>
+      <c r="F228" s="287"/>
     </row>
     <row r="229" s="244" customFormat="1" spans="1:6">
-      <c r="A229" s="284"/>
-      <c r="B229" s="289"/>
-      <c r="C229" s="297"/>
+      <c r="A229" s="286"/>
+      <c r="B229" s="293"/>
+      <c r="C229" s="303"/>
       <c r="D229" s="7"/>
       <c r="E229" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F229" s="285"/>
+      <c r="F229" s="287"/>
     </row>
     <row r="230" s="244" customFormat="1" spans="1:6">
-      <c r="A230" s="286"/>
-      <c r="B230" s="289"/>
-      <c r="C230" s="297"/>
+      <c r="A230" s="288"/>
+      <c r="B230" s="293"/>
+      <c r="C230" s="303"/>
       <c r="D230" s="7"/>
       <c r="E230" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F230" s="267"/>
+      <c r="F230" s="289"/>
     </row>
     <row r="231" s="244" customFormat="1" spans="1:6">
-      <c r="A231" s="280"/>
-      <c r="B231" s="289"/>
-      <c r="C231" s="297"/>
+      <c r="A231" s="282"/>
+      <c r="B231" s="293"/>
+      <c r="C231" s="303"/>
       <c r="D231" s="7"/>
       <c r="E231" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F231" s="283">
+      <c r="F231" s="285">
         <f>SUM(E231:E241)</f>
         <v>0</v>
       </c>
     </row>
     <row r="232" s="244" customFormat="1" spans="1:6">
-      <c r="A232" s="284"/>
-      <c r="B232" s="289"/>
-      <c r="C232" s="297"/>
+      <c r="A232" s="286"/>
+      <c r="B232" s="293"/>
+      <c r="C232" s="303"/>
       <c r="D232" s="7"/>
       <c r="E232" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F232" s="285"/>
+      <c r="F232" s="287"/>
     </row>
     <row r="233" s="244" customFormat="1" spans="1:6">
-      <c r="A233" s="284"/>
-      <c r="B233" s="289"/>
-      <c r="C233" s="297"/>
+      <c r="A233" s="286"/>
+      <c r="B233" s="293"/>
+      <c r="C233" s="303"/>
       <c r="D233" s="7"/>
       <c r="E233" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F233" s="285"/>
+      <c r="F233" s="287"/>
     </row>
     <row r="234" s="244" customFormat="1" spans="1:6">
-      <c r="A234" s="284"/>
-      <c r="B234" s="289"/>
-      <c r="C234" s="297"/>
+      <c r="A234" s="286"/>
+      <c r="B234" s="293"/>
+      <c r="C234" s="303"/>
       <c r="D234" s="7"/>
       <c r="E234" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F234" s="285"/>
+      <c r="F234" s="287"/>
     </row>
     <row r="235" s="244" customFormat="1" spans="1:6">
-      <c r="A235" s="284"/>
-      <c r="B235" s="289"/>
-      <c r="C235" s="297"/>
+      <c r="A235" s="286"/>
+      <c r="B235" s="293"/>
+      <c r="C235" s="303"/>
       <c r="D235" s="7"/>
       <c r="E235" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F235" s="285"/>
+      <c r="F235" s="287"/>
     </row>
     <row r="236" s="244" customFormat="1" spans="1:6">
-      <c r="A236" s="284"/>
-      <c r="B236" s="289"/>
-      <c r="C236" s="297"/>
+      <c r="A236" s="286"/>
+      <c r="B236" s="293"/>
+      <c r="C236" s="303"/>
       <c r="D236" s="7"/>
       <c r="E236" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F236" s="285"/>
+      <c r="F236" s="287"/>
     </row>
     <row r="237" s="244" customFormat="1" spans="1:6">
-      <c r="A237" s="284"/>
-      <c r="B237" s="289"/>
-      <c r="C237" s="297"/>
+      <c r="A237" s="286"/>
+      <c r="B237" s="293"/>
+      <c r="C237" s="303"/>
       <c r="D237" s="7"/>
       <c r="E237" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F237" s="285"/>
+      <c r="F237" s="287"/>
     </row>
     <row r="238" s="244" customFormat="1" spans="1:6">
-      <c r="A238" s="284"/>
-      <c r="B238" s="289"/>
-      <c r="C238" s="297"/>
+      <c r="A238" s="286"/>
+      <c r="B238" s="293"/>
+      <c r="C238" s="303"/>
       <c r="D238" s="7"/>
       <c r="E238" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F238" s="285"/>
+      <c r="F238" s="287"/>
     </row>
     <row r="239" s="244" customFormat="1" spans="1:6">
-      <c r="A239" s="284"/>
-      <c r="B239" s="289"/>
-      <c r="C239" s="297"/>
+      <c r="A239" s="286"/>
+      <c r="B239" s="293"/>
+      <c r="C239" s="303"/>
       <c r="D239" s="7"/>
       <c r="E239" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F239" s="285"/>
+      <c r="F239" s="287"/>
     </row>
     <row r="240" s="244" customFormat="1" spans="1:6">
-      <c r="A240" s="284"/>
-      <c r="B240" s="289"/>
-      <c r="C240" s="297"/>
+      <c r="A240" s="286"/>
+      <c r="B240" s="293"/>
+      <c r="C240" s="303"/>
       <c r="D240" s="7"/>
       <c r="E240" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F240" s="285"/>
+      <c r="F240" s="287"/>
     </row>
     <row r="241" s="244" customFormat="1" spans="1:6">
-      <c r="A241" s="286"/>
-      <c r="B241" s="289"/>
-      <c r="C241" s="297"/>
+      <c r="A241" s="288"/>
+      <c r="B241" s="293"/>
+      <c r="C241" s="303"/>
       <c r="D241" s="7"/>
       <c r="E241" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F241" s="267"/>
+      <c r="F241" s="289"/>
     </row>
     <row r="242" s="244" customFormat="1" spans="1:6">
-      <c r="A242" s="280"/>
-      <c r="B242" s="289"/>
-      <c r="C242" s="297"/>
+      <c r="A242" s="282"/>
+      <c r="B242" s="293"/>
+      <c r="C242" s="303"/>
       <c r="D242" s="7"/>
       <c r="E242" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F242" s="283">
+      <c r="F242" s="285">
         <f>SUM(E242:E252)</f>
         <v>0</v>
       </c>
     </row>
     <row r="243" s="244" customFormat="1" spans="1:6">
-      <c r="A243" s="284"/>
-      <c r="B243" s="289"/>
-      <c r="C243" s="297"/>
+      <c r="A243" s="286"/>
+      <c r="B243" s="293"/>
+      <c r="C243" s="303"/>
       <c r="D243" s="7"/>
       <c r="E243" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F243" s="285"/>
+      <c r="F243" s="287"/>
     </row>
     <row r="244" s="244" customFormat="1" spans="1:6">
-      <c r="A244" s="284"/>
-      <c r="B244" s="289"/>
-      <c r="C244" s="297"/>
+      <c r="A244" s="286"/>
+      <c r="B244" s="293"/>
+      <c r="C244" s="303"/>
       <c r="D244" s="7"/>
       <c r="E244" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F244" s="285"/>
+      <c r="F244" s="287"/>
     </row>
     <row r="245" s="244" customFormat="1" spans="1:6">
-      <c r="A245" s="284"/>
-      <c r="B245" s="289"/>
-      <c r="C245" s="297"/>
+      <c r="A245" s="286"/>
+      <c r="B245" s="293"/>
+      <c r="C245" s="303"/>
       <c r="D245" s="7"/>
       <c r="E245" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F245" s="285"/>
+      <c r="F245" s="287"/>
     </row>
     <row r="246" s="244" customFormat="1" spans="1:6">
-      <c r="A246" s="284"/>
-      <c r="B246" s="289"/>
-      <c r="C246" s="297"/>
+      <c r="A246" s="286"/>
+      <c r="B246" s="293"/>
+      <c r="C246" s="303"/>
       <c r="D246" s="7"/>
       <c r="E246" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F246" s="285"/>
+      <c r="F246" s="287"/>
     </row>
     <row r="247" s="244" customFormat="1" spans="1:6">
-      <c r="A247" s="284"/>
-      <c r="B247" s="289"/>
-      <c r="C247" s="297"/>
+      <c r="A247" s="286"/>
+      <c r="B247" s="293"/>
+      <c r="C247" s="303"/>
       <c r="D247" s="7"/>
       <c r="E247" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F247" s="285"/>
+      <c r="F247" s="287"/>
     </row>
     <row r="248" s="244" customFormat="1" spans="1:6">
-      <c r="A248" s="284"/>
-      <c r="B248" s="289"/>
-      <c r="C248" s="297"/>
+      <c r="A248" s="286"/>
+      <c r="B248" s="293"/>
+      <c r="C248" s="303"/>
       <c r="D248" s="7"/>
       <c r="E248" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F248" s="285"/>
+      <c r="F248" s="287"/>
     </row>
     <row r="249" s="244" customFormat="1" spans="1:6">
-      <c r="A249" s="284"/>
-      <c r="B249" s="289"/>
-      <c r="C249" s="297"/>
+      <c r="A249" s="286"/>
+      <c r="B249" s="293"/>
+      <c r="C249" s="303"/>
       <c r="D249" s="7"/>
       <c r="E249" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F249" s="285"/>
+      <c r="F249" s="287"/>
     </row>
     <row r="250" s="244" customFormat="1" spans="1:6">
-      <c r="A250" s="284"/>
-      <c r="B250" s="289"/>
-      <c r="C250" s="297"/>
+      <c r="A250" s="286"/>
+      <c r="B250" s="293"/>
+      <c r="C250" s="303"/>
       <c r="D250" s="7"/>
       <c r="E250" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F250" s="285"/>
+      <c r="F250" s="287"/>
     </row>
     <row r="251" s="244" customFormat="1" spans="1:6">
-      <c r="A251" s="284"/>
-      <c r="B251" s="289"/>
-      <c r="C251" s="297"/>
+      <c r="A251" s="286"/>
+      <c r="B251" s="293"/>
+      <c r="C251" s="303"/>
       <c r="D251" s="7"/>
       <c r="E251" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F251" s="285"/>
+      <c r="F251" s="287"/>
     </row>
     <row r="252" s="244" customFormat="1" spans="1:6">
-      <c r="A252" s="286"/>
-      <c r="B252" s="289"/>
-      <c r="C252" s="297"/>
+      <c r="A252" s="288"/>
+      <c r="B252" s="293"/>
+      <c r="C252" s="303"/>
       <c r="D252" s="7"/>
       <c r="E252" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F252" s="267"/>
+      <c r="F252" s="289"/>
     </row>
     <row r="253" s="244" customFormat="1" spans="1:6">
-      <c r="A253" s="280"/>
-      <c r="B253" s="289"/>
-      <c r="C253" s="297"/>
+      <c r="A253" s="282"/>
+      <c r="B253" s="293"/>
+      <c r="C253" s="303"/>
       <c r="D253" s="7"/>
       <c r="E253" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F253" s="283">
+      <c r="F253" s="285">
         <f>SUM(E253:E262)</f>
         <v>0</v>
       </c>
     </row>
     <row r="254" s="244" customFormat="1" spans="1:6">
-      <c r="A254" s="284"/>
-      <c r="B254" s="289"/>
-      <c r="C254" s="297"/>
+      <c r="A254" s="286"/>
+      <c r="B254" s="293"/>
+      <c r="C254" s="303"/>
       <c r="D254" s="7"/>
       <c r="E254" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F254" s="285"/>
+      <c r="F254" s="287"/>
     </row>
     <row r="255" s="244" customFormat="1" spans="1:6">
-      <c r="A255" s="284"/>
-      <c r="B255" s="289"/>
-      <c r="C255" s="297"/>
+      <c r="A255" s="286"/>
+      <c r="B255" s="293"/>
+      <c r="C255" s="303"/>
       <c r="D255" s="7"/>
       <c r="E255" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F255" s="285"/>
+      <c r="F255" s="287"/>
     </row>
     <row r="256" s="244" customFormat="1" spans="1:6">
-      <c r="A256" s="284"/>
-      <c r="B256" s="289"/>
-      <c r="C256" s="297"/>
+      <c r="A256" s="286"/>
+      <c r="B256" s="293"/>
+      <c r="C256" s="303"/>
       <c r="D256" s="7"/>
       <c r="E256" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F256" s="285"/>
+      <c r="F256" s="287"/>
     </row>
     <row r="257" s="244" customFormat="1" spans="1:6">
-      <c r="A257" s="284"/>
-      <c r="B257" s="289"/>
-      <c r="C257" s="297"/>
+      <c r="A257" s="286"/>
+      <c r="B257" s="293"/>
+      <c r="C257" s="303"/>
       <c r="D257" s="7"/>
       <c r="E257" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F257" s="285"/>
+      <c r="F257" s="287"/>
     </row>
     <row r="258" s="244" customFormat="1" spans="1:6">
-      <c r="A258" s="284"/>
-      <c r="B258" s="289"/>
-      <c r="C258" s="297"/>
+      <c r="A258" s="286"/>
+      <c r="B258" s="293"/>
+      <c r="C258" s="303"/>
       <c r="D258" s="7"/>
       <c r="E258" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F258" s="285"/>
+      <c r="F258" s="287"/>
     </row>
     <row r="259" s="244" customFormat="1" spans="1:6">
-      <c r="A259" s="284"/>
-      <c r="B259" s="289"/>
-      <c r="C259" s="297"/>
+      <c r="A259" s="286"/>
+      <c r="B259" s="293"/>
+      <c r="C259" s="303"/>
       <c r="D259" s="7"/>
       <c r="E259" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F259" s="285"/>
+      <c r="F259" s="287"/>
     </row>
     <row r="260" s="244" customFormat="1" spans="1:6">
-      <c r="A260" s="284"/>
-      <c r="B260" s="289"/>
-      <c r="C260" s="297"/>
+      <c r="A260" s="286"/>
+      <c r="B260" s="293"/>
+      <c r="C260" s="303"/>
       <c r="D260" s="7"/>
       <c r="E260" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F260" s="285"/>
+      <c r="F260" s="287"/>
     </row>
     <row r="261" s="244" customFormat="1" spans="1:6">
-      <c r="A261" s="284"/>
-      <c r="B261" s="289"/>
-      <c r="C261" s="297"/>
+      <c r="A261" s="286"/>
+      <c r="B261" s="293"/>
+      <c r="C261" s="303"/>
       <c r="D261" s="7"/>
       <c r="E261" s="7">
         <f t="shared" ref="E261:E274" si="5">SUM(C261*D261)</f>
         <v>0</v>
       </c>
-      <c r="F261" s="285"/>
+      <c r="F261" s="287"/>
     </row>
     <row r="262" s="244" customFormat="1" spans="1:6">
-      <c r="A262" s="286"/>
-      <c r="B262" s="289"/>
-      <c r="C262" s="297"/>
+      <c r="A262" s="288"/>
+      <c r="B262" s="293"/>
+      <c r="C262" s="303"/>
       <c r="D262" s="7"/>
       <c r="E262" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F262" s="267"/>
+      <c r="F262" s="289"/>
     </row>
     <row r="263" s="244" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A263" s="298"/>
-      <c r="B263" s="289"/>
-      <c r="C263" s="297"/>
+      <c r="A263" s="306"/>
+      <c r="B263" s="293"/>
+      <c r="C263" s="303"/>
       <c r="D263" s="7"/>
       <c r="E263" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F263" s="256">
+      <c r="F263" s="302">
         <f>SUM(E263)</f>
         <v>0</v>
       </c>
     </row>
     <row r="264" s="244" customFormat="1" spans="1:6">
-      <c r="A264" s="280"/>
-      <c r="B264" s="289"/>
-      <c r="C264" s="297"/>
+      <c r="A264" s="282"/>
+      <c r="B264" s="293"/>
+      <c r="C264" s="303"/>
       <c r="D264" s="7"/>
       <c r="E264" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F264" s="283">
+      <c r="F264" s="285">
         <f>SUM(E264:E274)</f>
         <v>0</v>
       </c>
     </row>
     <row r="265" s="244" customFormat="1" spans="1:6">
-      <c r="A265" s="284"/>
-      <c r="B265" s="289"/>
-      <c r="C265" s="297"/>
+      <c r="A265" s="286"/>
+      <c r="B265" s="293"/>
+      <c r="C265" s="303"/>
       <c r="D265" s="7"/>
       <c r="E265" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F265" s="285"/>
+      <c r="F265" s="287"/>
     </row>
     <row r="266" s="244" customFormat="1" spans="1:6">
-      <c r="A266" s="284"/>
-      <c r="B266" s="289"/>
-      <c r="C266" s="297"/>
+      <c r="A266" s="286"/>
+      <c r="B266" s="293"/>
+      <c r="C266" s="303"/>
       <c r="D266" s="7"/>
       <c r="E266" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F266" s="285"/>
+      <c r="F266" s="287"/>
     </row>
     <row r="267" s="244" customFormat="1" spans="1:6">
-      <c r="A267" s="284"/>
-      <c r="B267" s="289"/>
-      <c r="C267" s="297"/>
+      <c r="A267" s="286"/>
+      <c r="B267" s="293"/>
+      <c r="C267" s="303"/>
       <c r="D267" s="7"/>
       <c r="E267" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F267" s="285"/>
+      <c r="F267" s="287"/>
     </row>
     <row r="268" s="244" customFormat="1" spans="1:6">
-      <c r="A268" s="284"/>
-      <c r="B268" s="289"/>
-      <c r="C268" s="297"/>
+      <c r="A268" s="286"/>
+      <c r="B268" s="293"/>
+      <c r="C268" s="303"/>
       <c r="D268" s="7"/>
       <c r="E268" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F268" s="285"/>
+      <c r="F268" s="287"/>
     </row>
     <row r="269" s="244" customFormat="1" spans="1:6">
-      <c r="A269" s="284"/>
-      <c r="B269" s="289"/>
-      <c r="C269" s="297"/>
+      <c r="A269" s="286"/>
+      <c r="B269" s="293"/>
+      <c r="C269" s="303"/>
       <c r="D269" s="7"/>
       <c r="E269" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F269" s="285"/>
+      <c r="F269" s="287"/>
     </row>
     <row r="270" s="244" customFormat="1" spans="1:6">
-      <c r="A270" s="284"/>
-      <c r="B270" s="289"/>
-      <c r="C270" s="297"/>
+      <c r="A270" s="286"/>
+      <c r="B270" s="293"/>
+      <c r="C270" s="303"/>
       <c r="D270" s="7"/>
       <c r="E270" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F270" s="285"/>
+      <c r="F270" s="287"/>
     </row>
     <row r="271" s="244" customFormat="1" spans="1:6">
-      <c r="A271" s="284"/>
-      <c r="B271" s="289"/>
-      <c r="C271" s="297"/>
+      <c r="A271" s="286"/>
+      <c r="B271" s="293"/>
+      <c r="C271" s="303"/>
       <c r="D271" s="7"/>
       <c r="E271" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F271" s="285"/>
+      <c r="F271" s="287"/>
     </row>
     <row r="272" s="244" customFormat="1" spans="1:6">
-      <c r="A272" s="284"/>
-      <c r="B272" s="289"/>
-      <c r="C272" s="297"/>
+      <c r="A272" s="286"/>
+      <c r="B272" s="293"/>
+      <c r="C272" s="303"/>
       <c r="D272" s="7"/>
       <c r="E272" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F272" s="285"/>
+      <c r="F272" s="287"/>
     </row>
     <row r="273" s="244" customFormat="1" spans="1:6">
-      <c r="A273" s="284"/>
-      <c r="B273" s="289"/>
-      <c r="C273" s="297"/>
+      <c r="A273" s="286"/>
+      <c r="B273" s="293"/>
+      <c r="C273" s="303"/>
       <c r="D273" s="7"/>
       <c r="E273" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F273" s="285"/>
+      <c r="F273" s="287"/>
     </row>
     <row r="274" s="244" customFormat="1" spans="1:6">
-      <c r="A274" s="286"/>
-      <c r="B274" s="289"/>
-      <c r="C274" s="297"/>
+      <c r="A274" s="288"/>
+      <c r="B274" s="293"/>
+      <c r="C274" s="303"/>
       <c r="D274" s="7"/>
       <c r="E274" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F274" s="267"/>
+      <c r="F274" s="289"/>
     </row>
     <row r="275" s="244" customFormat="1" spans="1:6">
-      <c r="A275" s="246"/>
+      <c r="A275" s="279"/>
       <c r="C275" s="245"/>
       <c r="E275" s="7"/>
-      <c r="F275" s="256">
+      <c r="F275" s="302">
         <f>SUM(F2:F274)</f>
-        <v>1804000</v>
-      </c>
-    </row>
-    <row r="276" s="244" customFormat="1" spans="1:3">
-      <c r="A276" s="246"/>
+        <v>2296000</v>
+      </c>
+    </row>
+    <row r="276" s="244" customFormat="1" spans="1:6">
+      <c r="A276" s="279"/>
       <c r="C276" s="245"/>
-    </row>
-    <row r="277" s="244" customFormat="1" spans="1:3">
-      <c r="A277" s="246"/>
+      <c r="F276" s="280"/>
+    </row>
+    <row r="277" s="244" customFormat="1" spans="1:6">
+      <c r="A277" s="279"/>
       <c r="C277" s="245"/>
-    </row>
-    <row r="278" s="244" customFormat="1" spans="1:3">
-      <c r="A278" s="246"/>
+      <c r="F277" s="280"/>
+    </row>
+    <row r="278" s="244" customFormat="1" spans="1:6">
+      <c r="A278" s="279"/>
       <c r="C278" s="245"/>
-    </row>
-    <row r="279" s="244" customFormat="1" spans="1:3">
-      <c r="A279" s="246"/>
+      <c r="F278" s="280"/>
+    </row>
+    <row r="279" s="244" customFormat="1" spans="1:6">
+      <c r="A279" s="279"/>
       <c r="C279" s="245"/>
-    </row>
-    <row r="280" s="244" customFormat="1" spans="1:3">
-      <c r="A280" s="246"/>
+      <c r="F279" s="280"/>
+    </row>
+    <row r="280" s="244" customFormat="1" spans="1:6">
+      <c r="A280" s="279"/>
       <c r="C280" s="245"/>
-    </row>
-    <row r="281" s="244" customFormat="1" spans="1:3">
-      <c r="A281" s="246"/>
+      <c r="F280" s="280"/>
+    </row>
+    <row r="281" s="244" customFormat="1" spans="1:6">
+      <c r="A281" s="279"/>
       <c r="C281" s="245"/>
-    </row>
-    <row r="282" s="244" customFormat="1" spans="1:3">
-      <c r="A282" s="246"/>
+      <c r="F281" s="280"/>
+    </row>
+    <row r="282" s="244" customFormat="1" spans="1:6">
+      <c r="A282" s="279"/>
       <c r="C282" s="245"/>
-    </row>
-    <row r="283" s="244" customFormat="1" spans="1:3">
-      <c r="A283" s="246"/>
+      <c r="F282" s="280"/>
+    </row>
+    <row r="283" s="244" customFormat="1" spans="1:6">
+      <c r="A283" s="279"/>
       <c r="C283" s="245"/>
-    </row>
-    <row r="284" s="244" customFormat="1" spans="1:3">
-      <c r="A284" s="246"/>
+      <c r="F283" s="280"/>
+    </row>
+    <row r="284" s="244" customFormat="1" spans="1:6">
+      <c r="A284" s="279"/>
       <c r="C284" s="245"/>
-    </row>
-    <row r="285" s="244" customFormat="1" spans="1:3">
-      <c r="A285" s="246"/>
+      <c r="F284" s="280"/>
+    </row>
+    <row r="285" s="244" customFormat="1" spans="1:6">
+      <c r="A285" s="279"/>
       <c r="C285" s="245"/>
-    </row>
-    <row r="286" s="244" customFormat="1" spans="1:3">
-      <c r="A286" s="246"/>
+      <c r="F285" s="280"/>
+    </row>
+    <row r="286" s="244" customFormat="1" spans="1:6">
+      <c r="A286" s="279"/>
       <c r="C286" s="245"/>
-    </row>
-    <row r="287" s="244" customFormat="1" spans="1:3">
-      <c r="A287" s="246"/>
+      <c r="F286" s="280"/>
+    </row>
+    <row r="287" s="244" customFormat="1" spans="1:6">
+      <c r="A287" s="279"/>
       <c r="C287" s="245"/>
-    </row>
-    <row r="288" s="244" customFormat="1" spans="1:3">
-      <c r="A288" s="246"/>
+      <c r="F287" s="280"/>
+    </row>
+    <row r="288" s="244" customFormat="1" spans="1:6">
+      <c r="A288" s="279"/>
       <c r="C288" s="245"/>
-    </row>
-    <row r="289" s="244" customFormat="1" spans="1:3">
-      <c r="A289" s="246"/>
+      <c r="F288" s="280"/>
+    </row>
+    <row r="289" s="244" customFormat="1" spans="1:6">
+      <c r="A289" s="279"/>
       <c r="C289" s="245"/>
-    </row>
-    <row r="290" s="244" customFormat="1" spans="1:3">
-      <c r="A290" s="246"/>
+      <c r="F289" s="280"/>
+    </row>
+    <row r="290" s="244" customFormat="1" spans="1:6">
+      <c r="A290" s="279"/>
       <c r="C290" s="245"/>
-    </row>
-    <row r="291" s="244" customFormat="1" spans="1:3">
-      <c r="A291" s="246"/>
+      <c r="F290" s="280"/>
+    </row>
+    <row r="291" s="244" customFormat="1" spans="1:6">
+      <c r="A291" s="279"/>
       <c r="C291" s="245"/>
-    </row>
-    <row r="292" s="244" customFormat="1" spans="1:3">
-      <c r="A292" s="246"/>
+      <c r="F291" s="280"/>
+    </row>
+    <row r="292" s="244" customFormat="1" spans="1:6">
+      <c r="A292" s="279"/>
       <c r="C292" s="245"/>
-    </row>
-    <row r="293" s="244" customFormat="1" spans="1:3">
-      <c r="A293" s="246"/>
+      <c r="F292" s="280"/>
+    </row>
+    <row r="293" s="244" customFormat="1" spans="1:6">
+      <c r="A293" s="279"/>
       <c r="C293" s="245"/>
-    </row>
-    <row r="294" s="244" customFormat="1" spans="1:3">
-      <c r="A294" s="246"/>
+      <c r="F293" s="280"/>
+    </row>
+    <row r="294" s="244" customFormat="1" spans="1:6">
+      <c r="A294" s="279"/>
       <c r="C294" s="245"/>
-    </row>
-    <row r="295" s="244" customFormat="1" spans="1:3">
-      <c r="A295" s="246"/>
+      <c r="F294" s="280"/>
+    </row>
+    <row r="295" s="244" customFormat="1" spans="1:6">
+      <c r="A295" s="279"/>
       <c r="C295" s="245"/>
-    </row>
-    <row r="296" s="244" customFormat="1" spans="1:3">
-      <c r="A296" s="246"/>
+      <c r="F295" s="280"/>
+    </row>
+    <row r="296" s="244" customFormat="1" spans="1:6">
+      <c r="A296" s="279"/>
       <c r="C296" s="245"/>
-    </row>
-    <row r="297" s="244" customFormat="1" spans="1:3">
-      <c r="A297" s="246"/>
+      <c r="F296" s="280"/>
+    </row>
+    <row r="297" s="244" customFormat="1" spans="1:6">
+      <c r="A297" s="279"/>
       <c r="C297" s="245"/>
-    </row>
-    <row r="298" s="244" customFormat="1" spans="1:3">
-      <c r="A298" s="246"/>
+      <c r="F297" s="280"/>
+    </row>
+    <row r="298" s="244" customFormat="1" spans="1:6">
+      <c r="A298" s="279"/>
       <c r="C298" s="245"/>
-    </row>
-    <row r="299" s="244" customFormat="1" spans="1:3">
-      <c r="A299" s="246"/>
+      <c r="F298" s="280"/>
+    </row>
+    <row r="299" s="244" customFormat="1" spans="1:6">
+      <c r="A299" s="279"/>
       <c r="C299" s="245"/>
-    </row>
-    <row r="300" s="244" customFormat="1" spans="1:3">
-      <c r="A300" s="246"/>
+      <c r="F299" s="280"/>
+    </row>
+    <row r="300" s="244" customFormat="1" spans="1:6">
+      <c r="A300" s="279"/>
       <c r="C300" s="245"/>
-    </row>
-    <row r="301" s="244" customFormat="1" spans="1:3">
-      <c r="A301" s="246"/>
+      <c r="F300" s="280"/>
+    </row>
+    <row r="301" s="244" customFormat="1" spans="1:6">
+      <c r="A301" s="279"/>
       <c r="C301" s="245"/>
-    </row>
-    <row r="302" s="244" customFormat="1" spans="1:3">
-      <c r="A302" s="246"/>
+      <c r="F301" s="280"/>
+    </row>
+    <row r="302" s="244" customFormat="1" spans="1:6">
+      <c r="A302" s="279"/>
       <c r="C302" s="245"/>
-    </row>
-    <row r="303" s="244" customFormat="1" spans="1:3">
-      <c r="A303" s="246"/>
+      <c r="F302" s="280"/>
+    </row>
+    <row r="303" s="244" customFormat="1" spans="1:6">
+      <c r="A303" s="279"/>
       <c r="C303" s="245"/>
-    </row>
-    <row r="304" s="244" customFormat="1" spans="1:3">
-      <c r="A304" s="246"/>
+      <c r="F303" s="280"/>
+    </row>
+    <row r="304" s="244" customFormat="1" spans="1:6">
+      <c r="A304" s="279"/>
       <c r="C304" s="245"/>
-    </row>
-    <row r="305" s="244" customFormat="1" spans="1:3">
-      <c r="A305" s="246"/>
+      <c r="F304" s="280"/>
+    </row>
+    <row r="305" s="244" customFormat="1" spans="1:6">
+      <c r="A305" s="279"/>
       <c r="C305" s="245"/>
-    </row>
-    <row r="306" s="244" customFormat="1" spans="1:3">
-      <c r="A306" s="246"/>
+      <c r="F305" s="280"/>
+    </row>
+    <row r="306" s="244" customFormat="1" spans="1:6">
+      <c r="A306" s="279"/>
       <c r="C306" s="245"/>
-    </row>
-    <row r="307" s="244" customFormat="1" spans="1:3">
-      <c r="A307" s="246"/>
+      <c r="F306" s="280"/>
+    </row>
+    <row r="307" s="244" customFormat="1" spans="1:6">
+      <c r="A307" s="279"/>
       <c r="C307" s="245"/>
-    </row>
-    <row r="308" s="244" customFormat="1" spans="1:3">
-      <c r="A308" s="246"/>
+      <c r="F307" s="280"/>
+    </row>
+    <row r="308" s="244" customFormat="1" spans="1:6">
+      <c r="A308" s="279"/>
       <c r="C308" s="245"/>
-    </row>
-    <row r="309" s="244" customFormat="1" spans="1:3">
-      <c r="A309" s="246"/>
+      <c r="F308" s="280"/>
+    </row>
+    <row r="309" s="244" customFormat="1" spans="1:6">
+      <c r="A309" s="279"/>
       <c r="C309" s="245"/>
-    </row>
-    <row r="310" s="244" customFormat="1" spans="1:3">
-      <c r="A310" s="246"/>
+      <c r="F309" s="280"/>
+    </row>
+    <row r="310" s="244" customFormat="1" spans="1:6">
+      <c r="A310" s="279"/>
       <c r="C310" s="245"/>
-    </row>
-    <row r="311" s="244" customFormat="1" spans="1:3">
-      <c r="A311" s="246"/>
+      <c r="F310" s="280"/>
+    </row>
+    <row r="311" s="244" customFormat="1" spans="1:6">
+      <c r="A311" s="279"/>
       <c r="C311" s="245"/>
-    </row>
-    <row r="312" s="244" customFormat="1" spans="1:3">
-      <c r="A312" s="246"/>
+      <c r="F311" s="280"/>
+    </row>
+    <row r="312" s="244" customFormat="1" spans="1:6">
+      <c r="A312" s="279"/>
       <c r="C312" s="245"/>
-    </row>
-    <row r="313" s="244" customFormat="1" spans="1:3">
-      <c r="A313" s="246"/>
+      <c r="F312" s="280"/>
+    </row>
+    <row r="313" s="244" customFormat="1" spans="1:6">
+      <c r="A313" s="279"/>
       <c r="C313" s="245"/>
-    </row>
-    <row r="314" s="244" customFormat="1" spans="1:3">
-      <c r="A314" s="246"/>
+      <c r="F313" s="280"/>
+    </row>
+    <row r="314" s="244" customFormat="1" spans="1:6">
+      <c r="A314" s="279"/>
       <c r="C314" s="245"/>
-    </row>
-    <row r="315" s="244" customFormat="1" spans="1:3">
-      <c r="A315" s="246"/>
+      <c r="F314" s="280"/>
+    </row>
+    <row r="315" s="244" customFormat="1" spans="1:6">
+      <c r="A315" s="279"/>
       <c r="C315" s="245"/>
-    </row>
-    <row r="316" s="244" customFormat="1" spans="1:3">
-      <c r="A316" s="246"/>
+      <c r="F315" s="280"/>
+    </row>
+    <row r="316" s="244" customFormat="1" spans="1:6">
+      <c r="A316" s="279"/>
       <c r="C316" s="245"/>
-    </row>
-    <row r="317" s="244" customFormat="1" spans="1:3">
-      <c r="A317" s="246"/>
+      <c r="F316" s="280"/>
+    </row>
+    <row r="317" s="244" customFormat="1" spans="1:6">
+      <c r="A317" s="279"/>
       <c r="C317" s="245"/>
-    </row>
-    <row r="318" s="244" customFormat="1" spans="1:3">
-      <c r="A318" s="246"/>
+      <c r="F317" s="280"/>
+    </row>
+    <row r="318" s="244" customFormat="1" spans="1:6">
+      <c r="A318" s="279"/>
       <c r="C318" s="245"/>
-    </row>
-    <row r="319" s="244" customFormat="1" spans="1:3">
-      <c r="A319" s="246"/>
+      <c r="F318" s="280"/>
+    </row>
+    <row r="319" s="244" customFormat="1" spans="1:6">
+      <c r="A319" s="279"/>
       <c r="C319" s="245"/>
-    </row>
-    <row r="320" s="244" customFormat="1" spans="1:3">
-      <c r="A320" s="246"/>
+      <c r="F319" s="280"/>
+    </row>
+    <row r="320" s="244" customFormat="1" spans="1:6">
+      <c r="A320" s="279"/>
       <c r="C320" s="245"/>
-    </row>
-    <row r="321" s="244" customFormat="1" spans="1:3">
-      <c r="A321" s="246"/>
+      <c r="F320" s="280"/>
+    </row>
+    <row r="321" s="244" customFormat="1" spans="1:6">
+      <c r="A321" s="279"/>
       <c r="C321" s="245"/>
-    </row>
-    <row r="322" s="244" customFormat="1" spans="1:3">
-      <c r="A322" s="246"/>
+      <c r="F321" s="280"/>
+    </row>
+    <row r="322" s="244" customFormat="1" spans="1:6">
+      <c r="A322" s="279"/>
       <c r="C322" s="245"/>
-    </row>
-    <row r="323" s="244" customFormat="1" spans="1:3">
-      <c r="A323" s="246"/>
+      <c r="F322" s="280"/>
+    </row>
+    <row r="323" s="244" customFormat="1" spans="1:6">
+      <c r="A323" s="279"/>
       <c r="C323" s="245"/>
-    </row>
-    <row r="324" s="244" customFormat="1" spans="1:3">
-      <c r="A324" s="246"/>
+      <c r="F323" s="280"/>
+    </row>
+    <row r="324" s="244" customFormat="1" spans="1:6">
+      <c r="A324" s="279"/>
       <c r="C324" s="245"/>
-    </row>
-    <row r="325" s="244" customFormat="1" spans="1:3">
-      <c r="A325" s="246"/>
+      <c r="F324" s="280"/>
+    </row>
+    <row r="325" s="244" customFormat="1" spans="1:6">
+      <c r="A325" s="279"/>
       <c r="C325" s="245"/>
-    </row>
-    <row r="326" s="244" customFormat="1" spans="1:3">
-      <c r="A326" s="246"/>
+      <c r="F325" s="280"/>
+    </row>
+    <row r="326" s="244" customFormat="1" spans="1:6">
+      <c r="A326" s="279"/>
       <c r="C326" s="245"/>
-    </row>
-    <row r="327" s="244" customFormat="1" spans="1:3">
-      <c r="A327" s="246"/>
+      <c r="F326" s="280"/>
+    </row>
+    <row r="327" s="244" customFormat="1" spans="1:6">
+      <c r="A327" s="279"/>
       <c r="C327" s="245"/>
-    </row>
-    <row r="328" s="244" customFormat="1" spans="1:3">
-      <c r="A328" s="246"/>
+      <c r="F327" s="280"/>
+    </row>
+    <row r="328" s="244" customFormat="1" spans="1:6">
+      <c r="A328" s="279"/>
       <c r="C328" s="245"/>
-    </row>
-    <row r="329" s="244" customFormat="1" spans="1:3">
-      <c r="A329" s="246"/>
+      <c r="F328" s="280"/>
+    </row>
+    <row r="329" s="244" customFormat="1" spans="1:6">
+      <c r="A329" s="279"/>
       <c r="C329" s="245"/>
-    </row>
-    <row r="330" s="244" customFormat="1" spans="1:3">
-      <c r="A330" s="246"/>
+      <c r="F329" s="280"/>
+    </row>
+    <row r="330" s="244" customFormat="1" spans="1:6">
+      <c r="A330" s="279"/>
       <c r="C330" s="245"/>
-    </row>
-    <row r="331" s="244" customFormat="1" spans="1:3">
-      <c r="A331" s="246"/>
+      <c r="F330" s="280"/>
+    </row>
+    <row r="331" s="244" customFormat="1" spans="1:6">
+      <c r="A331" s="279"/>
       <c r="C331" s="245"/>
-    </row>
-    <row r="332" s="244" customFormat="1" spans="1:3">
-      <c r="A332" s="246"/>
+      <c r="F331" s="280"/>
+    </row>
+    <row r="332" s="244" customFormat="1" spans="1:6">
+      <c r="A332" s="279"/>
       <c r="C332" s="245"/>
-    </row>
-    <row r="333" s="244" customFormat="1" spans="1:3">
-      <c r="A333" s="246"/>
+      <c r="F332" s="280"/>
+    </row>
+    <row r="333" s="244" customFormat="1" spans="1:6">
+      <c r="A333" s="279"/>
       <c r="C333" s="245"/>
-    </row>
-    <row r="334" s="244" customFormat="1" spans="1:3">
-      <c r="A334" s="246"/>
+      <c r="F333" s="280"/>
+    </row>
+    <row r="334" s="244" customFormat="1" spans="1:6">
+      <c r="A334" s="279"/>
       <c r="C334" s="245"/>
-    </row>
-    <row r="335" s="244" customFormat="1" spans="1:3">
-      <c r="A335" s="246"/>
+      <c r="F334" s="280"/>
+    </row>
+    <row r="335" s="244" customFormat="1" spans="1:6">
+      <c r="A335" s="279"/>
       <c r="C335" s="245"/>
-    </row>
-    <row r="336" s="244" customFormat="1" spans="1:3">
-      <c r="A336" s="246"/>
+      <c r="F335" s="280"/>
+    </row>
+    <row r="336" s="244" customFormat="1" spans="1:6">
+      <c r="A336" s="279"/>
       <c r="C336" s="245"/>
-    </row>
-    <row r="337" s="244" customFormat="1" spans="1:3">
-      <c r="A337" s="246"/>
+      <c r="F336" s="280"/>
+    </row>
+    <row r="337" s="244" customFormat="1" spans="1:6">
+      <c r="A337" s="279"/>
       <c r="C337" s="245"/>
-    </row>
-    <row r="338" s="244" customFormat="1" spans="1:3">
-      <c r="A338" s="246"/>
+      <c r="F337" s="280"/>
+    </row>
+    <row r="338" s="244" customFormat="1" spans="1:6">
+      <c r="A338" s="279"/>
       <c r="C338" s="245"/>
-    </row>
-    <row r="339" s="244" customFormat="1" spans="1:3">
-      <c r="A339" s="246"/>
+      <c r="F338" s="280"/>
+    </row>
+    <row r="339" s="244" customFormat="1" spans="1:6">
+      <c r="A339" s="279"/>
       <c r="C339" s="245"/>
-    </row>
-    <row r="340" s="244" customFormat="1" spans="1:3">
-      <c r="A340" s="246"/>
+      <c r="F339" s="280"/>
+    </row>
+    <row r="340" s="244" customFormat="1" spans="1:6">
+      <c r="A340" s="279"/>
       <c r="C340" s="245"/>
-    </row>
-    <row r="341" s="244" customFormat="1" spans="1:3">
-      <c r="A341" s="246"/>
+      <c r="F340" s="280"/>
+    </row>
+    <row r="341" s="244" customFormat="1" spans="1:6">
+      <c r="A341" s="279"/>
       <c r="C341" s="245"/>
-    </row>
-    <row r="342" s="244" customFormat="1" spans="1:3">
-      <c r="A342" s="246"/>
+      <c r="F341" s="280"/>
+    </row>
+    <row r="342" s="244" customFormat="1" spans="1:6">
+      <c r="A342" s="279"/>
       <c r="C342" s="245"/>
-    </row>
-    <row r="343" s="244" customFormat="1" spans="1:3">
-      <c r="A343" s="246"/>
+      <c r="F342" s="280"/>
+    </row>
+    <row r="343" s="244" customFormat="1" spans="1:6">
+      <c r="A343" s="279"/>
       <c r="C343" s="245"/>
-    </row>
-    <row r="344" s="244" customFormat="1" spans="1:3">
-      <c r="A344" s="246"/>
+      <c r="F343" s="280"/>
+    </row>
+    <row r="344" s="244" customFormat="1" spans="1:6">
+      <c r="A344" s="279"/>
       <c r="C344" s="245"/>
-    </row>
-    <row r="345" s="244" customFormat="1" spans="1:3">
-      <c r="A345" s="246"/>
+      <c r="F344" s="280"/>
+    </row>
+    <row r="345" s="244" customFormat="1" spans="1:6">
+      <c r="A345" s="279"/>
       <c r="C345" s="245"/>
-    </row>
-    <row r="346" s="244" customFormat="1" spans="1:3">
-      <c r="A346" s="246"/>
+      <c r="F345" s="280"/>
+    </row>
+    <row r="346" s="244" customFormat="1" spans="1:6">
+      <c r="A346" s="279"/>
       <c r="C346" s="245"/>
-    </row>
-    <row r="347" s="244" customFormat="1" spans="1:3">
-      <c r="A347" s="246"/>
+      <c r="F346" s="280"/>
+    </row>
+    <row r="347" s="244" customFormat="1" spans="1:6">
+      <c r="A347" s="279"/>
       <c r="C347" s="245"/>
-    </row>
-    <row r="348" s="244" customFormat="1" spans="1:3">
-      <c r="A348" s="246"/>
+      <c r="F347" s="280"/>
+    </row>
+    <row r="348" s="244" customFormat="1" spans="1:6">
+      <c r="A348" s="279"/>
       <c r="C348" s="245"/>
-    </row>
-    <row r="349" s="244" customFormat="1" spans="1:3">
-      <c r="A349" s="246"/>
+      <c r="F348" s="280"/>
+    </row>
+    <row r="349" s="244" customFormat="1" spans="1:6">
+      <c r="A349" s="279"/>
       <c r="C349" s="245"/>
-    </row>
-    <row r="350" s="244" customFormat="1" spans="1:3">
-      <c r="A350" s="246"/>
+      <c r="F349" s="280"/>
+    </row>
+    <row r="350" s="244" customFormat="1" spans="1:6">
+      <c r="A350" s="279"/>
       <c r="C350" s="245"/>
-    </row>
-    <row r="351" s="244" customFormat="1" spans="1:3">
-      <c r="A351" s="246"/>
+      <c r="F350" s="280"/>
+    </row>
+    <row r="351" s="244" customFormat="1" spans="1:6">
+      <c r="A351" s="279"/>
       <c r="C351" s="245"/>
-    </row>
-    <row r="352" s="244" customFormat="1" spans="1:3">
-      <c r="A352" s="246"/>
+      <c r="F351" s="280"/>
+    </row>
+    <row r="352" s="244" customFormat="1" spans="1:6">
+      <c r="A352" s="279"/>
       <c r="C352" s="245"/>
-    </row>
-    <row r="353" s="244" customFormat="1" spans="1:3">
-      <c r="A353" s="246"/>
+      <c r="F352" s="280"/>
+    </row>
+    <row r="353" s="244" customFormat="1" spans="1:6">
+      <c r="A353" s="279"/>
       <c r="C353" s="245"/>
-    </row>
-    <row r="354" s="244" customFormat="1" spans="1:3">
-      <c r="A354" s="246"/>
+      <c r="F353" s="280"/>
+    </row>
+    <row r="354" s="244" customFormat="1" spans="1:6">
+      <c r="A354" s="279"/>
       <c r="C354" s="245"/>
-    </row>
-    <row r="355" s="244" customFormat="1" spans="1:3">
-      <c r="A355" s="246"/>
+      <c r="F354" s="280"/>
+    </row>
+    <row r="355" s="244" customFormat="1" spans="1:6">
+      <c r="A355" s="279"/>
       <c r="C355" s="245"/>
-    </row>
-    <row r="356" s="244" customFormat="1" spans="1:3">
-      <c r="A356" s="246"/>
+      <c r="F355" s="280"/>
+    </row>
+    <row r="356" s="244" customFormat="1" spans="1:6">
+      <c r="A356" s="279"/>
       <c r="C356" s="245"/>
-    </row>
-    <row r="357" s="244" customFormat="1" spans="1:3">
-      <c r="A357" s="246"/>
+      <c r="F356" s="280"/>
+    </row>
+    <row r="357" s="244" customFormat="1" spans="1:6">
+      <c r="A357" s="279"/>
       <c r="C357" s="245"/>
-    </row>
-    <row r="358" s="244" customFormat="1" spans="1:3">
-      <c r="A358" s="246"/>
+      <c r="F357" s="280"/>
+    </row>
+    <row r="358" s="244" customFormat="1" spans="1:6">
+      <c r="A358" s="279"/>
       <c r="C358" s="245"/>
-    </row>
-    <row r="359" s="244" customFormat="1" spans="1:3">
-      <c r="A359" s="246"/>
+      <c r="F358" s="280"/>
+    </row>
+    <row r="359" s="244" customFormat="1" spans="1:6">
+      <c r="A359" s="279"/>
       <c r="C359" s="245"/>
-    </row>
-    <row r="360" s="244" customFormat="1" spans="1:3">
-      <c r="A360" s="246"/>
+      <c r="F359" s="280"/>
+    </row>
+    <row r="360" s="244" customFormat="1" spans="1:6">
+      <c r="A360" s="279"/>
       <c r="C360" s="245"/>
-    </row>
-    <row r="361" s="244" customFormat="1" spans="1:3">
-      <c r="A361" s="246"/>
+      <c r="F360" s="280"/>
+    </row>
+    <row r="361" s="244" customFormat="1" spans="1:6">
+      <c r="A361" s="279"/>
       <c r="C361" s="245"/>
-    </row>
-    <row r="362" s="244" customFormat="1" spans="1:3">
-      <c r="A362" s="246"/>
+      <c r="F361" s="280"/>
+    </row>
+    <row r="362" s="244" customFormat="1" spans="1:6">
+      <c r="A362" s="279"/>
       <c r="C362" s="245"/>
-    </row>
-    <row r="363" s="244" customFormat="1" spans="1:3">
-      <c r="A363" s="246"/>
+      <c r="F362" s="280"/>
+    </row>
+    <row r="363" s="244" customFormat="1" spans="1:6">
+      <c r="A363" s="279"/>
       <c r="C363" s="245"/>
-    </row>
-    <row r="364" s="244" customFormat="1" spans="1:3">
-      <c r="A364" s="246"/>
+      <c r="F363" s="280"/>
+    </row>
+    <row r="364" s="244" customFormat="1" spans="1:6">
+      <c r="A364" s="279"/>
       <c r="C364" s="245"/>
-    </row>
-    <row r="365" s="244" customFormat="1" spans="1:3">
-      <c r="A365" s="246"/>
+      <c r="F364" s="280"/>
+    </row>
+    <row r="365" s="244" customFormat="1" spans="1:6">
+      <c r="A365" s="279"/>
       <c r="C365" s="245"/>
-    </row>
-    <row r="366" s="244" customFormat="1" spans="1:3">
-      <c r="A366" s="246"/>
+      <c r="F365" s="280"/>
+    </row>
+    <row r="366" s="244" customFormat="1" spans="1:6">
+      <c r="A366" s="279"/>
       <c r="C366" s="245"/>
-    </row>
-    <row r="367" s="244" customFormat="1" spans="1:3">
-      <c r="A367" s="246"/>
+      <c r="F366" s="280"/>
+    </row>
+    <row r="367" s="244" customFormat="1" spans="1:6">
+      <c r="A367" s="279"/>
       <c r="C367" s="245"/>
-    </row>
-    <row r="368" s="244" customFormat="1" spans="1:3">
-      <c r="A368" s="246"/>
+      <c r="F367" s="280"/>
+    </row>
+    <row r="368" s="244" customFormat="1" spans="1:6">
+      <c r="A368" s="279"/>
       <c r="C368" s="245"/>
-    </row>
-    <row r="369" s="244" customFormat="1" spans="1:3">
-      <c r="A369" s="246"/>
+      <c r="F368" s="280"/>
+    </row>
+    <row r="369" s="244" customFormat="1" spans="1:6">
+      <c r="A369" s="279"/>
       <c r="C369" s="245"/>
-    </row>
-    <row r="370" s="244" customFormat="1" spans="1:3">
-      <c r="A370" s="246"/>
+      <c r="F369" s="280"/>
+    </row>
+    <row r="370" s="244" customFormat="1" spans="1:6">
+      <c r="A370" s="279"/>
       <c r="C370" s="245"/>
-    </row>
-    <row r="371" s="244" customFormat="1" spans="1:3">
-      <c r="A371" s="246"/>
+      <c r="F370" s="280"/>
+    </row>
+    <row r="371" s="244" customFormat="1" spans="1:6">
+      <c r="A371" s="279"/>
       <c r="C371" s="245"/>
-    </row>
-    <row r="372" s="244" customFormat="1" spans="1:3">
-      <c r="A372" s="246"/>
+      <c r="F371" s="280"/>
+    </row>
+    <row r="372" s="244" customFormat="1" spans="1:6">
+      <c r="A372" s="279"/>
       <c r="C372" s="245"/>
-    </row>
-    <row r="373" s="244" customFormat="1" spans="1:3">
-      <c r="A373" s="246"/>
+      <c r="F372" s="280"/>
+    </row>
+    <row r="373" s="244" customFormat="1" spans="1:6">
+      <c r="A373" s="279"/>
       <c r="C373" s="245"/>
-    </row>
-    <row r="374" s="244" customFormat="1" spans="1:3">
-      <c r="A374" s="246"/>
+      <c r="F373" s="280"/>
+    </row>
+    <row r="374" s="244" customFormat="1" spans="1:6">
+      <c r="A374" s="279"/>
       <c r="C374" s="245"/>
-    </row>
-    <row r="375" s="244" customFormat="1" spans="1:3">
-      <c r="A375" s="246"/>
+      <c r="F374" s="280"/>
+    </row>
+    <row r="375" s="244" customFormat="1" spans="1:6">
+      <c r="A375" s="279"/>
       <c r="C375" s="245"/>
-    </row>
-    <row r="376" s="244" customFormat="1" spans="1:3">
-      <c r="A376" s="246"/>
+      <c r="F375" s="280"/>
+    </row>
+    <row r="376" s="244" customFormat="1" spans="1:6">
+      <c r="A376" s="279"/>
       <c r="C376" s="245"/>
-    </row>
-    <row r="377" s="244" customFormat="1" spans="1:3">
-      <c r="A377" s="246"/>
+      <c r="F376" s="280"/>
+    </row>
+    <row r="377" s="244" customFormat="1" spans="1:6">
+      <c r="A377" s="279"/>
       <c r="C377" s="245"/>
+      <c r="F377" s="280"/>
     </row>
     <row r="378" s="244" customFormat="1" spans="1:7">
-      <c r="A378" s="246"/>
+      <c r="A378" s="279"/>
       <c r="C378" s="245"/>
+      <c r="F378" s="280"/>
       <c r="G378" s="268"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="24">
     <mergeCell ref="A2:A12"/>
     <mergeCell ref="A13:A25"/>
     <mergeCell ref="A26:A34"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="A48:A56"/>
-    <mergeCell ref="A57:A71"/>
-    <mergeCell ref="A72:A83"/>
-    <mergeCell ref="A84:A90"/>
-    <mergeCell ref="A91:A105"/>
-    <mergeCell ref="A106:A121"/>
-    <mergeCell ref="A123:A127"/>
-    <mergeCell ref="A128:A134"/>
-    <mergeCell ref="A135:A142"/>
-    <mergeCell ref="A143:A149"/>
-    <mergeCell ref="A150:A159"/>
-    <mergeCell ref="A160:A173"/>
-    <mergeCell ref="A175:A190"/>
+    <mergeCell ref="A35:A45"/>
     <mergeCell ref="A191:A198"/>
     <mergeCell ref="A199:A210"/>
     <mergeCell ref="A211:A219"/>
@@ -6697,21 +6877,7 @@
     <mergeCell ref="F2:F12"/>
     <mergeCell ref="F13:F25"/>
     <mergeCell ref="F26:F34"/>
-    <mergeCell ref="F36:F41"/>
-    <mergeCell ref="F42:F47"/>
-    <mergeCell ref="F48:F56"/>
-    <mergeCell ref="F57:F71"/>
-    <mergeCell ref="F72:F83"/>
-    <mergeCell ref="F84:F90"/>
-    <mergeCell ref="F91:F105"/>
-    <mergeCell ref="F106:F121"/>
-    <mergeCell ref="F123:F127"/>
-    <mergeCell ref="F128:F134"/>
-    <mergeCell ref="F135:F142"/>
-    <mergeCell ref="F143:F149"/>
-    <mergeCell ref="F150:F159"/>
-    <mergeCell ref="F160:F173"/>
-    <mergeCell ref="F175:F190"/>
+    <mergeCell ref="F35:F45"/>
     <mergeCell ref="F191:F198"/>
     <mergeCell ref="F199:F210"/>
     <mergeCell ref="F211:F219"/>
@@ -6746,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -6785,7 +6951,7 @@
       <c r="D3" s="27"/>
       <c r="E3" s="17"/>
       <c r="F3" s="118" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G3" s="41">
         <f>G2*11%</f>
@@ -6827,7 +6993,7 @@
       <c r="D6" s="125"/>
       <c r="E6" s="7"/>
       <c r="F6" s="126" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G6" s="7">
         <f>G5*11%</f>
@@ -6909,7 +7075,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="87" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B14" s="88"/>
       <c r="C14" s="88"/>
@@ -6963,16 +7129,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -7111,7 +7277,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="87" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B14" s="88"/>
       <c r="C14" s="88"/>
@@ -7165,16 +7331,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -7183,7 +7349,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="138.55" customHeight="1" spans="1:8">
@@ -7211,7 +7377,7 @@
       </c>
       <c r="E3" s="101"/>
       <c r="F3" s="82" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G3" s="102">
         <f>G2*11%</f>
@@ -7259,7 +7425,7 @@
       </c>
       <c r="E6" s="81"/>
       <c r="F6" s="82" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G6" s="102">
         <f>G5*11%</f>
@@ -7304,7 +7470,7 @@
       <c r="D9" s="104"/>
       <c r="E9" s="81"/>
       <c r="F9" s="82" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G9" s="102">
         <f>G8*11%</f>
@@ -7349,7 +7515,7 @@
       <c r="D12" s="104"/>
       <c r="E12" s="81"/>
       <c r="F12" s="82" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G12" s="102">
         <f>G11*11%</f>
@@ -7391,7 +7557,7 @@
       <c r="D15" s="104"/>
       <c r="E15" s="81"/>
       <c r="F15" s="82" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G15" s="102">
         <f>G14*11%</f>
@@ -7416,7 +7582,7 @@
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:8">
       <c r="A17" s="87" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B17" s="88"/>
       <c r="C17" s="88"/>
@@ -7474,19 +7640,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E1" s="35" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>5</v>
@@ -7518,7 +7684,7 @@
     </row>
     <row r="4" ht="23" customHeight="1" spans="1:7">
       <c r="A4" s="94" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B4" s="95"/>
       <c r="C4" s="95"/>
@@ -7559,16 +7725,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -7591,7 +7757,7 @@
     </row>
     <row r="3" ht="23.25" spans="1:7">
       <c r="A3" s="29" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="79"/>
@@ -7601,7 +7767,7 @@
       </c>
       <c r="E3" s="81"/>
       <c r="F3" s="81" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G3" s="82">
         <f>G2*11%</f>
@@ -7656,7 +7822,7 @@
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:7">
       <c r="A8" s="87" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B8" s="88"/>
       <c r="C8" s="88"/>
@@ -7703,19 +7869,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="321" customHeight="1" spans="1:6">
@@ -7778,16 +7944,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -7888,7 +8054,7 @@
     </row>
     <row r="12" ht="27" customHeight="1" spans="1:7">
       <c r="A12" s="61" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B12" s="62"/>
       <c r="C12" s="62"/>
@@ -7941,13 +8107,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>3</v>
@@ -7956,7 +8122,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="324.4" customHeight="1" spans="1:7">
@@ -8015,22 +8181,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="177" customHeight="1" spans="1:7">
@@ -8091,10 +8257,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>5</v>
@@ -8105,11 +8271,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C2" s="5">
         <f>'BUK BUNGA (Groceries)'!F275</f>
-        <v>1804000</v>
+        <v>2296000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8117,7 +8283,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C3" s="5">
         <f>'WARUNG EKA (Drinks, Etc)'!G118</f>
@@ -8129,7 +8295,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C4" s="5">
         <f>'DEWATA COCONUT (Coconut)'!E10</f>
@@ -8141,7 +8307,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C5" s="5">
         <f>'SEDANA JAYA'!F37</f>
@@ -8153,7 +8319,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C6" s="5">
         <f>'PNB (Alcohol)'!H7</f>
@@ -8165,7 +8331,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C7" s="5">
         <f>'DSP (Alcohol)'!F16</f>
@@ -8177,7 +8343,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8" s="5">
         <f>'DSP ARYA BIMA (Alcohol)'!E3</f>
@@ -8189,7 +8355,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C9" s="5">
         <f>'SELERA OR STIR UP (Syrup)'!F9</f>
@@ -8201,7 +8367,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C10" s="5">
         <f>'DW BALI (Alcohol)'!E4</f>
@@ -8213,7 +8379,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C11" s="5">
         <f>'DDB (Alcohol)'!E14</f>
@@ -8225,7 +8391,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C12" s="5">
         <f>'NANO DEWATA (Alcohol)'!E14</f>
@@ -8237,7 +8403,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C13" s="5">
         <f>'BALI PERMATA JAYA (Corona Beer)'!E17</f>
@@ -8249,7 +8415,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C14" s="7">
         <f>'BLACK COFFEE ROASTERS (Coffee)'!F4</f>
@@ -8261,7 +8427,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C15" s="5">
         <f>'PT. PRASIDA LANTUR MAJU (Wine)'!E8</f>
@@ -8273,7 +8439,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C16" s="8">
         <f>'PT LOVINA BEACH BREWERY'!D3</f>
@@ -8285,7 +8451,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C17" s="5">
         <f>'CHAI CHITAI (Tea Leaf,etc)'!E12</f>
@@ -8297,7 +8463,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C18" s="5">
         <f>'MULIA JAYA (Passion Fruit)'!D3</f>
@@ -8309,7 +8475,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C19" s="5">
         <f>'Dewata Kencana Distribusi (Vdka'!E3</f>
@@ -8323,7 +8489,7 @@
       <c r="B20" s="9"/>
       <c r="C20" s="10">
         <f>SUM(C2:C13)</f>
-        <v>7133100</v>
+        <v>7625100</v>
       </c>
     </row>
   </sheetData>
@@ -8359,7 +8525,7 @@
   <sheetData>
     <row r="1" s="244" customFormat="1" ht="21" customHeight="1" spans="1:7">
       <c r="A1" s="250" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B1" s="251" t="s">
         <v>0</v>
@@ -8374,10 +8540,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="252" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G1" s="252" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
@@ -8388,7 +8554,7 @@
         <v>45992</v>
       </c>
       <c r="C2" s="255" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D2" s="114">
         <v>5</v>
@@ -8409,7 +8575,7 @@
       <c r="A3" s="43"/>
       <c r="B3" s="42"/>
       <c r="C3" s="255" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D3" s="114">
         <v>1</v>
@@ -8427,7 +8593,7 @@
       <c r="A4" s="259"/>
       <c r="B4" s="260"/>
       <c r="C4" s="255" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" s="114">
         <v>1</v>
@@ -8449,7 +8615,7 @@
         <v>45993</v>
       </c>
       <c r="C5" s="255" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" s="114">
         <v>5</v>
@@ -8470,7 +8636,7 @@
       <c r="A6" s="204"/>
       <c r="B6" s="42"/>
       <c r="C6" s="255" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D6" s="114">
         <v>1</v>
@@ -8488,7 +8654,7 @@
       <c r="A7" s="262"/>
       <c r="B7" s="260"/>
       <c r="C7" s="255" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D7" s="114">
         <v>1</v>
@@ -8510,7 +8676,7 @@
         <v>45994</v>
       </c>
       <c r="C8" s="255" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D8" s="114">
         <v>6</v>
@@ -8531,7 +8697,7 @@
       <c r="A9" s="204"/>
       <c r="B9" s="42"/>
       <c r="C9" s="255" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D9" s="114">
         <v>1</v>
@@ -8549,7 +8715,7 @@
       <c r="A10" s="204"/>
       <c r="B10" s="42"/>
       <c r="C10" s="255" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" s="114">
         <v>1</v>
@@ -8567,7 +8733,7 @@
       <c r="A11" s="204"/>
       <c r="B11" s="42"/>
       <c r="C11" s="255" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D11" s="114">
         <v>1</v>
@@ -8585,7 +8751,7 @@
       <c r="A12" s="204"/>
       <c r="B12" s="42"/>
       <c r="C12" s="264" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D12" s="114">
         <v>2</v>
@@ -8603,7 +8769,7 @@
       <c r="A13" s="262"/>
       <c r="B13" s="260"/>
       <c r="C13" s="255" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D13" s="114">
         <v>1</v>
@@ -8625,7 +8791,7 @@
         <v>45995</v>
       </c>
       <c r="C14" s="255" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D14" s="114">
         <v>6</v>
@@ -8646,7 +8812,7 @@
       <c r="A15" s="262"/>
       <c r="B15" s="260"/>
       <c r="C15" s="264" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D15" s="114">
         <v>2</v>
@@ -9984,7 +10150,7 @@
     </row>
     <row r="118" s="244" customFormat="1" spans="1:7">
       <c r="A118" s="270" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B118" s="125"/>
       <c r="C118" s="271"/>
@@ -10365,16 +10531,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>3</v>
@@ -10391,7 +10557,7 @@
         <v>12340</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D2" s="16">
         <v>20</v>
@@ -10413,7 +10579,7 @@
         <v>12357</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D3" s="16">
         <v>20</v>
@@ -10435,7 +10601,7 @@
         <v>11374</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D4" s="16">
         <v>20</v>
@@ -10567,7 +10733,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="224" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F1" s="224" t="s">
         <v>5</v>
@@ -10615,7 +10781,7 @@
     <row r="4" s="217" customFormat="1" spans="1:7">
       <c r="A4" s="230"/>
       <c r="B4" s="226" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C4" s="227">
         <v>0.3</v>
@@ -10633,7 +10799,7 @@
     <row r="5" s="217" customFormat="1" spans="1:6">
       <c r="A5" s="230"/>
       <c r="B5" s="226" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C5" s="227">
         <v>1</v>
@@ -10719,7 +10885,7 @@
     <row r="10" s="217" customFormat="1" spans="1:6">
       <c r="A10" s="233"/>
       <c r="B10" s="226" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C10" s="227">
         <v>2</v>
@@ -10776,7 +10942,7 @@
     <row r="13" s="217" customFormat="1" spans="1:6">
       <c r="A13" s="230"/>
       <c r="B13" s="226" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C13" s="227">
         <v>8</v>
@@ -10827,7 +10993,7 @@
     <row r="16" s="217" customFormat="1" spans="1:6">
       <c r="A16" s="230"/>
       <c r="B16" s="226" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C16" s="227">
         <v>2</v>
@@ -10861,7 +11027,7 @@
     <row r="18" s="217" customFormat="1" spans="1:6">
       <c r="A18" s="230"/>
       <c r="B18" s="226" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C18" s="227">
         <v>1</v>
@@ -10895,7 +11061,7 @@
     <row r="20" s="217" customFormat="1" spans="1:6">
       <c r="A20" s="233"/>
       <c r="B20" s="226" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C20" s="227">
         <v>1</v>
@@ -12915,19 +13081,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>4</v>
@@ -12941,10 +13107,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="211" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D2" s="16">
         <v>3</v>
@@ -13085,31 +13251,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="176" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="176" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E1" s="176" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="176" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="176" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="176" t="s">
-        <v>55</v>
-      </c>
       <c r="H1" s="176" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I1" s="176" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="176" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" ht="160" customHeight="1" spans="1:10">
@@ -13487,16 +13653,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="166" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="166" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="166" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E1" s="166" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F1" s="166" t="s">
         <v>3</v>
@@ -13558,22 +13724,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="135" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="135" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="135" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E1" s="135" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F1" s="135" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="135" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H1" s="136" t="s">
         <v>5</v>
@@ -13584,10 +13750,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="137" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C2" s="138" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D2" s="139">
         <v>5</v>
@@ -13660,7 +13826,7 @@
       </c>
       <c r="E7" s="153"/>
       <c r="F7" s="154" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G7" s="154"/>
       <c r="H7" s="154">
@@ -13689,7 +13855,7 @@
       <c r="C9" s="160"/>
       <c r="D9" s="160"/>
       <c r="E9" s="161" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F9" s="162">
         <f>SUM(E8)</f>
@@ -13765,16 +13931,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -13809,7 +13975,7 @@
     </row>
     <row r="4" ht="23.25" spans="1:7">
       <c r="A4" s="87" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B4" s="88"/>
       <c r="C4" s="88"/>

--- a/DECEMBER/DECEMBER BAR.xlsx
+++ b/DECEMBER/DECEMBER BAR.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="114">
   <si>
     <t>DATE</t>
   </si>
@@ -187,15 +187,6 @@
   </si>
   <si>
     <t>APPLE</t>
-  </si>
-  <si>
-    <t>ONION</t>
-  </si>
-  <si>
-    <t>BANANA</t>
-  </si>
-  <si>
-    <t>QUAIL EGG</t>
   </si>
   <si>
     <t>INV NO</t>
@@ -1452,7 +1443,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="316">
+  <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2254,33 +2245,6 @@
     <xf numFmtId="179" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2374,6 +2338,9 @@
     <xf numFmtId="179" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2387,9 +2354,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3544,18 +3508,18 @@
       <c r="E1" s="253" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="291" t="s">
+      <c r="F1" s="282" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A2" s="292">
+      <c r="A2" s="283">
         <v>45995</v>
       </c>
-      <c r="B2" s="293" t="s">
+      <c r="B2" s="284" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="294">
+      <c r="C2" s="285">
         <v>5</v>
       </c>
       <c r="D2" s="7">
@@ -3565,17 +3529,17 @@
         <f t="shared" ref="E2:E15" si="0">SUM(C2*D2)</f>
         <v>100000</v>
       </c>
-      <c r="F2" s="295">
+      <c r="F2" s="286">
         <f>SUM(E2:E12)</f>
         <v>572000</v>
       </c>
     </row>
     <row r="3" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A3" s="296"/>
-      <c r="B3" s="293" t="s">
+      <c r="A3" s="287"/>
+      <c r="B3" s="284" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="294">
+      <c r="C3" s="285">
         <v>2</v>
       </c>
       <c r="D3" s="7">
@@ -3585,14 +3549,14 @@
         <f t="shared" si="0"/>
         <v>140000</v>
       </c>
-      <c r="F3" s="297"/>
+      <c r="F3" s="288"/>
     </row>
     <row r="4" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A4" s="296"/>
-      <c r="B4" s="293" t="s">
+      <c r="A4" s="287"/>
+      <c r="B4" s="284" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="294">
+      <c r="C4" s="285">
         <v>6</v>
       </c>
       <c r="D4" s="7">
@@ -3602,14 +3566,14 @@
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
-      <c r="F4" s="297"/>
+      <c r="F4" s="288"/>
     </row>
     <row r="5" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A5" s="296"/>
-      <c r="B5" s="293" t="s">
+      <c r="A5" s="287"/>
+      <c r="B5" s="284" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="294">
+      <c r="C5" s="285">
         <v>1</v>
       </c>
       <c r="D5" s="7">
@@ -3619,14 +3583,14 @@
         <f t="shared" si="0"/>
         <v>38000</v>
       </c>
-      <c r="F5" s="297"/>
+      <c r="F5" s="288"/>
     </row>
     <row r="6" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A6" s="296"/>
-      <c r="B6" s="293" t="s">
+      <c r="A6" s="287"/>
+      <c r="B6" s="284" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="294">
+      <c r="C6" s="285">
         <v>0.3</v>
       </c>
       <c r="D6" s="7">
@@ -3636,14 +3600,14 @@
         <f t="shared" si="0"/>
         <v>6000</v>
       </c>
-      <c r="F6" s="297"/>
+      <c r="F6" s="288"/>
     </row>
     <row r="7" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A7" s="296"/>
-      <c r="B7" s="293" t="s">
+      <c r="A7" s="287"/>
+      <c r="B7" s="284" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="294">
+      <c r="C7" s="285">
         <v>1</v>
       </c>
       <c r="D7" s="7">
@@ -3653,14 +3617,14 @@
         <f t="shared" si="0"/>
         <v>25000</v>
       </c>
-      <c r="F7" s="297"/>
+      <c r="F7" s="288"/>
     </row>
     <row r="8" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A8" s="296"/>
-      <c r="B8" s="293" t="s">
+      <c r="A8" s="287"/>
+      <c r="B8" s="284" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="294">
+      <c r="C8" s="285">
         <v>1</v>
       </c>
       <c r="D8" s="7">
@@ -3670,14 +3634,14 @@
         <f t="shared" si="0"/>
         <v>30000</v>
       </c>
-      <c r="F8" s="297"/>
+      <c r="F8" s="288"/>
     </row>
     <row r="9" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A9" s="296"/>
-      <c r="B9" s="293" t="s">
+      <c r="A9" s="287"/>
+      <c r="B9" s="284" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="294">
+      <c r="C9" s="285">
         <v>1</v>
       </c>
       <c r="D9" s="7">
@@ -3687,14 +3651,14 @@
         <f t="shared" si="0"/>
         <v>12000</v>
       </c>
-      <c r="F9" s="297"/>
+      <c r="F9" s="288"/>
     </row>
     <row r="10" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A10" s="296"/>
-      <c r="B10" s="293" t="s">
+      <c r="A10" s="287"/>
+      <c r="B10" s="284" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="294">
+      <c r="C10" s="285">
         <v>3</v>
       </c>
       <c r="D10" s="7">
@@ -3704,14 +3668,14 @@
         <f t="shared" si="0"/>
         <v>72000</v>
       </c>
-      <c r="F10" s="297"/>
+      <c r="F10" s="288"/>
     </row>
     <row r="11" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A11" s="296"/>
-      <c r="B11" s="293" t="s">
+      <c r="A11" s="287"/>
+      <c r="B11" s="284" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="294">
+      <c r="C11" s="285">
         <v>1</v>
       </c>
       <c r="D11" s="7">
@@ -3721,14 +3685,14 @@
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="F11" s="297"/>
+      <c r="F11" s="288"/>
     </row>
     <row r="12" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A12" s="298"/>
-      <c r="B12" s="293" t="s">
+      <c r="A12" s="289"/>
+      <c r="B12" s="284" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="294">
+      <c r="C12" s="285">
         <v>1</v>
       </c>
       <c r="D12" s="7">
@@ -3738,16 +3702,16 @@
         <f t="shared" si="0"/>
         <v>49000</v>
       </c>
-      <c r="F12" s="299"/>
+      <c r="F12" s="290"/>
     </row>
     <row r="13" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A13" s="292">
+      <c r="A13" s="283">
         <v>45996</v>
       </c>
-      <c r="B13" s="293" t="s">
+      <c r="B13" s="284" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="294">
+      <c r="C13" s="285">
         <v>8</v>
       </c>
       <c r="D13" s="7">
@@ -3757,17 +3721,17 @@
         <f t="shared" si="0"/>
         <v>80000</v>
       </c>
-      <c r="F13" s="295">
+      <c r="F13" s="286">
         <f>SUM(E13:E25)</f>
         <v>730000</v>
       </c>
     </row>
     <row r="14" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A14" s="296"/>
-      <c r="B14" s="293" t="s">
+      <c r="A14" s="287"/>
+      <c r="B14" s="284" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="294">
+      <c r="C14" s="285">
         <v>2</v>
       </c>
       <c r="D14" s="7">
@@ -3777,14 +3741,14 @@
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="F14" s="297"/>
+      <c r="F14" s="288"/>
     </row>
     <row r="15" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A15" s="296"/>
-      <c r="B15" s="293" t="s">
+      <c r="A15" s="287"/>
+      <c r="B15" s="284" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="294">
+      <c r="C15" s="285">
         <v>2</v>
       </c>
       <c r="D15" s="7">
@@ -3794,14 +3758,14 @@
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
-      <c r="F15" s="297"/>
+      <c r="F15" s="288"/>
     </row>
     <row r="16" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A16" s="296"/>
-      <c r="B16" s="293" t="s">
+      <c r="A16" s="287"/>
+      <c r="B16" s="284" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="294">
+      <c r="C16" s="285">
         <v>0.5</v>
       </c>
       <c r="D16" s="7">
@@ -3810,14 +3774,14 @@
       <c r="E16" s="7">
         <v>48000</v>
       </c>
-      <c r="F16" s="297"/>
+      <c r="F16" s="288"/>
     </row>
     <row r="17" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A17" s="296"/>
-      <c r="B17" s="293" t="s">
+      <c r="A17" s="287"/>
+      <c r="B17" s="284" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="294">
+      <c r="C17" s="285">
         <v>1.1</v>
       </c>
       <c r="D17" s="7">
@@ -3826,14 +3790,14 @@
       <c r="E17" s="7">
         <v>42000</v>
       </c>
-      <c r="F17" s="297"/>
+      <c r="F17" s="288"/>
     </row>
     <row r="18" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A18" s="296"/>
-      <c r="B18" s="293" t="s">
+      <c r="A18" s="287"/>
+      <c r="B18" s="284" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="294">
+      <c r="C18" s="285">
         <v>5</v>
       </c>
       <c r="D18" s="7">
@@ -3843,32 +3807,32 @@
         <f t="shared" ref="E18:E25" si="1">SUM(C18*D18)</f>
         <v>120000</v>
       </c>
-      <c r="F18" s="297"/>
+      <c r="F18" s="288"/>
     </row>
     <row r="19" s="245" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A19" s="296"/>
-      <c r="B19" s="300" t="s">
+      <c r="A19" s="287"/>
+      <c r="B19" s="291" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="301">
+      <c r="C19" s="292">
         <v>3</v>
       </c>
-      <c r="D19" s="302">
+      <c r="D19" s="293">
         <v>40000</v>
       </c>
       <c r="E19" s="7">
         <f t="shared" si="1"/>
         <v>120000</v>
       </c>
-      <c r="F19" s="297"/>
-      <c r="G19" s="280"/>
+      <c r="F19" s="288"/>
+      <c r="G19" s="271"/>
     </row>
     <row r="20" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A20" s="296"/>
-      <c r="B20" s="303" t="s">
+      <c r="A20" s="287"/>
+      <c r="B20" s="294" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="294">
+      <c r="C20" s="285">
         <v>1</v>
       </c>
       <c r="D20" s="257">
@@ -3878,14 +3842,14 @@
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F20" s="297"/>
+      <c r="F20" s="288"/>
     </row>
     <row r="21" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A21" s="296"/>
-      <c r="B21" s="303" t="s">
+      <c r="A21" s="287"/>
+      <c r="B21" s="294" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="294">
+      <c r="C21" s="285">
         <v>2</v>
       </c>
       <c r="D21" s="257">
@@ -3895,14 +3859,14 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F21" s="297"/>
+      <c r="F21" s="288"/>
     </row>
     <row r="22" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A22" s="296"/>
-      <c r="B22" s="303" t="s">
+      <c r="A22" s="287"/>
+      <c r="B22" s="294" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="294">
+      <c r="C22" s="285">
         <v>0.5</v>
       </c>
       <c r="D22" s="257">
@@ -3912,14 +3876,14 @@
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
-      <c r="F22" s="297"/>
+      <c r="F22" s="288"/>
     </row>
     <row r="23" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A23" s="296"/>
-      <c r="B23" s="303" t="s">
+      <c r="A23" s="287"/>
+      <c r="B23" s="294" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="294">
+      <c r="C23" s="285">
         <v>1</v>
       </c>
       <c r="D23" s="257">
@@ -3929,14 +3893,14 @@
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="F23" s="297"/>
+      <c r="F23" s="288"/>
     </row>
     <row r="24" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A24" s="296"/>
-      <c r="B24" s="303" t="s">
+      <c r="A24" s="287"/>
+      <c r="B24" s="294" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="294">
+      <c r="C24" s="285">
         <v>0.3</v>
       </c>
       <c r="D24" s="257">
@@ -3946,14 +3910,14 @@
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F24" s="297"/>
+      <c r="F24" s="288"/>
     </row>
     <row r="25" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A25" s="298"/>
-      <c r="B25" s="303" t="s">
+      <c r="A25" s="289"/>
+      <c r="B25" s="294" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="294">
+      <c r="C25" s="285">
         <v>1</v>
       </c>
       <c r="D25" s="257">
@@ -3963,16 +3927,16 @@
         <f t="shared" si="1"/>
         <v>35000</v>
       </c>
-      <c r="F25" s="299"/>
+      <c r="F25" s="290"/>
     </row>
     <row r="26" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A26" s="292">
+      <c r="A26" s="283">
         <v>45997</v>
       </c>
-      <c r="B26" s="303" t="s">
+      <c r="B26" s="294" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="294">
+      <c r="C26" s="285">
         <v>3.995</v>
       </c>
       <c r="D26" s="257">
@@ -3981,17 +3945,17 @@
       <c r="E26" s="7">
         <v>60000</v>
       </c>
-      <c r="F26" s="295">
+      <c r="F26" s="286">
         <f>SUM(E26:E34)</f>
         <v>422000</v>
       </c>
     </row>
     <row r="27" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A27" s="296"/>
-      <c r="B27" s="303" t="s">
+      <c r="A27" s="287"/>
+      <c r="B27" s="294" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="294">
+      <c r="C27" s="285">
         <v>2</v>
       </c>
       <c r="D27" s="257">
@@ -4001,14 +3965,14 @@
         <f>SUM(C27*D27)</f>
         <v>40000</v>
       </c>
-      <c r="F27" s="297"/>
+      <c r="F27" s="288"/>
     </row>
     <row r="28" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A28" s="296"/>
-      <c r="B28" s="303" t="s">
+      <c r="A28" s="287"/>
+      <c r="B28" s="294" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="294">
+      <c r="C28" s="285">
         <v>0.5</v>
       </c>
       <c r="D28" s="257">
@@ -4017,14 +3981,14 @@
       <c r="E28" s="7">
         <v>18000</v>
       </c>
-      <c r="F28" s="297"/>
+      <c r="F28" s="288"/>
     </row>
     <row r="29" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A29" s="296"/>
-      <c r="B29" s="303" t="s">
+      <c r="A29" s="287"/>
+      <c r="B29" s="294" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="294">
+      <c r="C29" s="285">
         <v>0.1</v>
       </c>
       <c r="D29" s="257">
@@ -4034,14 +3998,14 @@
         <f t="shared" ref="E29:E34" si="2">SUM(C29*D29)</f>
         <v>8000</v>
       </c>
-      <c r="F29" s="297"/>
+      <c r="F29" s="288"/>
     </row>
     <row r="30" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A30" s="296"/>
-      <c r="B30" s="303" t="s">
+      <c r="A30" s="287"/>
+      <c r="B30" s="294" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="294">
+      <c r="C30" s="285">
         <v>0.5</v>
       </c>
       <c r="D30" s="257">
@@ -4051,14 +4015,14 @@
         <f t="shared" si="2"/>
         <v>15000</v>
       </c>
-      <c r="F30" s="297"/>
+      <c r="F30" s="288"/>
     </row>
     <row r="31" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A31" s="296"/>
-      <c r="B31" s="303" t="s">
+      <c r="A31" s="287"/>
+      <c r="B31" s="294" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="294">
+      <c r="C31" s="285">
         <v>4</v>
       </c>
       <c r="D31" s="257">
@@ -4068,14 +4032,14 @@
         <f t="shared" si="2"/>
         <v>80000</v>
       </c>
-      <c r="F31" s="297"/>
+      <c r="F31" s="288"/>
     </row>
     <row r="32" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A32" s="296"/>
-      <c r="B32" s="293" t="s">
+      <c r="A32" s="287"/>
+      <c r="B32" s="284" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="294">
+      <c r="C32" s="285">
         <v>4</v>
       </c>
       <c r="D32" s="7">
@@ -4085,14 +4049,14 @@
         <f t="shared" si="2"/>
         <v>96000</v>
       </c>
-      <c r="F32" s="297"/>
+      <c r="F32" s="288"/>
     </row>
     <row r="33" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A33" s="296"/>
-      <c r="B33" s="293" t="s">
+      <c r="A33" s="287"/>
+      <c r="B33" s="284" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="294">
+      <c r="C33" s="285">
         <v>2</v>
       </c>
       <c r="D33" s="7">
@@ -4102,14 +4066,14 @@
         <f t="shared" si="2"/>
         <v>80000</v>
       </c>
-      <c r="F33" s="297"/>
+      <c r="F33" s="288"/>
     </row>
     <row r="34" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A34" s="298"/>
-      <c r="B34" s="293" t="s">
+      <c r="A34" s="289"/>
+      <c r="B34" s="284" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="294">
+      <c r="C34" s="285">
         <v>1</v>
       </c>
       <c r="D34" s="7">
@@ -4119,16 +4083,16 @@
         <f t="shared" si="2"/>
         <v>25000</v>
       </c>
-      <c r="F34" s="299"/>
+      <c r="F34" s="290"/>
     </row>
     <row r="35" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A35" s="304">
+      <c r="A35" s="295">
         <v>45998</v>
       </c>
-      <c r="B35" s="303" t="s">
+      <c r="B35" s="294" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="294">
+      <c r="C35" s="285">
         <v>8.945</v>
       </c>
       <c r="D35" s="7">
@@ -4137,17 +4101,17 @@
       <c r="E35" s="7">
         <v>134000</v>
       </c>
-      <c r="F35" s="297">
+      <c r="F35" s="288">
         <f>SUM(E35:E42)</f>
         <v>517000</v>
       </c>
     </row>
     <row r="36" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A36" s="304"/>
-      <c r="B36" s="303" t="s">
+      <c r="A36" s="295"/>
+      <c r="B36" s="294" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="294">
+      <c r="C36" s="285">
         <v>2</v>
       </c>
       <c r="D36" s="7">
@@ -4157,14 +4121,14 @@
         <f t="shared" ref="E35:E44" si="3">SUM(C36*D36)</f>
         <v>40000</v>
       </c>
-      <c r="F36" s="297"/>
+      <c r="F36" s="288"/>
     </row>
     <row r="37" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A37" s="304"/>
-      <c r="B37" s="303" t="s">
+      <c r="A37" s="295"/>
+      <c r="B37" s="294" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="294">
+      <c r="C37" s="285">
         <v>0.3</v>
       </c>
       <c r="D37" s="7">
@@ -4174,14 +4138,14 @@
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="F37" s="297"/>
+      <c r="F37" s="288"/>
     </row>
     <row r="38" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A38" s="304"/>
-      <c r="B38" s="303" t="s">
+      <c r="A38" s="295"/>
+      <c r="B38" s="294" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="294">
+      <c r="C38" s="285">
         <v>1</v>
       </c>
       <c r="D38" s="7">
@@ -4191,14 +4155,14 @@
         <f t="shared" si="3"/>
         <v>30000</v>
       </c>
-      <c r="F38" s="297"/>
+      <c r="F38" s="288"/>
     </row>
     <row r="39" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A39" s="304"/>
-      <c r="B39" s="303" t="s">
+      <c r="A39" s="295"/>
+      <c r="B39" s="294" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="294">
+      <c r="C39" s="285">
         <v>0.5</v>
       </c>
       <c r="D39" s="7">
@@ -4208,14 +4172,14 @@
         <f t="shared" si="3"/>
         <v>15000</v>
       </c>
-      <c r="F39" s="297"/>
+      <c r="F39" s="288"/>
     </row>
     <row r="40" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A40" s="304"/>
-      <c r="B40" s="303" t="s">
+      <c r="A40" s="295"/>
+      <c r="B40" s="294" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="294">
+      <c r="C40" s="285">
         <v>4</v>
       </c>
       <c r="D40" s="7">
@@ -4225,14 +4189,14 @@
         <f t="shared" si="3"/>
         <v>96000</v>
       </c>
-      <c r="F40" s="297"/>
+      <c r="F40" s="288"/>
     </row>
     <row r="41" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A41" s="304"/>
-      <c r="B41" s="303" t="s">
+      <c r="A41" s="295"/>
+      <c r="B41" s="294" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="294">
+      <c r="C41" s="285">
         <v>2</v>
       </c>
       <c r="D41" s="7">
@@ -4242,14 +4206,14 @@
         <f t="shared" si="3"/>
         <v>80000</v>
       </c>
-      <c r="F41" s="297"/>
+      <c r="F41" s="288"/>
     </row>
     <row r="42" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A42" s="304"/>
-      <c r="B42" s="303" t="s">
+      <c r="A42" s="295"/>
+      <c r="B42" s="294" t="s">
         <v>32</v>
       </c>
-      <c r="C42" s="294">
+      <c r="C42" s="285">
         <v>2</v>
       </c>
       <c r="D42" s="7">
@@ -4259,16 +4223,16 @@
         <f t="shared" si="3"/>
         <v>98000</v>
       </c>
-      <c r="F42" s="297"/>
+      <c r="F42" s="288"/>
     </row>
     <row r="43" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A43" s="292">
+      <c r="A43" s="283">
         <v>45999</v>
       </c>
-      <c r="B43" s="303" t="s">
+      <c r="B43" s="294" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="294">
+      <c r="C43" s="285">
         <v>3</v>
       </c>
       <c r="D43" s="7">
@@ -4278,17 +4242,17 @@
         <f t="shared" si="3"/>
         <v>30000</v>
       </c>
-      <c r="F43" s="305">
+      <c r="F43" s="296">
         <f>SUM(E43:E47)</f>
         <v>357000</v>
       </c>
     </row>
     <row r="44" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A44" s="296"/>
-      <c r="B44" s="303" t="s">
+      <c r="A44" s="287"/>
+      <c r="B44" s="294" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="294">
+      <c r="C44" s="285">
         <v>2.7</v>
       </c>
       <c r="D44" s="7">
@@ -4298,14 +4262,14 @@
         <f t="shared" si="3"/>
         <v>54000</v>
       </c>
-      <c r="F44" s="305"/>
+      <c r="F44" s="296"/>
     </row>
     <row r="45" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A45" s="296"/>
-      <c r="B45" s="303" t="s">
+      <c r="A45" s="287"/>
+      <c r="B45" s="294" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="294">
+      <c r="C45" s="285">
         <v>3.09</v>
       </c>
       <c r="D45" s="7">
@@ -4314,14 +4278,14 @@
       <c r="E45" s="7">
         <v>216000</v>
       </c>
-      <c r="F45" s="305"/>
+      <c r="F45" s="296"/>
     </row>
     <row r="46" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A46" s="296"/>
-      <c r="B46" s="303" t="s">
+      <c r="A46" s="287"/>
+      <c r="B46" s="294" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="294">
+      <c r="C46" s="285">
         <v>0.3</v>
       </c>
       <c r="D46" s="7">
@@ -4331,14 +4295,14 @@
         <f>SUM(C46*D46)</f>
         <v>9000</v>
       </c>
-      <c r="F46" s="305"/>
+      <c r="F46" s="296"/>
     </row>
     <row r="47" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A47" s="296"/>
-      <c r="B47" s="303" t="s">
+      <c r="A47" s="287"/>
+      <c r="B47" s="294" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="294">
+      <c r="C47" s="285">
         <v>2</v>
       </c>
       <c r="D47" s="7">
@@ -4348,16 +4312,16 @@
         <f>SUM(C47*D47)</f>
         <v>48000</v>
       </c>
-      <c r="F47" s="305"/>
+      <c r="F47" s="296"/>
     </row>
     <row r="48" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A48" s="292">
+      <c r="A48" s="283">
         <v>46000</v>
       </c>
-      <c r="B48" s="303" t="s">
+      <c r="B48" s="294" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="294">
+      <c r="C48" s="285">
         <v>2</v>
       </c>
       <c r="D48" s="7">
@@ -4367,17 +4331,17 @@
         <f t="shared" ref="E48:E81" si="4">SUM(C48*D48)</f>
         <v>40000</v>
       </c>
-      <c r="F48" s="295">
+      <c r="F48" s="286">
         <f>SUM(E48:E58)</f>
         <v>612000</v>
       </c>
     </row>
     <row r="49" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A49" s="296"/>
-      <c r="B49" s="303" t="s">
+      <c r="A49" s="287"/>
+      <c r="B49" s="294" t="s">
         <v>17</v>
       </c>
-      <c r="C49" s="294">
+      <c r="C49" s="285">
         <v>2</v>
       </c>
       <c r="D49" s="7">
@@ -4387,14 +4351,14 @@
         <f t="shared" si="4"/>
         <v>70000</v>
       </c>
-      <c r="F49" s="297"/>
+      <c r="F49" s="288"/>
     </row>
     <row r="50" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A50" s="296"/>
-      <c r="B50" s="303" t="s">
+      <c r="A50" s="287"/>
+      <c r="B50" s="294" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="294">
+      <c r="C50" s="285">
         <v>5</v>
       </c>
       <c r="D50" s="7">
@@ -4404,14 +4368,14 @@
         <f t="shared" si="4"/>
         <v>120000</v>
       </c>
-      <c r="F50" s="297"/>
+      <c r="F50" s="288"/>
     </row>
     <row r="51" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A51" s="296"/>
-      <c r="B51" s="303" t="s">
+      <c r="A51" s="287"/>
+      <c r="B51" s="294" t="s">
         <v>32</v>
       </c>
-      <c r="C51" s="294">
+      <c r="C51" s="285">
         <v>1</v>
       </c>
       <c r="D51" s="7">
@@ -4421,14 +4385,14 @@
         <f t="shared" si="4"/>
         <v>49000</v>
       </c>
-      <c r="F51" s="297"/>
+      <c r="F51" s="288"/>
     </row>
     <row r="52" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A52" s="296"/>
-      <c r="B52" s="303" t="s">
+      <c r="A52" s="287"/>
+      <c r="B52" s="294" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="294">
+      <c r="C52" s="285">
         <v>1</v>
       </c>
       <c r="D52" s="7">
@@ -4438,14 +4402,14 @@
         <f t="shared" si="4"/>
         <v>65000</v>
       </c>
-      <c r="F52" s="297"/>
+      <c r="F52" s="288"/>
     </row>
     <row r="53" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A53" s="296"/>
-      <c r="B53" s="303" t="s">
+      <c r="A53" s="287"/>
+      <c r="B53" s="294" t="s">
         <v>18</v>
       </c>
-      <c r="C53" s="294">
+      <c r="C53" s="285">
         <v>0.5</v>
       </c>
       <c r="D53" s="7">
@@ -4454,14 +4418,14 @@
       <c r="E53" s="7">
         <v>48000</v>
       </c>
-      <c r="F53" s="297"/>
+      <c r="F53" s="288"/>
     </row>
     <row r="54" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A54" s="296"/>
-      <c r="B54" s="303" t="s">
+      <c r="A54" s="287"/>
+      <c r="B54" s="294" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="294">
+      <c r="C54" s="285">
         <v>1</v>
       </c>
       <c r="D54" s="7">
@@ -4471,14 +4435,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F54" s="297"/>
+      <c r="F54" s="288"/>
     </row>
     <row r="55" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A55" s="296"/>
-      <c r="B55" s="303" t="s">
+      <c r="A55" s="287"/>
+      <c r="B55" s="294" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="294">
+      <c r="C55" s="285">
         <v>9</v>
       </c>
       <c r="D55" s="7">
@@ -4488,14 +4452,14 @@
         <f t="shared" si="4"/>
         <v>90000</v>
       </c>
-      <c r="F55" s="297"/>
+      <c r="F55" s="288"/>
     </row>
     <row r="56" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A56" s="296"/>
-      <c r="B56" s="293" t="s">
+      <c r="A56" s="287"/>
+      <c r="B56" s="284" t="s">
         <v>7</v>
       </c>
-      <c r="C56" s="294">
+      <c r="C56" s="285">
         <v>1</v>
       </c>
       <c r="D56" s="7">
@@ -4505,14 +4469,14 @@
         <f t="shared" si="4"/>
         <v>70000</v>
       </c>
-      <c r="F56" s="297"/>
+      <c r="F56" s="288"/>
     </row>
     <row r="57" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A57" s="296"/>
-      <c r="B57" s="293" t="s">
+      <c r="A57" s="287"/>
+      <c r="B57" s="284" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="294">
+      <c r="C57" s="285">
         <v>2</v>
       </c>
       <c r="D57" s="7">
@@ -4522,14 +4486,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F57" s="297"/>
+      <c r="F57" s="288"/>
     </row>
     <row r="58" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A58" s="298"/>
-      <c r="B58" s="293" t="s">
+      <c r="A58" s="289"/>
+      <c r="B58" s="284" t="s">
         <v>34</v>
       </c>
-      <c r="C58" s="294">
+      <c r="C58" s="285">
         <v>1</v>
       </c>
       <c r="D58" s="7">
@@ -4539,16 +4503,16 @@
         <f t="shared" si="4"/>
         <v>5000</v>
       </c>
-      <c r="F58" s="299"/>
+      <c r="F58" s="290"/>
     </row>
     <row r="59" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A59" s="292">
+      <c r="A59" s="283">
         <v>46001</v>
       </c>
-      <c r="B59" s="293" t="s">
+      <c r="B59" s="284" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="294">
+      <c r="C59" s="285">
         <v>3</v>
       </c>
       <c r="D59" s="7">
@@ -4558,17 +4522,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F59" s="295">
+      <c r="F59" s="286">
         <f>SUM(E59:E67)</f>
         <v>586000</v>
       </c>
     </row>
     <row r="60" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A60" s="296"/>
-      <c r="B60" s="293" t="s">
+      <c r="A60" s="287"/>
+      <c r="B60" s="284" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="294">
+      <c r="C60" s="285">
         <v>2</v>
       </c>
       <c r="D60" s="7">
@@ -4578,14 +4542,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F60" s="297"/>
+      <c r="F60" s="288"/>
     </row>
     <row r="61" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A61" s="296"/>
-      <c r="B61" s="293" t="s">
+      <c r="A61" s="287"/>
+      <c r="B61" s="284" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="294">
+      <c r="C61" s="285">
         <v>8</v>
       </c>
       <c r="D61" s="7">
@@ -4595,14 +4559,14 @@
         <f t="shared" si="4"/>
         <v>80000</v>
       </c>
-      <c r="F61" s="297"/>
+      <c r="F61" s="288"/>
     </row>
     <row r="62" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A62" s="296"/>
-      <c r="B62" s="293" t="s">
+      <c r="A62" s="287"/>
+      <c r="B62" s="284" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="294">
+      <c r="C62" s="285">
         <v>1</v>
       </c>
       <c r="D62" s="7">
@@ -4612,14 +4576,14 @@
         <f t="shared" si="4"/>
         <v>38000</v>
       </c>
-      <c r="F62" s="297"/>
+      <c r="F62" s="288"/>
     </row>
     <row r="63" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A63" s="296"/>
-      <c r="B63" s="293" t="s">
+      <c r="A63" s="287"/>
+      <c r="B63" s="284" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="294">
+      <c r="C63" s="285">
         <v>1</v>
       </c>
       <c r="D63" s="7">
@@ -4629,14 +4593,14 @@
         <f t="shared" si="4"/>
         <v>20000</v>
       </c>
-      <c r="F63" s="297"/>
+      <c r="F63" s="288"/>
     </row>
     <row r="64" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A64" s="296"/>
-      <c r="B64" s="293" t="s">
+      <c r="A64" s="287"/>
+      <c r="B64" s="284" t="s">
         <v>22</v>
       </c>
-      <c r="C64" s="294">
+      <c r="C64" s="285">
         <v>0.5</v>
       </c>
       <c r="D64" s="7">
@@ -4646,14 +4610,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F64" s="297"/>
+      <c r="F64" s="288"/>
     </row>
     <row r="65" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A65" s="296"/>
-      <c r="B65" s="293" t="s">
+      <c r="A65" s="287"/>
+      <c r="B65" s="284" t="s">
         <v>14</v>
       </c>
-      <c r="C65" s="294">
+      <c r="C65" s="285">
         <v>6</v>
       </c>
       <c r="D65" s="7">
@@ -4663,14 +4627,14 @@
         <f t="shared" si="4"/>
         <v>144000</v>
       </c>
-      <c r="F65" s="297"/>
+      <c r="F65" s="288"/>
     </row>
     <row r="66" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A66" s="296"/>
-      <c r="B66" s="293" t="s">
+      <c r="A66" s="287"/>
+      <c r="B66" s="284" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="294">
+      <c r="C66" s="285">
         <v>1</v>
       </c>
       <c r="D66" s="7">
@@ -4680,14 +4644,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F66" s="297"/>
+      <c r="F66" s="288"/>
     </row>
     <row r="67" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A67" s="298"/>
-      <c r="B67" s="293" t="s">
+      <c r="A67" s="289"/>
+      <c r="B67" s="284" t="s">
         <v>32</v>
       </c>
-      <c r="C67" s="294">
+      <c r="C67" s="285">
         <v>1</v>
       </c>
       <c r="D67" s="7">
@@ -4697,16 +4661,16 @@
         <f t="shared" si="4"/>
         <v>49000</v>
       </c>
-      <c r="F67" s="299"/>
+      <c r="F67" s="290"/>
     </row>
     <row r="68" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A68" s="292">
+      <c r="A68" s="283">
         <v>46002</v>
       </c>
-      <c r="B68" s="293" t="s">
+      <c r="B68" s="284" t="s">
         <v>6</v>
       </c>
-      <c r="C68" s="294">
+      <c r="C68" s="285">
         <v>3</v>
       </c>
       <c r="D68" s="7">
@@ -4716,17 +4680,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F68" s="295">
+      <c r="F68" s="286">
         <f>SUM(E68:E78)</f>
         <v>541000</v>
       </c>
     </row>
     <row r="69" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A69" s="296"/>
-      <c r="B69" s="293" t="s">
+      <c r="A69" s="287"/>
+      <c r="B69" s="284" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="294">
+      <c r="C69" s="285">
         <v>2</v>
       </c>
       <c r="D69" s="7">
@@ -4736,14 +4700,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F69" s="297"/>
+      <c r="F69" s="288"/>
     </row>
     <row r="70" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A70" s="296"/>
-      <c r="B70" s="293" t="s">
+      <c r="A70" s="287"/>
+      <c r="B70" s="284" t="s">
         <v>8</v>
       </c>
-      <c r="C70" s="294">
+      <c r="C70" s="285">
         <v>4</v>
       </c>
       <c r="D70" s="7">
@@ -4753,14 +4717,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F70" s="297"/>
+      <c r="F70" s="288"/>
     </row>
     <row r="71" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A71" s="296"/>
-      <c r="B71" s="293" t="s">
+      <c r="A71" s="287"/>
+      <c r="B71" s="284" t="s">
         <v>9</v>
       </c>
-      <c r="C71" s="294">
+      <c r="C71" s="285">
         <v>1</v>
       </c>
       <c r="D71" s="7">
@@ -4770,14 +4734,14 @@
         <f t="shared" si="4"/>
         <v>38000</v>
       </c>
-      <c r="F71" s="297"/>
+      <c r="F71" s="288"/>
     </row>
     <row r="72" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A72" s="296"/>
-      <c r="B72" s="293" t="s">
+      <c r="A72" s="287"/>
+      <c r="B72" s="284" t="s">
         <v>10</v>
       </c>
-      <c r="C72" s="294">
+      <c r="C72" s="285">
         <v>1</v>
       </c>
       <c r="D72" s="7">
@@ -4787,14 +4751,14 @@
         <f t="shared" si="4"/>
         <v>20000</v>
       </c>
-      <c r="F72" s="297"/>
+      <c r="F72" s="288"/>
     </row>
     <row r="73" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A73" s="296"/>
-      <c r="B73" s="293" t="s">
+      <c r="A73" s="287"/>
+      <c r="B73" s="284" t="s">
         <v>22</v>
       </c>
-      <c r="C73" s="294">
+      <c r="C73" s="285">
         <v>0.5</v>
       </c>
       <c r="D73" s="7">
@@ -4804,14 +4768,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F73" s="297"/>
+      <c r="F73" s="288"/>
     </row>
     <row r="74" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A74" s="296"/>
-      <c r="B74" s="293" t="s">
+      <c r="A74" s="287"/>
+      <c r="B74" s="284" t="s">
         <v>12</v>
       </c>
-      <c r="C74" s="294">
+      <c r="C74" s="285">
         <v>1</v>
       </c>
       <c r="D74" s="7">
@@ -4821,14 +4785,14 @@
         <f t="shared" si="4"/>
         <v>30000</v>
       </c>
-      <c r="F74" s="297"/>
+      <c r="F74" s="288"/>
     </row>
     <row r="75" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A75" s="296"/>
-      <c r="B75" s="293" t="s">
+      <c r="A75" s="287"/>
+      <c r="B75" s="284" t="s">
         <v>18</v>
       </c>
-      <c r="C75" s="294">
+      <c r="C75" s="285">
         <v>1</v>
       </c>
       <c r="D75" s="7">
@@ -4838,14 +4802,14 @@
         <f t="shared" si="4"/>
         <v>95000</v>
       </c>
-      <c r="F75" s="297"/>
+      <c r="F75" s="288"/>
     </row>
     <row r="76" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A76" s="296"/>
-      <c r="B76" s="293" t="s">
+      <c r="A76" s="287"/>
+      <c r="B76" s="284" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="294">
+      <c r="C76" s="285">
         <v>1</v>
       </c>
       <c r="D76" s="7">
@@ -4855,14 +4819,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F76" s="297"/>
+      <c r="F76" s="288"/>
     </row>
     <row r="77" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A77" s="296"/>
-      <c r="B77" s="293" t="s">
+      <c r="A77" s="287"/>
+      <c r="B77" s="284" t="s">
         <v>14</v>
       </c>
-      <c r="C77" s="294">
+      <c r="C77" s="285">
         <v>2</v>
       </c>
       <c r="D77" s="7">
@@ -4872,14 +4836,14 @@
         <f t="shared" si="4"/>
         <v>48000</v>
       </c>
-      <c r="F77" s="297"/>
+      <c r="F77" s="288"/>
     </row>
     <row r="78" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A78" s="298"/>
-      <c r="B78" s="293" t="s">
+      <c r="A78" s="289"/>
+      <c r="B78" s="284" t="s">
         <v>15</v>
       </c>
-      <c r="C78" s="294">
+      <c r="C78" s="285">
         <v>1</v>
       </c>
       <c r="D78" s="7">
@@ -4889,16 +4853,16 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F78" s="299"/>
+      <c r="F78" s="290"/>
     </row>
     <row r="79" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A79" s="306">
+      <c r="A79" s="283">
         <v>46003</v>
       </c>
-      <c r="B79" s="293" t="s">
+      <c r="B79" s="284" t="s">
         <v>6</v>
       </c>
-      <c r="C79" s="294">
+      <c r="C79" s="285">
         <v>3</v>
       </c>
       <c r="D79" s="7">
@@ -4908,17 +4872,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F79" s="307">
+      <c r="F79" s="286">
         <f>-SUM(E79:E93)</f>
         <v>-900000</v>
       </c>
     </row>
     <row r="80" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A80" s="308"/>
-      <c r="B80" s="293" t="s">
+      <c r="A80" s="287"/>
+      <c r="B80" s="284" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="294">
+      <c r="C80" s="285">
         <v>2</v>
       </c>
       <c r="D80" s="7">
@@ -4928,14 +4892,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F80" s="309"/>
+      <c r="F80" s="288"/>
     </row>
     <row r="81" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A81" s="308"/>
-      <c r="B81" s="293" t="s">
+      <c r="A81" s="287"/>
+      <c r="B81" s="284" t="s">
         <v>8</v>
       </c>
-      <c r="C81" s="294">
+      <c r="C81" s="285">
         <v>6</v>
       </c>
       <c r="D81" s="7">
@@ -4945,14 +4909,14 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F81" s="309"/>
+      <c r="F81" s="288"/>
     </row>
     <row r="82" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A82" s="308"/>
-      <c r="B82" s="293" t="s">
+      <c r="A82" s="287"/>
+      <c r="B82" s="284" t="s">
         <v>35</v>
       </c>
-      <c r="C82" s="294">
+      <c r="C82" s="285">
         <v>2</v>
       </c>
       <c r="D82" s="7">
@@ -4962,14 +4926,14 @@
         <f t="shared" ref="E82:E145" si="5">SUM(C82*D82)</f>
         <v>96000</v>
       </c>
-      <c r="F82" s="309"/>
+      <c r="F82" s="288"/>
     </row>
     <row r="83" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A83" s="308"/>
-      <c r="B83" s="293" t="s">
+      <c r="A83" s="287"/>
+      <c r="B83" s="284" t="s">
         <v>24</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="285">
         <v>8.18</v>
       </c>
       <c r="D83" s="7">
@@ -4978,14 +4942,14 @@
       <c r="E83" s="7">
         <v>123000</v>
       </c>
-      <c r="F83" s="309"/>
+      <c r="F83" s="288"/>
     </row>
     <row r="84" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A84" s="308"/>
-      <c r="B84" s="293" t="s">
+      <c r="A84" s="287"/>
+      <c r="B84" s="284" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="294">
+      <c r="C84" s="285">
         <v>0.3</v>
       </c>
       <c r="D84" s="7">
@@ -4995,14 +4959,14 @@
         <f t="shared" si="5"/>
         <v>6000</v>
       </c>
-      <c r="F84" s="309"/>
+      <c r="F84" s="288"/>
     </row>
     <row r="85" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A85" s="308"/>
-      <c r="B85" s="293" t="s">
+      <c r="A85" s="287"/>
+      <c r="B85" s="284" t="s">
         <v>22</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="285">
         <v>0.5</v>
       </c>
       <c r="D85" s="7">
@@ -5012,14 +4976,14 @@
         <f t="shared" si="5"/>
         <v>15000</v>
       </c>
-      <c r="F85" s="309"/>
+      <c r="F85" s="288"/>
     </row>
     <row r="86" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A86" s="308"/>
-      <c r="B86" s="293" t="s">
+      <c r="A86" s="287"/>
+      <c r="B86" s="284" t="s">
         <v>31</v>
       </c>
-      <c r="C86" s="294">
+      <c r="C86" s="285">
         <v>0.5</v>
       </c>
       <c r="D86" s="7">
@@ -5029,14 +4993,14 @@
         <f t="shared" si="5"/>
         <v>40000</v>
       </c>
-      <c r="F86" s="309"/>
+      <c r="F86" s="288"/>
     </row>
     <row r="87" s="245" customFormat="1" ht="14" customHeight="1" spans="1:8">
-      <c r="A87" s="308"/>
-      <c r="B87" s="293" t="s">
+      <c r="A87" s="287"/>
+      <c r="B87" s="284" t="s">
         <v>18</v>
       </c>
-      <c r="C87" s="294">
+      <c r="C87" s="285">
         <v>0.5</v>
       </c>
       <c r="D87" s="7">
@@ -5045,15 +5009,15 @@
       <c r="E87" s="7">
         <v>48000</v>
       </c>
-      <c r="F87" s="309"/>
-      <c r="H87" s="280"/>
+      <c r="F87" s="288"/>
+      <c r="H87" s="271"/>
     </row>
     <row r="88" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A88" s="308"/>
-      <c r="B88" s="293" t="s">
+      <c r="A88" s="287"/>
+      <c r="B88" s="284" t="s">
         <v>13</v>
       </c>
-      <c r="C88" s="294">
+      <c r="C88" s="285">
         <v>1</v>
       </c>
       <c r="D88" s="7">
@@ -5063,14 +5027,14 @@
         <f t="shared" si="5"/>
         <v>15000</v>
       </c>
-      <c r="F88" s="309"/>
+      <c r="F88" s="288"/>
     </row>
     <row r="89" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A89" s="308"/>
-      <c r="B89" s="293" t="s">
+      <c r="A89" s="287"/>
+      <c r="B89" s="284" t="s">
         <v>14</v>
       </c>
-      <c r="C89" s="294">
+      <c r="C89" s="285">
         <v>2</v>
       </c>
       <c r="D89" s="7">
@@ -5080,14 +5044,14 @@
         <f t="shared" si="5"/>
         <v>48000</v>
       </c>
-      <c r="F89" s="309"/>
+      <c r="F89" s="288"/>
     </row>
     <row r="90" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A90" s="308"/>
-      <c r="B90" s="293" t="s">
+      <c r="A90" s="287"/>
+      <c r="B90" s="284" t="s">
         <v>15</v>
       </c>
-      <c r="C90" s="294">
+      <c r="C90" s="285">
         <v>1</v>
       </c>
       <c r="D90" s="7">
@@ -5097,14 +5061,14 @@
         <f t="shared" si="5"/>
         <v>40000</v>
       </c>
-      <c r="F90" s="309"/>
+      <c r="F90" s="288"/>
     </row>
     <row r="91" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A91" s="308"/>
-      <c r="B91" s="293" t="s">
+      <c r="A91" s="287"/>
+      <c r="B91" s="284" t="s">
         <v>32</v>
       </c>
-      <c r="C91" s="294">
+      <c r="C91" s="285">
         <v>1</v>
       </c>
       <c r="D91" s="7">
@@ -5114,14 +5078,14 @@
         <f t="shared" si="5"/>
         <v>49000</v>
       </c>
-      <c r="F91" s="309"/>
+      <c r="F91" s="288"/>
     </row>
     <row r="92" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A92" s="308"/>
-      <c r="B92" s="293" t="s">
+      <c r="A92" s="287"/>
+      <c r="B92" s="284" t="s">
         <v>21</v>
       </c>
-      <c r="C92" s="294">
+      <c r="C92" s="285">
         <v>4</v>
       </c>
       <c r="D92" s="7">
@@ -5131,14 +5095,14 @@
         <f t="shared" si="5"/>
         <v>80000</v>
       </c>
-      <c r="F92" s="309"/>
+      <c r="F92" s="288"/>
     </row>
     <row r="93" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A93" s="310"/>
-      <c r="B93" s="293" t="s">
+      <c r="A93" s="289"/>
+      <c r="B93" s="284" t="s">
         <v>27</v>
       </c>
-      <c r="C93" s="294">
+      <c r="C93" s="285">
         <v>4</v>
       </c>
       <c r="D93" s="7">
@@ -5148,2227 +5112,2250 @@
         <f t="shared" si="5"/>
         <v>80000</v>
       </c>
-      <c r="F93" s="311"/>
+      <c r="F93" s="290"/>
     </row>
     <row r="94" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A94" s="304">
-        <v>46003</v>
-      </c>
-      <c r="B94" s="303" t="s">
-        <v>36</v>
-      </c>
-      <c r="C94" s="312">
-        <v>2</v>
-      </c>
-      <c r="D94" s="7"/>
+      <c r="A94" s="297">
+        <v>46004</v>
+      </c>
+      <c r="B94" s="294" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="298">
+        <v>8</v>
+      </c>
+      <c r="D94" s="7">
+        <v>10000</v>
+      </c>
       <c r="E94" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F94" s="307"/>
+        <v>80000</v>
+      </c>
+      <c r="F94" s="299">
+        <f>SUM(E94:E99)</f>
+        <v>479000</v>
+      </c>
     </row>
     <row r="95" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A95" s="304"/>
-      <c r="B95" s="303" t="s">
-        <v>37</v>
-      </c>
-      <c r="C95" s="312">
-        <v>16</v>
-      </c>
-      <c r="D95" s="7"/>
+      <c r="A95" s="300"/>
+      <c r="B95" s="294" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" s="298">
+        <v>7.155</v>
+      </c>
+      <c r="D95" s="7">
+        <v>15000</v>
+      </c>
       <c r="E95" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F95" s="309"/>
+        <v>107000</v>
+      </c>
+      <c r="F95" s="301"/>
     </row>
     <row r="96" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A96" s="304"/>
-      <c r="B96" s="303" t="s">
-        <v>38</v>
-      </c>
-      <c r="C96" s="312">
-        <v>25</v>
-      </c>
-      <c r="D96" s="7"/>
+      <c r="A96" s="300"/>
+      <c r="B96" s="294" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" s="298">
+        <v>2</v>
+      </c>
+      <c r="D96" s="7">
+        <v>38000</v>
+      </c>
       <c r="E96" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F96" s="311"/>
+        <v>76000</v>
+      </c>
+      <c r="F96" s="301"/>
     </row>
     <row r="97" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A97" s="304"/>
-      <c r="B97" s="303"/>
-      <c r="C97" s="312"/>
-      <c r="D97" s="7"/>
+      <c r="A97" s="300"/>
+      <c r="B97" s="294" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="298">
+        <v>2</v>
+      </c>
+      <c r="D97" s="7">
+        <v>20000</v>
+      </c>
       <c r="E97" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F97" s="313">
-        <f>SUM(E97:E103)</f>
-        <v>0</v>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="F97" s="301"/>
     </row>
     <row r="98" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A98" s="304"/>
-      <c r="B98" s="303"/>
-      <c r="C98" s="312"/>
-      <c r="D98" s="7"/>
+      <c r="A98" s="300"/>
+      <c r="B98" s="294" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" s="298">
+        <v>4</v>
+      </c>
+      <c r="D98" s="7">
+        <v>24000</v>
+      </c>
       <c r="E98" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F98" s="313"/>
+        <v>96000</v>
+      </c>
+      <c r="F98" s="301"/>
     </row>
     <row r="99" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A99" s="304"/>
-      <c r="B99" s="303"/>
-      <c r="C99" s="312"/>
-      <c r="D99" s="7"/>
+      <c r="A99" s="302"/>
+      <c r="B99" s="294" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="298">
+        <v>2</v>
+      </c>
+      <c r="D99" s="7">
+        <v>40000</v>
+      </c>
       <c r="E99" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F99" s="313"/>
+        <v>80000</v>
+      </c>
+      <c r="F99" s="303"/>
     </row>
     <row r="100" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A100" s="304"/>
-      <c r="B100" s="303"/>
-      <c r="C100" s="312"/>
+      <c r="A100" s="295"/>
+      <c r="B100" s="294"/>
+      <c r="C100" s="298"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F100" s="313"/>
+      <c r="F100" s="304"/>
     </row>
     <row r="101" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A101" s="304"/>
-      <c r="B101" s="303"/>
-      <c r="C101" s="312"/>
+      <c r="A101" s="295"/>
+      <c r="B101" s="294"/>
+      <c r="C101" s="298"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F101" s="313"/>
+      <c r="F101" s="304"/>
     </row>
     <row r="102" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A102" s="304"/>
-      <c r="B102" s="303"/>
-      <c r="C102" s="312"/>
+      <c r="A102" s="295"/>
+      <c r="B102" s="294"/>
+      <c r="C102" s="298"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F102" s="313"/>
+      <c r="F102" s="304"/>
     </row>
     <row r="103" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A103" s="304"/>
-      <c r="B103" s="303"/>
-      <c r="C103" s="312"/>
+      <c r="A103" s="295"/>
+      <c r="B103" s="294"/>
+      <c r="C103" s="298"/>
       <c r="D103" s="7"/>
       <c r="E103" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F103" s="313"/>
+      <c r="F103" s="304"/>
     </row>
     <row r="104" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A104" s="304"/>
-      <c r="B104" s="303"/>
-      <c r="C104" s="312"/>
+      <c r="A104" s="295"/>
+      <c r="B104" s="294"/>
+      <c r="C104" s="298"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F104" s="313">
+      <c r="F104" s="304">
         <f>SUM(E104:E118)</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A105" s="304"/>
-      <c r="B105" s="303"/>
-      <c r="C105" s="312"/>
+      <c r="A105" s="295"/>
+      <c r="B105" s="294"/>
+      <c r="C105" s="298"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F105" s="313"/>
+      <c r="F105" s="304"/>
     </row>
     <row r="106" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A106" s="304"/>
-      <c r="B106" s="303"/>
-      <c r="C106" s="312"/>
+      <c r="A106" s="295"/>
+      <c r="B106" s="294"/>
+      <c r="C106" s="298"/>
       <c r="D106" s="7"/>
       <c r="E106" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F106" s="313"/>
+      <c r="F106" s="304"/>
     </row>
     <row r="107" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A107" s="304"/>
-      <c r="B107" s="303"/>
-      <c r="C107" s="312"/>
+      <c r="A107" s="295"/>
+      <c r="B107" s="294"/>
+      <c r="C107" s="298"/>
       <c r="D107" s="7"/>
       <c r="E107" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="304"/>
     </row>
     <row r="108" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A108" s="304"/>
-      <c r="B108" s="303"/>
-      <c r="C108" s="312"/>
+      <c r="A108" s="295"/>
+      <c r="B108" s="294"/>
+      <c r="C108" s="298"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F108" s="313"/>
+      <c r="F108" s="304"/>
     </row>
     <row r="109" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A109" s="304"/>
-      <c r="B109" s="303"/>
-      <c r="C109" s="312"/>
+      <c r="A109" s="295"/>
+      <c r="B109" s="294"/>
+      <c r="C109" s="298"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F109" s="313"/>
+      <c r="F109" s="304"/>
     </row>
     <row r="110" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A110" s="304"/>
-      <c r="B110" s="303"/>
-      <c r="C110" s="312"/>
+      <c r="A110" s="295"/>
+      <c r="B110" s="294"/>
+      <c r="C110" s="298"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F110" s="313"/>
+      <c r="F110" s="304"/>
     </row>
     <row r="111" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A111" s="304"/>
-      <c r="B111" s="303"/>
-      <c r="C111" s="312"/>
+      <c r="A111" s="295"/>
+      <c r="B111" s="294"/>
+      <c r="C111" s="298"/>
       <c r="D111" s="7"/>
       <c r="E111" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F111" s="313"/>
+      <c r="F111" s="304"/>
     </row>
     <row r="112" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A112" s="304"/>
-      <c r="B112" s="303"/>
-      <c r="C112" s="312"/>
+      <c r="A112" s="295"/>
+      <c r="B112" s="294"/>
+      <c r="C112" s="298"/>
       <c r="D112" s="7"/>
       <c r="E112" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F112" s="313"/>
+      <c r="F112" s="304"/>
     </row>
     <row r="113" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A113" s="304"/>
-      <c r="B113" s="303"/>
-      <c r="C113" s="312"/>
+      <c r="A113" s="295"/>
+      <c r="B113" s="294"/>
+      <c r="C113" s="298"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F113" s="313"/>
+      <c r="F113" s="304"/>
     </row>
     <row r="114" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A114" s="304"/>
-      <c r="B114" s="303"/>
-      <c r="C114" s="312"/>
+      <c r="A114" s="295"/>
+      <c r="B114" s="294"/>
+      <c r="C114" s="298"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F114" s="313"/>
+      <c r="F114" s="304"/>
     </row>
     <row r="115" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A115" s="304"/>
-      <c r="B115" s="303"/>
-      <c r="C115" s="312"/>
+      <c r="A115" s="295"/>
+      <c r="B115" s="294"/>
+      <c r="C115" s="298"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F115" s="313"/>
+      <c r="F115" s="304"/>
     </row>
     <row r="116" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A116" s="304"/>
-      <c r="B116" s="303"/>
-      <c r="C116" s="312"/>
+      <c r="A116" s="295"/>
+      <c r="B116" s="294"/>
+      <c r="C116" s="298"/>
       <c r="D116" s="7"/>
       <c r="E116" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F116" s="313"/>
+      <c r="F116" s="304"/>
     </row>
     <row r="117" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A117" s="304"/>
-      <c r="B117" s="303"/>
-      <c r="C117" s="312"/>
+      <c r="A117" s="295"/>
+      <c r="B117" s="294"/>
+      <c r="C117" s="298"/>
       <c r="D117" s="7"/>
       <c r="E117" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F117" s="313"/>
+      <c r="F117" s="304"/>
     </row>
     <row r="118" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A118" s="304"/>
-      <c r="B118" s="303"/>
-      <c r="C118" s="312"/>
+      <c r="A118" s="295"/>
+      <c r="B118" s="294"/>
+      <c r="C118" s="298"/>
       <c r="D118" s="7"/>
       <c r="E118" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F118" s="313"/>
+      <c r="F118" s="304"/>
     </row>
     <row r="119" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A119" s="304"/>
-      <c r="B119" s="303"/>
-      <c r="C119" s="312"/>
+      <c r="A119" s="295"/>
+      <c r="B119" s="294"/>
+      <c r="C119" s="298"/>
       <c r="D119" s="7"/>
       <c r="E119" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F119" s="313">
+      <c r="F119" s="304">
         <f>SUM(E119:E134)</f>
         <v>0</v>
       </c>
     </row>
     <row r="120" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A120" s="304"/>
-      <c r="B120" s="303"/>
-      <c r="C120" s="312"/>
+      <c r="A120" s="295"/>
+      <c r="B120" s="294"/>
+      <c r="C120" s="298"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F120" s="313"/>
+      <c r="F120" s="304"/>
     </row>
     <row r="121" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A121" s="304"/>
-      <c r="B121" s="303"/>
-      <c r="C121" s="312"/>
+      <c r="A121" s="295"/>
+      <c r="B121" s="294"/>
+      <c r="C121" s="298"/>
       <c r="D121" s="7"/>
       <c r="E121" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F121" s="313"/>
+      <c r="F121" s="304"/>
     </row>
     <row r="122" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A122" s="304"/>
-      <c r="B122" s="303"/>
-      <c r="C122" s="312"/>
+      <c r="A122" s="295"/>
+      <c r="B122" s="294"/>
+      <c r="C122" s="298"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F122" s="313"/>
+      <c r="F122" s="304"/>
     </row>
     <row r="123" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A123" s="304"/>
-      <c r="B123" s="303"/>
-      <c r="C123" s="312"/>
+      <c r="A123" s="295"/>
+      <c r="B123" s="294"/>
+      <c r="C123" s="298"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F123" s="313"/>
+      <c r="F123" s="304"/>
     </row>
     <row r="124" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A124" s="304"/>
-      <c r="B124" s="303"/>
-      <c r="C124" s="312"/>
+      <c r="A124" s="295"/>
+      <c r="B124" s="294"/>
+      <c r="C124" s="298"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F124" s="313"/>
+      <c r="F124" s="304"/>
     </row>
     <row r="125" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A125" s="304"/>
-      <c r="B125" s="303"/>
-      <c r="C125" s="312"/>
+      <c r="A125" s="295"/>
+      <c r="B125" s="294"/>
+      <c r="C125" s="298"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F125" s="313"/>
+      <c r="F125" s="304"/>
     </row>
     <row r="126" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A126" s="304"/>
-      <c r="B126" s="303"/>
-      <c r="C126" s="312"/>
+      <c r="A126" s="295"/>
+      <c r="B126" s="294"/>
+      <c r="C126" s="298"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F126" s="313"/>
+      <c r="F126" s="304"/>
     </row>
     <row r="127" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A127" s="304"/>
-      <c r="B127" s="303"/>
-      <c r="C127" s="312"/>
+      <c r="A127" s="295"/>
+      <c r="B127" s="294"/>
+      <c r="C127" s="298"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F127" s="313"/>
+      <c r="F127" s="304"/>
     </row>
     <row r="128" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A128" s="304"/>
-      <c r="B128" s="303"/>
-      <c r="C128" s="312"/>
+      <c r="A128" s="295"/>
+      <c r="B128" s="294"/>
+      <c r="C128" s="298"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F128" s="313"/>
+      <c r="F128" s="304"/>
     </row>
     <row r="129" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A129" s="304"/>
-      <c r="B129" s="303"/>
-      <c r="C129" s="312"/>
+      <c r="A129" s="295"/>
+      <c r="B129" s="294"/>
+      <c r="C129" s="298"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F129" s="313"/>
+      <c r="F129" s="304"/>
     </row>
     <row r="130" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A130" s="304"/>
-      <c r="B130" s="303"/>
-      <c r="C130" s="312"/>
+      <c r="A130" s="295"/>
+      <c r="B130" s="294"/>
+      <c r="C130" s="298"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F130" s="313"/>
+      <c r="F130" s="304"/>
     </row>
     <row r="131" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A131" s="304"/>
-      <c r="B131" s="303"/>
-      <c r="C131" s="312"/>
+      <c r="A131" s="295"/>
+      <c r="B131" s="294"/>
+      <c r="C131" s="298"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F131" s="313"/>
+      <c r="F131" s="304"/>
     </row>
     <row r="132" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A132" s="304"/>
-      <c r="B132" s="303"/>
-      <c r="C132" s="312"/>
+      <c r="A132" s="295"/>
+      <c r="B132" s="294"/>
+      <c r="C132" s="298"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F132" s="313"/>
+      <c r="F132" s="304"/>
     </row>
     <row r="133" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A133" s="304"/>
-      <c r="B133" s="303"/>
-      <c r="C133" s="312"/>
+      <c r="A133" s="295"/>
+      <c r="B133" s="294"/>
+      <c r="C133" s="298"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F133" s="313"/>
+      <c r="F133" s="304"/>
     </row>
     <row r="134" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A134" s="304"/>
-      <c r="B134" s="303"/>
-      <c r="C134" s="312"/>
+      <c r="A134" s="295"/>
+      <c r="B134" s="294"/>
+      <c r="C134" s="298"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F134" s="313"/>
+      <c r="F134" s="304"/>
     </row>
     <row r="135" s="245" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A135" s="304"/>
-      <c r="B135" s="303"/>
-      <c r="C135" s="312"/>
+      <c r="A135" s="295"/>
+      <c r="B135" s="294"/>
+      <c r="C135" s="298"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F135" s="313">
+      <c r="F135" s="304">
         <f>SUM(E135)</f>
         <v>0</v>
       </c>
     </row>
     <row r="136" s="245" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A136" s="304"/>
-      <c r="B136" s="303"/>
-      <c r="C136" s="312"/>
+      <c r="A136" s="295"/>
+      <c r="B136" s="294"/>
+      <c r="C136" s="298"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F136" s="313">
+      <c r="F136" s="304">
         <f>SUM(E136:E140)</f>
         <v>0</v>
       </c>
-      <c r="G136" s="280"/>
+      <c r="G136" s="271"/>
     </row>
     <row r="137" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A137" s="304"/>
-      <c r="B137" s="303"/>
-      <c r="C137" s="312"/>
+      <c r="A137" s="295"/>
+      <c r="B137" s="294"/>
+      <c r="C137" s="298"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F137" s="313"/>
+      <c r="F137" s="304"/>
     </row>
     <row r="138" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A138" s="304"/>
-      <c r="B138" s="303"/>
-      <c r="C138" s="312"/>
+      <c r="A138" s="295"/>
+      <c r="B138" s="294"/>
+      <c r="C138" s="298"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F138" s="313"/>
+      <c r="F138" s="304"/>
     </row>
     <row r="139" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A139" s="304"/>
-      <c r="B139" s="303"/>
-      <c r="C139" s="312"/>
+      <c r="A139" s="295"/>
+      <c r="B139" s="294"/>
+      <c r="C139" s="298"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F139" s="313"/>
+      <c r="F139" s="304"/>
     </row>
     <row r="140" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A140" s="304"/>
-      <c r="B140" s="303"/>
-      <c r="C140" s="312"/>
+      <c r="A140" s="295"/>
+      <c r="B140" s="294"/>
+      <c r="C140" s="298"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F140" s="313"/>
+      <c r="F140" s="304"/>
     </row>
     <row r="141" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A141" s="304"/>
-      <c r="B141" s="314"/>
-      <c r="C141" s="315"/>
-      <c r="D141" s="279"/>
+      <c r="A141" s="295"/>
+      <c r="B141" s="305"/>
+      <c r="C141" s="306"/>
+      <c r="D141" s="270"/>
       <c r="E141" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F141" s="313">
+      <c r="F141" s="304">
         <f>SUM(E141:E147)</f>
         <v>0</v>
       </c>
     </row>
     <row r="142" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A142" s="304"/>
-      <c r="B142" s="303"/>
-      <c r="C142" s="312"/>
+      <c r="A142" s="295"/>
+      <c r="B142" s="294"/>
+      <c r="C142" s="298"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F142" s="313"/>
+      <c r="F142" s="304"/>
     </row>
     <row r="143" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A143" s="304"/>
-      <c r="B143" s="303"/>
-      <c r="C143" s="312"/>
+      <c r="A143" s="295"/>
+      <c r="B143" s="294"/>
+      <c r="C143" s="298"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F143" s="313"/>
+      <c r="F143" s="304"/>
     </row>
     <row r="144" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A144" s="304"/>
-      <c r="B144" s="303"/>
-      <c r="C144" s="312"/>
+      <c r="A144" s="295"/>
+      <c r="B144" s="294"/>
+      <c r="C144" s="298"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F144" s="313"/>
+      <c r="F144" s="304"/>
     </row>
     <row r="145" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A145" s="304"/>
-      <c r="B145" s="303"/>
-      <c r="C145" s="312"/>
+      <c r="A145" s="295"/>
+      <c r="B145" s="294"/>
+      <c r="C145" s="298"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F145" s="313"/>
+      <c r="F145" s="304"/>
     </row>
     <row r="146" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A146" s="304"/>
-      <c r="B146" s="303"/>
-      <c r="C146" s="312"/>
+      <c r="A146" s="295"/>
+      <c r="B146" s="294"/>
+      <c r="C146" s="298"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7">
         <f t="shared" ref="E146:E209" si="6">SUM(C146*D146)</f>
         <v>0</v>
       </c>
-      <c r="F146" s="313"/>
+      <c r="F146" s="304"/>
     </row>
     <row r="147" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A147" s="304"/>
-      <c r="B147" s="303"/>
-      <c r="C147" s="312"/>
+      <c r="A147" s="295"/>
+      <c r="B147" s="294"/>
+      <c r="C147" s="298"/>
       <c r="D147" s="257"/>
       <c r="E147" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F147" s="313"/>
+      <c r="F147" s="304"/>
     </row>
     <row r="148" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A148" s="304"/>
-      <c r="B148" s="303"/>
-      <c r="C148" s="312"/>
+      <c r="A148" s="295"/>
+      <c r="B148" s="294"/>
+      <c r="C148" s="298"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F148" s="313">
+      <c r="F148" s="304">
         <f>SUM(E148:E155)</f>
         <v>0</v>
       </c>
     </row>
     <row r="149" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A149" s="304"/>
-      <c r="B149" s="303"/>
-      <c r="C149" s="312"/>
+      <c r="A149" s="295"/>
+      <c r="B149" s="294"/>
+      <c r="C149" s="298"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F149" s="313"/>
+      <c r="F149" s="304"/>
     </row>
     <row r="150" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A150" s="304"/>
-      <c r="B150" s="303"/>
-      <c r="C150" s="312"/>
+      <c r="A150" s="295"/>
+      <c r="B150" s="294"/>
+      <c r="C150" s="298"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F150" s="313"/>
+      <c r="F150" s="304"/>
     </row>
     <row r="151" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A151" s="304"/>
-      <c r="B151" s="303"/>
-      <c r="C151" s="312"/>
+      <c r="A151" s="295"/>
+      <c r="B151" s="294"/>
+      <c r="C151" s="298"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F151" s="313"/>
+      <c r="F151" s="304"/>
     </row>
     <row r="152" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A152" s="304"/>
-      <c r="B152" s="303"/>
-      <c r="C152" s="312"/>
+      <c r="A152" s="295"/>
+      <c r="B152" s="294"/>
+      <c r="C152" s="298"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F152" s="313"/>
+      <c r="F152" s="304"/>
     </row>
     <row r="153" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A153" s="304"/>
-      <c r="B153" s="303"/>
-      <c r="C153" s="312"/>
+      <c r="A153" s="295"/>
+      <c r="B153" s="294"/>
+      <c r="C153" s="298"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F153" s="313"/>
+      <c r="F153" s="304"/>
     </row>
     <row r="154" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A154" s="304"/>
-      <c r="B154" s="303"/>
-      <c r="C154" s="312"/>
+      <c r="A154" s="295"/>
+      <c r="B154" s="294"/>
+      <c r="C154" s="298"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F154" s="313"/>
+      <c r="F154" s="304"/>
     </row>
     <row r="155" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A155" s="304"/>
-      <c r="B155" s="303"/>
-      <c r="C155" s="312"/>
+      <c r="A155" s="295"/>
+      <c r="B155" s="294"/>
+      <c r="C155" s="298"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F155" s="313"/>
+      <c r="F155" s="304"/>
     </row>
     <row r="156" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A156" s="304"/>
-      <c r="B156" s="303"/>
-      <c r="C156" s="312"/>
+      <c r="A156" s="295"/>
+      <c r="B156" s="294"/>
+      <c r="C156" s="298"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F156" s="313">
+      <c r="F156" s="304">
         <f>SUM(E156:E162)</f>
         <v>0</v>
       </c>
     </row>
     <row r="157" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A157" s="304"/>
-      <c r="B157" s="303"/>
-      <c r="C157" s="312"/>
+      <c r="A157" s="295"/>
+      <c r="B157" s="294"/>
+      <c r="C157" s="298"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F157" s="313"/>
+      <c r="F157" s="304"/>
     </row>
     <row r="158" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A158" s="304"/>
-      <c r="B158" s="303"/>
-      <c r="C158" s="312"/>
+      <c r="A158" s="295"/>
+      <c r="B158" s="294"/>
+      <c r="C158" s="298"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F158" s="313"/>
+      <c r="F158" s="304"/>
     </row>
     <row r="159" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A159" s="304"/>
-      <c r="B159" s="303"/>
-      <c r="C159" s="312"/>
+      <c r="A159" s="295"/>
+      <c r="B159" s="294"/>
+      <c r="C159" s="298"/>
       <c r="D159" s="7"/>
       <c r="E159" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F159" s="313"/>
+      <c r="F159" s="304"/>
     </row>
     <row r="160" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A160" s="304"/>
-      <c r="B160" s="303"/>
-      <c r="C160" s="312"/>
+      <c r="A160" s="295"/>
+      <c r="B160" s="294"/>
+      <c r="C160" s="298"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F160" s="313"/>
+      <c r="F160" s="304"/>
     </row>
     <row r="161" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A161" s="304"/>
-      <c r="B161" s="303"/>
-      <c r="C161" s="312"/>
+      <c r="A161" s="295"/>
+      <c r="B161" s="294"/>
+      <c r="C161" s="298"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F161" s="313"/>
+      <c r="F161" s="304"/>
     </row>
     <row r="162" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A162" s="304"/>
-      <c r="B162" s="303"/>
-      <c r="C162" s="312"/>
+      <c r="A162" s="295"/>
+      <c r="B162" s="294"/>
+      <c r="C162" s="298"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F162" s="313"/>
+      <c r="F162" s="304"/>
     </row>
     <row r="163" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A163" s="304"/>
-      <c r="B163" s="303"/>
-      <c r="C163" s="312"/>
+      <c r="A163" s="295"/>
+      <c r="B163" s="294"/>
+      <c r="C163" s="298"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F163" s="313">
+      <c r="F163" s="304">
         <f>SUM(E163:E172)</f>
         <v>0</v>
       </c>
     </row>
     <row r="164" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A164" s="304"/>
-      <c r="B164" s="303"/>
-      <c r="C164" s="312"/>
+      <c r="A164" s="295"/>
+      <c r="B164" s="294"/>
+      <c r="C164" s="298"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F164" s="313"/>
+      <c r="F164" s="304"/>
     </row>
     <row r="165" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A165" s="304"/>
-      <c r="B165" s="303"/>
-      <c r="C165" s="312"/>
+      <c r="A165" s="295"/>
+      <c r="B165" s="294"/>
+      <c r="C165" s="298"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F165" s="313"/>
+      <c r="F165" s="304"/>
     </row>
     <row r="166" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A166" s="304"/>
-      <c r="B166" s="303"/>
-      <c r="C166" s="312"/>
+      <c r="A166" s="295"/>
+      <c r="B166" s="294"/>
+      <c r="C166" s="298"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F166" s="313"/>
+      <c r="F166" s="304"/>
     </row>
     <row r="167" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A167" s="304"/>
-      <c r="B167" s="303"/>
-      <c r="C167" s="312"/>
+      <c r="A167" s="295"/>
+      <c r="B167" s="294"/>
+      <c r="C167" s="298"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F167" s="313"/>
+      <c r="F167" s="304"/>
     </row>
     <row r="168" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A168" s="304"/>
-      <c r="B168" s="303"/>
-      <c r="C168" s="312"/>
+      <c r="A168" s="295"/>
+      <c r="B168" s="294"/>
+      <c r="C168" s="298"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F168" s="313"/>
+      <c r="F168" s="304"/>
     </row>
     <row r="169" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A169" s="304"/>
-      <c r="B169" s="303"/>
-      <c r="C169" s="312"/>
+      <c r="A169" s="295"/>
+      <c r="B169" s="294"/>
+      <c r="C169" s="298"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F169" s="313"/>
+      <c r="F169" s="304"/>
     </row>
     <row r="170" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A170" s="304"/>
-      <c r="B170" s="303"/>
-      <c r="C170" s="312"/>
+      <c r="A170" s="295"/>
+      <c r="B170" s="294"/>
+      <c r="C170" s="298"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F170" s="313"/>
+      <c r="F170" s="304"/>
     </row>
     <row r="171" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A171" s="304"/>
-      <c r="B171" s="303"/>
-      <c r="C171" s="312"/>
+      <c r="A171" s="295"/>
+      <c r="B171" s="294"/>
+      <c r="C171" s="298"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F171" s="313"/>
+      <c r="F171" s="304"/>
     </row>
     <row r="172" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A172" s="304"/>
-      <c r="B172" s="303"/>
-      <c r="C172" s="312"/>
+      <c r="A172" s="295"/>
+      <c r="B172" s="294"/>
+      <c r="C172" s="298"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F172" s="313"/>
+      <c r="F172" s="304"/>
     </row>
     <row r="173" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A173" s="304"/>
-      <c r="B173" s="303"/>
-      <c r="C173" s="312"/>
+      <c r="A173" s="295"/>
+      <c r="B173" s="294"/>
+      <c r="C173" s="298"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F173" s="313">
+      <c r="F173" s="304">
         <f>SUM(E173:E186)</f>
         <v>0</v>
       </c>
     </row>
     <row r="174" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A174" s="304"/>
-      <c r="B174" s="303"/>
-      <c r="C174" s="312"/>
+      <c r="A174" s="295"/>
+      <c r="B174" s="294"/>
+      <c r="C174" s="298"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F174" s="313"/>
+      <c r="F174" s="304"/>
     </row>
     <row r="175" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A175" s="304"/>
-      <c r="B175" s="303"/>
-      <c r="C175" s="312"/>
+      <c r="A175" s="295"/>
+      <c r="B175" s="294"/>
+      <c r="C175" s="298"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F175" s="313"/>
+      <c r="F175" s="304"/>
     </row>
     <row r="176" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A176" s="304"/>
-      <c r="B176" s="303"/>
-      <c r="C176" s="312"/>
+      <c r="A176" s="295"/>
+      <c r="B176" s="294"/>
+      <c r="C176" s="298"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F176" s="313"/>
+      <c r="F176" s="304"/>
     </row>
     <row r="177" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A177" s="304"/>
-      <c r="B177" s="303"/>
-      <c r="C177" s="312"/>
+      <c r="A177" s="295"/>
+      <c r="B177" s="294"/>
+      <c r="C177" s="298"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F177" s="313"/>
+      <c r="F177" s="304"/>
     </row>
     <row r="178" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A178" s="304"/>
-      <c r="B178" s="303"/>
-      <c r="C178" s="312"/>
+      <c r="A178" s="295"/>
+      <c r="B178" s="294"/>
+      <c r="C178" s="298"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F178" s="313"/>
+      <c r="F178" s="304"/>
     </row>
     <row r="179" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A179" s="304"/>
-      <c r="B179" s="303"/>
-      <c r="C179" s="312"/>
+      <c r="A179" s="295"/>
+      <c r="B179" s="294"/>
+      <c r="C179" s="298"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F179" s="313"/>
+      <c r="F179" s="304"/>
     </row>
     <row r="180" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A180" s="304"/>
-      <c r="B180" s="303"/>
-      <c r="C180" s="312"/>
+      <c r="A180" s="295"/>
+      <c r="B180" s="294"/>
+      <c r="C180" s="298"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F180" s="313"/>
+      <c r="F180" s="304"/>
     </row>
     <row r="181" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A181" s="304"/>
-      <c r="B181" s="303"/>
-      <c r="C181" s="312"/>
+      <c r="A181" s="295"/>
+      <c r="B181" s="294"/>
+      <c r="C181" s="298"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F181" s="313"/>
+      <c r="F181" s="304"/>
     </row>
     <row r="182" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A182" s="304"/>
-      <c r="B182" s="303"/>
-      <c r="C182" s="312"/>
+      <c r="A182" s="295"/>
+      <c r="B182" s="294"/>
+      <c r="C182" s="298"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F182" s="313"/>
+      <c r="F182" s="304"/>
     </row>
     <row r="183" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A183" s="304"/>
-      <c r="B183" s="303"/>
-      <c r="C183" s="312"/>
+      <c r="A183" s="295"/>
+      <c r="B183" s="294"/>
+      <c r="C183" s="298"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F183" s="313"/>
+      <c r="F183" s="304"/>
     </row>
     <row r="184" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A184" s="304"/>
-      <c r="B184" s="303"/>
-      <c r="C184" s="312"/>
+      <c r="A184" s="295"/>
+      <c r="B184" s="294"/>
+      <c r="C184" s="298"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F184" s="313"/>
+      <c r="F184" s="304"/>
     </row>
     <row r="185" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A185" s="304"/>
-      <c r="B185" s="303"/>
-      <c r="C185" s="312"/>
+      <c r="A185" s="295"/>
+      <c r="B185" s="294"/>
+      <c r="C185" s="298"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F185" s="313"/>
+      <c r="F185" s="304"/>
     </row>
     <row r="186" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A186" s="304"/>
-      <c r="B186" s="303"/>
-      <c r="C186" s="312"/>
+      <c r="A186" s="295"/>
+      <c r="B186" s="294"/>
+      <c r="C186" s="298"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F186" s="313"/>
+      <c r="F186" s="304"/>
     </row>
     <row r="187" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A187" s="304"/>
-      <c r="B187" s="303"/>
-      <c r="C187" s="312"/>
+      <c r="A187" s="295"/>
+      <c r="B187" s="294"/>
+      <c r="C187" s="298"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F187" s="313">
+      <c r="F187" s="304">
         <f>SUM(E187)</f>
         <v>0</v>
       </c>
     </row>
     <row r="188" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A188" s="304"/>
-      <c r="B188" s="303"/>
-      <c r="C188" s="312"/>
+      <c r="A188" s="295"/>
+      <c r="B188" s="294"/>
+      <c r="C188" s="298"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F188" s="313">
+      <c r="F188" s="304">
         <f>SUM(E188:E203)</f>
         <v>0</v>
       </c>
     </row>
     <row r="189" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A189" s="304"/>
-      <c r="B189" s="303"/>
-      <c r="C189" s="312"/>
+      <c r="A189" s="295"/>
+      <c r="B189" s="294"/>
+      <c r="C189" s="298"/>
       <c r="D189" s="7"/>
       <c r="E189" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F189" s="313"/>
+      <c r="F189" s="304"/>
     </row>
     <row r="190" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A190" s="304"/>
-      <c r="B190" s="303"/>
-      <c r="C190" s="312"/>
+      <c r="A190" s="295"/>
+      <c r="B190" s="294"/>
+      <c r="C190" s="298"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F190" s="313"/>
+      <c r="F190" s="304"/>
     </row>
     <row r="191" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A191" s="304"/>
-      <c r="B191" s="303"/>
-      <c r="C191" s="312"/>
+      <c r="A191" s="295"/>
+      <c r="B191" s="294"/>
+      <c r="C191" s="298"/>
       <c r="D191" s="7"/>
       <c r="E191" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F191" s="313"/>
+      <c r="F191" s="304"/>
     </row>
     <row r="192" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A192" s="304"/>
-      <c r="B192" s="303"/>
-      <c r="C192" s="312"/>
+      <c r="A192" s="295"/>
+      <c r="B192" s="294"/>
+      <c r="C192" s="298"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F192" s="313"/>
+      <c r="F192" s="304"/>
     </row>
     <row r="193" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A193" s="304"/>
-      <c r="B193" s="303"/>
-      <c r="C193" s="312"/>
+      <c r="A193" s="295"/>
+      <c r="B193" s="294"/>
+      <c r="C193" s="298"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F193" s="313"/>
+      <c r="F193" s="304"/>
     </row>
     <row r="194" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A194" s="304"/>
-      <c r="B194" s="303"/>
-      <c r="C194" s="312"/>
+      <c r="A194" s="295"/>
+      <c r="B194" s="294"/>
+      <c r="C194" s="298"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F194" s="313"/>
+      <c r="F194" s="304"/>
     </row>
     <row r="195" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A195" s="304"/>
-      <c r="B195" s="303"/>
-      <c r="C195" s="312"/>
+      <c r="A195" s="295"/>
+      <c r="B195" s="294"/>
+      <c r="C195" s="298"/>
       <c r="D195" s="7"/>
       <c r="E195" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F195" s="313"/>
+      <c r="F195" s="304"/>
     </row>
     <row r="196" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A196" s="304"/>
-      <c r="B196" s="303"/>
-      <c r="C196" s="312"/>
+      <c r="A196" s="295"/>
+      <c r="B196" s="294"/>
+      <c r="C196" s="298"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F196" s="313"/>
+      <c r="F196" s="304"/>
     </row>
     <row r="197" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A197" s="304"/>
-      <c r="B197" s="303"/>
-      <c r="C197" s="312"/>
+      <c r="A197" s="295"/>
+      <c r="B197" s="294"/>
+      <c r="C197" s="298"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F197" s="313"/>
+      <c r="F197" s="304"/>
     </row>
     <row r="198" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A198" s="304"/>
-      <c r="B198" s="303"/>
-      <c r="C198" s="312"/>
+      <c r="A198" s="295"/>
+      <c r="B198" s="294"/>
+      <c r="C198" s="298"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F198" s="313"/>
+      <c r="F198" s="304"/>
     </row>
     <row r="199" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A199" s="304"/>
-      <c r="B199" s="303"/>
-      <c r="C199" s="312"/>
+      <c r="A199" s="295"/>
+      <c r="B199" s="294"/>
+      <c r="C199" s="298"/>
       <c r="D199" s="7"/>
       <c r="E199" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F199" s="313"/>
+      <c r="F199" s="304"/>
     </row>
     <row r="200" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A200" s="304"/>
-      <c r="B200" s="303"/>
-      <c r="C200" s="312"/>
+      <c r="A200" s="295"/>
+      <c r="B200" s="294"/>
+      <c r="C200" s="298"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F200" s="313"/>
+      <c r="F200" s="304"/>
     </row>
     <row r="201" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A201" s="304"/>
-      <c r="B201" s="303"/>
-      <c r="C201" s="312"/>
+      <c r="A201" s="295"/>
+      <c r="B201" s="294"/>
+      <c r="C201" s="298"/>
       <c r="D201" s="7"/>
       <c r="E201" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F201" s="313"/>
+      <c r="F201" s="304"/>
     </row>
     <row r="202" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A202" s="304"/>
-      <c r="B202" s="314"/>
-      <c r="C202" s="315"/>
-      <c r="D202" s="279"/>
+      <c r="A202" s="295"/>
+      <c r="B202" s="305"/>
+      <c r="C202" s="306"/>
+      <c r="D202" s="270"/>
       <c r="E202" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F202" s="313"/>
+      <c r="F202" s="304"/>
     </row>
     <row r="203" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A203" s="304"/>
-      <c r="B203" s="303"/>
-      <c r="C203" s="312"/>
+      <c r="A203" s="295"/>
+      <c r="B203" s="294"/>
+      <c r="C203" s="298"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F203" s="313"/>
+      <c r="F203" s="304"/>
     </row>
     <row r="204" s="245" customFormat="1" spans="1:6">
-      <c r="A204" s="292"/>
-      <c r="B204" s="303"/>
-      <c r="C204" s="312"/>
+      <c r="A204" s="283"/>
+      <c r="B204" s="294"/>
+      <c r="C204" s="298"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F204" s="295">
+      <c r="F204" s="286">
         <f>SUM(E204:E211)</f>
         <v>0</v>
       </c>
     </row>
     <row r="205" s="245" customFormat="1" spans="1:6">
-      <c r="A205" s="296"/>
-      <c r="B205" s="303"/>
-      <c r="C205" s="312"/>
+      <c r="A205" s="287"/>
+      <c r="B205" s="294"/>
+      <c r="C205" s="298"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F205" s="297"/>
+      <c r="F205" s="288"/>
     </row>
     <row r="206" s="245" customFormat="1" spans="1:6">
-      <c r="A206" s="296"/>
-      <c r="B206" s="303"/>
-      <c r="C206" s="312"/>
+      <c r="A206" s="287"/>
+      <c r="B206" s="294"/>
+      <c r="C206" s="298"/>
       <c r="D206" s="7"/>
       <c r="E206" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F206" s="297"/>
+      <c r="F206" s="288"/>
     </row>
     <row r="207" s="245" customFormat="1" spans="1:6">
-      <c r="A207" s="296"/>
-      <c r="B207" s="303"/>
-      <c r="C207" s="312"/>
+      <c r="A207" s="287"/>
+      <c r="B207" s="294"/>
+      <c r="C207" s="298"/>
       <c r="D207" s="7"/>
       <c r="E207" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F207" s="297"/>
+      <c r="F207" s="288"/>
     </row>
     <row r="208" s="245" customFormat="1" spans="1:6">
-      <c r="A208" s="296"/>
-      <c r="B208" s="303"/>
-      <c r="C208" s="312"/>
+      <c r="A208" s="287"/>
+      <c r="B208" s="294"/>
+      <c r="C208" s="298"/>
       <c r="D208" s="7"/>
       <c r="E208" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F208" s="297"/>
+      <c r="F208" s="288"/>
     </row>
     <row r="209" s="245" customFormat="1" spans="1:6">
-      <c r="A209" s="296"/>
-      <c r="B209" s="303"/>
-      <c r="C209" s="312"/>
+      <c r="A209" s="287"/>
+      <c r="B209" s="294"/>
+      <c r="C209" s="298"/>
       <c r="D209" s="7"/>
       <c r="E209" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F209" s="297"/>
+      <c r="F209" s="288"/>
     </row>
     <row r="210" s="245" customFormat="1" spans="1:6">
-      <c r="A210" s="296"/>
-      <c r="B210" s="303"/>
-      <c r="C210" s="312"/>
+      <c r="A210" s="287"/>
+      <c r="B210" s="294"/>
+      <c r="C210" s="298"/>
       <c r="D210" s="7"/>
       <c r="E210" s="7">
         <f t="shared" ref="E210:E273" si="7">SUM(C210*D210)</f>
         <v>0</v>
       </c>
-      <c r="F210" s="297"/>
+      <c r="F210" s="288"/>
     </row>
     <row r="211" s="245" customFormat="1" spans="1:6">
-      <c r="A211" s="298"/>
-      <c r="B211" s="303"/>
-      <c r="C211" s="312"/>
+      <c r="A211" s="289"/>
+      <c r="B211" s="294"/>
+      <c r="C211" s="298"/>
       <c r="D211" s="7"/>
       <c r="E211" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F211" s="299"/>
+      <c r="F211" s="290"/>
     </row>
     <row r="212" s="245" customFormat="1" spans="1:6">
-      <c r="A212" s="292"/>
-      <c r="B212" s="303"/>
-      <c r="C212" s="312"/>
+      <c r="A212" s="283"/>
+      <c r="B212" s="294"/>
+      <c r="C212" s="298"/>
       <c r="D212" s="7"/>
       <c r="E212" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F212" s="295">
+      <c r="F212" s="286">
         <f>SUM(E212:E223)</f>
         <v>0</v>
       </c>
     </row>
     <row r="213" s="245" customFormat="1" spans="1:6">
-      <c r="A213" s="296"/>
-      <c r="B213" s="303"/>
-      <c r="C213" s="312"/>
+      <c r="A213" s="287"/>
+      <c r="B213" s="294"/>
+      <c r="C213" s="298"/>
       <c r="D213" s="7"/>
       <c r="E213" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F213" s="297"/>
+      <c r="F213" s="288"/>
     </row>
     <row r="214" s="245" customFormat="1" spans="1:6">
-      <c r="A214" s="296"/>
-      <c r="B214" s="303"/>
-      <c r="C214" s="312"/>
+      <c r="A214" s="287"/>
+      <c r="B214" s="294"/>
+      <c r="C214" s="298"/>
       <c r="D214" s="7"/>
       <c r="E214" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F214" s="297"/>
+      <c r="F214" s="288"/>
     </row>
     <row r="215" s="245" customFormat="1" spans="1:6">
-      <c r="A215" s="296"/>
-      <c r="B215" s="303"/>
-      <c r="C215" s="312"/>
+      <c r="A215" s="287"/>
+      <c r="B215" s="294"/>
+      <c r="C215" s="298"/>
       <c r="D215" s="7"/>
       <c r="E215" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F215" s="297"/>
+      <c r="F215" s="288"/>
     </row>
     <row r="216" s="245" customFormat="1" spans="1:6">
-      <c r="A216" s="296"/>
-      <c r="B216" s="303"/>
-      <c r="C216" s="312"/>
+      <c r="A216" s="287"/>
+      <c r="B216" s="294"/>
+      <c r="C216" s="298"/>
       <c r="D216" s="7"/>
       <c r="E216" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F216" s="297"/>
+      <c r="F216" s="288"/>
     </row>
     <row r="217" s="245" customFormat="1" spans="1:6">
-      <c r="A217" s="296"/>
-      <c r="B217" s="303"/>
-      <c r="C217" s="312"/>
+      <c r="A217" s="287"/>
+      <c r="B217" s="294"/>
+      <c r="C217" s="298"/>
       <c r="D217" s="7"/>
       <c r="E217" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F217" s="297"/>
+      <c r="F217" s="288"/>
     </row>
     <row r="218" s="245" customFormat="1" spans="1:6">
-      <c r="A218" s="296"/>
-      <c r="B218" s="303"/>
-      <c r="C218" s="312"/>
+      <c r="A218" s="287"/>
+      <c r="B218" s="294"/>
+      <c r="C218" s="298"/>
       <c r="D218" s="7"/>
       <c r="E218" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F218" s="297"/>
+      <c r="F218" s="288"/>
     </row>
     <row r="219" s="245" customFormat="1" spans="1:6">
-      <c r="A219" s="296"/>
-      <c r="B219" s="303"/>
-      <c r="C219" s="312"/>
+      <c r="A219" s="287"/>
+      <c r="B219" s="294"/>
+      <c r="C219" s="298"/>
       <c r="D219" s="7"/>
       <c r="E219" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F219" s="297"/>
+      <c r="F219" s="288"/>
     </row>
     <row r="220" s="245" customFormat="1" spans="1:6">
-      <c r="A220" s="296"/>
-      <c r="B220" s="303"/>
-      <c r="C220" s="312"/>
+      <c r="A220" s="287"/>
+      <c r="B220" s="294"/>
+      <c r="C220" s="298"/>
       <c r="D220" s="7"/>
       <c r="E220" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F220" s="297"/>
+      <c r="F220" s="288"/>
     </row>
     <row r="221" s="245" customFormat="1" spans="1:6">
-      <c r="A221" s="296"/>
-      <c r="B221" s="303"/>
-      <c r="C221" s="312"/>
+      <c r="A221" s="287"/>
+      <c r="B221" s="294"/>
+      <c r="C221" s="298"/>
       <c r="D221" s="7"/>
       <c r="E221" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F221" s="297"/>
+      <c r="F221" s="288"/>
     </row>
     <row r="222" s="245" customFormat="1" spans="1:6">
-      <c r="A222" s="296"/>
-      <c r="B222" s="303"/>
-      <c r="C222" s="312"/>
+      <c r="A222" s="287"/>
+      <c r="B222" s="294"/>
+      <c r="C222" s="298"/>
       <c r="D222" s="7"/>
       <c r="E222" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F222" s="297"/>
+      <c r="F222" s="288"/>
     </row>
     <row r="223" s="245" customFormat="1" spans="1:6">
-      <c r="A223" s="298"/>
-      <c r="B223" s="303"/>
-      <c r="C223" s="312"/>
+      <c r="A223" s="289"/>
+      <c r="B223" s="294"/>
+      <c r="C223" s="298"/>
       <c r="D223" s="7"/>
       <c r="E223" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F223" s="299"/>
+      <c r="F223" s="290"/>
     </row>
     <row r="224" s="245" customFormat="1" spans="1:6">
-      <c r="A224" s="292"/>
-      <c r="B224" s="303"/>
-      <c r="C224" s="312"/>
+      <c r="A224" s="283"/>
+      <c r="B224" s="294"/>
+      <c r="C224" s="298"/>
       <c r="D224" s="7"/>
       <c r="E224" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F224" s="295">
+      <c r="F224" s="286">
         <f>SUM(E224:E232)</f>
         <v>0</v>
       </c>
     </row>
     <row r="225" s="245" customFormat="1" spans="1:6">
-      <c r="A225" s="296"/>
-      <c r="B225" s="303"/>
-      <c r="C225" s="312"/>
+      <c r="A225" s="287"/>
+      <c r="B225" s="294"/>
+      <c r="C225" s="298"/>
       <c r="D225" s="7"/>
       <c r="E225" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F225" s="297"/>
+      <c r="F225" s="288"/>
     </row>
     <row r="226" s="245" customFormat="1" spans="1:6">
-      <c r="A226" s="296"/>
-      <c r="B226" s="303"/>
-      <c r="C226" s="312"/>
+      <c r="A226" s="287"/>
+      <c r="B226" s="294"/>
+      <c r="C226" s="298"/>
       <c r="D226" s="7"/>
       <c r="E226" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F226" s="297"/>
+      <c r="F226" s="288"/>
     </row>
     <row r="227" s="245" customFormat="1" spans="1:6">
-      <c r="A227" s="296"/>
-      <c r="B227" s="303"/>
-      <c r="C227" s="312"/>
+      <c r="A227" s="287"/>
+      <c r="B227" s="294"/>
+      <c r="C227" s="298"/>
       <c r="D227" s="7"/>
       <c r="E227" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F227" s="297"/>
+      <c r="F227" s="288"/>
     </row>
     <row r="228" s="245" customFormat="1" spans="1:6">
-      <c r="A228" s="296"/>
-      <c r="B228" s="303"/>
-      <c r="C228" s="312"/>
+      <c r="A228" s="287"/>
+      <c r="B228" s="294"/>
+      <c r="C228" s="298"/>
       <c r="D228" s="7"/>
       <c r="E228" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F228" s="297"/>
+      <c r="F228" s="288"/>
     </row>
     <row r="229" s="245" customFormat="1" spans="1:6">
-      <c r="A229" s="296"/>
-      <c r="B229" s="303"/>
-      <c r="C229" s="312"/>
+      <c r="A229" s="287"/>
+      <c r="B229" s="294"/>
+      <c r="C229" s="298"/>
       <c r="D229" s="7"/>
       <c r="E229" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F229" s="297"/>
+      <c r="F229" s="288"/>
     </row>
     <row r="230" s="245" customFormat="1" spans="1:6">
-      <c r="A230" s="296"/>
-      <c r="B230" s="303"/>
-      <c r="C230" s="312"/>
+      <c r="A230" s="287"/>
+      <c r="B230" s="294"/>
+      <c r="C230" s="298"/>
       <c r="D230" s="7"/>
       <c r="E230" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F230" s="297"/>
+      <c r="F230" s="288"/>
     </row>
     <row r="231" s="245" customFormat="1" spans="1:6">
-      <c r="A231" s="296"/>
-      <c r="B231" s="303"/>
-      <c r="C231" s="312"/>
+      <c r="A231" s="287"/>
+      <c r="B231" s="294"/>
+      <c r="C231" s="298"/>
       <c r="D231" s="7"/>
       <c r="E231" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F231" s="297"/>
+      <c r="F231" s="288"/>
     </row>
     <row r="232" s="245" customFormat="1" spans="1:6">
-      <c r="A232" s="298"/>
-      <c r="B232" s="303"/>
-      <c r="C232" s="312"/>
+      <c r="A232" s="289"/>
+      <c r="B232" s="294"/>
+      <c r="C232" s="298"/>
       <c r="D232" s="7"/>
       <c r="E232" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F232" s="299"/>
+      <c r="F232" s="290"/>
     </row>
     <row r="233" s="245" customFormat="1" spans="1:6">
-      <c r="A233" s="292"/>
-      <c r="B233" s="303"/>
-      <c r="C233" s="312"/>
+      <c r="A233" s="283"/>
+      <c r="B233" s="294"/>
+      <c r="C233" s="298"/>
       <c r="D233" s="7"/>
       <c r="E233" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F233" s="295">
+      <c r="F233" s="286">
         <f>SUM(E233:E243)</f>
         <v>0</v>
       </c>
     </row>
     <row r="234" s="245" customFormat="1" spans="1:6">
-      <c r="A234" s="296"/>
-      <c r="B234" s="303"/>
-      <c r="C234" s="312"/>
+      <c r="A234" s="287"/>
+      <c r="B234" s="294"/>
+      <c r="C234" s="298"/>
       <c r="D234" s="7"/>
       <c r="E234" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F234" s="297"/>
+      <c r="F234" s="288"/>
     </row>
     <row r="235" s="245" customFormat="1" spans="1:6">
-      <c r="A235" s="296"/>
-      <c r="B235" s="303"/>
-      <c r="C235" s="312"/>
+      <c r="A235" s="287"/>
+      <c r="B235" s="294"/>
+      <c r="C235" s="298"/>
       <c r="D235" s="7"/>
       <c r="E235" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F235" s="297"/>
+      <c r="F235" s="288"/>
     </row>
     <row r="236" s="245" customFormat="1" spans="1:6">
-      <c r="A236" s="296"/>
-      <c r="B236" s="303"/>
-      <c r="C236" s="312"/>
+      <c r="A236" s="287"/>
+      <c r="B236" s="294"/>
+      <c r="C236" s="298"/>
       <c r="D236" s="7"/>
       <c r="E236" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F236" s="297"/>
+      <c r="F236" s="288"/>
     </row>
     <row r="237" s="245" customFormat="1" spans="1:6">
-      <c r="A237" s="296"/>
-      <c r="B237" s="303"/>
-      <c r="C237" s="312"/>
+      <c r="A237" s="287"/>
+      <c r="B237" s="294"/>
+      <c r="C237" s="298"/>
       <c r="D237" s="7"/>
       <c r="E237" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F237" s="297"/>
+      <c r="F237" s="288"/>
     </row>
     <row r="238" s="245" customFormat="1" spans="1:6">
-      <c r="A238" s="296"/>
-      <c r="B238" s="303"/>
-      <c r="C238" s="312"/>
+      <c r="A238" s="287"/>
+      <c r="B238" s="294"/>
+      <c r="C238" s="298"/>
       <c r="D238" s="7"/>
       <c r="E238" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F238" s="297"/>
+      <c r="F238" s="288"/>
     </row>
     <row r="239" s="245" customFormat="1" spans="1:6">
-      <c r="A239" s="296"/>
-      <c r="B239" s="303"/>
-      <c r="C239" s="312"/>
+      <c r="A239" s="287"/>
+      <c r="B239" s="294"/>
+      <c r="C239" s="298"/>
       <c r="D239" s="7"/>
       <c r="E239" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F239" s="297"/>
+      <c r="F239" s="288"/>
     </row>
     <row r="240" s="245" customFormat="1" spans="1:6">
-      <c r="A240" s="296"/>
-      <c r="B240" s="303"/>
-      <c r="C240" s="312"/>
+      <c r="A240" s="287"/>
+      <c r="B240" s="294"/>
+      <c r="C240" s="298"/>
       <c r="D240" s="7"/>
       <c r="E240" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F240" s="297"/>
+      <c r="F240" s="288"/>
     </row>
     <row r="241" s="245" customFormat="1" spans="1:6">
-      <c r="A241" s="296"/>
-      <c r="B241" s="303"/>
-      <c r="C241" s="312"/>
+      <c r="A241" s="287"/>
+      <c r="B241" s="294"/>
+      <c r="C241" s="298"/>
       <c r="D241" s="7"/>
       <c r="E241" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F241" s="297"/>
+      <c r="F241" s="288"/>
     </row>
     <row r="242" s="245" customFormat="1" spans="1:6">
-      <c r="A242" s="296"/>
-      <c r="B242" s="303"/>
-      <c r="C242" s="312"/>
+      <c r="A242" s="287"/>
+      <c r="B242" s="294"/>
+      <c r="C242" s="298"/>
       <c r="D242" s="7"/>
       <c r="E242" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F242" s="297"/>
+      <c r="F242" s="288"/>
     </row>
     <row r="243" s="245" customFormat="1" spans="1:6">
-      <c r="A243" s="298"/>
-      <c r="B243" s="303"/>
-      <c r="C243" s="312"/>
+      <c r="A243" s="289"/>
+      <c r="B243" s="294"/>
+      <c r="C243" s="298"/>
       <c r="D243" s="7"/>
       <c r="E243" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F243" s="299"/>
+      <c r="F243" s="290"/>
     </row>
     <row r="244" s="245" customFormat="1" spans="1:6">
-      <c r="A244" s="292"/>
-      <c r="B244" s="303"/>
-      <c r="C244" s="312"/>
+      <c r="A244" s="283"/>
+      <c r="B244" s="294"/>
+      <c r="C244" s="298"/>
       <c r="D244" s="7"/>
       <c r="E244" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F244" s="295">
+      <c r="F244" s="286">
         <f>SUM(E244:E254)</f>
         <v>0</v>
       </c>
     </row>
     <row r="245" s="245" customFormat="1" spans="1:6">
-      <c r="A245" s="296"/>
-      <c r="B245" s="303"/>
-      <c r="C245" s="312"/>
+      <c r="A245" s="287"/>
+      <c r="B245" s="294"/>
+      <c r="C245" s="298"/>
       <c r="D245" s="7"/>
       <c r="E245" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F245" s="297"/>
+      <c r="F245" s="288"/>
     </row>
     <row r="246" s="245" customFormat="1" spans="1:6">
-      <c r="A246" s="296"/>
-      <c r="B246" s="303"/>
-      <c r="C246" s="312"/>
+      <c r="A246" s="287"/>
+      <c r="B246" s="294"/>
+      <c r="C246" s="298"/>
       <c r="D246" s="7"/>
       <c r="E246" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F246" s="297"/>
+      <c r="F246" s="288"/>
     </row>
     <row r="247" s="245" customFormat="1" spans="1:6">
-      <c r="A247" s="296"/>
-      <c r="B247" s="303"/>
-      <c r="C247" s="312"/>
+      <c r="A247" s="287"/>
+      <c r="B247" s="294"/>
+      <c r="C247" s="298"/>
       <c r="D247" s="7"/>
       <c r="E247" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F247" s="297"/>
+      <c r="F247" s="288"/>
     </row>
     <row r="248" s="245" customFormat="1" spans="1:6">
-      <c r="A248" s="296"/>
-      <c r="B248" s="303"/>
-      <c r="C248" s="312"/>
+      <c r="A248" s="287"/>
+      <c r="B248" s="294"/>
+      <c r="C248" s="298"/>
       <c r="D248" s="7"/>
       <c r="E248" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F248" s="297"/>
+      <c r="F248" s="288"/>
     </row>
     <row r="249" s="245" customFormat="1" spans="1:6">
-      <c r="A249" s="296"/>
-      <c r="B249" s="303"/>
-      <c r="C249" s="312"/>
+      <c r="A249" s="287"/>
+      <c r="B249" s="294"/>
+      <c r="C249" s="298"/>
       <c r="D249" s="7"/>
       <c r="E249" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F249" s="297"/>
+      <c r="F249" s="288"/>
     </row>
     <row r="250" s="245" customFormat="1" spans="1:6">
-      <c r="A250" s="296"/>
-      <c r="B250" s="303"/>
-      <c r="C250" s="312"/>
+      <c r="A250" s="287"/>
+      <c r="B250" s="294"/>
+      <c r="C250" s="298"/>
       <c r="D250" s="7"/>
       <c r="E250" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F250" s="297"/>
+      <c r="F250" s="288"/>
     </row>
     <row r="251" s="245" customFormat="1" spans="1:6">
-      <c r="A251" s="296"/>
-      <c r="B251" s="303"/>
-      <c r="C251" s="312"/>
+      <c r="A251" s="287"/>
+      <c r="B251" s="294"/>
+      <c r="C251" s="298"/>
       <c r="D251" s="7"/>
       <c r="E251" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F251" s="297"/>
+      <c r="F251" s="288"/>
     </row>
     <row r="252" s="245" customFormat="1" spans="1:6">
-      <c r="A252" s="296"/>
-      <c r="B252" s="303"/>
-      <c r="C252" s="312"/>
+      <c r="A252" s="287"/>
+      <c r="B252" s="294"/>
+      <c r="C252" s="298"/>
       <c r="D252" s="7"/>
       <c r="E252" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F252" s="297"/>
+      <c r="F252" s="288"/>
     </row>
     <row r="253" s="245" customFormat="1" spans="1:6">
-      <c r="A253" s="296"/>
-      <c r="B253" s="303"/>
-      <c r="C253" s="312"/>
+      <c r="A253" s="287"/>
+      <c r="B253" s="294"/>
+      <c r="C253" s="298"/>
       <c r="D253" s="7"/>
       <c r="E253" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F253" s="297"/>
+      <c r="F253" s="288"/>
     </row>
     <row r="254" s="245" customFormat="1" spans="1:6">
-      <c r="A254" s="298"/>
-      <c r="B254" s="303"/>
-      <c r="C254" s="312"/>
+      <c r="A254" s="289"/>
+      <c r="B254" s="294"/>
+      <c r="C254" s="298"/>
       <c r="D254" s="7"/>
       <c r="E254" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F254" s="299"/>
+      <c r="F254" s="290"/>
     </row>
     <row r="255" s="245" customFormat="1" spans="1:6">
-      <c r="A255" s="292"/>
-      <c r="B255" s="303"/>
-      <c r="C255" s="312"/>
+      <c r="A255" s="283"/>
+      <c r="B255" s="294"/>
+      <c r="C255" s="298"/>
       <c r="D255" s="7"/>
       <c r="E255" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F255" s="295">
+      <c r="F255" s="286">
         <f>SUM(E255:E265)</f>
         <v>0</v>
       </c>
     </row>
     <row r="256" s="245" customFormat="1" spans="1:6">
-      <c r="A256" s="296"/>
-      <c r="B256" s="303"/>
-      <c r="C256" s="312"/>
+      <c r="A256" s="287"/>
+      <c r="B256" s="294"/>
+      <c r="C256" s="298"/>
       <c r="D256" s="7"/>
       <c r="E256" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F256" s="297"/>
+      <c r="F256" s="288"/>
     </row>
     <row r="257" s="245" customFormat="1" spans="1:6">
-      <c r="A257" s="296"/>
-      <c r="B257" s="303"/>
-      <c r="C257" s="312"/>
+      <c r="A257" s="287"/>
+      <c r="B257" s="294"/>
+      <c r="C257" s="298"/>
       <c r="D257" s="7"/>
       <c r="E257" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F257" s="297"/>
+      <c r="F257" s="288"/>
     </row>
     <row r="258" s="245" customFormat="1" spans="1:6">
-      <c r="A258" s="296"/>
-      <c r="B258" s="303"/>
-      <c r="C258" s="312"/>
+      <c r="A258" s="287"/>
+      <c r="B258" s="294"/>
+      <c r="C258" s="298"/>
       <c r="D258" s="7"/>
       <c r="E258" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F258" s="297"/>
+      <c r="F258" s="288"/>
     </row>
     <row r="259" s="245" customFormat="1" spans="1:6">
-      <c r="A259" s="296"/>
-      <c r="B259" s="303"/>
-      <c r="C259" s="312"/>
+      <c r="A259" s="287"/>
+      <c r="B259" s="294"/>
+      <c r="C259" s="298"/>
       <c r="D259" s="7"/>
       <c r="E259" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F259" s="297"/>
+      <c r="F259" s="288"/>
     </row>
     <row r="260" s="245" customFormat="1" spans="1:6">
-      <c r="A260" s="296"/>
-      <c r="B260" s="303"/>
-      <c r="C260" s="312"/>
+      <c r="A260" s="287"/>
+      <c r="B260" s="294"/>
+      <c r="C260" s="298"/>
       <c r="D260" s="7"/>
       <c r="E260" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F260" s="297"/>
+      <c r="F260" s="288"/>
     </row>
     <row r="261" s="245" customFormat="1" spans="1:6">
-      <c r="A261" s="296"/>
-      <c r="B261" s="303"/>
-      <c r="C261" s="312"/>
+      <c r="A261" s="287"/>
+      <c r="B261" s="294"/>
+      <c r="C261" s="298"/>
       <c r="D261" s="7"/>
       <c r="E261" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F261" s="297"/>
+      <c r="F261" s="288"/>
     </row>
     <row r="262" s="245" customFormat="1" spans="1:6">
-      <c r="A262" s="296"/>
-      <c r="B262" s="303"/>
-      <c r="C262" s="312"/>
+      <c r="A262" s="287"/>
+      <c r="B262" s="294"/>
+      <c r="C262" s="298"/>
       <c r="D262" s="7"/>
       <c r="E262" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F262" s="297"/>
+      <c r="F262" s="288"/>
     </row>
     <row r="263" s="245" customFormat="1" spans="1:6">
-      <c r="A263" s="296"/>
-      <c r="B263" s="303"/>
-      <c r="C263" s="312"/>
+      <c r="A263" s="287"/>
+      <c r="B263" s="294"/>
+      <c r="C263" s="298"/>
       <c r="D263" s="7"/>
       <c r="E263" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F263" s="297"/>
+      <c r="F263" s="288"/>
     </row>
     <row r="264" s="245" customFormat="1" spans="1:6">
-      <c r="A264" s="296"/>
-      <c r="B264" s="303"/>
-      <c r="C264" s="312"/>
+      <c r="A264" s="287"/>
+      <c r="B264" s="294"/>
+      <c r="C264" s="298"/>
       <c r="D264" s="7"/>
       <c r="E264" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F264" s="297"/>
+      <c r="F264" s="288"/>
     </row>
     <row r="265" s="245" customFormat="1" spans="1:6">
-      <c r="A265" s="298"/>
-      <c r="B265" s="303"/>
-      <c r="C265" s="312"/>
+      <c r="A265" s="289"/>
+      <c r="B265" s="294"/>
+      <c r="C265" s="298"/>
       <c r="D265" s="7"/>
       <c r="E265" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F265" s="299"/>
+      <c r="F265" s="290"/>
     </row>
     <row r="266" s="245" customFormat="1" spans="1:6">
-      <c r="A266" s="292"/>
-      <c r="B266" s="303"/>
-      <c r="C266" s="312"/>
+      <c r="A266" s="283"/>
+      <c r="B266" s="294"/>
+      <c r="C266" s="298"/>
       <c r="D266" s="7"/>
       <c r="E266" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F266" s="295">
+      <c r="F266" s="286">
         <f>SUM(E266:E275)</f>
         <v>0</v>
       </c>
     </row>
     <row r="267" s="245" customFormat="1" spans="1:6">
-      <c r="A267" s="296"/>
-      <c r="B267" s="303"/>
-      <c r="C267" s="312"/>
+      <c r="A267" s="287"/>
+      <c r="B267" s="294"/>
+      <c r="C267" s="298"/>
       <c r="D267" s="7"/>
       <c r="E267" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F267" s="297"/>
+      <c r="F267" s="288"/>
     </row>
     <row r="268" s="245" customFormat="1" spans="1:6">
-      <c r="A268" s="296"/>
-      <c r="B268" s="303"/>
-      <c r="C268" s="312"/>
+      <c r="A268" s="287"/>
+      <c r="B268" s="294"/>
+      <c r="C268" s="298"/>
       <c r="D268" s="7"/>
       <c r="E268" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F268" s="297"/>
+      <c r="F268" s="288"/>
     </row>
     <row r="269" s="245" customFormat="1" spans="1:6">
-      <c r="A269" s="296"/>
-      <c r="B269" s="303"/>
-      <c r="C269" s="312"/>
+      <c r="A269" s="287"/>
+      <c r="B269" s="294"/>
+      <c r="C269" s="298"/>
       <c r="D269" s="7"/>
       <c r="E269" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F269" s="297"/>
+      <c r="F269" s="288"/>
     </row>
     <row r="270" s="245" customFormat="1" spans="1:6">
-      <c r="A270" s="296"/>
-      <c r="B270" s="303"/>
-      <c r="C270" s="312"/>
+      <c r="A270" s="287"/>
+      <c r="B270" s="294"/>
+      <c r="C270" s="298"/>
       <c r="D270" s="7"/>
       <c r="E270" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F270" s="297"/>
+      <c r="F270" s="288"/>
     </row>
     <row r="271" s="245" customFormat="1" spans="1:6">
-      <c r="A271" s="296"/>
-      <c r="B271" s="303"/>
-      <c r="C271" s="312"/>
+      <c r="A271" s="287"/>
+      <c r="B271" s="294"/>
+      <c r="C271" s="298"/>
       <c r="D271" s="7"/>
       <c r="E271" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F271" s="297"/>
+      <c r="F271" s="288"/>
     </row>
     <row r="272" s="245" customFormat="1" spans="1:6">
-      <c r="A272" s="296"/>
-      <c r="B272" s="303"/>
-      <c r="C272" s="312"/>
+      <c r="A272" s="287"/>
+      <c r="B272" s="294"/>
+      <c r="C272" s="298"/>
       <c r="D272" s="7"/>
       <c r="E272" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F272" s="297"/>
+      <c r="F272" s="288"/>
     </row>
     <row r="273" s="245" customFormat="1" spans="1:6">
-      <c r="A273" s="296"/>
-      <c r="B273" s="303"/>
-      <c r="C273" s="312"/>
+      <c r="A273" s="287"/>
+      <c r="B273" s="294"/>
+      <c r="C273" s="298"/>
       <c r="D273" s="7"/>
       <c r="E273" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F273" s="297"/>
+      <c r="F273" s="288"/>
     </row>
     <row r="274" s="245" customFormat="1" spans="1:6">
-      <c r="A274" s="296"/>
-      <c r="B274" s="303"/>
-      <c r="C274" s="312"/>
+      <c r="A274" s="287"/>
+      <c r="B274" s="294"/>
+      <c r="C274" s="298"/>
       <c r="D274" s="7"/>
       <c r="E274" s="7">
         <f t="shared" ref="E274:E287" si="8">SUM(C274*D274)</f>
         <v>0</v>
       </c>
-      <c r="F274" s="297"/>
+      <c r="F274" s="288"/>
     </row>
     <row r="275" s="245" customFormat="1" spans="1:6">
-      <c r="A275" s="298"/>
-      <c r="B275" s="303"/>
-      <c r="C275" s="312"/>
+      <c r="A275" s="289"/>
+      <c r="B275" s="294"/>
+      <c r="C275" s="298"/>
       <c r="D275" s="7"/>
       <c r="E275" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F275" s="299"/>
+      <c r="F275" s="290"/>
     </row>
     <row r="276" s="245" customFormat="1" ht="15.75" spans="1:6">
-      <c r="A276" s="304"/>
-      <c r="B276" s="303"/>
-      <c r="C276" s="312"/>
+      <c r="A276" s="295"/>
+      <c r="B276" s="294"/>
+      <c r="C276" s="298"/>
       <c r="D276" s="7"/>
       <c r="E276" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F276" s="313">
+      <c r="F276" s="304">
         <f>SUM(E276)</f>
         <v>0</v>
       </c>
     </row>
     <row r="277" s="245" customFormat="1" spans="1:6">
-      <c r="A277" s="292"/>
-      <c r="B277" s="303"/>
-      <c r="C277" s="312"/>
+      <c r="A277" s="283"/>
+      <c r="B277" s="294"/>
+      <c r="C277" s="298"/>
       <c r="D277" s="7"/>
       <c r="E277" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F277" s="295">
+      <c r="F277" s="286">
         <f>SUM(E277:E287)</f>
         <v>0</v>
       </c>
     </row>
     <row r="278" s="245" customFormat="1" spans="1:6">
-      <c r="A278" s="296"/>
-      <c r="B278" s="303"/>
-      <c r="C278" s="312"/>
+      <c r="A278" s="287"/>
+      <c r="B278" s="294"/>
+      <c r="C278" s="298"/>
       <c r="D278" s="7"/>
       <c r="E278" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F278" s="297"/>
+      <c r="F278" s="288"/>
     </row>
     <row r="279" s="245" customFormat="1" spans="1:6">
-      <c r="A279" s="296"/>
-      <c r="B279" s="303"/>
-      <c r="C279" s="312"/>
+      <c r="A279" s="287"/>
+      <c r="B279" s="294"/>
+      <c r="C279" s="298"/>
       <c r="D279" s="7"/>
       <c r="E279" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F279" s="297"/>
+      <c r="F279" s="288"/>
     </row>
     <row r="280" s="245" customFormat="1" spans="1:6">
-      <c r="A280" s="296"/>
-      <c r="B280" s="303"/>
-      <c r="C280" s="312"/>
+      <c r="A280" s="287"/>
+      <c r="B280" s="294"/>
+      <c r="C280" s="298"/>
       <c r="D280" s="7"/>
       <c r="E280" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F280" s="297"/>
+      <c r="F280" s="288"/>
     </row>
     <row r="281" s="245" customFormat="1" spans="1:6">
-      <c r="A281" s="296"/>
-      <c r="B281" s="303"/>
-      <c r="C281" s="312"/>
+      <c r="A281" s="287"/>
+      <c r="B281" s="294"/>
+      <c r="C281" s="298"/>
       <c r="D281" s="7"/>
       <c r="E281" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F281" s="297"/>
+      <c r="F281" s="288"/>
     </row>
     <row r="282" s="245" customFormat="1" spans="1:6">
-      <c r="A282" s="296"/>
-      <c r="B282" s="303"/>
-      <c r="C282" s="312"/>
+      <c r="A282" s="287"/>
+      <c r="B282" s="294"/>
+      <c r="C282" s="298"/>
       <c r="D282" s="7"/>
       <c r="E282" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F282" s="297"/>
+      <c r="F282" s="288"/>
     </row>
     <row r="283" s="245" customFormat="1" spans="1:6">
-      <c r="A283" s="296"/>
-      <c r="B283" s="303"/>
-      <c r="C283" s="312"/>
+      <c r="A283" s="287"/>
+      <c r="B283" s="294"/>
+      <c r="C283" s="298"/>
       <c r="D283" s="7"/>
       <c r="E283" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F283" s="297"/>
+      <c r="F283" s="288"/>
     </row>
     <row r="284" s="245" customFormat="1" spans="1:6">
-      <c r="A284" s="296"/>
-      <c r="B284" s="303"/>
-      <c r="C284" s="312"/>
+      <c r="A284" s="287"/>
+      <c r="B284" s="294"/>
+      <c r="C284" s="298"/>
       <c r="D284" s="7"/>
       <c r="E284" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F284" s="297"/>
+      <c r="F284" s="288"/>
     </row>
     <row r="285" s="245" customFormat="1" spans="1:6">
-      <c r="A285" s="296"/>
-      <c r="B285" s="303"/>
-      <c r="C285" s="312"/>
+      <c r="A285" s="287"/>
+      <c r="B285" s="294"/>
+      <c r="C285" s="298"/>
       <c r="D285" s="7"/>
       <c r="E285" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F285" s="297"/>
+      <c r="F285" s="288"/>
     </row>
     <row r="286" s="245" customFormat="1" spans="1:6">
-      <c r="A286" s="296"/>
-      <c r="B286" s="303"/>
-      <c r="C286" s="312"/>
+      <c r="A286" s="287"/>
+      <c r="B286" s="294"/>
+      <c r="C286" s="298"/>
       <c r="D286" s="7"/>
       <c r="E286" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F286" s="297"/>
+      <c r="F286" s="288"/>
     </row>
     <row r="287" s="245" customFormat="1" spans="1:6">
-      <c r="A287" s="298"/>
-      <c r="B287" s="303"/>
-      <c r="C287" s="312"/>
+      <c r="A287" s="289"/>
+      <c r="B287" s="294"/>
+      <c r="C287" s="298"/>
       <c r="D287" s="7"/>
       <c r="E287" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F287" s="299"/>
+      <c r="F287" s="290"/>
     </row>
     <row r="288" s="245" customFormat="1" spans="1:6">
       <c r="A288" s="247"/>
       <c r="C288" s="246"/>
       <c r="E288" s="7"/>
-      <c r="F288" s="313">
+      <c r="F288" s="304">
         <f>SUM(F2:F287)</f>
-        <v>3437000</v>
+        <v>3916000</v>
       </c>
     </row>
     <row r="289" s="245" customFormat="1" spans="1:3">
@@ -7782,10 +7769,10 @@
     <row r="391" s="245" customFormat="1" spans="1:7">
       <c r="A391" s="247"/>
       <c r="C391" s="246"/>
-      <c r="G391" s="280"/>
+      <c r="G391" s="271"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="36">
     <mergeCell ref="A2:A12"/>
     <mergeCell ref="A13:A25"/>
     <mergeCell ref="A26:A34"/>
@@ -7795,6 +7782,7 @@
     <mergeCell ref="A59:A67"/>
     <mergeCell ref="A68:A78"/>
     <mergeCell ref="A79:A93"/>
+    <mergeCell ref="A94:A99"/>
     <mergeCell ref="A204:A211"/>
     <mergeCell ref="A212:A223"/>
     <mergeCell ref="A224:A232"/>
@@ -7812,7 +7800,7 @@
     <mergeCell ref="F59:F67"/>
     <mergeCell ref="F68:F78"/>
     <mergeCell ref="F79:F93"/>
-    <mergeCell ref="F94:F96"/>
+    <mergeCell ref="F94:F99"/>
     <mergeCell ref="F204:F211"/>
     <mergeCell ref="F212:F223"/>
     <mergeCell ref="F224:F232"/>
@@ -7847,16 +7835,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="35" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="35" t="s">
-        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -7873,7 +7861,7 @@
         <v>38678</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D2" s="27">
         <v>3</v>
@@ -7896,7 +7884,7 @@
       <c r="D3" s="27"/>
       <c r="E3" s="17"/>
       <c r="F3" s="119" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G3" s="41">
         <f>G2*11%</f>
@@ -7938,7 +7926,7 @@
       <c r="D6" s="126"/>
       <c r="E6" s="7"/>
       <c r="F6" s="127" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G6" s="7">
         <f>G5*11%</f>
@@ -8020,7 +8008,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="87" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B14" s="88"/>
       <c r="C14" s="88"/>
@@ -8075,16 +8063,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="35" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="35" t="s">
-        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -8223,7 +8211,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="87" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B14" s="88"/>
       <c r="C14" s="88"/>
@@ -8277,16 +8265,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="35" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="35" t="s">
-        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -8295,7 +8283,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" ht="147.55" customHeight="1" spans="1:8">
@@ -8303,10 +8291,10 @@
         <v>45999</v>
       </c>
       <c r="B2" s="93" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D2" s="49">
         <v>24</v>
@@ -8333,7 +8321,7 @@
       </c>
       <c r="E3" s="102"/>
       <c r="F3" s="82" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G3" s="103">
         <f>G2*11%</f>
@@ -8381,7 +8369,7 @@
       </c>
       <c r="E6" s="81"/>
       <c r="F6" s="82" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G6" s="103">
         <f>G5*11%</f>
@@ -8426,7 +8414,7 @@
       <c r="D9" s="105"/>
       <c r="E9" s="81"/>
       <c r="F9" s="82" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G9" s="103">
         <f>G8*11%</f>
@@ -8471,7 +8459,7 @@
       <c r="D12" s="105"/>
       <c r="E12" s="81"/>
       <c r="F12" s="82" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G12" s="103">
         <f>G11*11%</f>
@@ -8513,7 +8501,7 @@
       <c r="D15" s="105"/>
       <c r="E15" s="81"/>
       <c r="F15" s="82" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G15" s="103">
         <f>G14*11%</f>
@@ -8538,7 +8526,7 @@
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:8">
       <c r="A17" s="87" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B17" s="88"/>
       <c r="C17" s="88"/>
@@ -8597,19 +8585,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E1" s="35" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>5</v>
@@ -8641,7 +8629,7 @@
     </row>
     <row r="4" ht="23" customHeight="1" spans="1:7">
       <c r="A4" s="94" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B4" s="95"/>
       <c r="C4" s="95"/>
@@ -8682,16 +8670,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="35" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="35" t="s">
-        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -8705,10 +8693,10 @@
         <v>45999</v>
       </c>
       <c r="B2" s="77" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D2" s="27">
         <v>3</v>
@@ -8724,7 +8712,7 @@
     </row>
     <row r="3" ht="23.25" spans="1:7">
       <c r="A3" s="29" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="79"/>
@@ -8734,7 +8722,7 @@
       </c>
       <c r="E3" s="81"/>
       <c r="F3" s="81" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G3" s="82">
         <f>G2*11%</f>
@@ -8789,7 +8777,7 @@
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:7">
       <c r="A8" s="87" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B8" s="88"/>
       <c r="C8" s="88"/>
@@ -8837,19 +8825,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>57</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" ht="321" customHeight="1" spans="1:6">
@@ -8912,16 +8900,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="35" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="35" t="s">
-        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -9022,7 +9010,7 @@
     </row>
     <row r="12" ht="27" customHeight="1" spans="1:7">
       <c r="A12" s="61" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B12" s="62"/>
       <c r="C12" s="62"/>
@@ -9075,13 +9063,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>3</v>
@@ -9090,7 +9078,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" ht="324.4" customHeight="1" spans="1:7">
@@ -9149,22 +9137,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" ht="177" customHeight="1" spans="1:7">
@@ -9225,10 +9213,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>5</v>
@@ -9239,11 +9227,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" s="5">
         <f>'BUK BUNGA (Groceries)'!F288</f>
-        <v>3437000</v>
+        <v>3916000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9251,7 +9239,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C3" s="5">
         <f>'WARUNG EKA (Drinks, Etc)'!G117</f>
@@ -9263,7 +9251,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C4" s="5">
         <f>'DEWATA COCONUT (Coconut)'!E10</f>
@@ -9275,7 +9263,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C5" s="5">
         <f>'SEDANA JAYA'!F37</f>
@@ -9287,7 +9275,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C6" s="5">
         <f>'PNB (Alcohol)'!H7</f>
@@ -9299,7 +9287,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C7" s="5">
         <f>'DSP (Alcohol)'!F16</f>
@@ -9311,7 +9299,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C8" s="5">
         <f>'DSP ARYA BIMA (Alcohol)'!E3</f>
@@ -9323,7 +9311,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C9" s="5" t="str">
         <f>'SELERA OR STIR UP (Syrup)'!F19</f>
@@ -9335,7 +9323,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C10" s="5">
         <f>'DW BALI (Alcohol)'!E4</f>
@@ -9347,7 +9335,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C11" s="5">
         <f>'DDB (Alcohol)'!E14</f>
@@ -9359,7 +9347,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C12" s="5">
         <f>'NANO DEWATA (Alcohol)'!E14</f>
@@ -9371,7 +9359,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C13" s="5">
         <f>'BALI PERMATA JAYA (Corona Beer)'!E17</f>
@@ -9383,7 +9371,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C14" s="7">
         <f>'BLACK COFFEE ROASTERS (Coffee)'!F4</f>
@@ -9395,7 +9383,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C15" s="5">
         <f>'PT. PRASIDA LANTUR MAJU (Wine)'!E8</f>
@@ -9407,7 +9395,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C16" s="8">
         <f>'PT LOVINA BEACH BREWERY'!D3</f>
@@ -9419,7 +9407,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C17" s="5">
         <f>'CHAI CHITAI (Tea Leaf,etc)'!E12</f>
@@ -9431,7 +9419,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C18" s="5">
         <f>'MULIA JAYA (Passion Fruit)'!D3</f>
@@ -9443,7 +9431,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C19" s="5">
         <f>'Dewata Kencana Distribusi (Vdka'!E3</f>
@@ -9457,7 +9445,7 @@
       <c r="B20" s="9"/>
       <c r="C20" s="10">
         <f>SUM(C2:C13)</f>
-        <v>19081109.94</v>
+        <v>19560109.94</v>
       </c>
     </row>
   </sheetData>
@@ -9493,7 +9481,7 @@
   <sheetData>
     <row r="1" s="245" customFormat="1" ht="21" customHeight="1" spans="1:7">
       <c r="A1" s="251" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B1" s="252" t="s">
         <v>0</v>
@@ -9508,10 +9496,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="253" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G1" s="253" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
@@ -9522,7 +9510,7 @@
         <v>45992</v>
       </c>
       <c r="C2" s="256" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D2" s="115">
         <v>5</v>
@@ -9543,7 +9531,7 @@
       <c r="A3" s="43"/>
       <c r="B3" s="42"/>
       <c r="C3" s="256" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D3" s="115">
         <v>1</v>
@@ -9561,7 +9549,7 @@
       <c r="A4" s="260"/>
       <c r="B4" s="261"/>
       <c r="C4" s="256" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D4" s="115">
         <v>1</v>
@@ -9583,7 +9571,7 @@
         <v>45993</v>
       </c>
       <c r="C5" s="256" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D5" s="115">
         <v>5</v>
@@ -9604,7 +9592,7 @@
       <c r="A6" s="205"/>
       <c r="B6" s="42"/>
       <c r="C6" s="256" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D6" s="115">
         <v>1</v>
@@ -9622,7 +9610,7 @@
       <c r="A7" s="203"/>
       <c r="B7" s="261"/>
       <c r="C7" s="256" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D7" s="115">
         <v>1</v>
@@ -9644,7 +9632,7 @@
         <v>45994</v>
       </c>
       <c r="C8" s="256" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D8" s="115">
         <v>6</v>
@@ -9665,7 +9653,7 @@
       <c r="A9" s="205"/>
       <c r="B9" s="42"/>
       <c r="C9" s="256" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D9" s="115">
         <v>1</v>
@@ -9683,7 +9671,7 @@
       <c r="A10" s="205"/>
       <c r="B10" s="42"/>
       <c r="C10" s="256" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D10" s="115">
         <v>1</v>
@@ -9701,7 +9689,7 @@
       <c r="A11" s="205"/>
       <c r="B11" s="42"/>
       <c r="C11" s="256" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D11" s="115">
         <v>1</v>
@@ -9719,7 +9707,7 @@
       <c r="A12" s="205"/>
       <c r="B12" s="42"/>
       <c r="C12" s="264" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D12" s="115">
         <v>2</v>
@@ -9737,7 +9725,7 @@
       <c r="A13" s="203"/>
       <c r="B13" s="261"/>
       <c r="C13" s="256" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="115">
         <v>1</v>
@@ -9759,7 +9747,7 @@
         <v>45995</v>
       </c>
       <c r="C14" s="256" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D14" s="115">
         <v>6</v>
@@ -9780,7 +9768,7 @@
       <c r="A15" s="203"/>
       <c r="B15" s="261"/>
       <c r="C15" s="264" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D15" s="115">
         <v>2</v>
@@ -9802,7 +9790,7 @@
         <v>45997</v>
       </c>
       <c r="C16" s="264" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D16" s="115">
         <v>2</v>
@@ -9823,7 +9811,7 @@
       <c r="A17" s="205"/>
       <c r="B17" s="42"/>
       <c r="C17" s="264" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D17" s="115">
         <v>1</v>
@@ -9841,7 +9829,7 @@
       <c r="A18" s="203"/>
       <c r="B18" s="261"/>
       <c r="C18" s="264" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D18" s="115">
         <v>5</v>
@@ -9863,7 +9851,7 @@
         <v>45998</v>
       </c>
       <c r="C19" s="256" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D19" s="115">
         <v>2</v>
@@ -9884,7 +9872,7 @@
       <c r="A20" s="205"/>
       <c r="B20" s="42"/>
       <c r="C20" s="256" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D20" s="115">
         <v>1</v>
@@ -9902,7 +9890,7 @@
       <c r="A21" s="205"/>
       <c r="B21" s="42"/>
       <c r="C21" s="256" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D21" s="115">
         <v>5</v>
@@ -9920,7 +9908,7 @@
       <c r="A22" s="205"/>
       <c r="B22" s="42"/>
       <c r="C22" s="256" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D22" s="115">
         <v>1</v>
@@ -9938,7 +9926,7 @@
       <c r="A23" s="203"/>
       <c r="B23" s="261"/>
       <c r="C23" s="264" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D23" s="115">
         <v>2</v>
@@ -9960,7 +9948,7 @@
         <v>45999</v>
       </c>
       <c r="C24" s="256" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D24" s="115">
         <v>1</v>
@@ -9981,7 +9969,7 @@
       <c r="A25" s="205"/>
       <c r="B25" s="42"/>
       <c r="C25" s="256" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D25" s="115">
         <v>1</v>
@@ -9999,7 +9987,7 @@
       <c r="A26" s="205"/>
       <c r="B26" s="42"/>
       <c r="C26" s="264" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D26" s="115">
         <v>1</v>
@@ -10017,7 +10005,7 @@
       <c r="A27" s="203"/>
       <c r="B27" s="261"/>
       <c r="C27" s="256" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D27" s="115">
         <v>4</v>
@@ -10039,7 +10027,7 @@
         <v>46000</v>
       </c>
       <c r="C28" s="264" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D28" s="115">
         <v>5</v>
@@ -10060,7 +10048,7 @@
       <c r="A29" s="205"/>
       <c r="B29" s="42"/>
       <c r="C29" s="256" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D29" s="115">
         <v>1</v>
@@ -10078,7 +10066,7 @@
       <c r="A30" s="203"/>
       <c r="B30" s="261"/>
       <c r="C30" s="256" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D30" s="115">
         <v>1</v>
@@ -10100,7 +10088,7 @@
         <v>46001</v>
       </c>
       <c r="C31" s="265" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D31" s="115">
         <v>6</v>
@@ -10121,7 +10109,7 @@
       <c r="A32" s="49"/>
       <c r="B32" s="25"/>
       <c r="C32" s="266" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D32" s="115">
         <v>1</v>
@@ -10139,7 +10127,7 @@
       <c r="A33" s="49"/>
       <c r="B33" s="25"/>
       <c r="C33" s="265" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D33" s="115">
         <v>1</v>
@@ -10157,7 +10145,7 @@
       <c r="A34" s="49"/>
       <c r="B34" s="25"/>
       <c r="C34" s="265" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D34" s="115">
         <v>1</v>
@@ -10175,7 +10163,7 @@
       <c r="A35" s="49"/>
       <c r="B35" s="25"/>
       <c r="C35" s="265" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D35" s="115">
         <v>1</v>
@@ -10193,7 +10181,7 @@
       <c r="A36" s="49"/>
       <c r="B36" s="25"/>
       <c r="C36" s="265" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D36" s="115">
         <v>1</v>
@@ -10211,7 +10199,7 @@
       <c r="A37" s="49"/>
       <c r="B37" s="25"/>
       <c r="C37" s="265" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D37" s="115">
         <v>2</v>
@@ -10233,7 +10221,7 @@
         <v>46002</v>
       </c>
       <c r="C38" s="256" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D38" s="115">
         <v>6</v>
@@ -10254,7 +10242,7 @@
       <c r="A39" s="205"/>
       <c r="B39" s="42"/>
       <c r="C39" s="256" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D39" s="115">
         <v>2</v>
@@ -10272,7 +10260,7 @@
       <c r="A40" s="205"/>
       <c r="B40" s="42"/>
       <c r="C40" s="256" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D40" s="115">
         <v>1</v>
@@ -10287,14 +10275,14 @@
       <c r="G40" s="262"/>
     </row>
     <row r="41" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A41" s="267">
+      <c r="A41" s="202">
         <v>74702</v>
       </c>
-      <c r="B41" s="268">
+      <c r="B41" s="36">
         <v>46003</v>
       </c>
       <c r="C41" s="256" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D41" s="115">
         <v>6</v>
@@ -10306,16 +10294,16 @@
         <f t="shared" si="2"/>
         <v>48000</v>
       </c>
-      <c r="G41" s="269">
+      <c r="G41" s="258">
         <f>SUM(F41:F45)</f>
         <v>717000</v>
       </c>
     </row>
     <row r="42" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A42" s="270"/>
-      <c r="B42" s="271"/>
+      <c r="A42" s="205"/>
+      <c r="B42" s="42"/>
       <c r="C42" s="256" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D42" s="115">
         <v>1</v>
@@ -10327,13 +10315,13 @@
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="G42" s="272"/>
+      <c r="G42" s="259"/>
     </row>
     <row r="43" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A43" s="270"/>
-      <c r="B43" s="271"/>
+      <c r="A43" s="205"/>
+      <c r="B43" s="42"/>
       <c r="C43" s="256" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D43" s="115">
         <v>2</v>
@@ -10345,13 +10333,13 @@
         <f t="shared" si="2"/>
         <v>44000</v>
       </c>
-      <c r="G43" s="272"/>
+      <c r="G43" s="259"/>
     </row>
     <row r="44" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A44" s="270"/>
-      <c r="B44" s="271"/>
+      <c r="A44" s="205"/>
+      <c r="B44" s="42"/>
       <c r="C44" s="256" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D44" s="115">
         <v>1</v>
@@ -10363,13 +10351,13 @@
         <f t="shared" si="2"/>
         <v>480000</v>
       </c>
-      <c r="G44" s="272"/>
+      <c r="G44" s="259"/>
     </row>
     <row r="45" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A45" s="273"/>
-      <c r="B45" s="274"/>
+      <c r="A45" s="203"/>
+      <c r="B45" s="261"/>
       <c r="C45" s="256" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D45" s="115">
         <v>1</v>
@@ -10381,11 +10369,11 @@
         <f t="shared" ref="F45:F71" si="3">SUM(D45*E45)</f>
         <v>125000</v>
       </c>
-      <c r="G45" s="275"/>
+      <c r="G45" s="262"/>
     </row>
     <row r="46" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A46" s="200"/>
-      <c r="B46" s="276"/>
+      <c r="B46" s="267"/>
       <c r="C46" s="256"/>
       <c r="D46" s="115"/>
       <c r="E46" s="7"/>
@@ -10393,11 +10381,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G46" s="277"/>
+      <c r="G46" s="268"/>
     </row>
     <row r="47" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A47" s="200"/>
-      <c r="B47" s="276"/>
+      <c r="B47" s="267"/>
       <c r="C47" s="256"/>
       <c r="D47" s="115"/>
       <c r="E47" s="7"/>
@@ -10405,11 +10393,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G47" s="277"/>
+      <c r="G47" s="268"/>
     </row>
     <row r="48" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A48" s="200"/>
-      <c r="B48" s="276"/>
+      <c r="B48" s="267"/>
       <c r="C48" s="256"/>
       <c r="D48" s="115"/>
       <c r="E48" s="7"/>
@@ -10417,11 +10405,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G48" s="277"/>
+      <c r="G48" s="268"/>
     </row>
     <row r="49" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A49" s="200"/>
-      <c r="B49" s="276"/>
+      <c r="B49" s="267"/>
       <c r="C49" s="256"/>
       <c r="D49" s="115"/>
       <c r="E49" s="7"/>
@@ -10429,11 +10417,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G49" s="277"/>
+      <c r="G49" s="268"/>
     </row>
     <row r="50" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A50" s="200"/>
-      <c r="B50" s="276"/>
+      <c r="B50" s="267"/>
       <c r="C50" s="256"/>
       <c r="D50" s="115"/>
       <c r="E50" s="7"/>
@@ -10441,11 +10429,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G50" s="277"/>
+      <c r="G50" s="268"/>
     </row>
     <row r="51" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A51" s="200"/>
-      <c r="B51" s="276"/>
+      <c r="B51" s="267"/>
       <c r="C51" s="256"/>
       <c r="D51" s="115"/>
       <c r="E51" s="7"/>
@@ -10453,11 +10441,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G51" s="277"/>
+      <c r="G51" s="268"/>
     </row>
     <row r="52" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A52" s="200"/>
-      <c r="B52" s="276"/>
+      <c r="B52" s="267"/>
       <c r="C52" s="256"/>
       <c r="D52" s="115"/>
       <c r="E52" s="7"/>
@@ -10465,11 +10453,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G52" s="277"/>
+      <c r="G52" s="268"/>
     </row>
     <row r="53" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A53" s="200"/>
-      <c r="B53" s="276"/>
+      <c r="B53" s="267"/>
       <c r="C53" s="256"/>
       <c r="D53" s="115"/>
       <c r="E53" s="7"/>
@@ -10477,7 +10465,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G53" s="277"/>
+      <c r="G53" s="268"/>
     </row>
     <row r="54" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A54" s="49"/>
@@ -10489,7 +10477,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G54" s="277">
+      <c r="G54" s="268">
         <f>SUM(F54:F57)</f>
         <v>0</v>
       </c>
@@ -10497,14 +10485,14 @@
     <row r="55" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A55" s="49"/>
       <c r="B55" s="25"/>
-      <c r="C55" s="278"/>
+      <c r="C55" s="269"/>
       <c r="D55" s="260"/>
-      <c r="E55" s="279"/>
+      <c r="E55" s="270"/>
       <c r="F55" s="257">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G55" s="277"/>
+      <c r="G55" s="268"/>
     </row>
     <row r="56" s="245" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A56" s="49"/>
@@ -10516,7 +10504,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G56" s="277"/>
+      <c r="G56" s="268"/>
     </row>
     <row r="57" s="245" customFormat="1" spans="1:7">
       <c r="A57" s="49"/>
@@ -10528,7 +10516,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G57" s="277"/>
+      <c r="G57" s="268"/>
     </row>
     <row r="58" s="245" customFormat="1" spans="1:7">
       <c r="A58" s="205"/>
@@ -10540,7 +10528,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G58" s="277">
+      <c r="G58" s="268">
         <f>SUM(F58:F59)</f>
         <v>0</v>
       </c>
@@ -10555,7 +10543,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G59" s="277"/>
+      <c r="G59" s="268"/>
     </row>
     <row r="60" s="245" customFormat="1" spans="1:7">
       <c r="A60" s="202"/>
@@ -10567,7 +10555,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G60" s="277">
+      <c r="G60" s="268">
         <f>SUM(F60:F62)</f>
         <v>0</v>
       </c>
@@ -10582,7 +10570,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G61" s="277"/>
+      <c r="G61" s="268"/>
     </row>
     <row r="62" s="245" customFormat="1" spans="1:7">
       <c r="A62" s="203"/>
@@ -10594,7 +10582,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G62" s="277"/>
+      <c r="G62" s="268"/>
     </row>
     <row r="63" s="245" customFormat="1" spans="1:7">
       <c r="A63" s="49"/>
@@ -10606,7 +10594,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G63" s="277">
+      <c r="G63" s="268">
         <f>SUM(F63:F67)</f>
         <v>0</v>
       </c>
@@ -10621,7 +10609,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G64" s="277"/>
+      <c r="G64" s="268"/>
     </row>
     <row r="65" s="245" customFormat="1" spans="1:7">
       <c r="A65" s="49"/>
@@ -10633,7 +10621,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G65" s="277"/>
+      <c r="G65" s="268"/>
     </row>
     <row r="66" s="245" customFormat="1" spans="1:7">
       <c r="A66" s="49"/>
@@ -10645,7 +10633,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G66" s="277"/>
+      <c r="G66" s="268"/>
     </row>
     <row r="67" s="245" customFormat="1" spans="1:8">
       <c r="A67" s="49"/>
@@ -10657,8 +10645,8 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G67" s="277"/>
-      <c r="H67" s="280"/>
+      <c r="G67" s="268"/>
+      <c r="H67" s="271"/>
     </row>
     <row r="68" s="245" customFormat="1" ht="15.75" spans="1:14">
       <c r="A68" s="49"/>
@@ -10670,17 +10658,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G68" s="277">
+      <c r="G68" s="268">
         <f>SUM(F68)</f>
         <v>0</v>
       </c>
-      <c r="H68" s="280"/>
-      <c r="I68" s="285"/>
-      <c r="J68" s="286"/>
-      <c r="K68" s="287"/>
-      <c r="L68" s="288"/>
-      <c r="M68" s="288"/>
-      <c r="N68" s="289"/>
+      <c r="H68" s="271"/>
+      <c r="I68" s="276"/>
+      <c r="J68" s="277"/>
+      <c r="K68" s="278"/>
+      <c r="L68" s="279"/>
+      <c r="M68" s="279"/>
+      <c r="N68" s="280"/>
     </row>
     <row r="69" s="245" customFormat="1" ht="15.75" spans="1:14">
       <c r="A69" s="202"/>
@@ -10692,16 +10680,16 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G69" s="277">
+      <c r="G69" s="268">
         <f>SUM(F69:F71)</f>
         <v>0</v>
       </c>
-      <c r="I69" s="290"/>
-      <c r="J69" s="286"/>
-      <c r="K69" s="287"/>
-      <c r="L69" s="288"/>
-      <c r="M69" s="288"/>
-      <c r="N69" s="288"/>
+      <c r="I69" s="281"/>
+      <c r="J69" s="277"/>
+      <c r="K69" s="278"/>
+      <c r="L69" s="279"/>
+      <c r="M69" s="279"/>
+      <c r="N69" s="279"/>
     </row>
     <row r="70" s="245" customFormat="1" ht="15.75" spans="1:14">
       <c r="A70" s="205"/>
@@ -10713,13 +10701,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G70" s="277"/>
-      <c r="I70" s="290"/>
-      <c r="J70" s="286"/>
-      <c r="K70" s="287"/>
-      <c r="L70" s="288"/>
-      <c r="M70" s="288"/>
-      <c r="N70" s="288"/>
+      <c r="G70" s="268"/>
+      <c r="I70" s="281"/>
+      <c r="J70" s="277"/>
+      <c r="K70" s="278"/>
+      <c r="L70" s="279"/>
+      <c r="M70" s="279"/>
+      <c r="N70" s="279"/>
     </row>
     <row r="71" s="245" customFormat="1" ht="15.75" spans="1:14">
       <c r="A71" s="203"/>
@@ -10731,25 +10719,25 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G71" s="277"/>
-      <c r="I71" s="290"/>
-      <c r="J71" s="286"/>
-      <c r="K71" s="287"/>
-      <c r="L71" s="288"/>
-      <c r="M71" s="288"/>
-      <c r="N71" s="288"/>
+      <c r="G71" s="268"/>
+      <c r="I71" s="281"/>
+      <c r="J71" s="277"/>
+      <c r="K71" s="278"/>
+      <c r="L71" s="279"/>
+      <c r="M71" s="279"/>
+      <c r="N71" s="279"/>
     </row>
     <row r="72" s="245" customFormat="1" spans="1:7">
       <c r="A72" s="202"/>
       <c r="B72" s="36"/>
-      <c r="C72" s="281"/>
+      <c r="C72" s="272"/>
       <c r="D72" s="115"/>
       <c r="E72" s="257"/>
       <c r="F72" s="257">
         <f t="shared" ref="F72:F83" si="4">D72*E72</f>
         <v>0</v>
       </c>
-      <c r="G72" s="277">
+      <c r="G72" s="268">
         <f>SUM(F72:F78)</f>
         <v>0</v>
       </c>
@@ -10757,86 +10745,86 @@
     <row r="73" s="245" customFormat="1" spans="1:7">
       <c r="A73" s="205"/>
       <c r="B73" s="42"/>
-      <c r="C73" s="281"/>
+      <c r="C73" s="272"/>
       <c r="D73" s="115"/>
       <c r="E73" s="257"/>
       <c r="F73" s="257">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G73" s="277"/>
+      <c r="G73" s="268"/>
     </row>
     <row r="74" s="245" customFormat="1" spans="1:7">
       <c r="A74" s="205"/>
       <c r="B74" s="42"/>
-      <c r="C74" s="281"/>
+      <c r="C74" s="272"/>
       <c r="D74" s="115"/>
       <c r="E74" s="257"/>
       <c r="F74" s="257">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G74" s="277"/>
+      <c r="G74" s="268"/>
     </row>
     <row r="75" s="245" customFormat="1" spans="1:7">
       <c r="A75" s="205"/>
       <c r="B75" s="42"/>
-      <c r="C75" s="281"/>
+      <c r="C75" s="272"/>
       <c r="D75" s="115"/>
       <c r="E75" s="257"/>
       <c r="F75" s="257">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G75" s="277"/>
+      <c r="G75" s="268"/>
     </row>
     <row r="76" s="245" customFormat="1" spans="1:7">
       <c r="A76" s="205"/>
       <c r="B76" s="42"/>
-      <c r="C76" s="281"/>
+      <c r="C76" s="272"/>
       <c r="D76" s="115"/>
       <c r="E76" s="257"/>
       <c r="F76" s="257">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G76" s="277"/>
+      <c r="G76" s="268"/>
     </row>
     <row r="77" s="245" customFormat="1" spans="1:7">
       <c r="A77" s="205"/>
       <c r="B77" s="42"/>
-      <c r="C77" s="281"/>
+      <c r="C77" s="272"/>
       <c r="D77" s="115"/>
       <c r="E77" s="257"/>
       <c r="F77" s="257">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G77" s="277"/>
+      <c r="G77" s="268"/>
     </row>
     <row r="78" s="245" customFormat="1" spans="1:7">
       <c r="A78" s="203"/>
       <c r="B78" s="261"/>
-      <c r="C78" s="281"/>
+      <c r="C78" s="272"/>
       <c r="D78" s="115"/>
       <c r="E78" s="257"/>
       <c r="F78" s="257">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G78" s="277"/>
+      <c r="G78" s="268"/>
     </row>
     <row r="79" s="245" customFormat="1" spans="1:7">
       <c r="A79" s="202"/>
       <c r="B79" s="36"/>
-      <c r="C79" s="281"/>
+      <c r="C79" s="272"/>
       <c r="D79" s="115"/>
       <c r="E79" s="257"/>
       <c r="F79" s="257">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G79" s="277">
+      <c r="G79" s="268">
         <f>SUM(F79:F83)</f>
         <v>0</v>
       </c>
@@ -10844,62 +10832,62 @@
     <row r="80" s="245" customFormat="1" spans="1:7">
       <c r="A80" s="205"/>
       <c r="B80" s="42"/>
-      <c r="C80" s="281"/>
+      <c r="C80" s="272"/>
       <c r="D80" s="115"/>
       <c r="E80" s="257"/>
       <c r="F80" s="257">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G80" s="277"/>
+      <c r="G80" s="268"/>
     </row>
     <row r="81" s="245" customFormat="1" spans="1:7">
       <c r="A81" s="205"/>
       <c r="B81" s="42"/>
-      <c r="C81" s="281"/>
+      <c r="C81" s="272"/>
       <c r="D81" s="115"/>
       <c r="E81" s="257"/>
       <c r="F81" s="257">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G81" s="277"/>
+      <c r="G81" s="268"/>
     </row>
     <row r="82" s="245" customFormat="1" spans="1:7">
       <c r="A82" s="205"/>
       <c r="B82" s="42"/>
-      <c r="C82" s="281"/>
+      <c r="C82" s="272"/>
       <c r="D82" s="115"/>
       <c r="E82" s="257"/>
       <c r="F82" s="257">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G82" s="277"/>
+      <c r="G82" s="268"/>
     </row>
     <row r="83" s="245" customFormat="1" spans="1:7">
       <c r="A83" s="203"/>
       <c r="B83" s="261"/>
-      <c r="C83" s="281"/>
+      <c r="C83" s="272"/>
       <c r="D83" s="115"/>
       <c r="E83" s="257"/>
       <c r="F83" s="257">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G83" s="277"/>
+      <c r="G83" s="268"/>
     </row>
     <row r="84" s="245" customFormat="1" spans="1:7">
       <c r="A84" s="202"/>
       <c r="B84" s="36"/>
-      <c r="C84" s="281"/>
+      <c r="C84" s="272"/>
       <c r="D84" s="115"/>
       <c r="E84" s="257"/>
       <c r="F84" s="257">
         <f t="shared" ref="F84:F92" si="5">D84*E84</f>
         <v>0</v>
       </c>
-      <c r="G84" s="277">
+      <c r="G84" s="268">
         <f>SUM(F84:F89)</f>
         <v>0</v>
       </c>
@@ -10907,74 +10895,74 @@
     <row r="85" s="245" customFormat="1" spans="1:7">
       <c r="A85" s="205"/>
       <c r="B85" s="42"/>
-      <c r="C85" s="281"/>
+      <c r="C85" s="272"/>
       <c r="D85" s="115"/>
       <c r="E85" s="257"/>
       <c r="F85" s="257">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G85" s="277"/>
+      <c r="G85" s="268"/>
     </row>
     <row r="86" s="245" customFormat="1" spans="1:7">
       <c r="A86" s="205"/>
       <c r="B86" s="42"/>
-      <c r="C86" s="281"/>
+      <c r="C86" s="272"/>
       <c r="D86" s="115"/>
       <c r="E86" s="257"/>
       <c r="F86" s="257">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G86" s="277"/>
+      <c r="G86" s="268"/>
     </row>
     <row r="87" s="245" customFormat="1" spans="1:7">
       <c r="A87" s="205"/>
       <c r="B87" s="42"/>
-      <c r="C87" s="281"/>
+      <c r="C87" s="272"/>
       <c r="D87" s="115"/>
       <c r="E87" s="257"/>
       <c r="F87" s="257">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G87" s="277"/>
+      <c r="G87" s="268"/>
     </row>
     <row r="88" s="245" customFormat="1" spans="1:7">
       <c r="A88" s="205"/>
       <c r="B88" s="42"/>
-      <c r="C88" s="281"/>
+      <c r="C88" s="272"/>
       <c r="D88" s="115"/>
       <c r="E88" s="257"/>
       <c r="F88" s="257">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G88" s="277"/>
+      <c r="G88" s="268"/>
     </row>
     <row r="89" s="245" customFormat="1" spans="1:7">
       <c r="A89" s="203"/>
       <c r="B89" s="261"/>
-      <c r="C89" s="281"/>
+      <c r="C89" s="272"/>
       <c r="D89" s="115"/>
       <c r="E89" s="257"/>
       <c r="F89" s="257">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G89" s="277"/>
+      <c r="G89" s="268"/>
     </row>
     <row r="90" s="245" customFormat="1" spans="1:7">
       <c r="A90" s="202"/>
       <c r="B90" s="36"/>
-      <c r="C90" s="281"/>
+      <c r="C90" s="272"/>
       <c r="D90" s="115"/>
       <c r="E90" s="257"/>
       <c r="F90" s="257">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G90" s="277">
+      <c r="G90" s="268">
         <f>SUM(F90:F92)</f>
         <v>0</v>
       </c>
@@ -10982,38 +10970,38 @@
     <row r="91" s="245" customFormat="1" spans="1:7">
       <c r="A91" s="205"/>
       <c r="B91" s="42"/>
-      <c r="C91" s="281"/>
+      <c r="C91" s="272"/>
       <c r="D91" s="115"/>
       <c r="E91" s="257"/>
       <c r="F91" s="257">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G91" s="277"/>
+      <c r="G91" s="268"/>
     </row>
     <row r="92" s="245" customFormat="1" spans="1:7">
       <c r="A92" s="203"/>
       <c r="B92" s="261"/>
-      <c r="C92" s="281"/>
+      <c r="C92" s="272"/>
       <c r="D92" s="115"/>
       <c r="E92" s="257"/>
       <c r="F92" s="257">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G92" s="277"/>
+      <c r="G92" s="268"/>
     </row>
     <row r="93" s="245" customFormat="1" spans="1:7">
       <c r="A93" s="202"/>
       <c r="B93" s="36"/>
-      <c r="C93" s="281"/>
+      <c r="C93" s="272"/>
       <c r="D93" s="115"/>
       <c r="E93" s="257"/>
       <c r="F93" s="257">
         <f t="shared" ref="F93:F113" si="6">D93*E93</f>
         <v>0</v>
       </c>
-      <c r="G93" s="277">
+      <c r="G93" s="268">
         <f>SUM(F93:F98)</f>
         <v>0</v>
       </c>
@@ -11021,74 +11009,74 @@
     <row r="94" s="245" customFormat="1" spans="1:7">
       <c r="A94" s="205"/>
       <c r="B94" s="42"/>
-      <c r="C94" s="281"/>
+      <c r="C94" s="272"/>
       <c r="D94" s="115"/>
       <c r="E94" s="257"/>
       <c r="F94" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G94" s="277"/>
+      <c r="G94" s="268"/>
     </row>
     <row r="95" s="245" customFormat="1" spans="1:7">
       <c r="A95" s="205"/>
       <c r="B95" s="42"/>
-      <c r="C95" s="281"/>
+      <c r="C95" s="272"/>
       <c r="D95" s="115"/>
       <c r="E95" s="257"/>
       <c r="F95" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G95" s="277"/>
+      <c r="G95" s="268"/>
     </row>
     <row r="96" s="245" customFormat="1" spans="1:7">
       <c r="A96" s="205"/>
       <c r="B96" s="42"/>
-      <c r="C96" s="281"/>
+      <c r="C96" s="272"/>
       <c r="D96" s="115"/>
       <c r="E96" s="257"/>
       <c r="F96" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G96" s="277"/>
+      <c r="G96" s="268"/>
     </row>
     <row r="97" s="245" customFormat="1" spans="1:7">
       <c r="A97" s="205"/>
       <c r="B97" s="42"/>
-      <c r="C97" s="281"/>
+      <c r="C97" s="272"/>
       <c r="D97" s="115"/>
       <c r="E97" s="257"/>
       <c r="F97" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G97" s="277"/>
+      <c r="G97" s="268"/>
     </row>
     <row r="98" s="245" customFormat="1" spans="1:7">
       <c r="A98" s="203"/>
       <c r="B98" s="261"/>
-      <c r="C98" s="281"/>
+      <c r="C98" s="272"/>
       <c r="D98" s="115"/>
       <c r="E98" s="257"/>
       <c r="F98" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G98" s="277"/>
+      <c r="G98" s="268"/>
     </row>
     <row r="99" s="245" customFormat="1" spans="1:7">
       <c r="A99" s="202"/>
       <c r="B99" s="36"/>
-      <c r="C99" s="281"/>
+      <c r="C99" s="272"/>
       <c r="D99" s="115"/>
       <c r="E99" s="257"/>
       <c r="F99" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G99" s="277">
+      <c r="G99" s="268">
         <f>SUM(F99:F103)</f>
         <v>0</v>
       </c>
@@ -11096,62 +11084,62 @@
     <row r="100" s="245" customFormat="1" spans="1:7">
       <c r="A100" s="205"/>
       <c r="B100" s="42"/>
-      <c r="C100" s="281"/>
+      <c r="C100" s="272"/>
       <c r="D100" s="115"/>
       <c r="E100" s="257"/>
       <c r="F100" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G100" s="277"/>
+      <c r="G100" s="268"/>
     </row>
     <row r="101" s="245" customFormat="1" spans="1:7">
       <c r="A101" s="205"/>
       <c r="B101" s="42"/>
-      <c r="C101" s="281"/>
+      <c r="C101" s="272"/>
       <c r="D101" s="115"/>
       <c r="E101" s="257"/>
       <c r="F101" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G101" s="277"/>
+      <c r="G101" s="268"/>
     </row>
     <row r="102" s="245" customFormat="1" spans="1:7">
       <c r="A102" s="205"/>
       <c r="B102" s="42"/>
-      <c r="C102" s="281"/>
+      <c r="C102" s="272"/>
       <c r="D102" s="115"/>
       <c r="E102" s="257"/>
       <c r="F102" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G102" s="277"/>
+      <c r="G102" s="268"/>
     </row>
     <row r="103" s="245" customFormat="1" spans="1:7">
       <c r="A103" s="203"/>
       <c r="B103" s="261"/>
-      <c r="C103" s="281"/>
+      <c r="C103" s="272"/>
       <c r="D103" s="115"/>
       <c r="E103" s="257"/>
       <c r="F103" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G103" s="277"/>
+      <c r="G103" s="268"/>
     </row>
     <row r="104" s="245" customFormat="1" spans="1:7">
       <c r="A104" s="202"/>
       <c r="B104" s="36"/>
-      <c r="C104" s="281"/>
+      <c r="C104" s="272"/>
       <c r="D104" s="115"/>
       <c r="E104" s="257"/>
       <c r="F104" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G104" s="277">
+      <c r="G104" s="268">
         <f>SUM(F104:F109)</f>
         <v>0</v>
       </c>
@@ -11159,74 +11147,74 @@
     <row r="105" s="245" customFormat="1" spans="1:7">
       <c r="A105" s="205"/>
       <c r="B105" s="42"/>
-      <c r="C105" s="281"/>
+      <c r="C105" s="272"/>
       <c r="D105" s="115"/>
       <c r="E105" s="257"/>
       <c r="F105" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G105" s="277"/>
+      <c r="G105" s="268"/>
     </row>
     <row r="106" s="245" customFormat="1" spans="1:7">
       <c r="A106" s="205"/>
       <c r="B106" s="42"/>
-      <c r="C106" s="281"/>
+      <c r="C106" s="272"/>
       <c r="D106" s="115"/>
       <c r="E106" s="257"/>
       <c r="F106" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G106" s="277"/>
+      <c r="G106" s="268"/>
     </row>
     <row r="107" s="245" customFormat="1" spans="1:7">
       <c r="A107" s="205"/>
       <c r="B107" s="42"/>
-      <c r="C107" s="281"/>
+      <c r="C107" s="272"/>
       <c r="D107" s="115"/>
       <c r="E107" s="257"/>
       <c r="F107" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G107" s="277"/>
+      <c r="G107" s="268"/>
     </row>
     <row r="108" s="245" customFormat="1" spans="1:7">
       <c r="A108" s="205"/>
       <c r="B108" s="42"/>
-      <c r="C108" s="281"/>
+      <c r="C108" s="272"/>
       <c r="D108" s="115"/>
       <c r="E108" s="257"/>
       <c r="F108" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G108" s="277"/>
+      <c r="G108" s="268"/>
     </row>
     <row r="109" s="245" customFormat="1" spans="1:7">
       <c r="A109" s="203"/>
       <c r="B109" s="261"/>
-      <c r="C109" s="281"/>
+      <c r="C109" s="272"/>
       <c r="D109" s="115"/>
       <c r="E109" s="257"/>
       <c r="F109" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G109" s="277"/>
+      <c r="G109" s="268"/>
     </row>
     <row r="110" s="245" customFormat="1" spans="1:7">
       <c r="A110" s="202"/>
       <c r="B110" s="36"/>
-      <c r="C110" s="281"/>
+      <c r="C110" s="272"/>
       <c r="D110" s="115"/>
       <c r="E110" s="257"/>
       <c r="F110" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G110" s="277">
+      <c r="G110" s="268">
         <f>SUM(F110:F113)</f>
         <v>0</v>
       </c>
@@ -11234,50 +11222,50 @@
     <row r="111" s="245" customFormat="1" spans="1:7">
       <c r="A111" s="205"/>
       <c r="B111" s="42"/>
-      <c r="C111" s="281"/>
+      <c r="C111" s="272"/>
       <c r="D111" s="115"/>
       <c r="E111" s="257"/>
       <c r="F111" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G111" s="277"/>
+      <c r="G111" s="268"/>
     </row>
     <row r="112" s="245" customFormat="1" spans="1:7">
       <c r="A112" s="205"/>
       <c r="B112" s="42"/>
-      <c r="C112" s="281"/>
+      <c r="C112" s="272"/>
       <c r="D112" s="115"/>
       <c r="E112" s="257"/>
       <c r="F112" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G112" s="277"/>
+      <c r="G112" s="268"/>
     </row>
     <row r="113" s="245" customFormat="1" spans="1:7">
       <c r="A113" s="205"/>
       <c r="B113" s="42"/>
-      <c r="C113" s="281"/>
+      <c r="C113" s="272"/>
       <c r="D113" s="115"/>
       <c r="E113" s="257"/>
       <c r="F113" s="257">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G113" s="277"/>
+      <c r="G113" s="268"/>
     </row>
     <row r="114" s="245" customFormat="1" spans="1:7">
       <c r="A114" s="202"/>
       <c r="B114" s="36"/>
-      <c r="C114" s="281"/>
+      <c r="C114" s="272"/>
       <c r="D114" s="115"/>
       <c r="E114" s="257"/>
       <c r="F114" s="257">
         <f t="shared" ref="F114:F116" si="7">D114*E114</f>
         <v>0</v>
       </c>
-      <c r="G114" s="277">
+      <c r="G114" s="268">
         <f>SUM(F114:F116)</f>
         <v>0</v>
       </c>
@@ -11285,36 +11273,36 @@
     <row r="115" s="245" customFormat="1" spans="1:7">
       <c r="A115" s="205"/>
       <c r="B115" s="42"/>
-      <c r="C115" s="281"/>
+      <c r="C115" s="272"/>
       <c r="D115" s="115"/>
       <c r="E115" s="257"/>
       <c r="F115" s="257">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G115" s="277"/>
+      <c r="G115" s="268"/>
     </row>
     <row r="116" s="245" customFormat="1" spans="1:7">
       <c r="A116" s="203"/>
       <c r="B116" s="261"/>
-      <c r="C116" s="281"/>
+      <c r="C116" s="272"/>
       <c r="D116" s="115"/>
       <c r="E116" s="257"/>
       <c r="F116" s="257">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G116" s="277"/>
+      <c r="G116" s="268"/>
     </row>
     <row r="117" s="245" customFormat="1" spans="1:7">
-      <c r="A117" s="282" t="s">
-        <v>53</v>
+      <c r="A117" s="273" t="s">
+        <v>50</v>
       </c>
       <c r="B117" s="126"/>
-      <c r="C117" s="283"/>
+      <c r="C117" s="274"/>
       <c r="D117" s="126"/>
       <c r="E117" s="126"/>
-      <c r="F117" s="284"/>
+      <c r="F117" s="275"/>
       <c r="G117" s="60">
         <f>SUM(G2:G116)</f>
         <v>3914000</v>
@@ -11599,7 +11587,7 @@
       <c r="D152" s="249"/>
       <c r="E152" s="250"/>
       <c r="G152" s="246"/>
-      <c r="H152" s="280"/>
+      <c r="H152" s="271"/>
     </row>
   </sheetData>
   <mergeCells count="63">
@@ -11690,16 +11678,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>57</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>3</v>
@@ -11716,7 +11704,7 @@
         <v>12340</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D2" s="16">
         <v>20</v>
@@ -11738,7 +11726,7 @@
         <v>12357</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D3" s="16">
         <v>20</v>
@@ -11760,7 +11748,7 @@
         <v>11374</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D4" s="16">
         <v>20</v>
@@ -11782,7 +11770,7 @@
         <v>13396</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D5" s="16">
         <v>20</v>
@@ -11804,7 +11792,7 @@
         <v>11474</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D6" s="16">
         <v>20</v>
@@ -11912,7 +11900,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="225" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F1" s="225" t="s">
         <v>5</v>
@@ -11960,7 +11948,7 @@
     <row r="4" s="218" customFormat="1" spans="1:7">
       <c r="A4" s="231"/>
       <c r="B4" s="227" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C4" s="228">
         <v>0.3</v>
@@ -11978,7 +11966,7 @@
     <row r="5" s="218" customFormat="1" spans="1:6">
       <c r="A5" s="231"/>
       <c r="B5" s="227" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C5" s="228">
         <v>1</v>
@@ -12064,7 +12052,7 @@
     <row r="10" s="218" customFormat="1" spans="1:6">
       <c r="A10" s="234"/>
       <c r="B10" s="227" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C10" s="228">
         <v>2</v>
@@ -12121,7 +12109,7 @@
     <row r="13" s="218" customFormat="1" spans="1:6">
       <c r="A13" s="231"/>
       <c r="B13" s="227" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C13" s="228">
         <v>8</v>
@@ -12172,7 +12160,7 @@
     <row r="16" s="218" customFormat="1" spans="1:6">
       <c r="A16" s="231"/>
       <c r="B16" s="227" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C16" s="228">
         <v>2</v>
@@ -12206,7 +12194,7 @@
     <row r="18" s="218" customFormat="1" spans="1:6">
       <c r="A18" s="231"/>
       <c r="B18" s="227" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C18" s="228">
         <v>1</v>
@@ -12240,7 +12228,7 @@
     <row r="20" s="218" customFormat="1" spans="1:6">
       <c r="A20" s="234"/>
       <c r="B20" s="227" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C20" s="228">
         <v>1</v>
@@ -14260,19 +14248,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>57</v>
-      </c>
       <c r="F1" s="13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>4</v>
@@ -14286,10 +14274,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="212" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D2" s="16">
         <v>3</v>
@@ -14430,31 +14418,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="177" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C1" s="177" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D1" s="177" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E1" s="177" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="177" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G1" s="177" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H1" s="177" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I1" s="177" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="177" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" ht="387.45" customHeight="1" spans="1:10">
@@ -14462,10 +14450,10 @@
         <v>46000</v>
       </c>
       <c r="B2" s="179" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C2" s="171" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D2" s="180">
         <v>4</v>
@@ -14496,10 +14484,10 @@
         <v>46002</v>
       </c>
       <c r="B3" s="184" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C3" s="171" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D3" s="180">
         <v>4</v>
@@ -14529,7 +14517,7 @@
       <c r="A4" s="185"/>
       <c r="B4" s="186"/>
       <c r="C4" s="187" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D4" s="188">
         <v>4</v>
@@ -14862,16 +14850,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="168" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="168" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="168" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="168" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="168" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="168" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="168" t="s">
-        <v>57</v>
       </c>
       <c r="F1" s="168" t="s">
         <v>3</v>
@@ -14933,22 +14921,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="137" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="137" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="137" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="137" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="137" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="137" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="137" t="s">
-        <v>57</v>
       </c>
       <c r="F1" s="137" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="137" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H1" s="138" t="s">
         <v>5</v>
@@ -14959,10 +14947,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="139" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" s="140" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D2" s="141">
         <v>5</v>
@@ -15032,7 +15020,7 @@
       </c>
       <c r="E7" s="155"/>
       <c r="F7" s="156" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G7" s="156"/>
       <c r="H7" s="156">
@@ -15060,10 +15048,10 @@
         <v>45999</v>
       </c>
       <c r="B9" s="139" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C9" s="160" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D9" s="154">
         <v>3</v>
@@ -15085,7 +15073,7 @@
       <c r="A10" s="145"/>
       <c r="B10" s="145"/>
       <c r="C10" s="160" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D10" s="154">
         <v>3</v>
@@ -15104,7 +15092,7 @@
       <c r="A11" s="165"/>
       <c r="B11" s="165"/>
       <c r="C11" s="160" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D11" s="154">
         <v>2</v>
@@ -15131,7 +15119,7 @@
       </c>
       <c r="E12" s="155"/>
       <c r="F12" s="156" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G12" s="156"/>
       <c r="H12" s="156">
@@ -15159,10 +15147,10 @@
         <v>45992</v>
       </c>
       <c r="B14" s="139" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C14" s="140" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D14" s="141">
         <v>5</v>
@@ -15235,7 +15223,7 @@
       </c>
       <c r="E19" s="155"/>
       <c r="F19" s="156" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G19" s="156"/>
       <c r="H19" s="156">
@@ -15341,16 +15329,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="35" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="35" t="s">
-        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -15364,10 +15352,10 @@
         <v>46001</v>
       </c>
       <c r="B2" s="115" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D2" s="115">
         <v>2</v>
@@ -15386,10 +15374,10 @@
         <v>46001</v>
       </c>
       <c r="B3" s="93" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D3" s="115">
         <v>4</v>
@@ -15405,7 +15393,7 @@
     </row>
     <row r="4" ht="23.25" spans="1:7">
       <c r="A4" s="87" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B4" s="88"/>
       <c r="C4" s="88"/>

--- a/DECEMBER/DECEMBER BAR.xlsx
+++ b/DECEMBER/DECEMBER BAR.xlsx
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="119">
   <si>
     <t>DATE</t>
   </si>
@@ -215,6 +215,15 @@
     <t>APPLE</t>
   </si>
   <si>
+    <t>GREEN APPLE</t>
+  </si>
+  <si>
+    <t>SARIWANGI TEA</t>
+  </si>
+  <si>
+    <t>BEETROOT</t>
+  </si>
+  <si>
     <t>INV NO</t>
   </si>
   <si>
@@ -288,9 +297,6 @@
   </si>
   <si>
     <t>PINEAPPLE</t>
-  </si>
-  <si>
-    <t>GREEN APPLE</t>
   </si>
   <si>
     <t>STRAWBERRY</t>
@@ -1478,7 +1484,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="301">
+  <cellXfs count="309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2371,6 +2377,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="30" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="30" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3496,7 +3526,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H391"/>
+  <dimension ref="A1:H400"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="251" customWidth="1"/>
@@ -4940,7 +4970,7 @@
         <v>48000</v>
       </c>
       <c r="E82" s="7">
-        <f t="shared" ref="E82:E145" si="5">SUM(C82*D82)</f>
+        <f>SUM(C82*D82)</f>
         <v>96000</v>
       </c>
       <c r="F82" s="294"/>
@@ -4973,7 +5003,7 @@
         <v>20000</v>
       </c>
       <c r="E84" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C84*D84)</f>
         <v>6000</v>
       </c>
       <c r="F84" s="294"/>
@@ -4990,7 +5020,7 @@
         <v>30000</v>
       </c>
       <c r="E85" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C85*D85)</f>
         <v>15000</v>
       </c>
       <c r="F85" s="294"/>
@@ -5007,7 +5037,7 @@
         <v>80000</v>
       </c>
       <c r="E86" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C86*D86)</f>
         <v>40000</v>
       </c>
       <c r="F86" s="294"/>
@@ -5041,7 +5071,7 @@
         <v>15000</v>
       </c>
       <c r="E88" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C88*D88)</f>
         <v>15000</v>
       </c>
       <c r="F88" s="294"/>
@@ -5058,7 +5088,7 @@
         <v>24000</v>
       </c>
       <c r="E89" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C89*D89)</f>
         <v>48000</v>
       </c>
       <c r="F89" s="294"/>
@@ -5075,7 +5105,7 @@
         <v>40000</v>
       </c>
       <c r="E90" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C90*D90)</f>
         <v>40000</v>
       </c>
       <c r="F90" s="294"/>
@@ -5092,7 +5122,7 @@
         <v>49000</v>
       </c>
       <c r="E91" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C91*D91)</f>
         <v>49000</v>
       </c>
       <c r="F91" s="294"/>
@@ -5109,7 +5139,7 @@
         <v>20000</v>
       </c>
       <c r="E92" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C92*D92)</f>
         <v>80000</v>
       </c>
       <c r="F92" s="294"/>
@@ -5126,7 +5156,7 @@
         <v>20000</v>
       </c>
       <c r="E93" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C93*D93)</f>
         <v>80000</v>
       </c>
       <c r="F93" s="295"/>
@@ -5145,7 +5175,7 @@
         <v>10000</v>
       </c>
       <c r="E94" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C94*D94)</f>
         <v>80000</v>
       </c>
       <c r="F94" s="293">
@@ -5181,7 +5211,7 @@
         <v>38000</v>
       </c>
       <c r="E96" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C96*D96)</f>
         <v>76000</v>
       </c>
       <c r="F96" s="294"/>
@@ -5198,7 +5228,7 @@
         <v>20000</v>
       </c>
       <c r="E97" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C97*D97)</f>
         <v>40000</v>
       </c>
       <c r="F97" s="294"/>
@@ -5215,7 +5245,7 @@
         <v>24000</v>
       </c>
       <c r="E98" s="7">
-        <f t="shared" si="5"/>
+        <f>SUM(C98*D98)</f>
         <v>96000</v>
       </c>
       <c r="F98" s="294"/>
@@ -5232,258 +5262,391 @@
         <v>40000</v>
       </c>
       <c r="E99" s="7">
+        <f>SUM(C99*D99)</f>
+        <v>80000</v>
+      </c>
+      <c r="F99" s="295"/>
+    </row>
+    <row r="100" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
+      <c r="A100" s="298">
+        <v>46005</v>
+      </c>
+      <c r="B100" s="290" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" s="297">
+        <v>8</v>
+      </c>
+      <c r="D100" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E100" s="22">
+        <f t="shared" ref="E100:E108" si="5">SUM(C100*D100)</f>
+        <v>80000</v>
+      </c>
+      <c r="F100" s="301">
+        <f>SUM(E100:E108)</f>
+        <v>506000</v>
+      </c>
+    </row>
+    <row r="101" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
+      <c r="A101" s="298"/>
+      <c r="B101" s="290" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" s="297">
+        <v>8.23</v>
+      </c>
+      <c r="D101" s="7">
+        <v>15000</v>
+      </c>
+      <c r="E101" s="22">
+        <v>123000</v>
+      </c>
+      <c r="F101" s="302"/>
+    </row>
+    <row r="102" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
+      <c r="A102" s="298"/>
+      <c r="B102" s="290" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="297">
+        <v>2</v>
+      </c>
+      <c r="D102" s="7">
+        <v>20000</v>
+      </c>
+      <c r="E102" s="22">
         <f t="shared" si="5"/>
-        <v>80000</v>
-      </c>
-      <c r="F99" s="295"/>
-    </row>
-    <row r="100" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A100" s="291"/>
-      <c r="B100" s="290"/>
-      <c r="C100" s="297"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7">
+        <v>40000</v>
+      </c>
+      <c r="F102" s="302"/>
+    </row>
+    <row r="103" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
+      <c r="A103" s="298"/>
+      <c r="B103" s="290" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="297">
+        <v>0.3</v>
+      </c>
+      <c r="D103" s="7">
+        <v>20000</v>
+      </c>
+      <c r="E103" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F100" s="298"/>
-    </row>
-    <row r="101" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A101" s="291"/>
-      <c r="B101" s="290"/>
-      <c r="C101" s="297"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7">
+        <v>6000</v>
+      </c>
+      <c r="F103" s="302"/>
+    </row>
+    <row r="104" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
+      <c r="A104" s="298"/>
+      <c r="B104" s="290" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" s="297">
+        <v>1</v>
+      </c>
+      <c r="D104" s="7">
+        <v>15000</v>
+      </c>
+      <c r="E104" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F101" s="298"/>
-    </row>
-    <row r="102" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A102" s="291"/>
-      <c r="B102" s="290"/>
-      <c r="C102" s="297"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7">
+        <v>15000</v>
+      </c>
+      <c r="F104" s="302"/>
+    </row>
+    <row r="105" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
+      <c r="A105" s="298"/>
+      <c r="B105" s="290" t="s">
+        <v>36</v>
+      </c>
+      <c r="C105" s="297">
+        <v>1</v>
+      </c>
+      <c r="D105" s="7">
+        <v>48000</v>
+      </c>
+      <c r="E105" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F102" s="298"/>
-    </row>
-    <row r="103" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A103" s="291"/>
-      <c r="B103" s="290"/>
-      <c r="C103" s="297"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7">
+        <v>48000</v>
+      </c>
+      <c r="F105" s="302"/>
+    </row>
+    <row r="106" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
+      <c r="A106" s="298"/>
+      <c r="B106" s="290" t="s">
+        <v>14</v>
+      </c>
+      <c r="C106" s="297">
+        <v>5</v>
+      </c>
+      <c r="D106" s="7">
+        <v>24000</v>
+      </c>
+      <c r="E106" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F103" s="298"/>
-    </row>
-    <row r="104" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A104" s="291"/>
-      <c r="B104" s="290"/>
-      <c r="C104" s="297"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="7">
+        <v>120000</v>
+      </c>
+      <c r="F106" s="302"/>
+    </row>
+    <row r="107" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
+      <c r="A107" s="298"/>
+      <c r="B107" s="290" t="s">
+        <v>32</v>
+      </c>
+      <c r="C107" s="297">
+        <v>1</v>
+      </c>
+      <c r="D107" s="7">
+        <v>49000</v>
+      </c>
+      <c r="E107" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F104" s="298">
-        <f>SUM(E104:E118)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A105" s="291"/>
-      <c r="B105" s="290"/>
-      <c r="C105" s="297"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7">
+        <v>49000</v>
+      </c>
+      <c r="F107" s="302"/>
+    </row>
+    <row r="108" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
+      <c r="A108" s="298"/>
+      <c r="B108" s="290" t="s">
+        <v>37</v>
+      </c>
+      <c r="C108" s="297">
+        <v>1</v>
+      </c>
+      <c r="D108" s="7">
+        <v>25000</v>
+      </c>
+      <c r="E108" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F105" s="298"/>
-    </row>
-    <row r="106" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A106" s="291"/>
-      <c r="B106" s="290"/>
-      <c r="C106" s="297"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F106" s="298"/>
-    </row>
-    <row r="107" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A107" s="291"/>
-      <c r="B107" s="290"/>
-      <c r="C107" s="297"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F107" s="298"/>
-    </row>
-    <row r="108" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A108" s="291"/>
-      <c r="B108" s="290"/>
-      <c r="C108" s="297"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F108" s="298"/>
+        <v>25000</v>
+      </c>
+      <c r="F108" s="302"/>
     </row>
     <row r="109" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A109" s="291"/>
-      <c r="B109" s="290"/>
-      <c r="C109" s="297"/>
-      <c r="D109" s="7"/>
+      <c r="A109" s="299">
+        <v>46006</v>
+      </c>
+      <c r="B109" s="290" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" s="297">
+        <v>4</v>
+      </c>
+      <c r="D109" s="7">
+        <v>10000</v>
+      </c>
       <c r="E109" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F109" s="298"/>
+        <f t="shared" ref="E109:E154" si="6">SUM(C109*D109)</f>
+        <v>40000</v>
+      </c>
+      <c r="F109" s="303">
+        <f>SUM(E109:E121)</f>
+        <v>630000</v>
+      </c>
     </row>
     <row r="110" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A110" s="291"/>
-      <c r="B110" s="290"/>
-      <c r="C110" s="297"/>
-      <c r="D110" s="7"/>
+      <c r="A110" s="298"/>
+      <c r="B110" s="290" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" s="297">
+        <v>3.43</v>
+      </c>
+      <c r="D110" s="7">
+        <v>15000</v>
+      </c>
       <c r="E110" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F110" s="298"/>
+        <v>51000</v>
+      </c>
+      <c r="F110" s="304"/>
     </row>
     <row r="111" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A111" s="291"/>
-      <c r="B111" s="290"/>
-      <c r="C111" s="297"/>
-      <c r="D111" s="7"/>
+      <c r="A111" s="298"/>
+      <c r="B111" s="290" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="297">
+        <v>2</v>
+      </c>
+      <c r="D111" s="7">
+        <v>20000</v>
+      </c>
       <c r="E111" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F111" s="298"/>
+        <f t="shared" si="6"/>
+        <v>40000</v>
+      </c>
+      <c r="F111" s="304"/>
     </row>
     <row r="112" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A112" s="291"/>
-      <c r="B112" s="290"/>
-      <c r="C112" s="297"/>
-      <c r="D112" s="7"/>
+      <c r="A112" s="298"/>
+      <c r="B112" s="290" t="s">
+        <v>10</v>
+      </c>
+      <c r="C112" s="297">
+        <v>0.3</v>
+      </c>
+      <c r="D112" s="7">
+        <v>20000</v>
+      </c>
       <c r="E112" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F112" s="298"/>
+        <f t="shared" si="6"/>
+        <v>6000</v>
+      </c>
+      <c r="F112" s="304"/>
     </row>
     <row r="113" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A113" s="291"/>
-      <c r="B113" s="290"/>
-      <c r="C113" s="297"/>
-      <c r="D113" s="7"/>
+      <c r="A113" s="298"/>
+      <c r="B113" s="290" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="297">
+        <v>2</v>
+      </c>
+      <c r="D113" s="7">
+        <v>15000</v>
+      </c>
       <c r="E113" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F113" s="298"/>
+        <f t="shared" si="6"/>
+        <v>30000</v>
+      </c>
+      <c r="F113" s="304"/>
     </row>
     <row r="114" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A114" s="291"/>
-      <c r="B114" s="290"/>
-      <c r="C114" s="297"/>
-      <c r="D114" s="7"/>
+      <c r="A114" s="298"/>
+      <c r="B114" s="290" t="s">
+        <v>36</v>
+      </c>
+      <c r="C114" s="297">
+        <v>2</v>
+      </c>
+      <c r="D114" s="7">
+        <v>48000</v>
+      </c>
       <c r="E114" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F114" s="298"/>
+        <f t="shared" si="6"/>
+        <v>96000</v>
+      </c>
+      <c r="F114" s="304"/>
     </row>
     <row r="115" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A115" s="291"/>
-      <c r="B115" s="290"/>
-      <c r="C115" s="297"/>
-      <c r="D115" s="7"/>
+      <c r="A115" s="298"/>
+      <c r="B115" s="290" t="s">
+        <v>38</v>
+      </c>
+      <c r="C115" s="297">
+        <v>1</v>
+      </c>
+      <c r="D115" s="7">
+        <v>45000</v>
+      </c>
       <c r="E115" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F115" s="298"/>
+        <f t="shared" si="6"/>
+        <v>45000</v>
+      </c>
+      <c r="F115" s="304"/>
     </row>
     <row r="116" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A116" s="291"/>
-      <c r="B116" s="290"/>
-      <c r="C116" s="297"/>
-      <c r="D116" s="7"/>
+      <c r="A116" s="298"/>
+      <c r="B116" s="290" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" s="297">
+        <v>1.2</v>
+      </c>
+      <c r="D116" s="7">
+        <v>38000</v>
+      </c>
       <c r="E116" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F116" s="298"/>
+        <v>46000</v>
+      </c>
+      <c r="F116" s="304"/>
     </row>
     <row r="117" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A117" s="291"/>
-      <c r="B117" s="290"/>
-      <c r="C117" s="297"/>
-      <c r="D117" s="7"/>
+      <c r="A117" s="298"/>
+      <c r="B117" s="290" t="s">
+        <v>22</v>
+      </c>
+      <c r="C117" s="297">
+        <v>0.5</v>
+      </c>
+      <c r="D117" s="7">
+        <v>30000</v>
+      </c>
       <c r="E117" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F117" s="298"/>
+        <f t="shared" si="6"/>
+        <v>15000</v>
+      </c>
+      <c r="F117" s="304"/>
     </row>
     <row r="118" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A118" s="291"/>
-      <c r="B118" s="290"/>
-      <c r="C118" s="297"/>
-      <c r="D118" s="7"/>
+      <c r="A118" s="298"/>
+      <c r="B118" s="290" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" s="297">
+        <v>3</v>
+      </c>
+      <c r="D118" s="7">
+        <v>24000</v>
+      </c>
       <c r="E118" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F118" s="298"/>
+        <f t="shared" si="6"/>
+        <v>72000</v>
+      </c>
+      <c r="F118" s="304"/>
     </row>
     <row r="119" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A119" s="291"/>
-      <c r="B119" s="290"/>
-      <c r="C119" s="297"/>
-      <c r="D119" s="7"/>
+      <c r="A119" s="298"/>
+      <c r="B119" s="290" t="s">
+        <v>32</v>
+      </c>
+      <c r="C119" s="297">
+        <v>1</v>
+      </c>
+      <c r="D119" s="7">
+        <v>49000</v>
+      </c>
       <c r="E119" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F119" s="298">
-        <f>SUM(E119:E134)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="6"/>
+        <v>49000</v>
+      </c>
+      <c r="F119" s="304"/>
     </row>
     <row r="120" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A120" s="291"/>
-      <c r="B120" s="290"/>
-      <c r="C120" s="297"/>
-      <c r="D120" s="7"/>
+      <c r="A120" s="298"/>
+      <c r="B120" s="290" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" s="297">
+        <v>1</v>
+      </c>
+      <c r="D120" s="7">
+        <v>40000</v>
+      </c>
       <c r="E120" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F120" s="298"/>
+        <f t="shared" si="6"/>
+        <v>40000</v>
+      </c>
+      <c r="F120" s="304"/>
     </row>
     <row r="121" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A121" s="291"/>
-      <c r="B121" s="290"/>
-      <c r="C121" s="297"/>
-      <c r="D121" s="7"/>
+      <c r="A121" s="300"/>
+      <c r="B121" s="290" t="s">
+        <v>27</v>
+      </c>
+      <c r="C121" s="297">
+        <v>5</v>
+      </c>
+      <c r="D121" s="7">
+        <v>20000</v>
+      </c>
       <c r="E121" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F121" s="298"/>
+        <f t="shared" si="6"/>
+        <v>100000</v>
+      </c>
+      <c r="F121" s="305"/>
     </row>
     <row r="122" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A122" s="291"/>
@@ -5491,10 +5654,10 @@
       <c r="C122" s="297"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F122" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F122" s="306"/>
     </row>
     <row r="123" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A123" s="291"/>
@@ -5502,10 +5665,10 @@
       <c r="C123" s="297"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F123" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F123" s="306"/>
     </row>
     <row r="124" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A124" s="291"/>
@@ -5513,10 +5676,10 @@
       <c r="C124" s="297"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F124" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F124" s="306"/>
     </row>
     <row r="125" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A125" s="291"/>
@@ -5524,10 +5687,10 @@
       <c r="C125" s="297"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F125" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F125" s="306"/>
     </row>
     <row r="126" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A126" s="291"/>
@@ -5535,10 +5698,10 @@
       <c r="C126" s="297"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F126" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F126" s="306"/>
     </row>
     <row r="127" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A127" s="291"/>
@@ -5546,10 +5709,10 @@
       <c r="C127" s="297"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F127" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F127" s="306"/>
     </row>
     <row r="128" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A128" s="291"/>
@@ -5557,10 +5720,13 @@
       <c r="C128" s="297"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F128" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F128" s="306">
+        <f>SUM(E128:E143)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="129" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A129" s="291"/>
@@ -5568,10 +5734,10 @@
       <c r="C129" s="297"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F129" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F129" s="306"/>
     </row>
     <row r="130" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A130" s="291"/>
@@ -5579,10 +5745,10 @@
       <c r="C130" s="297"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F130" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F130" s="306"/>
     </row>
     <row r="131" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A131" s="291"/>
@@ -5590,10 +5756,10 @@
       <c r="C131" s="297"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F131" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F131" s="306"/>
     </row>
     <row r="132" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A132" s="291"/>
@@ -5601,10 +5767,10 @@
       <c r="C132" s="297"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F132" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F132" s="306"/>
     </row>
     <row r="133" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A133" s="291"/>
@@ -5612,10 +5778,10 @@
       <c r="C133" s="297"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F133" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F133" s="306"/>
     </row>
     <row r="134" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A134" s="291"/>
@@ -5623,10 +5789,10 @@
       <c r="C134" s="297"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F134" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F134" s="306"/>
     </row>
     <row r="135" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A135" s="291"/>
@@ -5634,130 +5800,127 @@
       <c r="C135" s="297"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F135" s="298">
-        <f>SUM(E135)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" s="249" customFormat="1" ht="14" customHeight="1" spans="1:7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F135" s="306"/>
+    </row>
+    <row r="136" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A136" s="291"/>
       <c r="B136" s="290"/>
       <c r="C136" s="297"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F136" s="298">
-        <f>SUM(E136:E140)</f>
-        <v>0</v>
-      </c>
-      <c r="G136" s="275"/>
-    </row>
-    <row r="137" s="249" customFormat="1" ht="17.6" spans="1:6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F136" s="306"/>
+    </row>
+    <row r="137" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A137" s="291"/>
       <c r="B137" s="290"/>
       <c r="C137" s="297"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F137" s="298"/>
-    </row>
-    <row r="138" s="249" customFormat="1" ht="17.6" spans="1:6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F137" s="306"/>
+    </row>
+    <row r="138" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A138" s="291"/>
       <c r="B138" s="290"/>
       <c r="C138" s="297"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F138" s="298"/>
-    </row>
-    <row r="139" s="249" customFormat="1" ht="17.6" spans="1:6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F138" s="306"/>
+    </row>
+    <row r="139" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A139" s="291"/>
       <c r="B139" s="290"/>
       <c r="C139" s="297"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F139" s="298"/>
-    </row>
-    <row r="140" s="249" customFormat="1" ht="17.6" spans="1:6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F139" s="306"/>
+    </row>
+    <row r="140" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A140" s="291"/>
       <c r="B140" s="290"/>
       <c r="C140" s="297"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F140" s="298"/>
-    </row>
-    <row r="141" s="249" customFormat="1" ht="17.6" spans="1:6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F140" s="306"/>
+    </row>
+    <row r="141" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A141" s="291"/>
-      <c r="B141" s="299"/>
-      <c r="C141" s="300"/>
-      <c r="D141" s="134"/>
+      <c r="B141" s="290"/>
+      <c r="C141" s="297"/>
+      <c r="D141" s="7"/>
       <c r="E141" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F141" s="298">
-        <f>SUM(E141:E147)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" s="249" customFormat="1" ht="17.6" spans="1:6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F141" s="306"/>
+    </row>
+    <row r="142" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A142" s="291"/>
       <c r="B142" s="290"/>
       <c r="C142" s="297"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F142" s="298"/>
-    </row>
-    <row r="143" s="249" customFormat="1" ht="17.6" spans="1:6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F142" s="306"/>
+    </row>
+    <row r="143" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A143" s="291"/>
       <c r="B143" s="290"/>
       <c r="C143" s="297"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F143" s="298"/>
-    </row>
-    <row r="144" s="249" customFormat="1" ht="17.6" spans="1:6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F143" s="306"/>
+    </row>
+    <row r="144" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
       <c r="A144" s="291"/>
       <c r="B144" s="290"/>
       <c r="C144" s="297"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F144" s="298"/>
-    </row>
-    <row r="145" s="249" customFormat="1" ht="17.6" spans="1:6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F144" s="306">
+        <f>SUM(E144)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" s="249" customFormat="1" ht="14" customHeight="1" spans="1:7">
       <c r="A145" s="291"/>
       <c r="B145" s="290"/>
       <c r="C145" s="297"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F145" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F145" s="306">
+        <f>SUM(E145:E149)</f>
+        <v>0</v>
+      </c>
+      <c r="G145" s="275"/>
     </row>
     <row r="146" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A146" s="291"/>
@@ -5765,21 +5928,21 @@
       <c r="C146" s="297"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7">
-        <f t="shared" ref="E146:E209" si="6">SUM(C146*D146)</f>
-        <v>0</v>
-      </c>
-      <c r="F146" s="298"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F146" s="306"/>
     </row>
     <row r="147" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A147" s="291"/>
       <c r="B147" s="290"/>
       <c r="C147" s="297"/>
-      <c r="D147" s="266"/>
+      <c r="D147" s="7"/>
       <c r="E147" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F147" s="298"/>
+      <c r="F147" s="306"/>
     </row>
     <row r="148" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A148" s="291"/>
@@ -5790,10 +5953,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F148" s="298">
-        <f>SUM(E148:E155)</f>
-        <v>0</v>
-      </c>
+      <c r="F148" s="306"/>
     </row>
     <row r="149" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A149" s="291"/>
@@ -5804,18 +5964,21 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F149" s="298"/>
+      <c r="F149" s="306"/>
     </row>
     <row r="150" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A150" s="291"/>
-      <c r="B150" s="290"/>
-      <c r="C150" s="297"/>
-      <c r="D150" s="7"/>
+      <c r="B150" s="307"/>
+      <c r="C150" s="308"/>
+      <c r="D150" s="134"/>
       <c r="E150" s="7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F150" s="298"/>
+      <c r="F150" s="306">
+        <f>SUM(E150:E156)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="151" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A151" s="291"/>
@@ -5826,7 +5989,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F151" s="298"/>
+      <c r="F151" s="306"/>
     </row>
     <row r="152" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A152" s="291"/>
@@ -5837,7 +6000,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F152" s="298"/>
+      <c r="F152" s="306"/>
     </row>
     <row r="153" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A153" s="291"/>
@@ -5848,7 +6011,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F153" s="298"/>
+      <c r="F153" s="306"/>
     </row>
     <row r="154" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A154" s="291"/>
@@ -5859,7 +6022,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F154" s="298"/>
+      <c r="F154" s="306"/>
     </row>
     <row r="155" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A155" s="291"/>
@@ -5867,24 +6030,21 @@
       <c r="C155" s="297"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F155" s="298"/>
+        <f t="shared" ref="E155:E218" si="7">SUM(C155*D155)</f>
+        <v>0</v>
+      </c>
+      <c r="F155" s="306"/>
     </row>
     <row r="156" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A156" s="291"/>
       <c r="B156" s="290"/>
       <c r="C156" s="297"/>
-      <c r="D156" s="7"/>
+      <c r="D156" s="266"/>
       <c r="E156" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F156" s="298">
-        <f>SUM(E156:E162)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F156" s="306"/>
     </row>
     <row r="157" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A157" s="291"/>
@@ -5892,10 +6052,13 @@
       <c r="C157" s="297"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F157" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F157" s="306">
+        <f>SUM(E157:E164)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="158" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A158" s="291"/>
@@ -5903,10 +6066,10 @@
       <c r="C158" s="297"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F158" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F158" s="306"/>
     </row>
     <row r="159" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A159" s="291"/>
@@ -5914,10 +6077,10 @@
       <c r="C159" s="297"/>
       <c r="D159" s="7"/>
       <c r="E159" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F159" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F159" s="306"/>
     </row>
     <row r="160" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A160" s="291"/>
@@ -5925,10 +6088,10 @@
       <c r="C160" s="297"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F160" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F160" s="306"/>
     </row>
     <row r="161" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A161" s="291"/>
@@ -5936,10 +6099,10 @@
       <c r="C161" s="297"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F161" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F161" s="306"/>
     </row>
     <row r="162" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A162" s="291"/>
@@ -5947,10 +6110,10 @@
       <c r="C162" s="297"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F162" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F162" s="306"/>
     </row>
     <row r="163" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A163" s="291"/>
@@ -5958,13 +6121,10 @@
       <c r="C163" s="297"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F163" s="298">
-        <f>SUM(E163:E172)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F163" s="306"/>
     </row>
     <row r="164" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A164" s="291"/>
@@ -5972,10 +6132,10 @@
       <c r="C164" s="297"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F164" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F164" s="306"/>
     </row>
     <row r="165" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A165" s="291"/>
@@ -5983,10 +6143,13 @@
       <c r="C165" s="297"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F165" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F165" s="306">
+        <f>SUM(E165:E171)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="166" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A166" s="291"/>
@@ -5994,10 +6157,10 @@
       <c r="C166" s="297"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F166" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F166" s="306"/>
     </row>
     <row r="167" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A167" s="291"/>
@@ -6005,10 +6168,10 @@
       <c r="C167" s="297"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F167" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F167" s="306"/>
     </row>
     <row r="168" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A168" s="291"/>
@@ -6016,10 +6179,10 @@
       <c r="C168" s="297"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F168" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F168" s="306"/>
     </row>
     <row r="169" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A169" s="291"/>
@@ -6027,10 +6190,10 @@
       <c r="C169" s="297"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F169" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F169" s="306"/>
     </row>
     <row r="170" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A170" s="291"/>
@@ -6038,10 +6201,10 @@
       <c r="C170" s="297"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F170" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F170" s="306"/>
     </row>
     <row r="171" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A171" s="291"/>
@@ -6049,10 +6212,10 @@
       <c r="C171" s="297"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F171" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F171" s="306"/>
     </row>
     <row r="172" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A172" s="291"/>
@@ -6060,10 +6223,13 @@
       <c r="C172" s="297"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F172" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F172" s="306">
+        <f>SUM(E172:E181)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="173" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A173" s="291"/>
@@ -6071,13 +6237,10 @@
       <c r="C173" s="297"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F173" s="298">
-        <f>SUM(E173:E186)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F173" s="306"/>
     </row>
     <row r="174" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A174" s="291"/>
@@ -6085,10 +6248,10 @@
       <c r="C174" s="297"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F174" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F174" s="306"/>
     </row>
     <row r="175" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A175" s="291"/>
@@ -6096,10 +6259,10 @@
       <c r="C175" s="297"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F175" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F175" s="306"/>
     </row>
     <row r="176" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A176" s="291"/>
@@ -6107,10 +6270,10 @@
       <c r="C176" s="297"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F176" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F176" s="306"/>
     </row>
     <row r="177" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A177" s="291"/>
@@ -6118,10 +6281,10 @@
       <c r="C177" s="297"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F177" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F177" s="306"/>
     </row>
     <row r="178" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A178" s="291"/>
@@ -6129,10 +6292,10 @@
       <c r="C178" s="297"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F178" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F178" s="306"/>
     </row>
     <row r="179" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A179" s="291"/>
@@ -6140,10 +6303,10 @@
       <c r="C179" s="297"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F179" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F179" s="306"/>
     </row>
     <row r="180" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A180" s="291"/>
@@ -6151,10 +6314,10 @@
       <c r="C180" s="297"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F180" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F180" s="306"/>
     </row>
     <row r="181" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A181" s="291"/>
@@ -6162,10 +6325,10 @@
       <c r="C181" s="297"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F181" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F181" s="306"/>
     </row>
     <row r="182" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A182" s="291"/>
@@ -6173,10 +6336,13 @@
       <c r="C182" s="297"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F182" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F182" s="306">
+        <f>SUM(E182:E195)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="183" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A183" s="291"/>
@@ -6184,10 +6350,10 @@
       <c r="C183" s="297"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F183" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F183" s="306"/>
     </row>
     <row r="184" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A184" s="291"/>
@@ -6195,10 +6361,10 @@
       <c r="C184" s="297"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F184" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F184" s="306"/>
     </row>
     <row r="185" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A185" s="291"/>
@@ -6206,10 +6372,10 @@
       <c r="C185" s="297"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F185" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F185" s="306"/>
     </row>
     <row r="186" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A186" s="291"/>
@@ -6217,10 +6383,10 @@
       <c r="C186" s="297"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F186" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F186" s="306"/>
     </row>
     <row r="187" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A187" s="291"/>
@@ -6228,13 +6394,10 @@
       <c r="C187" s="297"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F187" s="298">
-        <f>SUM(E187)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F187" s="306"/>
     </row>
     <row r="188" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A188" s="291"/>
@@ -6242,13 +6405,10 @@
       <c r="C188" s="297"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F188" s="298">
-        <f>SUM(E188:E203)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F188" s="306"/>
     </row>
     <row r="189" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A189" s="291"/>
@@ -6256,10 +6416,10 @@
       <c r="C189" s="297"/>
       <c r="D189" s="7"/>
       <c r="E189" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F189" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F189" s="306"/>
     </row>
     <row r="190" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A190" s="291"/>
@@ -6267,10 +6427,10 @@
       <c r="C190" s="297"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F190" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F190" s="306"/>
     </row>
     <row r="191" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A191" s="291"/>
@@ -6278,10 +6438,10 @@
       <c r="C191" s="297"/>
       <c r="D191" s="7"/>
       <c r="E191" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F191" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F191" s="306"/>
     </row>
     <row r="192" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A192" s="291"/>
@@ -6289,10 +6449,10 @@
       <c r="C192" s="297"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F192" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F192" s="306"/>
     </row>
     <row r="193" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A193" s="291"/>
@@ -6300,10 +6460,10 @@
       <c r="C193" s="297"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F193" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F193" s="306"/>
     </row>
     <row r="194" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A194" s="291"/>
@@ -6311,10 +6471,10 @@
       <c r="C194" s="297"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F194" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F194" s="306"/>
     </row>
     <row r="195" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A195" s="291"/>
@@ -6322,10 +6482,10 @@
       <c r="C195" s="297"/>
       <c r="D195" s="7"/>
       <c r="E195" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F195" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F195" s="306"/>
     </row>
     <row r="196" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A196" s="291"/>
@@ -6333,10 +6493,13 @@
       <c r="C196" s="297"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F196" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F196" s="306">
+        <f>SUM(E196)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="197" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A197" s="291"/>
@@ -6344,10 +6507,13 @@
       <c r="C197" s="297"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F197" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F197" s="306">
+        <f>SUM(E197:E212)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="198" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A198" s="291"/>
@@ -6355,10 +6521,10 @@
       <c r="C198" s="297"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F198" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F198" s="306"/>
     </row>
     <row r="199" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A199" s="291"/>
@@ -6366,10 +6532,10 @@
       <c r="C199" s="297"/>
       <c r="D199" s="7"/>
       <c r="E199" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F199" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F199" s="306"/>
     </row>
     <row r="200" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A200" s="291"/>
@@ -6377,10 +6543,10 @@
       <c r="C200" s="297"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F200" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F200" s="306"/>
     </row>
     <row r="201" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A201" s="291"/>
@@ -6388,21 +6554,21 @@
       <c r="C201" s="297"/>
       <c r="D201" s="7"/>
       <c r="E201" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F201" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F201" s="306"/>
     </row>
     <row r="202" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A202" s="291"/>
-      <c r="B202" s="299"/>
-      <c r="C202" s="300"/>
-      <c r="D202" s="134"/>
+      <c r="B202" s="290"/>
+      <c r="C202" s="297"/>
+      <c r="D202" s="7"/>
       <c r="E202" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F202" s="298"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F202" s="306"/>
     </row>
     <row r="203" s="249" customFormat="1" ht="17.6" spans="1:6">
       <c r="A203" s="291"/>
@@ -6410,104 +6576,101 @@
       <c r="C203" s="297"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F203" s="298"/>
-    </row>
-    <row r="204" s="249" customFormat="1" spans="1:6">
-      <c r="A204" s="283"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F203" s="306"/>
+    </row>
+    <row r="204" s="249" customFormat="1" ht="17.6" spans="1:6">
+      <c r="A204" s="291"/>
       <c r="B204" s="290"/>
       <c r="C204" s="297"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F204" s="293">
-        <f>SUM(E204:E211)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" s="249" customFormat="1" spans="1:6">
-      <c r="A205" s="286"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F204" s="306"/>
+    </row>
+    <row r="205" s="249" customFormat="1" ht="17.6" spans="1:6">
+      <c r="A205" s="291"/>
       <c r="B205" s="290"/>
       <c r="C205" s="297"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F205" s="294"/>
-    </row>
-    <row r="206" s="249" customFormat="1" spans="1:6">
-      <c r="A206" s="286"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F205" s="306"/>
+    </row>
+    <row r="206" s="249" customFormat="1" ht="17.6" spans="1:6">
+      <c r="A206" s="291"/>
       <c r="B206" s="290"/>
       <c r="C206" s="297"/>
       <c r="D206" s="7"/>
       <c r="E206" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F206" s="294"/>
-    </row>
-    <row r="207" s="249" customFormat="1" spans="1:6">
-      <c r="A207" s="286"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F206" s="306"/>
+    </row>
+    <row r="207" s="249" customFormat="1" ht="17.6" spans="1:6">
+      <c r="A207" s="291"/>
       <c r="B207" s="290"/>
       <c r="C207" s="297"/>
       <c r="D207" s="7"/>
       <c r="E207" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F207" s="294"/>
-    </row>
-    <row r="208" s="249" customFormat="1" spans="1:6">
-      <c r="A208" s="286"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F207" s="306"/>
+    </row>
+    <row r="208" s="249" customFormat="1" ht="17.6" spans="1:6">
+      <c r="A208" s="291"/>
       <c r="B208" s="290"/>
       <c r="C208" s="297"/>
       <c r="D208" s="7"/>
       <c r="E208" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F208" s="294"/>
-    </row>
-    <row r="209" s="249" customFormat="1" spans="1:6">
-      <c r="A209" s="286"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F208" s="306"/>
+    </row>
+    <row r="209" s="249" customFormat="1" ht="17.6" spans="1:6">
+      <c r="A209" s="291"/>
       <c r="B209" s="290"/>
       <c r="C209" s="297"/>
       <c r="D209" s="7"/>
       <c r="E209" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F209" s="294"/>
-    </row>
-    <row r="210" s="249" customFormat="1" spans="1:6">
-      <c r="A210" s="286"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F209" s="306"/>
+    </row>
+    <row r="210" s="249" customFormat="1" ht="17.6" spans="1:6">
+      <c r="A210" s="291"/>
       <c r="B210" s="290"/>
       <c r="C210" s="297"/>
       <c r="D210" s="7"/>
       <c r="E210" s="7">
-        <f t="shared" ref="E210:E273" si="7">SUM(C210*D210)</f>
-        <v>0</v>
-      </c>
-      <c r="F210" s="294"/>
-    </row>
-    <row r="211" s="249" customFormat="1" spans="1:6">
-      <c r="A211" s="287"/>
-      <c r="B211" s="290"/>
-      <c r="C211" s="297"/>
-      <c r="D211" s="7"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F210" s="306"/>
+    </row>
+    <row r="211" s="249" customFormat="1" ht="17.6" spans="1:6">
+      <c r="A211" s="291"/>
+      <c r="B211" s="307"/>
+      <c r="C211" s="308"/>
+      <c r="D211" s="134"/>
       <c r="E211" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F211" s="295"/>
-    </row>
-    <row r="212" s="249" customFormat="1" spans="1:6">
-      <c r="A212" s="283"/>
+      <c r="F211" s="306"/>
+    </row>
+    <row r="212" s="249" customFormat="1" ht="17.6" spans="1:6">
+      <c r="A212" s="291"/>
       <c r="B212" s="290"/>
       <c r="C212" s="297"/>
       <c r="D212" s="7"/>
@@ -6515,13 +6678,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F212" s="293">
-        <f>SUM(E212:E223)</f>
-        <v>0</v>
-      </c>
+      <c r="F212" s="306"/>
     </row>
     <row r="213" s="249" customFormat="1" spans="1:6">
-      <c r="A213" s="286"/>
+      <c r="A213" s="283"/>
       <c r="B213" s="290"/>
       <c r="C213" s="297"/>
       <c r="D213" s="7"/>
@@ -6529,7 +6689,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F213" s="294"/>
+      <c r="F213" s="293">
+        <f>SUM(E213:E220)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="214" s="249" customFormat="1" spans="1:6">
       <c r="A214" s="286"/>
@@ -6592,32 +6755,35 @@
       <c r="C219" s="297"/>
       <c r="D219" s="7"/>
       <c r="E219" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="E219:E282" si="8">SUM(C219*D219)</f>
         <v>0</v>
       </c>
       <c r="F219" s="294"/>
     </row>
     <row r="220" s="249" customFormat="1" spans="1:6">
-      <c r="A220" s="286"/>
+      <c r="A220" s="287"/>
       <c r="B220" s="290"/>
       <c r="C220" s="297"/>
       <c r="D220" s="7"/>
       <c r="E220" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F220" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F220" s="295"/>
     </row>
     <row r="221" s="249" customFormat="1" spans="1:6">
-      <c r="A221" s="286"/>
+      <c r="A221" s="283"/>
       <c r="B221" s="290"/>
       <c r="C221" s="297"/>
       <c r="D221" s="7"/>
       <c r="E221" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F221" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F221" s="293">
+        <f>SUM(E221:E232)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="222" s="249" customFormat="1" spans="1:6">
       <c r="A222" s="286"/>
@@ -6625,35 +6791,32 @@
       <c r="C222" s="297"/>
       <c r="D222" s="7"/>
       <c r="E222" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F222" s="294"/>
     </row>
     <row r="223" s="249" customFormat="1" spans="1:6">
-      <c r="A223" s="287"/>
+      <c r="A223" s="286"/>
       <c r="B223" s="290"/>
       <c r="C223" s="297"/>
       <c r="D223" s="7"/>
       <c r="E223" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F223" s="295"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F223" s="294"/>
     </row>
     <row r="224" s="249" customFormat="1" spans="1:6">
-      <c r="A224" s="283"/>
+      <c r="A224" s="286"/>
       <c r="B224" s="290"/>
       <c r="C224" s="297"/>
       <c r="D224" s="7"/>
       <c r="E224" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F224" s="293">
-        <f>SUM(E224:E232)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F224" s="294"/>
     </row>
     <row r="225" s="249" customFormat="1" spans="1:6">
       <c r="A225" s="286"/>
@@ -6661,7 +6824,7 @@
       <c r="C225" s="297"/>
       <c r="D225" s="7"/>
       <c r="E225" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F225" s="294"/>
@@ -6672,7 +6835,7 @@
       <c r="C226" s="297"/>
       <c r="D226" s="7"/>
       <c r="E226" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F226" s="294"/>
@@ -6683,7 +6846,7 @@
       <c r="C227" s="297"/>
       <c r="D227" s="7"/>
       <c r="E227" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F227" s="294"/>
@@ -6694,7 +6857,7 @@
       <c r="C228" s="297"/>
       <c r="D228" s="7"/>
       <c r="E228" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F228" s="294"/>
@@ -6705,7 +6868,7 @@
       <c r="C229" s="297"/>
       <c r="D229" s="7"/>
       <c r="E229" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F229" s="294"/>
@@ -6716,7 +6879,7 @@
       <c r="C230" s="297"/>
       <c r="D230" s="7"/>
       <c r="E230" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F230" s="294"/>
@@ -6727,7 +6890,7 @@
       <c r="C231" s="297"/>
       <c r="D231" s="7"/>
       <c r="E231" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F231" s="294"/>
@@ -6738,7 +6901,7 @@
       <c r="C232" s="297"/>
       <c r="D232" s="7"/>
       <c r="E232" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F232" s="295"/>
@@ -6749,11 +6912,11 @@
       <c r="C233" s="297"/>
       <c r="D233" s="7"/>
       <c r="E233" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F233" s="293">
-        <f>SUM(E233:E243)</f>
+        <f>SUM(E233:E241)</f>
         <v>0</v>
       </c>
     </row>
@@ -6763,7 +6926,7 @@
       <c r="C234" s="297"/>
       <c r="D234" s="7"/>
       <c r="E234" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F234" s="294"/>
@@ -6774,7 +6937,7 @@
       <c r="C235" s="297"/>
       <c r="D235" s="7"/>
       <c r="E235" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F235" s="294"/>
@@ -6785,7 +6948,7 @@
       <c r="C236" s="297"/>
       <c r="D236" s="7"/>
       <c r="E236" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F236" s="294"/>
@@ -6796,7 +6959,7 @@
       <c r="C237" s="297"/>
       <c r="D237" s="7"/>
       <c r="E237" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F237" s="294"/>
@@ -6807,7 +6970,7 @@
       <c r="C238" s="297"/>
       <c r="D238" s="7"/>
       <c r="E238" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F238" s="294"/>
@@ -6818,7 +6981,7 @@
       <c r="C239" s="297"/>
       <c r="D239" s="7"/>
       <c r="E239" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F239" s="294"/>
@@ -6829,57 +6992,57 @@
       <c r="C240" s="297"/>
       <c r="D240" s="7"/>
       <c r="E240" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F240" s="294"/>
     </row>
     <row r="241" s="249" customFormat="1" spans="1:6">
-      <c r="A241" s="286"/>
+      <c r="A241" s="287"/>
       <c r="B241" s="290"/>
       <c r="C241" s="297"/>
       <c r="D241" s="7"/>
       <c r="E241" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F241" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F241" s="295"/>
     </row>
     <row r="242" s="249" customFormat="1" spans="1:6">
-      <c r="A242" s="286"/>
+      <c r="A242" s="283"/>
       <c r="B242" s="290"/>
       <c r="C242" s="297"/>
       <c r="D242" s="7"/>
       <c r="E242" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F242" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F242" s="293">
+        <f>SUM(E242:E252)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="243" s="249" customFormat="1" spans="1:6">
-      <c r="A243" s="287"/>
+      <c r="A243" s="286"/>
       <c r="B243" s="290"/>
       <c r="C243" s="297"/>
       <c r="D243" s="7"/>
       <c r="E243" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F243" s="295"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F243" s="294"/>
     </row>
     <row r="244" s="249" customFormat="1" spans="1:6">
-      <c r="A244" s="283"/>
+      <c r="A244" s="286"/>
       <c r="B244" s="290"/>
       <c r="C244" s="297"/>
       <c r="D244" s="7"/>
       <c r="E244" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F244" s="293">
-        <f>SUM(E244:E254)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F244" s="294"/>
     </row>
     <row r="245" s="249" customFormat="1" spans="1:6">
       <c r="A245" s="286"/>
@@ -6887,7 +7050,7 @@
       <c r="C245" s="297"/>
       <c r="D245" s="7"/>
       <c r="E245" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F245" s="294"/>
@@ -6898,7 +7061,7 @@
       <c r="C246" s="297"/>
       <c r="D246" s="7"/>
       <c r="E246" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F246" s="294"/>
@@ -6909,7 +7072,7 @@
       <c r="C247" s="297"/>
       <c r="D247" s="7"/>
       <c r="E247" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F247" s="294"/>
@@ -6920,7 +7083,7 @@
       <c r="C248" s="297"/>
       <c r="D248" s="7"/>
       <c r="E248" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F248" s="294"/>
@@ -6931,7 +7094,7 @@
       <c r="C249" s="297"/>
       <c r="D249" s="7"/>
       <c r="E249" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F249" s="294"/>
@@ -6942,7 +7105,7 @@
       <c r="C250" s="297"/>
       <c r="D250" s="7"/>
       <c r="E250" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F250" s="294"/>
@@ -6953,57 +7116,57 @@
       <c r="C251" s="297"/>
       <c r="D251" s="7"/>
       <c r="E251" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F251" s="294"/>
     </row>
     <row r="252" s="249" customFormat="1" spans="1:6">
-      <c r="A252" s="286"/>
+      <c r="A252" s="287"/>
       <c r="B252" s="290"/>
       <c r="C252" s="297"/>
       <c r="D252" s="7"/>
       <c r="E252" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F252" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F252" s="295"/>
     </row>
     <row r="253" s="249" customFormat="1" spans="1:6">
-      <c r="A253" s="286"/>
+      <c r="A253" s="283"/>
       <c r="B253" s="290"/>
       <c r="C253" s="297"/>
       <c r="D253" s="7"/>
       <c r="E253" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F253" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F253" s="293">
+        <f>SUM(E253:E263)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="254" s="249" customFormat="1" spans="1:6">
-      <c r="A254" s="287"/>
+      <c r="A254" s="286"/>
       <c r="B254" s="290"/>
       <c r="C254" s="297"/>
       <c r="D254" s="7"/>
       <c r="E254" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F254" s="295"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F254" s="294"/>
     </row>
     <row r="255" s="249" customFormat="1" spans="1:6">
-      <c r="A255" s="283"/>
+      <c r="A255" s="286"/>
       <c r="B255" s="290"/>
       <c r="C255" s="297"/>
       <c r="D255" s="7"/>
       <c r="E255" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F255" s="293">
-        <f>SUM(E255:E265)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F255" s="294"/>
     </row>
     <row r="256" s="249" customFormat="1" spans="1:6">
       <c r="A256" s="286"/>
@@ -7011,7 +7174,7 @@
       <c r="C256" s="297"/>
       <c r="D256" s="7"/>
       <c r="E256" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F256" s="294"/>
@@ -7022,7 +7185,7 @@
       <c r="C257" s="297"/>
       <c r="D257" s="7"/>
       <c r="E257" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F257" s="294"/>
@@ -7033,7 +7196,7 @@
       <c r="C258" s="297"/>
       <c r="D258" s="7"/>
       <c r="E258" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F258" s="294"/>
@@ -7044,7 +7207,7 @@
       <c r="C259" s="297"/>
       <c r="D259" s="7"/>
       <c r="E259" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F259" s="294"/>
@@ -7055,7 +7218,7 @@
       <c r="C260" s="297"/>
       <c r="D260" s="7"/>
       <c r="E260" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F260" s="294"/>
@@ -7066,7 +7229,7 @@
       <c r="C261" s="297"/>
       <c r="D261" s="7"/>
       <c r="E261" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F261" s="294"/>
@@ -7077,57 +7240,57 @@
       <c r="C262" s="297"/>
       <c r="D262" s="7"/>
       <c r="E262" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F262" s="294"/>
     </row>
     <row r="263" s="249" customFormat="1" spans="1:6">
-      <c r="A263" s="286"/>
+      <c r="A263" s="287"/>
       <c r="B263" s="290"/>
       <c r="C263" s="297"/>
       <c r="D263" s="7"/>
       <c r="E263" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F263" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F263" s="295"/>
     </row>
     <row r="264" s="249" customFormat="1" spans="1:6">
-      <c r="A264" s="286"/>
+      <c r="A264" s="283"/>
       <c r="B264" s="290"/>
       <c r="C264" s="297"/>
       <c r="D264" s="7"/>
       <c r="E264" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F264" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F264" s="293">
+        <f>SUM(E264:E274)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="265" s="249" customFormat="1" spans="1:6">
-      <c r="A265" s="287"/>
+      <c r="A265" s="286"/>
       <c r="B265" s="290"/>
       <c r="C265" s="297"/>
       <c r="D265" s="7"/>
       <c r="E265" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F265" s="295"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F265" s="294"/>
     </row>
     <row r="266" s="249" customFormat="1" spans="1:6">
-      <c r="A266" s="283"/>
+      <c r="A266" s="286"/>
       <c r="B266" s="290"/>
       <c r="C266" s="297"/>
       <c r="D266" s="7"/>
       <c r="E266" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F266" s="293">
-        <f>SUM(E266:E275)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F266" s="294"/>
     </row>
     <row r="267" s="249" customFormat="1" spans="1:6">
       <c r="A267" s="286"/>
@@ -7135,7 +7298,7 @@
       <c r="C267" s="297"/>
       <c r="D267" s="7"/>
       <c r="E267" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F267" s="294"/>
@@ -7146,7 +7309,7 @@
       <c r="C268" s="297"/>
       <c r="D268" s="7"/>
       <c r="E268" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F268" s="294"/>
@@ -7157,7 +7320,7 @@
       <c r="C269" s="297"/>
       <c r="D269" s="7"/>
       <c r="E269" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F269" s="294"/>
@@ -7168,7 +7331,7 @@
       <c r="C270" s="297"/>
       <c r="D270" s="7"/>
       <c r="E270" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F270" s="294"/>
@@ -7179,7 +7342,7 @@
       <c r="C271" s="297"/>
       <c r="D271" s="7"/>
       <c r="E271" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F271" s="294"/>
@@ -7190,7 +7353,7 @@
       <c r="C272" s="297"/>
       <c r="D272" s="7"/>
       <c r="E272" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F272" s="294"/>
@@ -7201,24 +7364,24 @@
       <c r="C273" s="297"/>
       <c r="D273" s="7"/>
       <c r="E273" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F273" s="294"/>
     </row>
     <row r="274" s="249" customFormat="1" spans="1:6">
-      <c r="A274" s="286"/>
+      <c r="A274" s="287"/>
       <c r="B274" s="290"/>
       <c r="C274" s="297"/>
       <c r="D274" s="7"/>
       <c r="E274" s="7">
-        <f t="shared" ref="E274:E287" si="8">SUM(C274*D274)</f>
-        <v>0</v>
-      </c>
-      <c r="F274" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F274" s="295"/>
     </row>
     <row r="275" s="249" customFormat="1" spans="1:6">
-      <c r="A275" s="287"/>
+      <c r="A275" s="283"/>
       <c r="B275" s="290"/>
       <c r="C275" s="297"/>
       <c r="D275" s="7"/>
@@ -7226,10 +7389,13 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F275" s="295"/>
-    </row>
-    <row r="276" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A276" s="291"/>
+      <c r="F275" s="293">
+        <f>SUM(E275:E284)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" s="249" customFormat="1" spans="1:6">
+      <c r="A276" s="286"/>
       <c r="B276" s="290"/>
       <c r="C276" s="297"/>
       <c r="D276" s="7"/>
@@ -7237,13 +7403,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F276" s="298">
-        <f>SUM(E276)</f>
-        <v>0</v>
-      </c>
+      <c r="F276" s="294"/>
     </row>
     <row r="277" s="249" customFormat="1" spans="1:6">
-      <c r="A277" s="283"/>
+      <c r="A277" s="286"/>
       <c r="B277" s="290"/>
       <c r="C277" s="297"/>
       <c r="D277" s="7"/>
@@ -7251,10 +7414,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F277" s="293">
-        <f>SUM(E277:E287)</f>
-        <v>0</v>
-      </c>
+      <c r="F277" s="294"/>
     </row>
     <row r="278" s="249" customFormat="1" spans="1:6">
       <c r="A278" s="286"/>
@@ -7317,99 +7477,168 @@
       <c r="C283" s="297"/>
       <c r="D283" s="7"/>
       <c r="E283" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="E283:E296" si="9">SUM(C283*D283)</f>
         <v>0</v>
       </c>
       <c r="F283" s="294"/>
     </row>
     <row r="284" s="249" customFormat="1" spans="1:6">
-      <c r="A284" s="286"/>
+      <c r="A284" s="287"/>
       <c r="B284" s="290"/>
       <c r="C284" s="297"/>
       <c r="D284" s="7"/>
       <c r="E284" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F284" s="294"/>
-    </row>
-    <row r="285" s="249" customFormat="1" spans="1:6">
-      <c r="A285" s="286"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F284" s="295"/>
+    </row>
+    <row r="285" s="249" customFormat="1" ht="17.6" spans="1:6">
+      <c r="A285" s="291"/>
       <c r="B285" s="290"/>
       <c r="C285" s="297"/>
       <c r="D285" s="7"/>
       <c r="E285" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F285" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F285" s="306">
+        <f>SUM(E285)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="286" s="249" customFormat="1" spans="1:6">
-      <c r="A286" s="286"/>
+      <c r="A286" s="283"/>
       <c r="B286" s="290"/>
       <c r="C286" s="297"/>
       <c r="D286" s="7"/>
       <c r="E286" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F286" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F286" s="293">
+        <f>SUM(E286:E296)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="287" s="249" customFormat="1" spans="1:6">
-      <c r="A287" s="287"/>
+      <c r="A287" s="286"/>
       <c r="B287" s="290"/>
       <c r="C287" s="297"/>
       <c r="D287" s="7"/>
       <c r="E287" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F287" s="295"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F287" s="294"/>
     </row>
     <row r="288" s="249" customFormat="1" spans="1:6">
-      <c r="A288" s="251"/>
-      <c r="C288" s="250"/>
-      <c r="E288" s="7"/>
-      <c r="F288" s="298">
-        <f>SUM(F2:F287)</f>
-        <v>3916000</v>
-      </c>
-    </row>
-    <row r="289" s="249" customFormat="1" spans="1:3">
-      <c r="A289" s="251"/>
-      <c r="C289" s="250"/>
-    </row>
-    <row r="290" s="249" customFormat="1" spans="1:3">
-      <c r="A290" s="251"/>
-      <c r="C290" s="250"/>
-    </row>
-    <row r="291" s="249" customFormat="1" spans="1:3">
-      <c r="A291" s="251"/>
-      <c r="C291" s="250"/>
-    </row>
-    <row r="292" s="249" customFormat="1" spans="1:3">
-      <c r="A292" s="251"/>
-      <c r="C292" s="250"/>
-    </row>
-    <row r="293" s="249" customFormat="1" spans="1:3">
-      <c r="A293" s="251"/>
-      <c r="C293" s="250"/>
-    </row>
-    <row r="294" s="249" customFormat="1" spans="1:3">
-      <c r="A294" s="251"/>
-      <c r="C294" s="250"/>
-    </row>
-    <row r="295" s="249" customFormat="1" spans="1:3">
-      <c r="A295" s="251"/>
-      <c r="C295" s="250"/>
-    </row>
-    <row r="296" s="249" customFormat="1" spans="1:3">
-      <c r="A296" s="251"/>
-      <c r="C296" s="250"/>
-    </row>
-    <row r="297" s="249" customFormat="1" spans="1:3">
+      <c r="A288" s="286"/>
+      <c r="B288" s="290"/>
+      <c r="C288" s="297"/>
+      <c r="D288" s="7"/>
+      <c r="E288" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F288" s="294"/>
+    </row>
+    <row r="289" s="249" customFormat="1" spans="1:6">
+      <c r="A289" s="286"/>
+      <c r="B289" s="290"/>
+      <c r="C289" s="297"/>
+      <c r="D289" s="7"/>
+      <c r="E289" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F289" s="294"/>
+    </row>
+    <row r="290" s="249" customFormat="1" spans="1:6">
+      <c r="A290" s="286"/>
+      <c r="B290" s="290"/>
+      <c r="C290" s="297"/>
+      <c r="D290" s="7"/>
+      <c r="E290" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F290" s="294"/>
+    </row>
+    <row r="291" s="249" customFormat="1" spans="1:6">
+      <c r="A291" s="286"/>
+      <c r="B291" s="290"/>
+      <c r="C291" s="297"/>
+      <c r="D291" s="7"/>
+      <c r="E291" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F291" s="294"/>
+    </row>
+    <row r="292" s="249" customFormat="1" spans="1:6">
+      <c r="A292" s="286"/>
+      <c r="B292" s="290"/>
+      <c r="C292" s="297"/>
+      <c r="D292" s="7"/>
+      <c r="E292" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F292" s="294"/>
+    </row>
+    <row r="293" s="249" customFormat="1" spans="1:6">
+      <c r="A293" s="286"/>
+      <c r="B293" s="290"/>
+      <c r="C293" s="297"/>
+      <c r="D293" s="7"/>
+      <c r="E293" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F293" s="294"/>
+    </row>
+    <row r="294" s="249" customFormat="1" spans="1:6">
+      <c r="A294" s="286"/>
+      <c r="B294" s="290"/>
+      <c r="C294" s="297"/>
+      <c r="D294" s="7"/>
+      <c r="E294" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F294" s="294"/>
+    </row>
+    <row r="295" s="249" customFormat="1" spans="1:6">
+      <c r="A295" s="286"/>
+      <c r="B295" s="290"/>
+      <c r="C295" s="297"/>
+      <c r="D295" s="7"/>
+      <c r="E295" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F295" s="294"/>
+    </row>
+    <row r="296" s="249" customFormat="1" spans="1:6">
+      <c r="A296" s="287"/>
+      <c r="B296" s="290"/>
+      <c r="C296" s="297"/>
+      <c r="D296" s="7"/>
+      <c r="E296" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F296" s="295"/>
+    </row>
+    <row r="297" s="249" customFormat="1" spans="1:6">
       <c r="A297" s="251"/>
       <c r="C297" s="250"/>
+      <c r="E297" s="7"/>
+      <c r="F297" s="306">
+        <f>SUM(F2:F296)</f>
+        <v>5052000</v>
+      </c>
     </row>
     <row r="298" s="249" customFormat="1" spans="1:3">
       <c r="A298" s="251"/>
@@ -7783,13 +8012,49 @@
       <c r="A390" s="251"/>
       <c r="C390" s="250"/>
     </row>
-    <row r="391" s="249" customFormat="1" spans="1:7">
+    <row r="391" s="249" customFormat="1" spans="1:3">
       <c r="A391" s="251"/>
       <c r="C391" s="250"/>
-      <c r="G391" s="275"/>
+    </row>
+    <row r="392" s="249" customFormat="1" spans="1:3">
+      <c r="A392" s="251"/>
+      <c r="C392" s="250"/>
+    </row>
+    <row r="393" s="249" customFormat="1" spans="1:3">
+      <c r="A393" s="251"/>
+      <c r="C393" s="250"/>
+    </row>
+    <row r="394" s="249" customFormat="1" spans="1:3">
+      <c r="A394" s="251"/>
+      <c r="C394" s="250"/>
+    </row>
+    <row r="395" s="249" customFormat="1" spans="1:3">
+      <c r="A395" s="251"/>
+      <c r="C395" s="250"/>
+    </row>
+    <row r="396" s="249" customFormat="1" spans="1:3">
+      <c r="A396" s="251"/>
+      <c r="C396" s="250"/>
+    </row>
+    <row r="397" s="249" customFormat="1" spans="1:3">
+      <c r="A397" s="251"/>
+      <c r="C397" s="250"/>
+    </row>
+    <row r="398" s="249" customFormat="1" spans="1:3">
+      <c r="A398" s="251"/>
+      <c r="C398" s="250"/>
+    </row>
+    <row r="399" s="249" customFormat="1" spans="1:3">
+      <c r="A399" s="251"/>
+      <c r="C399" s="250"/>
+    </row>
+    <row r="400" s="249" customFormat="1" spans="1:7">
+      <c r="A400" s="251"/>
+      <c r="C400" s="250"/>
+      <c r="G400" s="275"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="40">
     <mergeCell ref="A2:A12"/>
     <mergeCell ref="A13:A25"/>
     <mergeCell ref="A26:A34"/>
@@ -7800,14 +8065,16 @@
     <mergeCell ref="A68:A78"/>
     <mergeCell ref="A79:A93"/>
     <mergeCell ref="A94:A99"/>
-    <mergeCell ref="A204:A211"/>
-    <mergeCell ref="A212:A223"/>
-    <mergeCell ref="A224:A232"/>
-    <mergeCell ref="A233:A243"/>
-    <mergeCell ref="A244:A254"/>
-    <mergeCell ref="A255:A265"/>
-    <mergeCell ref="A266:A275"/>
-    <mergeCell ref="A277:A287"/>
+    <mergeCell ref="A100:A108"/>
+    <mergeCell ref="A109:A121"/>
+    <mergeCell ref="A213:A220"/>
+    <mergeCell ref="A221:A232"/>
+    <mergeCell ref="A233:A241"/>
+    <mergeCell ref="A242:A252"/>
+    <mergeCell ref="A253:A263"/>
+    <mergeCell ref="A264:A274"/>
+    <mergeCell ref="A275:A284"/>
+    <mergeCell ref="A286:A296"/>
     <mergeCell ref="F2:F12"/>
     <mergeCell ref="F13:F25"/>
     <mergeCell ref="F26:F34"/>
@@ -7818,14 +8085,16 @@
     <mergeCell ref="F68:F78"/>
     <mergeCell ref="F79:F93"/>
     <mergeCell ref="F94:F99"/>
-    <mergeCell ref="F204:F211"/>
-    <mergeCell ref="F212:F223"/>
-    <mergeCell ref="F224:F232"/>
-    <mergeCell ref="F233:F243"/>
-    <mergeCell ref="F244:F254"/>
-    <mergeCell ref="F255:F265"/>
-    <mergeCell ref="F266:F275"/>
-    <mergeCell ref="F277:F287"/>
+    <mergeCell ref="F100:F108"/>
+    <mergeCell ref="F109:F121"/>
+    <mergeCell ref="F213:F220"/>
+    <mergeCell ref="F221:F232"/>
+    <mergeCell ref="F233:F241"/>
+    <mergeCell ref="F242:F252"/>
+    <mergeCell ref="F253:F263"/>
+    <mergeCell ref="F264:F274"/>
+    <mergeCell ref="F275:F284"/>
+    <mergeCell ref="F286:F296"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -7852,16 +8121,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -7878,7 +8147,7 @@
         <v>38678</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" s="27">
         <v>3</v>
@@ -7901,7 +8170,7 @@
       <c r="D3" s="27"/>
       <c r="E3" s="17"/>
       <c r="F3" s="123" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G3" s="53">
         <f>G2*11%</f>
@@ -7943,7 +8212,7 @@
       <c r="D6" s="122"/>
       <c r="E6" s="7"/>
       <c r="F6" s="127" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G6" s="7">
         <f>G5*11%</f>
@@ -8025,7 +8294,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="81" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B14" s="82"/>
       <c r="C14" s="82"/>
@@ -8080,16 +8349,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -8228,7 +8497,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="81" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B14" s="82"/>
       <c r="C14" s="82"/>
@@ -8282,16 +8551,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -8300,7 +8569,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" ht="147.55" customHeight="1" spans="1:8">
@@ -8308,10 +8577,10 @@
         <v>45999</v>
       </c>
       <c r="B2" s="93" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D2" s="56">
         <v>24</v>
@@ -8338,7 +8607,7 @@
       </c>
       <c r="E3" s="106"/>
       <c r="F3" s="86" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G3" s="107">
         <f>G2*11%</f>
@@ -8386,7 +8655,7 @@
       </c>
       <c r="E6" s="85"/>
       <c r="F6" s="86" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G6" s="107">
         <f>G5*11%</f>
@@ -8431,7 +8700,7 @@
       <c r="D9" s="102"/>
       <c r="E9" s="85"/>
       <c r="F9" s="86" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G9" s="107">
         <f>G8*11%</f>
@@ -8476,7 +8745,7 @@
       <c r="D12" s="102"/>
       <c r="E12" s="85"/>
       <c r="F12" s="86" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G12" s="107">
         <f>G11*11%</f>
@@ -8518,7 +8787,7 @@
       <c r="D15" s="102"/>
       <c r="E15" s="85"/>
       <c r="F15" s="86" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G15" s="107">
         <f>G14*11%</f>
@@ -8543,7 +8812,7 @@
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:8">
       <c r="A17" s="81" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B17" s="82"/>
       <c r="C17" s="82"/>
@@ -8602,19 +8871,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="35" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>5</v>
@@ -8646,7 +8915,7 @@
     </row>
     <row r="4" ht="23" customHeight="1" spans="1:7">
       <c r="A4" s="94" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B4" s="95"/>
       <c r="C4" s="95"/>
@@ -8687,16 +8956,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -8710,10 +8979,10 @@
         <v>45999</v>
       </c>
       <c r="B2" s="77" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D2" s="27">
         <v>3</v>
@@ -8729,7 +8998,7 @@
     </row>
     <row r="3" ht="26" spans="1:7">
       <c r="A3" s="28" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="78"/>
@@ -8739,7 +9008,7 @@
       </c>
       <c r="E3" s="85"/>
       <c r="F3" s="85" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G3" s="86">
         <f>G2*11%</f>
@@ -8794,7 +9063,7 @@
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:7">
       <c r="A8" s="81" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B8" s="82"/>
       <c r="C8" s="82"/>
@@ -8842,19 +9111,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" ht="321" customHeight="1" spans="1:6">
@@ -8917,16 +9186,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -9027,7 +9296,7 @@
     </row>
     <row r="12" ht="27" customHeight="1" spans="1:7">
       <c r="A12" s="49" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B12" s="50"/>
       <c r="C12" s="50"/>
@@ -9080,13 +9349,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>3</v>
@@ -9095,7 +9364,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" ht="324.4" customHeight="1" spans="1:7">
@@ -9154,22 +9423,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" ht="177" customHeight="1" spans="1:7">
@@ -9230,10 +9499,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>5</v>
@@ -9244,11 +9513,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C2" s="5">
-        <f>'BUK BUNGA (Groceries)'!F288</f>
-        <v>3916000</v>
+        <f>'BUK BUNGA (Groceries)'!F297</f>
+        <v>5052000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9256,7 +9525,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C3" s="5">
         <f>'WARUNG EKA (Drinks, Etc)'!G117</f>
@@ -9268,7 +9537,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C4" s="5">
         <f>'DEWATA COCONUT (Coconut)'!E10</f>
@@ -9280,7 +9549,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="5">
         <f>'SEDANA JAYA'!F37</f>
@@ -9292,7 +9561,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" s="5">
         <f>'PNB (Alcohol)'!H7</f>
@@ -9304,7 +9573,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C7" s="5">
         <f>'DSP (Alcohol)'!F16</f>
@@ -9316,7 +9585,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C8" s="5">
         <f>'DSP ARYA BIMA (Alcohol)'!E3</f>
@@ -9328,7 +9597,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="5" t="str">
         <f>'SELERA OR STIR UP (Syrup)'!F19</f>
@@ -9340,7 +9609,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C10" s="5">
         <f>'DW BALI (Alcohol)'!E6</f>
@@ -9352,7 +9621,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C11" s="5">
         <f>'DDB (Alcohol)'!E14</f>
@@ -9364,7 +9633,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C12" s="5">
         <f>'NANO DEWATA (Alcohol)'!E14</f>
@@ -9376,7 +9645,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C13" s="5">
         <f>'BALI PERMATA JAYA (Corona Beer)'!E17</f>
@@ -9388,7 +9657,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C14" s="7">
         <f>'BLACK COFFEE ROASTERS (Coffee)'!F4</f>
@@ -9400,7 +9669,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C15" s="5">
         <f>'PT. PRASIDA LANTUR MAJU (Wine)'!E8</f>
@@ -9412,7 +9681,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C16" s="8">
         <f>'PT LOVINA BEACH BREWERY'!D3</f>
@@ -9424,7 +9693,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C17" s="5">
         <f>'CHAI CHITAI (Tea Leaf,etc)'!E12</f>
@@ -9436,7 +9705,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C18" s="5">
         <f>'MULIA JAYA (Passion Fruit)'!D3</f>
@@ -9448,7 +9717,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C19" s="5">
         <f>'Dewata Kencana Distribusi (Vdka'!E3</f>
@@ -9462,7 +9731,7 @@
       <c r="B20" s="9"/>
       <c r="C20" s="10">
         <f>SUM(C2:C13)</f>
-        <v>17668109.94</v>
+        <v>18804109.94</v>
       </c>
     </row>
   </sheetData>
@@ -9498,7 +9767,7 @@
   <sheetData>
     <row r="1" s="249" customFormat="1" ht="21" customHeight="1" spans="1:7">
       <c r="A1" s="255" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B1" s="256" t="s">
         <v>0</v>
@@ -9513,10 +9782,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="257" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G1" s="257" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
@@ -9527,7 +9796,7 @@
         <v>45992</v>
       </c>
       <c r="C2" s="259" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D2" s="115">
         <v>5</v>
@@ -9548,7 +9817,7 @@
       <c r="A3" s="41"/>
       <c r="B3" s="40"/>
       <c r="C3" s="259" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D3" s="115">
         <v>1</v>
@@ -9566,7 +9835,7 @@
       <c r="A4" s="260"/>
       <c r="B4" s="131"/>
       <c r="C4" s="259" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D4" s="115">
         <v>1</v>
@@ -9588,7 +9857,7 @@
         <v>45993</v>
       </c>
       <c r="C5" s="259" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D5" s="115">
         <v>5</v>
@@ -9609,7 +9878,7 @@
       <c r="A6" s="209"/>
       <c r="B6" s="40"/>
       <c r="C6" s="259" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D6" s="115">
         <v>1</v>
@@ -9627,7 +9896,7 @@
       <c r="A7" s="207"/>
       <c r="B7" s="131"/>
       <c r="C7" s="259" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7" s="115">
         <v>1</v>
@@ -9649,7 +9918,7 @@
         <v>45994</v>
       </c>
       <c r="C8" s="259" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D8" s="115">
         <v>6</v>
@@ -9670,7 +9939,7 @@
       <c r="A9" s="209"/>
       <c r="B9" s="40"/>
       <c r="C9" s="259" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D9" s="115">
         <v>1</v>
@@ -9688,7 +9957,7 @@
       <c r="A10" s="209"/>
       <c r="B10" s="40"/>
       <c r="C10" s="259" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D10" s="115">
         <v>1</v>
@@ -9706,7 +9975,7 @@
       <c r="A11" s="209"/>
       <c r="B11" s="40"/>
       <c r="C11" s="259" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D11" s="115">
         <v>1</v>
@@ -9724,7 +9993,7 @@
       <c r="A12" s="209"/>
       <c r="B12" s="40"/>
       <c r="C12" s="261" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D12" s="115">
         <v>2</v>
@@ -9742,7 +10011,7 @@
       <c r="A13" s="207"/>
       <c r="B13" s="131"/>
       <c r="C13" s="259" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D13" s="115">
         <v>1</v>
@@ -9764,7 +10033,7 @@
         <v>45995</v>
       </c>
       <c r="C14" s="259" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D14" s="115">
         <v>6</v>
@@ -9785,7 +10054,7 @@
       <c r="A15" s="207"/>
       <c r="B15" s="131"/>
       <c r="C15" s="261" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D15" s="115">
         <v>2</v>
@@ -9807,7 +10076,7 @@
         <v>45997</v>
       </c>
       <c r="C16" s="261" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D16" s="115">
         <v>2</v>
@@ -9828,7 +10097,7 @@
       <c r="A17" s="209"/>
       <c r="B17" s="40"/>
       <c r="C17" s="261" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D17" s="115">
         <v>1</v>
@@ -9846,7 +10115,7 @@
       <c r="A18" s="207"/>
       <c r="B18" s="131"/>
       <c r="C18" s="261" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D18" s="115">
         <v>5</v>
@@ -9868,7 +10137,7 @@
         <v>45998</v>
       </c>
       <c r="C19" s="259" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D19" s="115">
         <v>2</v>
@@ -9889,7 +10158,7 @@
       <c r="A20" s="209"/>
       <c r="B20" s="40"/>
       <c r="C20" s="259" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D20" s="115">
         <v>1</v>
@@ -9907,7 +10176,7 @@
       <c r="A21" s="209"/>
       <c r="B21" s="40"/>
       <c r="C21" s="259" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D21" s="115">
         <v>5</v>
@@ -9925,7 +10194,7 @@
       <c r="A22" s="209"/>
       <c r="B22" s="40"/>
       <c r="C22" s="259" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D22" s="115">
         <v>1</v>
@@ -9943,7 +10212,7 @@
       <c r="A23" s="207"/>
       <c r="B23" s="131"/>
       <c r="C23" s="261" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D23" s="115">
         <v>2</v>
@@ -9965,7 +10234,7 @@
         <v>45999</v>
       </c>
       <c r="C24" s="259" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D24" s="115">
         <v>1</v>
@@ -9986,7 +10255,7 @@
       <c r="A25" s="209"/>
       <c r="B25" s="40"/>
       <c r="C25" s="259" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D25" s="115">
         <v>1</v>
@@ -10004,7 +10273,7 @@
       <c r="A26" s="209"/>
       <c r="B26" s="40"/>
       <c r="C26" s="261" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D26" s="115">
         <v>1</v>
@@ -10022,7 +10291,7 @@
       <c r="A27" s="207"/>
       <c r="B27" s="131"/>
       <c r="C27" s="259" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D27" s="115">
         <v>4</v>
@@ -10044,7 +10313,7 @@
         <v>46000</v>
       </c>
       <c r="C28" s="261" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D28" s="115">
         <v>5</v>
@@ -10065,7 +10334,7 @@
       <c r="A29" s="209"/>
       <c r="B29" s="40"/>
       <c r="C29" s="259" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D29" s="115">
         <v>1</v>
@@ -10083,7 +10352,7 @@
       <c r="A30" s="207"/>
       <c r="B30" s="131"/>
       <c r="C30" s="259" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D30" s="115">
         <v>1</v>
@@ -10105,7 +10374,7 @@
         <v>46001</v>
       </c>
       <c r="C31" s="262" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D31" s="115">
         <v>6</v>
@@ -10126,7 +10395,7 @@
       <c r="A32" s="56"/>
       <c r="B32" s="25"/>
       <c r="C32" s="263" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D32" s="115">
         <v>1</v>
@@ -10144,7 +10413,7 @@
       <c r="A33" s="56"/>
       <c r="B33" s="25"/>
       <c r="C33" s="262" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D33" s="115">
         <v>1</v>
@@ -10162,7 +10431,7 @@
       <c r="A34" s="56"/>
       <c r="B34" s="25"/>
       <c r="C34" s="262" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D34" s="115">
         <v>1</v>
@@ -10180,7 +10449,7 @@
       <c r="A35" s="56"/>
       <c r="B35" s="25"/>
       <c r="C35" s="262" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D35" s="115">
         <v>1</v>
@@ -10198,7 +10467,7 @@
       <c r="A36" s="56"/>
       <c r="B36" s="25"/>
       <c r="C36" s="262" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D36" s="115">
         <v>1</v>
@@ -10216,7 +10485,7 @@
       <c r="A37" s="56"/>
       <c r="B37" s="25"/>
       <c r="C37" s="262" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D37" s="115">
         <v>2</v>
@@ -10238,7 +10507,7 @@
         <v>46002</v>
       </c>
       <c r="C38" s="259" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D38" s="115">
         <v>6</v>
@@ -10259,7 +10528,7 @@
       <c r="A39" s="209"/>
       <c r="B39" s="40"/>
       <c r="C39" s="259" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D39" s="115">
         <v>2</v>
@@ -10277,7 +10546,7 @@
       <c r="A40" s="209"/>
       <c r="B40" s="40"/>
       <c r="C40" s="259" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D40" s="115">
         <v>1</v>
@@ -10299,7 +10568,7 @@
         <v>46003</v>
       </c>
       <c r="C41" s="259" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D41" s="115">
         <v>6</v>
@@ -10320,7 +10589,7 @@
       <c r="A42" s="209"/>
       <c r="B42" s="40"/>
       <c r="C42" s="259" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D42" s="115">
         <v>1</v>
@@ -10338,7 +10607,7 @@
       <c r="A43" s="209"/>
       <c r="B43" s="40"/>
       <c r="C43" s="259" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D43" s="115">
         <v>2</v>
@@ -10356,7 +10625,7 @@
       <c r="A44" s="209"/>
       <c r="B44" s="40"/>
       <c r="C44" s="259" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D44" s="115">
         <v>1</v>
@@ -10374,7 +10643,7 @@
       <c r="A45" s="207"/>
       <c r="B45" s="131"/>
       <c r="C45" s="259" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D45" s="115">
         <v>1</v>
@@ -10396,7 +10665,7 @@
         <v>46004</v>
       </c>
       <c r="C46" s="259" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D46" s="115">
         <v>1</v>
@@ -10417,7 +10686,7 @@
       <c r="A47" s="207"/>
       <c r="B47" s="131"/>
       <c r="C47" s="259" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D47" s="115">
         <v>6</v>
@@ -11332,7 +11601,7 @@
     </row>
     <row r="117" s="249" customFormat="1" spans="1:7">
       <c r="A117" s="273" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B117" s="122"/>
       <c r="C117" s="274"/>
@@ -11717,16 +11986,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>3</v>
@@ -11743,7 +12012,7 @@
         <v>12340</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D2" s="16">
         <v>20</v>
@@ -11765,7 +12034,7 @@
         <v>12357</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D3" s="16">
         <v>20</v>
@@ -11787,7 +12056,7 @@
         <v>11374</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" s="16">
         <v>20</v>
@@ -11809,7 +12078,7 @@
         <v>13396</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D5" s="16">
         <v>20</v>
@@ -11831,7 +12100,7 @@
         <v>11474</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D6" s="16">
         <v>20</v>
@@ -11939,7 +12208,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="229" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F1" s="229" t="s">
         <v>5</v>
@@ -11987,7 +12256,7 @@
     <row r="4" s="222" customFormat="1" spans="1:7">
       <c r="A4" s="234"/>
       <c r="B4" s="231" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C4" s="232">
         <v>0.3</v>
@@ -12005,7 +12274,7 @@
     <row r="5" s="222" customFormat="1" spans="1:6">
       <c r="A5" s="234"/>
       <c r="B5" s="231" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C5" s="232">
         <v>1</v>
@@ -12091,7 +12360,7 @@
     <row r="10" s="222" customFormat="1" spans="1:6">
       <c r="A10" s="235"/>
       <c r="B10" s="231" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10" s="232">
         <v>2</v>
@@ -12148,7 +12417,7 @@
     <row r="13" s="222" customFormat="1" spans="1:6">
       <c r="A13" s="234"/>
       <c r="B13" s="231" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C13" s="232">
         <v>8</v>
@@ -12199,7 +12468,7 @@
     <row r="16" s="222" customFormat="1" spans="1:6">
       <c r="A16" s="234"/>
       <c r="B16" s="231" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C16" s="232">
         <v>2</v>
@@ -12233,7 +12502,7 @@
     <row r="18" s="222" customFormat="1" spans="1:6">
       <c r="A18" s="234"/>
       <c r="B18" s="231" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C18" s="232">
         <v>1</v>
@@ -12267,7 +12536,7 @@
     <row r="20" s="222" customFormat="1" spans="1:6">
       <c r="A20" s="235"/>
       <c r="B20" s="231" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C20" s="232">
         <v>1</v>
@@ -14287,19 +14556,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>4</v>
@@ -14313,10 +14582,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="216" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" s="16">
         <v>3</v>
@@ -14457,31 +14726,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="181" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="181" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="181" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="181" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="181" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G1" s="181" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="181" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I1" s="181" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="181" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" ht="387.45" customHeight="1" spans="1:10">
@@ -14489,10 +14758,10 @@
         <v>46000</v>
       </c>
       <c r="B2" s="183" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2" s="175" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" s="184">
         <v>4</v>
@@ -14523,10 +14792,10 @@
         <v>46002</v>
       </c>
       <c r="B3" s="186" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="175" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" s="184">
         <v>4</v>
@@ -14556,7 +14825,7 @@
       <c r="A4" s="187"/>
       <c r="B4" s="188"/>
       <c r="C4" s="189" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" s="190">
         <v>4</v>
@@ -14889,16 +15158,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="172" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="172" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="172" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="172" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F1" s="172" t="s">
         <v>3</v>
@@ -14960,22 +15229,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="141" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="141" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="141" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="141" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F1" s="141" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="141" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H1" s="153" t="s">
         <v>5</v>
@@ -14986,10 +15255,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C2" s="143" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D2" s="144">
         <v>5</v>
@@ -15059,7 +15328,7 @@
       </c>
       <c r="E7" s="161"/>
       <c r="F7" s="162" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G7" s="162"/>
       <c r="H7" s="162">
@@ -15087,10 +15356,10 @@
         <v>45999</v>
       </c>
       <c r="B9" s="142" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9" s="151" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" s="150">
         <v>3</v>
@@ -15112,7 +15381,7 @@
       <c r="A10" s="145"/>
       <c r="B10" s="145"/>
       <c r="C10" s="151" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" s="150">
         <v>3</v>
@@ -15131,7 +15400,7 @@
       <c r="A11" s="152"/>
       <c r="B11" s="152"/>
       <c r="C11" s="151" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D11" s="150">
         <v>2</v>
@@ -15158,7 +15427,7 @@
       </c>
       <c r="E12" s="161"/>
       <c r="F12" s="162" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G12" s="162"/>
       <c r="H12" s="162">
@@ -15186,10 +15455,10 @@
         <v>45992</v>
       </c>
       <c r="B14" s="142" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="143" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" s="144">
         <v>5</v>
@@ -15262,7 +15531,7 @@
       </c>
       <c r="E19" s="161"/>
       <c r="F19" s="162" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G19" s="162"/>
       <c r="H19" s="162">
@@ -15368,22 +15637,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H1" s="35" t="s">
         <v>5</v>
@@ -15394,10 +15663,10 @@
         <v>46001</v>
       </c>
       <c r="B2" s="115" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D2" s="115">
         <v>2</v>
@@ -15420,10 +15689,10 @@
         <v>46001</v>
       </c>
       <c r="B3" s="93" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3" s="115">
         <v>4</v>
@@ -15446,10 +15715,10 @@
         <v>46004</v>
       </c>
       <c r="B4" s="130" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4" s="115">
         <v>1</v>
@@ -15474,7 +15743,7 @@
       <c r="A5" s="131"/>
       <c r="B5" s="132"/>
       <c r="C5" s="38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" s="115">
         <v>1</v>
@@ -15491,7 +15760,7 @@
     </row>
     <row r="6" ht="26" spans="1:8">
       <c r="A6" s="81" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B6" s="82"/>
       <c r="C6" s="82"/>

--- a/DECEMBER/DECEMBER BAR.xlsx
+++ b/DECEMBER/DECEMBER BAR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17000"/>
+    <workbookView windowHeight="17000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="BUK BUNGA (Groceries)" sheetId="28" r:id="rId1"/>
@@ -101,11 +101,89 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_E993176563EA4A59A99F5C983CF8DE4D" descr="PHOTO-2025-12-16-22-47-51"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:srcRect l="7339" r="3075" b="8025"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="7289800" y="6405880"/>
+          <a:ext cx="5084445" cy="9266555"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_A7288E1D8486499C936AD7CFEE5889FB" descr="PHOTO-2025-12-16-22-53-51"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:srcRect l="6175" t="14438" r="1976" b="5076"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="7352030" y="7620"/>
+          <a:ext cx="4000500" cy="6055360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_EC8B07304AE24AABAA210E4FDB7BE2A3" descr="PHOTO-2025-12-16-22-53-10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:srcRect l="11965" t="9771" b="12627"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="8303895" y="2152015"/>
+          <a:ext cx="5131435" cy="7811135"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="127">
   <si>
     <t>DATE</t>
   </si>
@@ -266,6 +344,9 @@
     <t>COKE ZERO CAN 330ML</t>
   </si>
   <si>
+    <t>SCHWEPPES TONIC WATER CAN 250ML</t>
+  </si>
+  <si>
     <t>GRAND TOTAL</t>
   </si>
   <si>
@@ -338,6 +419,18 @@
     <t>DA VINCI LEONARDO PROSECCO DOC</t>
   </si>
   <si>
+    <t>SO/DSP/25/12/0908</t>
+  </si>
+  <si>
+    <t>DONA DOMINGA CLASICO DE FAMILIA SYRAH</t>
+  </si>
+  <si>
+    <t>SO/DSP/25/12/1004</t>
+  </si>
+  <si>
+    <t>SAN MARZANO TALO PRIMITIVO MERLOT</t>
+  </si>
+  <si>
     <t>SO-2504780</t>
   </si>
   <si>
@@ -393,6 +486,15 @@
   </si>
   <si>
     <t>CORONA BEER</t>
+  </si>
+  <si>
+    <t>BL2-10-2320</t>
+  </si>
+  <si>
+    <t>CANGGU BLEND 1KG</t>
+  </si>
+  <si>
+    <t>BL2-10-2348</t>
   </si>
   <si>
     <t>Total</t>
@@ -1484,7 +1586,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="309">
+  <cellXfs count="321">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2277,9 +2379,42 @@
     <xf numFmtId="181" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="27" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="29" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2298,6 +2433,15 @@
     <xf numFmtId="180" fontId="9" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2379,21 +2523,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="30" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="181" fontId="30" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2401,16 +2539,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2959,6 +3097,84 @@
         <a:xfrm>
           <a:off x="21306155" y="5387975"/>
           <a:ext cx="3827145" cy="4925695"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>360680</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>4377690</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>5169535</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="ID_061DAB7DDA8F473B95DF7FDF52C799D7" descr="PHOTO-2025-12-16-23-39-35"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:srcRect l="2390" t="13970" r="3423" b="18309"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21640165" y="10387965"/>
+          <a:ext cx="4017010" cy="5137785"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>339725</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>4398645</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>5169535</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_B9A46A50A1B54A72895601589A7F8868" descr="PHOTO-2025-12-16-23-38-51"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:srcRect l="3405" t="11288" r="2944" b="22140"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21619210" y="15588615"/>
+          <a:ext cx="4058920" cy="5137785"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3555,18 +3771,18 @@
       <c r="E1" s="257" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="292" t="s">
+      <c r="F1" s="306" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A2" s="283">
+      <c r="A2" s="297">
         <v>45995</v>
       </c>
-      <c r="B2" s="284" t="s">
+      <c r="B2" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="285">
+      <c r="C2" s="299">
         <v>5</v>
       </c>
       <c r="D2" s="7">
@@ -3576,17 +3792,17 @@
         <f t="shared" ref="E2:E15" si="0">SUM(C2*D2)</f>
         <v>100000</v>
       </c>
-      <c r="F2" s="293">
+      <c r="F2" s="307">
         <f>SUM(E2:E12)</f>
         <v>572000</v>
       </c>
     </row>
     <row r="3" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A3" s="286"/>
-      <c r="B3" s="284" t="s">
+      <c r="A3" s="300"/>
+      <c r="B3" s="298" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="285">
+      <c r="C3" s="299">
         <v>2</v>
       </c>
       <c r="D3" s="7">
@@ -3596,14 +3812,14 @@
         <f t="shared" si="0"/>
         <v>140000</v>
       </c>
-      <c r="F3" s="294"/>
+      <c r="F3" s="308"/>
     </row>
     <row r="4" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A4" s="286"/>
-      <c r="B4" s="284" t="s">
+      <c r="A4" s="300"/>
+      <c r="B4" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="285">
+      <c r="C4" s="299">
         <v>6</v>
       </c>
       <c r="D4" s="7">
@@ -3613,14 +3829,14 @@
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
-      <c r="F4" s="294"/>
+      <c r="F4" s="308"/>
     </row>
     <row r="5" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A5" s="286"/>
-      <c r="B5" s="284" t="s">
+      <c r="A5" s="300"/>
+      <c r="B5" s="298" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="285">
+      <c r="C5" s="299">
         <v>1</v>
       </c>
       <c r="D5" s="7">
@@ -3630,14 +3846,14 @@
         <f t="shared" si="0"/>
         <v>38000</v>
       </c>
-      <c r="F5" s="294"/>
+      <c r="F5" s="308"/>
     </row>
     <row r="6" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A6" s="286"/>
-      <c r="B6" s="284" t="s">
+      <c r="A6" s="300"/>
+      <c r="B6" s="298" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="285">
+      <c r="C6" s="299">
         <v>0.3</v>
       </c>
       <c r="D6" s="7">
@@ -3647,14 +3863,14 @@
         <f t="shared" si="0"/>
         <v>6000</v>
       </c>
-      <c r="F6" s="294"/>
+      <c r="F6" s="308"/>
     </row>
     <row r="7" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A7" s="286"/>
-      <c r="B7" s="284" t="s">
+      <c r="A7" s="300"/>
+      <c r="B7" s="298" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="285">
+      <c r="C7" s="299">
         <v>1</v>
       </c>
       <c r="D7" s="7">
@@ -3664,14 +3880,14 @@
         <f t="shared" si="0"/>
         <v>25000</v>
       </c>
-      <c r="F7" s="294"/>
+      <c r="F7" s="308"/>
     </row>
     <row r="8" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A8" s="286"/>
-      <c r="B8" s="284" t="s">
+      <c r="A8" s="300"/>
+      <c r="B8" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="285">
+      <c r="C8" s="299">
         <v>1</v>
       </c>
       <c r="D8" s="7">
@@ -3681,14 +3897,14 @@
         <f t="shared" si="0"/>
         <v>30000</v>
       </c>
-      <c r="F8" s="294"/>
+      <c r="F8" s="308"/>
     </row>
     <row r="9" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A9" s="286"/>
-      <c r="B9" s="284" t="s">
+      <c r="A9" s="300"/>
+      <c r="B9" s="298" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="285">
+      <c r="C9" s="299">
         <v>1</v>
       </c>
       <c r="D9" s="7">
@@ -3698,14 +3914,14 @@
         <f t="shared" si="0"/>
         <v>12000</v>
       </c>
-      <c r="F9" s="294"/>
+      <c r="F9" s="308"/>
     </row>
     <row r="10" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A10" s="286"/>
-      <c r="B10" s="284" t="s">
+      <c r="A10" s="300"/>
+      <c r="B10" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="285">
+      <c r="C10" s="299">
         <v>3</v>
       </c>
       <c r="D10" s="7">
@@ -3715,14 +3931,14 @@
         <f t="shared" si="0"/>
         <v>72000</v>
       </c>
-      <c r="F10" s="294"/>
+      <c r="F10" s="308"/>
     </row>
     <row r="11" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A11" s="286"/>
-      <c r="B11" s="284" t="s">
+      <c r="A11" s="300"/>
+      <c r="B11" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="285">
+      <c r="C11" s="299">
         <v>1</v>
       </c>
       <c r="D11" s="7">
@@ -3732,14 +3948,14 @@
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="F11" s="294"/>
+      <c r="F11" s="308"/>
     </row>
     <row r="12" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A12" s="287"/>
-      <c r="B12" s="284" t="s">
+      <c r="A12" s="301"/>
+      <c r="B12" s="298" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="285">
+      <c r="C12" s="299">
         <v>1</v>
       </c>
       <c r="D12" s="7">
@@ -3749,16 +3965,16 @@
         <f t="shared" si="0"/>
         <v>49000</v>
       </c>
-      <c r="F12" s="295"/>
+      <c r="F12" s="309"/>
     </row>
     <row r="13" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A13" s="283">
+      <c r="A13" s="297">
         <v>45996</v>
       </c>
-      <c r="B13" s="284" t="s">
+      <c r="B13" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="285">
+      <c r="C13" s="299">
         <v>8</v>
       </c>
       <c r="D13" s="7">
@@ -3768,17 +3984,17 @@
         <f t="shared" si="0"/>
         <v>80000</v>
       </c>
-      <c r="F13" s="293">
+      <c r="F13" s="307">
         <f>SUM(E13:E25)</f>
         <v>730000</v>
       </c>
     </row>
     <row r="14" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A14" s="286"/>
-      <c r="B14" s="284" t="s">
+      <c r="A14" s="300"/>
+      <c r="B14" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="285">
+      <c r="C14" s="299">
         <v>2</v>
       </c>
       <c r="D14" s="7">
@@ -3788,14 +4004,14 @@
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="F14" s="294"/>
+      <c r="F14" s="308"/>
     </row>
     <row r="15" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A15" s="286"/>
-      <c r="B15" s="284" t="s">
+      <c r="A15" s="300"/>
+      <c r="B15" s="298" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="285">
+      <c r="C15" s="299">
         <v>2</v>
       </c>
       <c r="D15" s="7">
@@ -3805,14 +4021,14 @@
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
-      <c r="F15" s="294"/>
+      <c r="F15" s="308"/>
     </row>
     <row r="16" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A16" s="286"/>
-      <c r="B16" s="284" t="s">
+      <c r="A16" s="300"/>
+      <c r="B16" s="298" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="285">
+      <c r="C16" s="299">
         <v>0.5</v>
       </c>
       <c r="D16" s="7">
@@ -3821,14 +4037,14 @@
       <c r="E16" s="7">
         <v>48000</v>
       </c>
-      <c r="F16" s="294"/>
+      <c r="F16" s="308"/>
     </row>
     <row r="17" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A17" s="286"/>
-      <c r="B17" s="284" t="s">
+      <c r="A17" s="300"/>
+      <c r="B17" s="298" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="285">
+      <c r="C17" s="299">
         <v>1.1</v>
       </c>
       <c r="D17" s="7">
@@ -3837,14 +4053,14 @@
       <c r="E17" s="7">
         <v>42000</v>
       </c>
-      <c r="F17" s="294"/>
+      <c r="F17" s="308"/>
     </row>
     <row r="18" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A18" s="286"/>
-      <c r="B18" s="284" t="s">
+      <c r="A18" s="300"/>
+      <c r="B18" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="285">
+      <c r="C18" s="299">
         <v>5</v>
       </c>
       <c r="D18" s="7">
@@ -3854,14 +4070,14 @@
         <f t="shared" ref="E18:E25" si="1">SUM(C18*D18)</f>
         <v>120000</v>
       </c>
-      <c r="F18" s="294"/>
+      <c r="F18" s="308"/>
     </row>
     <row r="19" s="249" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A19" s="286"/>
-      <c r="B19" s="288" t="s">
+      <c r="A19" s="300"/>
+      <c r="B19" s="302" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="303">
         <v>3</v>
       </c>
       <c r="D19" s="133">
@@ -3871,222 +4087,222 @@
         <f t="shared" si="1"/>
         <v>120000</v>
       </c>
-      <c r="F19" s="294"/>
-      <c r="G19" s="275"/>
+      <c r="F19" s="308"/>
+      <c r="G19" s="289"/>
     </row>
     <row r="20" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A20" s="286"/>
-      <c r="B20" s="290" t="s">
+      <c r="A20" s="300"/>
+      <c r="B20" s="304" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="285">
+      <c r="C20" s="299">
         <v>1</v>
       </c>
-      <c r="D20" s="266">
+      <c r="D20" s="277">
         <v>45000</v>
       </c>
       <c r="E20" s="7">
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F20" s="294"/>
+      <c r="F20" s="308"/>
     </row>
     <row r="21" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A21" s="286"/>
-      <c r="B21" s="290" t="s">
+      <c r="A21" s="300"/>
+      <c r="B21" s="304" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="285">
+      <c r="C21" s="299">
         <v>2</v>
       </c>
-      <c r="D21" s="266">
+      <c r="D21" s="277">
         <v>20000</v>
       </c>
       <c r="E21" s="7">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F21" s="294"/>
+      <c r="F21" s="308"/>
     </row>
     <row r="22" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A22" s="286"/>
-      <c r="B22" s="290" t="s">
+      <c r="A22" s="300"/>
+      <c r="B22" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="285">
+      <c r="C22" s="299">
         <v>0.5</v>
       </c>
-      <c r="D22" s="266">
+      <c r="D22" s="277">
         <v>30000</v>
       </c>
       <c r="E22" s="7">
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
-      <c r="F22" s="294"/>
+      <c r="F22" s="308"/>
     </row>
     <row r="23" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A23" s="286"/>
-      <c r="B23" s="290" t="s">
+      <c r="A23" s="300"/>
+      <c r="B23" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="285">
+      <c r="C23" s="299">
         <v>1</v>
       </c>
-      <c r="D23" s="266">
+      <c r="D23" s="277">
         <v>30000</v>
       </c>
       <c r="E23" s="7">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="F23" s="294"/>
+      <c r="F23" s="308"/>
     </row>
     <row r="24" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A24" s="286"/>
-      <c r="B24" s="290" t="s">
+      <c r="A24" s="300"/>
+      <c r="B24" s="304" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="285">
+      <c r="C24" s="299">
         <v>0.3</v>
       </c>
-      <c r="D24" s="266">
+      <c r="D24" s="277">
         <v>150000</v>
       </c>
       <c r="E24" s="7">
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F24" s="294"/>
+      <c r="F24" s="308"/>
     </row>
     <row r="25" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A25" s="287"/>
-      <c r="B25" s="290" t="s">
+      <c r="A25" s="301"/>
+      <c r="B25" s="304" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="285">
+      <c r="C25" s="299">
         <v>1</v>
       </c>
-      <c r="D25" s="266">
+      <c r="D25" s="277">
         <v>35000</v>
       </c>
       <c r="E25" s="7">
         <f t="shared" si="1"/>
         <v>35000</v>
       </c>
-      <c r="F25" s="295"/>
+      <c r="F25" s="309"/>
     </row>
     <row r="26" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A26" s="283">
+      <c r="A26" s="297">
         <v>45997</v>
       </c>
-      <c r="B26" s="290" t="s">
+      <c r="B26" s="304" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="285">
+      <c r="C26" s="299">
         <v>3.995</v>
       </c>
-      <c r="D26" s="266">
+      <c r="D26" s="277">
         <v>15000</v>
       </c>
       <c r="E26" s="7">
         <v>60000</v>
       </c>
-      <c r="F26" s="293">
+      <c r="F26" s="307">
         <f>SUM(E26:E34)</f>
         <v>422000</v>
       </c>
     </row>
     <row r="27" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A27" s="286"/>
-      <c r="B27" s="290" t="s">
+      <c r="A27" s="300"/>
+      <c r="B27" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="285">
+      <c r="C27" s="299">
         <v>2</v>
       </c>
-      <c r="D27" s="266">
+      <c r="D27" s="277">
         <v>20000</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(C27*D27)</f>
         <v>40000</v>
       </c>
-      <c r="F27" s="294"/>
+      <c r="F27" s="308"/>
     </row>
     <row r="28" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A28" s="286"/>
-      <c r="B28" s="290" t="s">
+      <c r="A28" s="300"/>
+      <c r="B28" s="304" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="285">
+      <c r="C28" s="299">
         <v>0.5</v>
       </c>
-      <c r="D28" s="266">
+      <c r="D28" s="277">
         <v>35000</v>
       </c>
       <c r="E28" s="7">
         <v>18000</v>
       </c>
-      <c r="F28" s="294"/>
+      <c r="F28" s="308"/>
     </row>
     <row r="29" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A29" s="286"/>
-      <c r="B29" s="290" t="s">
+      <c r="A29" s="300"/>
+      <c r="B29" s="304" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="285">
+      <c r="C29" s="299">
         <v>0.1</v>
       </c>
-      <c r="D29" s="266">
+      <c r="D29" s="277">
         <v>80000</v>
       </c>
       <c r="E29" s="7">
         <f t="shared" ref="E29:E34" si="2">SUM(C29*D29)</f>
         <v>8000</v>
       </c>
-      <c r="F29" s="294"/>
+      <c r="F29" s="308"/>
     </row>
     <row r="30" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A30" s="286"/>
-      <c r="B30" s="290" t="s">
+      <c r="A30" s="300"/>
+      <c r="B30" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="285">
+      <c r="C30" s="299">
         <v>0.5</v>
       </c>
-      <c r="D30" s="266">
+      <c r="D30" s="277">
         <v>30000</v>
       </c>
       <c r="E30" s="7">
         <f t="shared" si="2"/>
         <v>15000</v>
       </c>
-      <c r="F30" s="294"/>
+      <c r="F30" s="308"/>
     </row>
     <row r="31" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A31" s="286"/>
-      <c r="B31" s="290" t="s">
+      <c r="A31" s="300"/>
+      <c r="B31" s="304" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="285">
+      <c r="C31" s="299">
         <v>4</v>
       </c>
-      <c r="D31" s="266">
+      <c r="D31" s="277">
         <v>20000</v>
       </c>
       <c r="E31" s="7">
         <f t="shared" si="2"/>
         <v>80000</v>
       </c>
-      <c r="F31" s="294"/>
+      <c r="F31" s="308"/>
     </row>
     <row r="32" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A32" s="286"/>
-      <c r="B32" s="284" t="s">
+      <c r="A32" s="300"/>
+      <c r="B32" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="285">
+      <c r="C32" s="299">
         <v>4</v>
       </c>
       <c r="D32" s="7">
@@ -4096,14 +4312,14 @@
         <f t="shared" si="2"/>
         <v>96000</v>
       </c>
-      <c r="F32" s="294"/>
+      <c r="F32" s="308"/>
     </row>
     <row r="33" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A33" s="286"/>
-      <c r="B33" s="284" t="s">
+      <c r="A33" s="300"/>
+      <c r="B33" s="298" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="285">
+      <c r="C33" s="299">
         <v>2</v>
       </c>
       <c r="D33" s="7">
@@ -4113,14 +4329,14 @@
         <f t="shared" si="2"/>
         <v>80000</v>
       </c>
-      <c r="F33" s="294"/>
+      <c r="F33" s="308"/>
     </row>
     <row r="34" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A34" s="287"/>
-      <c r="B34" s="284" t="s">
+      <c r="A34" s="301"/>
+      <c r="B34" s="298" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="285">
+      <c r="C34" s="299">
         <v>1</v>
       </c>
       <c r="D34" s="7">
@@ -4130,16 +4346,16 @@
         <f t="shared" si="2"/>
         <v>25000</v>
       </c>
-      <c r="F34" s="295"/>
+      <c r="F34" s="309"/>
     </row>
     <row r="35" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A35" s="291">
+      <c r="A35" s="305">
         <v>45998</v>
       </c>
-      <c r="B35" s="290" t="s">
+      <c r="B35" s="304" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="285">
+      <c r="C35" s="299">
         <v>8.945</v>
       </c>
       <c r="D35" s="7">
@@ -4148,17 +4364,17 @@
       <c r="E35" s="7">
         <v>134000</v>
       </c>
-      <c r="F35" s="294">
+      <c r="F35" s="308">
         <f>SUM(E35:E42)</f>
         <v>517000</v>
       </c>
     </row>
     <row r="36" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A36" s="291"/>
-      <c r="B36" s="290" t="s">
+      <c r="A36" s="305"/>
+      <c r="B36" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="285">
+      <c r="C36" s="299">
         <v>2</v>
       </c>
       <c r="D36" s="7">
@@ -4168,14 +4384,14 @@
         <f t="shared" ref="E35:E44" si="3">SUM(C36*D36)</f>
         <v>40000</v>
       </c>
-      <c r="F36" s="294"/>
+      <c r="F36" s="308"/>
     </row>
     <row r="37" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A37" s="291"/>
-      <c r="B37" s="290" t="s">
+      <c r="A37" s="305"/>
+      <c r="B37" s="304" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="285">
+      <c r="C37" s="299">
         <v>0.3</v>
       </c>
       <c r="D37" s="7">
@@ -4185,14 +4401,14 @@
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="F37" s="294"/>
+      <c r="F37" s="308"/>
     </row>
     <row r="38" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A38" s="291"/>
-      <c r="B38" s="290" t="s">
+      <c r="A38" s="305"/>
+      <c r="B38" s="304" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="285">
+      <c r="C38" s="299">
         <v>1</v>
       </c>
       <c r="D38" s="7">
@@ -4202,14 +4418,14 @@
         <f t="shared" si="3"/>
         <v>30000</v>
       </c>
-      <c r="F38" s="294"/>
+      <c r="F38" s="308"/>
     </row>
     <row r="39" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A39" s="291"/>
-      <c r="B39" s="290" t="s">
+      <c r="A39" s="305"/>
+      <c r="B39" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="285">
+      <c r="C39" s="299">
         <v>0.5</v>
       </c>
       <c r="D39" s="7">
@@ -4219,14 +4435,14 @@
         <f t="shared" si="3"/>
         <v>15000</v>
       </c>
-      <c r="F39" s="294"/>
+      <c r="F39" s="308"/>
     </row>
     <row r="40" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A40" s="291"/>
-      <c r="B40" s="290" t="s">
+      <c r="A40" s="305"/>
+      <c r="B40" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="285">
+      <c r="C40" s="299">
         <v>4</v>
       </c>
       <c r="D40" s="7">
@@ -4236,14 +4452,14 @@
         <f t="shared" si="3"/>
         <v>96000</v>
       </c>
-      <c r="F40" s="294"/>
+      <c r="F40" s="308"/>
     </row>
     <row r="41" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A41" s="291"/>
-      <c r="B41" s="290" t="s">
+      <c r="A41" s="305"/>
+      <c r="B41" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="285">
+      <c r="C41" s="299">
         <v>2</v>
       </c>
       <c r="D41" s="7">
@@ -4253,14 +4469,14 @@
         <f t="shared" si="3"/>
         <v>80000</v>
       </c>
-      <c r="F41" s="294"/>
+      <c r="F41" s="308"/>
     </row>
     <row r="42" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A42" s="291"/>
-      <c r="B42" s="290" t="s">
+      <c r="A42" s="305"/>
+      <c r="B42" s="304" t="s">
         <v>32</v>
       </c>
-      <c r="C42" s="285">
+      <c r="C42" s="299">
         <v>2</v>
       </c>
       <c r="D42" s="7">
@@ -4270,16 +4486,16 @@
         <f t="shared" si="3"/>
         <v>98000</v>
       </c>
-      <c r="F42" s="294"/>
+      <c r="F42" s="308"/>
     </row>
     <row r="43" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A43" s="283">
+      <c r="A43" s="297">
         <v>45999</v>
       </c>
-      <c r="B43" s="290" t="s">
+      <c r="B43" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="285">
+      <c r="C43" s="299">
         <v>3</v>
       </c>
       <c r="D43" s="7">
@@ -4289,17 +4505,17 @@
         <f t="shared" si="3"/>
         <v>30000</v>
       </c>
-      <c r="F43" s="296">
+      <c r="F43" s="310">
         <f>SUM(E43:E47)</f>
         <v>357000</v>
       </c>
     </row>
     <row r="44" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A44" s="286"/>
-      <c r="B44" s="290" t="s">
+      <c r="A44" s="300"/>
+      <c r="B44" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="285">
+      <c r="C44" s="299">
         <v>2.7</v>
       </c>
       <c r="D44" s="7">
@@ -4309,14 +4525,14 @@
         <f t="shared" si="3"/>
         <v>54000</v>
       </c>
-      <c r="F44" s="296"/>
+      <c r="F44" s="310"/>
     </row>
     <row r="45" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A45" s="286"/>
-      <c r="B45" s="290" t="s">
+      <c r="A45" s="300"/>
+      <c r="B45" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="285">
+      <c r="C45" s="299">
         <v>3.09</v>
       </c>
       <c r="D45" s="7">
@@ -4325,14 +4541,14 @@
       <c r="E45" s="7">
         <v>216000</v>
       </c>
-      <c r="F45" s="296"/>
+      <c r="F45" s="310"/>
     </row>
     <row r="46" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A46" s="286"/>
-      <c r="B46" s="290" t="s">
+      <c r="A46" s="300"/>
+      <c r="B46" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="285">
+      <c r="C46" s="299">
         <v>0.3</v>
       </c>
       <c r="D46" s="7">
@@ -4342,14 +4558,14 @@
         <f>SUM(C46*D46)</f>
         <v>9000</v>
       </c>
-      <c r="F46" s="296"/>
+      <c r="F46" s="310"/>
     </row>
     <row r="47" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A47" s="286"/>
-      <c r="B47" s="290" t="s">
+      <c r="A47" s="300"/>
+      <c r="B47" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="285">
+      <c r="C47" s="299">
         <v>2</v>
       </c>
       <c r="D47" s="7">
@@ -4359,36 +4575,36 @@
         <f>SUM(C47*D47)</f>
         <v>48000</v>
       </c>
-      <c r="F47" s="296"/>
+      <c r="F47" s="310"/>
     </row>
     <row r="48" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A48" s="283">
+      <c r="A48" s="297">
         <v>46000</v>
       </c>
-      <c r="B48" s="290" t="s">
+      <c r="B48" s="304" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="285">
+      <c r="C48" s="299">
         <v>2</v>
       </c>
       <c r="D48" s="7">
         <v>20000</v>
       </c>
       <c r="E48" s="7">
-        <f t="shared" ref="E48:E81" si="4">SUM(C48*D48)</f>
+        <f t="shared" ref="E48:E82" si="4">SUM(C48*D48)</f>
         <v>40000</v>
       </c>
-      <c r="F48" s="293">
+      <c r="F48" s="307">
         <f>SUM(E48:E58)</f>
         <v>612000</v>
       </c>
     </row>
     <row r="49" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A49" s="286"/>
-      <c r="B49" s="290" t="s">
+      <c r="A49" s="300"/>
+      <c r="B49" s="304" t="s">
         <v>17</v>
       </c>
-      <c r="C49" s="285">
+      <c r="C49" s="299">
         <v>2</v>
       </c>
       <c r="D49" s="7">
@@ -4398,14 +4614,14 @@
         <f t="shared" si="4"/>
         <v>70000</v>
       </c>
-      <c r="F49" s="294"/>
+      <c r="F49" s="308"/>
     </row>
     <row r="50" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A50" s="286"/>
-      <c r="B50" s="290" t="s">
+      <c r="A50" s="300"/>
+      <c r="B50" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="285">
+      <c r="C50" s="299">
         <v>5</v>
       </c>
       <c r="D50" s="7">
@@ -4415,14 +4631,14 @@
         <f t="shared" si="4"/>
         <v>120000</v>
       </c>
-      <c r="F50" s="294"/>
+      <c r="F50" s="308"/>
     </row>
     <row r="51" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A51" s="286"/>
-      <c r="B51" s="290" t="s">
+      <c r="A51" s="300"/>
+      <c r="B51" s="304" t="s">
         <v>32</v>
       </c>
-      <c r="C51" s="285">
+      <c r="C51" s="299">
         <v>1</v>
       </c>
       <c r="D51" s="7">
@@ -4432,14 +4648,14 @@
         <f t="shared" si="4"/>
         <v>49000</v>
       </c>
-      <c r="F51" s="294"/>
+      <c r="F51" s="308"/>
     </row>
     <row r="52" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A52" s="286"/>
-      <c r="B52" s="290" t="s">
+      <c r="A52" s="300"/>
+      <c r="B52" s="304" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="285">
+      <c r="C52" s="299">
         <v>1</v>
       </c>
       <c r="D52" s="7">
@@ -4449,14 +4665,14 @@
         <f t="shared" si="4"/>
         <v>65000</v>
       </c>
-      <c r="F52" s="294"/>
+      <c r="F52" s="308"/>
     </row>
     <row r="53" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A53" s="286"/>
-      <c r="B53" s="290" t="s">
+      <c r="A53" s="300"/>
+      <c r="B53" s="304" t="s">
         <v>18</v>
       </c>
-      <c r="C53" s="285">
+      <c r="C53" s="299">
         <v>0.5</v>
       </c>
       <c r="D53" s="7">
@@ -4465,14 +4681,14 @@
       <c r="E53" s="7">
         <v>48000</v>
       </c>
-      <c r="F53" s="294"/>
+      <c r="F53" s="308"/>
     </row>
     <row r="54" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A54" s="286"/>
-      <c r="B54" s="290" t="s">
+      <c r="A54" s="300"/>
+      <c r="B54" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="285">
+      <c r="C54" s="299">
         <v>1</v>
       </c>
       <c r="D54" s="7">
@@ -4482,14 +4698,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F54" s="294"/>
+      <c r="F54" s="308"/>
     </row>
     <row r="55" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A55" s="286"/>
-      <c r="B55" s="290" t="s">
+      <c r="A55" s="300"/>
+      <c r="B55" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="285">
+      <c r="C55" s="299">
         <v>9</v>
       </c>
       <c r="D55" s="7">
@@ -4499,14 +4715,14 @@
         <f t="shared" si="4"/>
         <v>90000</v>
       </c>
-      <c r="F55" s="294"/>
+      <c r="F55" s="308"/>
     </row>
     <row r="56" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A56" s="286"/>
-      <c r="B56" s="284" t="s">
+      <c r="A56" s="300"/>
+      <c r="B56" s="298" t="s">
         <v>7</v>
       </c>
-      <c r="C56" s="285">
+      <c r="C56" s="299">
         <v>1</v>
       </c>
       <c r="D56" s="7">
@@ -4516,14 +4732,14 @@
         <f t="shared" si="4"/>
         <v>70000</v>
       </c>
-      <c r="F56" s="294"/>
+      <c r="F56" s="308"/>
     </row>
     <row r="57" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A57" s="286"/>
-      <c r="B57" s="284" t="s">
+      <c r="A57" s="300"/>
+      <c r="B57" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="285">
+      <c r="C57" s="299">
         <v>2</v>
       </c>
       <c r="D57" s="7">
@@ -4533,14 +4749,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F57" s="294"/>
+      <c r="F57" s="308"/>
     </row>
     <row r="58" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A58" s="287"/>
-      <c r="B58" s="284" t="s">
+      <c r="A58" s="301"/>
+      <c r="B58" s="298" t="s">
         <v>34</v>
       </c>
-      <c r="C58" s="285">
+      <c r="C58" s="299">
         <v>1</v>
       </c>
       <c r="D58" s="7">
@@ -4550,16 +4766,16 @@
         <f t="shared" si="4"/>
         <v>5000</v>
       </c>
-      <c r="F58" s="295"/>
+      <c r="F58" s="309"/>
     </row>
     <row r="59" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A59" s="283">
+      <c r="A59" s="297">
         <v>46001</v>
       </c>
-      <c r="B59" s="284" t="s">
+      <c r="B59" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="285">
+      <c r="C59" s="299">
         <v>3</v>
       </c>
       <c r="D59" s="7">
@@ -4569,17 +4785,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F59" s="293">
+      <c r="F59" s="307">
         <f>SUM(E59:E67)</f>
         <v>586000</v>
       </c>
     </row>
     <row r="60" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A60" s="286"/>
-      <c r="B60" s="284" t="s">
+      <c r="A60" s="300"/>
+      <c r="B60" s="298" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="285">
+      <c r="C60" s="299">
         <v>2</v>
       </c>
       <c r="D60" s="7">
@@ -4589,14 +4805,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F60" s="294"/>
+      <c r="F60" s="308"/>
     </row>
     <row r="61" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A61" s="286"/>
-      <c r="B61" s="284" t="s">
+      <c r="A61" s="300"/>
+      <c r="B61" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="285">
+      <c r="C61" s="299">
         <v>8</v>
       </c>
       <c r="D61" s="7">
@@ -4606,14 +4822,14 @@
         <f t="shared" si="4"/>
         <v>80000</v>
       </c>
-      <c r="F61" s="294"/>
+      <c r="F61" s="308"/>
     </row>
     <row r="62" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A62" s="286"/>
-      <c r="B62" s="284" t="s">
+      <c r="A62" s="300"/>
+      <c r="B62" s="298" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="285">
+      <c r="C62" s="299">
         <v>1</v>
       </c>
       <c r="D62" s="7">
@@ -4623,14 +4839,14 @@
         <f t="shared" si="4"/>
         <v>38000</v>
       </c>
-      <c r="F62" s="294"/>
+      <c r="F62" s="308"/>
     </row>
     <row r="63" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A63" s="286"/>
-      <c r="B63" s="284" t="s">
+      <c r="A63" s="300"/>
+      <c r="B63" s="298" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="285">
+      <c r="C63" s="299">
         <v>1</v>
       </c>
       <c r="D63" s="7">
@@ -4640,14 +4856,14 @@
         <f t="shared" si="4"/>
         <v>20000</v>
       </c>
-      <c r="F63" s="294"/>
+      <c r="F63" s="308"/>
     </row>
     <row r="64" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A64" s="286"/>
-      <c r="B64" s="284" t="s">
+      <c r="A64" s="300"/>
+      <c r="B64" s="298" t="s">
         <v>22</v>
       </c>
-      <c r="C64" s="285">
+      <c r="C64" s="299">
         <v>0.5</v>
       </c>
       <c r="D64" s="7">
@@ -4657,14 +4873,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F64" s="294"/>
+      <c r="F64" s="308"/>
     </row>
     <row r="65" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A65" s="286"/>
-      <c r="B65" s="284" t="s">
+      <c r="A65" s="300"/>
+      <c r="B65" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C65" s="285">
+      <c r="C65" s="299">
         <v>6</v>
       </c>
       <c r="D65" s="7">
@@ -4674,14 +4890,14 @@
         <f t="shared" si="4"/>
         <v>144000</v>
       </c>
-      <c r="F65" s="294"/>
+      <c r="F65" s="308"/>
     </row>
     <row r="66" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A66" s="286"/>
-      <c r="B66" s="284" t="s">
+      <c r="A66" s="300"/>
+      <c r="B66" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="285">
+      <c r="C66" s="299">
         <v>1</v>
       </c>
       <c r="D66" s="7">
@@ -4691,14 +4907,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F66" s="294"/>
+      <c r="F66" s="308"/>
     </row>
     <row r="67" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A67" s="287"/>
-      <c r="B67" s="284" t="s">
+      <c r="A67" s="301"/>
+      <c r="B67" s="298" t="s">
         <v>32</v>
       </c>
-      <c r="C67" s="285">
+      <c r="C67" s="299">
         <v>1</v>
       </c>
       <c r="D67" s="7">
@@ -4708,16 +4924,16 @@
         <f t="shared" si="4"/>
         <v>49000</v>
       </c>
-      <c r="F67" s="295"/>
+      <c r="F67" s="309"/>
     </row>
     <row r="68" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A68" s="283">
+      <c r="A68" s="297">
         <v>46002</v>
       </c>
-      <c r="B68" s="284" t="s">
+      <c r="B68" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C68" s="285">
+      <c r="C68" s="299">
         <v>3</v>
       </c>
       <c r="D68" s="7">
@@ -4727,17 +4943,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F68" s="293">
+      <c r="F68" s="307">
         <f>SUM(E68:E78)</f>
         <v>541000</v>
       </c>
     </row>
     <row r="69" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A69" s="286"/>
-      <c r="B69" s="284" t="s">
+      <c r="A69" s="300"/>
+      <c r="B69" s="298" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="285">
+      <c r="C69" s="299">
         <v>2</v>
       </c>
       <c r="D69" s="7">
@@ -4747,14 +4963,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F69" s="294"/>
+      <c r="F69" s="308"/>
     </row>
     <row r="70" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A70" s="286"/>
-      <c r="B70" s="284" t="s">
+      <c r="A70" s="300"/>
+      <c r="B70" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="C70" s="285">
+      <c r="C70" s="299">
         <v>4</v>
       </c>
       <c r="D70" s="7">
@@ -4764,14 +4980,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F70" s="294"/>
+      <c r="F70" s="308"/>
     </row>
     <row r="71" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A71" s="286"/>
-      <c r="B71" s="284" t="s">
+      <c r="A71" s="300"/>
+      <c r="B71" s="298" t="s">
         <v>9</v>
       </c>
-      <c r="C71" s="285">
+      <c r="C71" s="299">
         <v>1</v>
       </c>
       <c r="D71" s="7">
@@ -4781,14 +4997,14 @@
         <f t="shared" si="4"/>
         <v>38000</v>
       </c>
-      <c r="F71" s="294"/>
+      <c r="F71" s="308"/>
     </row>
     <row r="72" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A72" s="286"/>
-      <c r="B72" s="284" t="s">
+      <c r="A72" s="300"/>
+      <c r="B72" s="298" t="s">
         <v>10</v>
       </c>
-      <c r="C72" s="285">
+      <c r="C72" s="299">
         <v>1</v>
       </c>
       <c r="D72" s="7">
@@ -4798,14 +5014,14 @@
         <f t="shared" si="4"/>
         <v>20000</v>
       </c>
-      <c r="F72" s="294"/>
+      <c r="F72" s="308"/>
     </row>
     <row r="73" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A73" s="286"/>
-      <c r="B73" s="284" t="s">
+      <c r="A73" s="300"/>
+      <c r="B73" s="298" t="s">
         <v>22</v>
       </c>
-      <c r="C73" s="285">
+      <c r="C73" s="299">
         <v>0.5</v>
       </c>
       <c r="D73" s="7">
@@ -4815,14 +5031,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F73" s="294"/>
+      <c r="F73" s="308"/>
     </row>
     <row r="74" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A74" s="286"/>
-      <c r="B74" s="284" t="s">
+      <c r="A74" s="300"/>
+      <c r="B74" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="C74" s="285">
+      <c r="C74" s="299">
         <v>1</v>
       </c>
       <c r="D74" s="7">
@@ -4832,14 +5048,14 @@
         <f t="shared" si="4"/>
         <v>30000</v>
       </c>
-      <c r="F74" s="294"/>
+      <c r="F74" s="308"/>
     </row>
     <row r="75" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A75" s="286"/>
-      <c r="B75" s="284" t="s">
+      <c r="A75" s="300"/>
+      <c r="B75" s="298" t="s">
         <v>18</v>
       </c>
-      <c r="C75" s="285">
+      <c r="C75" s="299">
         <v>1</v>
       </c>
       <c r="D75" s="7">
@@ -4849,14 +5065,14 @@
         <f t="shared" si="4"/>
         <v>95000</v>
       </c>
-      <c r="F75" s="294"/>
+      <c r="F75" s="308"/>
     </row>
     <row r="76" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A76" s="286"/>
-      <c r="B76" s="284" t="s">
+      <c r="A76" s="300"/>
+      <c r="B76" s="298" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="285">
+      <c r="C76" s="299">
         <v>1</v>
       </c>
       <c r="D76" s="7">
@@ -4866,14 +5082,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F76" s="294"/>
+      <c r="F76" s="308"/>
     </row>
     <row r="77" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A77" s="286"/>
-      <c r="B77" s="284" t="s">
+      <c r="A77" s="300"/>
+      <c r="B77" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C77" s="285">
+      <c r="C77" s="299">
         <v>2</v>
       </c>
       <c r="D77" s="7">
@@ -4883,14 +5099,14 @@
         <f t="shared" si="4"/>
         <v>48000</v>
       </c>
-      <c r="F77" s="294"/>
+      <c r="F77" s="308"/>
     </row>
     <row r="78" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A78" s="287"/>
-      <c r="B78" s="284" t="s">
+      <c r="A78" s="301"/>
+      <c r="B78" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="C78" s="285">
+      <c r="C78" s="299">
         <v>1</v>
       </c>
       <c r="D78" s="7">
@@ -4900,16 +5116,16 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F78" s="295"/>
+      <c r="F78" s="309"/>
     </row>
     <row r="79" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A79" s="283">
+      <c r="A79" s="297">
         <v>46003</v>
       </c>
-      <c r="B79" s="284" t="s">
+      <c r="B79" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C79" s="285">
+      <c r="C79" s="299">
         <v>3</v>
       </c>
       <c r="D79" s="7">
@@ -4919,17 +5135,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F79" s="293">
+      <c r="F79" s="307">
         <f>-SUM(E79:E93)</f>
         <v>-900000</v>
       </c>
     </row>
     <row r="80" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A80" s="286"/>
-      <c r="B80" s="284" t="s">
+      <c r="A80" s="300"/>
+      <c r="B80" s="298" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="285">
+      <c r="C80" s="299">
         <v>2</v>
       </c>
       <c r="D80" s="7">
@@ -4939,14 +5155,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F80" s="294"/>
+      <c r="F80" s="308"/>
     </row>
     <row r="81" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A81" s="286"/>
-      <c r="B81" s="284" t="s">
+      <c r="A81" s="300"/>
+      <c r="B81" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="C81" s="285">
+      <c r="C81" s="299">
         <v>6</v>
       </c>
       <c r="D81" s="7">
@@ -4956,31 +5172,31 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F81" s="294"/>
+      <c r="F81" s="308"/>
     </row>
     <row r="82" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A82" s="286"/>
-      <c r="B82" s="284" t="s">
+      <c r="A82" s="300"/>
+      <c r="B82" s="298" t="s">
         <v>35</v>
       </c>
-      <c r="C82" s="285">
+      <c r="C82" s="299">
         <v>2</v>
       </c>
       <c r="D82" s="7">
         <v>48000</v>
       </c>
       <c r="E82" s="7">
-        <f>SUM(C82*D82)</f>
+        <f t="shared" si="4"/>
         <v>96000</v>
       </c>
-      <c r="F82" s="294"/>
+      <c r="F82" s="308"/>
     </row>
     <row r="83" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A83" s="286"/>
-      <c r="B83" s="284" t="s">
+      <c r="A83" s="300"/>
+      <c r="B83" s="298" t="s">
         <v>24</v>
       </c>
-      <c r="C83" s="285">
+      <c r="C83" s="299">
         <v>8.18</v>
       </c>
       <c r="D83" s="7">
@@ -4989,14 +5205,14 @@
       <c r="E83" s="7">
         <v>123000</v>
       </c>
-      <c r="F83" s="294"/>
+      <c r="F83" s="308"/>
     </row>
     <row r="84" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A84" s="286"/>
-      <c r="B84" s="284" t="s">
+      <c r="A84" s="300"/>
+      <c r="B84" s="298" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="285">
+      <c r="C84" s="299">
         <v>0.3</v>
       </c>
       <c r="D84" s="7">
@@ -5006,14 +5222,14 @@
         <f>SUM(C84*D84)</f>
         <v>6000</v>
       </c>
-      <c r="F84" s="294"/>
+      <c r="F84" s="308"/>
     </row>
     <row r="85" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A85" s="286"/>
-      <c r="B85" s="284" t="s">
+      <c r="A85" s="300"/>
+      <c r="B85" s="298" t="s">
         <v>22</v>
       </c>
-      <c r="C85" s="285">
+      <c r="C85" s="299">
         <v>0.5</v>
       </c>
       <c r="D85" s="7">
@@ -5023,14 +5239,14 @@
         <f>SUM(C85*D85)</f>
         <v>15000</v>
       </c>
-      <c r="F85" s="294"/>
+      <c r="F85" s="308"/>
     </row>
     <row r="86" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A86" s="286"/>
-      <c r="B86" s="284" t="s">
+      <c r="A86" s="300"/>
+      <c r="B86" s="298" t="s">
         <v>31</v>
       </c>
-      <c r="C86" s="285">
+      <c r="C86" s="299">
         <v>0.5</v>
       </c>
       <c r="D86" s="7">
@@ -5040,14 +5256,14 @@
         <f>SUM(C86*D86)</f>
         <v>40000</v>
       </c>
-      <c r="F86" s="294"/>
+      <c r="F86" s="308"/>
     </row>
     <row r="87" s="249" customFormat="1" ht="14" customHeight="1" spans="1:8">
-      <c r="A87" s="286"/>
-      <c r="B87" s="284" t="s">
+      <c r="A87" s="300"/>
+      <c r="B87" s="298" t="s">
         <v>18</v>
       </c>
-      <c r="C87" s="285">
+      <c r="C87" s="299">
         <v>0.5</v>
       </c>
       <c r="D87" s="7">
@@ -5056,139 +5272,139 @@
       <c r="E87" s="7">
         <v>48000</v>
       </c>
-      <c r="F87" s="294"/>
-      <c r="H87" s="275"/>
+      <c r="F87" s="308"/>
+      <c r="H87" s="289"/>
     </row>
     <row r="88" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A88" s="286"/>
-      <c r="B88" s="284" t="s">
+      <c r="A88" s="300"/>
+      <c r="B88" s="298" t="s">
         <v>13</v>
       </c>
-      <c r="C88" s="285">
+      <c r="C88" s="299">
         <v>1</v>
       </c>
       <c r="D88" s="7">
         <v>15000</v>
       </c>
       <c r="E88" s="7">
-        <f>SUM(C88*D88)</f>
+        <f t="shared" ref="E88:E94" si="5">SUM(C88*D88)</f>
         <v>15000</v>
       </c>
-      <c r="F88" s="294"/>
+      <c r="F88" s="308"/>
     </row>
     <row r="89" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A89" s="286"/>
-      <c r="B89" s="284" t="s">
+      <c r="A89" s="300"/>
+      <c r="B89" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C89" s="285">
+      <c r="C89" s="299">
         <v>2</v>
       </c>
       <c r="D89" s="7">
         <v>24000</v>
       </c>
       <c r="E89" s="7">
-        <f>SUM(C89*D89)</f>
+        <f t="shared" si="5"/>
         <v>48000</v>
       </c>
-      <c r="F89" s="294"/>
+      <c r="F89" s="308"/>
     </row>
     <row r="90" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A90" s="286"/>
-      <c r="B90" s="284" t="s">
+      <c r="A90" s="300"/>
+      <c r="B90" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="C90" s="285">
+      <c r="C90" s="299">
         <v>1</v>
       </c>
       <c r="D90" s="7">
         <v>40000</v>
       </c>
       <c r="E90" s="7">
-        <f>SUM(C90*D90)</f>
+        <f t="shared" si="5"/>
         <v>40000</v>
       </c>
-      <c r="F90" s="294"/>
+      <c r="F90" s="308"/>
     </row>
     <row r="91" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A91" s="286"/>
-      <c r="B91" s="284" t="s">
+      <c r="A91" s="300"/>
+      <c r="B91" s="298" t="s">
         <v>32</v>
       </c>
-      <c r="C91" s="285">
+      <c r="C91" s="299">
         <v>1</v>
       </c>
       <c r="D91" s="7">
         <v>49000</v>
       </c>
       <c r="E91" s="7">
-        <f>SUM(C91*D91)</f>
+        <f t="shared" si="5"/>
         <v>49000</v>
       </c>
-      <c r="F91" s="294"/>
+      <c r="F91" s="308"/>
     </row>
     <row r="92" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A92" s="286"/>
-      <c r="B92" s="284" t="s">
+      <c r="A92" s="300"/>
+      <c r="B92" s="298" t="s">
         <v>21</v>
       </c>
-      <c r="C92" s="285">
+      <c r="C92" s="299">
         <v>4</v>
       </c>
       <c r="D92" s="7">
         <v>20000</v>
       </c>
       <c r="E92" s="7">
-        <f>SUM(C92*D92)</f>
+        <f t="shared" si="5"/>
         <v>80000</v>
       </c>
-      <c r="F92" s="294"/>
+      <c r="F92" s="308"/>
     </row>
     <row r="93" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A93" s="287"/>
-      <c r="B93" s="284" t="s">
+      <c r="A93" s="301"/>
+      <c r="B93" s="298" t="s">
         <v>27</v>
       </c>
-      <c r="C93" s="285">
+      <c r="C93" s="299">
         <v>4</v>
       </c>
       <c r="D93" s="7">
         <v>20000</v>
       </c>
       <c r="E93" s="7">
-        <f>SUM(C93*D93)</f>
+        <f t="shared" si="5"/>
         <v>80000</v>
       </c>
-      <c r="F93" s="295"/>
+      <c r="F93" s="309"/>
     </row>
     <row r="94" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A94" s="283">
+      <c r="A94" s="297">
         <v>46004</v>
       </c>
-      <c r="B94" s="290" t="s">
+      <c r="B94" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C94" s="297">
+      <c r="C94" s="311">
         <v>8</v>
       </c>
       <c r="D94" s="7">
         <v>10000</v>
       </c>
       <c r="E94" s="7">
-        <f>SUM(C94*D94)</f>
+        <f t="shared" si="5"/>
         <v>80000</v>
       </c>
-      <c r="F94" s="293">
+      <c r="F94" s="307">
         <f>SUM(E94:E99)</f>
         <v>479000</v>
       </c>
     </row>
     <row r="95" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A95" s="286"/>
-      <c r="B95" s="290" t="s">
+      <c r="A95" s="300"/>
+      <c r="B95" s="304" t="s">
         <v>24</v>
       </c>
-      <c r="C95" s="297">
+      <c r="C95" s="311">
         <v>7.155</v>
       </c>
       <c r="D95" s="7">
@@ -5197,14 +5413,14 @@
       <c r="E95" s="7">
         <v>107000</v>
       </c>
-      <c r="F95" s="294"/>
+      <c r="F95" s="308"/>
     </row>
     <row r="96" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A96" s="286"/>
-      <c r="B96" s="290" t="s">
+      <c r="A96" s="300"/>
+      <c r="B96" s="304" t="s">
         <v>11</v>
       </c>
-      <c r="C96" s="297">
+      <c r="C96" s="311">
         <v>2</v>
       </c>
       <c r="D96" s="7">
@@ -5214,14 +5430,14 @@
         <f>SUM(C96*D96)</f>
         <v>76000</v>
       </c>
-      <c r="F96" s="294"/>
+      <c r="F96" s="308"/>
     </row>
     <row r="97" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A97" s="286"/>
-      <c r="B97" s="290" t="s">
+      <c r="A97" s="300"/>
+      <c r="B97" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C97" s="297">
+      <c r="C97" s="311">
         <v>2</v>
       </c>
       <c r="D97" s="7">
@@ -5231,14 +5447,14 @@
         <f>SUM(C97*D97)</f>
         <v>40000</v>
       </c>
-      <c r="F97" s="294"/>
+      <c r="F97" s="308"/>
     </row>
     <row r="98" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A98" s="286"/>
-      <c r="B98" s="290" t="s">
+      <c r="A98" s="300"/>
+      <c r="B98" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C98" s="297">
+      <c r="C98" s="311">
         <v>4</v>
       </c>
       <c r="D98" s="7">
@@ -5248,14 +5464,14 @@
         <f>SUM(C98*D98)</f>
         <v>96000</v>
       </c>
-      <c r="F98" s="294"/>
+      <c r="F98" s="308"/>
     </row>
     <row r="99" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A99" s="287"/>
-      <c r="B99" s="290" t="s">
+      <c r="A99" s="301"/>
+      <c r="B99" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="C99" s="297">
+      <c r="C99" s="311">
         <v>2</v>
       </c>
       <c r="D99" s="7">
@@ -5265,36 +5481,36 @@
         <f>SUM(C99*D99)</f>
         <v>80000</v>
       </c>
-      <c r="F99" s="295"/>
+      <c r="F99" s="309"/>
     </row>
     <row r="100" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A100" s="298">
+      <c r="A100" s="300">
         <v>46005</v>
       </c>
-      <c r="B100" s="290" t="s">
+      <c r="B100" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C100" s="297">
+      <c r="C100" s="311">
         <v>8</v>
       </c>
       <c r="D100" s="7">
         <v>10000</v>
       </c>
       <c r="E100" s="22">
-        <f t="shared" ref="E100:E108" si="5">SUM(C100*D100)</f>
+        <f t="shared" ref="E100:E108" si="6">SUM(C100*D100)</f>
         <v>80000</v>
       </c>
-      <c r="F100" s="301">
+      <c r="F100" s="310">
         <f>SUM(E100:E108)</f>
         <v>506000</v>
       </c>
     </row>
     <row r="101" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A101" s="298"/>
-      <c r="B101" s="290" t="s">
+      <c r="A101" s="300"/>
+      <c r="B101" s="304" t="s">
         <v>24</v>
       </c>
-      <c r="C101" s="297">
+      <c r="C101" s="311">
         <v>8.23</v>
       </c>
       <c r="D101" s="7">
@@ -5303,155 +5519,155 @@
       <c r="E101" s="22">
         <v>123000</v>
       </c>
-      <c r="F101" s="302"/>
+      <c r="F101" s="311"/>
     </row>
     <row r="102" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A102" s="298"/>
-      <c r="B102" s="290" t="s">
+      <c r="A102" s="300"/>
+      <c r="B102" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C102" s="297">
+      <c r="C102" s="311">
         <v>2</v>
       </c>
       <c r="D102" s="7">
         <v>20000</v>
       </c>
       <c r="E102" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>40000</v>
       </c>
-      <c r="F102" s="302"/>
+      <c r="F102" s="311"/>
     </row>
     <row r="103" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A103" s="298"/>
-      <c r="B103" s="290" t="s">
+      <c r="A103" s="300"/>
+      <c r="B103" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="C103" s="297">
+      <c r="C103" s="311">
         <v>0.3</v>
       </c>
       <c r="D103" s="7">
         <v>20000</v>
       </c>
       <c r="E103" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6000</v>
       </c>
-      <c r="F103" s="302"/>
+      <c r="F103" s="311"/>
     </row>
     <row r="104" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A104" s="298"/>
-      <c r="B104" s="290" t="s">
+      <c r="A104" s="300"/>
+      <c r="B104" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="C104" s="297">
+      <c r="C104" s="311">
         <v>1</v>
       </c>
       <c r="D104" s="7">
         <v>15000</v>
       </c>
       <c r="E104" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>15000</v>
       </c>
-      <c r="F104" s="302"/>
+      <c r="F104" s="311"/>
     </row>
     <row r="105" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A105" s="298"/>
-      <c r="B105" s="290" t="s">
+      <c r="A105" s="300"/>
+      <c r="B105" s="304" t="s">
         <v>36</v>
       </c>
-      <c r="C105" s="297">
+      <c r="C105" s="311">
         <v>1</v>
       </c>
       <c r="D105" s="7">
         <v>48000</v>
       </c>
       <c r="E105" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>48000</v>
       </c>
-      <c r="F105" s="302"/>
+      <c r="F105" s="311"/>
     </row>
     <row r="106" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A106" s="298"/>
-      <c r="B106" s="290" t="s">
+      <c r="A106" s="300"/>
+      <c r="B106" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C106" s="297">
+      <c r="C106" s="311">
         <v>5</v>
       </c>
       <c r="D106" s="7">
         <v>24000</v>
       </c>
       <c r="E106" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>120000</v>
       </c>
-      <c r="F106" s="302"/>
+      <c r="F106" s="311"/>
     </row>
     <row r="107" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A107" s="298"/>
-      <c r="B107" s="290" t="s">
+      <c r="A107" s="300"/>
+      <c r="B107" s="304" t="s">
         <v>32</v>
       </c>
-      <c r="C107" s="297">
+      <c r="C107" s="311">
         <v>1</v>
       </c>
       <c r="D107" s="7">
         <v>49000</v>
       </c>
       <c r="E107" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>49000</v>
       </c>
-      <c r="F107" s="302"/>
+      <c r="F107" s="311"/>
     </row>
     <row r="108" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A108" s="298"/>
-      <c r="B108" s="290" t="s">
+      <c r="A108" s="300"/>
+      <c r="B108" s="304" t="s">
         <v>37</v>
       </c>
-      <c r="C108" s="297">
+      <c r="C108" s="311">
         <v>1</v>
       </c>
       <c r="D108" s="7">
         <v>25000</v>
       </c>
       <c r="E108" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>25000</v>
       </c>
-      <c r="F108" s="302"/>
+      <c r="F108" s="311"/>
     </row>
     <row r="109" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A109" s="299">
+      <c r="A109" s="297">
         <v>46006</v>
       </c>
-      <c r="B109" s="290" t="s">
+      <c r="B109" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C109" s="297">
+      <c r="C109" s="311">
         <v>4</v>
       </c>
       <c r="D109" s="7">
         <v>10000</v>
       </c>
       <c r="E109" s="7">
-        <f t="shared" ref="E109:E154" si="6">SUM(C109*D109)</f>
+        <f t="shared" ref="E109:E154" si="7">SUM(C109*D109)</f>
         <v>40000</v>
       </c>
-      <c r="F109" s="303">
+      <c r="F109" s="307">
         <f>SUM(E109:E121)</f>
         <v>630000</v>
       </c>
     </row>
     <row r="110" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A110" s="298"/>
-      <c r="B110" s="290" t="s">
+      <c r="A110" s="300"/>
+      <c r="B110" s="304" t="s">
         <v>24</v>
       </c>
-      <c r="C110" s="297">
+      <c r="C110" s="311">
         <v>3.43</v>
       </c>
       <c r="D110" s="7">
@@ -5460,99 +5676,99 @@
       <c r="E110" s="7">
         <v>51000</v>
       </c>
-      <c r="F110" s="304"/>
+      <c r="F110" s="308"/>
     </row>
     <row r="111" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A111" s="298"/>
-      <c r="B111" s="290" t="s">
+      <c r="A111" s="300"/>
+      <c r="B111" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C111" s="297">
+      <c r="C111" s="311">
         <v>2</v>
       </c>
       <c r="D111" s="7">
         <v>20000</v>
       </c>
       <c r="E111" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F111" s="304"/>
+      <c r="F111" s="308"/>
     </row>
     <row r="112" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A112" s="298"/>
-      <c r="B112" s="290" t="s">
+      <c r="A112" s="300"/>
+      <c r="B112" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="C112" s="297">
+      <c r="C112" s="311">
         <v>0.3</v>
       </c>
       <c r="D112" s="7">
         <v>20000</v>
       </c>
       <c r="E112" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6000</v>
       </c>
-      <c r="F112" s="304"/>
+      <c r="F112" s="308"/>
     </row>
     <row r="113" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A113" s="298"/>
-      <c r="B113" s="290" t="s">
+      <c r="A113" s="300"/>
+      <c r="B113" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="C113" s="297">
+      <c r="C113" s="311">
         <v>2</v>
       </c>
       <c r="D113" s="7">
         <v>15000</v>
       </c>
       <c r="E113" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>30000</v>
       </c>
-      <c r="F113" s="304"/>
+      <c r="F113" s="308"/>
     </row>
     <row r="114" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A114" s="298"/>
-      <c r="B114" s="290" t="s">
+      <c r="A114" s="300"/>
+      <c r="B114" s="304" t="s">
         <v>36</v>
       </c>
-      <c r="C114" s="297">
+      <c r="C114" s="311">
         <v>2</v>
       </c>
       <c r="D114" s="7">
         <v>48000</v>
       </c>
       <c r="E114" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>96000</v>
       </c>
-      <c r="F114" s="304"/>
+      <c r="F114" s="308"/>
     </row>
     <row r="115" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A115" s="298"/>
-      <c r="B115" s="290" t="s">
+      <c r="A115" s="300"/>
+      <c r="B115" s="304" t="s">
         <v>38</v>
       </c>
-      <c r="C115" s="297">
+      <c r="C115" s="311">
         <v>1</v>
       </c>
       <c r="D115" s="7">
         <v>45000</v>
       </c>
       <c r="E115" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>45000</v>
       </c>
-      <c r="F115" s="304"/>
+      <c r="F115" s="308"/>
     </row>
     <row r="116" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A116" s="298"/>
-      <c r="B116" s="290" t="s">
+      <c r="A116" s="300"/>
+      <c r="B116" s="304" t="s">
         <v>11</v>
       </c>
-      <c r="C116" s="297">
+      <c r="C116" s="311">
         <v>1.2</v>
       </c>
       <c r="D116" s="7">
@@ -5561,2083 +5777,2136 @@
       <c r="E116" s="7">
         <v>46000</v>
       </c>
-      <c r="F116" s="304"/>
+      <c r="F116" s="308"/>
     </row>
     <row r="117" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A117" s="298"/>
-      <c r="B117" s="290" t="s">
+      <c r="A117" s="300"/>
+      <c r="B117" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C117" s="297">
+      <c r="C117" s="311">
         <v>0.5</v>
       </c>
       <c r="D117" s="7">
         <v>30000</v>
       </c>
       <c r="E117" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>15000</v>
       </c>
-      <c r="F117" s="304"/>
+      <c r="F117" s="308"/>
     </row>
     <row r="118" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A118" s="298"/>
-      <c r="B118" s="290" t="s">
+      <c r="A118" s="300"/>
+      <c r="B118" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C118" s="297">
+      <c r="C118" s="311">
         <v>3</v>
       </c>
       <c r="D118" s="7">
         <v>24000</v>
       </c>
       <c r="E118" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>72000</v>
       </c>
-      <c r="F118" s="304"/>
+      <c r="F118" s="308"/>
     </row>
     <row r="119" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A119" s="298"/>
-      <c r="B119" s="290" t="s">
+      <c r="A119" s="300"/>
+      <c r="B119" s="304" t="s">
         <v>32</v>
       </c>
-      <c r="C119" s="297">
+      <c r="C119" s="311">
         <v>1</v>
       </c>
       <c r="D119" s="7">
         <v>49000</v>
       </c>
       <c r="E119" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>49000</v>
       </c>
-      <c r="F119" s="304"/>
+      <c r="F119" s="308"/>
     </row>
     <row r="120" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A120" s="298"/>
-      <c r="B120" s="290" t="s">
+      <c r="A120" s="300"/>
+      <c r="B120" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="C120" s="297">
+      <c r="C120" s="311">
         <v>1</v>
       </c>
       <c r="D120" s="7">
         <v>40000</v>
       </c>
       <c r="E120" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F120" s="304"/>
+      <c r="F120" s="308"/>
     </row>
     <row r="121" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A121" s="300"/>
-      <c r="B121" s="290" t="s">
+      <c r="A121" s="301"/>
+      <c r="B121" s="304" t="s">
         <v>27</v>
       </c>
-      <c r="C121" s="297">
+      <c r="C121" s="311">
         <v>5</v>
       </c>
       <c r="D121" s="7">
         <v>20000</v>
       </c>
       <c r="E121" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="F121" s="305"/>
+      <c r="F121" s="309"/>
     </row>
     <row r="122" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A122" s="291"/>
-      <c r="B122" s="290"/>
-      <c r="C122" s="297"/>
-      <c r="D122" s="7"/>
+      <c r="A122" s="312">
+        <v>46007</v>
+      </c>
+      <c r="B122" s="304" t="s">
+        <v>8</v>
+      </c>
+      <c r="C122" s="311">
+        <v>5</v>
+      </c>
+      <c r="D122" s="7">
+        <v>10000</v>
+      </c>
       <c r="E122" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F122" s="306"/>
+        <f t="shared" si="7"/>
+        <v>50000</v>
+      </c>
+      <c r="F122" s="315">
+        <f>SUM(E122:E128)</f>
+        <v>412000</v>
+      </c>
     </row>
     <row r="123" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A123" s="291"/>
-      <c r="B123" s="290"/>
-      <c r="C123" s="297"/>
-      <c r="D123" s="7"/>
+      <c r="A123" s="313"/>
+      <c r="B123" s="304" t="s">
+        <v>24</v>
+      </c>
+      <c r="C123" s="311">
+        <v>6.15</v>
+      </c>
+      <c r="D123" s="7">
+        <v>15000</v>
+      </c>
       <c r="E123" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F123" s="306"/>
+        <v>92000</v>
+      </c>
+      <c r="F123" s="316"/>
     </row>
     <row r="124" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A124" s="291"/>
-      <c r="B124" s="290"/>
-      <c r="C124" s="297"/>
-      <c r="D124" s="7"/>
+      <c r="A124" s="313"/>
+      <c r="B124" s="304" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="311">
+        <v>2</v>
+      </c>
+      <c r="D124" s="7">
+        <v>20000</v>
+      </c>
       <c r="E124" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F124" s="306"/>
+        <f t="shared" si="7"/>
+        <v>40000</v>
+      </c>
+      <c r="F124" s="316"/>
     </row>
     <row r="125" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A125" s="291"/>
-      <c r="B125" s="290"/>
-      <c r="C125" s="297"/>
-      <c r="D125" s="7"/>
+      <c r="A125" s="313"/>
+      <c r="B125" s="304" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125" s="311">
+        <v>0.3</v>
+      </c>
+      <c r="D125" s="7">
+        <v>15000</v>
+      </c>
       <c r="E125" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F125" s="306"/>
+        <v>5000</v>
+      </c>
+      <c r="F125" s="316"/>
     </row>
     <row r="126" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A126" s="291"/>
-      <c r="B126" s="290"/>
-      <c r="C126" s="297"/>
-      <c r="D126" s="7"/>
+      <c r="A126" s="313"/>
+      <c r="B126" s="304" t="s">
+        <v>14</v>
+      </c>
+      <c r="C126" s="311">
+        <v>4</v>
+      </c>
+      <c r="D126" s="7">
+        <v>24000</v>
+      </c>
       <c r="E126" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F126" s="306"/>
+        <f t="shared" si="7"/>
+        <v>96000</v>
+      </c>
+      <c r="F126" s="316"/>
     </row>
     <row r="127" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A127" s="291"/>
-      <c r="B127" s="290"/>
-      <c r="C127" s="297"/>
-      <c r="D127" s="7"/>
+      <c r="A127" s="313"/>
+      <c r="B127" s="304" t="s">
+        <v>32</v>
+      </c>
+      <c r="C127" s="311">
+        <v>1</v>
+      </c>
+      <c r="D127" s="7">
+        <v>49000</v>
+      </c>
       <c r="E127" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F127" s="306"/>
+        <f t="shared" si="7"/>
+        <v>49000</v>
+      </c>
+      <c r="F127" s="316"/>
     </row>
     <row r="128" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A128" s="291"/>
-      <c r="B128" s="290"/>
-      <c r="C128" s="297"/>
-      <c r="D128" s="7"/>
+      <c r="A128" s="314"/>
+      <c r="B128" s="304" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128" s="311">
+        <v>2</v>
+      </c>
+      <c r="D128" s="7">
+        <v>40000</v>
+      </c>
       <c r="E128" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F128" s="306">
-        <f>SUM(E128:E143)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>80000</v>
+      </c>
+      <c r="F128" s="317"/>
     </row>
     <row r="129" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A129" s="291"/>
-      <c r="B129" s="290"/>
-      <c r="C129" s="297"/>
-      <c r="D129" s="7"/>
+      <c r="A129" s="305">
+        <v>46007</v>
+      </c>
+      <c r="B129" s="304" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="311">
+        <v>3</v>
+      </c>
+      <c r="D129" s="7">
+        <v>70000</v>
+      </c>
       <c r="E129" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F129" s="306"/>
+        <f t="shared" si="7"/>
+        <v>210000</v>
+      </c>
+      <c r="F129" s="320">
+        <f>SUM(E129)</f>
+        <v>210000</v>
+      </c>
     </row>
     <row r="130" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A130" s="291"/>
-      <c r="B130" s="290"/>
-      <c r="C130" s="297"/>
+      <c r="A130" s="305"/>
+      <c r="B130" s="304"/>
+      <c r="C130" s="311"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F130" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F130" s="320"/>
     </row>
     <row r="131" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A131" s="291"/>
-      <c r="B131" s="290"/>
-      <c r="C131" s="297"/>
+      <c r="A131" s="305"/>
+      <c r="B131" s="304"/>
+      <c r="C131" s="311"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F131" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F131" s="320"/>
     </row>
     <row r="132" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A132" s="291"/>
-      <c r="B132" s="290"/>
-      <c r="C132" s="297"/>
+      <c r="A132" s="305"/>
+      <c r="B132" s="304"/>
+      <c r="C132" s="311"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F132" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F132" s="320"/>
     </row>
     <row r="133" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A133" s="291"/>
-      <c r="B133" s="290"/>
-      <c r="C133" s="297"/>
+      <c r="A133" s="305"/>
+      <c r="B133" s="304"/>
+      <c r="C133" s="311"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F133" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F133" s="320"/>
     </row>
     <row r="134" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A134" s="291"/>
-      <c r="B134" s="290"/>
-      <c r="C134" s="297"/>
+      <c r="A134" s="305"/>
+      <c r="B134" s="304"/>
+      <c r="C134" s="311"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F134" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F134" s="320"/>
     </row>
     <row r="135" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A135" s="291"/>
-      <c r="B135" s="290"/>
-      <c r="C135" s="297"/>
+      <c r="A135" s="305"/>
+      <c r="B135" s="304"/>
+      <c r="C135" s="311"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F135" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F135" s="320"/>
     </row>
     <row r="136" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A136" s="291"/>
-      <c r="B136" s="290"/>
-      <c r="C136" s="297"/>
+      <c r="A136" s="305"/>
+      <c r="B136" s="304"/>
+      <c r="C136" s="311"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F136" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F136" s="320"/>
     </row>
     <row r="137" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A137" s="291"/>
-      <c r="B137" s="290"/>
-      <c r="C137" s="297"/>
+      <c r="A137" s="305"/>
+      <c r="B137" s="304"/>
+      <c r="C137" s="311"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F137" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F137" s="320"/>
     </row>
     <row r="138" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A138" s="291"/>
-      <c r="B138" s="290"/>
-      <c r="C138" s="297"/>
+      <c r="A138" s="305"/>
+      <c r="B138" s="304"/>
+      <c r="C138" s="311"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F138" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F138" s="320"/>
     </row>
     <row r="139" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A139" s="291"/>
-      <c r="B139" s="290"/>
-      <c r="C139" s="297"/>
+      <c r="A139" s="305"/>
+      <c r="B139" s="304"/>
+      <c r="C139" s="311"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F139" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F139" s="320"/>
     </row>
     <row r="140" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A140" s="291"/>
-      <c r="B140" s="290"/>
-      <c r="C140" s="297"/>
+      <c r="A140" s="305"/>
+      <c r="B140" s="304"/>
+      <c r="C140" s="311"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F140" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F140" s="320"/>
     </row>
     <row r="141" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A141" s="291"/>
-      <c r="B141" s="290"/>
-      <c r="C141" s="297"/>
+      <c r="A141" s="305"/>
+      <c r="B141" s="304"/>
+      <c r="C141" s="311"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F141" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F141" s="320"/>
     </row>
     <row r="142" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A142" s="291"/>
-      <c r="B142" s="290"/>
-      <c r="C142" s="297"/>
+      <c r="A142" s="305"/>
+      <c r="B142" s="304"/>
+      <c r="C142" s="311"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F142" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F142" s="320"/>
     </row>
     <row r="143" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A143" s="291"/>
-      <c r="B143" s="290"/>
-      <c r="C143" s="297"/>
+      <c r="A143" s="305"/>
+      <c r="B143" s="304"/>
+      <c r="C143" s="311"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F143" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F143" s="320"/>
     </row>
     <row r="144" s="249" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A144" s="291"/>
-      <c r="B144" s="290"/>
-      <c r="C144" s="297"/>
+      <c r="A144" s="305"/>
+      <c r="B144" s="304"/>
+      <c r="C144" s="311"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F144" s="306">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F144" s="320">
         <f>SUM(E144)</f>
         <v>0</v>
       </c>
     </row>
     <row r="145" s="249" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A145" s="291"/>
-      <c r="B145" s="290"/>
-      <c r="C145" s="297"/>
+      <c r="A145" s="305"/>
+      <c r="B145" s="304"/>
+      <c r="C145" s="311"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F145" s="306">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F145" s="320">
         <f>SUM(E145:E149)</f>
         <v>0</v>
       </c>
-      <c r="G145" s="275"/>
+      <c r="G145" s="289"/>
     </row>
     <row r="146" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A146" s="291"/>
-      <c r="B146" s="290"/>
-      <c r="C146" s="297"/>
+      <c r="A146" s="305"/>
+      <c r="B146" s="304"/>
+      <c r="C146" s="311"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F146" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F146" s="320"/>
     </row>
     <row r="147" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A147" s="291"/>
-      <c r="B147" s="290"/>
-      <c r="C147" s="297"/>
+      <c r="A147" s="305"/>
+      <c r="B147" s="304"/>
+      <c r="C147" s="311"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F147" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F147" s="320"/>
     </row>
     <row r="148" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A148" s="291"/>
-      <c r="B148" s="290"/>
-      <c r="C148" s="297"/>
+      <c r="A148" s="305"/>
+      <c r="B148" s="304"/>
+      <c r="C148" s="311"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F148" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F148" s="320"/>
     </row>
     <row r="149" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A149" s="291"/>
-      <c r="B149" s="290"/>
-      <c r="C149" s="297"/>
+      <c r="A149" s="305"/>
+      <c r="B149" s="304"/>
+      <c r="C149" s="311"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F149" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F149" s="320"/>
     </row>
     <row r="150" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A150" s="291"/>
-      <c r="B150" s="307"/>
-      <c r="C150" s="308"/>
+      <c r="A150" s="305"/>
+      <c r="B150" s="318"/>
+      <c r="C150" s="319"/>
       <c r="D150" s="134"/>
       <c r="E150" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F150" s="306">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F150" s="320">
         <f>SUM(E150:E156)</f>
         <v>0</v>
       </c>
     </row>
     <row r="151" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A151" s="291"/>
-      <c r="B151" s="290"/>
-      <c r="C151" s="297"/>
+      <c r="A151" s="305"/>
+      <c r="B151" s="304"/>
+      <c r="C151" s="311"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F151" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F151" s="320"/>
     </row>
     <row r="152" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A152" s="291"/>
-      <c r="B152" s="290"/>
-      <c r="C152" s="297"/>
+      <c r="A152" s="305"/>
+      <c r="B152" s="304"/>
+      <c r="C152" s="311"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F152" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F152" s="320"/>
     </row>
     <row r="153" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A153" s="291"/>
-      <c r="B153" s="290"/>
-      <c r="C153" s="297"/>
+      <c r="A153" s="305"/>
+      <c r="B153" s="304"/>
+      <c r="C153" s="311"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F153" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F153" s="320"/>
     </row>
     <row r="154" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A154" s="291"/>
-      <c r="B154" s="290"/>
-      <c r="C154" s="297"/>
+      <c r="A154" s="305"/>
+      <c r="B154" s="304"/>
+      <c r="C154" s="311"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F154" s="306"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F154" s="320"/>
     </row>
     <row r="155" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A155" s="291"/>
-      <c r="B155" s="290"/>
-      <c r="C155" s="297"/>
+      <c r="A155" s="305"/>
+      <c r="B155" s="304"/>
+      <c r="C155" s="311"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7">
-        <f t="shared" ref="E155:E218" si="7">SUM(C155*D155)</f>
-        <v>0</v>
-      </c>
-      <c r="F155" s="306"/>
+        <f t="shared" ref="E155:E218" si="8">SUM(C155*D155)</f>
+        <v>0</v>
+      </c>
+      <c r="F155" s="320"/>
     </row>
     <row r="156" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A156" s="291"/>
-      <c r="B156" s="290"/>
-      <c r="C156" s="297"/>
-      <c r="D156" s="266"/>
+      <c r="A156" s="305"/>
+      <c r="B156" s="304"/>
+      <c r="C156" s="311"/>
+      <c r="D156" s="277"/>
       <c r="E156" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F156" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F156" s="320"/>
     </row>
     <row r="157" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A157" s="291"/>
-      <c r="B157" s="290"/>
-      <c r="C157" s="297"/>
+      <c r="A157" s="305"/>
+      <c r="B157" s="304"/>
+      <c r="C157" s="311"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F157" s="306">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F157" s="320">
         <f>SUM(E157:E164)</f>
         <v>0</v>
       </c>
     </row>
     <row r="158" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A158" s="291"/>
-      <c r="B158" s="290"/>
-      <c r="C158" s="297"/>
+      <c r="A158" s="305"/>
+      <c r="B158" s="304"/>
+      <c r="C158" s="311"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F158" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F158" s="320"/>
     </row>
     <row r="159" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A159" s="291"/>
-      <c r="B159" s="290"/>
-      <c r="C159" s="297"/>
+      <c r="A159" s="305"/>
+      <c r="B159" s="304"/>
+      <c r="C159" s="311"/>
       <c r="D159" s="7"/>
       <c r="E159" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F159" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F159" s="320"/>
     </row>
     <row r="160" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A160" s="291"/>
-      <c r="B160" s="290"/>
-      <c r="C160" s="297"/>
+      <c r="A160" s="305"/>
+      <c r="B160" s="304"/>
+      <c r="C160" s="311"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F160" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F160" s="320"/>
     </row>
     <row r="161" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A161" s="291"/>
-      <c r="B161" s="290"/>
-      <c r="C161" s="297"/>
+      <c r="A161" s="305"/>
+      <c r="B161" s="304"/>
+      <c r="C161" s="311"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F161" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F161" s="320"/>
     </row>
     <row r="162" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A162" s="291"/>
-      <c r="B162" s="290"/>
-      <c r="C162" s="297"/>
+      <c r="A162" s="305"/>
+      <c r="B162" s="304"/>
+      <c r="C162" s="311"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F162" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F162" s="320"/>
     </row>
     <row r="163" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A163" s="291"/>
-      <c r="B163" s="290"/>
-      <c r="C163" s="297"/>
+      <c r="A163" s="305"/>
+      <c r="B163" s="304"/>
+      <c r="C163" s="311"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F163" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F163" s="320"/>
     </row>
     <row r="164" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A164" s="291"/>
-      <c r="B164" s="290"/>
-      <c r="C164" s="297"/>
+      <c r="A164" s="305"/>
+      <c r="B164" s="304"/>
+      <c r="C164" s="311"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F164" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F164" s="320"/>
     </row>
     <row r="165" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A165" s="291"/>
-      <c r="B165" s="290"/>
-      <c r="C165" s="297"/>
+      <c r="A165" s="305"/>
+      <c r="B165" s="304"/>
+      <c r="C165" s="311"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F165" s="306">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F165" s="320">
         <f>SUM(E165:E171)</f>
         <v>0</v>
       </c>
     </row>
     <row r="166" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A166" s="291"/>
-      <c r="B166" s="290"/>
-      <c r="C166" s="297"/>
+      <c r="A166" s="305"/>
+      <c r="B166" s="304"/>
+      <c r="C166" s="311"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F166" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F166" s="320"/>
     </row>
     <row r="167" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A167" s="291"/>
-      <c r="B167" s="290"/>
-      <c r="C167" s="297"/>
+      <c r="A167" s="305"/>
+      <c r="B167" s="304"/>
+      <c r="C167" s="311"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F167" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F167" s="320"/>
     </row>
     <row r="168" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A168" s="291"/>
-      <c r="B168" s="290"/>
-      <c r="C168" s="297"/>
+      <c r="A168" s="305"/>
+      <c r="B168" s="304"/>
+      <c r="C168" s="311"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F168" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F168" s="320"/>
     </row>
     <row r="169" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A169" s="291"/>
-      <c r="B169" s="290"/>
-      <c r="C169" s="297"/>
+      <c r="A169" s="305"/>
+      <c r="B169" s="304"/>
+      <c r="C169" s="311"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F169" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F169" s="320"/>
     </row>
     <row r="170" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A170" s="291"/>
-      <c r="B170" s="290"/>
-      <c r="C170" s="297"/>
+      <c r="A170" s="305"/>
+      <c r="B170" s="304"/>
+      <c r="C170" s="311"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F170" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F170" s="320"/>
     </row>
     <row r="171" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A171" s="291"/>
-      <c r="B171" s="290"/>
-      <c r="C171" s="297"/>
+      <c r="A171" s="305"/>
+      <c r="B171" s="304"/>
+      <c r="C171" s="311"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F171" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F171" s="320"/>
     </row>
     <row r="172" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A172" s="291"/>
-      <c r="B172" s="290"/>
-      <c r="C172" s="297"/>
+      <c r="A172" s="305"/>
+      <c r="B172" s="304"/>
+      <c r="C172" s="311"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F172" s="306">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F172" s="320">
         <f>SUM(E172:E181)</f>
         <v>0</v>
       </c>
     </row>
     <row r="173" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A173" s="291"/>
-      <c r="B173" s="290"/>
-      <c r="C173" s="297"/>
+      <c r="A173" s="305"/>
+      <c r="B173" s="304"/>
+      <c r="C173" s="311"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F173" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F173" s="320"/>
     </row>
     <row r="174" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A174" s="291"/>
-      <c r="B174" s="290"/>
-      <c r="C174" s="297"/>
+      <c r="A174" s="305"/>
+      <c r="B174" s="304"/>
+      <c r="C174" s="311"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F174" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F174" s="320"/>
     </row>
     <row r="175" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A175" s="291"/>
-      <c r="B175" s="290"/>
-      <c r="C175" s="297"/>
+      <c r="A175" s="305"/>
+      <c r="B175" s="304"/>
+      <c r="C175" s="311"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F175" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F175" s="320"/>
     </row>
     <row r="176" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A176" s="291"/>
-      <c r="B176" s="290"/>
-      <c r="C176" s="297"/>
+      <c r="A176" s="305"/>
+      <c r="B176" s="304"/>
+      <c r="C176" s="311"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F176" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F176" s="320"/>
     </row>
     <row r="177" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A177" s="291"/>
-      <c r="B177" s="290"/>
-      <c r="C177" s="297"/>
+      <c r="A177" s="305"/>
+      <c r="B177" s="304"/>
+      <c r="C177" s="311"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F177" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F177" s="320"/>
     </row>
     <row r="178" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A178" s="291"/>
-      <c r="B178" s="290"/>
-      <c r="C178" s="297"/>
+      <c r="A178" s="305"/>
+      <c r="B178" s="304"/>
+      <c r="C178" s="311"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F178" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F178" s="320"/>
     </row>
     <row r="179" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A179" s="291"/>
-      <c r="B179" s="290"/>
-      <c r="C179" s="297"/>
+      <c r="A179" s="305"/>
+      <c r="B179" s="304"/>
+      <c r="C179" s="311"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F179" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F179" s="320"/>
     </row>
     <row r="180" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A180" s="291"/>
-      <c r="B180" s="290"/>
-      <c r="C180" s="297"/>
+      <c r="A180" s="305"/>
+      <c r="B180" s="304"/>
+      <c r="C180" s="311"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F180" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F180" s="320"/>
     </row>
     <row r="181" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A181" s="291"/>
-      <c r="B181" s="290"/>
-      <c r="C181" s="297"/>
+      <c r="A181" s="305"/>
+      <c r="B181" s="304"/>
+      <c r="C181" s="311"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F181" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F181" s="320"/>
     </row>
     <row r="182" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A182" s="291"/>
-      <c r="B182" s="290"/>
-      <c r="C182" s="297"/>
+      <c r="A182" s="305"/>
+      <c r="B182" s="304"/>
+      <c r="C182" s="311"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F182" s="306">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F182" s="320">
         <f>SUM(E182:E195)</f>
         <v>0</v>
       </c>
     </row>
     <row r="183" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A183" s="291"/>
-      <c r="B183" s="290"/>
-      <c r="C183" s="297"/>
+      <c r="A183" s="305"/>
+      <c r="B183" s="304"/>
+      <c r="C183" s="311"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F183" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F183" s="320"/>
     </row>
     <row r="184" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A184" s="291"/>
-      <c r="B184" s="290"/>
-      <c r="C184" s="297"/>
+      <c r="A184" s="305"/>
+      <c r="B184" s="304"/>
+      <c r="C184" s="311"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F184" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F184" s="320"/>
     </row>
     <row r="185" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A185" s="291"/>
-      <c r="B185" s="290"/>
-      <c r="C185" s="297"/>
+      <c r="A185" s="305"/>
+      <c r="B185" s="304"/>
+      <c r="C185" s="311"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F185" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F185" s="320"/>
     </row>
     <row r="186" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A186" s="291"/>
-      <c r="B186" s="290"/>
-      <c r="C186" s="297"/>
+      <c r="A186" s="305"/>
+      <c r="B186" s="304"/>
+      <c r="C186" s="311"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F186" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F186" s="320"/>
     </row>
     <row r="187" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A187" s="291"/>
-      <c r="B187" s="290"/>
-      <c r="C187" s="297"/>
+      <c r="A187" s="305"/>
+      <c r="B187" s="304"/>
+      <c r="C187" s="311"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F187" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F187" s="320"/>
     </row>
     <row r="188" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A188" s="291"/>
-      <c r="B188" s="290"/>
-      <c r="C188" s="297"/>
+      <c r="A188" s="305"/>
+      <c r="B188" s="304"/>
+      <c r="C188" s="311"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F188" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F188" s="320"/>
     </row>
     <row r="189" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A189" s="291"/>
-      <c r="B189" s="290"/>
-      <c r="C189" s="297"/>
+      <c r="A189" s="305"/>
+      <c r="B189" s="304"/>
+      <c r="C189" s="311"/>
       <c r="D189" s="7"/>
       <c r="E189" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F189" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F189" s="320"/>
     </row>
     <row r="190" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A190" s="291"/>
-      <c r="B190" s="290"/>
-      <c r="C190" s="297"/>
+      <c r="A190" s="305"/>
+      <c r="B190" s="304"/>
+      <c r="C190" s="311"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F190" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F190" s="320"/>
     </row>
     <row r="191" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A191" s="291"/>
-      <c r="B191" s="290"/>
-      <c r="C191" s="297"/>
+      <c r="A191" s="305"/>
+      <c r="B191" s="304"/>
+      <c r="C191" s="311"/>
       <c r="D191" s="7"/>
       <c r="E191" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F191" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F191" s="320"/>
     </row>
     <row r="192" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A192" s="291"/>
-      <c r="B192" s="290"/>
-      <c r="C192" s="297"/>
+      <c r="A192" s="305"/>
+      <c r="B192" s="304"/>
+      <c r="C192" s="311"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F192" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F192" s="320"/>
     </row>
     <row r="193" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A193" s="291"/>
-      <c r="B193" s="290"/>
-      <c r="C193" s="297"/>
+      <c r="A193" s="305"/>
+      <c r="B193" s="304"/>
+      <c r="C193" s="311"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F193" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F193" s="320"/>
     </row>
     <row r="194" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A194" s="291"/>
-      <c r="B194" s="290"/>
-      <c r="C194" s="297"/>
+      <c r="A194" s="305"/>
+      <c r="B194" s="304"/>
+      <c r="C194" s="311"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F194" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F194" s="320"/>
     </row>
     <row r="195" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A195" s="291"/>
-      <c r="B195" s="290"/>
-      <c r="C195" s="297"/>
+      <c r="A195" s="305"/>
+      <c r="B195" s="304"/>
+      <c r="C195" s="311"/>
       <c r="D195" s="7"/>
       <c r="E195" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F195" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F195" s="320"/>
     </row>
     <row r="196" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A196" s="291"/>
-      <c r="B196" s="290"/>
-      <c r="C196" s="297"/>
+      <c r="A196" s="305"/>
+      <c r="B196" s="304"/>
+      <c r="C196" s="311"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F196" s="306">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F196" s="320">
         <f>SUM(E196)</f>
         <v>0</v>
       </c>
     </row>
     <row r="197" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A197" s="291"/>
-      <c r="B197" s="290"/>
-      <c r="C197" s="297"/>
+      <c r="A197" s="305"/>
+      <c r="B197" s="304"/>
+      <c r="C197" s="311"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F197" s="306">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F197" s="320">
         <f>SUM(E197:E212)</f>
         <v>0</v>
       </c>
     </row>
     <row r="198" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A198" s="291"/>
-      <c r="B198" s="290"/>
-      <c r="C198" s="297"/>
+      <c r="A198" s="305"/>
+      <c r="B198" s="304"/>
+      <c r="C198" s="311"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F198" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F198" s="320"/>
     </row>
     <row r="199" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A199" s="291"/>
-      <c r="B199" s="290"/>
-      <c r="C199" s="297"/>
+      <c r="A199" s="305"/>
+      <c r="B199" s="304"/>
+      <c r="C199" s="311"/>
       <c r="D199" s="7"/>
       <c r="E199" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F199" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F199" s="320"/>
     </row>
     <row r="200" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A200" s="291"/>
-      <c r="B200" s="290"/>
-      <c r="C200" s="297"/>
+      <c r="A200" s="305"/>
+      <c r="B200" s="304"/>
+      <c r="C200" s="311"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F200" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F200" s="320"/>
     </row>
     <row r="201" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A201" s="291"/>
-      <c r="B201" s="290"/>
-      <c r="C201" s="297"/>
+      <c r="A201" s="305"/>
+      <c r="B201" s="304"/>
+      <c r="C201" s="311"/>
       <c r="D201" s="7"/>
       <c r="E201" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F201" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F201" s="320"/>
     </row>
     <row r="202" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A202" s="291"/>
-      <c r="B202" s="290"/>
-      <c r="C202" s="297"/>
+      <c r="A202" s="305"/>
+      <c r="B202" s="304"/>
+      <c r="C202" s="311"/>
       <c r="D202" s="7"/>
       <c r="E202" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F202" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F202" s="320"/>
     </row>
     <row r="203" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A203" s="291"/>
-      <c r="B203" s="290"/>
-      <c r="C203" s="297"/>
+      <c r="A203" s="305"/>
+      <c r="B203" s="304"/>
+      <c r="C203" s="311"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F203" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F203" s="320"/>
     </row>
     <row r="204" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A204" s="291"/>
-      <c r="B204" s="290"/>
-      <c r="C204" s="297"/>
+      <c r="A204" s="305"/>
+      <c r="B204" s="304"/>
+      <c r="C204" s="311"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F204" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F204" s="320"/>
     </row>
     <row r="205" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A205" s="291"/>
-      <c r="B205" s="290"/>
-      <c r="C205" s="297"/>
+      <c r="A205" s="305"/>
+      <c r="B205" s="304"/>
+      <c r="C205" s="311"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F205" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F205" s="320"/>
     </row>
     <row r="206" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A206" s="291"/>
-      <c r="B206" s="290"/>
-      <c r="C206" s="297"/>
+      <c r="A206" s="305"/>
+      <c r="B206" s="304"/>
+      <c r="C206" s="311"/>
       <c r="D206" s="7"/>
       <c r="E206" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F206" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F206" s="320"/>
     </row>
     <row r="207" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A207" s="291"/>
-      <c r="B207" s="290"/>
-      <c r="C207" s="297"/>
+      <c r="A207" s="305"/>
+      <c r="B207" s="304"/>
+      <c r="C207" s="311"/>
       <c r="D207" s="7"/>
       <c r="E207" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F207" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F207" s="320"/>
     </row>
     <row r="208" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A208" s="291"/>
-      <c r="B208" s="290"/>
-      <c r="C208" s="297"/>
+      <c r="A208" s="305"/>
+      <c r="B208" s="304"/>
+      <c r="C208" s="311"/>
       <c r="D208" s="7"/>
       <c r="E208" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F208" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F208" s="320"/>
     </row>
     <row r="209" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A209" s="291"/>
-      <c r="B209" s="290"/>
-      <c r="C209" s="297"/>
+      <c r="A209" s="305"/>
+      <c r="B209" s="304"/>
+      <c r="C209" s="311"/>
       <c r="D209" s="7"/>
       <c r="E209" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F209" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F209" s="320"/>
     </row>
     <row r="210" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A210" s="291"/>
-      <c r="B210" s="290"/>
-      <c r="C210" s="297"/>
+      <c r="A210" s="305"/>
+      <c r="B210" s="304"/>
+      <c r="C210" s="311"/>
       <c r="D210" s="7"/>
       <c r="E210" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F210" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F210" s="320"/>
     </row>
     <row r="211" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A211" s="291"/>
-      <c r="B211" s="307"/>
-      <c r="C211" s="308"/>
+      <c r="A211" s="305"/>
+      <c r="B211" s="318"/>
+      <c r="C211" s="319"/>
       <c r="D211" s="134"/>
       <c r="E211" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F211" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F211" s="320"/>
     </row>
     <row r="212" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A212" s="291"/>
-      <c r="B212" s="290"/>
-      <c r="C212" s="297"/>
+      <c r="A212" s="305"/>
+      <c r="B212" s="304"/>
+      <c r="C212" s="311"/>
       <c r="D212" s="7"/>
       <c r="E212" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F212" s="306"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F212" s="320"/>
     </row>
     <row r="213" s="249" customFormat="1" spans="1:6">
-      <c r="A213" s="283"/>
-      <c r="B213" s="290"/>
-      <c r="C213" s="297"/>
+      <c r="A213" s="297"/>
+      <c r="B213" s="304"/>
+      <c r="C213" s="311"/>
       <c r="D213" s="7"/>
       <c r="E213" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F213" s="293">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F213" s="307">
         <f>SUM(E213:E220)</f>
         <v>0</v>
       </c>
     </row>
     <row r="214" s="249" customFormat="1" spans="1:6">
-      <c r="A214" s="286"/>
-      <c r="B214" s="290"/>
-      <c r="C214" s="297"/>
+      <c r="A214" s="300"/>
+      <c r="B214" s="304"/>
+      <c r="C214" s="311"/>
       <c r="D214" s="7"/>
       <c r="E214" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F214" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F214" s="308"/>
     </row>
     <row r="215" s="249" customFormat="1" spans="1:6">
-      <c r="A215" s="286"/>
-      <c r="B215" s="290"/>
-      <c r="C215" s="297"/>
+      <c r="A215" s="300"/>
+      <c r="B215" s="304"/>
+      <c r="C215" s="311"/>
       <c r="D215" s="7"/>
       <c r="E215" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F215" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F215" s="308"/>
     </row>
     <row r="216" s="249" customFormat="1" spans="1:6">
-      <c r="A216" s="286"/>
-      <c r="B216" s="290"/>
-      <c r="C216" s="297"/>
+      <c r="A216" s="300"/>
+      <c r="B216" s="304"/>
+      <c r="C216" s="311"/>
       <c r="D216" s="7"/>
       <c r="E216" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F216" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F216" s="308"/>
     </row>
     <row r="217" s="249" customFormat="1" spans="1:6">
-      <c r="A217" s="286"/>
-      <c r="B217" s="290"/>
-      <c r="C217" s="297"/>
+      <c r="A217" s="300"/>
+      <c r="B217" s="304"/>
+      <c r="C217" s="311"/>
       <c r="D217" s="7"/>
       <c r="E217" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F217" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F217" s="308"/>
     </row>
     <row r="218" s="249" customFormat="1" spans="1:6">
-      <c r="A218" s="286"/>
-      <c r="B218" s="290"/>
-      <c r="C218" s="297"/>
+      <c r="A218" s="300"/>
+      <c r="B218" s="304"/>
+      <c r="C218" s="311"/>
       <c r="D218" s="7"/>
       <c r="E218" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F218" s="294"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F218" s="308"/>
     </row>
     <row r="219" s="249" customFormat="1" spans="1:6">
-      <c r="A219" s="286"/>
-      <c r="B219" s="290"/>
-      <c r="C219" s="297"/>
+      <c r="A219" s="300"/>
+      <c r="B219" s="304"/>
+      <c r="C219" s="311"/>
       <c r="D219" s="7"/>
       <c r="E219" s="7">
-        <f t="shared" ref="E219:E282" si="8">SUM(C219*D219)</f>
-        <v>0</v>
-      </c>
-      <c r="F219" s="294"/>
+        <f t="shared" ref="E219:E282" si="9">SUM(C219*D219)</f>
+        <v>0</v>
+      </c>
+      <c r="F219" s="308"/>
     </row>
     <row r="220" s="249" customFormat="1" spans="1:6">
-      <c r="A220" s="287"/>
-      <c r="B220" s="290"/>
-      <c r="C220" s="297"/>
+      <c r="A220" s="301"/>
+      <c r="B220" s="304"/>
+      <c r="C220" s="311"/>
       <c r="D220" s="7"/>
       <c r="E220" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F220" s="295"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F220" s="309"/>
     </row>
     <row r="221" s="249" customFormat="1" spans="1:6">
-      <c r="A221" s="283"/>
-      <c r="B221" s="290"/>
-      <c r="C221" s="297"/>
+      <c r="A221" s="297"/>
+      <c r="B221" s="304"/>
+      <c r="C221" s="311"/>
       <c r="D221" s="7"/>
       <c r="E221" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F221" s="293">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F221" s="307">
         <f>SUM(E221:E232)</f>
         <v>0</v>
       </c>
     </row>
     <row r="222" s="249" customFormat="1" spans="1:6">
-      <c r="A222" s="286"/>
-      <c r="B222" s="290"/>
-      <c r="C222" s="297"/>
+      <c r="A222" s="300"/>
+      <c r="B222" s="304"/>
+      <c r="C222" s="311"/>
       <c r="D222" s="7"/>
       <c r="E222" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F222" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F222" s="308"/>
     </row>
     <row r="223" s="249" customFormat="1" spans="1:6">
-      <c r="A223" s="286"/>
-      <c r="B223" s="290"/>
-      <c r="C223" s="297"/>
+      <c r="A223" s="300"/>
+      <c r="B223" s="304"/>
+      <c r="C223" s="311"/>
       <c r="D223" s="7"/>
       <c r="E223" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F223" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F223" s="308"/>
     </row>
     <row r="224" s="249" customFormat="1" spans="1:6">
-      <c r="A224" s="286"/>
-      <c r="B224" s="290"/>
-      <c r="C224" s="297"/>
+      <c r="A224" s="300"/>
+      <c r="B224" s="304"/>
+      <c r="C224" s="311"/>
       <c r="D224" s="7"/>
       <c r="E224" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F224" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F224" s="308"/>
     </row>
     <row r="225" s="249" customFormat="1" spans="1:6">
-      <c r="A225" s="286"/>
-      <c r="B225" s="290"/>
-      <c r="C225" s="297"/>
+      <c r="A225" s="300"/>
+      <c r="B225" s="304"/>
+      <c r="C225" s="311"/>
       <c r="D225" s="7"/>
       <c r="E225" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F225" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F225" s="308"/>
     </row>
     <row r="226" s="249" customFormat="1" spans="1:6">
-      <c r="A226" s="286"/>
-      <c r="B226" s="290"/>
-      <c r="C226" s="297"/>
+      <c r="A226" s="300"/>
+      <c r="B226" s="304"/>
+      <c r="C226" s="311"/>
       <c r="D226" s="7"/>
       <c r="E226" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F226" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F226" s="308"/>
     </row>
     <row r="227" s="249" customFormat="1" spans="1:6">
-      <c r="A227" s="286"/>
-      <c r="B227" s="290"/>
-      <c r="C227" s="297"/>
+      <c r="A227" s="300"/>
+      <c r="B227" s="304"/>
+      <c r="C227" s="311"/>
       <c r="D227" s="7"/>
       <c r="E227" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F227" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F227" s="308"/>
     </row>
     <row r="228" s="249" customFormat="1" spans="1:6">
-      <c r="A228" s="286"/>
-      <c r="B228" s="290"/>
-      <c r="C228" s="297"/>
+      <c r="A228" s="300"/>
+      <c r="B228" s="304"/>
+      <c r="C228" s="311"/>
       <c r="D228" s="7"/>
       <c r="E228" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F228" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F228" s="308"/>
     </row>
     <row r="229" s="249" customFormat="1" spans="1:6">
-      <c r="A229" s="286"/>
-      <c r="B229" s="290"/>
-      <c r="C229" s="297"/>
+      <c r="A229" s="300"/>
+      <c r="B229" s="304"/>
+      <c r="C229" s="311"/>
       <c r="D229" s="7"/>
       <c r="E229" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F229" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F229" s="308"/>
     </row>
     <row r="230" s="249" customFormat="1" spans="1:6">
-      <c r="A230" s="286"/>
-      <c r="B230" s="290"/>
-      <c r="C230" s="297"/>
+      <c r="A230" s="300"/>
+      <c r="B230" s="304"/>
+      <c r="C230" s="311"/>
       <c r="D230" s="7"/>
       <c r="E230" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F230" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F230" s="308"/>
     </row>
     <row r="231" s="249" customFormat="1" spans="1:6">
-      <c r="A231" s="286"/>
-      <c r="B231" s="290"/>
-      <c r="C231" s="297"/>
+      <c r="A231" s="300"/>
+      <c r="B231" s="304"/>
+      <c r="C231" s="311"/>
       <c r="D231" s="7"/>
       <c r="E231" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F231" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F231" s="308"/>
     </row>
     <row r="232" s="249" customFormat="1" spans="1:6">
-      <c r="A232" s="287"/>
-      <c r="B232" s="290"/>
-      <c r="C232" s="297"/>
+      <c r="A232" s="301"/>
+      <c r="B232" s="304"/>
+      <c r="C232" s="311"/>
       <c r="D232" s="7"/>
       <c r="E232" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F232" s="295"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F232" s="309"/>
     </row>
     <row r="233" s="249" customFormat="1" spans="1:6">
-      <c r="A233" s="283"/>
-      <c r="B233" s="290"/>
-      <c r="C233" s="297"/>
+      <c r="A233" s="297"/>
+      <c r="B233" s="304"/>
+      <c r="C233" s="311"/>
       <c r="D233" s="7"/>
       <c r="E233" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F233" s="293">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F233" s="307">
         <f>SUM(E233:E241)</f>
         <v>0</v>
       </c>
     </row>
     <row r="234" s="249" customFormat="1" spans="1:6">
-      <c r="A234" s="286"/>
-      <c r="B234" s="290"/>
-      <c r="C234" s="297"/>
+      <c r="A234" s="300"/>
+      <c r="B234" s="304"/>
+      <c r="C234" s="311"/>
       <c r="D234" s="7"/>
       <c r="E234" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F234" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F234" s="308"/>
     </row>
     <row r="235" s="249" customFormat="1" spans="1:6">
-      <c r="A235" s="286"/>
-      <c r="B235" s="290"/>
-      <c r="C235" s="297"/>
+      <c r="A235" s="300"/>
+      <c r="B235" s="304"/>
+      <c r="C235" s="311"/>
       <c r="D235" s="7"/>
       <c r="E235" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F235" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F235" s="308"/>
     </row>
     <row r="236" s="249" customFormat="1" spans="1:6">
-      <c r="A236" s="286"/>
-      <c r="B236" s="290"/>
-      <c r="C236" s="297"/>
+      <c r="A236" s="300"/>
+      <c r="B236" s="304"/>
+      <c r="C236" s="311"/>
       <c r="D236" s="7"/>
       <c r="E236" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F236" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F236" s="308"/>
     </row>
     <row r="237" s="249" customFormat="1" spans="1:6">
-      <c r="A237" s="286"/>
-      <c r="B237" s="290"/>
-      <c r="C237" s="297"/>
+      <c r="A237" s="300"/>
+      <c r="B237" s="304"/>
+      <c r="C237" s="311"/>
       <c r="D237" s="7"/>
       <c r="E237" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F237" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F237" s="308"/>
     </row>
     <row r="238" s="249" customFormat="1" spans="1:6">
-      <c r="A238" s="286"/>
-      <c r="B238" s="290"/>
-      <c r="C238" s="297"/>
+      <c r="A238" s="300"/>
+      <c r="B238" s="304"/>
+      <c r="C238" s="311"/>
       <c r="D238" s="7"/>
       <c r="E238" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F238" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F238" s="308"/>
     </row>
     <row r="239" s="249" customFormat="1" spans="1:6">
-      <c r="A239" s="286"/>
-      <c r="B239" s="290"/>
-      <c r="C239" s="297"/>
+      <c r="A239" s="300"/>
+      <c r="B239" s="304"/>
+      <c r="C239" s="311"/>
       <c r="D239" s="7"/>
       <c r="E239" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F239" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F239" s="308"/>
     </row>
     <row r="240" s="249" customFormat="1" spans="1:6">
-      <c r="A240" s="286"/>
-      <c r="B240" s="290"/>
-      <c r="C240" s="297"/>
+      <c r="A240" s="300"/>
+      <c r="B240" s="304"/>
+      <c r="C240" s="311"/>
       <c r="D240" s="7"/>
       <c r="E240" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F240" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F240" s="308"/>
     </row>
     <row r="241" s="249" customFormat="1" spans="1:6">
-      <c r="A241" s="287"/>
-      <c r="B241" s="290"/>
-      <c r="C241" s="297"/>
+      <c r="A241" s="301"/>
+      <c r="B241" s="304"/>
+      <c r="C241" s="311"/>
       <c r="D241" s="7"/>
       <c r="E241" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F241" s="295"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F241" s="309"/>
     </row>
     <row r="242" s="249" customFormat="1" spans="1:6">
-      <c r="A242" s="283"/>
-      <c r="B242" s="290"/>
-      <c r="C242" s="297"/>
+      <c r="A242" s="297"/>
+      <c r="B242" s="304"/>
+      <c r="C242" s="311"/>
       <c r="D242" s="7"/>
       <c r="E242" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F242" s="293">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F242" s="307">
         <f>SUM(E242:E252)</f>
         <v>0</v>
       </c>
     </row>
     <row r="243" s="249" customFormat="1" spans="1:6">
-      <c r="A243" s="286"/>
-      <c r="B243" s="290"/>
-      <c r="C243" s="297"/>
+      <c r="A243" s="300"/>
+      <c r="B243" s="304"/>
+      <c r="C243" s="311"/>
       <c r="D243" s="7"/>
       <c r="E243" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F243" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F243" s="308"/>
     </row>
     <row r="244" s="249" customFormat="1" spans="1:6">
-      <c r="A244" s="286"/>
-      <c r="B244" s="290"/>
-      <c r="C244" s="297"/>
+      <c r="A244" s="300"/>
+      <c r="B244" s="304"/>
+      <c r="C244" s="311"/>
       <c r="D244" s="7"/>
       <c r="E244" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F244" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F244" s="308"/>
     </row>
     <row r="245" s="249" customFormat="1" spans="1:6">
-      <c r="A245" s="286"/>
-      <c r="B245" s="290"/>
-      <c r="C245" s="297"/>
+      <c r="A245" s="300"/>
+      <c r="B245" s="304"/>
+      <c r="C245" s="311"/>
       <c r="D245" s="7"/>
       <c r="E245" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F245" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F245" s="308"/>
     </row>
     <row r="246" s="249" customFormat="1" spans="1:6">
-      <c r="A246" s="286"/>
-      <c r="B246" s="290"/>
-      <c r="C246" s="297"/>
+      <c r="A246" s="300"/>
+      <c r="B246" s="304"/>
+      <c r="C246" s="311"/>
       <c r="D246" s="7"/>
       <c r="E246" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F246" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F246" s="308"/>
     </row>
     <row r="247" s="249" customFormat="1" spans="1:6">
-      <c r="A247" s="286"/>
-      <c r="B247" s="290"/>
-      <c r="C247" s="297"/>
+      <c r="A247" s="300"/>
+      <c r="B247" s="304"/>
+      <c r="C247" s="311"/>
       <c r="D247" s="7"/>
       <c r="E247" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F247" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F247" s="308"/>
     </row>
     <row r="248" s="249" customFormat="1" spans="1:6">
-      <c r="A248" s="286"/>
-      <c r="B248" s="290"/>
-      <c r="C248" s="297"/>
+      <c r="A248" s="300"/>
+      <c r="B248" s="304"/>
+      <c r="C248" s="311"/>
       <c r="D248" s="7"/>
       <c r="E248" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F248" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F248" s="308"/>
     </row>
     <row r="249" s="249" customFormat="1" spans="1:6">
-      <c r="A249" s="286"/>
-      <c r="B249" s="290"/>
-      <c r="C249" s="297"/>
+      <c r="A249" s="300"/>
+      <c r="B249" s="304"/>
+      <c r="C249" s="311"/>
       <c r="D249" s="7"/>
       <c r="E249" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F249" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F249" s="308"/>
     </row>
     <row r="250" s="249" customFormat="1" spans="1:6">
-      <c r="A250" s="286"/>
-      <c r="B250" s="290"/>
-      <c r="C250" s="297"/>
+      <c r="A250" s="300"/>
+      <c r="B250" s="304"/>
+      <c r="C250" s="311"/>
       <c r="D250" s="7"/>
       <c r="E250" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F250" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F250" s="308"/>
     </row>
     <row r="251" s="249" customFormat="1" spans="1:6">
-      <c r="A251" s="286"/>
-      <c r="B251" s="290"/>
-      <c r="C251" s="297"/>
+      <c r="A251" s="300"/>
+      <c r="B251" s="304"/>
+      <c r="C251" s="311"/>
       <c r="D251" s="7"/>
       <c r="E251" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F251" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F251" s="308"/>
     </row>
     <row r="252" s="249" customFormat="1" spans="1:6">
-      <c r="A252" s="287"/>
-      <c r="B252" s="290"/>
-      <c r="C252" s="297"/>
+      <c r="A252" s="301"/>
+      <c r="B252" s="304"/>
+      <c r="C252" s="311"/>
       <c r="D252" s="7"/>
       <c r="E252" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F252" s="295"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F252" s="309"/>
     </row>
     <row r="253" s="249" customFormat="1" spans="1:6">
-      <c r="A253" s="283"/>
-      <c r="B253" s="290"/>
-      <c r="C253" s="297"/>
+      <c r="A253" s="297"/>
+      <c r="B253" s="304"/>
+      <c r="C253" s="311"/>
       <c r="D253" s="7"/>
       <c r="E253" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F253" s="293">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F253" s="307">
         <f>SUM(E253:E263)</f>
         <v>0</v>
       </c>
     </row>
     <row r="254" s="249" customFormat="1" spans="1:6">
-      <c r="A254" s="286"/>
-      <c r="B254" s="290"/>
-      <c r="C254" s="297"/>
+      <c r="A254" s="300"/>
+      <c r="B254" s="304"/>
+      <c r="C254" s="311"/>
       <c r="D254" s="7"/>
       <c r="E254" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F254" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F254" s="308"/>
     </row>
     <row r="255" s="249" customFormat="1" spans="1:6">
-      <c r="A255" s="286"/>
-      <c r="B255" s="290"/>
-      <c r="C255" s="297"/>
+      <c r="A255" s="300"/>
+      <c r="B255" s="304"/>
+      <c r="C255" s="311"/>
       <c r="D255" s="7"/>
       <c r="E255" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F255" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F255" s="308"/>
     </row>
     <row r="256" s="249" customFormat="1" spans="1:6">
-      <c r="A256" s="286"/>
-      <c r="B256" s="290"/>
-      <c r="C256" s="297"/>
+      <c r="A256" s="300"/>
+      <c r="B256" s="304"/>
+      <c r="C256" s="311"/>
       <c r="D256" s="7"/>
       <c r="E256" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F256" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F256" s="308"/>
     </row>
     <row r="257" s="249" customFormat="1" spans="1:6">
-      <c r="A257" s="286"/>
-      <c r="B257" s="290"/>
-      <c r="C257" s="297"/>
+      <c r="A257" s="300"/>
+      <c r="B257" s="304"/>
+      <c r="C257" s="311"/>
       <c r="D257" s="7"/>
       <c r="E257" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F257" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F257" s="308"/>
     </row>
     <row r="258" s="249" customFormat="1" spans="1:6">
-      <c r="A258" s="286"/>
-      <c r="B258" s="290"/>
-      <c r="C258" s="297"/>
+      <c r="A258" s="300"/>
+      <c r="B258" s="304"/>
+      <c r="C258" s="311"/>
       <c r="D258" s="7"/>
       <c r="E258" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F258" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F258" s="308"/>
     </row>
     <row r="259" s="249" customFormat="1" spans="1:6">
-      <c r="A259" s="286"/>
-      <c r="B259" s="290"/>
-      <c r="C259" s="297"/>
+      <c r="A259" s="300"/>
+      <c r="B259" s="304"/>
+      <c r="C259" s="311"/>
       <c r="D259" s="7"/>
       <c r="E259" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F259" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F259" s="308"/>
     </row>
     <row r="260" s="249" customFormat="1" spans="1:6">
-      <c r="A260" s="286"/>
-      <c r="B260" s="290"/>
-      <c r="C260" s="297"/>
+      <c r="A260" s="300"/>
+      <c r="B260" s="304"/>
+      <c r="C260" s="311"/>
       <c r="D260" s="7"/>
       <c r="E260" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F260" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F260" s="308"/>
     </row>
     <row r="261" s="249" customFormat="1" spans="1:6">
-      <c r="A261" s="286"/>
-      <c r="B261" s="290"/>
-      <c r="C261" s="297"/>
+      <c r="A261" s="300"/>
+      <c r="B261" s="304"/>
+      <c r="C261" s="311"/>
       <c r="D261" s="7"/>
       <c r="E261" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F261" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F261" s="308"/>
     </row>
     <row r="262" s="249" customFormat="1" spans="1:6">
-      <c r="A262" s="286"/>
-      <c r="B262" s="290"/>
-      <c r="C262" s="297"/>
+      <c r="A262" s="300"/>
+      <c r="B262" s="304"/>
+      <c r="C262" s="311"/>
       <c r="D262" s="7"/>
       <c r="E262" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F262" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F262" s="308"/>
     </row>
     <row r="263" s="249" customFormat="1" spans="1:6">
-      <c r="A263" s="287"/>
-      <c r="B263" s="290"/>
-      <c r="C263" s="297"/>
+      <c r="A263" s="301"/>
+      <c r="B263" s="304"/>
+      <c r="C263" s="311"/>
       <c r="D263" s="7"/>
       <c r="E263" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F263" s="295"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F263" s="309"/>
     </row>
     <row r="264" s="249" customFormat="1" spans="1:6">
-      <c r="A264" s="283"/>
-      <c r="B264" s="290"/>
-      <c r="C264" s="297"/>
+      <c r="A264" s="297"/>
+      <c r="B264" s="304"/>
+      <c r="C264" s="311"/>
       <c r="D264" s="7"/>
       <c r="E264" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F264" s="293">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F264" s="307">
         <f>SUM(E264:E274)</f>
         <v>0</v>
       </c>
     </row>
     <row r="265" s="249" customFormat="1" spans="1:6">
-      <c r="A265" s="286"/>
-      <c r="B265" s="290"/>
-      <c r="C265" s="297"/>
+      <c r="A265" s="300"/>
+      <c r="B265" s="304"/>
+      <c r="C265" s="311"/>
       <c r="D265" s="7"/>
       <c r="E265" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F265" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F265" s="308"/>
     </row>
     <row r="266" s="249" customFormat="1" spans="1:6">
-      <c r="A266" s="286"/>
-      <c r="B266" s="290"/>
-      <c r="C266" s="297"/>
+      <c r="A266" s="300"/>
+      <c r="B266" s="304"/>
+      <c r="C266" s="311"/>
       <c r="D266" s="7"/>
       <c r="E266" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F266" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F266" s="308"/>
     </row>
     <row r="267" s="249" customFormat="1" spans="1:6">
-      <c r="A267" s="286"/>
-      <c r="B267" s="290"/>
-      <c r="C267" s="297"/>
+      <c r="A267" s="300"/>
+      <c r="B267" s="304"/>
+      <c r="C267" s="311"/>
       <c r="D267" s="7"/>
       <c r="E267" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F267" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F267" s="308"/>
     </row>
     <row r="268" s="249" customFormat="1" spans="1:6">
-      <c r="A268" s="286"/>
-      <c r="B268" s="290"/>
-      <c r="C268" s="297"/>
+      <c r="A268" s="300"/>
+      <c r="B268" s="304"/>
+      <c r="C268" s="311"/>
       <c r="D268" s="7"/>
       <c r="E268" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F268" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F268" s="308"/>
     </row>
     <row r="269" s="249" customFormat="1" spans="1:6">
-      <c r="A269" s="286"/>
-      <c r="B269" s="290"/>
-      <c r="C269" s="297"/>
+      <c r="A269" s="300"/>
+      <c r="B269" s="304"/>
+      <c r="C269" s="311"/>
       <c r="D269" s="7"/>
       <c r="E269" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F269" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F269" s="308"/>
     </row>
     <row r="270" s="249" customFormat="1" spans="1:6">
-      <c r="A270" s="286"/>
-      <c r="B270" s="290"/>
-      <c r="C270" s="297"/>
+      <c r="A270" s="300"/>
+      <c r="B270" s="304"/>
+      <c r="C270" s="311"/>
       <c r="D270" s="7"/>
       <c r="E270" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F270" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F270" s="308"/>
     </row>
     <row r="271" s="249" customFormat="1" spans="1:6">
-      <c r="A271" s="286"/>
-      <c r="B271" s="290"/>
-      <c r="C271" s="297"/>
+      <c r="A271" s="300"/>
+      <c r="B271" s="304"/>
+      <c r="C271" s="311"/>
       <c r="D271" s="7"/>
       <c r="E271" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F271" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F271" s="308"/>
     </row>
     <row r="272" s="249" customFormat="1" spans="1:6">
-      <c r="A272" s="286"/>
-      <c r="B272" s="290"/>
-      <c r="C272" s="297"/>
+      <c r="A272" s="300"/>
+      <c r="B272" s="304"/>
+      <c r="C272" s="311"/>
       <c r="D272" s="7"/>
       <c r="E272" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F272" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F272" s="308"/>
     </row>
     <row r="273" s="249" customFormat="1" spans="1:6">
-      <c r="A273" s="286"/>
-      <c r="B273" s="290"/>
-      <c r="C273" s="297"/>
+      <c r="A273" s="300"/>
+      <c r="B273" s="304"/>
+      <c r="C273" s="311"/>
       <c r="D273" s="7"/>
       <c r="E273" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F273" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F273" s="308"/>
     </row>
     <row r="274" s="249" customFormat="1" spans="1:6">
-      <c r="A274" s="287"/>
-      <c r="B274" s="290"/>
-      <c r="C274" s="297"/>
+      <c r="A274" s="301"/>
+      <c r="B274" s="304"/>
+      <c r="C274" s="311"/>
       <c r="D274" s="7"/>
       <c r="E274" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F274" s="295"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F274" s="309"/>
     </row>
     <row r="275" s="249" customFormat="1" spans="1:6">
-      <c r="A275" s="283"/>
-      <c r="B275" s="290"/>
-      <c r="C275" s="297"/>
+      <c r="A275" s="297"/>
+      <c r="B275" s="304"/>
+      <c r="C275" s="311"/>
       <c r="D275" s="7"/>
       <c r="E275" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F275" s="293">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F275" s="307">
         <f>SUM(E275:E284)</f>
         <v>0</v>
       </c>
     </row>
     <row r="276" s="249" customFormat="1" spans="1:6">
-      <c r="A276" s="286"/>
-      <c r="B276" s="290"/>
-      <c r="C276" s="297"/>
+      <c r="A276" s="300"/>
+      <c r="B276" s="304"/>
+      <c r="C276" s="311"/>
       <c r="D276" s="7"/>
       <c r="E276" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F276" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F276" s="308"/>
     </row>
     <row r="277" s="249" customFormat="1" spans="1:6">
-      <c r="A277" s="286"/>
-      <c r="B277" s="290"/>
-      <c r="C277" s="297"/>
+      <c r="A277" s="300"/>
+      <c r="B277" s="304"/>
+      <c r="C277" s="311"/>
       <c r="D277" s="7"/>
       <c r="E277" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F277" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F277" s="308"/>
     </row>
     <row r="278" s="249" customFormat="1" spans="1:6">
-      <c r="A278" s="286"/>
-      <c r="B278" s="290"/>
-      <c r="C278" s="297"/>
+      <c r="A278" s="300"/>
+      <c r="B278" s="304"/>
+      <c r="C278" s="311"/>
       <c r="D278" s="7"/>
       <c r="E278" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F278" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F278" s="308"/>
     </row>
     <row r="279" s="249" customFormat="1" spans="1:6">
-      <c r="A279" s="286"/>
-      <c r="B279" s="290"/>
-      <c r="C279" s="297"/>
+      <c r="A279" s="300"/>
+      <c r="B279" s="304"/>
+      <c r="C279" s="311"/>
       <c r="D279" s="7"/>
       <c r="E279" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F279" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F279" s="308"/>
     </row>
     <row r="280" s="249" customFormat="1" spans="1:6">
-      <c r="A280" s="286"/>
-      <c r="B280" s="290"/>
-      <c r="C280" s="297"/>
+      <c r="A280" s="300"/>
+      <c r="B280" s="304"/>
+      <c r="C280" s="311"/>
       <c r="D280" s="7"/>
       <c r="E280" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F280" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F280" s="308"/>
     </row>
     <row r="281" s="249" customFormat="1" spans="1:6">
-      <c r="A281" s="286"/>
-      <c r="B281" s="290"/>
-      <c r="C281" s="297"/>
+      <c r="A281" s="300"/>
+      <c r="B281" s="304"/>
+      <c r="C281" s="311"/>
       <c r="D281" s="7"/>
       <c r="E281" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F281" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F281" s="308"/>
     </row>
     <row r="282" s="249" customFormat="1" spans="1:6">
-      <c r="A282" s="286"/>
-      <c r="B282" s="290"/>
-      <c r="C282" s="297"/>
+      <c r="A282" s="300"/>
+      <c r="B282" s="304"/>
+      <c r="C282" s="311"/>
       <c r="D282" s="7"/>
       <c r="E282" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F282" s="294"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F282" s="308"/>
     </row>
     <row r="283" s="249" customFormat="1" spans="1:6">
-      <c r="A283" s="286"/>
-      <c r="B283" s="290"/>
-      <c r="C283" s="297"/>
+      <c r="A283" s="300"/>
+      <c r="B283" s="304"/>
+      <c r="C283" s="311"/>
       <c r="D283" s="7"/>
       <c r="E283" s="7">
-        <f t="shared" ref="E283:E296" si="9">SUM(C283*D283)</f>
-        <v>0</v>
-      </c>
-      <c r="F283" s="294"/>
+        <f t="shared" ref="E283:E296" si="10">SUM(C283*D283)</f>
+        <v>0</v>
+      </c>
+      <c r="F283" s="308"/>
     </row>
     <row r="284" s="249" customFormat="1" spans="1:6">
-      <c r="A284" s="287"/>
-      <c r="B284" s="290"/>
-      <c r="C284" s="297"/>
+      <c r="A284" s="301"/>
+      <c r="B284" s="304"/>
+      <c r="C284" s="311"/>
       <c r="D284" s="7"/>
       <c r="E284" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F284" s="295"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F284" s="309"/>
     </row>
     <row r="285" s="249" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A285" s="291"/>
-      <c r="B285" s="290"/>
-      <c r="C285" s="297"/>
+      <c r="A285" s="305"/>
+      <c r="B285" s="304"/>
+      <c r="C285" s="311"/>
       <c r="D285" s="7"/>
       <c r="E285" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F285" s="306">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F285" s="320">
         <f>SUM(E285)</f>
         <v>0</v>
       </c>
     </row>
     <row r="286" s="249" customFormat="1" spans="1:6">
-      <c r="A286" s="283"/>
-      <c r="B286" s="290"/>
-      <c r="C286" s="297"/>
+      <c r="A286" s="297"/>
+      <c r="B286" s="304"/>
+      <c r="C286" s="311"/>
       <c r="D286" s="7"/>
       <c r="E286" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F286" s="293">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F286" s="307">
         <f>SUM(E286:E296)</f>
         <v>0</v>
       </c>
     </row>
     <row r="287" s="249" customFormat="1" spans="1:6">
-      <c r="A287" s="286"/>
-      <c r="B287" s="290"/>
-      <c r="C287" s="297"/>
+      <c r="A287" s="300"/>
+      <c r="B287" s="304"/>
+      <c r="C287" s="311"/>
       <c r="D287" s="7"/>
       <c r="E287" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F287" s="294"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F287" s="308"/>
     </row>
     <row r="288" s="249" customFormat="1" spans="1:6">
-      <c r="A288" s="286"/>
-      <c r="B288" s="290"/>
-      <c r="C288" s="297"/>
+      <c r="A288" s="300"/>
+      <c r="B288" s="304"/>
+      <c r="C288" s="311"/>
       <c r="D288" s="7"/>
       <c r="E288" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F288" s="294"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F288" s="308"/>
     </row>
     <row r="289" s="249" customFormat="1" spans="1:6">
-      <c r="A289" s="286"/>
-      <c r="B289" s="290"/>
-      <c r="C289" s="297"/>
+      <c r="A289" s="300"/>
+      <c r="B289" s="304"/>
+      <c r="C289" s="311"/>
       <c r="D289" s="7"/>
       <c r="E289" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F289" s="294"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F289" s="308"/>
     </row>
     <row r="290" s="249" customFormat="1" spans="1:6">
-      <c r="A290" s="286"/>
-      <c r="B290" s="290"/>
-      <c r="C290" s="297"/>
+      <c r="A290" s="300"/>
+      <c r="B290" s="304"/>
+      <c r="C290" s="311"/>
       <c r="D290" s="7"/>
       <c r="E290" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F290" s="294"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F290" s="308"/>
     </row>
     <row r="291" s="249" customFormat="1" spans="1:6">
-      <c r="A291" s="286"/>
-      <c r="B291" s="290"/>
-      <c r="C291" s="297"/>
+      <c r="A291" s="300"/>
+      <c r="B291" s="304"/>
+      <c r="C291" s="311"/>
       <c r="D291" s="7"/>
       <c r="E291" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F291" s="294"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F291" s="308"/>
     </row>
     <row r="292" s="249" customFormat="1" spans="1:6">
-      <c r="A292" s="286"/>
-      <c r="B292" s="290"/>
-      <c r="C292" s="297"/>
+      <c r="A292" s="300"/>
+      <c r="B292" s="304"/>
+      <c r="C292" s="311"/>
       <c r="D292" s="7"/>
       <c r="E292" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F292" s="294"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F292" s="308"/>
     </row>
     <row r="293" s="249" customFormat="1" spans="1:6">
-      <c r="A293" s="286"/>
-      <c r="B293" s="290"/>
-      <c r="C293" s="297"/>
+      <c r="A293" s="300"/>
+      <c r="B293" s="304"/>
+      <c r="C293" s="311"/>
       <c r="D293" s="7"/>
       <c r="E293" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F293" s="294"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F293" s="308"/>
     </row>
     <row r="294" s="249" customFormat="1" spans="1:6">
-      <c r="A294" s="286"/>
-      <c r="B294" s="290"/>
-      <c r="C294" s="297"/>
+      <c r="A294" s="300"/>
+      <c r="B294" s="304"/>
+      <c r="C294" s="311"/>
       <c r="D294" s="7"/>
       <c r="E294" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F294" s="294"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F294" s="308"/>
     </row>
     <row r="295" s="249" customFormat="1" spans="1:6">
-      <c r="A295" s="286"/>
-      <c r="B295" s="290"/>
-      <c r="C295" s="297"/>
+      <c r="A295" s="300"/>
+      <c r="B295" s="304"/>
+      <c r="C295" s="311"/>
       <c r="D295" s="7"/>
       <c r="E295" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F295" s="294"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F295" s="308"/>
     </row>
     <row r="296" s="249" customFormat="1" spans="1:6">
-      <c r="A296" s="287"/>
-      <c r="B296" s="290"/>
-      <c r="C296" s="297"/>
+      <c r="A296" s="301"/>
+      <c r="B296" s="304"/>
+      <c r="C296" s="311"/>
       <c r="D296" s="7"/>
       <c r="E296" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F296" s="295"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F296" s="309"/>
     </row>
     <row r="297" s="249" customFormat="1" spans="1:6">
       <c r="A297" s="251"/>
       <c r="C297" s="250"/>
       <c r="E297" s="7"/>
-      <c r="F297" s="306">
+      <c r="F297" s="320">
         <f>SUM(F2:F296)</f>
-        <v>5052000</v>
+        <v>5674000</v>
       </c>
     </row>
     <row r="298" s="249" customFormat="1" spans="1:3">
@@ -8051,10 +8320,10 @@
     <row r="400" s="249" customFormat="1" spans="1:7">
       <c r="A400" s="251"/>
       <c r="C400" s="250"/>
-      <c r="G400" s="275"/>
+      <c r="G400" s="289"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="42">
     <mergeCell ref="A2:A12"/>
     <mergeCell ref="A13:A25"/>
     <mergeCell ref="A26:A34"/>
@@ -8067,6 +8336,7 @@
     <mergeCell ref="A94:A99"/>
     <mergeCell ref="A100:A108"/>
     <mergeCell ref="A109:A121"/>
+    <mergeCell ref="A122:A128"/>
     <mergeCell ref="A213:A220"/>
     <mergeCell ref="A221:A232"/>
     <mergeCell ref="A233:A241"/>
@@ -8087,6 +8357,7 @@
     <mergeCell ref="F94:F99"/>
     <mergeCell ref="F100:F108"/>
     <mergeCell ref="F109:F121"/>
+    <mergeCell ref="F122:F128"/>
     <mergeCell ref="F213:F220"/>
     <mergeCell ref="F221:F232"/>
     <mergeCell ref="F233:F241"/>
@@ -8121,16 +8392,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -8147,7 +8418,7 @@
         <v>38678</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D2" s="27">
         <v>3</v>
@@ -8170,7 +8441,7 @@
       <c r="D3" s="27"/>
       <c r="E3" s="17"/>
       <c r="F3" s="123" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G3" s="53">
         <f>G2*11%</f>
@@ -8212,7 +8483,7 @@
       <c r="D6" s="122"/>
       <c r="E6" s="7"/>
       <c r="F6" s="127" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G6" s="7">
         <f>G5*11%</f>
@@ -8294,7 +8565,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="81" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="82"/>
       <c r="C14" s="82"/>
@@ -8349,16 +8620,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -8497,7 +8768,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="81" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="82"/>
       <c r="C14" s="82"/>
@@ -8551,16 +8822,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -8569,7 +8840,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" ht="147.55" customHeight="1" spans="1:8">
@@ -8577,10 +8848,10 @@
         <v>45999</v>
       </c>
       <c r="B2" s="93" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D2" s="56">
         <v>24</v>
@@ -8607,7 +8878,7 @@
       </c>
       <c r="E3" s="106"/>
       <c r="F3" s="86" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G3" s="107">
         <f>G2*11%</f>
@@ -8655,7 +8926,7 @@
       </c>
       <c r="E6" s="85"/>
       <c r="F6" s="86" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G6" s="107">
         <f>G5*11%</f>
@@ -8700,7 +8971,7 @@
       <c r="D9" s="102"/>
       <c r="E9" s="85"/>
       <c r="F9" s="86" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G9" s="107">
         <f>G8*11%</f>
@@ -8745,7 +9016,7 @@
       <c r="D12" s="102"/>
       <c r="E12" s="85"/>
       <c r="F12" s="86" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G12" s="107">
         <f>G11*11%</f>
@@ -8787,7 +9058,7 @@
       <c r="D15" s="102"/>
       <c r="E15" s="85"/>
       <c r="F15" s="86" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G15" s="107">
         <f>G14*11%</f>
@@ -8812,7 +9083,7 @@
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:8">
       <c r="A17" s="81" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="82"/>
       <c r="C17" s="82"/>
@@ -8871,51 +9142,77 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="35" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="158" customHeight="1" spans="1:7">
-      <c r="A2" s="25"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="17"/>
+    <row r="2" ht="192.8" spans="1:7">
+      <c r="A2" s="25">
+        <v>46001</v>
+      </c>
+      <c r="B2" s="93" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="56">
+        <v>10</v>
+      </c>
+      <c r="E2" s="21">
+        <v>280000</v>
+      </c>
+      <c r="F2" s="17" t="str">
+        <f>_xlfn.DISPIMG("ID_A7288E1D8486499C936AD7CFEE5889FB",1)</f>
+        <v>=DISPIMG("ID_A7288E1D8486499C936AD7CFEE5889FB",1)</v>
+      </c>
       <c r="G2" s="21">
         <f>SUM(D2*E2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" ht="155.75" customHeight="1" spans="1:7">
-      <c r="A3" s="25"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="17"/>
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="3" ht="191.7" spans="1:7">
+      <c r="A3" s="25">
+        <v>46006</v>
+      </c>
+      <c r="B3" s="93" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="56">
+        <v>10</v>
+      </c>
+      <c r="E3" s="21">
+        <v>280000</v>
+      </c>
+      <c r="F3" s="17" t="str">
+        <f>_xlfn.DISPIMG("ID_EC8B07304AE24AABAA210E4FDB7BE2A3",1)</f>
+        <v>=DISPIMG("ID_EC8B07304AE24AABAA210E4FDB7BE2A3",1)</v>
+      </c>
       <c r="G3" s="21">
         <f>SUM(D3*E3)</f>
-        <v>0</v>
+        <v>2800000</v>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1" spans="1:7">
       <c r="A4" s="94" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B4" s="95"/>
       <c r="C4" s="95"/>
@@ -8923,7 +9220,7 @@
       <c r="E4" s="95"/>
       <c r="F4" s="96">
         <f>SUM(G2:G3)</f>
-        <v>0</v>
+        <v>5600000</v>
       </c>
       <c r="G4" s="96"/>
     </row>
@@ -8956,16 +9253,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -8979,10 +9276,10 @@
         <v>45999</v>
       </c>
       <c r="B2" s="77" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D2" s="27">
         <v>3</v>
@@ -9008,7 +9305,7 @@
       </c>
       <c r="E3" s="85"/>
       <c r="F3" s="85" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G3" s="86">
         <f>G2*11%</f>
@@ -9063,7 +9360,7 @@
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:7">
       <c r="A8" s="81" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" s="82"/>
       <c r="C8" s="82"/>
@@ -9111,19 +9408,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" ht="321" customHeight="1" spans="1:6">
@@ -9186,16 +9483,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -9296,7 +9593,7 @@
     </row>
     <row r="12" ht="27" customHeight="1" spans="1:7">
       <c r="A12" s="49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="50"/>
       <c r="C12" s="50"/>
@@ -9349,13 +9646,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>3</v>
@@ -9364,7 +9661,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" ht="324.4" customHeight="1" spans="1:7">
@@ -9423,22 +9720,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" ht="177" customHeight="1" spans="1:7">
@@ -9499,10 +9796,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>5</v>
@@ -9513,11 +9810,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C2" s="5">
         <f>'BUK BUNGA (Groceries)'!F297</f>
-        <v>5052000</v>
+        <v>5674000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9525,11 +9822,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C3" s="5">
         <f>'WARUNG EKA (Drinks, Etc)'!G117</f>
-        <v>3982000</v>
+        <v>5228000</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9537,11 +9834,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C4" s="5">
         <f>'DEWATA COCONUT (Coconut)'!E10</f>
-        <v>1200000</v>
+        <v>1440000</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9549,7 +9846,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C5" s="5">
         <f>'SEDANA JAYA'!F37</f>
@@ -9561,7 +9858,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C6" s="5">
         <f>'PNB (Alcohol)'!H7</f>
@@ -9573,11 +9870,11 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C7" s="5">
         <f>'DSP (Alcohol)'!F16</f>
-        <v>3780000</v>
+        <v>5575500</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:3">
@@ -9585,7 +9882,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C8" s="5">
         <f>'DSP ARYA BIMA (Alcohol)'!E3</f>
@@ -9597,7 +9894,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C9" s="5" t="str">
         <f>'SELERA OR STIR UP (Syrup)'!F19</f>
@@ -9609,7 +9906,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C10" s="5">
         <f>'DW BALI (Alcohol)'!E6</f>
@@ -9621,7 +9918,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C11" s="5">
         <f>'DDB (Alcohol)'!E14</f>
@@ -9633,7 +9930,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C12" s="5">
         <f>'NANO DEWATA (Alcohol)'!E14</f>
@@ -9645,7 +9942,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C13" s="5">
         <f>'BALI PERMATA JAYA (Corona Beer)'!E17</f>
@@ -9657,11 +9954,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C14" s="7">
         <f>'BLACK COFFEE ROASTERS (Coffee)'!F4</f>
-        <v>0</v>
+        <v>5600000</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9669,7 +9966,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C15" s="5">
         <f>'PT. PRASIDA LANTUR MAJU (Wine)'!E8</f>
@@ -9681,7 +9978,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C16" s="8">
         <f>'PT LOVINA BEACH BREWERY'!D3</f>
@@ -9693,7 +9990,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C17" s="5">
         <f>'CHAI CHITAI (Tea Leaf,etc)'!E12</f>
@@ -9705,7 +10002,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C18" s="5">
         <f>'MULIA JAYA (Passion Fruit)'!D3</f>
@@ -9717,7 +10014,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C19" s="5">
         <f>'Dewata Kencana Distribusi (Vdka'!E3</f>
@@ -9731,7 +10028,7 @@
       <c r="B20" s="9"/>
       <c r="C20" s="10">
         <f>SUM(C2:C13)</f>
-        <v>18804109.94</v>
+        <v>22707609.94</v>
       </c>
     </row>
   </sheetData>
@@ -9778,7 +10075,7 @@
       <c r="D1" s="258" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="265" t="s">
+      <c r="E1" s="276" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="257" t="s">
@@ -9804,11 +10101,11 @@
       <c r="E2" s="7">
         <v>8000</v>
       </c>
-      <c r="F2" s="266">
+      <c r="F2" s="277">
         <f>SUM(D2*E2)</f>
         <v>40000</v>
       </c>
-      <c r="G2" s="267">
+      <c r="G2" s="278">
         <f>SUM(F2:F4)</f>
         <v>82000</v>
       </c>
@@ -9825,11 +10122,11 @@
       <c r="E3" s="7">
         <v>20000</v>
       </c>
-      <c r="F3" s="266">
+      <c r="F3" s="277">
         <f>SUM(D3*E3)</f>
         <v>20000</v>
       </c>
-      <c r="G3" s="268"/>
+      <c r="G3" s="279"/>
     </row>
     <row r="4" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A4" s="260"/>
@@ -9843,11 +10140,11 @@
       <c r="E4" s="7">
         <v>22000</v>
       </c>
-      <c r="F4" s="266">
+      <c r="F4" s="277">
         <f t="shared" ref="F4:F9" si="0">SUM(D4*E4)</f>
         <v>22000</v>
       </c>
-      <c r="G4" s="269"/>
+      <c r="G4" s="280"/>
     </row>
     <row r="5" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A5" s="206">
@@ -9865,11 +10162,11 @@
       <c r="E5" s="7">
         <v>8000</v>
       </c>
-      <c r="F5" s="266">
+      <c r="F5" s="277">
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="G5" s="267">
+      <c r="G5" s="278">
         <f>SUM(F5:F7)</f>
         <v>82000</v>
       </c>
@@ -9886,11 +10183,11 @@
       <c r="E6" s="7">
         <v>20000</v>
       </c>
-      <c r="F6" s="266">
+      <c r="F6" s="277">
         <f t="shared" si="0"/>
         <v>20000</v>
       </c>
-      <c r="G6" s="268"/>
+      <c r="G6" s="279"/>
     </row>
     <row r="7" s="249" customFormat="1" ht="18" customHeight="1" spans="1:7">
       <c r="A7" s="207"/>
@@ -9904,11 +10201,11 @@
       <c r="E7" s="7">
         <v>22000</v>
       </c>
-      <c r="F7" s="266">
+      <c r="F7" s="277">
         <f t="shared" si="0"/>
         <v>22000</v>
       </c>
-      <c r="G7" s="270"/>
+      <c r="G7" s="281"/>
     </row>
     <row r="8" s="249" customFormat="1" ht="18" customHeight="1" spans="1:7">
       <c r="A8" s="206">
@@ -9926,11 +10223,11 @@
       <c r="E8" s="7">
         <v>8000</v>
       </c>
-      <c r="F8" s="266">
+      <c r="F8" s="277">
         <f t="shared" si="0"/>
         <v>48000</v>
       </c>
-      <c r="G8" s="267">
+      <c r="G8" s="278">
         <f>SUM(F8:F13)</f>
         <v>703000</v>
       </c>
@@ -9947,11 +10244,11 @@
       <c r="E9" s="7">
         <v>135000</v>
       </c>
-      <c r="F9" s="266">
+      <c r="F9" s="277">
         <f t="shared" si="0"/>
         <v>135000</v>
       </c>
-      <c r="G9" s="268"/>
+      <c r="G9" s="279"/>
     </row>
     <row r="10" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A10" s="209"/>
@@ -9965,11 +10262,11 @@
       <c r="E10" s="7">
         <v>135000</v>
       </c>
-      <c r="F10" s="266">
+      <c r="F10" s="277">
         <f t="shared" ref="F10:F22" si="1">SUM(D10*E10)</f>
         <v>135000</v>
       </c>
-      <c r="G10" s="268"/>
+      <c r="G10" s="279"/>
     </row>
     <row r="11" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A11" s="209"/>
@@ -9983,11 +10280,11 @@
       <c r="E11" s="7">
         <v>20000</v>
       </c>
-      <c r="F11" s="266">
+      <c r="F11" s="277">
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="G11" s="268"/>
+      <c r="G11" s="279"/>
     </row>
     <row r="12" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A12" s="209"/>
@@ -10001,11 +10298,11 @@
       <c r="E12" s="7">
         <v>120000</v>
       </c>
-      <c r="F12" s="266">
+      <c r="F12" s="277">
         <f t="shared" si="1"/>
         <v>240000</v>
       </c>
-      <c r="G12" s="268"/>
+      <c r="G12" s="279"/>
     </row>
     <row r="13" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A13" s="207"/>
@@ -10019,11 +10316,11 @@
       <c r="E13" s="7">
         <v>125000</v>
       </c>
-      <c r="F13" s="266">
+      <c r="F13" s="277">
         <f t="shared" si="1"/>
         <v>125000</v>
       </c>
-      <c r="G13" s="269"/>
+      <c r="G13" s="280"/>
     </row>
     <row r="14" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A14" s="206">
@@ -10041,11 +10338,11 @@
       <c r="E14" s="7">
         <v>8000</v>
       </c>
-      <c r="F14" s="266">
+      <c r="F14" s="277">
         <f t="shared" si="1"/>
         <v>48000</v>
       </c>
-      <c r="G14" s="267">
+      <c r="G14" s="278">
         <f>SUM(F14:F15)</f>
         <v>92000</v>
       </c>
@@ -10062,11 +10359,11 @@
       <c r="E15" s="7">
         <v>22000</v>
       </c>
-      <c r="F15" s="266">
+      <c r="F15" s="277">
         <f t="shared" si="1"/>
         <v>44000</v>
       </c>
-      <c r="G15" s="269"/>
+      <c r="G15" s="280"/>
     </row>
     <row r="16" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A16" s="206">
@@ -10084,11 +10381,11 @@
       <c r="E16" s="7">
         <v>20000</v>
       </c>
-      <c r="F16" s="266">
+      <c r="F16" s="277">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="G16" s="267">
+      <c r="G16" s="278">
         <f>SUM(F16:F18)</f>
         <v>102000</v>
       </c>
@@ -10105,11 +10402,11 @@
       <c r="E17" s="7">
         <v>22000</v>
       </c>
-      <c r="F17" s="266">
+      <c r="F17" s="277">
         <f t="shared" si="1"/>
         <v>22000</v>
       </c>
-      <c r="G17" s="268"/>
+      <c r="G17" s="279"/>
     </row>
     <row r="18" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A18" s="207"/>
@@ -10123,11 +10420,11 @@
       <c r="E18" s="7">
         <v>8000</v>
       </c>
-      <c r="F18" s="266">
+      <c r="F18" s="277">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="G18" s="269"/>
+      <c r="G18" s="280"/>
     </row>
     <row r="19" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A19" s="206">
@@ -10145,11 +10442,11 @@
       <c r="E19" s="7">
         <v>22000</v>
       </c>
-      <c r="F19" s="266">
+      <c r="F19" s="277">
         <f t="shared" si="1"/>
         <v>44000</v>
       </c>
-      <c r="G19" s="267">
+      <c r="G19" s="278">
         <f>SUM(F19:F23)</f>
         <v>814000</v>
       </c>
@@ -10166,11 +10463,11 @@
       <c r="E20" s="7">
         <v>20000</v>
       </c>
-      <c r="F20" s="266">
+      <c r="F20" s="277">
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="G20" s="268"/>
+      <c r="G20" s="279"/>
     </row>
     <row r="21" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A21" s="209"/>
@@ -10184,11 +10481,11 @@
       <c r="E21" s="7">
         <v>8000</v>
       </c>
-      <c r="F21" s="266">
+      <c r="F21" s="277">
         <f t="shared" ref="F21:F45" si="2">SUM(D21*E21)</f>
         <v>40000</v>
       </c>
-      <c r="G21" s="268"/>
+      <c r="G21" s="279"/>
     </row>
     <row r="22" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A22" s="209"/>
@@ -10202,11 +10499,11 @@
       <c r="E22" s="7">
         <v>480000</v>
       </c>
-      <c r="F22" s="266">
+      <c r="F22" s="277">
         <f t="shared" si="2"/>
         <v>480000</v>
       </c>
-      <c r="G22" s="268"/>
+      <c r="G22" s="279"/>
     </row>
     <row r="23" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A23" s="207"/>
@@ -10220,11 +10517,11 @@
       <c r="E23" s="7">
         <v>115000</v>
       </c>
-      <c r="F23" s="266">
+      <c r="F23" s="277">
         <f t="shared" si="2"/>
         <v>230000</v>
       </c>
-      <c r="G23" s="269"/>
+      <c r="G23" s="280"/>
     </row>
     <row r="24" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A24" s="206">
@@ -10242,11 +10539,11 @@
       <c r="E24" s="7">
         <v>125000</v>
       </c>
-      <c r="F24" s="266">
+      <c r="F24" s="277">
         <f t="shared" si="2"/>
         <v>125000</v>
       </c>
-      <c r="G24" s="267">
+      <c r="G24" s="278">
         <f>SUM(F24:F27)</f>
         <v>302000</v>
       </c>
@@ -10263,11 +10560,11 @@
       <c r="E25" s="7">
         <v>125000</v>
       </c>
-      <c r="F25" s="266">
+      <c r="F25" s="277">
         <f t="shared" si="2"/>
         <v>125000</v>
       </c>
-      <c r="G25" s="268"/>
+      <c r="G25" s="279"/>
     </row>
     <row r="26" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A26" s="209"/>
@@ -10281,11 +10578,11 @@
       <c r="E26" s="7">
         <v>20000</v>
       </c>
-      <c r="F26" s="266">
+      <c r="F26" s="277">
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="G26" s="268"/>
+      <c r="G26" s="279"/>
     </row>
     <row r="27" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A27" s="207"/>
@@ -10299,11 +10596,11 @@
       <c r="E27" s="7">
         <v>8000</v>
       </c>
-      <c r="F27" s="266">
+      <c r="F27" s="277">
         <f t="shared" si="2"/>
         <v>32000</v>
       </c>
-      <c r="G27" s="269"/>
+      <c r="G27" s="280"/>
     </row>
     <row r="28" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A28" s="206">
@@ -10321,11 +10618,11 @@
       <c r="E28" s="7">
         <v>10000</v>
       </c>
-      <c r="F28" s="266">
+      <c r="F28" s="277">
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="G28" s="267">
+      <c r="G28" s="278">
         <f>SUM(F28:F30)</f>
         <v>92000</v>
       </c>
@@ -10342,11 +10639,11 @@
       <c r="E29" s="7">
         <v>20000</v>
       </c>
-      <c r="F29" s="266">
+      <c r="F29" s="277">
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="G29" s="268"/>
+      <c r="G29" s="279"/>
     </row>
     <row r="30" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A30" s="207"/>
@@ -10360,11 +10657,11 @@
       <c r="E30" s="7">
         <v>22000</v>
       </c>
-      <c r="F30" s="266">
+      <c r="F30" s="277">
         <f t="shared" si="2"/>
         <v>22000</v>
       </c>
-      <c r="G30" s="269"/>
+      <c r="G30" s="280"/>
     </row>
     <row r="31" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A31" s="56">
@@ -10382,11 +10679,11 @@
       <c r="E31" s="7">
         <v>8000</v>
       </c>
-      <c r="F31" s="266">
+      <c r="F31" s="277">
         <f t="shared" si="2"/>
         <v>48000</v>
       </c>
-      <c r="G31" s="267">
+      <c r="G31" s="278">
         <f>SUM(F31:F37)</f>
         <v>705000</v>
       </c>
@@ -10403,11 +10700,11 @@
       <c r="E32" s="7">
         <v>20000</v>
       </c>
-      <c r="F32" s="266">
+      <c r="F32" s="277">
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="G32" s="268"/>
+      <c r="G32" s="279"/>
     </row>
     <row r="33" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A33" s="56"/>
@@ -10421,11 +10718,11 @@
       <c r="E33" s="7">
         <v>22000</v>
       </c>
-      <c r="F33" s="266">
+      <c r="F33" s="277">
         <f t="shared" si="2"/>
         <v>22000</v>
       </c>
-      <c r="G33" s="268"/>
+      <c r="G33" s="279"/>
     </row>
     <row r="34" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A34" s="56"/>
@@ -10439,11 +10736,11 @@
       <c r="E34" s="7">
         <v>135000</v>
       </c>
-      <c r="F34" s="266">
+      <c r="F34" s="277">
         <f t="shared" si="2"/>
         <v>135000</v>
       </c>
-      <c r="G34" s="268"/>
+      <c r="G34" s="279"/>
     </row>
     <row r="35" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A35" s="56"/>
@@ -10457,11 +10754,11 @@
       <c r="E35" s="7">
         <v>125000</v>
       </c>
-      <c r="F35" s="266">
+      <c r="F35" s="277">
         <f t="shared" si="2"/>
         <v>125000</v>
       </c>
-      <c r="G35" s="268"/>
+      <c r="G35" s="279"/>
     </row>
     <row r="36" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A36" s="56"/>
@@ -10475,11 +10772,11 @@
       <c r="E36" s="7">
         <v>125000</v>
       </c>
-      <c r="F36" s="266">
+      <c r="F36" s="277">
         <f t="shared" si="2"/>
         <v>125000</v>
       </c>
-      <c r="G36" s="268"/>
+      <c r="G36" s="279"/>
     </row>
     <row r="37" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A37" s="56"/>
@@ -10493,11 +10790,11 @@
       <c r="E37" s="7">
         <v>115000</v>
       </c>
-      <c r="F37" s="266">
+      <c r="F37" s="277">
         <f t="shared" si="2"/>
         <v>230000</v>
       </c>
-      <c r="G37" s="269"/>
+      <c r="G37" s="280"/>
     </row>
     <row r="38" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A38" s="206">
@@ -10515,11 +10812,11 @@
       <c r="E38" s="7">
         <v>8000</v>
       </c>
-      <c r="F38" s="266">
+      <c r="F38" s="277">
         <f t="shared" si="2"/>
         <v>48000</v>
       </c>
-      <c r="G38" s="267">
+      <c r="G38" s="278">
         <f>SUM(F38:F40)</f>
         <v>223000</v>
       </c>
@@ -10536,11 +10833,11 @@
       <c r="E39" s="7">
         <v>20000</v>
       </c>
-      <c r="F39" s="266">
+      <c r="F39" s="277">
         <f t="shared" si="2"/>
         <v>40000</v>
       </c>
-      <c r="G39" s="268"/>
+      <c r="G39" s="279"/>
     </row>
     <row r="40" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A40" s="209"/>
@@ -10554,11 +10851,11 @@
       <c r="E40" s="7">
         <v>135000</v>
       </c>
-      <c r="F40" s="266">
+      <c r="F40" s="277">
         <f t="shared" si="2"/>
         <v>135000</v>
       </c>
-      <c r="G40" s="269"/>
+      <c r="G40" s="280"/>
     </row>
     <row r="41" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A41" s="206">
@@ -10576,11 +10873,11 @@
       <c r="E41" s="7">
         <v>8000</v>
       </c>
-      <c r="F41" s="266">
+      <c r="F41" s="277">
         <f t="shared" si="2"/>
         <v>48000</v>
       </c>
-      <c r="G41" s="267">
+      <c r="G41" s="278">
         <f>SUM(F41:F45)</f>
         <v>717000</v>
       </c>
@@ -10597,11 +10894,11 @@
       <c r="E42" s="7">
         <v>20000</v>
       </c>
-      <c r="F42" s="266">
+      <c r="F42" s="277">
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="G42" s="268"/>
+      <c r="G42" s="279"/>
     </row>
     <row r="43" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A43" s="209"/>
@@ -10615,11 +10912,11 @@
       <c r="E43" s="7">
         <v>22000</v>
       </c>
-      <c r="F43" s="266">
+      <c r="F43" s="277">
         <f t="shared" si="2"/>
         <v>44000</v>
       </c>
-      <c r="G43" s="268"/>
+      <c r="G43" s="279"/>
     </row>
     <row r="44" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A44" s="209"/>
@@ -10633,11 +10930,11 @@
       <c r="E44" s="7">
         <v>480000</v>
       </c>
-      <c r="F44" s="266">
+      <c r="F44" s="277">
         <f t="shared" si="2"/>
         <v>480000</v>
       </c>
-      <c r="G44" s="268"/>
+      <c r="G44" s="279"/>
     </row>
     <row r="45" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A45" s="207"/>
@@ -10651,11 +10948,11 @@
       <c r="E45" s="7">
         <v>125000</v>
       </c>
-      <c r="F45" s="266">
+      <c r="F45" s="277">
         <f t="shared" ref="F45:F71" si="3">SUM(D45*E45)</f>
         <v>125000</v>
       </c>
-      <c r="G45" s="269"/>
+      <c r="G45" s="280"/>
     </row>
     <row r="46" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
       <c r="A46" s="206">
@@ -10673,11 +10970,11 @@
       <c r="E46" s="7">
         <v>20000</v>
       </c>
-      <c r="F46" s="266">
+      <c r="F46" s="277">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="G46" s="267">
+      <c r="G46" s="278">
         <f>SUM(F46:F47)</f>
         <v>68000</v>
       </c>
@@ -10694,200 +10991,290 @@
       <c r="E47" s="7">
         <v>8000</v>
       </c>
-      <c r="F47" s="266">
+      <c r="F47" s="277">
         <f t="shared" si="3"/>
         <v>48000</v>
       </c>
-      <c r="G47" s="269"/>
+      <c r="G47" s="280"/>
     </row>
     <row r="48" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A48" s="204"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="259"/>
-      <c r="D48" s="115"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="266">
+      <c r="A48" s="264">
+        <v>74836</v>
+      </c>
+      <c r="B48" s="265">
+        <v>46005</v>
+      </c>
+      <c r="C48" s="259" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="115">
+        <v>5</v>
+      </c>
+      <c r="E48" s="7">
+        <v>8000</v>
+      </c>
+      <c r="F48" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="271"/>
+        <v>40000</v>
+      </c>
+      <c r="G48" s="282">
+        <f>SUM(F48:F50)</f>
+        <v>82000</v>
+      </c>
     </row>
     <row r="49" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A49" s="204"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="259"/>
-      <c r="D49" s="115"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="266">
+      <c r="A49" s="266"/>
+      <c r="B49" s="267"/>
+      <c r="C49" s="259" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" s="115">
+        <v>1</v>
+      </c>
+      <c r="E49" s="7">
+        <v>20000</v>
+      </c>
+      <c r="F49" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G49" s="271"/>
+        <v>20000</v>
+      </c>
+      <c r="G49" s="283"/>
     </row>
     <row r="50" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A50" s="204"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="259"/>
-      <c r="D50" s="115"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="266">
+      <c r="A50" s="268"/>
+      <c r="B50" s="269"/>
+      <c r="C50" s="259" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" s="115">
+        <v>1</v>
+      </c>
+      <c r="E50" s="7">
+        <v>22000</v>
+      </c>
+      <c r="F50" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G50" s="271"/>
+        <v>22000</v>
+      </c>
+      <c r="G50" s="284"/>
     </row>
     <row r="51" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A51" s="204"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="259"/>
-      <c r="D51" s="115"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="266">
+      <c r="A51" s="264">
+        <v>74890</v>
+      </c>
+      <c r="B51" s="265">
+        <v>46006</v>
+      </c>
+      <c r="C51" s="259" t="s">
+        <v>42</v>
+      </c>
+      <c r="D51" s="115">
+        <v>6</v>
+      </c>
+      <c r="E51" s="7">
+        <v>8000</v>
+      </c>
+      <c r="F51" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="271"/>
+        <v>48000</v>
+      </c>
+      <c r="G51" s="282">
+        <f>SUM(F51:F55)</f>
+        <v>455000</v>
+      </c>
     </row>
     <row r="52" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A52" s="204"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="259"/>
-      <c r="D52" s="115"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="266">
+      <c r="A52" s="266"/>
+      <c r="B52" s="267"/>
+      <c r="C52" s="259" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" s="115">
+        <v>1</v>
+      </c>
+      <c r="E52" s="7">
+        <v>20000</v>
+      </c>
+      <c r="F52" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G52" s="271"/>
+        <v>20000</v>
+      </c>
+      <c r="G52" s="283"/>
     </row>
     <row r="53" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A53" s="204"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="259"/>
-      <c r="D53" s="115"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="266">
+      <c r="A53" s="266"/>
+      <c r="B53" s="267"/>
+      <c r="C53" s="259" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" s="115">
+        <v>1</v>
+      </c>
+      <c r="E53" s="7">
+        <v>22000</v>
+      </c>
+      <c r="F53" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G53" s="271"/>
+        <v>22000</v>
+      </c>
+      <c r="G53" s="283"/>
     </row>
     <row r="54" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A54" s="56"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="259"/>
-      <c r="D54" s="115"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="266">
+      <c r="A54" s="266"/>
+      <c r="B54" s="267"/>
+      <c r="C54" s="259" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="115">
+        <v>1</v>
+      </c>
+      <c r="E54" s="7">
+        <v>125000</v>
+      </c>
+      <c r="F54" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G54" s="271">
-        <f>SUM(F54:F57)</f>
-        <v>0</v>
-      </c>
+        <v>125000</v>
+      </c>
+      <c r="G54" s="283"/>
     </row>
     <row r="55" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A55" s="56"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="264"/>
-      <c r="D55" s="260"/>
-      <c r="E55" s="134"/>
-      <c r="F55" s="266">
+      <c r="A55" s="268"/>
+      <c r="B55" s="269"/>
+      <c r="C55" s="270" t="s">
+        <v>47</v>
+      </c>
+      <c r="D55" s="260">
+        <v>2</v>
+      </c>
+      <c r="E55" s="134">
+        <v>120000</v>
+      </c>
+      <c r="F55" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G55" s="271"/>
+        <v>240000</v>
+      </c>
+      <c r="G55" s="284"/>
     </row>
     <row r="56" s="249" customFormat="1" ht="19" customHeight="1" spans="1:7">
-      <c r="A56" s="56"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="259"/>
-      <c r="D56" s="115"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="266">
+      <c r="A56" s="271">
+        <v>74965</v>
+      </c>
+      <c r="B56" s="272">
+        <v>46007</v>
+      </c>
+      <c r="C56" s="259" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56" s="115">
+        <v>5</v>
+      </c>
+      <c r="E56" s="7">
+        <v>8000</v>
+      </c>
+      <c r="F56" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G56" s="271"/>
+        <v>40000</v>
+      </c>
+      <c r="G56" s="282">
+        <f>SUM(F56:F60)</f>
+        <v>709000</v>
+      </c>
     </row>
     <row r="57" s="249" customFormat="1" spans="1:7">
-      <c r="A57" s="56"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="259"/>
-      <c r="D57" s="115"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="266">
+      <c r="A57" s="271"/>
+      <c r="B57" s="272"/>
+      <c r="C57" s="259" t="s">
+        <v>43</v>
+      </c>
+      <c r="D57" s="115">
+        <v>1</v>
+      </c>
+      <c r="E57" s="7">
+        <v>20000</v>
+      </c>
+      <c r="F57" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G57" s="271"/>
+        <v>20000</v>
+      </c>
+      <c r="G57" s="283"/>
     </row>
     <row r="58" s="249" customFormat="1" spans="1:7">
-      <c r="A58" s="209"/>
-      <c r="B58" s="40"/>
-      <c r="C58" s="259"/>
-      <c r="D58" s="115"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="266">
+      <c r="A58" s="271"/>
+      <c r="B58" s="272"/>
+      <c r="C58" s="259" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58" s="115">
+        <v>2</v>
+      </c>
+      <c r="E58" s="7">
+        <v>22000</v>
+      </c>
+      <c r="F58" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G58" s="271">
-        <f>SUM(F58:F59)</f>
-        <v>0</v>
-      </c>
+        <v>44000</v>
+      </c>
+      <c r="G58" s="283"/>
     </row>
     <row r="59" s="249" customFormat="1" spans="1:7">
-      <c r="A59" s="207"/>
-      <c r="B59" s="131"/>
-      <c r="C59" s="259"/>
-      <c r="D59" s="115"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="266">
+      <c r="A59" s="271"/>
+      <c r="B59" s="272"/>
+      <c r="C59" s="259" t="s">
+        <v>49</v>
+      </c>
+      <c r="D59" s="115">
+        <v>1</v>
+      </c>
+      <c r="E59" s="7">
+        <v>480000</v>
+      </c>
+      <c r="F59" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G59" s="271"/>
+        <v>480000</v>
+      </c>
+      <c r="G59" s="283"/>
     </row>
     <row r="60" s="249" customFormat="1" spans="1:7">
-      <c r="A60" s="206"/>
-      <c r="B60" s="36"/>
-      <c r="C60" s="259"/>
-      <c r="D60" s="115"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="266">
+      <c r="A60" s="271"/>
+      <c r="B60" s="272"/>
+      <c r="C60" s="259" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" s="115">
+        <v>1</v>
+      </c>
+      <c r="E60" s="7">
+        <v>125000</v>
+      </c>
+      <c r="F60" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G60" s="271">
-        <f>SUM(F60:F62)</f>
-        <v>0</v>
-      </c>
+        <v>125000</v>
+      </c>
+      <c r="G60" s="284"/>
     </row>
     <row r="61" s="249" customFormat="1" spans="1:7">
-      <c r="A61" s="209"/>
-      <c r="B61" s="40"/>
+      <c r="A61" s="273"/>
+      <c r="B61" s="274"/>
       <c r="C61" s="259"/>
       <c r="D61" s="115"/>
       <c r="E61" s="7"/>
-      <c r="F61" s="266">
+      <c r="F61" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G61" s="271"/>
+      <c r="G61" s="285"/>
     </row>
     <row r="62" s="249" customFormat="1" spans="1:7">
-      <c r="A62" s="207"/>
-      <c r="B62" s="131"/>
+      <c r="A62" s="211"/>
+      <c r="B62" s="275"/>
       <c r="C62" s="259"/>
       <c r="D62" s="115"/>
       <c r="E62" s="7"/>
-      <c r="F62" s="266">
+      <c r="F62" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G62" s="271"/>
+      <c r="G62" s="285"/>
     </row>
     <row r="63" s="249" customFormat="1" spans="1:7">
       <c r="A63" s="56"/>
@@ -10895,11 +11282,11 @@
       <c r="C63" s="259"/>
       <c r="D63" s="115"/>
       <c r="E63" s="7"/>
-      <c r="F63" s="266">
+      <c r="F63" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G63" s="271">
+      <c r="G63" s="285">
         <f>SUM(F63:F67)</f>
         <v>0</v>
       </c>
@@ -10910,11 +11297,11 @@
       <c r="C64" s="259"/>
       <c r="D64" s="115"/>
       <c r="E64" s="7"/>
-      <c r="F64" s="266">
+      <c r="F64" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G64" s="271"/>
+      <c r="G64" s="285"/>
     </row>
     <row r="65" s="249" customFormat="1" spans="1:7">
       <c r="A65" s="56"/>
@@ -10922,11 +11309,11 @@
       <c r="C65" s="259"/>
       <c r="D65" s="115"/>
       <c r="E65" s="7"/>
-      <c r="F65" s="266">
+      <c r="F65" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G65" s="271"/>
+      <c r="G65" s="285"/>
     </row>
     <row r="66" s="249" customFormat="1" spans="1:7">
       <c r="A66" s="56"/>
@@ -10934,11 +11321,11 @@
       <c r="C66" s="259"/>
       <c r="D66" s="115"/>
       <c r="E66" s="7"/>
-      <c r="F66" s="266">
+      <c r="F66" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G66" s="271"/>
+      <c r="G66" s="285"/>
     </row>
     <row r="67" s="249" customFormat="1" spans="1:8">
       <c r="A67" s="56"/>
@@ -10946,12 +11333,12 @@
       <c r="C67" s="259"/>
       <c r="D67" s="115"/>
       <c r="E67" s="7"/>
-      <c r="F67" s="266">
+      <c r="F67" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G67" s="271"/>
-      <c r="H67" s="275"/>
+      <c r="G67" s="285"/>
+      <c r="H67" s="289"/>
     </row>
     <row r="68" s="249" customFormat="1" ht="17.6" spans="1:14">
       <c r="A68" s="56"/>
@@ -10959,21 +11346,21 @@
       <c r="C68" s="259"/>
       <c r="D68" s="115"/>
       <c r="E68" s="7"/>
-      <c r="F68" s="266">
+      <c r="F68" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G68" s="271">
+      <c r="G68" s="285">
         <f>SUM(F68)</f>
         <v>0</v>
       </c>
-      <c r="H68" s="275"/>
-      <c r="I68" s="277"/>
-      <c r="J68" s="278"/>
-      <c r="K68" s="279"/>
-      <c r="L68" s="280"/>
-      <c r="M68" s="280"/>
-      <c r="N68" s="282"/>
+      <c r="H68" s="289"/>
+      <c r="I68" s="291"/>
+      <c r="J68" s="292"/>
+      <c r="K68" s="293"/>
+      <c r="L68" s="294"/>
+      <c r="M68" s="294"/>
+      <c r="N68" s="296"/>
     </row>
     <row r="69" s="249" customFormat="1" ht="17.6" spans="1:14">
       <c r="A69" s="206"/>
@@ -10981,20 +11368,20 @@
       <c r="C69" s="259"/>
       <c r="D69" s="115"/>
       <c r="E69" s="7"/>
-      <c r="F69" s="266">
+      <c r="F69" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G69" s="271">
+      <c r="G69" s="285">
         <f>SUM(F69:F71)</f>
         <v>0</v>
       </c>
-      <c r="I69" s="281"/>
-      <c r="J69" s="278"/>
-      <c r="K69" s="279"/>
-      <c r="L69" s="280"/>
-      <c r="M69" s="280"/>
-      <c r="N69" s="280"/>
+      <c r="I69" s="295"/>
+      <c r="J69" s="292"/>
+      <c r="K69" s="293"/>
+      <c r="L69" s="294"/>
+      <c r="M69" s="294"/>
+      <c r="N69" s="294"/>
     </row>
     <row r="70" s="249" customFormat="1" ht="17.6" spans="1:14">
       <c r="A70" s="209"/>
@@ -11002,17 +11389,17 @@
       <c r="C70" s="259"/>
       <c r="D70" s="115"/>
       <c r="E70" s="7"/>
-      <c r="F70" s="266">
+      <c r="F70" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G70" s="271"/>
-      <c r="I70" s="281"/>
-      <c r="J70" s="278"/>
-      <c r="K70" s="279"/>
-      <c r="L70" s="280"/>
-      <c r="M70" s="280"/>
-      <c r="N70" s="280"/>
+      <c r="G70" s="285"/>
+      <c r="I70" s="295"/>
+      <c r="J70" s="292"/>
+      <c r="K70" s="293"/>
+      <c r="L70" s="294"/>
+      <c r="M70" s="294"/>
+      <c r="N70" s="294"/>
     </row>
     <row r="71" s="249" customFormat="1" ht="17.6" spans="1:14">
       <c r="A71" s="207"/>
@@ -11020,29 +11407,29 @@
       <c r="C71" s="259"/>
       <c r="D71" s="115"/>
       <c r="E71" s="7"/>
-      <c r="F71" s="266">
+      <c r="F71" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G71" s="271"/>
-      <c r="I71" s="281"/>
-      <c r="J71" s="278"/>
-      <c r="K71" s="279"/>
-      <c r="L71" s="280"/>
-      <c r="M71" s="280"/>
-      <c r="N71" s="280"/>
+      <c r="G71" s="285"/>
+      <c r="I71" s="295"/>
+      <c r="J71" s="292"/>
+      <c r="K71" s="293"/>
+      <c r="L71" s="294"/>
+      <c r="M71" s="294"/>
+      <c r="N71" s="294"/>
     </row>
     <row r="72" s="249" customFormat="1" spans="1:7">
       <c r="A72" s="206"/>
       <c r="B72" s="36"/>
-      <c r="C72" s="272"/>
+      <c r="C72" s="286"/>
       <c r="D72" s="115"/>
-      <c r="E72" s="266"/>
-      <c r="F72" s="266">
+      <c r="E72" s="277"/>
+      <c r="F72" s="277">
         <f t="shared" ref="F72:F83" si="4">D72*E72</f>
         <v>0</v>
       </c>
-      <c r="G72" s="271">
+      <c r="G72" s="285">
         <f>SUM(F72:F78)</f>
         <v>0</v>
       </c>
@@ -11050,86 +11437,86 @@
     <row r="73" s="249" customFormat="1" spans="1:7">
       <c r="A73" s="209"/>
       <c r="B73" s="40"/>
-      <c r="C73" s="272"/>
+      <c r="C73" s="286"/>
       <c r="D73" s="115"/>
-      <c r="E73" s="266"/>
-      <c r="F73" s="266">
+      <c r="E73" s="277"/>
+      <c r="F73" s="277">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G73" s="271"/>
+      <c r="G73" s="285"/>
     </row>
     <row r="74" s="249" customFormat="1" spans="1:7">
       <c r="A74" s="209"/>
       <c r="B74" s="40"/>
-      <c r="C74" s="272"/>
+      <c r="C74" s="286"/>
       <c r="D74" s="115"/>
-      <c r="E74" s="266"/>
-      <c r="F74" s="266">
+      <c r="E74" s="277"/>
+      <c r="F74" s="277">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G74" s="271"/>
+      <c r="G74" s="285"/>
     </row>
     <row r="75" s="249" customFormat="1" spans="1:7">
       <c r="A75" s="209"/>
       <c r="B75" s="40"/>
-      <c r="C75" s="272"/>
+      <c r="C75" s="286"/>
       <c r="D75" s="115"/>
-      <c r="E75" s="266"/>
-      <c r="F75" s="266">
+      <c r="E75" s="277"/>
+      <c r="F75" s="277">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G75" s="271"/>
+      <c r="G75" s="285"/>
     </row>
     <row r="76" s="249" customFormat="1" spans="1:7">
       <c r="A76" s="209"/>
       <c r="B76" s="40"/>
-      <c r="C76" s="272"/>
+      <c r="C76" s="286"/>
       <c r="D76" s="115"/>
-      <c r="E76" s="266"/>
-      <c r="F76" s="266">
+      <c r="E76" s="277"/>
+      <c r="F76" s="277">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G76" s="271"/>
+      <c r="G76" s="285"/>
     </row>
     <row r="77" s="249" customFormat="1" spans="1:7">
       <c r="A77" s="209"/>
       <c r="B77" s="40"/>
-      <c r="C77" s="272"/>
+      <c r="C77" s="286"/>
       <c r="D77" s="115"/>
-      <c r="E77" s="266"/>
-      <c r="F77" s="266">
+      <c r="E77" s="277"/>
+      <c r="F77" s="277">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G77" s="271"/>
+      <c r="G77" s="285"/>
     </row>
     <row r="78" s="249" customFormat="1" spans="1:7">
       <c r="A78" s="207"/>
       <c r="B78" s="131"/>
-      <c r="C78" s="272"/>
+      <c r="C78" s="286"/>
       <c r="D78" s="115"/>
-      <c r="E78" s="266"/>
-      <c r="F78" s="266">
+      <c r="E78" s="277"/>
+      <c r="F78" s="277">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G78" s="271"/>
+      <c r="G78" s="285"/>
     </row>
     <row r="79" s="249" customFormat="1" spans="1:7">
       <c r="A79" s="206"/>
       <c r="B79" s="36"/>
-      <c r="C79" s="272"/>
+      <c r="C79" s="286"/>
       <c r="D79" s="115"/>
-      <c r="E79" s="266"/>
-      <c r="F79" s="266">
+      <c r="E79" s="277"/>
+      <c r="F79" s="277">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G79" s="271">
+      <c r="G79" s="285">
         <f>SUM(F79:F83)</f>
         <v>0</v>
       </c>
@@ -11137,62 +11524,62 @@
     <row r="80" s="249" customFormat="1" spans="1:7">
       <c r="A80" s="209"/>
       <c r="B80" s="40"/>
-      <c r="C80" s="272"/>
+      <c r="C80" s="286"/>
       <c r="D80" s="115"/>
-      <c r="E80" s="266"/>
-      <c r="F80" s="266">
+      <c r="E80" s="277"/>
+      <c r="F80" s="277">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G80" s="271"/>
+      <c r="G80" s="285"/>
     </row>
     <row r="81" s="249" customFormat="1" spans="1:7">
       <c r="A81" s="209"/>
       <c r="B81" s="40"/>
-      <c r="C81" s="272"/>
+      <c r="C81" s="286"/>
       <c r="D81" s="115"/>
-      <c r="E81" s="266"/>
-      <c r="F81" s="266">
+      <c r="E81" s="277"/>
+      <c r="F81" s="277">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G81" s="271"/>
+      <c r="G81" s="285"/>
     </row>
     <row r="82" s="249" customFormat="1" spans="1:7">
       <c r="A82" s="209"/>
       <c r="B82" s="40"/>
-      <c r="C82" s="272"/>
+      <c r="C82" s="286"/>
       <c r="D82" s="115"/>
-      <c r="E82" s="266"/>
-      <c r="F82" s="266">
+      <c r="E82" s="277"/>
+      <c r="F82" s="277">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G82" s="271"/>
+      <c r="G82" s="285"/>
     </row>
     <row r="83" s="249" customFormat="1" spans="1:7">
       <c r="A83" s="207"/>
       <c r="B83" s="131"/>
-      <c r="C83" s="272"/>
+      <c r="C83" s="286"/>
       <c r="D83" s="115"/>
-      <c r="E83" s="266"/>
-      <c r="F83" s="266">
+      <c r="E83" s="277"/>
+      <c r="F83" s="277">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G83" s="271"/>
+      <c r="G83" s="285"/>
     </row>
     <row r="84" s="249" customFormat="1" spans="1:7">
       <c r="A84" s="206"/>
       <c r="B84" s="36"/>
-      <c r="C84" s="272"/>
+      <c r="C84" s="286"/>
       <c r="D84" s="115"/>
-      <c r="E84" s="266"/>
-      <c r="F84" s="266">
+      <c r="E84" s="277"/>
+      <c r="F84" s="277">
         <f t="shared" ref="F84:F92" si="5">D84*E84</f>
         <v>0</v>
       </c>
-      <c r="G84" s="271">
+      <c r="G84" s="285">
         <f>SUM(F84:F89)</f>
         <v>0</v>
       </c>
@@ -11200,74 +11587,74 @@
     <row r="85" s="249" customFormat="1" spans="1:7">
       <c r="A85" s="209"/>
       <c r="B85" s="40"/>
-      <c r="C85" s="272"/>
+      <c r="C85" s="286"/>
       <c r="D85" s="115"/>
-      <c r="E85" s="266"/>
-      <c r="F85" s="266">
+      <c r="E85" s="277"/>
+      <c r="F85" s="277">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G85" s="271"/>
+      <c r="G85" s="285"/>
     </row>
     <row r="86" s="249" customFormat="1" spans="1:7">
       <c r="A86" s="209"/>
       <c r="B86" s="40"/>
-      <c r="C86" s="272"/>
+      <c r="C86" s="286"/>
       <c r="D86" s="115"/>
-      <c r="E86" s="266"/>
-      <c r="F86" s="266">
+      <c r="E86" s="277"/>
+      <c r="F86" s="277">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G86" s="271"/>
+      <c r="G86" s="285"/>
     </row>
     <row r="87" s="249" customFormat="1" spans="1:7">
       <c r="A87" s="209"/>
       <c r="B87" s="40"/>
-      <c r="C87" s="272"/>
+      <c r="C87" s="286"/>
       <c r="D87" s="115"/>
-      <c r="E87" s="266"/>
-      <c r="F87" s="266">
+      <c r="E87" s="277"/>
+      <c r="F87" s="277">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G87" s="271"/>
+      <c r="G87" s="285"/>
     </row>
     <row r="88" s="249" customFormat="1" spans="1:7">
       <c r="A88" s="209"/>
       <c r="B88" s="40"/>
-      <c r="C88" s="272"/>
+      <c r="C88" s="286"/>
       <c r="D88" s="115"/>
-      <c r="E88" s="266"/>
-      <c r="F88" s="266">
+      <c r="E88" s="277"/>
+      <c r="F88" s="277">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G88" s="271"/>
+      <c r="G88" s="285"/>
     </row>
     <row r="89" s="249" customFormat="1" spans="1:7">
       <c r="A89" s="207"/>
       <c r="B89" s="131"/>
-      <c r="C89" s="272"/>
+      <c r="C89" s="286"/>
       <c r="D89" s="115"/>
-      <c r="E89" s="266"/>
-      <c r="F89" s="266">
+      <c r="E89" s="277"/>
+      <c r="F89" s="277">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G89" s="271"/>
+      <c r="G89" s="285"/>
     </row>
     <row r="90" s="249" customFormat="1" spans="1:7">
       <c r="A90" s="206"/>
       <c r="B90" s="36"/>
-      <c r="C90" s="272"/>
+      <c r="C90" s="286"/>
       <c r="D90" s="115"/>
-      <c r="E90" s="266"/>
-      <c r="F90" s="266">
+      <c r="E90" s="277"/>
+      <c r="F90" s="277">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G90" s="271">
+      <c r="G90" s="285">
         <f>SUM(F90:F92)</f>
         <v>0</v>
       </c>
@@ -11275,38 +11662,38 @@
     <row r="91" s="249" customFormat="1" spans="1:7">
       <c r="A91" s="209"/>
       <c r="B91" s="40"/>
-      <c r="C91" s="272"/>
+      <c r="C91" s="286"/>
       <c r="D91" s="115"/>
-      <c r="E91" s="266"/>
-      <c r="F91" s="266">
+      <c r="E91" s="277"/>
+      <c r="F91" s="277">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G91" s="271"/>
+      <c r="G91" s="285"/>
     </row>
     <row r="92" s="249" customFormat="1" spans="1:7">
       <c r="A92" s="207"/>
       <c r="B92" s="131"/>
-      <c r="C92" s="272"/>
+      <c r="C92" s="286"/>
       <c r="D92" s="115"/>
-      <c r="E92" s="266"/>
-      <c r="F92" s="266">
+      <c r="E92" s="277"/>
+      <c r="F92" s="277">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G92" s="271"/>
+      <c r="G92" s="285"/>
     </row>
     <row r="93" s="249" customFormat="1" spans="1:7">
       <c r="A93" s="206"/>
       <c r="B93" s="36"/>
-      <c r="C93" s="272"/>
+      <c r="C93" s="286"/>
       <c r="D93" s="115"/>
-      <c r="E93" s="266"/>
-      <c r="F93" s="266">
+      <c r="E93" s="277"/>
+      <c r="F93" s="277">
         <f t="shared" ref="F93:F113" si="6">D93*E93</f>
         <v>0</v>
       </c>
-      <c r="G93" s="271">
+      <c r="G93" s="285">
         <f>SUM(F93:F98)</f>
         <v>0</v>
       </c>
@@ -11314,74 +11701,74 @@
     <row r="94" s="249" customFormat="1" spans="1:7">
       <c r="A94" s="209"/>
       <c r="B94" s="40"/>
-      <c r="C94" s="272"/>
+      <c r="C94" s="286"/>
       <c r="D94" s="115"/>
-      <c r="E94" s="266"/>
-      <c r="F94" s="266">
+      <c r="E94" s="277"/>
+      <c r="F94" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G94" s="271"/>
+      <c r="G94" s="285"/>
     </row>
     <row r="95" s="249" customFormat="1" spans="1:7">
       <c r="A95" s="209"/>
       <c r="B95" s="40"/>
-      <c r="C95" s="272"/>
+      <c r="C95" s="286"/>
       <c r="D95" s="115"/>
-      <c r="E95" s="266"/>
-      <c r="F95" s="266">
+      <c r="E95" s="277"/>
+      <c r="F95" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G95" s="271"/>
+      <c r="G95" s="285"/>
     </row>
     <row r="96" s="249" customFormat="1" spans="1:7">
       <c r="A96" s="209"/>
       <c r="B96" s="40"/>
-      <c r="C96" s="272"/>
+      <c r="C96" s="286"/>
       <c r="D96" s="115"/>
-      <c r="E96" s="266"/>
-      <c r="F96" s="266">
+      <c r="E96" s="277"/>
+      <c r="F96" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G96" s="271"/>
+      <c r="G96" s="285"/>
     </row>
     <row r="97" s="249" customFormat="1" spans="1:7">
       <c r="A97" s="209"/>
       <c r="B97" s="40"/>
-      <c r="C97" s="272"/>
+      <c r="C97" s="286"/>
       <c r="D97" s="115"/>
-      <c r="E97" s="266"/>
-      <c r="F97" s="266">
+      <c r="E97" s="277"/>
+      <c r="F97" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G97" s="271"/>
+      <c r="G97" s="285"/>
     </row>
     <row r="98" s="249" customFormat="1" spans="1:7">
       <c r="A98" s="207"/>
       <c r="B98" s="131"/>
-      <c r="C98" s="272"/>
+      <c r="C98" s="286"/>
       <c r="D98" s="115"/>
-      <c r="E98" s="266"/>
-      <c r="F98" s="266">
+      <c r="E98" s="277"/>
+      <c r="F98" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G98" s="271"/>
+      <c r="G98" s="285"/>
     </row>
     <row r="99" s="249" customFormat="1" spans="1:7">
       <c r="A99" s="206"/>
       <c r="B99" s="36"/>
-      <c r="C99" s="272"/>
+      <c r="C99" s="286"/>
       <c r="D99" s="115"/>
-      <c r="E99" s="266"/>
-      <c r="F99" s="266">
+      <c r="E99" s="277"/>
+      <c r="F99" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G99" s="271">
+      <c r="G99" s="285">
         <f>SUM(F99:F103)</f>
         <v>0</v>
       </c>
@@ -11389,62 +11776,62 @@
     <row r="100" s="249" customFormat="1" spans="1:7">
       <c r="A100" s="209"/>
       <c r="B100" s="40"/>
-      <c r="C100" s="272"/>
+      <c r="C100" s="286"/>
       <c r="D100" s="115"/>
-      <c r="E100" s="266"/>
-      <c r="F100" s="266">
+      <c r="E100" s="277"/>
+      <c r="F100" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G100" s="271"/>
+      <c r="G100" s="285"/>
     </row>
     <row r="101" s="249" customFormat="1" spans="1:7">
       <c r="A101" s="209"/>
       <c r="B101" s="40"/>
-      <c r="C101" s="272"/>
+      <c r="C101" s="286"/>
       <c r="D101" s="115"/>
-      <c r="E101" s="266"/>
-      <c r="F101" s="266">
+      <c r="E101" s="277"/>
+      <c r="F101" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G101" s="271"/>
+      <c r="G101" s="285"/>
     </row>
     <row r="102" s="249" customFormat="1" spans="1:7">
       <c r="A102" s="209"/>
       <c r="B102" s="40"/>
-      <c r="C102" s="272"/>
+      <c r="C102" s="286"/>
       <c r="D102" s="115"/>
-      <c r="E102" s="266"/>
-      <c r="F102" s="266">
+      <c r="E102" s="277"/>
+      <c r="F102" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G102" s="271"/>
+      <c r="G102" s="285"/>
     </row>
     <row r="103" s="249" customFormat="1" spans="1:7">
       <c r="A103" s="207"/>
       <c r="B103" s="131"/>
-      <c r="C103" s="272"/>
+      <c r="C103" s="286"/>
       <c r="D103" s="115"/>
-      <c r="E103" s="266"/>
-      <c r="F103" s="266">
+      <c r="E103" s="277"/>
+      <c r="F103" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G103" s="271"/>
+      <c r="G103" s="285"/>
     </row>
     <row r="104" s="249" customFormat="1" spans="1:7">
       <c r="A104" s="206"/>
       <c r="B104" s="36"/>
-      <c r="C104" s="272"/>
+      <c r="C104" s="286"/>
       <c r="D104" s="115"/>
-      <c r="E104" s="266"/>
-      <c r="F104" s="266">
+      <c r="E104" s="277"/>
+      <c r="F104" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G104" s="271">
+      <c r="G104" s="285">
         <f>SUM(F104:F109)</f>
         <v>0</v>
       </c>
@@ -11452,74 +11839,74 @@
     <row r="105" s="249" customFormat="1" spans="1:7">
       <c r="A105" s="209"/>
       <c r="B105" s="40"/>
-      <c r="C105" s="272"/>
+      <c r="C105" s="286"/>
       <c r="D105" s="115"/>
-      <c r="E105" s="266"/>
-      <c r="F105" s="266">
+      <c r="E105" s="277"/>
+      <c r="F105" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G105" s="271"/>
+      <c r="G105" s="285"/>
     </row>
     <row r="106" s="249" customFormat="1" spans="1:7">
       <c r="A106" s="209"/>
       <c r="B106" s="40"/>
-      <c r="C106" s="272"/>
+      <c r="C106" s="286"/>
       <c r="D106" s="115"/>
-      <c r="E106" s="266"/>
-      <c r="F106" s="266">
+      <c r="E106" s="277"/>
+      <c r="F106" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G106" s="271"/>
+      <c r="G106" s="285"/>
     </row>
     <row r="107" s="249" customFormat="1" spans="1:7">
       <c r="A107" s="209"/>
       <c r="B107" s="40"/>
-      <c r="C107" s="272"/>
+      <c r="C107" s="286"/>
       <c r="D107" s="115"/>
-      <c r="E107" s="266"/>
-      <c r="F107" s="266">
+      <c r="E107" s="277"/>
+      <c r="F107" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G107" s="271"/>
+      <c r="G107" s="285"/>
     </row>
     <row r="108" s="249" customFormat="1" spans="1:7">
       <c r="A108" s="209"/>
       <c r="B108" s="40"/>
-      <c r="C108" s="272"/>
+      <c r="C108" s="286"/>
       <c r="D108" s="115"/>
-      <c r="E108" s="266"/>
-      <c r="F108" s="266">
+      <c r="E108" s="277"/>
+      <c r="F108" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G108" s="271"/>
+      <c r="G108" s="285"/>
     </row>
     <row r="109" s="249" customFormat="1" spans="1:7">
       <c r="A109" s="207"/>
       <c r="B109" s="131"/>
-      <c r="C109" s="272"/>
+      <c r="C109" s="286"/>
       <c r="D109" s="115"/>
-      <c r="E109" s="266"/>
-      <c r="F109" s="266">
+      <c r="E109" s="277"/>
+      <c r="F109" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G109" s="271"/>
+      <c r="G109" s="285"/>
     </row>
     <row r="110" s="249" customFormat="1" spans="1:7">
       <c r="A110" s="206"/>
       <c r="B110" s="36"/>
-      <c r="C110" s="272"/>
+      <c r="C110" s="286"/>
       <c r="D110" s="115"/>
-      <c r="E110" s="266"/>
-      <c r="F110" s="266">
+      <c r="E110" s="277"/>
+      <c r="F110" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G110" s="271">
+      <c r="G110" s="285">
         <f>SUM(F110:F113)</f>
         <v>0</v>
       </c>
@@ -11527,50 +11914,50 @@
     <row r="111" s="249" customFormat="1" spans="1:7">
       <c r="A111" s="209"/>
       <c r="B111" s="40"/>
-      <c r="C111" s="272"/>
+      <c r="C111" s="286"/>
       <c r="D111" s="115"/>
-      <c r="E111" s="266"/>
-      <c r="F111" s="266">
+      <c r="E111" s="277"/>
+      <c r="F111" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G111" s="271"/>
+      <c r="G111" s="285"/>
     </row>
     <row r="112" s="249" customFormat="1" spans="1:7">
       <c r="A112" s="209"/>
       <c r="B112" s="40"/>
-      <c r="C112" s="272"/>
+      <c r="C112" s="286"/>
       <c r="D112" s="115"/>
-      <c r="E112" s="266"/>
-      <c r="F112" s="266">
+      <c r="E112" s="277"/>
+      <c r="F112" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G112" s="271"/>
+      <c r="G112" s="285"/>
     </row>
     <row r="113" s="249" customFormat="1" spans="1:7">
       <c r="A113" s="209"/>
       <c r="B113" s="40"/>
-      <c r="C113" s="272"/>
+      <c r="C113" s="286"/>
       <c r="D113" s="115"/>
-      <c r="E113" s="266"/>
-      <c r="F113" s="266">
+      <c r="E113" s="277"/>
+      <c r="F113" s="277">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G113" s="271"/>
+      <c r="G113" s="285"/>
     </row>
     <row r="114" s="249" customFormat="1" spans="1:7">
       <c r="A114" s="206"/>
       <c r="B114" s="36"/>
-      <c r="C114" s="272"/>
+      <c r="C114" s="286"/>
       <c r="D114" s="115"/>
-      <c r="E114" s="266"/>
-      <c r="F114" s="266">
+      <c r="E114" s="277"/>
+      <c r="F114" s="277">
         <f t="shared" ref="F114:F116" si="7">D114*E114</f>
         <v>0</v>
       </c>
-      <c r="G114" s="271">
+      <c r="G114" s="285">
         <f>SUM(F114:F116)</f>
         <v>0</v>
       </c>
@@ -11578,39 +11965,39 @@
     <row r="115" s="249" customFormat="1" spans="1:7">
       <c r="A115" s="209"/>
       <c r="B115" s="40"/>
-      <c r="C115" s="272"/>
+      <c r="C115" s="286"/>
       <c r="D115" s="115"/>
-      <c r="E115" s="266"/>
-      <c r="F115" s="266">
+      <c r="E115" s="277"/>
+      <c r="F115" s="277">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G115" s="271"/>
+      <c r="G115" s="285"/>
     </row>
     <row r="116" s="249" customFormat="1" spans="1:7">
       <c r="A116" s="207"/>
       <c r="B116" s="131"/>
-      <c r="C116" s="272"/>
+      <c r="C116" s="286"/>
       <c r="D116" s="115"/>
-      <c r="E116" s="266"/>
-      <c r="F116" s="266">
+      <c r="E116" s="277"/>
+      <c r="F116" s="277">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G116" s="271"/>
+      <c r="G116" s="285"/>
     </row>
     <row r="117" s="249" customFormat="1" spans="1:7">
-      <c r="A117" s="273" t="s">
-        <v>53</v>
+      <c r="A117" s="287" t="s">
+        <v>54</v>
       </c>
       <c r="B117" s="122"/>
-      <c r="C117" s="274"/>
+      <c r="C117" s="288"/>
       <c r="D117" s="122"/>
       <c r="E117" s="122"/>
-      <c r="F117" s="276"/>
+      <c r="F117" s="290"/>
       <c r="G117" s="63">
         <f>SUM(G2:G116)</f>
-        <v>3982000</v>
+        <v>5228000</v>
       </c>
     </row>
     <row r="118" s="249" customFormat="1" spans="1:7">
@@ -11892,10 +12279,10 @@
       <c r="D152" s="253"/>
       <c r="E152" s="254"/>
       <c r="G152" s="250"/>
-      <c r="H152" s="275"/>
+      <c r="H152" s="289"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="69">
     <mergeCell ref="A117:F117"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
@@ -11909,9 +12296,9 @@
     <mergeCell ref="A38:A40"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="A56:A60"/>
     <mergeCell ref="A63:A67"/>
     <mergeCell ref="A69:A71"/>
     <mergeCell ref="A72:A78"/>
@@ -11935,9 +12322,9 @@
     <mergeCell ref="B38:B40"/>
     <mergeCell ref="B41:B45"/>
     <mergeCell ref="B46:B47"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="B56:B60"/>
     <mergeCell ref="B63:B67"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="B72:B78"/>
@@ -11961,6 +12348,9 @@
     <mergeCell ref="G38:G40"/>
     <mergeCell ref="G41:G45"/>
     <mergeCell ref="G46:G47"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="G51:G55"/>
+    <mergeCell ref="G56:G60"/>
     <mergeCell ref="N69:N71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11986,16 +12376,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>3</v>
@@ -12012,7 +12402,7 @@
         <v>12340</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" s="16">
         <v>20</v>
@@ -12034,7 +12424,7 @@
         <v>12357</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="16">
         <v>20</v>
@@ -12056,7 +12446,7 @@
         <v>11374</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" s="16">
         <v>20</v>
@@ -12078,7 +12468,7 @@
         <v>13396</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" s="16">
         <v>20</v>
@@ -12100,7 +12490,7 @@
         <v>11474</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" s="16">
         <v>20</v>
@@ -12114,16 +12504,29 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="7" ht="113.5" customHeight="1" spans="1:7">
-      <c r="A7" s="93"/>
-      <c r="B7" s="115"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="247"/>
+    <row r="7" ht="137.45" spans="1:7">
+      <c r="A7" s="93">
+        <v>46006</v>
+      </c>
+      <c r="B7" s="115">
+        <v>13509</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="16">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <f>_xlfn.DISPIMG("ID_E993176563EA4A59A99F5C983CF8DE4D",1)</f>
+        <v>=DISPIMG("ID_E993176563EA4A59A99F5C983CF8DE4D",1)</v>
+      </c>
+      <c r="F7" s="247">
+        <v>12000</v>
+      </c>
       <c r="G7" s="247">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="8" ht="110.25" customHeight="1" spans="1:7">
@@ -12157,7 +12560,7 @@
       <c r="D10" s="246"/>
       <c r="E10" s="248">
         <f>SUM(G2:G9)</f>
-        <v>1200000</v>
+        <v>1440000</v>
       </c>
       <c r="F10" s="248"/>
       <c r="G10" s="248"/>
@@ -12208,7 +12611,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="229" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="229" t="s">
         <v>5</v>
@@ -12256,7 +12659,7 @@
     <row r="4" s="222" customFormat="1" spans="1:7">
       <c r="A4" s="234"/>
       <c r="B4" s="231" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="232">
         <v>0.3</v>
@@ -12274,7 +12677,7 @@
     <row r="5" s="222" customFormat="1" spans="1:6">
       <c r="A5" s="234"/>
       <c r="B5" s="231" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="232">
         <v>1</v>
@@ -12360,7 +12763,7 @@
     <row r="10" s="222" customFormat="1" spans="1:6">
       <c r="A10" s="235"/>
       <c r="B10" s="231" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="232">
         <v>2</v>
@@ -12417,7 +12820,7 @@
     <row r="13" s="222" customFormat="1" spans="1:6">
       <c r="A13" s="234"/>
       <c r="B13" s="231" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" s="232">
         <v>8</v>
@@ -12502,7 +12905,7 @@
     <row r="18" s="222" customFormat="1" spans="1:6">
       <c r="A18" s="234"/>
       <c r="B18" s="231" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="232">
         <v>1</v>
@@ -12536,7 +12939,7 @@
     <row r="20" s="222" customFormat="1" spans="1:6">
       <c r="A20" s="235"/>
       <c r="B20" s="231" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C20" s="232">
         <v>1</v>
@@ -14556,19 +14959,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>4</v>
@@ -14582,10 +14985,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="216" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" s="16">
         <v>3</v>
@@ -14726,22 +15129,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="181" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="181" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="181" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="181" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="181" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G1" s="181" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H1" s="181" t="s">
         <v>40</v>
@@ -14750,7 +15153,7 @@
         <v>5</v>
       </c>
       <c r="J1" s="181" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" ht="387.45" customHeight="1" spans="1:10">
@@ -14758,10 +15161,10 @@
         <v>46000</v>
       </c>
       <c r="B2" s="183" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" s="175" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2" s="184">
         <v>4</v>
@@ -14792,10 +15195,10 @@
         <v>46002</v>
       </c>
       <c r="B3" s="186" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="175" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" s="184">
         <v>4</v>
@@ -14825,7 +15228,7 @@
       <c r="A4" s="187"/>
       <c r="B4" s="188"/>
       <c r="C4" s="189" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" s="190">
         <v>4</v>
@@ -14848,51 +15251,71 @@
       <c r="I4" s="199"/>
       <c r="J4" s="207"/>
     </row>
-    <row r="5" ht="383.5" customHeight="1" spans="1:10">
-      <c r="A5" s="182"/>
-      <c r="B5" s="183"/>
-      <c r="C5" s="175"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="197"/>
+    <row r="5" ht="409.5" customHeight="1" spans="1:10">
+      <c r="A5" s="182">
+        <v>46006</v>
+      </c>
+      <c r="B5" s="183" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="175" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="184">
+        <v>3</v>
+      </c>
+      <c r="E5" s="197">
+        <v>290000</v>
+      </c>
       <c r="F5" s="197">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="G5" s="197">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="H5" s="198">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>783000</v>
       </c>
       <c r="I5" s="197">
         <f>SUM(H5)</f>
-        <v>0</v>
+        <v>783000</v>
       </c>
       <c r="J5" s="17"/>
     </row>
-    <row r="6" ht="365" customHeight="1" spans="1:10">
-      <c r="A6" s="182"/>
-      <c r="B6" s="183"/>
-      <c r="C6" s="175"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="197"/>
+    <row r="6" ht="409.5" customHeight="1" spans="1:10">
+      <c r="A6" s="182">
+        <v>46007</v>
+      </c>
+      <c r="B6" s="183" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="175" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="184">
+        <v>3</v>
+      </c>
+      <c r="E6" s="197">
+        <v>375000</v>
+      </c>
       <c r="F6" s="197">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>37500</v>
       </c>
       <c r="G6" s="197">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>337500</v>
       </c>
       <c r="H6" s="198">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1012500</v>
       </c>
       <c r="I6" s="197">
         <f>SUM(H6)</f>
-        <v>0</v>
+        <v>1012500</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -15113,7 +15536,7 @@
       <c r="E16" s="196"/>
       <c r="F16" s="203">
         <f>SUM(I2:I15)</f>
-        <v>3780000</v>
+        <v>5575500</v>
       </c>
       <c r="G16" s="203"/>
       <c r="H16" s="203"/>
@@ -15158,16 +15581,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="172" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="172" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="172" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="172" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="172" t="s">
         <v>3</v>
@@ -15229,16 +15652,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="141" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="141" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="141" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="141" t="s">
         <v>3</v>
@@ -15255,10 +15678,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C2" s="143" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D2" s="144">
         <v>5</v>
@@ -15328,7 +15751,7 @@
       </c>
       <c r="E7" s="161"/>
       <c r="F7" s="162" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G7" s="162"/>
       <c r="H7" s="162">
@@ -15356,10 +15779,10 @@
         <v>45999</v>
       </c>
       <c r="B9" s="142" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C9" s="151" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D9" s="150">
         <v>3</v>
@@ -15381,7 +15804,7 @@
       <c r="A10" s="145"/>
       <c r="B10" s="145"/>
       <c r="C10" s="151" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D10" s="150">
         <v>3</v>
@@ -15400,7 +15823,7 @@
       <c r="A11" s="152"/>
       <c r="B11" s="152"/>
       <c r="C11" s="151" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D11" s="150">
         <v>2</v>
@@ -15427,7 +15850,7 @@
       </c>
       <c r="E12" s="161"/>
       <c r="F12" s="162" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G12" s="162"/>
       <c r="H12" s="162">
@@ -15455,10 +15878,10 @@
         <v>45992</v>
       </c>
       <c r="B14" s="142" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C14" s="143" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D14" s="144">
         <v>5</v>
@@ -15531,7 +15954,7 @@
       </c>
       <c r="E19" s="161"/>
       <c r="F19" s="162" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G19" s="162"/>
       <c r="H19" s="162">
@@ -15637,16 +16060,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -15663,10 +16086,10 @@
         <v>46001</v>
       </c>
       <c r="B2" s="115" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D2" s="115">
         <v>2</v>
@@ -15689,10 +16112,10 @@
         <v>46001</v>
       </c>
       <c r="B3" s="93" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D3" s="115">
         <v>4</v>
@@ -15715,10 +16138,10 @@
         <v>46004</v>
       </c>
       <c r="B4" s="130" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D4" s="115">
         <v>1</v>
@@ -15743,7 +16166,7 @@
       <c r="A5" s="131"/>
       <c r="B5" s="132"/>
       <c r="C5" s="38" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D5" s="115">
         <v>1</v>
@@ -15760,7 +16183,7 @@
     </row>
     <row r="6" ht="26" spans="1:8">
       <c r="A6" s="81" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="82"/>
       <c r="C6" s="82"/>

--- a/DECEMBER/DECEMBER BAR.xlsx
+++ b/DECEMBER/DECEMBER BAR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17000" firstSheet="1" activeTab="3"/>
+    <workbookView windowHeight="17000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="BUK BUNGA (Groceries)" sheetId="28" r:id="rId1"/>
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="131">
   <si>
     <t>DATE</t>
   </si>
@@ -1624,7 +1624,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="299">
+  <cellXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2429,6 +2429,24 @@
     <xf numFmtId="0" fontId="27" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2441,6 +2459,15 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2519,8 +2546,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="30" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="30" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3821,18 +3866,18 @@
       <c r="E1" s="252" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="289" t="s">
+      <c r="F1" s="298" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A2" s="280">
+      <c r="A2" s="289">
         <v>45995</v>
       </c>
-      <c r="B2" s="281" t="s">
+      <c r="B2" s="290" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="282">
+      <c r="C2" s="291">
         <v>5</v>
       </c>
       <c r="D2" s="7">
@@ -3842,17 +3887,17 @@
         <f t="shared" ref="E2:E15" si="0">SUM(C2*D2)</f>
         <v>100000</v>
       </c>
-      <c r="F2" s="290">
+      <c r="F2" s="299">
         <f>SUM(E2:E12)</f>
         <v>572000</v>
       </c>
     </row>
     <row r="3" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A3" s="283"/>
-      <c r="B3" s="281" t="s">
+      <c r="A3" s="292"/>
+      <c r="B3" s="290" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="282">
+      <c r="C3" s="291">
         <v>2</v>
       </c>
       <c r="D3" s="7">
@@ -3862,14 +3907,14 @@
         <f t="shared" si="0"/>
         <v>140000</v>
       </c>
-      <c r="F3" s="291"/>
+      <c r="F3" s="300"/>
     </row>
     <row r="4" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A4" s="283"/>
-      <c r="B4" s="281" t="s">
+      <c r="A4" s="292"/>
+      <c r="B4" s="290" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="282">
+      <c r="C4" s="291">
         <v>6</v>
       </c>
       <c r="D4" s="7">
@@ -3879,14 +3924,14 @@
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
-      <c r="F4" s="291"/>
+      <c r="F4" s="300"/>
     </row>
     <row r="5" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A5" s="283"/>
-      <c r="B5" s="281" t="s">
+      <c r="A5" s="292"/>
+      <c r="B5" s="290" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="282">
+      <c r="C5" s="291">
         <v>1</v>
       </c>
       <c r="D5" s="7">
@@ -3896,14 +3941,14 @@
         <f t="shared" si="0"/>
         <v>38000</v>
       </c>
-      <c r="F5" s="291"/>
+      <c r="F5" s="300"/>
     </row>
     <row r="6" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A6" s="283"/>
-      <c r="B6" s="281" t="s">
+      <c r="A6" s="292"/>
+      <c r="B6" s="290" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="282">
+      <c r="C6" s="291">
         <v>0.3</v>
       </c>
       <c r="D6" s="7">
@@ -3913,14 +3958,14 @@
         <f t="shared" si="0"/>
         <v>6000</v>
       </c>
-      <c r="F6" s="291"/>
+      <c r="F6" s="300"/>
     </row>
     <row r="7" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A7" s="283"/>
-      <c r="B7" s="281" t="s">
+      <c r="A7" s="292"/>
+      <c r="B7" s="290" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="282">
+      <c r="C7" s="291">
         <v>1</v>
       </c>
       <c r="D7" s="7">
@@ -3930,14 +3975,14 @@
         <f t="shared" si="0"/>
         <v>25000</v>
       </c>
-      <c r="F7" s="291"/>
+      <c r="F7" s="300"/>
     </row>
     <row r="8" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A8" s="283"/>
-      <c r="B8" s="281" t="s">
+      <c r="A8" s="292"/>
+      <c r="B8" s="290" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="282">
+      <c r="C8" s="291">
         <v>1</v>
       </c>
       <c r="D8" s="7">
@@ -3947,14 +3992,14 @@
         <f t="shared" si="0"/>
         <v>30000</v>
       </c>
-      <c r="F8" s="291"/>
+      <c r="F8" s="300"/>
     </row>
     <row r="9" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A9" s="283"/>
-      <c r="B9" s="281" t="s">
+      <c r="A9" s="292"/>
+      <c r="B9" s="290" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="282">
+      <c r="C9" s="291">
         <v>1</v>
       </c>
       <c r="D9" s="7">
@@ -3964,14 +4009,14 @@
         <f t="shared" si="0"/>
         <v>12000</v>
       </c>
-      <c r="F9" s="291"/>
+      <c r="F9" s="300"/>
     </row>
     <row r="10" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A10" s="283"/>
-      <c r="B10" s="281" t="s">
+      <c r="A10" s="292"/>
+      <c r="B10" s="290" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="282">
+      <c r="C10" s="291">
         <v>3</v>
       </c>
       <c r="D10" s="7">
@@ -3981,14 +4026,14 @@
         <f t="shared" si="0"/>
         <v>72000</v>
       </c>
-      <c r="F10" s="291"/>
+      <c r="F10" s="300"/>
     </row>
     <row r="11" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A11" s="283"/>
-      <c r="B11" s="281" t="s">
+      <c r="A11" s="292"/>
+      <c r="B11" s="290" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="282">
+      <c r="C11" s="291">
         <v>1</v>
       </c>
       <c r="D11" s="7">
@@ -3998,14 +4043,14 @@
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="F11" s="291"/>
+      <c r="F11" s="300"/>
     </row>
     <row r="12" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A12" s="284"/>
-      <c r="B12" s="281" t="s">
+      <c r="A12" s="293"/>
+      <c r="B12" s="290" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="282">
+      <c r="C12" s="291">
         <v>1</v>
       </c>
       <c r="D12" s="7">
@@ -4015,16 +4060,16 @@
         <f t="shared" si="0"/>
         <v>49000</v>
       </c>
-      <c r="F12" s="292"/>
+      <c r="F12" s="301"/>
     </row>
     <row r="13" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A13" s="280">
+      <c r="A13" s="289">
         <v>45996</v>
       </c>
-      <c r="B13" s="281" t="s">
+      <c r="B13" s="290" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="282">
+      <c r="C13" s="291">
         <v>8</v>
       </c>
       <c r="D13" s="7">
@@ -4034,17 +4079,17 @@
         <f t="shared" si="0"/>
         <v>80000</v>
       </c>
-      <c r="F13" s="290">
+      <c r="F13" s="299">
         <f>SUM(E13:E25)</f>
         <v>730000</v>
       </c>
     </row>
     <row r="14" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A14" s="283"/>
-      <c r="B14" s="281" t="s">
+      <c r="A14" s="292"/>
+      <c r="B14" s="290" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="282">
+      <c r="C14" s="291">
         <v>2</v>
       </c>
       <c r="D14" s="7">
@@ -4054,14 +4099,14 @@
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="F14" s="291"/>
+      <c r="F14" s="300"/>
     </row>
     <row r="15" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A15" s="283"/>
-      <c r="B15" s="281" t="s">
+      <c r="A15" s="292"/>
+      <c r="B15" s="290" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="282">
+      <c r="C15" s="291">
         <v>2</v>
       </c>
       <c r="D15" s="7">
@@ -4071,14 +4116,14 @@
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
-      <c r="F15" s="291"/>
+      <c r="F15" s="300"/>
     </row>
     <row r="16" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A16" s="283"/>
-      <c r="B16" s="281" t="s">
+      <c r="A16" s="292"/>
+      <c r="B16" s="290" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="282">
+      <c r="C16" s="291">
         <v>0.5</v>
       </c>
       <c r="D16" s="7">
@@ -4087,14 +4132,14 @@
       <c r="E16" s="7">
         <v>48000</v>
       </c>
-      <c r="F16" s="291"/>
+      <c r="F16" s="300"/>
     </row>
     <row r="17" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A17" s="283"/>
-      <c r="B17" s="281" t="s">
+      <c r="A17" s="292"/>
+      <c r="B17" s="290" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="282">
+      <c r="C17" s="291">
         <v>1.1</v>
       </c>
       <c r="D17" s="7">
@@ -4103,14 +4148,14 @@
       <c r="E17" s="7">
         <v>42000</v>
       </c>
-      <c r="F17" s="291"/>
+      <c r="F17" s="300"/>
     </row>
     <row r="18" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A18" s="283"/>
-      <c r="B18" s="281" t="s">
+      <c r="A18" s="292"/>
+      <c r="B18" s="290" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="282">
+      <c r="C18" s="291">
         <v>5</v>
       </c>
       <c r="D18" s="7">
@@ -4120,14 +4165,14 @@
         <f t="shared" ref="E18:E25" si="1">SUM(C18*D18)</f>
         <v>120000</v>
       </c>
-      <c r="F18" s="291"/>
+      <c r="F18" s="300"/>
     </row>
     <row r="19" s="244" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A19" s="283"/>
-      <c r="B19" s="285" t="s">
+      <c r="A19" s="292"/>
+      <c r="B19" s="294" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="286">
+      <c r="C19" s="295">
         <v>3</v>
       </c>
       <c r="D19" s="133">
@@ -4137,15 +4182,15 @@
         <f t="shared" si="1"/>
         <v>120000</v>
       </c>
-      <c r="F19" s="291"/>
-      <c r="G19" s="271"/>
+      <c r="F19" s="300"/>
+      <c r="G19" s="277"/>
     </row>
     <row r="20" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A20" s="283"/>
-      <c r="B20" s="287" t="s">
+      <c r="A20" s="292"/>
+      <c r="B20" s="296" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="282">
+      <c r="C20" s="291">
         <v>1</v>
       </c>
       <c r="D20" s="262">
@@ -4155,14 +4200,14 @@
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F20" s="291"/>
+      <c r="F20" s="300"/>
     </row>
     <row r="21" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A21" s="283"/>
-      <c r="B21" s="287" t="s">
+      <c r="A21" s="292"/>
+      <c r="B21" s="296" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="282">
+      <c r="C21" s="291">
         <v>2</v>
       </c>
       <c r="D21" s="262">
@@ -4172,14 +4217,14 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F21" s="291"/>
+      <c r="F21" s="300"/>
     </row>
     <row r="22" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A22" s="283"/>
-      <c r="B22" s="287" t="s">
+      <c r="A22" s="292"/>
+      <c r="B22" s="296" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="282">
+      <c r="C22" s="291">
         <v>0.5</v>
       </c>
       <c r="D22" s="262">
@@ -4189,14 +4234,14 @@
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
-      <c r="F22" s="291"/>
+      <c r="F22" s="300"/>
     </row>
     <row r="23" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A23" s="283"/>
-      <c r="B23" s="287" t="s">
+      <c r="A23" s="292"/>
+      <c r="B23" s="296" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="282">
+      <c r="C23" s="291">
         <v>1</v>
       </c>
       <c r="D23" s="262">
@@ -4206,14 +4251,14 @@
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="F23" s="291"/>
+      <c r="F23" s="300"/>
     </row>
     <row r="24" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A24" s="283"/>
-      <c r="B24" s="287" t="s">
+      <c r="A24" s="292"/>
+      <c r="B24" s="296" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="282">
+      <c r="C24" s="291">
         <v>0.3</v>
       </c>
       <c r="D24" s="262">
@@ -4223,14 +4268,14 @@
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F24" s="291"/>
+      <c r="F24" s="300"/>
     </row>
     <row r="25" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A25" s="284"/>
-      <c r="B25" s="287" t="s">
+      <c r="A25" s="293"/>
+      <c r="B25" s="296" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="282">
+      <c r="C25" s="291">
         <v>1</v>
       </c>
       <c r="D25" s="262">
@@ -4240,16 +4285,16 @@
         <f t="shared" si="1"/>
         <v>35000</v>
       </c>
-      <c r="F25" s="292"/>
+      <c r="F25" s="301"/>
     </row>
     <row r="26" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A26" s="280">
+      <c r="A26" s="289">
         <v>45997</v>
       </c>
-      <c r="B26" s="287" t="s">
+      <c r="B26" s="296" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="282">
+      <c r="C26" s="291">
         <v>3.995</v>
       </c>
       <c r="D26" s="262">
@@ -4258,17 +4303,17 @@
       <c r="E26" s="7">
         <v>60000</v>
       </c>
-      <c r="F26" s="290">
+      <c r="F26" s="299">
         <f>SUM(E26:E34)</f>
         <v>422000</v>
       </c>
     </row>
     <row r="27" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A27" s="283"/>
-      <c r="B27" s="287" t="s">
+      <c r="A27" s="292"/>
+      <c r="B27" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="282">
+      <c r="C27" s="291">
         <v>2</v>
       </c>
       <c r="D27" s="262">
@@ -4278,14 +4323,14 @@
         <f>SUM(C27*D27)</f>
         <v>40000</v>
       </c>
-      <c r="F27" s="291"/>
+      <c r="F27" s="300"/>
     </row>
     <row r="28" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A28" s="283"/>
-      <c r="B28" s="287" t="s">
+      <c r="A28" s="292"/>
+      <c r="B28" s="296" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="282">
+      <c r="C28" s="291">
         <v>0.5</v>
       </c>
       <c r="D28" s="262">
@@ -4294,14 +4339,14 @@
       <c r="E28" s="7">
         <v>18000</v>
       </c>
-      <c r="F28" s="291"/>
+      <c r="F28" s="300"/>
     </row>
     <row r="29" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A29" s="283"/>
-      <c r="B29" s="287" t="s">
+      <c r="A29" s="292"/>
+      <c r="B29" s="296" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="282">
+      <c r="C29" s="291">
         <v>0.1</v>
       </c>
       <c r="D29" s="262">
@@ -4311,14 +4356,14 @@
         <f t="shared" ref="E29:E34" si="2">SUM(C29*D29)</f>
         <v>8000</v>
       </c>
-      <c r="F29" s="291"/>
+      <c r="F29" s="300"/>
     </row>
     <row r="30" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A30" s="283"/>
-      <c r="B30" s="287" t="s">
+      <c r="A30" s="292"/>
+      <c r="B30" s="296" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="282">
+      <c r="C30" s="291">
         <v>0.5</v>
       </c>
       <c r="D30" s="262">
@@ -4328,14 +4373,14 @@
         <f t="shared" si="2"/>
         <v>15000</v>
       </c>
-      <c r="F30" s="291"/>
+      <c r="F30" s="300"/>
     </row>
     <row r="31" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A31" s="283"/>
-      <c r="B31" s="287" t="s">
+      <c r="A31" s="292"/>
+      <c r="B31" s="296" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="282">
+      <c r="C31" s="291">
         <v>4</v>
       </c>
       <c r="D31" s="262">
@@ -4345,14 +4390,14 @@
         <f t="shared" si="2"/>
         <v>80000</v>
       </c>
-      <c r="F31" s="291"/>
+      <c r="F31" s="300"/>
     </row>
     <row r="32" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A32" s="283"/>
-      <c r="B32" s="281" t="s">
+      <c r="A32" s="292"/>
+      <c r="B32" s="290" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="282">
+      <c r="C32" s="291">
         <v>4</v>
       </c>
       <c r="D32" s="7">
@@ -4362,14 +4407,14 @@
         <f t="shared" si="2"/>
         <v>96000</v>
       </c>
-      <c r="F32" s="291"/>
+      <c r="F32" s="300"/>
     </row>
     <row r="33" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A33" s="283"/>
-      <c r="B33" s="281" t="s">
+      <c r="A33" s="292"/>
+      <c r="B33" s="290" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="282">
+      <c r="C33" s="291">
         <v>2</v>
       </c>
       <c r="D33" s="7">
@@ -4379,14 +4424,14 @@
         <f t="shared" si="2"/>
         <v>80000</v>
       </c>
-      <c r="F33" s="291"/>
+      <c r="F33" s="300"/>
     </row>
     <row r="34" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A34" s="284"/>
-      <c r="B34" s="281" t="s">
+      <c r="A34" s="293"/>
+      <c r="B34" s="290" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="282">
+      <c r="C34" s="291">
         <v>1</v>
       </c>
       <c r="D34" s="7">
@@ -4396,16 +4441,16 @@
         <f t="shared" si="2"/>
         <v>25000</v>
       </c>
-      <c r="F34" s="292"/>
+      <c r="F34" s="301"/>
     </row>
     <row r="35" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A35" s="288">
+      <c r="A35" s="297">
         <v>45998</v>
       </c>
-      <c r="B35" s="287" t="s">
+      <c r="B35" s="296" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="282">
+      <c r="C35" s="291">
         <v>8.945</v>
       </c>
       <c r="D35" s="7">
@@ -4414,17 +4459,17 @@
       <c r="E35" s="7">
         <v>134000</v>
       </c>
-      <c r="F35" s="291">
+      <c r="F35" s="300">
         <f>SUM(E35:E42)</f>
         <v>517000</v>
       </c>
     </row>
     <row r="36" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A36" s="288"/>
-      <c r="B36" s="287" t="s">
+      <c r="A36" s="297"/>
+      <c r="B36" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="282">
+      <c r="C36" s="291">
         <v>2</v>
       </c>
       <c r="D36" s="7">
@@ -4434,14 +4479,14 @@
         <f t="shared" ref="E35:E44" si="3">SUM(C36*D36)</f>
         <v>40000</v>
       </c>
-      <c r="F36" s="291"/>
+      <c r="F36" s="300"/>
     </row>
     <row r="37" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A37" s="288"/>
-      <c r="B37" s="287" t="s">
+      <c r="A37" s="297"/>
+      <c r="B37" s="296" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="282">
+      <c r="C37" s="291">
         <v>0.3</v>
       </c>
       <c r="D37" s="7">
@@ -4451,14 +4496,14 @@
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="F37" s="291"/>
+      <c r="F37" s="300"/>
     </row>
     <row r="38" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A38" s="288"/>
-      <c r="B38" s="287" t="s">
+      <c r="A38" s="297"/>
+      <c r="B38" s="296" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="282">
+      <c r="C38" s="291">
         <v>1</v>
       </c>
       <c r="D38" s="7">
@@ -4468,14 +4513,14 @@
         <f t="shared" si="3"/>
         <v>30000</v>
       </c>
-      <c r="F38" s="291"/>
+      <c r="F38" s="300"/>
     </row>
     <row r="39" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A39" s="288"/>
-      <c r="B39" s="287" t="s">
+      <c r="A39" s="297"/>
+      <c r="B39" s="296" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="282">
+      <c r="C39" s="291">
         <v>0.5</v>
       </c>
       <c r="D39" s="7">
@@ -4485,14 +4530,14 @@
         <f t="shared" si="3"/>
         <v>15000</v>
       </c>
-      <c r="F39" s="291"/>
+      <c r="F39" s="300"/>
     </row>
     <row r="40" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A40" s="288"/>
-      <c r="B40" s="287" t="s">
+      <c r="A40" s="297"/>
+      <c r="B40" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="282">
+      <c r="C40" s="291">
         <v>4</v>
       </c>
       <c r="D40" s="7">
@@ -4502,14 +4547,14 @@
         <f t="shared" si="3"/>
         <v>96000</v>
       </c>
-      <c r="F40" s="291"/>
+      <c r="F40" s="300"/>
     </row>
     <row r="41" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A41" s="288"/>
-      <c r="B41" s="287" t="s">
+      <c r="A41" s="297"/>
+      <c r="B41" s="296" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="282">
+      <c r="C41" s="291">
         <v>2</v>
       </c>
       <c r="D41" s="7">
@@ -4519,14 +4564,14 @@
         <f t="shared" si="3"/>
         <v>80000</v>
       </c>
-      <c r="F41" s="291"/>
+      <c r="F41" s="300"/>
     </row>
     <row r="42" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A42" s="288"/>
-      <c r="B42" s="287" t="s">
+      <c r="A42" s="297"/>
+      <c r="B42" s="296" t="s">
         <v>32</v>
       </c>
-      <c r="C42" s="282">
+      <c r="C42" s="291">
         <v>2</v>
       </c>
       <c r="D42" s="7">
@@ -4536,16 +4581,16 @@
         <f t="shared" si="3"/>
         <v>98000</v>
       </c>
-      <c r="F42" s="291"/>
+      <c r="F42" s="300"/>
     </row>
     <row r="43" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A43" s="280">
+      <c r="A43" s="289">
         <v>45999</v>
       </c>
-      <c r="B43" s="287" t="s">
+      <c r="B43" s="296" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="282">
+      <c r="C43" s="291">
         <v>3</v>
       </c>
       <c r="D43" s="7">
@@ -4555,17 +4600,17 @@
         <f t="shared" si="3"/>
         <v>30000</v>
       </c>
-      <c r="F43" s="293">
+      <c r="F43" s="302">
         <f>SUM(E43:E47)</f>
         <v>357000</v>
       </c>
     </row>
     <row r="44" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A44" s="283"/>
-      <c r="B44" s="287" t="s">
+      <c r="A44" s="292"/>
+      <c r="B44" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="282">
+      <c r="C44" s="291">
         <v>2.7</v>
       </c>
       <c r="D44" s="7">
@@ -4575,14 +4620,14 @@
         <f t="shared" si="3"/>
         <v>54000</v>
       </c>
-      <c r="F44" s="293"/>
+      <c r="F44" s="302"/>
     </row>
     <row r="45" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A45" s="283"/>
-      <c r="B45" s="287" t="s">
+      <c r="A45" s="292"/>
+      <c r="B45" s="296" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="282">
+      <c r="C45" s="291">
         <v>3.09</v>
       </c>
       <c r="D45" s="7">
@@ -4591,14 +4636,14 @@
       <c r="E45" s="7">
         <v>216000</v>
       </c>
-      <c r="F45" s="293"/>
+      <c r="F45" s="302"/>
     </row>
     <row r="46" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A46" s="283"/>
-      <c r="B46" s="287" t="s">
+      <c r="A46" s="292"/>
+      <c r="B46" s="296" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="282">
+      <c r="C46" s="291">
         <v>0.3</v>
       </c>
       <c r="D46" s="7">
@@ -4608,14 +4653,14 @@
         <f>SUM(C46*D46)</f>
         <v>9000</v>
       </c>
-      <c r="F46" s="293"/>
+      <c r="F46" s="302"/>
     </row>
     <row r="47" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A47" s="283"/>
-      <c r="B47" s="287" t="s">
+      <c r="A47" s="292"/>
+      <c r="B47" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="282">
+      <c r="C47" s="291">
         <v>2</v>
       </c>
       <c r="D47" s="7">
@@ -4625,16 +4670,16 @@
         <f>SUM(C47*D47)</f>
         <v>48000</v>
       </c>
-      <c r="F47" s="293"/>
+      <c r="F47" s="302"/>
     </row>
     <row r="48" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A48" s="280">
+      <c r="A48" s="289">
         <v>46000</v>
       </c>
-      <c r="B48" s="287" t="s">
+      <c r="B48" s="296" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="282">
+      <c r="C48" s="291">
         <v>2</v>
       </c>
       <c r="D48" s="7">
@@ -4644,17 +4689,17 @@
         <f t="shared" ref="E48:E82" si="4">SUM(C48*D48)</f>
         <v>40000</v>
       </c>
-      <c r="F48" s="290">
+      <c r="F48" s="299">
         <f>SUM(E48:E58)</f>
         <v>612000</v>
       </c>
     </row>
     <row r="49" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A49" s="283"/>
-      <c r="B49" s="287" t="s">
+      <c r="A49" s="292"/>
+      <c r="B49" s="296" t="s">
         <v>17</v>
       </c>
-      <c r="C49" s="282">
+      <c r="C49" s="291">
         <v>2</v>
       </c>
       <c r="D49" s="7">
@@ -4664,14 +4709,14 @@
         <f t="shared" si="4"/>
         <v>70000</v>
       </c>
-      <c r="F49" s="291"/>
+      <c r="F49" s="300"/>
     </row>
     <row r="50" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A50" s="283"/>
-      <c r="B50" s="287" t="s">
+      <c r="A50" s="292"/>
+      <c r="B50" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="282">
+      <c r="C50" s="291">
         <v>5</v>
       </c>
       <c r="D50" s="7">
@@ -4681,14 +4726,14 @@
         <f t="shared" si="4"/>
         <v>120000</v>
       </c>
-      <c r="F50" s="291"/>
+      <c r="F50" s="300"/>
     </row>
     <row r="51" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A51" s="283"/>
-      <c r="B51" s="287" t="s">
+      <c r="A51" s="292"/>
+      <c r="B51" s="296" t="s">
         <v>32</v>
       </c>
-      <c r="C51" s="282">
+      <c r="C51" s="291">
         <v>1</v>
       </c>
       <c r="D51" s="7">
@@ -4698,14 +4743,14 @@
         <f t="shared" si="4"/>
         <v>49000</v>
       </c>
-      <c r="F51" s="291"/>
+      <c r="F51" s="300"/>
     </row>
     <row r="52" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A52" s="283"/>
-      <c r="B52" s="287" t="s">
+      <c r="A52" s="292"/>
+      <c r="B52" s="296" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="282">
+      <c r="C52" s="291">
         <v>1</v>
       </c>
       <c r="D52" s="7">
@@ -4715,14 +4760,14 @@
         <f t="shared" si="4"/>
         <v>65000</v>
       </c>
-      <c r="F52" s="291"/>
+      <c r="F52" s="300"/>
     </row>
     <row r="53" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A53" s="283"/>
-      <c r="B53" s="287" t="s">
+      <c r="A53" s="292"/>
+      <c r="B53" s="296" t="s">
         <v>18</v>
       </c>
-      <c r="C53" s="282">
+      <c r="C53" s="291">
         <v>0.5</v>
       </c>
       <c r="D53" s="7">
@@ -4731,14 +4776,14 @@
       <c r="E53" s="7">
         <v>48000</v>
       </c>
-      <c r="F53" s="291"/>
+      <c r="F53" s="300"/>
     </row>
     <row r="54" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A54" s="283"/>
-      <c r="B54" s="287" t="s">
+      <c r="A54" s="292"/>
+      <c r="B54" s="296" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="291">
         <v>1</v>
       </c>
       <c r="D54" s="7">
@@ -4748,14 +4793,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F54" s="291"/>
+      <c r="F54" s="300"/>
     </row>
     <row r="55" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A55" s="283"/>
-      <c r="B55" s="287" t="s">
+      <c r="A55" s="292"/>
+      <c r="B55" s="296" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="282">
+      <c r="C55" s="291">
         <v>9</v>
       </c>
       <c r="D55" s="7">
@@ -4765,14 +4810,14 @@
         <f t="shared" si="4"/>
         <v>90000</v>
       </c>
-      <c r="F55" s="291"/>
+      <c r="F55" s="300"/>
     </row>
     <row r="56" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A56" s="283"/>
-      <c r="B56" s="281" t="s">
+      <c r="A56" s="292"/>
+      <c r="B56" s="290" t="s">
         <v>7</v>
       </c>
-      <c r="C56" s="282">
+      <c r="C56" s="291">
         <v>1</v>
       </c>
       <c r="D56" s="7">
@@ -4782,14 +4827,14 @@
         <f t="shared" si="4"/>
         <v>70000</v>
       </c>
-      <c r="F56" s="291"/>
+      <c r="F56" s="300"/>
     </row>
     <row r="57" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A57" s="283"/>
-      <c r="B57" s="281" t="s">
+      <c r="A57" s="292"/>
+      <c r="B57" s="290" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="282">
+      <c r="C57" s="291">
         <v>2</v>
       </c>
       <c r="D57" s="7">
@@ -4799,14 +4844,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F57" s="291"/>
+      <c r="F57" s="300"/>
     </row>
     <row r="58" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A58" s="284"/>
-      <c r="B58" s="281" t="s">
+      <c r="A58" s="293"/>
+      <c r="B58" s="290" t="s">
         <v>34</v>
       </c>
-      <c r="C58" s="282">
+      <c r="C58" s="291">
         <v>1</v>
       </c>
       <c r="D58" s="7">
@@ -4816,16 +4861,16 @@
         <f t="shared" si="4"/>
         <v>5000</v>
       </c>
-      <c r="F58" s="292"/>
+      <c r="F58" s="301"/>
     </row>
     <row r="59" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A59" s="280">
+      <c r="A59" s="289">
         <v>46001</v>
       </c>
-      <c r="B59" s="281" t="s">
+      <c r="B59" s="290" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="282">
+      <c r="C59" s="291">
         <v>3</v>
       </c>
       <c r="D59" s="7">
@@ -4835,17 +4880,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F59" s="290">
+      <c r="F59" s="299">
         <f>SUM(E59:E67)</f>
         <v>586000</v>
       </c>
     </row>
     <row r="60" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A60" s="283"/>
-      <c r="B60" s="281" t="s">
+      <c r="A60" s="292"/>
+      <c r="B60" s="290" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="282">
+      <c r="C60" s="291">
         <v>2</v>
       </c>
       <c r="D60" s="7">
@@ -4855,14 +4900,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F60" s="291"/>
+      <c r="F60" s="300"/>
     </row>
     <row r="61" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A61" s="283"/>
-      <c r="B61" s="281" t="s">
+      <c r="A61" s="292"/>
+      <c r="B61" s="290" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="282">
+      <c r="C61" s="291">
         <v>8</v>
       </c>
       <c r="D61" s="7">
@@ -4872,14 +4917,14 @@
         <f t="shared" si="4"/>
         <v>80000</v>
       </c>
-      <c r="F61" s="291"/>
+      <c r="F61" s="300"/>
     </row>
     <row r="62" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A62" s="283"/>
-      <c r="B62" s="281" t="s">
+      <c r="A62" s="292"/>
+      <c r="B62" s="290" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="282">
+      <c r="C62" s="291">
         <v>1</v>
       </c>
       <c r="D62" s="7">
@@ -4889,14 +4934,14 @@
         <f t="shared" si="4"/>
         <v>38000</v>
       </c>
-      <c r="F62" s="291"/>
+      <c r="F62" s="300"/>
     </row>
     <row r="63" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A63" s="283"/>
-      <c r="B63" s="281" t="s">
+      <c r="A63" s="292"/>
+      <c r="B63" s="290" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="282">
+      <c r="C63" s="291">
         <v>1</v>
       </c>
       <c r="D63" s="7">
@@ -4906,14 +4951,14 @@
         <f t="shared" si="4"/>
         <v>20000</v>
       </c>
-      <c r="F63" s="291"/>
+      <c r="F63" s="300"/>
     </row>
     <row r="64" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A64" s="283"/>
-      <c r="B64" s="281" t="s">
+      <c r="A64" s="292"/>
+      <c r="B64" s="290" t="s">
         <v>22</v>
       </c>
-      <c r="C64" s="282">
+      <c r="C64" s="291">
         <v>0.5</v>
       </c>
       <c r="D64" s="7">
@@ -4923,14 +4968,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F64" s="291"/>
+      <c r="F64" s="300"/>
     </row>
     <row r="65" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A65" s="283"/>
-      <c r="B65" s="281" t="s">
+      <c r="A65" s="292"/>
+      <c r="B65" s="290" t="s">
         <v>14</v>
       </c>
-      <c r="C65" s="282">
+      <c r="C65" s="291">
         <v>6</v>
       </c>
       <c r="D65" s="7">
@@ -4940,14 +4985,14 @@
         <f t="shared" si="4"/>
         <v>144000</v>
       </c>
-      <c r="F65" s="291"/>
+      <c r="F65" s="300"/>
     </row>
     <row r="66" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A66" s="283"/>
-      <c r="B66" s="281" t="s">
+      <c r="A66" s="292"/>
+      <c r="B66" s="290" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="282">
+      <c r="C66" s="291">
         <v>1</v>
       </c>
       <c r="D66" s="7">
@@ -4957,14 +5002,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F66" s="291"/>
+      <c r="F66" s="300"/>
     </row>
     <row r="67" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A67" s="284"/>
-      <c r="B67" s="281" t="s">
+      <c r="A67" s="293"/>
+      <c r="B67" s="290" t="s">
         <v>32</v>
       </c>
-      <c r="C67" s="282">
+      <c r="C67" s="291">
         <v>1</v>
       </c>
       <c r="D67" s="7">
@@ -4974,16 +5019,16 @@
         <f t="shared" si="4"/>
         <v>49000</v>
       </c>
-      <c r="F67" s="292"/>
+      <c r="F67" s="301"/>
     </row>
     <row r="68" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A68" s="280">
+      <c r="A68" s="289">
         <v>46002</v>
       </c>
-      <c r="B68" s="281" t="s">
+      <c r="B68" s="290" t="s">
         <v>6</v>
       </c>
-      <c r="C68" s="282">
+      <c r="C68" s="291">
         <v>3</v>
       </c>
       <c r="D68" s="7">
@@ -4993,17 +5038,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F68" s="290">
+      <c r="F68" s="299">
         <f>SUM(E68:E78)</f>
         <v>541000</v>
       </c>
     </row>
     <row r="69" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A69" s="283"/>
-      <c r="B69" s="281" t="s">
+      <c r="A69" s="292"/>
+      <c r="B69" s="290" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="282">
+      <c r="C69" s="291">
         <v>2</v>
       </c>
       <c r="D69" s="7">
@@ -5013,14 +5058,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F69" s="291"/>
+      <c r="F69" s="300"/>
     </row>
     <row r="70" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A70" s="283"/>
-      <c r="B70" s="281" t="s">
+      <c r="A70" s="292"/>
+      <c r="B70" s="290" t="s">
         <v>8</v>
       </c>
-      <c r="C70" s="282">
+      <c r="C70" s="291">
         <v>4</v>
       </c>
       <c r="D70" s="7">
@@ -5030,14 +5075,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F70" s="291"/>
+      <c r="F70" s="300"/>
     </row>
     <row r="71" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A71" s="283"/>
-      <c r="B71" s="281" t="s">
+      <c r="A71" s="292"/>
+      <c r="B71" s="290" t="s">
         <v>9</v>
       </c>
-      <c r="C71" s="282">
+      <c r="C71" s="291">
         <v>1</v>
       </c>
       <c r="D71" s="7">
@@ -5047,14 +5092,14 @@
         <f t="shared" si="4"/>
         <v>38000</v>
       </c>
-      <c r="F71" s="291"/>
+      <c r="F71" s="300"/>
     </row>
     <row r="72" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A72" s="283"/>
-      <c r="B72" s="281" t="s">
+      <c r="A72" s="292"/>
+      <c r="B72" s="290" t="s">
         <v>10</v>
       </c>
-      <c r="C72" s="282">
+      <c r="C72" s="291">
         <v>1</v>
       </c>
       <c r="D72" s="7">
@@ -5064,14 +5109,14 @@
         <f t="shared" si="4"/>
         <v>20000</v>
       </c>
-      <c r="F72" s="291"/>
+      <c r="F72" s="300"/>
     </row>
     <row r="73" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A73" s="283"/>
-      <c r="B73" s="281" t="s">
+      <c r="A73" s="292"/>
+      <c r="B73" s="290" t="s">
         <v>22</v>
       </c>
-      <c r="C73" s="282">
+      <c r="C73" s="291">
         <v>0.5</v>
       </c>
       <c r="D73" s="7">
@@ -5081,14 +5126,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F73" s="291"/>
+      <c r="F73" s="300"/>
     </row>
     <row r="74" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A74" s="283"/>
-      <c r="B74" s="281" t="s">
+      <c r="A74" s="292"/>
+      <c r="B74" s="290" t="s">
         <v>12</v>
       </c>
-      <c r="C74" s="282">
+      <c r="C74" s="291">
         <v>1</v>
       </c>
       <c r="D74" s="7">
@@ -5098,14 +5143,14 @@
         <f t="shared" si="4"/>
         <v>30000</v>
       </c>
-      <c r="F74" s="291"/>
+      <c r="F74" s="300"/>
     </row>
     <row r="75" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A75" s="283"/>
-      <c r="B75" s="281" t="s">
+      <c r="A75" s="292"/>
+      <c r="B75" s="290" t="s">
         <v>18</v>
       </c>
-      <c r="C75" s="282">
+      <c r="C75" s="291">
         <v>1</v>
       </c>
       <c r="D75" s="7">
@@ -5115,14 +5160,14 @@
         <f t="shared" si="4"/>
         <v>95000</v>
       </c>
-      <c r="F75" s="291"/>
+      <c r="F75" s="300"/>
     </row>
     <row r="76" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A76" s="283"/>
-      <c r="B76" s="281" t="s">
+      <c r="A76" s="292"/>
+      <c r="B76" s="290" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="282">
+      <c r="C76" s="291">
         <v>1</v>
       </c>
       <c r="D76" s="7">
@@ -5132,14 +5177,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F76" s="291"/>
+      <c r="F76" s="300"/>
     </row>
     <row r="77" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A77" s="283"/>
-      <c r="B77" s="281" t="s">
+      <c r="A77" s="292"/>
+      <c r="B77" s="290" t="s">
         <v>14</v>
       </c>
-      <c r="C77" s="282">
+      <c r="C77" s="291">
         <v>2</v>
       </c>
       <c r="D77" s="7">
@@ -5149,14 +5194,14 @@
         <f t="shared" si="4"/>
         <v>48000</v>
       </c>
-      <c r="F77" s="291"/>
+      <c r="F77" s="300"/>
     </row>
     <row r="78" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A78" s="284"/>
-      <c r="B78" s="281" t="s">
+      <c r="A78" s="293"/>
+      <c r="B78" s="290" t="s">
         <v>15</v>
       </c>
-      <c r="C78" s="282">
+      <c r="C78" s="291">
         <v>1</v>
       </c>
       <c r="D78" s="7">
@@ -5166,16 +5211,16 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F78" s="292"/>
+      <c r="F78" s="301"/>
     </row>
     <row r="79" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A79" s="280">
+      <c r="A79" s="289">
         <v>46003</v>
       </c>
-      <c r="B79" s="281" t="s">
+      <c r="B79" s="290" t="s">
         <v>6</v>
       </c>
-      <c r="C79" s="282">
+      <c r="C79" s="291">
         <v>3</v>
       </c>
       <c r="D79" s="7">
@@ -5185,17 +5230,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F79" s="290">
+      <c r="F79" s="299">
         <f>-SUM(E79:E93)</f>
         <v>-900000</v>
       </c>
     </row>
     <row r="80" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A80" s="283"/>
-      <c r="B80" s="281" t="s">
+      <c r="A80" s="292"/>
+      <c r="B80" s="290" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="282">
+      <c r="C80" s="291">
         <v>2</v>
       </c>
       <c r="D80" s="7">
@@ -5205,14 +5250,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F80" s="291"/>
+      <c r="F80" s="300"/>
     </row>
     <row r="81" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A81" s="283"/>
-      <c r="B81" s="281" t="s">
+      <c r="A81" s="292"/>
+      <c r="B81" s="290" t="s">
         <v>8</v>
       </c>
-      <c r="C81" s="282">
+      <c r="C81" s="291">
         <v>6</v>
       </c>
       <c r="D81" s="7">
@@ -5222,14 +5267,14 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F81" s="291"/>
+      <c r="F81" s="300"/>
     </row>
     <row r="82" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A82" s="283"/>
-      <c r="B82" s="281" t="s">
+      <c r="A82" s="292"/>
+      <c r="B82" s="290" t="s">
         <v>35</v>
       </c>
-      <c r="C82" s="282">
+      <c r="C82" s="291">
         <v>2</v>
       </c>
       <c r="D82" s="7">
@@ -5239,14 +5284,14 @@
         <f t="shared" si="4"/>
         <v>96000</v>
       </c>
-      <c r="F82" s="291"/>
+      <c r="F82" s="300"/>
     </row>
     <row r="83" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A83" s="283"/>
-      <c r="B83" s="281" t="s">
+      <c r="A83" s="292"/>
+      <c r="B83" s="290" t="s">
         <v>24</v>
       </c>
-      <c r="C83" s="282">
+      <c r="C83" s="291">
         <v>8.18</v>
       </c>
       <c r="D83" s="7">
@@ -5255,14 +5300,14 @@
       <c r="E83" s="7">
         <v>123000</v>
       </c>
-      <c r="F83" s="291"/>
+      <c r="F83" s="300"/>
     </row>
     <row r="84" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A84" s="283"/>
-      <c r="B84" s="281" t="s">
+      <c r="A84" s="292"/>
+      <c r="B84" s="290" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="282">
+      <c r="C84" s="291">
         <v>0.3</v>
       </c>
       <c r="D84" s="7">
@@ -5272,14 +5317,14 @@
         <f>SUM(C84*D84)</f>
         <v>6000</v>
       </c>
-      <c r="F84" s="291"/>
+      <c r="F84" s="300"/>
     </row>
     <row r="85" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A85" s="283"/>
-      <c r="B85" s="281" t="s">
+      <c r="A85" s="292"/>
+      <c r="B85" s="290" t="s">
         <v>22</v>
       </c>
-      <c r="C85" s="282">
+      <c r="C85" s="291">
         <v>0.5</v>
       </c>
       <c r="D85" s="7">
@@ -5289,14 +5334,14 @@
         <f>SUM(C85*D85)</f>
         <v>15000</v>
       </c>
-      <c r="F85" s="291"/>
+      <c r="F85" s="300"/>
     </row>
     <row r="86" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A86" s="283"/>
-      <c r="B86" s="281" t="s">
+      <c r="A86" s="292"/>
+      <c r="B86" s="290" t="s">
         <v>31</v>
       </c>
-      <c r="C86" s="282">
+      <c r="C86" s="291">
         <v>0.5</v>
       </c>
       <c r="D86" s="7">
@@ -5306,14 +5351,14 @@
         <f>SUM(C86*D86)</f>
         <v>40000</v>
       </c>
-      <c r="F86" s="291"/>
+      <c r="F86" s="300"/>
     </row>
     <row r="87" s="244" customFormat="1" ht="14" customHeight="1" spans="1:8">
-      <c r="A87" s="283"/>
-      <c r="B87" s="281" t="s">
+      <c r="A87" s="292"/>
+      <c r="B87" s="290" t="s">
         <v>18</v>
       </c>
-      <c r="C87" s="282">
+      <c r="C87" s="291">
         <v>0.5</v>
       </c>
       <c r="D87" s="7">
@@ -5322,15 +5367,15 @@
       <c r="E87" s="7">
         <v>48000</v>
       </c>
-      <c r="F87" s="291"/>
-      <c r="H87" s="271"/>
+      <c r="F87" s="300"/>
+      <c r="H87" s="277"/>
     </row>
     <row r="88" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A88" s="283"/>
-      <c r="B88" s="281" t="s">
+      <c r="A88" s="292"/>
+      <c r="B88" s="290" t="s">
         <v>13</v>
       </c>
-      <c r="C88" s="282">
+      <c r="C88" s="291">
         <v>1</v>
       </c>
       <c r="D88" s="7">
@@ -5340,14 +5385,14 @@
         <f t="shared" ref="E88:E94" si="5">SUM(C88*D88)</f>
         <v>15000</v>
       </c>
-      <c r="F88" s="291"/>
+      <c r="F88" s="300"/>
     </row>
     <row r="89" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A89" s="283"/>
-      <c r="B89" s="281" t="s">
+      <c r="A89" s="292"/>
+      <c r="B89" s="290" t="s">
         <v>14</v>
       </c>
-      <c r="C89" s="282">
+      <c r="C89" s="291">
         <v>2</v>
       </c>
       <c r="D89" s="7">
@@ -5357,14 +5402,14 @@
         <f t="shared" si="5"/>
         <v>48000</v>
       </c>
-      <c r="F89" s="291"/>
+      <c r="F89" s="300"/>
     </row>
     <row r="90" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A90" s="283"/>
-      <c r="B90" s="281" t="s">
+      <c r="A90" s="292"/>
+      <c r="B90" s="290" t="s">
         <v>15</v>
       </c>
-      <c r="C90" s="282">
+      <c r="C90" s="291">
         <v>1</v>
       </c>
       <c r="D90" s="7">
@@ -5374,14 +5419,14 @@
         <f t="shared" si="5"/>
         <v>40000</v>
       </c>
-      <c r="F90" s="291"/>
+      <c r="F90" s="300"/>
     </row>
     <row r="91" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A91" s="283"/>
-      <c r="B91" s="281" t="s">
+      <c r="A91" s="292"/>
+      <c r="B91" s="290" t="s">
         <v>32</v>
       </c>
-      <c r="C91" s="282">
+      <c r="C91" s="291">
         <v>1</v>
       </c>
       <c r="D91" s="7">
@@ -5391,14 +5436,14 @@
         <f t="shared" si="5"/>
         <v>49000</v>
       </c>
-      <c r="F91" s="291"/>
+      <c r="F91" s="300"/>
     </row>
     <row r="92" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A92" s="283"/>
-      <c r="B92" s="281" t="s">
+      <c r="A92" s="292"/>
+      <c r="B92" s="290" t="s">
         <v>21</v>
       </c>
-      <c r="C92" s="282">
+      <c r="C92" s="291">
         <v>4</v>
       </c>
       <c r="D92" s="7">
@@ -5408,14 +5453,14 @@
         <f t="shared" si="5"/>
         <v>80000</v>
       </c>
-      <c r="F92" s="291"/>
+      <c r="F92" s="300"/>
     </row>
     <row r="93" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A93" s="284"/>
-      <c r="B93" s="281" t="s">
+      <c r="A93" s="293"/>
+      <c r="B93" s="290" t="s">
         <v>27</v>
       </c>
-      <c r="C93" s="282">
+      <c r="C93" s="291">
         <v>4</v>
       </c>
       <c r="D93" s="7">
@@ -5425,16 +5470,16 @@
         <f t="shared" si="5"/>
         <v>80000</v>
       </c>
-      <c r="F93" s="292"/>
+      <c r="F93" s="301"/>
     </row>
     <row r="94" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A94" s="280">
+      <c r="A94" s="289">
         <v>46004</v>
       </c>
-      <c r="B94" s="287" t="s">
+      <c r="B94" s="296" t="s">
         <v>8</v>
       </c>
-      <c r="C94" s="294">
+      <c r="C94" s="303">
         <v>8</v>
       </c>
       <c r="D94" s="7">
@@ -5444,17 +5489,17 @@
         <f t="shared" si="5"/>
         <v>80000</v>
       </c>
-      <c r="F94" s="290">
+      <c r="F94" s="299">
         <f>SUM(E94:E99)</f>
         <v>479000</v>
       </c>
     </row>
     <row r="95" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A95" s="283"/>
-      <c r="B95" s="287" t="s">
+      <c r="A95" s="292"/>
+      <c r="B95" s="296" t="s">
         <v>24</v>
       </c>
-      <c r="C95" s="294">
+      <c r="C95" s="303">
         <v>7.155</v>
       </c>
       <c r="D95" s="7">
@@ -5463,14 +5508,14 @@
       <c r="E95" s="7">
         <v>107000</v>
       </c>
-      <c r="F95" s="291"/>
+      <c r="F95" s="300"/>
     </row>
     <row r="96" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A96" s="283"/>
-      <c r="B96" s="287" t="s">
+      <c r="A96" s="292"/>
+      <c r="B96" s="296" t="s">
         <v>11</v>
       </c>
-      <c r="C96" s="294">
+      <c r="C96" s="303">
         <v>2</v>
       </c>
       <c r="D96" s="7">
@@ -5480,14 +5525,14 @@
         <f>SUM(C96*D96)</f>
         <v>76000</v>
       </c>
-      <c r="F96" s="291"/>
+      <c r="F96" s="300"/>
     </row>
     <row r="97" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A97" s="283"/>
-      <c r="B97" s="287" t="s">
+      <c r="A97" s="292"/>
+      <c r="B97" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="C97" s="294">
+      <c r="C97" s="303">
         <v>2</v>
       </c>
       <c r="D97" s="7">
@@ -5497,14 +5542,14 @@
         <f>SUM(C97*D97)</f>
         <v>40000</v>
       </c>
-      <c r="F97" s="291"/>
+      <c r="F97" s="300"/>
     </row>
     <row r="98" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A98" s="283"/>
-      <c r="B98" s="287" t="s">
+      <c r="A98" s="292"/>
+      <c r="B98" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="C98" s="294">
+      <c r="C98" s="303">
         <v>4</v>
       </c>
       <c r="D98" s="7">
@@ -5514,14 +5559,14 @@
         <f>SUM(C98*D98)</f>
         <v>96000</v>
       </c>
-      <c r="F98" s="291"/>
+      <c r="F98" s="300"/>
     </row>
     <row r="99" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A99" s="284"/>
-      <c r="B99" s="287" t="s">
+      <c r="A99" s="293"/>
+      <c r="B99" s="296" t="s">
         <v>15</v>
       </c>
-      <c r="C99" s="294">
+      <c r="C99" s="303">
         <v>2</v>
       </c>
       <c r="D99" s="7">
@@ -5531,16 +5576,16 @@
         <f>SUM(C99*D99)</f>
         <v>80000</v>
       </c>
-      <c r="F99" s="292"/>
+      <c r="F99" s="301"/>
     </row>
     <row r="100" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A100" s="283">
+      <c r="A100" s="292">
         <v>46005</v>
       </c>
-      <c r="B100" s="287" t="s">
+      <c r="B100" s="296" t="s">
         <v>8</v>
       </c>
-      <c r="C100" s="294">
+      <c r="C100" s="303">
         <v>8</v>
       </c>
       <c r="D100" s="7">
@@ -5550,17 +5595,17 @@
         <f t="shared" ref="E100:E108" si="6">SUM(C100*D100)</f>
         <v>80000</v>
       </c>
-      <c r="F100" s="293">
+      <c r="F100" s="302">
         <f>SUM(E100:E108)</f>
         <v>506000</v>
       </c>
     </row>
     <row r="101" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A101" s="283"/>
-      <c r="B101" s="287" t="s">
+      <c r="A101" s="292"/>
+      <c r="B101" s="296" t="s">
         <v>24</v>
       </c>
-      <c r="C101" s="294">
+      <c r="C101" s="303">
         <v>8.23</v>
       </c>
       <c r="D101" s="7">
@@ -5569,14 +5614,14 @@
       <c r="E101" s="22">
         <v>123000</v>
       </c>
-      <c r="F101" s="294"/>
+      <c r="F101" s="303"/>
     </row>
     <row r="102" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A102" s="283"/>
-      <c r="B102" s="287" t="s">
+      <c r="A102" s="292"/>
+      <c r="B102" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="C102" s="294">
+      <c r="C102" s="303">
         <v>2</v>
       </c>
       <c r="D102" s="7">
@@ -5586,14 +5631,14 @@
         <f t="shared" si="6"/>
         <v>40000</v>
       </c>
-      <c r="F102" s="294"/>
+      <c r="F102" s="303"/>
     </row>
     <row r="103" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A103" s="283"/>
-      <c r="B103" s="287" t="s">
+      <c r="A103" s="292"/>
+      <c r="B103" s="296" t="s">
         <v>10</v>
       </c>
-      <c r="C103" s="294">
+      <c r="C103" s="303">
         <v>0.3</v>
       </c>
       <c r="D103" s="7">
@@ -5603,14 +5648,14 @@
         <f t="shared" si="6"/>
         <v>6000</v>
       </c>
-      <c r="F103" s="294"/>
+      <c r="F103" s="303"/>
     </row>
     <row r="104" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A104" s="283"/>
-      <c r="B104" s="287" t="s">
+      <c r="A104" s="292"/>
+      <c r="B104" s="296" t="s">
         <v>13</v>
       </c>
-      <c r="C104" s="294">
+      <c r="C104" s="303">
         <v>1</v>
       </c>
       <c r="D104" s="7">
@@ -5620,14 +5665,14 @@
         <f t="shared" si="6"/>
         <v>15000</v>
       </c>
-      <c r="F104" s="294"/>
+      <c r="F104" s="303"/>
     </row>
     <row r="105" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A105" s="283"/>
-      <c r="B105" s="287" t="s">
+      <c r="A105" s="292"/>
+      <c r="B105" s="296" t="s">
         <v>36</v>
       </c>
-      <c r="C105" s="294">
+      <c r="C105" s="303">
         <v>1</v>
       </c>
       <c r="D105" s="7">
@@ -5637,14 +5682,14 @@
         <f t="shared" si="6"/>
         <v>48000</v>
       </c>
-      <c r="F105" s="294"/>
+      <c r="F105" s="303"/>
     </row>
     <row r="106" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A106" s="283"/>
-      <c r="B106" s="287" t="s">
+      <c r="A106" s="292"/>
+      <c r="B106" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="C106" s="294">
+      <c r="C106" s="303">
         <v>5</v>
       </c>
       <c r="D106" s="7">
@@ -5654,14 +5699,14 @@
         <f t="shared" si="6"/>
         <v>120000</v>
       </c>
-      <c r="F106" s="294"/>
+      <c r="F106" s="303"/>
     </row>
     <row r="107" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A107" s="283"/>
-      <c r="B107" s="287" t="s">
+      <c r="A107" s="292"/>
+      <c r="B107" s="296" t="s">
         <v>32</v>
       </c>
-      <c r="C107" s="294">
+      <c r="C107" s="303">
         <v>1</v>
       </c>
       <c r="D107" s="7">
@@ -5671,14 +5716,14 @@
         <f t="shared" si="6"/>
         <v>49000</v>
       </c>
-      <c r="F107" s="294"/>
+      <c r="F107" s="303"/>
     </row>
     <row r="108" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A108" s="283"/>
-      <c r="B108" s="287" t="s">
+      <c r="A108" s="292"/>
+      <c r="B108" s="296" t="s">
         <v>37</v>
       </c>
-      <c r="C108" s="294">
+      <c r="C108" s="303">
         <v>1</v>
       </c>
       <c r="D108" s="7">
@@ -5688,16 +5733,16 @@
         <f t="shared" si="6"/>
         <v>25000</v>
       </c>
-      <c r="F108" s="294"/>
+      <c r="F108" s="303"/>
     </row>
     <row r="109" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A109" s="280">
+      <c r="A109" s="289">
         <v>46006</v>
       </c>
-      <c r="B109" s="287" t="s">
+      <c r="B109" s="296" t="s">
         <v>8</v>
       </c>
-      <c r="C109" s="294">
+      <c r="C109" s="303">
         <v>4</v>
       </c>
       <c r="D109" s="7">
@@ -5707,17 +5752,17 @@
         <f t="shared" ref="E109:E154" si="7">SUM(C109*D109)</f>
         <v>40000</v>
       </c>
-      <c r="F109" s="290">
+      <c r="F109" s="299">
         <f>SUM(E109:E121)</f>
         <v>630000</v>
       </c>
     </row>
     <row r="110" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A110" s="283"/>
-      <c r="B110" s="287" t="s">
+      <c r="A110" s="292"/>
+      <c r="B110" s="296" t="s">
         <v>24</v>
       </c>
-      <c r="C110" s="294">
+      <c r="C110" s="303">
         <v>3.43</v>
       </c>
       <c r="D110" s="7">
@@ -5726,14 +5771,14 @@
       <c r="E110" s="7">
         <v>51000</v>
       </c>
-      <c r="F110" s="291"/>
+      <c r="F110" s="300"/>
     </row>
     <row r="111" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A111" s="283"/>
-      <c r="B111" s="287" t="s">
+      <c r="A111" s="292"/>
+      <c r="B111" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="C111" s="294">
+      <c r="C111" s="303">
         <v>2</v>
       </c>
       <c r="D111" s="7">
@@ -5743,14 +5788,14 @@
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F111" s="291"/>
+      <c r="F111" s="300"/>
     </row>
     <row r="112" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A112" s="283"/>
-      <c r="B112" s="287" t="s">
+      <c r="A112" s="292"/>
+      <c r="B112" s="296" t="s">
         <v>10</v>
       </c>
-      <c r="C112" s="294">
+      <c r="C112" s="303">
         <v>0.3</v>
       </c>
       <c r="D112" s="7">
@@ -5760,14 +5805,14 @@
         <f t="shared" si="7"/>
         <v>6000</v>
       </c>
-      <c r="F112" s="291"/>
+      <c r="F112" s="300"/>
     </row>
     <row r="113" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A113" s="283"/>
-      <c r="B113" s="287" t="s">
+      <c r="A113" s="292"/>
+      <c r="B113" s="296" t="s">
         <v>13</v>
       </c>
-      <c r="C113" s="294">
+      <c r="C113" s="303">
         <v>2</v>
       </c>
       <c r="D113" s="7">
@@ -5777,14 +5822,14 @@
         <f t="shared" si="7"/>
         <v>30000</v>
       </c>
-      <c r="F113" s="291"/>
+      <c r="F113" s="300"/>
     </row>
     <row r="114" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A114" s="283"/>
-      <c r="B114" s="287" t="s">
+      <c r="A114" s="292"/>
+      <c r="B114" s="296" t="s">
         <v>36</v>
       </c>
-      <c r="C114" s="294">
+      <c r="C114" s="303">
         <v>2</v>
       </c>
       <c r="D114" s="7">
@@ -5794,14 +5839,14 @@
         <f t="shared" si="7"/>
         <v>96000</v>
       </c>
-      <c r="F114" s="291"/>
+      <c r="F114" s="300"/>
     </row>
     <row r="115" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A115" s="283"/>
-      <c r="B115" s="287" t="s">
+      <c r="A115" s="292"/>
+      <c r="B115" s="296" t="s">
         <v>38</v>
       </c>
-      <c r="C115" s="294">
+      <c r="C115" s="303">
         <v>1</v>
       </c>
       <c r="D115" s="7">
@@ -5811,14 +5856,14 @@
         <f t="shared" si="7"/>
         <v>45000</v>
       </c>
-      <c r="F115" s="291"/>
+      <c r="F115" s="300"/>
     </row>
     <row r="116" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A116" s="283"/>
-      <c r="B116" s="287" t="s">
+      <c r="A116" s="292"/>
+      <c r="B116" s="296" t="s">
         <v>11</v>
       </c>
-      <c r="C116" s="294">
+      <c r="C116" s="303">
         <v>1.2</v>
       </c>
       <c r="D116" s="7">
@@ -5827,14 +5872,14 @@
       <c r="E116" s="7">
         <v>46000</v>
       </c>
-      <c r="F116" s="291"/>
+      <c r="F116" s="300"/>
     </row>
     <row r="117" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A117" s="283"/>
-      <c r="B117" s="287" t="s">
+      <c r="A117" s="292"/>
+      <c r="B117" s="296" t="s">
         <v>22</v>
       </c>
-      <c r="C117" s="294">
+      <c r="C117" s="303">
         <v>0.5</v>
       </c>
       <c r="D117" s="7">
@@ -5844,14 +5889,14 @@
         <f t="shared" si="7"/>
         <v>15000</v>
       </c>
-      <c r="F117" s="291"/>
+      <c r="F117" s="300"/>
     </row>
     <row r="118" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A118" s="283"/>
-      <c r="B118" s="287" t="s">
+      <c r="A118" s="292"/>
+      <c r="B118" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="C118" s="294">
+      <c r="C118" s="303">
         <v>3</v>
       </c>
       <c r="D118" s="7">
@@ -5861,14 +5906,14 @@
         <f t="shared" si="7"/>
         <v>72000</v>
       </c>
-      <c r="F118" s="291"/>
+      <c r="F118" s="300"/>
     </row>
     <row r="119" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A119" s="283"/>
-      <c r="B119" s="287" t="s">
+      <c r="A119" s="292"/>
+      <c r="B119" s="296" t="s">
         <v>32</v>
       </c>
-      <c r="C119" s="294">
+      <c r="C119" s="303">
         <v>1</v>
       </c>
       <c r="D119" s="7">
@@ -5878,14 +5923,14 @@
         <f t="shared" si="7"/>
         <v>49000</v>
       </c>
-      <c r="F119" s="291"/>
+      <c r="F119" s="300"/>
     </row>
     <row r="120" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A120" s="283"/>
-      <c r="B120" s="287" t="s">
+      <c r="A120" s="292"/>
+      <c r="B120" s="296" t="s">
         <v>15</v>
       </c>
-      <c r="C120" s="294">
+      <c r="C120" s="303">
         <v>1</v>
       </c>
       <c r="D120" s="7">
@@ -5895,14 +5940,14 @@
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F120" s="291"/>
+      <c r="F120" s="300"/>
     </row>
     <row r="121" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A121" s="284"/>
-      <c r="B121" s="287" t="s">
+      <c r="A121" s="293"/>
+      <c r="B121" s="296" t="s">
         <v>27</v>
       </c>
-      <c r="C121" s="294">
+      <c r="C121" s="303">
         <v>5</v>
       </c>
       <c r="D121" s="7">
@@ -5912,16 +5957,16 @@
         <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="F121" s="292"/>
+      <c r="F121" s="301"/>
     </row>
     <row r="122" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A122" s="280">
+      <c r="A122" s="289">
         <v>46007</v>
       </c>
-      <c r="B122" s="287" t="s">
+      <c r="B122" s="296" t="s">
         <v>8</v>
       </c>
-      <c r="C122" s="294">
+      <c r="C122" s="303">
         <v>5</v>
       </c>
       <c r="D122" s="7">
@@ -5931,17 +5976,17 @@
         <f t="shared" si="7"/>
         <v>50000</v>
       </c>
-      <c r="F122" s="290">
+      <c r="F122" s="299">
         <f>SUM(E122:E128)</f>
         <v>412000</v>
       </c>
     </row>
     <row r="123" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A123" s="283"/>
-      <c r="B123" s="287" t="s">
+      <c r="A123" s="292"/>
+      <c r="B123" s="296" t="s">
         <v>24</v>
       </c>
-      <c r="C123" s="294">
+      <c r="C123" s="303">
         <v>6.15</v>
       </c>
       <c r="D123" s="7">
@@ -5950,14 +5995,14 @@
       <c r="E123" s="7">
         <v>92000</v>
       </c>
-      <c r="F123" s="291"/>
+      <c r="F123" s="300"/>
     </row>
     <row r="124" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A124" s="283"/>
-      <c r="B124" s="287" t="s">
+      <c r="A124" s="292"/>
+      <c r="B124" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="C124" s="294">
+      <c r="C124" s="303">
         <v>2</v>
       </c>
       <c r="D124" s="7">
@@ -5967,14 +6012,14 @@
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F124" s="291"/>
+      <c r="F124" s="300"/>
     </row>
     <row r="125" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A125" s="283"/>
-      <c r="B125" s="287" t="s">
+      <c r="A125" s="292"/>
+      <c r="B125" s="296" t="s">
         <v>10</v>
       </c>
-      <c r="C125" s="294">
+      <c r="C125" s="303">
         <v>0.3</v>
       </c>
       <c r="D125" s="7">
@@ -5983,14 +6028,14 @@
       <c r="E125" s="7">
         <v>5000</v>
       </c>
-      <c r="F125" s="291"/>
+      <c r="F125" s="300"/>
     </row>
     <row r="126" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A126" s="283"/>
-      <c r="B126" s="287" t="s">
+      <c r="A126" s="292"/>
+      <c r="B126" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="C126" s="294">
+      <c r="C126" s="303">
         <v>4</v>
       </c>
       <c r="D126" s="7">
@@ -6000,14 +6045,14 @@
         <f t="shared" si="7"/>
         <v>96000</v>
       </c>
-      <c r="F126" s="291"/>
+      <c r="F126" s="300"/>
     </row>
     <row r="127" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A127" s="283"/>
-      <c r="B127" s="287" t="s">
+      <c r="A127" s="292"/>
+      <c r="B127" s="296" t="s">
         <v>32</v>
       </c>
-      <c r="C127" s="294">
+      <c r="C127" s="303">
         <v>1</v>
       </c>
       <c r="D127" s="7">
@@ -6017,14 +6062,14 @@
         <f t="shared" si="7"/>
         <v>49000</v>
       </c>
-      <c r="F127" s="291"/>
+      <c r="F127" s="300"/>
     </row>
     <row r="128" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A128" s="284"/>
-      <c r="B128" s="287" t="s">
+      <c r="A128" s="293"/>
+      <c r="B128" s="296" t="s">
         <v>15</v>
       </c>
-      <c r="C128" s="294">
+      <c r="C128" s="303">
         <v>2</v>
       </c>
       <c r="D128" s="7">
@@ -6034,16 +6079,16 @@
         <f t="shared" si="7"/>
         <v>80000</v>
       </c>
-      <c r="F128" s="295"/>
+      <c r="F128" s="304"/>
     </row>
     <row r="129" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A129" s="288">
+      <c r="A129" s="297">
         <v>46007</v>
       </c>
-      <c r="B129" s="287" t="s">
+      <c r="B129" s="296" t="s">
         <v>7</v>
       </c>
-      <c r="C129" s="294">
+      <c r="C129" s="303">
         <v>3</v>
       </c>
       <c r="D129" s="7">
@@ -6053,19 +6098,19 @@
         <f t="shared" si="7"/>
         <v>210000</v>
       </c>
-      <c r="F129" s="298">
+      <c r="F129" s="310">
         <f>SUM(E129)</f>
         <v>210000</v>
       </c>
     </row>
     <row r="130" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A130" s="280">
+      <c r="A130" s="289">
         <v>46008</v>
       </c>
-      <c r="B130" s="287" t="s">
+      <c r="B130" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="C130" s="294">
+      <c r="C130" s="303">
         <v>3</v>
       </c>
       <c r="D130" s="7">
@@ -6075,17 +6120,17 @@
         <f t="shared" si="7"/>
         <v>60000</v>
       </c>
-      <c r="F130" s="290">
+      <c r="F130" s="299">
         <f>SUM(E130:E138)</f>
         <v>586000</v>
       </c>
     </row>
     <row r="131" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A131" s="283"/>
-      <c r="B131" s="287" t="s">
+      <c r="A131" s="292"/>
+      <c r="B131" s="296" t="s">
         <v>7</v>
       </c>
-      <c r="C131" s="294">
+      <c r="C131" s="303">
         <v>3</v>
       </c>
       <c r="D131" s="7">
@@ -6095,14 +6140,14 @@
         <f t="shared" si="7"/>
         <v>210000</v>
       </c>
-      <c r="F131" s="291"/>
+      <c r="F131" s="300"/>
     </row>
     <row r="132" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A132" s="283"/>
-      <c r="B132" s="287" t="s">
+      <c r="A132" s="292"/>
+      <c r="B132" s="296" t="s">
         <v>8</v>
       </c>
-      <c r="C132" s="294">
+      <c r="C132" s="303">
         <v>4</v>
       </c>
       <c r="D132" s="7">
@@ -6112,14 +6157,14 @@
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F132" s="291"/>
+      <c r="F132" s="300"/>
     </row>
     <row r="133" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A133" s="283"/>
-      <c r="B133" s="287" t="s">
+      <c r="A133" s="292"/>
+      <c r="B133" s="296" t="s">
         <v>36</v>
       </c>
-      <c r="C133" s="294">
+      <c r="C133" s="303">
         <v>2</v>
       </c>
       <c r="D133" s="7">
@@ -6129,14 +6174,14 @@
         <f t="shared" si="7"/>
         <v>96000</v>
       </c>
-      <c r="F133" s="291"/>
+      <c r="F133" s="300"/>
     </row>
     <row r="134" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A134" s="283"/>
-      <c r="B134" s="287" t="s">
+      <c r="A134" s="292"/>
+      <c r="B134" s="296" t="s">
         <v>10</v>
       </c>
-      <c r="C134" s="294">
+      <c r="C134" s="303">
         <v>0.3</v>
       </c>
       <c r="D134" s="7">
@@ -6145,14 +6190,14 @@
       <c r="E134" s="7">
         <v>5000</v>
       </c>
-      <c r="F134" s="291"/>
+      <c r="F134" s="300"/>
     </row>
     <row r="135" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A135" s="283"/>
-      <c r="B135" s="287" t="s">
+      <c r="A135" s="292"/>
+      <c r="B135" s="296" t="s">
         <v>22</v>
       </c>
-      <c r="C135" s="294">
+      <c r="C135" s="303">
         <v>0.5</v>
       </c>
       <c r="D135" s="7">
@@ -6162,14 +6207,14 @@
         <f t="shared" si="7"/>
         <v>15000</v>
       </c>
-      <c r="F135" s="291"/>
+      <c r="F135" s="300"/>
     </row>
     <row r="136" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A136" s="283"/>
-      <c r="B136" s="287" t="s">
+      <c r="A136" s="292"/>
+      <c r="B136" s="296" t="s">
         <v>13</v>
       </c>
-      <c r="C136" s="294">
+      <c r="C136" s="303">
         <v>1</v>
       </c>
       <c r="D136" s="7">
@@ -6179,14 +6224,14 @@
         <f t="shared" si="7"/>
         <v>15000</v>
       </c>
-      <c r="F136" s="291"/>
+      <c r="F136" s="300"/>
     </row>
     <row r="137" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A137" s="283"/>
-      <c r="B137" s="287" t="s">
+      <c r="A137" s="292"/>
+      <c r="B137" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="C137" s="294">
+      <c r="C137" s="303">
         <v>4</v>
       </c>
       <c r="D137" s="7">
@@ -6196,14 +6241,14 @@
         <f t="shared" si="7"/>
         <v>96000</v>
       </c>
-      <c r="F137" s="291"/>
+      <c r="F137" s="300"/>
     </row>
     <row r="138" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A138" s="284"/>
-      <c r="B138" s="287" t="s">
+      <c r="A138" s="293"/>
+      <c r="B138" s="296" t="s">
         <v>32</v>
       </c>
-      <c r="C138" s="294">
+      <c r="C138" s="303">
         <v>1</v>
       </c>
       <c r="D138" s="7">
@@ -6213,16 +6258,16 @@
         <f t="shared" si="7"/>
         <v>49000</v>
       </c>
-      <c r="F138" s="292"/>
+      <c r="F138" s="301"/>
     </row>
     <row r="139" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A139" s="280">
+      <c r="A139" s="289">
         <v>46009</v>
       </c>
-      <c r="B139" s="287" t="s">
+      <c r="B139" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="C139" s="294">
+      <c r="C139" s="303">
         <v>5</v>
       </c>
       <c r="D139" s="7">
@@ -6232,17 +6277,17 @@
         <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="F139" s="290">
+      <c r="F139" s="299">
         <f>SUM(E139:E146)</f>
         <v>343000</v>
       </c>
     </row>
     <row r="140" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A140" s="283"/>
-      <c r="B140" s="287" t="s">
+      <c r="A140" s="292"/>
+      <c r="B140" s="296" t="s">
         <v>7</v>
       </c>
-      <c r="C140" s="294">
+      <c r="C140" s="303">
         <v>1</v>
       </c>
       <c r="D140" s="7">
@@ -6252,14 +6297,14 @@
         <f t="shared" si="7"/>
         <v>70000</v>
       </c>
-      <c r="F140" s="291"/>
+      <c r="F140" s="300"/>
     </row>
     <row r="141" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A141" s="283"/>
-      <c r="B141" s="287" t="s">
+      <c r="A141" s="292"/>
+      <c r="B141" s="296" t="s">
         <v>8</v>
       </c>
-      <c r="C141" s="294">
+      <c r="C141" s="303">
         <v>4</v>
       </c>
       <c r="D141" s="7">
@@ -6269,14 +6314,14 @@
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F141" s="291"/>
+      <c r="F141" s="300"/>
     </row>
     <row r="142" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A142" s="283"/>
-      <c r="B142" s="287" t="s">
+      <c r="A142" s="292"/>
+      <c r="B142" s="296" t="s">
         <v>36</v>
       </c>
-      <c r="C142" s="294">
+      <c r="C142" s="303">
         <v>1</v>
       </c>
       <c r="D142" s="7">
@@ -6286,14 +6331,14 @@
         <f t="shared" si="7"/>
         <v>48000</v>
       </c>
-      <c r="F142" s="291"/>
+      <c r="F142" s="300"/>
     </row>
     <row r="143" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A143" s="283"/>
-      <c r="B143" s="287" t="s">
+      <c r="A143" s="292"/>
+      <c r="B143" s="296" t="s">
         <v>10</v>
       </c>
-      <c r="C143" s="294">
+      <c r="C143" s="303">
         <v>0.3</v>
       </c>
       <c r="D143" s="7">
@@ -6302,14 +6347,14 @@
       <c r="E143" s="7">
         <v>5000</v>
       </c>
-      <c r="F143" s="291"/>
+      <c r="F143" s="300"/>
     </row>
     <row r="144" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A144" s="283"/>
-      <c r="B144" s="287" t="s">
+      <c r="A144" s="292"/>
+      <c r="B144" s="296" t="s">
         <v>22</v>
       </c>
-      <c r="C144" s="294">
+      <c r="C144" s="303">
         <v>0.5</v>
       </c>
       <c r="D144" s="7">
@@ -6319,14 +6364,14 @@
         <f t="shared" si="7"/>
         <v>15000</v>
       </c>
-      <c r="F144" s="291"/>
+      <c r="F144" s="300"/>
     </row>
     <row r="145" s="244" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A145" s="283"/>
-      <c r="B145" s="287" t="s">
+      <c r="A145" s="292"/>
+      <c r="B145" s="296" t="s">
         <v>13</v>
       </c>
-      <c r="C145" s="294">
+      <c r="C145" s="303">
         <v>1.15</v>
       </c>
       <c r="D145" s="7">
@@ -6335,15 +6380,15 @@
       <c r="E145" s="7">
         <v>17000</v>
       </c>
-      <c r="F145" s="291"/>
-      <c r="G145" s="271"/>
+      <c r="F145" s="300"/>
+      <c r="G145" s="277"/>
     </row>
     <row r="146" s="244" customFormat="1" spans="1:6">
-      <c r="A146" s="284"/>
-      <c r="B146" s="287" t="s">
+      <c r="A146" s="293"/>
+      <c r="B146" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="C146" s="294">
+      <c r="C146" s="303">
         <v>2</v>
       </c>
       <c r="D146" s="7">
@@ -6353,16 +6398,16 @@
         <f t="shared" si="7"/>
         <v>48000</v>
       </c>
-      <c r="F146" s="292"/>
+      <c r="F146" s="301"/>
     </row>
     <row r="147" s="244" customFormat="1" spans="1:6">
-      <c r="A147" s="280">
+      <c r="A147" s="289">
         <v>46010</v>
       </c>
-      <c r="B147" s="287" t="s">
+      <c r="B147" s="296" t="s">
         <v>8</v>
       </c>
-      <c r="C147" s="294">
+      <c r="C147" s="303">
         <v>5</v>
       </c>
       <c r="D147" s="7">
@@ -6372,17 +6417,17 @@
         <f t="shared" si="7"/>
         <v>50000</v>
       </c>
-      <c r="F147" s="290">
+      <c r="F147" s="299">
         <f>SUM(E147:E156)</f>
         <v>620000</v>
       </c>
     </row>
     <row r="148" s="244" customFormat="1" spans="1:6">
-      <c r="A148" s="283"/>
-      <c r="B148" s="287" t="s">
+      <c r="A148" s="292"/>
+      <c r="B148" s="296" t="s">
         <v>7</v>
       </c>
-      <c r="C148" s="294">
+      <c r="C148" s="303">
         <v>1</v>
       </c>
       <c r="D148" s="7">
@@ -6392,14 +6437,14 @@
         <f t="shared" si="7"/>
         <v>70000</v>
       </c>
-      <c r="F148" s="291"/>
+      <c r="F148" s="300"/>
     </row>
     <row r="149" s="244" customFormat="1" spans="1:6">
-      <c r="A149" s="283"/>
-      <c r="B149" s="287" t="s">
+      <c r="A149" s="292"/>
+      <c r="B149" s="296" t="s">
         <v>6</v>
       </c>
-      <c r="C149" s="294">
+      <c r="C149" s="303">
         <v>3</v>
       </c>
       <c r="D149" s="7">
@@ -6409,14 +6454,14 @@
         <f t="shared" si="7"/>
         <v>60000</v>
       </c>
-      <c r="F149" s="291"/>
+      <c r="F149" s="300"/>
     </row>
     <row r="150" s="244" customFormat="1" spans="1:6">
-      <c r="A150" s="283"/>
-      <c r="B150" s="296" t="s">
+      <c r="A150" s="292"/>
+      <c r="B150" s="305" t="s">
         <v>11</v>
       </c>
-      <c r="C150" s="297">
+      <c r="C150" s="306">
         <v>1</v>
       </c>
       <c r="D150" s="134">
@@ -6426,14 +6471,14 @@
         <f t="shared" si="7"/>
         <v>38000</v>
       </c>
-      <c r="F150" s="291"/>
+      <c r="F150" s="300"/>
     </row>
     <row r="151" s="244" customFormat="1" spans="1:6">
-      <c r="A151" s="283"/>
-      <c r="B151" s="287" t="s">
+      <c r="A151" s="292"/>
+      <c r="B151" s="296" t="s">
         <v>24</v>
       </c>
-      <c r="C151" s="294">
+      <c r="C151" s="303">
         <v>9.26</v>
       </c>
       <c r="D151" s="7">
@@ -6442,14 +6487,14 @@
       <c r="E151" s="7">
         <v>139000</v>
       </c>
-      <c r="F151" s="291"/>
+      <c r="F151" s="300"/>
     </row>
     <row r="152" s="244" customFormat="1" spans="1:6">
-      <c r="A152" s="283"/>
-      <c r="B152" s="287" t="s">
+      <c r="A152" s="292"/>
+      <c r="B152" s="296" t="s">
         <v>26</v>
       </c>
-      <c r="C152" s="294">
+      <c r="C152" s="303">
         <v>0.2</v>
       </c>
       <c r="D152" s="7">
@@ -6459,14 +6504,14 @@
         <f t="shared" si="7"/>
         <v>16000</v>
       </c>
-      <c r="F152" s="291"/>
+      <c r="F152" s="300"/>
     </row>
     <row r="153" s="244" customFormat="1" spans="1:6">
-      <c r="A153" s="283"/>
-      <c r="B153" s="287" t="s">
+      <c r="A153" s="292"/>
+      <c r="B153" s="296" t="s">
         <v>25</v>
       </c>
-      <c r="C153" s="294">
+      <c r="C153" s="303">
         <v>0.3</v>
       </c>
       <c r="D153" s="7">
@@ -6475,14 +6520,14 @@
       <c r="E153" s="7">
         <v>11000</v>
       </c>
-      <c r="F153" s="291"/>
+      <c r="F153" s="300"/>
     </row>
     <row r="154" s="244" customFormat="1" spans="1:6">
-      <c r="A154" s="283"/>
-      <c r="B154" s="287" t="s">
+      <c r="A154" s="292"/>
+      <c r="B154" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="C154" s="294">
+      <c r="C154" s="303">
         <v>4</v>
       </c>
       <c r="D154" s="7">
@@ -6492,14 +6537,14 @@
         <f t="shared" si="7"/>
         <v>96000</v>
       </c>
-      <c r="F154" s="291"/>
+      <c r="F154" s="300"/>
     </row>
     <row r="155" s="244" customFormat="1" spans="1:6">
-      <c r="A155" s="283"/>
-      <c r="B155" s="287" t="s">
+      <c r="A155" s="292"/>
+      <c r="B155" s="296" t="s">
         <v>28</v>
       </c>
-      <c r="C155" s="294">
+      <c r="C155" s="303">
         <v>2</v>
       </c>
       <c r="D155" s="7">
@@ -6509,14 +6554,14 @@
         <f t="shared" ref="E155:E218" si="8">SUM(C155*D155)</f>
         <v>80000</v>
       </c>
-      <c r="F155" s="291"/>
+      <c r="F155" s="300"/>
     </row>
     <row r="156" s="244" customFormat="1" spans="1:6">
-      <c r="A156" s="284"/>
-      <c r="B156" s="287" t="s">
+      <c r="A156" s="293"/>
+      <c r="B156" s="296" t="s">
         <v>21</v>
       </c>
-      <c r="C156" s="294">
+      <c r="C156" s="303">
         <v>3</v>
       </c>
       <c r="D156" s="262">
@@ -6526,1600 +6571,1619 @@
         <f t="shared" si="8"/>
         <v>60000</v>
       </c>
-      <c r="F156" s="292"/>
+      <c r="F156" s="301"/>
     </row>
     <row r="157" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A157" s="288"/>
-      <c r="B157" s="287"/>
-      <c r="C157" s="294"/>
-      <c r="D157" s="7"/>
+      <c r="A157" s="307">
+        <v>46011</v>
+      </c>
+      <c r="B157" s="296" t="s">
+        <v>10</v>
+      </c>
+      <c r="C157" s="303">
+        <v>0.5</v>
+      </c>
+      <c r="D157" s="7">
+        <v>15000</v>
+      </c>
       <c r="E157" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F157" s="298">
-        <f>SUM(E157:E164)</f>
-        <v>0</v>
+        <v>8000</v>
+      </c>
+      <c r="F157" s="311">
+        <f>SUM(E157:E159)</f>
+        <v>119000</v>
       </c>
     </row>
     <row r="158" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A158" s="288"/>
-      <c r="B158" s="287"/>
-      <c r="C158" s="294"/>
-      <c r="D158" s="7"/>
+      <c r="A158" s="308"/>
+      <c r="B158" s="296" t="s">
+        <v>22</v>
+      </c>
+      <c r="C158" s="303">
+        <v>0.5</v>
+      </c>
+      <c r="D158" s="7">
+        <v>30000</v>
+      </c>
       <c r="E158" s="7">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F158" s="298"/>
+        <v>15000</v>
+      </c>
+      <c r="F158" s="312"/>
     </row>
     <row r="159" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A159" s="288"/>
-      <c r="B159" s="287"/>
-      <c r="C159" s="294"/>
-      <c r="D159" s="7"/>
+      <c r="A159" s="309"/>
+      <c r="B159" s="296" t="s">
+        <v>14</v>
+      </c>
+      <c r="C159" s="303">
+        <v>4</v>
+      </c>
+      <c r="D159" s="7">
+        <v>24000</v>
+      </c>
       <c r="E159" s="7">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F159" s="298"/>
+        <v>96000</v>
+      </c>
+      <c r="F159" s="313"/>
     </row>
     <row r="160" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A160" s="288"/>
-      <c r="B160" s="287"/>
-      <c r="C160" s="294"/>
+      <c r="A160" s="297"/>
+      <c r="B160" s="296"/>
+      <c r="C160" s="303"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F160" s="298"/>
+      <c r="F160" s="310"/>
     </row>
     <row r="161" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A161" s="288"/>
-      <c r="B161" s="287"/>
-      <c r="C161" s="294"/>
+      <c r="A161" s="297"/>
+      <c r="B161" s="296"/>
+      <c r="C161" s="303"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F161" s="298"/>
+      <c r="F161" s="310"/>
     </row>
     <row r="162" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A162" s="288"/>
-      <c r="B162" s="287"/>
-      <c r="C162" s="294"/>
+      <c r="A162" s="297"/>
+      <c r="B162" s="296"/>
+      <c r="C162" s="303"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F162" s="298"/>
+      <c r="F162" s="310"/>
     </row>
     <row r="163" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A163" s="288"/>
-      <c r="B163" s="287"/>
-      <c r="C163" s="294"/>
+      <c r="A163" s="297"/>
+      <c r="B163" s="296"/>
+      <c r="C163" s="303"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F163" s="298"/>
+      <c r="F163" s="310"/>
     </row>
     <row r="164" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A164" s="288"/>
-      <c r="B164" s="287"/>
-      <c r="C164" s="294"/>
+      <c r="A164" s="297"/>
+      <c r="B164" s="296"/>
+      <c r="C164" s="303"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F164" s="298"/>
+      <c r="F164" s="310"/>
     </row>
     <row r="165" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A165" s="288"/>
-      <c r="B165" s="287"/>
-      <c r="C165" s="294"/>
+      <c r="A165" s="297"/>
+      <c r="B165" s="296"/>
+      <c r="C165" s="303"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F165" s="298">
+      <c r="F165" s="310">
         <f>SUM(E165:E171)</f>
         <v>0</v>
       </c>
     </row>
     <row r="166" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A166" s="288"/>
-      <c r="B166" s="287"/>
-      <c r="C166" s="294"/>
+      <c r="A166" s="297"/>
+      <c r="B166" s="296"/>
+      <c r="C166" s="303"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F166" s="298"/>
+      <c r="F166" s="310"/>
     </row>
     <row r="167" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A167" s="288"/>
-      <c r="B167" s="287"/>
-      <c r="C167" s="294"/>
+      <c r="A167" s="297"/>
+      <c r="B167" s="296"/>
+      <c r="C167" s="303"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F167" s="298"/>
+      <c r="F167" s="310"/>
     </row>
     <row r="168" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A168" s="288"/>
-      <c r="B168" s="287"/>
-      <c r="C168" s="294"/>
+      <c r="A168" s="297"/>
+      <c r="B168" s="296"/>
+      <c r="C168" s="303"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F168" s="298"/>
+      <c r="F168" s="310"/>
     </row>
     <row r="169" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A169" s="288"/>
-      <c r="B169" s="287"/>
-      <c r="C169" s="294"/>
+      <c r="A169" s="297"/>
+      <c r="B169" s="296"/>
+      <c r="C169" s="303"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F169" s="298"/>
+      <c r="F169" s="310"/>
     </row>
     <row r="170" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A170" s="288"/>
-      <c r="B170" s="287"/>
-      <c r="C170" s="294"/>
+      <c r="A170" s="297"/>
+      <c r="B170" s="296"/>
+      <c r="C170" s="303"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F170" s="298"/>
+      <c r="F170" s="310"/>
     </row>
     <row r="171" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A171" s="288"/>
-      <c r="B171" s="287"/>
-      <c r="C171" s="294"/>
+      <c r="A171" s="297"/>
+      <c r="B171" s="296"/>
+      <c r="C171" s="303"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F171" s="298"/>
+      <c r="F171" s="310"/>
     </row>
     <row r="172" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A172" s="288"/>
-      <c r="B172" s="287"/>
-      <c r="C172" s="294"/>
+      <c r="A172" s="297"/>
+      <c r="B172" s="296"/>
+      <c r="C172" s="303"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F172" s="298">
+      <c r="F172" s="310">
         <f>SUM(E172:E181)</f>
         <v>0</v>
       </c>
     </row>
     <row r="173" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A173" s="288"/>
-      <c r="B173" s="287"/>
-      <c r="C173" s="294"/>
+      <c r="A173" s="297"/>
+      <c r="B173" s="296"/>
+      <c r="C173" s="303"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F173" s="298"/>
+      <c r="F173" s="310"/>
     </row>
     <row r="174" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A174" s="288"/>
-      <c r="B174" s="287"/>
-      <c r="C174" s="294"/>
+      <c r="A174" s="297"/>
+      <c r="B174" s="296"/>
+      <c r="C174" s="303"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F174" s="298"/>
+      <c r="F174" s="310"/>
     </row>
     <row r="175" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A175" s="288"/>
-      <c r="B175" s="287"/>
-      <c r="C175" s="294"/>
+      <c r="A175" s="297"/>
+      <c r="B175" s="296"/>
+      <c r="C175" s="303"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F175" s="298"/>
+      <c r="F175" s="310"/>
     </row>
     <row r="176" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A176" s="288"/>
-      <c r="B176" s="287"/>
-      <c r="C176" s="294"/>
+      <c r="A176" s="297"/>
+      <c r="B176" s="296"/>
+      <c r="C176" s="303"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F176" s="298"/>
+      <c r="F176" s="310"/>
     </row>
     <row r="177" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A177" s="288"/>
-      <c r="B177" s="287"/>
-      <c r="C177" s="294"/>
+      <c r="A177" s="297"/>
+      <c r="B177" s="296"/>
+      <c r="C177" s="303"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F177" s="298"/>
+      <c r="F177" s="310"/>
     </row>
     <row r="178" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A178" s="288"/>
-      <c r="B178" s="287"/>
-      <c r="C178" s="294"/>
+      <c r="A178" s="297"/>
+      <c r="B178" s="296"/>
+      <c r="C178" s="303"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F178" s="298"/>
+      <c r="F178" s="310"/>
     </row>
     <row r="179" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A179" s="288"/>
-      <c r="B179" s="287"/>
-      <c r="C179" s="294"/>
+      <c r="A179" s="297"/>
+      <c r="B179" s="296"/>
+      <c r="C179" s="303"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F179" s="298"/>
+      <c r="F179" s="310"/>
     </row>
     <row r="180" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A180" s="288"/>
-      <c r="B180" s="287"/>
-      <c r="C180" s="294"/>
+      <c r="A180" s="297"/>
+      <c r="B180" s="296"/>
+      <c r="C180" s="303"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F180" s="298"/>
+      <c r="F180" s="310"/>
     </row>
     <row r="181" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A181" s="288"/>
-      <c r="B181" s="287"/>
-      <c r="C181" s="294"/>
+      <c r="A181" s="297"/>
+      <c r="B181" s="296"/>
+      <c r="C181" s="303"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F181" s="298"/>
+      <c r="F181" s="310"/>
     </row>
     <row r="182" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A182" s="288"/>
-      <c r="B182" s="287"/>
-      <c r="C182" s="294"/>
+      <c r="A182" s="297"/>
+      <c r="B182" s="296"/>
+      <c r="C182" s="303"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F182" s="298">
+      <c r="F182" s="310">
         <f>SUM(E182:E195)</f>
         <v>0</v>
       </c>
     </row>
     <row r="183" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A183" s="288"/>
-      <c r="B183" s="287"/>
-      <c r="C183" s="294"/>
+      <c r="A183" s="297"/>
+      <c r="B183" s="296"/>
+      <c r="C183" s="303"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F183" s="298"/>
+      <c r="F183" s="310"/>
     </row>
     <row r="184" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A184" s="288"/>
-      <c r="B184" s="287"/>
-      <c r="C184" s="294"/>
+      <c r="A184" s="297"/>
+      <c r="B184" s="296"/>
+      <c r="C184" s="303"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F184" s="298"/>
+      <c r="F184" s="310"/>
     </row>
     <row r="185" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A185" s="288"/>
-      <c r="B185" s="287"/>
-      <c r="C185" s="294"/>
+      <c r="A185" s="297"/>
+      <c r="B185" s="296"/>
+      <c r="C185" s="303"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F185" s="298"/>
+      <c r="F185" s="310"/>
     </row>
     <row r="186" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A186" s="288"/>
-      <c r="B186" s="287"/>
-      <c r="C186" s="294"/>
+      <c r="A186" s="297"/>
+      <c r="B186" s="296"/>
+      <c r="C186" s="303"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F186" s="298"/>
+      <c r="F186" s="310"/>
     </row>
     <row r="187" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A187" s="288"/>
-      <c r="B187" s="287"/>
-      <c r="C187" s="294"/>
+      <c r="A187" s="297"/>
+      <c r="B187" s="296"/>
+      <c r="C187" s="303"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F187" s="298"/>
+      <c r="F187" s="310"/>
     </row>
     <row r="188" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A188" s="288"/>
-      <c r="B188" s="287"/>
-      <c r="C188" s="294"/>
+      <c r="A188" s="297"/>
+      <c r="B188" s="296"/>
+      <c r="C188" s="303"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F188" s="298"/>
+      <c r="F188" s="310"/>
     </row>
     <row r="189" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A189" s="288"/>
-      <c r="B189" s="287"/>
-      <c r="C189" s="294"/>
+      <c r="A189" s="297"/>
+      <c r="B189" s="296"/>
+      <c r="C189" s="303"/>
       <c r="D189" s="7"/>
       <c r="E189" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F189" s="298"/>
+      <c r="F189" s="310"/>
     </row>
     <row r="190" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A190" s="288"/>
-      <c r="B190" s="287"/>
-      <c r="C190" s="294"/>
+      <c r="A190" s="297"/>
+      <c r="B190" s="296"/>
+      <c r="C190" s="303"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F190" s="298"/>
+      <c r="F190" s="310"/>
     </row>
     <row r="191" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A191" s="288"/>
-      <c r="B191" s="287"/>
-      <c r="C191" s="294"/>
+      <c r="A191" s="297"/>
+      <c r="B191" s="296"/>
+      <c r="C191" s="303"/>
       <c r="D191" s="7"/>
       <c r="E191" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F191" s="298"/>
+      <c r="F191" s="310"/>
     </row>
     <row r="192" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A192" s="288"/>
-      <c r="B192" s="287"/>
-      <c r="C192" s="294"/>
+      <c r="A192" s="297"/>
+      <c r="B192" s="296"/>
+      <c r="C192" s="303"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F192" s="298"/>
+      <c r="F192" s="310"/>
     </row>
     <row r="193" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A193" s="288"/>
-      <c r="B193" s="287"/>
-      <c r="C193" s="294"/>
+      <c r="A193" s="297"/>
+      <c r="B193" s="296"/>
+      <c r="C193" s="303"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F193" s="298"/>
+      <c r="F193" s="310"/>
     </row>
     <row r="194" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A194" s="288"/>
-      <c r="B194" s="287"/>
-      <c r="C194" s="294"/>
+      <c r="A194" s="297"/>
+      <c r="B194" s="296"/>
+      <c r="C194" s="303"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F194" s="298"/>
+      <c r="F194" s="310"/>
     </row>
     <row r="195" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A195" s="288"/>
-      <c r="B195" s="287"/>
-      <c r="C195" s="294"/>
+      <c r="A195" s="297"/>
+      <c r="B195" s="296"/>
+      <c r="C195" s="303"/>
       <c r="D195" s="7"/>
       <c r="E195" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F195" s="298"/>
+      <c r="F195" s="310"/>
     </row>
     <row r="196" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A196" s="288"/>
-      <c r="B196" s="287"/>
-      <c r="C196" s="294"/>
+      <c r="A196" s="297"/>
+      <c r="B196" s="296"/>
+      <c r="C196" s="303"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F196" s="298">
+      <c r="F196" s="310">
         <f>SUM(E196)</f>
         <v>0</v>
       </c>
     </row>
     <row r="197" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A197" s="288"/>
-      <c r="B197" s="287"/>
-      <c r="C197" s="294"/>
+      <c r="A197" s="297"/>
+      <c r="B197" s="296"/>
+      <c r="C197" s="303"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F197" s="298">
+      <c r="F197" s="310">
         <f>SUM(E197:E212)</f>
         <v>0</v>
       </c>
     </row>
     <row r="198" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A198" s="288"/>
-      <c r="B198" s="287"/>
-      <c r="C198" s="294"/>
+      <c r="A198" s="297"/>
+      <c r="B198" s="296"/>
+      <c r="C198" s="303"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F198" s="298"/>
+      <c r="F198" s="310"/>
     </row>
     <row r="199" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A199" s="288"/>
-      <c r="B199" s="287"/>
-      <c r="C199" s="294"/>
+      <c r="A199" s="297"/>
+      <c r="B199" s="296"/>
+      <c r="C199" s="303"/>
       <c r="D199" s="7"/>
       <c r="E199" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F199" s="298"/>
+      <c r="F199" s="310"/>
     </row>
     <row r="200" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A200" s="288"/>
-      <c r="B200" s="287"/>
-      <c r="C200" s="294"/>
+      <c r="A200" s="297"/>
+      <c r="B200" s="296"/>
+      <c r="C200" s="303"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F200" s="298"/>
+      <c r="F200" s="310"/>
     </row>
     <row r="201" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A201" s="288"/>
-      <c r="B201" s="287"/>
-      <c r="C201" s="294"/>
+      <c r="A201" s="297"/>
+      <c r="B201" s="296"/>
+      <c r="C201" s="303"/>
       <c r="D201" s="7"/>
       <c r="E201" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F201" s="298"/>
+      <c r="F201" s="310"/>
     </row>
     <row r="202" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A202" s="288"/>
-      <c r="B202" s="287"/>
-      <c r="C202" s="294"/>
+      <c r="A202" s="297"/>
+      <c r="B202" s="296"/>
+      <c r="C202" s="303"/>
       <c r="D202" s="7"/>
       <c r="E202" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F202" s="298"/>
+      <c r="F202" s="310"/>
     </row>
     <row r="203" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A203" s="288"/>
-      <c r="B203" s="287"/>
-      <c r="C203" s="294"/>
+      <c r="A203" s="297"/>
+      <c r="B203" s="296"/>
+      <c r="C203" s="303"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F203" s="298"/>
+      <c r="F203" s="310"/>
     </row>
     <row r="204" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A204" s="288"/>
-      <c r="B204" s="287"/>
-      <c r="C204" s="294"/>
+      <c r="A204" s="297"/>
+      <c r="B204" s="296"/>
+      <c r="C204" s="303"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F204" s="298"/>
+      <c r="F204" s="310"/>
     </row>
     <row r="205" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A205" s="288"/>
-      <c r="B205" s="287"/>
-      <c r="C205" s="294"/>
+      <c r="A205" s="297"/>
+      <c r="B205" s="296"/>
+      <c r="C205" s="303"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F205" s="298"/>
+      <c r="F205" s="310"/>
     </row>
     <row r="206" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A206" s="288"/>
-      <c r="B206" s="287"/>
-      <c r="C206" s="294"/>
+      <c r="A206" s="297"/>
+      <c r="B206" s="296"/>
+      <c r="C206" s="303"/>
       <c r="D206" s="7"/>
       <c r="E206" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F206" s="298"/>
+      <c r="F206" s="310"/>
     </row>
     <row r="207" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A207" s="288"/>
-      <c r="B207" s="287"/>
-      <c r="C207" s="294"/>
+      <c r="A207" s="297"/>
+      <c r="B207" s="296"/>
+      <c r="C207" s="303"/>
       <c r="D207" s="7"/>
       <c r="E207" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F207" s="298"/>
+      <c r="F207" s="310"/>
     </row>
     <row r="208" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A208" s="288"/>
-      <c r="B208" s="287"/>
-      <c r="C208" s="294"/>
+      <c r="A208" s="297"/>
+      <c r="B208" s="296"/>
+      <c r="C208" s="303"/>
       <c r="D208" s="7"/>
       <c r="E208" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F208" s="298"/>
+      <c r="F208" s="310"/>
     </row>
     <row r="209" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A209" s="288"/>
-      <c r="B209" s="287"/>
-      <c r="C209" s="294"/>
+      <c r="A209" s="297"/>
+      <c r="B209" s="296"/>
+      <c r="C209" s="303"/>
       <c r="D209" s="7"/>
       <c r="E209" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F209" s="298"/>
+      <c r="F209" s="310"/>
     </row>
     <row r="210" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A210" s="288"/>
-      <c r="B210" s="287"/>
-      <c r="C210" s="294"/>
+      <c r="A210" s="297"/>
+      <c r="B210" s="296"/>
+      <c r="C210" s="303"/>
       <c r="D210" s="7"/>
       <c r="E210" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F210" s="298"/>
+      <c r="F210" s="310"/>
     </row>
     <row r="211" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A211" s="288"/>
-      <c r="B211" s="296"/>
-      <c r="C211" s="297"/>
+      <c r="A211" s="297"/>
+      <c r="B211" s="305"/>
+      <c r="C211" s="306"/>
       <c r="D211" s="134"/>
       <c r="E211" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F211" s="298"/>
+      <c r="F211" s="310"/>
     </row>
     <row r="212" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A212" s="288"/>
-      <c r="B212" s="287"/>
-      <c r="C212" s="294"/>
+      <c r="A212" s="297"/>
+      <c r="B212" s="296"/>
+      <c r="C212" s="303"/>
       <c r="D212" s="7"/>
       <c r="E212" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F212" s="298"/>
+      <c r="F212" s="310"/>
     </row>
     <row r="213" s="244" customFormat="1" spans="1:6">
-      <c r="A213" s="280"/>
-      <c r="B213" s="287"/>
-      <c r="C213" s="294"/>
+      <c r="A213" s="289"/>
+      <c r="B213" s="296"/>
+      <c r="C213" s="303"/>
       <c r="D213" s="7"/>
       <c r="E213" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F213" s="290">
+      <c r="F213" s="299">
         <f>SUM(E213:E220)</f>
         <v>0</v>
       </c>
     </row>
     <row r="214" s="244" customFormat="1" spans="1:6">
-      <c r="A214" s="283"/>
-      <c r="B214" s="287"/>
-      <c r="C214" s="294"/>
+      <c r="A214" s="292"/>
+      <c r="B214" s="296"/>
+      <c r="C214" s="303"/>
       <c r="D214" s="7"/>
       <c r="E214" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F214" s="291"/>
+      <c r="F214" s="300"/>
     </row>
     <row r="215" s="244" customFormat="1" spans="1:6">
-      <c r="A215" s="283"/>
-      <c r="B215" s="287"/>
-      <c r="C215" s="294"/>
+      <c r="A215" s="292"/>
+      <c r="B215" s="296"/>
+      <c r="C215" s="303"/>
       <c r="D215" s="7"/>
       <c r="E215" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F215" s="291"/>
+      <c r="F215" s="300"/>
     </row>
     <row r="216" s="244" customFormat="1" spans="1:6">
-      <c r="A216" s="283"/>
-      <c r="B216" s="287"/>
-      <c r="C216" s="294"/>
+      <c r="A216" s="292"/>
+      <c r="B216" s="296"/>
+      <c r="C216" s="303"/>
       <c r="D216" s="7"/>
       <c r="E216" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F216" s="291"/>
+      <c r="F216" s="300"/>
     </row>
     <row r="217" s="244" customFormat="1" spans="1:6">
-      <c r="A217" s="283"/>
-      <c r="B217" s="287"/>
-      <c r="C217" s="294"/>
+      <c r="A217" s="292"/>
+      <c r="B217" s="296"/>
+      <c r="C217" s="303"/>
       <c r="D217" s="7"/>
       <c r="E217" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F217" s="291"/>
+      <c r="F217" s="300"/>
     </row>
     <row r="218" s="244" customFormat="1" spans="1:6">
-      <c r="A218" s="283"/>
-      <c r="B218" s="287"/>
-      <c r="C218" s="294"/>
+      <c r="A218" s="292"/>
+      <c r="B218" s="296"/>
+      <c r="C218" s="303"/>
       <c r="D218" s="7"/>
       <c r="E218" s="7">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F218" s="291"/>
+      <c r="F218" s="300"/>
     </row>
     <row r="219" s="244" customFormat="1" spans="1:6">
-      <c r="A219" s="283"/>
-      <c r="B219" s="287"/>
-      <c r="C219" s="294"/>
+      <c r="A219" s="292"/>
+      <c r="B219" s="296"/>
+      <c r="C219" s="303"/>
       <c r="D219" s="7"/>
       <c r="E219" s="7">
         <f t="shared" ref="E219:E282" si="9">SUM(C219*D219)</f>
         <v>0</v>
       </c>
-      <c r="F219" s="291"/>
+      <c r="F219" s="300"/>
     </row>
     <row r="220" s="244" customFormat="1" spans="1:6">
-      <c r="A220" s="284"/>
-      <c r="B220" s="287"/>
-      <c r="C220" s="294"/>
+      <c r="A220" s="293"/>
+      <c r="B220" s="296"/>
+      <c r="C220" s="303"/>
       <c r="D220" s="7"/>
       <c r="E220" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F220" s="292"/>
+      <c r="F220" s="301"/>
     </row>
     <row r="221" s="244" customFormat="1" spans="1:6">
-      <c r="A221" s="280"/>
-      <c r="B221" s="287"/>
-      <c r="C221" s="294"/>
+      <c r="A221" s="289"/>
+      <c r="B221" s="296"/>
+      <c r="C221" s="303"/>
       <c r="D221" s="7"/>
       <c r="E221" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F221" s="290">
+      <c r="F221" s="299">
         <f>SUM(E221:E232)</f>
         <v>0</v>
       </c>
     </row>
     <row r="222" s="244" customFormat="1" spans="1:6">
-      <c r="A222" s="283"/>
-      <c r="B222" s="287"/>
-      <c r="C222" s="294"/>
+      <c r="A222" s="292"/>
+      <c r="B222" s="296"/>
+      <c r="C222" s="303"/>
       <c r="D222" s="7"/>
       <c r="E222" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F222" s="291"/>
+      <c r="F222" s="300"/>
     </row>
     <row r="223" s="244" customFormat="1" spans="1:6">
-      <c r="A223" s="283"/>
-      <c r="B223" s="287"/>
-      <c r="C223" s="294"/>
+      <c r="A223" s="292"/>
+      <c r="B223" s="296"/>
+      <c r="C223" s="303"/>
       <c r="D223" s="7"/>
       <c r="E223" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F223" s="291"/>
+      <c r="F223" s="300"/>
     </row>
     <row r="224" s="244" customFormat="1" spans="1:6">
-      <c r="A224" s="283"/>
-      <c r="B224" s="287"/>
-      <c r="C224" s="294"/>
+      <c r="A224" s="292"/>
+      <c r="B224" s="296"/>
+      <c r="C224" s="303"/>
       <c r="D224" s="7"/>
       <c r="E224" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F224" s="291"/>
+      <c r="F224" s="300"/>
     </row>
     <row r="225" s="244" customFormat="1" spans="1:6">
-      <c r="A225" s="283"/>
-      <c r="B225" s="287"/>
-      <c r="C225" s="294"/>
+      <c r="A225" s="292"/>
+      <c r="B225" s="296"/>
+      <c r="C225" s="303"/>
       <c r="D225" s="7"/>
       <c r="E225" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F225" s="291"/>
+      <c r="F225" s="300"/>
     </row>
     <row r="226" s="244" customFormat="1" spans="1:6">
-      <c r="A226" s="283"/>
-      <c r="B226" s="287"/>
-      <c r="C226" s="294"/>
+      <c r="A226" s="292"/>
+      <c r="B226" s="296"/>
+      <c r="C226" s="303"/>
       <c r="D226" s="7"/>
       <c r="E226" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F226" s="291"/>
+      <c r="F226" s="300"/>
     </row>
     <row r="227" s="244" customFormat="1" spans="1:6">
-      <c r="A227" s="283"/>
-      <c r="B227" s="287"/>
-      <c r="C227" s="294"/>
+      <c r="A227" s="292"/>
+      <c r="B227" s="296"/>
+      <c r="C227" s="303"/>
       <c r="D227" s="7"/>
       <c r="E227" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F227" s="291"/>
+      <c r="F227" s="300"/>
     </row>
     <row r="228" s="244" customFormat="1" spans="1:6">
-      <c r="A228" s="283"/>
-      <c r="B228" s="287"/>
-      <c r="C228" s="294"/>
+      <c r="A228" s="292"/>
+      <c r="B228" s="296"/>
+      <c r="C228" s="303"/>
       <c r="D228" s="7"/>
       <c r="E228" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F228" s="291"/>
+      <c r="F228" s="300"/>
     </row>
     <row r="229" s="244" customFormat="1" spans="1:6">
-      <c r="A229" s="283"/>
-      <c r="B229" s="287"/>
-      <c r="C229" s="294"/>
+      <c r="A229" s="292"/>
+      <c r="B229" s="296"/>
+      <c r="C229" s="303"/>
       <c r="D229" s="7"/>
       <c r="E229" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F229" s="291"/>
+      <c r="F229" s="300"/>
     </row>
     <row r="230" s="244" customFormat="1" spans="1:6">
-      <c r="A230" s="283"/>
-      <c r="B230" s="287"/>
-      <c r="C230" s="294"/>
+      <c r="A230" s="292"/>
+      <c r="B230" s="296"/>
+      <c r="C230" s="303"/>
       <c r="D230" s="7"/>
       <c r="E230" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F230" s="291"/>
+      <c r="F230" s="300"/>
     </row>
     <row r="231" s="244" customFormat="1" spans="1:6">
-      <c r="A231" s="283"/>
-      <c r="B231" s="287"/>
-      <c r="C231" s="294"/>
+      <c r="A231" s="292"/>
+      <c r="B231" s="296"/>
+      <c r="C231" s="303"/>
       <c r="D231" s="7"/>
       <c r="E231" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F231" s="291"/>
+      <c r="F231" s="300"/>
     </row>
     <row r="232" s="244" customFormat="1" spans="1:6">
-      <c r="A232" s="284"/>
-      <c r="B232" s="287"/>
-      <c r="C232" s="294"/>
+      <c r="A232" s="293"/>
+      <c r="B232" s="296"/>
+      <c r="C232" s="303"/>
       <c r="D232" s="7"/>
       <c r="E232" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F232" s="292"/>
+      <c r="F232" s="301"/>
     </row>
     <row r="233" s="244" customFormat="1" spans="1:6">
-      <c r="A233" s="280"/>
-      <c r="B233" s="287"/>
-      <c r="C233" s="294"/>
+      <c r="A233" s="289"/>
+      <c r="B233" s="296"/>
+      <c r="C233" s="303"/>
       <c r="D233" s="7"/>
       <c r="E233" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F233" s="290">
+      <c r="F233" s="299">
         <f>SUM(E233:E241)</f>
         <v>0</v>
       </c>
     </row>
     <row r="234" s="244" customFormat="1" spans="1:6">
-      <c r="A234" s="283"/>
-      <c r="B234" s="287"/>
-      <c r="C234" s="294"/>
+      <c r="A234" s="292"/>
+      <c r="B234" s="296"/>
+      <c r="C234" s="303"/>
       <c r="D234" s="7"/>
       <c r="E234" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F234" s="291"/>
+      <c r="F234" s="300"/>
     </row>
     <row r="235" s="244" customFormat="1" spans="1:6">
-      <c r="A235" s="283"/>
-      <c r="B235" s="287"/>
-      <c r="C235" s="294"/>
+      <c r="A235" s="292"/>
+      <c r="B235" s="296"/>
+      <c r="C235" s="303"/>
       <c r="D235" s="7"/>
       <c r="E235" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F235" s="291"/>
+      <c r="F235" s="300"/>
     </row>
     <row r="236" s="244" customFormat="1" spans="1:6">
-      <c r="A236" s="283"/>
-      <c r="B236" s="287"/>
-      <c r="C236" s="294"/>
+      <c r="A236" s="292"/>
+      <c r="B236" s="296"/>
+      <c r="C236" s="303"/>
       <c r="D236" s="7"/>
       <c r="E236" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F236" s="291"/>
+      <c r="F236" s="300"/>
     </row>
     <row r="237" s="244" customFormat="1" spans="1:6">
-      <c r="A237" s="283"/>
-      <c r="B237" s="287"/>
-      <c r="C237" s="294"/>
+      <c r="A237" s="292"/>
+      <c r="B237" s="296"/>
+      <c r="C237" s="303"/>
       <c r="D237" s="7"/>
       <c r="E237" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F237" s="291"/>
+      <c r="F237" s="300"/>
     </row>
     <row r="238" s="244" customFormat="1" spans="1:6">
-      <c r="A238" s="283"/>
-      <c r="B238" s="287"/>
-      <c r="C238" s="294"/>
+      <c r="A238" s="292"/>
+      <c r="B238" s="296"/>
+      <c r="C238" s="303"/>
       <c r="D238" s="7"/>
       <c r="E238" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F238" s="291"/>
+      <c r="F238" s="300"/>
     </row>
     <row r="239" s="244" customFormat="1" spans="1:6">
-      <c r="A239" s="283"/>
-      <c r="B239" s="287"/>
-      <c r="C239" s="294"/>
+      <c r="A239" s="292"/>
+      <c r="B239" s="296"/>
+      <c r="C239" s="303"/>
       <c r="D239" s="7"/>
       <c r="E239" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F239" s="291"/>
+      <c r="F239" s="300"/>
     </row>
     <row r="240" s="244" customFormat="1" spans="1:6">
-      <c r="A240" s="283"/>
-      <c r="B240" s="287"/>
-      <c r="C240" s="294"/>
+      <c r="A240" s="292"/>
+      <c r="B240" s="296"/>
+      <c r="C240" s="303"/>
       <c r="D240" s="7"/>
       <c r="E240" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F240" s="291"/>
+      <c r="F240" s="300"/>
     </row>
     <row r="241" s="244" customFormat="1" spans="1:6">
-      <c r="A241" s="284"/>
-      <c r="B241" s="287"/>
-      <c r="C241" s="294"/>
+      <c r="A241" s="293"/>
+      <c r="B241" s="296"/>
+      <c r="C241" s="303"/>
       <c r="D241" s="7"/>
       <c r="E241" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F241" s="292"/>
+      <c r="F241" s="301"/>
     </row>
     <row r="242" s="244" customFormat="1" spans="1:6">
-      <c r="A242" s="280"/>
-      <c r="B242" s="287"/>
-      <c r="C242" s="294"/>
+      <c r="A242" s="289"/>
+      <c r="B242" s="296"/>
+      <c r="C242" s="303"/>
       <c r="D242" s="7"/>
       <c r="E242" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F242" s="290">
+      <c r="F242" s="299">
         <f>SUM(E242:E252)</f>
         <v>0</v>
       </c>
     </row>
     <row r="243" s="244" customFormat="1" spans="1:6">
-      <c r="A243" s="283"/>
-      <c r="B243" s="287"/>
-      <c r="C243" s="294"/>
+      <c r="A243" s="292"/>
+      <c r="B243" s="296"/>
+      <c r="C243" s="303"/>
       <c r="D243" s="7"/>
       <c r="E243" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F243" s="291"/>
+      <c r="F243" s="300"/>
     </row>
     <row r="244" s="244" customFormat="1" spans="1:6">
-      <c r="A244" s="283"/>
-      <c r="B244" s="287"/>
-      <c r="C244" s="294"/>
+      <c r="A244" s="292"/>
+      <c r="B244" s="296"/>
+      <c r="C244" s="303"/>
       <c r="D244" s="7"/>
       <c r="E244" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F244" s="291"/>
+      <c r="F244" s="300"/>
     </row>
     <row r="245" s="244" customFormat="1" spans="1:6">
-      <c r="A245" s="283"/>
-      <c r="B245" s="287"/>
-      <c r="C245" s="294"/>
+      <c r="A245" s="292"/>
+      <c r="B245" s="296"/>
+      <c r="C245" s="303"/>
       <c r="D245" s="7"/>
       <c r="E245" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F245" s="291"/>
+      <c r="F245" s="300"/>
     </row>
     <row r="246" s="244" customFormat="1" spans="1:6">
-      <c r="A246" s="283"/>
-      <c r="B246" s="287"/>
-      <c r="C246" s="294"/>
+      <c r="A246" s="292"/>
+      <c r="B246" s="296"/>
+      <c r="C246" s="303"/>
       <c r="D246" s="7"/>
       <c r="E246" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F246" s="291"/>
+      <c r="F246" s="300"/>
     </row>
     <row r="247" s="244" customFormat="1" spans="1:6">
-      <c r="A247" s="283"/>
-      <c r="B247" s="287"/>
-      <c r="C247" s="294"/>
+      <c r="A247" s="292"/>
+      <c r="B247" s="296"/>
+      <c r="C247" s="303"/>
       <c r="D247" s="7"/>
       <c r="E247" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F247" s="291"/>
+      <c r="F247" s="300"/>
     </row>
     <row r="248" s="244" customFormat="1" spans="1:6">
-      <c r="A248" s="283"/>
-      <c r="B248" s="287"/>
-      <c r="C248" s="294"/>
+      <c r="A248" s="292"/>
+      <c r="B248" s="296"/>
+      <c r="C248" s="303"/>
       <c r="D248" s="7"/>
       <c r="E248" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F248" s="291"/>
+      <c r="F248" s="300"/>
     </row>
     <row r="249" s="244" customFormat="1" spans="1:6">
-      <c r="A249" s="283"/>
-      <c r="B249" s="287"/>
-      <c r="C249" s="294"/>
+      <c r="A249" s="292"/>
+      <c r="B249" s="296"/>
+      <c r="C249" s="303"/>
       <c r="D249" s="7"/>
       <c r="E249" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F249" s="291"/>
+      <c r="F249" s="300"/>
     </row>
     <row r="250" s="244" customFormat="1" spans="1:6">
-      <c r="A250" s="283"/>
-      <c r="B250" s="287"/>
-      <c r="C250" s="294"/>
+      <c r="A250" s="292"/>
+      <c r="B250" s="296"/>
+      <c r="C250" s="303"/>
       <c r="D250" s="7"/>
       <c r="E250" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F250" s="291"/>
+      <c r="F250" s="300"/>
     </row>
     <row r="251" s="244" customFormat="1" spans="1:6">
-      <c r="A251" s="283"/>
-      <c r="B251" s="287"/>
-      <c r="C251" s="294"/>
+      <c r="A251" s="292"/>
+      <c r="B251" s="296"/>
+      <c r="C251" s="303"/>
       <c r="D251" s="7"/>
       <c r="E251" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F251" s="291"/>
+      <c r="F251" s="300"/>
     </row>
     <row r="252" s="244" customFormat="1" spans="1:6">
-      <c r="A252" s="284"/>
-      <c r="B252" s="287"/>
-      <c r="C252" s="294"/>
+      <c r="A252" s="293"/>
+      <c r="B252" s="296"/>
+      <c r="C252" s="303"/>
       <c r="D252" s="7"/>
       <c r="E252" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F252" s="292"/>
+      <c r="F252" s="301"/>
     </row>
     <row r="253" s="244" customFormat="1" spans="1:6">
-      <c r="A253" s="280"/>
-      <c r="B253" s="287"/>
-      <c r="C253" s="294"/>
+      <c r="A253" s="289"/>
+      <c r="B253" s="296"/>
+      <c r="C253" s="303"/>
       <c r="D253" s="7"/>
       <c r="E253" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F253" s="290">
+      <c r="F253" s="299">
         <f>SUM(E253:E263)</f>
         <v>0</v>
       </c>
     </row>
     <row r="254" s="244" customFormat="1" spans="1:6">
-      <c r="A254" s="283"/>
-      <c r="B254" s="287"/>
-      <c r="C254" s="294"/>
+      <c r="A254" s="292"/>
+      <c r="B254" s="296"/>
+      <c r="C254" s="303"/>
       <c r="D254" s="7"/>
       <c r="E254" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F254" s="291"/>
+      <c r="F254" s="300"/>
     </row>
     <row r="255" s="244" customFormat="1" spans="1:6">
-      <c r="A255" s="283"/>
-      <c r="B255" s="287"/>
-      <c r="C255" s="294"/>
+      <c r="A255" s="292"/>
+      <c r="B255" s="296"/>
+      <c r="C255" s="303"/>
       <c r="D255" s="7"/>
       <c r="E255" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F255" s="291"/>
+      <c r="F255" s="300"/>
     </row>
     <row r="256" s="244" customFormat="1" spans="1:6">
-      <c r="A256" s="283"/>
-      <c r="B256" s="287"/>
-      <c r="C256" s="294"/>
+      <c r="A256" s="292"/>
+      <c r="B256" s="296"/>
+      <c r="C256" s="303"/>
       <c r="D256" s="7"/>
       <c r="E256" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F256" s="291"/>
+      <c r="F256" s="300"/>
     </row>
     <row r="257" s="244" customFormat="1" spans="1:6">
-      <c r="A257" s="283"/>
-      <c r="B257" s="287"/>
-      <c r="C257" s="294"/>
+      <c r="A257" s="292"/>
+      <c r="B257" s="296"/>
+      <c r="C257" s="303"/>
       <c r="D257" s="7"/>
       <c r="E257" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F257" s="291"/>
+      <c r="F257" s="300"/>
     </row>
     <row r="258" s="244" customFormat="1" spans="1:6">
-      <c r="A258" s="283"/>
-      <c r="B258" s="287"/>
-      <c r="C258" s="294"/>
+      <c r="A258" s="292"/>
+      <c r="B258" s="296"/>
+      <c r="C258" s="303"/>
       <c r="D258" s="7"/>
       <c r="E258" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F258" s="291"/>
+      <c r="F258" s="300"/>
     </row>
     <row r="259" s="244" customFormat="1" spans="1:6">
-      <c r="A259" s="283"/>
-      <c r="B259" s="287"/>
-      <c r="C259" s="294"/>
+      <c r="A259" s="292"/>
+      <c r="B259" s="296"/>
+      <c r="C259" s="303"/>
       <c r="D259" s="7"/>
       <c r="E259" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F259" s="291"/>
+      <c r="F259" s="300"/>
     </row>
     <row r="260" s="244" customFormat="1" spans="1:6">
-      <c r="A260" s="283"/>
-      <c r="B260" s="287"/>
-      <c r="C260" s="294"/>
+      <c r="A260" s="292"/>
+      <c r="B260" s="296"/>
+      <c r="C260" s="303"/>
       <c r="D260" s="7"/>
       <c r="E260" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F260" s="291"/>
+      <c r="F260" s="300"/>
     </row>
     <row r="261" s="244" customFormat="1" spans="1:6">
-      <c r="A261" s="283"/>
-      <c r="B261" s="287"/>
-      <c r="C261" s="294"/>
+      <c r="A261" s="292"/>
+      <c r="B261" s="296"/>
+      <c r="C261" s="303"/>
       <c r="D261" s="7"/>
       <c r="E261" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F261" s="291"/>
+      <c r="F261" s="300"/>
     </row>
     <row r="262" s="244" customFormat="1" spans="1:6">
-      <c r="A262" s="283"/>
-      <c r="B262" s="287"/>
-      <c r="C262" s="294"/>
+      <c r="A262" s="292"/>
+      <c r="B262" s="296"/>
+      <c r="C262" s="303"/>
       <c r="D262" s="7"/>
       <c r="E262" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F262" s="291"/>
+      <c r="F262" s="300"/>
     </row>
     <row r="263" s="244" customFormat="1" spans="1:6">
-      <c r="A263" s="284"/>
-      <c r="B263" s="287"/>
-      <c r="C263" s="294"/>
+      <c r="A263" s="293"/>
+      <c r="B263" s="296"/>
+      <c r="C263" s="303"/>
       <c r="D263" s="7"/>
       <c r="E263" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F263" s="292"/>
+      <c r="F263" s="301"/>
     </row>
     <row r="264" s="244" customFormat="1" spans="1:6">
-      <c r="A264" s="280"/>
-      <c r="B264" s="287"/>
-      <c r="C264" s="294"/>
+      <c r="A264" s="289"/>
+      <c r="B264" s="296"/>
+      <c r="C264" s="303"/>
       <c r="D264" s="7"/>
       <c r="E264" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F264" s="290">
+      <c r="F264" s="299">
         <f>SUM(E264:E274)</f>
         <v>0</v>
       </c>
     </row>
     <row r="265" s="244" customFormat="1" spans="1:6">
-      <c r="A265" s="283"/>
-      <c r="B265" s="287"/>
-      <c r="C265" s="294"/>
+      <c r="A265" s="292"/>
+      <c r="B265" s="296"/>
+      <c r="C265" s="303"/>
       <c r="D265" s="7"/>
       <c r="E265" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F265" s="291"/>
+      <c r="F265" s="300"/>
     </row>
     <row r="266" s="244" customFormat="1" spans="1:6">
-      <c r="A266" s="283"/>
-      <c r="B266" s="287"/>
-      <c r="C266" s="294"/>
+      <c r="A266" s="292"/>
+      <c r="B266" s="296"/>
+      <c r="C266" s="303"/>
       <c r="D266" s="7"/>
       <c r="E266" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F266" s="291"/>
+      <c r="F266" s="300"/>
     </row>
     <row r="267" s="244" customFormat="1" spans="1:6">
-      <c r="A267" s="283"/>
-      <c r="B267" s="287"/>
-      <c r="C267" s="294"/>
+      <c r="A267" s="292"/>
+      <c r="B267" s="296"/>
+      <c r="C267" s="303"/>
       <c r="D267" s="7"/>
       <c r="E267" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F267" s="291"/>
+      <c r="F267" s="300"/>
     </row>
     <row r="268" s="244" customFormat="1" spans="1:6">
-      <c r="A268" s="283"/>
-      <c r="B268" s="287"/>
-      <c r="C268" s="294"/>
+      <c r="A268" s="292"/>
+      <c r="B268" s="296"/>
+      <c r="C268" s="303"/>
       <c r="D268" s="7"/>
       <c r="E268" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F268" s="291"/>
+      <c r="F268" s="300"/>
     </row>
     <row r="269" s="244" customFormat="1" spans="1:6">
-      <c r="A269" s="283"/>
-      <c r="B269" s="287"/>
-      <c r="C269" s="294"/>
+      <c r="A269" s="292"/>
+      <c r="B269" s="296"/>
+      <c r="C269" s="303"/>
       <c r="D269" s="7"/>
       <c r="E269" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F269" s="291"/>
+      <c r="F269" s="300"/>
     </row>
     <row r="270" s="244" customFormat="1" spans="1:6">
-      <c r="A270" s="283"/>
-      <c r="B270" s="287"/>
-      <c r="C270" s="294"/>
+      <c r="A270" s="292"/>
+      <c r="B270" s="296"/>
+      <c r="C270" s="303"/>
       <c r="D270" s="7"/>
       <c r="E270" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F270" s="291"/>
+      <c r="F270" s="300"/>
     </row>
     <row r="271" s="244" customFormat="1" spans="1:6">
-      <c r="A271" s="283"/>
-      <c r="B271" s="287"/>
-      <c r="C271" s="294"/>
+      <c r="A271" s="292"/>
+      <c r="B271" s="296"/>
+      <c r="C271" s="303"/>
       <c r="D271" s="7"/>
       <c r="E271" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F271" s="291"/>
+      <c r="F271" s="300"/>
     </row>
     <row r="272" s="244" customFormat="1" spans="1:6">
-      <c r="A272" s="283"/>
-      <c r="B272" s="287"/>
-      <c r="C272" s="294"/>
+      <c r="A272" s="292"/>
+      <c r="B272" s="296"/>
+      <c r="C272" s="303"/>
       <c r="D272" s="7"/>
       <c r="E272" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F272" s="291"/>
+      <c r="F272" s="300"/>
     </row>
     <row r="273" s="244" customFormat="1" spans="1:6">
-      <c r="A273" s="283"/>
-      <c r="B273" s="287"/>
-      <c r="C273" s="294"/>
+      <c r="A273" s="292"/>
+      <c r="B273" s="296"/>
+      <c r="C273" s="303"/>
       <c r="D273" s="7"/>
       <c r="E273" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F273" s="291"/>
+      <c r="F273" s="300"/>
     </row>
     <row r="274" s="244" customFormat="1" spans="1:6">
-      <c r="A274" s="284"/>
-      <c r="B274" s="287"/>
-      <c r="C274" s="294"/>
+      <c r="A274" s="293"/>
+      <c r="B274" s="296"/>
+      <c r="C274" s="303"/>
       <c r="D274" s="7"/>
       <c r="E274" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F274" s="292"/>
+      <c r="F274" s="301"/>
     </row>
     <row r="275" s="244" customFormat="1" spans="1:6">
-      <c r="A275" s="280"/>
-      <c r="B275" s="287"/>
-      <c r="C275" s="294"/>
+      <c r="A275" s="289"/>
+      <c r="B275" s="296"/>
+      <c r="C275" s="303"/>
       <c r="D275" s="7"/>
       <c r="E275" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F275" s="290">
+      <c r="F275" s="299">
         <f>SUM(E275:E284)</f>
         <v>0</v>
       </c>
     </row>
     <row r="276" s="244" customFormat="1" spans="1:6">
-      <c r="A276" s="283"/>
-      <c r="B276" s="287"/>
-      <c r="C276" s="294"/>
+      <c r="A276" s="292"/>
+      <c r="B276" s="296"/>
+      <c r="C276" s="303"/>
       <c r="D276" s="7"/>
       <c r="E276" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F276" s="291"/>
+      <c r="F276" s="300"/>
     </row>
     <row r="277" s="244" customFormat="1" spans="1:6">
-      <c r="A277" s="283"/>
-      <c r="B277" s="287"/>
-      <c r="C277" s="294"/>
+      <c r="A277" s="292"/>
+      <c r="B277" s="296"/>
+      <c r="C277" s="303"/>
       <c r="D277" s="7"/>
       <c r="E277" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F277" s="291"/>
+      <c r="F277" s="300"/>
     </row>
     <row r="278" s="244" customFormat="1" spans="1:6">
-      <c r="A278" s="283"/>
-      <c r="B278" s="287"/>
-      <c r="C278" s="294"/>
+      <c r="A278" s="292"/>
+      <c r="B278" s="296"/>
+      <c r="C278" s="303"/>
       <c r="D278" s="7"/>
       <c r="E278" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F278" s="291"/>
+      <c r="F278" s="300"/>
     </row>
     <row r="279" s="244" customFormat="1" spans="1:6">
-      <c r="A279" s="283"/>
-      <c r="B279" s="287"/>
-      <c r="C279" s="294"/>
+      <c r="A279" s="292"/>
+      <c r="B279" s="296"/>
+      <c r="C279" s="303"/>
       <c r="D279" s="7"/>
       <c r="E279" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F279" s="291"/>
+      <c r="F279" s="300"/>
     </row>
     <row r="280" s="244" customFormat="1" spans="1:6">
-      <c r="A280" s="283"/>
-      <c r="B280" s="287"/>
-      <c r="C280" s="294"/>
+      <c r="A280" s="292"/>
+      <c r="B280" s="296"/>
+      <c r="C280" s="303"/>
       <c r="D280" s="7"/>
       <c r="E280" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F280" s="291"/>
+      <c r="F280" s="300"/>
     </row>
     <row r="281" s="244" customFormat="1" spans="1:6">
-      <c r="A281" s="283"/>
-      <c r="B281" s="287"/>
-      <c r="C281" s="294"/>
+      <c r="A281" s="292"/>
+      <c r="B281" s="296"/>
+      <c r="C281" s="303"/>
       <c r="D281" s="7"/>
       <c r="E281" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F281" s="291"/>
+      <c r="F281" s="300"/>
     </row>
     <row r="282" s="244" customFormat="1" spans="1:6">
-      <c r="A282" s="283"/>
-      <c r="B282" s="287"/>
-      <c r="C282" s="294"/>
+      <c r="A282" s="292"/>
+      <c r="B282" s="296"/>
+      <c r="C282" s="303"/>
       <c r="D282" s="7"/>
       <c r="E282" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F282" s="291"/>
+      <c r="F282" s="300"/>
     </row>
     <row r="283" s="244" customFormat="1" spans="1:6">
-      <c r="A283" s="283"/>
-      <c r="B283" s="287"/>
-      <c r="C283" s="294"/>
+      <c r="A283" s="292"/>
+      <c r="B283" s="296"/>
+      <c r="C283" s="303"/>
       <c r="D283" s="7"/>
       <c r="E283" s="7">
         <f t="shared" ref="E283:E296" si="10">SUM(C283*D283)</f>
         <v>0</v>
       </c>
-      <c r="F283" s="291"/>
+      <c r="F283" s="300"/>
     </row>
     <row r="284" s="244" customFormat="1" spans="1:6">
-      <c r="A284" s="284"/>
-      <c r="B284" s="287"/>
-      <c r="C284" s="294"/>
+      <c r="A284" s="293"/>
+      <c r="B284" s="296"/>
+      <c r="C284" s="303"/>
       <c r="D284" s="7"/>
       <c r="E284" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F284" s="292"/>
+      <c r="F284" s="301"/>
     </row>
     <row r="285" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A285" s="288"/>
-      <c r="B285" s="287"/>
-      <c r="C285" s="294"/>
+      <c r="A285" s="297"/>
+      <c r="B285" s="296"/>
+      <c r="C285" s="303"/>
       <c r="D285" s="7"/>
       <c r="E285" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F285" s="298">
+      <c r="F285" s="310">
         <f>SUM(E285)</f>
         <v>0</v>
       </c>
     </row>
     <row r="286" s="244" customFormat="1" spans="1:6">
-      <c r="A286" s="280"/>
-      <c r="B286" s="287"/>
-      <c r="C286" s="294"/>
+      <c r="A286" s="289"/>
+      <c r="B286" s="296"/>
+      <c r="C286" s="303"/>
       <c r="D286" s="7"/>
       <c r="E286" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F286" s="290">
+      <c r="F286" s="299">
         <f>SUM(E286:E296)</f>
         <v>0</v>
       </c>
     </row>
     <row r="287" s="244" customFormat="1" spans="1:6">
-      <c r="A287" s="283"/>
-      <c r="B287" s="287"/>
-      <c r="C287" s="294"/>
+      <c r="A287" s="292"/>
+      <c r="B287" s="296"/>
+      <c r="C287" s="303"/>
       <c r="D287" s="7"/>
       <c r="E287" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F287" s="291"/>
+      <c r="F287" s="300"/>
     </row>
     <row r="288" s="244" customFormat="1" spans="1:6">
-      <c r="A288" s="283"/>
-      <c r="B288" s="287"/>
-      <c r="C288" s="294"/>
+      <c r="A288" s="292"/>
+      <c r="B288" s="296"/>
+      <c r="C288" s="303"/>
       <c r="D288" s="7"/>
       <c r="E288" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F288" s="291"/>
+      <c r="F288" s="300"/>
     </row>
     <row r="289" s="244" customFormat="1" spans="1:6">
-      <c r="A289" s="283"/>
-      <c r="B289" s="287"/>
-      <c r="C289" s="294"/>
+      <c r="A289" s="292"/>
+      <c r="B289" s="296"/>
+      <c r="C289" s="303"/>
       <c r="D289" s="7"/>
       <c r="E289" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F289" s="291"/>
+      <c r="F289" s="300"/>
     </row>
     <row r="290" s="244" customFormat="1" spans="1:6">
-      <c r="A290" s="283"/>
-      <c r="B290" s="287"/>
-      <c r="C290" s="294"/>
+      <c r="A290" s="292"/>
+      <c r="B290" s="296"/>
+      <c r="C290" s="303"/>
       <c r="D290" s="7"/>
       <c r="E290" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F290" s="291"/>
+      <c r="F290" s="300"/>
     </row>
     <row r="291" s="244" customFormat="1" spans="1:6">
-      <c r="A291" s="283"/>
-      <c r="B291" s="287"/>
-      <c r="C291" s="294"/>
+      <c r="A291" s="292"/>
+      <c r="B291" s="296"/>
+      <c r="C291" s="303"/>
       <c r="D291" s="7"/>
       <c r="E291" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F291" s="291"/>
+      <c r="F291" s="300"/>
     </row>
     <row r="292" s="244" customFormat="1" spans="1:6">
-      <c r="A292" s="283"/>
-      <c r="B292" s="287"/>
-      <c r="C292" s="294"/>
+      <c r="A292" s="292"/>
+      <c r="B292" s="296"/>
+      <c r="C292" s="303"/>
       <c r="D292" s="7"/>
       <c r="E292" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F292" s="291"/>
+      <c r="F292" s="300"/>
     </row>
     <row r="293" s="244" customFormat="1" spans="1:6">
-      <c r="A293" s="283"/>
-      <c r="B293" s="287"/>
-      <c r="C293" s="294"/>
+      <c r="A293" s="292"/>
+      <c r="B293" s="296"/>
+      <c r="C293" s="303"/>
       <c r="D293" s="7"/>
       <c r="E293" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F293" s="291"/>
+      <c r="F293" s="300"/>
     </row>
     <row r="294" s="244" customFormat="1" spans="1:6">
-      <c r="A294" s="283"/>
-      <c r="B294" s="287"/>
-      <c r="C294" s="294"/>
+      <c r="A294" s="292"/>
+      <c r="B294" s="296"/>
+      <c r="C294" s="303"/>
       <c r="D294" s="7"/>
       <c r="E294" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F294" s="291"/>
+      <c r="F294" s="300"/>
     </row>
     <row r="295" s="244" customFormat="1" spans="1:6">
-      <c r="A295" s="283"/>
-      <c r="B295" s="287"/>
-      <c r="C295" s="294"/>
+      <c r="A295" s="292"/>
+      <c r="B295" s="296"/>
+      <c r="C295" s="303"/>
       <c r="D295" s="7"/>
       <c r="E295" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F295" s="291"/>
+      <c r="F295" s="300"/>
     </row>
     <row r="296" s="244" customFormat="1" spans="1:6">
-      <c r="A296" s="284"/>
-      <c r="B296" s="287"/>
-      <c r="C296" s="294"/>
+      <c r="A296" s="293"/>
+      <c r="B296" s="296"/>
+      <c r="C296" s="303"/>
       <c r="D296" s="7"/>
       <c r="E296" s="7">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="F296" s="292"/>
+      <c r="F296" s="301"/>
     </row>
     <row r="297" s="244" customFormat="1" spans="1:6">
       <c r="A297" s="246"/>
       <c r="C297" s="245"/>
       <c r="E297" s="7"/>
-      <c r="F297" s="298">
+      <c r="F297" s="310">
         <f>SUM(F2:F296)</f>
-        <v>7223000</v>
+        <v>7342000</v>
       </c>
     </row>
     <row r="298" s="244" customFormat="1" spans="1:3">
@@ -8533,10 +8597,10 @@
     <row r="400" s="244" customFormat="1" spans="1:7">
       <c r="A400" s="246"/>
       <c r="C400" s="245"/>
-      <c r="G400" s="271"/>
+      <c r="G400" s="277"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="50">
     <mergeCell ref="A2:A12"/>
     <mergeCell ref="A13:A25"/>
     <mergeCell ref="A26:A34"/>
@@ -8553,6 +8617,7 @@
     <mergeCell ref="A130:A138"/>
     <mergeCell ref="A139:A146"/>
     <mergeCell ref="A147:A156"/>
+    <mergeCell ref="A157:A159"/>
     <mergeCell ref="A213:A220"/>
     <mergeCell ref="A221:A232"/>
     <mergeCell ref="A233:A241"/>
@@ -8577,6 +8642,7 @@
     <mergeCell ref="F130:F138"/>
     <mergeCell ref="F139:F146"/>
     <mergeCell ref="F147:F156"/>
+    <mergeCell ref="F157:F159"/>
     <mergeCell ref="F213:F220"/>
     <mergeCell ref="F221:F232"/>
     <mergeCell ref="F233:F241"/>
@@ -10033,7 +10099,7 @@
       </c>
       <c r="C2" s="5">
         <f>'BUK BUNGA (Groceries)'!F297</f>
-        <v>7223000</v>
+        <v>7342000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -10045,7 +10111,7 @@
       </c>
       <c r="C3" s="5">
         <f>'WARUNG EKA (Drinks, Etc)'!G117</f>
-        <v>6022000</v>
+        <v>6219000</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -10247,7 +10313,7 @@
       <c r="B20" s="9"/>
       <c r="C20" s="10">
         <f>SUM(C2:C13)</f>
-        <v>26883609.94</v>
+        <v>27199609.94</v>
       </c>
     </row>
   </sheetData>
@@ -11610,7 +11676,7 @@
         <v>20000</v>
       </c>
       <c r="G67" s="264"/>
-      <c r="H67" s="271"/>
+      <c r="H67" s="277"/>
     </row>
     <row r="68" s="244" customFormat="1" ht="17.6" spans="1:14">
       <c r="A68" s="206"/>
@@ -11629,13 +11695,13 @@
         <v>22000</v>
       </c>
       <c r="G68" s="266"/>
-      <c r="H68" s="271"/>
-      <c r="I68" s="274"/>
-      <c r="J68" s="275"/>
-      <c r="K68" s="276"/>
-      <c r="L68" s="277"/>
-      <c r="M68" s="277"/>
-      <c r="N68" s="279"/>
+      <c r="H68" s="277"/>
+      <c r="I68" s="283"/>
+      <c r="J68" s="284"/>
+      <c r="K68" s="285"/>
+      <c r="L68" s="286"/>
+      <c r="M68" s="286"/>
+      <c r="N68" s="288"/>
     </row>
     <row r="69" s="244" customFormat="1" ht="17.6" spans="1:14">
       <c r="A69" s="205">
@@ -11661,12 +11727,12 @@
         <f>SUM(F69:F72)</f>
         <v>209000</v>
       </c>
-      <c r="I69" s="278"/>
-      <c r="J69" s="275"/>
-      <c r="K69" s="276"/>
-      <c r="L69" s="277"/>
-      <c r="M69" s="277"/>
-      <c r="N69" s="277"/>
+      <c r="I69" s="287"/>
+      <c r="J69" s="284"/>
+      <c r="K69" s="285"/>
+      <c r="L69" s="286"/>
+      <c r="M69" s="286"/>
+      <c r="N69" s="286"/>
     </row>
     <row r="70" s="244" customFormat="1" ht="17.6" spans="1:14">
       <c r="A70" s="256"/>
@@ -11685,12 +11751,12 @@
         <v>20000</v>
       </c>
       <c r="G70" s="264"/>
-      <c r="I70" s="278"/>
-      <c r="J70" s="275"/>
-      <c r="K70" s="276"/>
-      <c r="L70" s="277"/>
-      <c r="M70" s="277"/>
-      <c r="N70" s="277"/>
+      <c r="I70" s="287"/>
+      <c r="J70" s="284"/>
+      <c r="K70" s="285"/>
+      <c r="L70" s="286"/>
+      <c r="M70" s="286"/>
+      <c r="N70" s="286"/>
     </row>
     <row r="71" s="244" customFormat="1" ht="17.6" spans="1:14">
       <c r="A71" s="256"/>
@@ -11709,12 +11775,12 @@
         <v>22000</v>
       </c>
       <c r="G71" s="264"/>
-      <c r="I71" s="278"/>
-      <c r="J71" s="275"/>
-      <c r="K71" s="276"/>
-      <c r="L71" s="277"/>
-      <c r="M71" s="277"/>
-      <c r="N71" s="277"/>
+      <c r="I71" s="287"/>
+      <c r="J71" s="284"/>
+      <c r="K71" s="285"/>
+      <c r="L71" s="286"/>
+      <c r="M71" s="286"/>
+      <c r="N71" s="286"/>
     </row>
     <row r="72" s="244" customFormat="1" spans="1:7">
       <c r="A72" s="206"/>
@@ -11735,44 +11801,69 @@
       <c r="G72" s="265"/>
     </row>
     <row r="73" s="244" customFormat="1" spans="1:7">
-      <c r="A73" s="203"/>
-      <c r="B73" s="268"/>
-      <c r="C73" s="267"/>
-      <c r="D73" s="115"/>
-      <c r="E73" s="262"/>
+      <c r="A73" s="268">
+        <v>75194</v>
+      </c>
+      <c r="B73" s="269">
+        <v>46011</v>
+      </c>
+      <c r="C73" s="267" t="s">
+        <v>44</v>
+      </c>
+      <c r="D73" s="115">
+        <v>1</v>
+      </c>
+      <c r="E73" s="262">
+        <v>22000</v>
+      </c>
       <c r="F73" s="262">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G73" s="272"/>
+        <v>22000</v>
+      </c>
+      <c r="G73" s="278">
+        <f>SUM(F73:F75)</f>
+        <v>197000</v>
+      </c>
     </row>
     <row r="74" s="244" customFormat="1" spans="1:7">
-      <c r="A74" s="203"/>
-      <c r="B74" s="268"/>
-      <c r="C74" s="267"/>
-      <c r="D74" s="115"/>
-      <c r="E74" s="262"/>
+      <c r="A74" s="270"/>
+      <c r="B74" s="271"/>
+      <c r="C74" s="267" t="s">
+        <v>42</v>
+      </c>
+      <c r="D74" s="115">
+        <v>5</v>
+      </c>
+      <c r="E74" s="262">
+        <v>10000</v>
+      </c>
       <c r="F74" s="262">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G74" s="272"/>
+        <v>50000</v>
+      </c>
+      <c r="G74" s="279"/>
     </row>
     <row r="75" s="244" customFormat="1" spans="1:7">
-      <c r="A75" s="203"/>
-      <c r="B75" s="268"/>
-      <c r="C75" s="267"/>
-      <c r="D75" s="115"/>
-      <c r="E75" s="262"/>
+      <c r="A75" s="272"/>
+      <c r="B75" s="273"/>
+      <c r="C75" s="267" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" s="115">
+        <v>1</v>
+      </c>
+      <c r="E75" s="262">
+        <v>125000</v>
+      </c>
       <c r="F75" s="262">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G75" s="272"/>
+        <v>125000</v>
+      </c>
+      <c r="G75" s="280"/>
     </row>
     <row r="76" s="244" customFormat="1" spans="1:7">
       <c r="A76" s="203"/>
-      <c r="B76" s="268"/>
+      <c r="B76" s="274"/>
       <c r="C76" s="267"/>
       <c r="D76" s="115"/>
       <c r="E76" s="262"/>
@@ -11780,11 +11871,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G76" s="272"/>
+      <c r="G76" s="281"/>
     </row>
     <row r="77" s="244" customFormat="1" spans="1:7">
       <c r="A77" s="203"/>
-      <c r="B77" s="268"/>
+      <c r="B77" s="274"/>
       <c r="C77" s="267"/>
       <c r="D77" s="115"/>
       <c r="E77" s="262"/>
@@ -11792,11 +11883,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G77" s="272"/>
+      <c r="G77" s="281"/>
     </row>
     <row r="78" s="244" customFormat="1" spans="1:7">
       <c r="A78" s="203"/>
-      <c r="B78" s="268"/>
+      <c r="B78" s="274"/>
       <c r="C78" s="267"/>
       <c r="D78" s="115"/>
       <c r="E78" s="262"/>
@@ -11804,11 +11895,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G78" s="272"/>
+      <c r="G78" s="281"/>
     </row>
     <row r="79" s="244" customFormat="1" spans="1:7">
       <c r="A79" s="203"/>
-      <c r="B79" s="268"/>
+      <c r="B79" s="274"/>
       <c r="C79" s="267"/>
       <c r="D79" s="115"/>
       <c r="E79" s="262"/>
@@ -11816,14 +11907,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G79" s="272">
+      <c r="G79" s="281">
         <f>SUM(F79:F83)</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" s="244" customFormat="1" spans="1:7">
       <c r="A80" s="203"/>
-      <c r="B80" s="268"/>
+      <c r="B80" s="274"/>
       <c r="C80" s="267"/>
       <c r="D80" s="115"/>
       <c r="E80" s="262"/>
@@ -11831,11 +11922,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G80" s="272"/>
+      <c r="G80" s="281"/>
     </row>
     <row r="81" s="244" customFormat="1" spans="1:7">
       <c r="A81" s="203"/>
-      <c r="B81" s="268"/>
+      <c r="B81" s="274"/>
       <c r="C81" s="267"/>
       <c r="D81" s="115"/>
       <c r="E81" s="262"/>
@@ -11843,11 +11934,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G81" s="272"/>
+      <c r="G81" s="281"/>
     </row>
     <row r="82" s="244" customFormat="1" spans="1:7">
       <c r="A82" s="203"/>
-      <c r="B82" s="268"/>
+      <c r="B82" s="274"/>
       <c r="C82" s="267"/>
       <c r="D82" s="115"/>
       <c r="E82" s="262"/>
@@ -11855,11 +11946,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G82" s="272"/>
+      <c r="G82" s="281"/>
     </row>
     <row r="83" s="244" customFormat="1" spans="1:7">
       <c r="A83" s="203"/>
-      <c r="B83" s="268"/>
+      <c r="B83" s="274"/>
       <c r="C83" s="267"/>
       <c r="D83" s="115"/>
       <c r="E83" s="262"/>
@@ -11867,11 +11958,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G83" s="272"/>
+      <c r="G83" s="281"/>
     </row>
     <row r="84" s="244" customFormat="1" spans="1:7">
       <c r="A84" s="203"/>
-      <c r="B84" s="268"/>
+      <c r="B84" s="274"/>
       <c r="C84" s="267"/>
       <c r="D84" s="115"/>
       <c r="E84" s="262"/>
@@ -11879,14 +11970,14 @@
         <f t="shared" ref="F84:F92" si="5">D84*E84</f>
         <v>0</v>
       </c>
-      <c r="G84" s="272">
+      <c r="G84" s="281">
         <f>SUM(F84:F89)</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" s="244" customFormat="1" spans="1:7">
       <c r="A85" s="203"/>
-      <c r="B85" s="268"/>
+      <c r="B85" s="274"/>
       <c r="C85" s="267"/>
       <c r="D85" s="115"/>
       <c r="E85" s="262"/>
@@ -11894,11 +11985,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G85" s="272"/>
+      <c r="G85" s="281"/>
     </row>
     <row r="86" s="244" customFormat="1" spans="1:7">
       <c r="A86" s="203"/>
-      <c r="B86" s="268"/>
+      <c r="B86" s="274"/>
       <c r="C86" s="267"/>
       <c r="D86" s="115"/>
       <c r="E86" s="262"/>
@@ -11906,11 +11997,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G86" s="272"/>
+      <c r="G86" s="281"/>
     </row>
     <row r="87" s="244" customFormat="1" spans="1:7">
       <c r="A87" s="203"/>
-      <c r="B87" s="268"/>
+      <c r="B87" s="274"/>
       <c r="C87" s="267"/>
       <c r="D87" s="115"/>
       <c r="E87" s="262"/>
@@ -11918,11 +12009,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G87" s="272"/>
+      <c r="G87" s="281"/>
     </row>
     <row r="88" s="244" customFormat="1" spans="1:7">
       <c r="A88" s="203"/>
-      <c r="B88" s="268"/>
+      <c r="B88" s="274"/>
       <c r="C88" s="267"/>
       <c r="D88" s="115"/>
       <c r="E88" s="262"/>
@@ -11930,11 +12021,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G88" s="272"/>
+      <c r="G88" s="281"/>
     </row>
     <row r="89" s="244" customFormat="1" spans="1:7">
       <c r="A89" s="203"/>
-      <c r="B89" s="268"/>
+      <c r="B89" s="274"/>
       <c r="C89" s="267"/>
       <c r="D89" s="115"/>
       <c r="E89" s="262"/>
@@ -11942,11 +12033,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G89" s="272"/>
+      <c r="G89" s="281"/>
     </row>
     <row r="90" s="244" customFormat="1" spans="1:7">
       <c r="A90" s="203"/>
-      <c r="B90" s="268"/>
+      <c r="B90" s="274"/>
       <c r="C90" s="267"/>
       <c r="D90" s="115"/>
       <c r="E90" s="262"/>
@@ -11954,14 +12045,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G90" s="272">
+      <c r="G90" s="281">
         <f>SUM(F90:F92)</f>
         <v>0</v>
       </c>
     </row>
     <row r="91" s="244" customFormat="1" spans="1:7">
       <c r="A91" s="203"/>
-      <c r="B91" s="268"/>
+      <c r="B91" s="274"/>
       <c r="C91" s="267"/>
       <c r="D91" s="115"/>
       <c r="E91" s="262"/>
@@ -11969,11 +12060,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G91" s="272"/>
+      <c r="G91" s="281"/>
     </row>
     <row r="92" s="244" customFormat="1" spans="1:7">
       <c r="A92" s="203"/>
-      <c r="B92" s="268"/>
+      <c r="B92" s="274"/>
       <c r="C92" s="267"/>
       <c r="D92" s="115"/>
       <c r="E92" s="262"/>
@@ -11981,11 +12072,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G92" s="272"/>
+      <c r="G92" s="281"/>
     </row>
     <row r="93" s="244" customFormat="1" spans="1:7">
       <c r="A93" s="203"/>
-      <c r="B93" s="268"/>
+      <c r="B93" s="274"/>
       <c r="C93" s="267"/>
       <c r="D93" s="115"/>
       <c r="E93" s="262"/>
@@ -11993,14 +12084,14 @@
         <f t="shared" ref="F93:F113" si="6">D93*E93</f>
         <v>0</v>
       </c>
-      <c r="G93" s="272">
+      <c r="G93" s="281">
         <f>SUM(F93:F98)</f>
         <v>0</v>
       </c>
     </row>
     <row r="94" s="244" customFormat="1" spans="1:7">
       <c r="A94" s="203"/>
-      <c r="B94" s="268"/>
+      <c r="B94" s="274"/>
       <c r="C94" s="267"/>
       <c r="D94" s="115"/>
       <c r="E94" s="262"/>
@@ -12008,11 +12099,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G94" s="272"/>
+      <c r="G94" s="281"/>
     </row>
     <row r="95" s="244" customFormat="1" spans="1:7">
       <c r="A95" s="203"/>
-      <c r="B95" s="268"/>
+      <c r="B95" s="274"/>
       <c r="C95" s="267"/>
       <c r="D95" s="115"/>
       <c r="E95" s="262"/>
@@ -12020,11 +12111,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G95" s="272"/>
+      <c r="G95" s="281"/>
     </row>
     <row r="96" s="244" customFormat="1" spans="1:7">
       <c r="A96" s="203"/>
-      <c r="B96" s="268"/>
+      <c r="B96" s="274"/>
       <c r="C96" s="267"/>
       <c r="D96" s="115"/>
       <c r="E96" s="262"/>
@@ -12032,11 +12123,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G96" s="272"/>
+      <c r="G96" s="281"/>
     </row>
     <row r="97" s="244" customFormat="1" spans="1:7">
       <c r="A97" s="203"/>
-      <c r="B97" s="268"/>
+      <c r="B97" s="274"/>
       <c r="C97" s="267"/>
       <c r="D97" s="115"/>
       <c r="E97" s="262"/>
@@ -12044,11 +12135,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G97" s="272"/>
+      <c r="G97" s="281"/>
     </row>
     <row r="98" s="244" customFormat="1" spans="1:7">
       <c r="A98" s="203"/>
-      <c r="B98" s="268"/>
+      <c r="B98" s="274"/>
       <c r="C98" s="267"/>
       <c r="D98" s="115"/>
       <c r="E98" s="262"/>
@@ -12056,11 +12147,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G98" s="272"/>
+      <c r="G98" s="281"/>
     </row>
     <row r="99" s="244" customFormat="1" spans="1:7">
       <c r="A99" s="203"/>
-      <c r="B99" s="268"/>
+      <c r="B99" s="274"/>
       <c r="C99" s="267"/>
       <c r="D99" s="115"/>
       <c r="E99" s="262"/>
@@ -12068,14 +12159,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G99" s="272">
+      <c r="G99" s="281">
         <f>SUM(F99:F103)</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" s="244" customFormat="1" spans="1:7">
       <c r="A100" s="203"/>
-      <c r="B100" s="268"/>
+      <c r="B100" s="274"/>
       <c r="C100" s="267"/>
       <c r="D100" s="115"/>
       <c r="E100" s="262"/>
@@ -12083,11 +12174,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G100" s="272"/>
+      <c r="G100" s="281"/>
     </row>
     <row r="101" s="244" customFormat="1" spans="1:7">
       <c r="A101" s="203"/>
-      <c r="B101" s="268"/>
+      <c r="B101" s="274"/>
       <c r="C101" s="267"/>
       <c r="D101" s="115"/>
       <c r="E101" s="262"/>
@@ -12095,11 +12186,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G101" s="272"/>
+      <c r="G101" s="281"/>
     </row>
     <row r="102" s="244" customFormat="1" spans="1:7">
       <c r="A102" s="203"/>
-      <c r="B102" s="268"/>
+      <c r="B102" s="274"/>
       <c r="C102" s="267"/>
       <c r="D102" s="115"/>
       <c r="E102" s="262"/>
@@ -12107,11 +12198,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G102" s="272"/>
+      <c r="G102" s="281"/>
     </row>
     <row r="103" s="244" customFormat="1" spans="1:7">
       <c r="A103" s="203"/>
-      <c r="B103" s="268"/>
+      <c r="B103" s="274"/>
       <c r="C103" s="267"/>
       <c r="D103" s="115"/>
       <c r="E103" s="262"/>
@@ -12119,11 +12210,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G103" s="272"/>
+      <c r="G103" s="281"/>
     </row>
     <row r="104" s="244" customFormat="1" spans="1:7">
       <c r="A104" s="203"/>
-      <c r="B104" s="268"/>
+      <c r="B104" s="274"/>
       <c r="C104" s="267"/>
       <c r="D104" s="115"/>
       <c r="E104" s="262"/>
@@ -12131,14 +12222,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G104" s="272">
+      <c r="G104" s="281">
         <f>SUM(F104:F109)</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" s="244" customFormat="1" spans="1:7">
       <c r="A105" s="203"/>
-      <c r="B105" s="268"/>
+      <c r="B105" s="274"/>
       <c r="C105" s="267"/>
       <c r="D105" s="115"/>
       <c r="E105" s="262"/>
@@ -12146,11 +12237,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G105" s="272"/>
+      <c r="G105" s="281"/>
     </row>
     <row r="106" s="244" customFormat="1" spans="1:7">
       <c r="A106" s="203"/>
-      <c r="B106" s="268"/>
+      <c r="B106" s="274"/>
       <c r="C106" s="267"/>
       <c r="D106" s="115"/>
       <c r="E106" s="262"/>
@@ -12158,11 +12249,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G106" s="272"/>
+      <c r="G106" s="281"/>
     </row>
     <row r="107" s="244" customFormat="1" spans="1:7">
       <c r="A107" s="203"/>
-      <c r="B107" s="268"/>
+      <c r="B107" s="274"/>
       <c r="C107" s="267"/>
       <c r="D107" s="115"/>
       <c r="E107" s="262"/>
@@ -12170,11 +12261,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G107" s="272"/>
+      <c r="G107" s="281"/>
     </row>
     <row r="108" s="244" customFormat="1" spans="1:7">
       <c r="A108" s="203"/>
-      <c r="B108" s="268"/>
+      <c r="B108" s="274"/>
       <c r="C108" s="267"/>
       <c r="D108" s="115"/>
       <c r="E108" s="262"/>
@@ -12182,11 +12273,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G108" s="272"/>
+      <c r="G108" s="281"/>
     </row>
     <row r="109" s="244" customFormat="1" spans="1:7">
       <c r="A109" s="203"/>
-      <c r="B109" s="268"/>
+      <c r="B109" s="274"/>
       <c r="C109" s="267"/>
       <c r="D109" s="115"/>
       <c r="E109" s="262"/>
@@ -12194,11 +12285,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G109" s="272"/>
+      <c r="G109" s="281"/>
     </row>
     <row r="110" s="244" customFormat="1" spans="1:7">
       <c r="A110" s="203"/>
-      <c r="B110" s="268"/>
+      <c r="B110" s="274"/>
       <c r="C110" s="267"/>
       <c r="D110" s="115"/>
       <c r="E110" s="262"/>
@@ -12206,14 +12297,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G110" s="272">
+      <c r="G110" s="281">
         <f>SUM(F110:F113)</f>
         <v>0</v>
       </c>
     </row>
     <row r="111" s="244" customFormat="1" spans="1:7">
       <c r="A111" s="203"/>
-      <c r="B111" s="268"/>
+      <c r="B111" s="274"/>
       <c r="C111" s="267"/>
       <c r="D111" s="115"/>
       <c r="E111" s="262"/>
@@ -12221,11 +12312,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G111" s="272"/>
+      <c r="G111" s="281"/>
     </row>
     <row r="112" s="244" customFormat="1" spans="1:7">
       <c r="A112" s="203"/>
-      <c r="B112" s="268"/>
+      <c r="B112" s="274"/>
       <c r="C112" s="267"/>
       <c r="D112" s="115"/>
       <c r="E112" s="262"/>
@@ -12233,11 +12324,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G112" s="272"/>
+      <c r="G112" s="281"/>
     </row>
     <row r="113" s="244" customFormat="1" spans="1:7">
       <c r="A113" s="203"/>
-      <c r="B113" s="268"/>
+      <c r="B113" s="274"/>
       <c r="C113" s="267"/>
       <c r="D113" s="115"/>
       <c r="E113" s="262"/>
@@ -12245,11 +12336,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G113" s="272"/>
+      <c r="G113" s="281"/>
     </row>
     <row r="114" s="244" customFormat="1" spans="1:7">
       <c r="A114" s="203"/>
-      <c r="B114" s="268"/>
+      <c r="B114" s="274"/>
       <c r="C114" s="267"/>
       <c r="D114" s="115"/>
       <c r="E114" s="262"/>
@@ -12257,14 +12348,14 @@
         <f t="shared" ref="F114:F116" si="7">D114*E114</f>
         <v>0</v>
       </c>
-      <c r="G114" s="272">
+      <c r="G114" s="281">
         <f>SUM(F114:F116)</f>
         <v>0</v>
       </c>
     </row>
     <row r="115" s="244" customFormat="1" spans="1:7">
       <c r="A115" s="203"/>
-      <c r="B115" s="268"/>
+      <c r="B115" s="274"/>
       <c r="C115" s="267"/>
       <c r="D115" s="115"/>
       <c r="E115" s="262"/>
@@ -12272,11 +12363,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G115" s="272"/>
+      <c r="G115" s="281"/>
     </row>
     <row r="116" s="244" customFormat="1" spans="1:7">
       <c r="A116" s="203"/>
-      <c r="B116" s="268"/>
+      <c r="B116" s="274"/>
       <c r="C116" s="267"/>
       <c r="D116" s="115"/>
       <c r="E116" s="262"/>
@@ -12284,20 +12375,20 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G116" s="272"/>
+      <c r="G116" s="281"/>
     </row>
     <row r="117" s="244" customFormat="1" spans="1:7">
-      <c r="A117" s="269" t="s">
+      <c r="A117" s="275" t="s">
         <v>54</v>
       </c>
       <c r="B117" s="122"/>
-      <c r="C117" s="270"/>
+      <c r="C117" s="276"/>
       <c r="D117" s="122"/>
       <c r="E117" s="122"/>
-      <c r="F117" s="273"/>
+      <c r="F117" s="282"/>
       <c r="G117" s="63">
         <f>SUM(G2:G116)</f>
-        <v>6022000</v>
+        <v>6219000</v>
       </c>
     </row>
     <row r="118" s="244" customFormat="1" spans="1:7">
@@ -12579,10 +12670,10 @@
       <c r="D152" s="248"/>
       <c r="E152" s="249"/>
       <c r="G152" s="245"/>
-      <c r="H152" s="271"/>
+      <c r="H152" s="277"/>
     </row>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="59">
     <mergeCell ref="A117:F117"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
@@ -12602,6 +12693,7 @@
     <mergeCell ref="A61:A65"/>
     <mergeCell ref="A66:A68"/>
     <mergeCell ref="A69:A72"/>
+    <mergeCell ref="A73:A75"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B13"/>
@@ -12620,6 +12712,7 @@
     <mergeCell ref="B61:B65"/>
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="B69:B72"/>
+    <mergeCell ref="B73:B75"/>
     <mergeCell ref="G2:G4"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="G8:G13"/>
@@ -12638,6 +12731,7 @@
     <mergeCell ref="G61:G65"/>
     <mergeCell ref="G66:G68"/>
     <mergeCell ref="G69:G72"/>
+    <mergeCell ref="G73:G75"/>
     <mergeCell ref="N69:N71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DECEMBER/DECEMBER BAR.xlsx
+++ b/DECEMBER/DECEMBER BAR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17000" activeTab="1"/>
+    <workbookView windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="BUK BUNGA (Groceries)" sheetId="28" r:id="rId1"/>
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="134">
   <si>
     <t>DATE</t>
   </si>
@@ -326,6 +326,15 @@
   </si>
   <si>
     <t>BEETROOT</t>
+  </si>
+  <si>
+    <t>PLASTIC WRAP</t>
+  </si>
+  <si>
+    <t>ORANGE</t>
+  </si>
+  <si>
+    <t>LEMON</t>
   </si>
   <si>
     <t>INV NO</t>
@@ -1624,7 +1633,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="314">
+  <cellXfs count="321">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2429,26 +2438,38 @@
     <xf numFmtId="0" fontId="27" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2459,13 +2480,25 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2546,26 +2579,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="30" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="30" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="30" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="30" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="30" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3109,6 +3139,45 @@
         <a:xfrm rot="16200000">
           <a:off x="5464810" y="8676005"/>
           <a:ext cx="1703070" cy="3107055"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>23495</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3154680</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>4065905</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="ID_7919D1CA34DD41EEA0BB89D6D8427B1F" descr="PHOTO-2025-12-21-23-16-41"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:srcRect l="3947" t="4108" r="5992" b="8804"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4751705" y="11123295"/>
+          <a:ext cx="3131185" cy="4043045"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3866,18 +3935,18 @@
       <c r="E1" s="252" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="298" t="s">
+      <c r="F1" s="306" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A2" s="289">
+      <c r="A2" s="297">
         <v>45995</v>
       </c>
-      <c r="B2" s="290" t="s">
+      <c r="B2" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="291">
+      <c r="C2" s="299">
         <v>5</v>
       </c>
       <c r="D2" s="7">
@@ -3887,17 +3956,17 @@
         <f t="shared" ref="E2:E15" si="0">SUM(C2*D2)</f>
         <v>100000</v>
       </c>
-      <c r="F2" s="299">
+      <c r="F2" s="307">
         <f>SUM(E2:E12)</f>
         <v>572000</v>
       </c>
     </row>
     <row r="3" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A3" s="292"/>
-      <c r="B3" s="290" t="s">
+      <c r="A3" s="300"/>
+      <c r="B3" s="298" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="291">
+      <c r="C3" s="299">
         <v>2</v>
       </c>
       <c r="D3" s="7">
@@ -3907,14 +3976,14 @@
         <f t="shared" si="0"/>
         <v>140000</v>
       </c>
-      <c r="F3" s="300"/>
+      <c r="F3" s="308"/>
     </row>
     <row r="4" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A4" s="292"/>
-      <c r="B4" s="290" t="s">
+      <c r="A4" s="300"/>
+      <c r="B4" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="291">
+      <c r="C4" s="299">
         <v>6</v>
       </c>
       <c r="D4" s="7">
@@ -3924,14 +3993,14 @@
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
-      <c r="F4" s="300"/>
+      <c r="F4" s="308"/>
     </row>
     <row r="5" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A5" s="292"/>
-      <c r="B5" s="290" t="s">
+      <c r="A5" s="300"/>
+      <c r="B5" s="298" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="291">
+      <c r="C5" s="299">
         <v>1</v>
       </c>
       <c r="D5" s="7">
@@ -3941,14 +4010,14 @@
         <f t="shared" si="0"/>
         <v>38000</v>
       </c>
-      <c r="F5" s="300"/>
+      <c r="F5" s="308"/>
     </row>
     <row r="6" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A6" s="292"/>
-      <c r="B6" s="290" t="s">
+      <c r="A6" s="300"/>
+      <c r="B6" s="298" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="291">
+      <c r="C6" s="299">
         <v>0.3</v>
       </c>
       <c r="D6" s="7">
@@ -3958,14 +4027,14 @@
         <f t="shared" si="0"/>
         <v>6000</v>
       </c>
-      <c r="F6" s="300"/>
+      <c r="F6" s="308"/>
     </row>
     <row r="7" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A7" s="292"/>
-      <c r="B7" s="290" t="s">
+      <c r="A7" s="300"/>
+      <c r="B7" s="298" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="291">
+      <c r="C7" s="299">
         <v>1</v>
       </c>
       <c r="D7" s="7">
@@ -3975,14 +4044,14 @@
         <f t="shared" si="0"/>
         <v>25000</v>
       </c>
-      <c r="F7" s="300"/>
+      <c r="F7" s="308"/>
     </row>
     <row r="8" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A8" s="292"/>
-      <c r="B8" s="290" t="s">
+      <c r="A8" s="300"/>
+      <c r="B8" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="291">
+      <c r="C8" s="299">
         <v>1</v>
       </c>
       <c r="D8" s="7">
@@ -3992,14 +4061,14 @@
         <f t="shared" si="0"/>
         <v>30000</v>
       </c>
-      <c r="F8" s="300"/>
+      <c r="F8" s="308"/>
     </row>
     <row r="9" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A9" s="292"/>
-      <c r="B9" s="290" t="s">
+      <c r="A9" s="300"/>
+      <c r="B9" s="298" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="291">
+      <c r="C9" s="299">
         <v>1</v>
       </c>
       <c r="D9" s="7">
@@ -4009,14 +4078,14 @@
         <f t="shared" si="0"/>
         <v>12000</v>
       </c>
-      <c r="F9" s="300"/>
+      <c r="F9" s="308"/>
     </row>
     <row r="10" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A10" s="292"/>
-      <c r="B10" s="290" t="s">
+      <c r="A10" s="300"/>
+      <c r="B10" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="291">
+      <c r="C10" s="299">
         <v>3</v>
       </c>
       <c r="D10" s="7">
@@ -4026,14 +4095,14 @@
         <f t="shared" si="0"/>
         <v>72000</v>
       </c>
-      <c r="F10" s="300"/>
+      <c r="F10" s="308"/>
     </row>
     <row r="11" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A11" s="292"/>
-      <c r="B11" s="290" t="s">
+      <c r="A11" s="300"/>
+      <c r="B11" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="291">
+      <c r="C11" s="299">
         <v>1</v>
       </c>
       <c r="D11" s="7">
@@ -4043,14 +4112,14 @@
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="F11" s="300"/>
+      <c r="F11" s="308"/>
     </row>
     <row r="12" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A12" s="293"/>
-      <c r="B12" s="290" t="s">
+      <c r="A12" s="301"/>
+      <c r="B12" s="298" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="291">
+      <c r="C12" s="299">
         <v>1</v>
       </c>
       <c r="D12" s="7">
@@ -4060,16 +4129,16 @@
         <f t="shared" si="0"/>
         <v>49000</v>
       </c>
-      <c r="F12" s="301"/>
+      <c r="F12" s="309"/>
     </row>
     <row r="13" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A13" s="289">
+      <c r="A13" s="297">
         <v>45996</v>
       </c>
-      <c r="B13" s="290" t="s">
+      <c r="B13" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="291">
+      <c r="C13" s="299">
         <v>8</v>
       </c>
       <c r="D13" s="7">
@@ -4079,17 +4148,17 @@
         <f t="shared" si="0"/>
         <v>80000</v>
       </c>
-      <c r="F13" s="299">
+      <c r="F13" s="307">
         <f>SUM(E13:E25)</f>
         <v>730000</v>
       </c>
     </row>
     <row r="14" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A14" s="292"/>
-      <c r="B14" s="290" t="s">
+      <c r="A14" s="300"/>
+      <c r="B14" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="291">
+      <c r="C14" s="299">
         <v>2</v>
       </c>
       <c r="D14" s="7">
@@ -4099,14 +4168,14 @@
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="F14" s="300"/>
+      <c r="F14" s="308"/>
     </row>
     <row r="15" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A15" s="292"/>
-      <c r="B15" s="290" t="s">
+      <c r="A15" s="300"/>
+      <c r="B15" s="298" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="291">
+      <c r="C15" s="299">
         <v>2</v>
       </c>
       <c r="D15" s="7">
@@ -4116,14 +4185,14 @@
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
-      <c r="F15" s="300"/>
+      <c r="F15" s="308"/>
     </row>
     <row r="16" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A16" s="292"/>
-      <c r="B16" s="290" t="s">
+      <c r="A16" s="300"/>
+      <c r="B16" s="298" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="291">
+      <c r="C16" s="299">
         <v>0.5</v>
       </c>
       <c r="D16" s="7">
@@ -4132,14 +4201,14 @@
       <c r="E16" s="7">
         <v>48000</v>
       </c>
-      <c r="F16" s="300"/>
+      <c r="F16" s="308"/>
     </row>
     <row r="17" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A17" s="292"/>
-      <c r="B17" s="290" t="s">
+      <c r="A17" s="300"/>
+      <c r="B17" s="298" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="291">
+      <c r="C17" s="299">
         <v>1.1</v>
       </c>
       <c r="D17" s="7">
@@ -4148,14 +4217,14 @@
       <c r="E17" s="7">
         <v>42000</v>
       </c>
-      <c r="F17" s="300"/>
+      <c r="F17" s="308"/>
     </row>
     <row r="18" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A18" s="292"/>
-      <c r="B18" s="290" t="s">
+      <c r="A18" s="300"/>
+      <c r="B18" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="291">
+      <c r="C18" s="299">
         <v>5</v>
       </c>
       <c r="D18" s="7">
@@ -4165,14 +4234,14 @@
         <f t="shared" ref="E18:E25" si="1">SUM(C18*D18)</f>
         <v>120000</v>
       </c>
-      <c r="F18" s="300"/>
+      <c r="F18" s="308"/>
     </row>
     <row r="19" s="244" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A19" s="292"/>
-      <c r="B19" s="294" t="s">
+      <c r="A19" s="300"/>
+      <c r="B19" s="302" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="295">
+      <c r="C19" s="303">
         <v>3</v>
       </c>
       <c r="D19" s="133">
@@ -4182,15 +4251,15 @@
         <f t="shared" si="1"/>
         <v>120000</v>
       </c>
-      <c r="F19" s="300"/>
-      <c r="G19" s="277"/>
+      <c r="F19" s="308"/>
+      <c r="G19" s="281"/>
     </row>
     <row r="20" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A20" s="292"/>
-      <c r="B20" s="296" t="s">
+      <c r="A20" s="300"/>
+      <c r="B20" s="304" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="291">
+      <c r="C20" s="299">
         <v>1</v>
       </c>
       <c r="D20" s="262">
@@ -4200,14 +4269,14 @@
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F20" s="300"/>
+      <c r="F20" s="308"/>
     </row>
     <row r="21" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A21" s="292"/>
-      <c r="B21" s="296" t="s">
+      <c r="A21" s="300"/>
+      <c r="B21" s="304" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="299">
         <v>2</v>
       </c>
       <c r="D21" s="262">
@@ -4217,14 +4286,14 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F21" s="300"/>
+      <c r="F21" s="308"/>
     </row>
     <row r="22" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A22" s="292"/>
-      <c r="B22" s="296" t="s">
+      <c r="A22" s="300"/>
+      <c r="B22" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="291">
+      <c r="C22" s="299">
         <v>0.5</v>
       </c>
       <c r="D22" s="262">
@@ -4234,14 +4303,14 @@
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
-      <c r="F22" s="300"/>
+      <c r="F22" s="308"/>
     </row>
     <row r="23" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A23" s="292"/>
-      <c r="B23" s="296" t="s">
+      <c r="A23" s="300"/>
+      <c r="B23" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="291">
+      <c r="C23" s="299">
         <v>1</v>
       </c>
       <c r="D23" s="262">
@@ -4251,14 +4320,14 @@
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="F23" s="300"/>
+      <c r="F23" s="308"/>
     </row>
     <row r="24" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A24" s="292"/>
-      <c r="B24" s="296" t="s">
+      <c r="A24" s="300"/>
+      <c r="B24" s="304" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="291">
+      <c r="C24" s="299">
         <v>0.3</v>
       </c>
       <c r="D24" s="262">
@@ -4268,14 +4337,14 @@
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F24" s="300"/>
+      <c r="F24" s="308"/>
     </row>
     <row r="25" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A25" s="293"/>
-      <c r="B25" s="296" t="s">
+      <c r="A25" s="301"/>
+      <c r="B25" s="304" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="291">
+      <c r="C25" s="299">
         <v>1</v>
       </c>
       <c r="D25" s="262">
@@ -4285,16 +4354,16 @@
         <f t="shared" si="1"/>
         <v>35000</v>
       </c>
-      <c r="F25" s="301"/>
+      <c r="F25" s="309"/>
     </row>
     <row r="26" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A26" s="289">
+      <c r="A26" s="297">
         <v>45997</v>
       </c>
-      <c r="B26" s="296" t="s">
+      <c r="B26" s="304" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="291">
+      <c r="C26" s="299">
         <v>3.995</v>
       </c>
       <c r="D26" s="262">
@@ -4303,17 +4372,17 @@
       <c r="E26" s="7">
         <v>60000</v>
       </c>
-      <c r="F26" s="299">
+      <c r="F26" s="307">
         <f>SUM(E26:E34)</f>
         <v>422000</v>
       </c>
     </row>
     <row r="27" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A27" s="292"/>
-      <c r="B27" s="296" t="s">
+      <c r="A27" s="300"/>
+      <c r="B27" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="291">
+      <c r="C27" s="299">
         <v>2</v>
       </c>
       <c r="D27" s="262">
@@ -4323,14 +4392,14 @@
         <f>SUM(C27*D27)</f>
         <v>40000</v>
       </c>
-      <c r="F27" s="300"/>
+      <c r="F27" s="308"/>
     </row>
     <row r="28" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A28" s="292"/>
-      <c r="B28" s="296" t="s">
+      <c r="A28" s="300"/>
+      <c r="B28" s="304" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="291">
+      <c r="C28" s="299">
         <v>0.5</v>
       </c>
       <c r="D28" s="262">
@@ -4339,14 +4408,14 @@
       <c r="E28" s="7">
         <v>18000</v>
       </c>
-      <c r="F28" s="300"/>
+      <c r="F28" s="308"/>
     </row>
     <row r="29" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A29" s="292"/>
-      <c r="B29" s="296" t="s">
+      <c r="A29" s="300"/>
+      <c r="B29" s="304" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="291">
+      <c r="C29" s="299">
         <v>0.1</v>
       </c>
       <c r="D29" s="262">
@@ -4356,14 +4425,14 @@
         <f t="shared" ref="E29:E34" si="2">SUM(C29*D29)</f>
         <v>8000</v>
       </c>
-      <c r="F29" s="300"/>
+      <c r="F29" s="308"/>
     </row>
     <row r="30" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A30" s="292"/>
-      <c r="B30" s="296" t="s">
+      <c r="A30" s="300"/>
+      <c r="B30" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="291">
+      <c r="C30" s="299">
         <v>0.5</v>
       </c>
       <c r="D30" s="262">
@@ -4373,14 +4442,14 @@
         <f t="shared" si="2"/>
         <v>15000</v>
       </c>
-      <c r="F30" s="300"/>
+      <c r="F30" s="308"/>
     </row>
     <row r="31" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A31" s="292"/>
-      <c r="B31" s="296" t="s">
+      <c r="A31" s="300"/>
+      <c r="B31" s="304" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="291">
+      <c r="C31" s="299">
         <v>4</v>
       </c>
       <c r="D31" s="262">
@@ -4390,14 +4459,14 @@
         <f t="shared" si="2"/>
         <v>80000</v>
       </c>
-      <c r="F31" s="300"/>
+      <c r="F31" s="308"/>
     </row>
     <row r="32" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A32" s="292"/>
-      <c r="B32" s="290" t="s">
+      <c r="A32" s="300"/>
+      <c r="B32" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="291">
+      <c r="C32" s="299">
         <v>4</v>
       </c>
       <c r="D32" s="7">
@@ -4407,14 +4476,14 @@
         <f t="shared" si="2"/>
         <v>96000</v>
       </c>
-      <c r="F32" s="300"/>
+      <c r="F32" s="308"/>
     </row>
     <row r="33" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A33" s="292"/>
-      <c r="B33" s="290" t="s">
+      <c r="A33" s="300"/>
+      <c r="B33" s="298" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="291">
+      <c r="C33" s="299">
         <v>2</v>
       </c>
       <c r="D33" s="7">
@@ -4424,14 +4493,14 @@
         <f t="shared" si="2"/>
         <v>80000</v>
       </c>
-      <c r="F33" s="300"/>
+      <c r="F33" s="308"/>
     </row>
     <row r="34" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A34" s="293"/>
-      <c r="B34" s="290" t="s">
+      <c r="A34" s="301"/>
+      <c r="B34" s="298" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="291">
+      <c r="C34" s="299">
         <v>1</v>
       </c>
       <c r="D34" s="7">
@@ -4441,16 +4510,16 @@
         <f t="shared" si="2"/>
         <v>25000</v>
       </c>
-      <c r="F34" s="301"/>
+      <c r="F34" s="309"/>
     </row>
     <row r="35" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A35" s="297">
+      <c r="A35" s="305">
         <v>45998</v>
       </c>
-      <c r="B35" s="296" t="s">
+      <c r="B35" s="304" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="291">
+      <c r="C35" s="299">
         <v>8.945</v>
       </c>
       <c r="D35" s="7">
@@ -4459,17 +4528,17 @@
       <c r="E35" s="7">
         <v>134000</v>
       </c>
-      <c r="F35" s="300">
+      <c r="F35" s="308">
         <f>SUM(E35:E42)</f>
         <v>517000</v>
       </c>
     </row>
     <row r="36" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A36" s="297"/>
-      <c r="B36" s="296" t="s">
+      <c r="A36" s="305"/>
+      <c r="B36" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="291">
+      <c r="C36" s="299">
         <v>2</v>
       </c>
       <c r="D36" s="7">
@@ -4479,14 +4548,14 @@
         <f t="shared" ref="E35:E44" si="3">SUM(C36*D36)</f>
         <v>40000</v>
       </c>
-      <c r="F36" s="300"/>
+      <c r="F36" s="308"/>
     </row>
     <row r="37" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A37" s="297"/>
-      <c r="B37" s="296" t="s">
+      <c r="A37" s="305"/>
+      <c r="B37" s="304" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="291">
+      <c r="C37" s="299">
         <v>0.3</v>
       </c>
       <c r="D37" s="7">
@@ -4496,14 +4565,14 @@
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="F37" s="300"/>
+      <c r="F37" s="308"/>
     </row>
     <row r="38" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A38" s="297"/>
-      <c r="B38" s="296" t="s">
+      <c r="A38" s="305"/>
+      <c r="B38" s="304" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="291">
+      <c r="C38" s="299">
         <v>1</v>
       </c>
       <c r="D38" s="7">
@@ -4513,14 +4582,14 @@
         <f t="shared" si="3"/>
         <v>30000</v>
       </c>
-      <c r="F38" s="300"/>
+      <c r="F38" s="308"/>
     </row>
     <row r="39" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A39" s="297"/>
-      <c r="B39" s="296" t="s">
+      <c r="A39" s="305"/>
+      <c r="B39" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="291">
+      <c r="C39" s="299">
         <v>0.5</v>
       </c>
       <c r="D39" s="7">
@@ -4530,14 +4599,14 @@
         <f t="shared" si="3"/>
         <v>15000</v>
       </c>
-      <c r="F39" s="300"/>
+      <c r="F39" s="308"/>
     </row>
     <row r="40" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A40" s="297"/>
-      <c r="B40" s="296" t="s">
+      <c r="A40" s="305"/>
+      <c r="B40" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="291">
+      <c r="C40" s="299">
         <v>4</v>
       </c>
       <c r="D40" s="7">
@@ -4547,14 +4616,14 @@
         <f t="shared" si="3"/>
         <v>96000</v>
       </c>
-      <c r="F40" s="300"/>
+      <c r="F40" s="308"/>
     </row>
     <row r="41" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A41" s="297"/>
-      <c r="B41" s="296" t="s">
+      <c r="A41" s="305"/>
+      <c r="B41" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="291">
+      <c r="C41" s="299">
         <v>2</v>
       </c>
       <c r="D41" s="7">
@@ -4564,14 +4633,14 @@
         <f t="shared" si="3"/>
         <v>80000</v>
       </c>
-      <c r="F41" s="300"/>
+      <c r="F41" s="308"/>
     </row>
     <row r="42" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A42" s="297"/>
-      <c r="B42" s="296" t="s">
+      <c r="A42" s="305"/>
+      <c r="B42" s="304" t="s">
         <v>32</v>
       </c>
-      <c r="C42" s="291">
+      <c r="C42" s="299">
         <v>2</v>
       </c>
       <c r="D42" s="7">
@@ -4581,16 +4650,16 @@
         <f t="shared" si="3"/>
         <v>98000</v>
       </c>
-      <c r="F42" s="300"/>
+      <c r="F42" s="308"/>
     </row>
     <row r="43" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A43" s="289">
+      <c r="A43" s="297">
         <v>45999</v>
       </c>
-      <c r="B43" s="296" t="s">
+      <c r="B43" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="291">
+      <c r="C43" s="299">
         <v>3</v>
       </c>
       <c r="D43" s="7">
@@ -4600,17 +4669,17 @@
         <f t="shared" si="3"/>
         <v>30000</v>
       </c>
-      <c r="F43" s="302">
+      <c r="F43" s="310">
         <f>SUM(E43:E47)</f>
         <v>357000</v>
       </c>
     </row>
     <row r="44" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A44" s="292"/>
-      <c r="B44" s="296" t="s">
+      <c r="A44" s="300"/>
+      <c r="B44" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="291">
+      <c r="C44" s="299">
         <v>2.7</v>
       </c>
       <c r="D44" s="7">
@@ -4620,14 +4689,14 @@
         <f t="shared" si="3"/>
         <v>54000</v>
       </c>
-      <c r="F44" s="302"/>
+      <c r="F44" s="310"/>
     </row>
     <row r="45" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A45" s="292"/>
-      <c r="B45" s="296" t="s">
+      <c r="A45" s="300"/>
+      <c r="B45" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="291">
+      <c r="C45" s="299">
         <v>3.09</v>
       </c>
       <c r="D45" s="7">
@@ -4636,14 +4705,14 @@
       <c r="E45" s="7">
         <v>216000</v>
       </c>
-      <c r="F45" s="302"/>
+      <c r="F45" s="310"/>
     </row>
     <row r="46" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A46" s="292"/>
-      <c r="B46" s="296" t="s">
+      <c r="A46" s="300"/>
+      <c r="B46" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="291">
+      <c r="C46" s="299">
         <v>0.3</v>
       </c>
       <c r="D46" s="7">
@@ -4653,14 +4722,14 @@
         <f>SUM(C46*D46)</f>
         <v>9000</v>
       </c>
-      <c r="F46" s="302"/>
+      <c r="F46" s="310"/>
     </row>
     <row r="47" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A47" s="292"/>
-      <c r="B47" s="296" t="s">
+      <c r="A47" s="300"/>
+      <c r="B47" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="291">
+      <c r="C47" s="299">
         <v>2</v>
       </c>
       <c r="D47" s="7">
@@ -4670,16 +4739,16 @@
         <f>SUM(C47*D47)</f>
         <v>48000</v>
       </c>
-      <c r="F47" s="302"/>
+      <c r="F47" s="310"/>
     </row>
     <row r="48" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A48" s="289">
+      <c r="A48" s="297">
         <v>46000</v>
       </c>
-      <c r="B48" s="296" t="s">
+      <c r="B48" s="304" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="291">
+      <c r="C48" s="299">
         <v>2</v>
       </c>
       <c r="D48" s="7">
@@ -4689,17 +4758,17 @@
         <f t="shared" ref="E48:E82" si="4">SUM(C48*D48)</f>
         <v>40000</v>
       </c>
-      <c r="F48" s="299">
+      <c r="F48" s="307">
         <f>SUM(E48:E58)</f>
         <v>612000</v>
       </c>
     </row>
     <row r="49" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A49" s="292"/>
-      <c r="B49" s="296" t="s">
+      <c r="A49" s="300"/>
+      <c r="B49" s="304" t="s">
         <v>17</v>
       </c>
-      <c r="C49" s="291">
+      <c r="C49" s="299">
         <v>2</v>
       </c>
       <c r="D49" s="7">
@@ -4709,14 +4778,14 @@
         <f t="shared" si="4"/>
         <v>70000</v>
       </c>
-      <c r="F49" s="300"/>
+      <c r="F49" s="308"/>
     </row>
     <row r="50" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A50" s="292"/>
-      <c r="B50" s="296" t="s">
+      <c r="A50" s="300"/>
+      <c r="B50" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="291">
+      <c r="C50" s="299">
         <v>5</v>
       </c>
       <c r="D50" s="7">
@@ -4726,14 +4795,14 @@
         <f t="shared" si="4"/>
         <v>120000</v>
       </c>
-      <c r="F50" s="300"/>
+      <c r="F50" s="308"/>
     </row>
     <row r="51" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A51" s="292"/>
-      <c r="B51" s="296" t="s">
+      <c r="A51" s="300"/>
+      <c r="B51" s="304" t="s">
         <v>32</v>
       </c>
-      <c r="C51" s="291">
+      <c r="C51" s="299">
         <v>1</v>
       </c>
       <c r="D51" s="7">
@@ -4743,14 +4812,14 @@
         <f t="shared" si="4"/>
         <v>49000</v>
       </c>
-      <c r="F51" s="300"/>
+      <c r="F51" s="308"/>
     </row>
     <row r="52" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A52" s="292"/>
-      <c r="B52" s="296" t="s">
+      <c r="A52" s="300"/>
+      <c r="B52" s="304" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="291">
+      <c r="C52" s="299">
         <v>1</v>
       </c>
       <c r="D52" s="7">
@@ -4760,14 +4829,14 @@
         <f t="shared" si="4"/>
         <v>65000</v>
       </c>
-      <c r="F52" s="300"/>
+      <c r="F52" s="308"/>
     </row>
     <row r="53" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A53" s="292"/>
-      <c r="B53" s="296" t="s">
+      <c r="A53" s="300"/>
+      <c r="B53" s="304" t="s">
         <v>18</v>
       </c>
-      <c r="C53" s="291">
+      <c r="C53" s="299">
         <v>0.5</v>
       </c>
       <c r="D53" s="7">
@@ -4776,14 +4845,14 @@
       <c r="E53" s="7">
         <v>48000</v>
       </c>
-      <c r="F53" s="300"/>
+      <c r="F53" s="308"/>
     </row>
     <row r="54" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A54" s="292"/>
-      <c r="B54" s="296" t="s">
+      <c r="A54" s="300"/>
+      <c r="B54" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="291">
+      <c r="C54" s="299">
         <v>1</v>
       </c>
       <c r="D54" s="7">
@@ -4793,14 +4862,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F54" s="300"/>
+      <c r="F54" s="308"/>
     </row>
     <row r="55" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A55" s="292"/>
-      <c r="B55" s="296" t="s">
+      <c r="A55" s="300"/>
+      <c r="B55" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="291">
+      <c r="C55" s="299">
         <v>9</v>
       </c>
       <c r="D55" s="7">
@@ -4810,14 +4879,14 @@
         <f t="shared" si="4"/>
         <v>90000</v>
       </c>
-      <c r="F55" s="300"/>
+      <c r="F55" s="308"/>
     </row>
     <row r="56" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A56" s="292"/>
-      <c r="B56" s="290" t="s">
+      <c r="A56" s="300"/>
+      <c r="B56" s="298" t="s">
         <v>7</v>
       </c>
-      <c r="C56" s="291">
+      <c r="C56" s="299">
         <v>1</v>
       </c>
       <c r="D56" s="7">
@@ -4827,14 +4896,14 @@
         <f t="shared" si="4"/>
         <v>70000</v>
       </c>
-      <c r="F56" s="300"/>
+      <c r="F56" s="308"/>
     </row>
     <row r="57" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A57" s="292"/>
-      <c r="B57" s="290" t="s">
+      <c r="A57" s="300"/>
+      <c r="B57" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="291">
+      <c r="C57" s="299">
         <v>2</v>
       </c>
       <c r="D57" s="7">
@@ -4844,14 +4913,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F57" s="300"/>
+      <c r="F57" s="308"/>
     </row>
     <row r="58" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A58" s="293"/>
-      <c r="B58" s="290" t="s">
+      <c r="A58" s="301"/>
+      <c r="B58" s="298" t="s">
         <v>34</v>
       </c>
-      <c r="C58" s="291">
+      <c r="C58" s="299">
         <v>1</v>
       </c>
       <c r="D58" s="7">
@@ -4861,16 +4930,16 @@
         <f t="shared" si="4"/>
         <v>5000</v>
       </c>
-      <c r="F58" s="301"/>
+      <c r="F58" s="309"/>
     </row>
     <row r="59" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A59" s="289">
+      <c r="A59" s="297">
         <v>46001</v>
       </c>
-      <c r="B59" s="290" t="s">
+      <c r="B59" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="291">
+      <c r="C59" s="299">
         <v>3</v>
       </c>
       <c r="D59" s="7">
@@ -4880,17 +4949,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F59" s="299">
+      <c r="F59" s="307">
         <f>SUM(E59:E67)</f>
         <v>586000</v>
       </c>
     </row>
     <row r="60" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A60" s="292"/>
-      <c r="B60" s="290" t="s">
+      <c r="A60" s="300"/>
+      <c r="B60" s="298" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="291">
+      <c r="C60" s="299">
         <v>2</v>
       </c>
       <c r="D60" s="7">
@@ -4900,14 +4969,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F60" s="300"/>
+      <c r="F60" s="308"/>
     </row>
     <row r="61" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A61" s="292"/>
-      <c r="B61" s="290" t="s">
+      <c r="A61" s="300"/>
+      <c r="B61" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="291">
+      <c r="C61" s="299">
         <v>8</v>
       </c>
       <c r="D61" s="7">
@@ -4917,14 +4986,14 @@
         <f t="shared" si="4"/>
         <v>80000</v>
       </c>
-      <c r="F61" s="300"/>
+      <c r="F61" s="308"/>
     </row>
     <row r="62" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A62" s="292"/>
-      <c r="B62" s="290" t="s">
+      <c r="A62" s="300"/>
+      <c r="B62" s="298" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="291">
+      <c r="C62" s="299">
         <v>1</v>
       </c>
       <c r="D62" s="7">
@@ -4934,14 +5003,14 @@
         <f t="shared" si="4"/>
         <v>38000</v>
       </c>
-      <c r="F62" s="300"/>
+      <c r="F62" s="308"/>
     </row>
     <row r="63" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A63" s="292"/>
-      <c r="B63" s="290" t="s">
+      <c r="A63" s="300"/>
+      <c r="B63" s="298" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="291">
+      <c r="C63" s="299">
         <v>1</v>
       </c>
       <c r="D63" s="7">
@@ -4951,14 +5020,14 @@
         <f t="shared" si="4"/>
         <v>20000</v>
       </c>
-      <c r="F63" s="300"/>
+      <c r="F63" s="308"/>
     </row>
     <row r="64" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A64" s="292"/>
-      <c r="B64" s="290" t="s">
+      <c r="A64" s="300"/>
+      <c r="B64" s="298" t="s">
         <v>22</v>
       </c>
-      <c r="C64" s="291">
+      <c r="C64" s="299">
         <v>0.5</v>
       </c>
       <c r="D64" s="7">
@@ -4968,14 +5037,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F64" s="300"/>
+      <c r="F64" s="308"/>
     </row>
     <row r="65" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A65" s="292"/>
-      <c r="B65" s="290" t="s">
+      <c r="A65" s="300"/>
+      <c r="B65" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C65" s="291">
+      <c r="C65" s="299">
         <v>6</v>
       </c>
       <c r="D65" s="7">
@@ -4985,14 +5054,14 @@
         <f t="shared" si="4"/>
         <v>144000</v>
       </c>
-      <c r="F65" s="300"/>
+      <c r="F65" s="308"/>
     </row>
     <row r="66" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A66" s="292"/>
-      <c r="B66" s="290" t="s">
+      <c r="A66" s="300"/>
+      <c r="B66" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="291">
+      <c r="C66" s="299">
         <v>1</v>
       </c>
       <c r="D66" s="7">
@@ -5002,14 +5071,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F66" s="300"/>
+      <c r="F66" s="308"/>
     </row>
     <row r="67" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A67" s="293"/>
-      <c r="B67" s="290" t="s">
+      <c r="A67" s="301"/>
+      <c r="B67" s="298" t="s">
         <v>32</v>
       </c>
-      <c r="C67" s="291">
+      <c r="C67" s="299">
         <v>1</v>
       </c>
       <c r="D67" s="7">
@@ -5019,16 +5088,16 @@
         <f t="shared" si="4"/>
         <v>49000</v>
       </c>
-      <c r="F67" s="301"/>
+      <c r="F67" s="309"/>
     </row>
     <row r="68" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A68" s="289">
+      <c r="A68" s="297">
         <v>46002</v>
       </c>
-      <c r="B68" s="290" t="s">
+      <c r="B68" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C68" s="291">
+      <c r="C68" s="299">
         <v>3</v>
       </c>
       <c r="D68" s="7">
@@ -5038,17 +5107,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F68" s="299">
+      <c r="F68" s="307">
         <f>SUM(E68:E78)</f>
         <v>541000</v>
       </c>
     </row>
     <row r="69" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A69" s="292"/>
-      <c r="B69" s="290" t="s">
+      <c r="A69" s="300"/>
+      <c r="B69" s="298" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="291">
+      <c r="C69" s="299">
         <v>2</v>
       </c>
       <c r="D69" s="7">
@@ -5058,14 +5127,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F69" s="300"/>
+      <c r="F69" s="308"/>
     </row>
     <row r="70" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A70" s="292"/>
-      <c r="B70" s="290" t="s">
+      <c r="A70" s="300"/>
+      <c r="B70" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="C70" s="291">
+      <c r="C70" s="299">
         <v>4</v>
       </c>
       <c r="D70" s="7">
@@ -5075,14 +5144,14 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F70" s="300"/>
+      <c r="F70" s="308"/>
     </row>
     <row r="71" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A71" s="292"/>
-      <c r="B71" s="290" t="s">
+      <c r="A71" s="300"/>
+      <c r="B71" s="298" t="s">
         <v>9</v>
       </c>
-      <c r="C71" s="291">
+      <c r="C71" s="299">
         <v>1</v>
       </c>
       <c r="D71" s="7">
@@ -5092,14 +5161,14 @@
         <f t="shared" si="4"/>
         <v>38000</v>
       </c>
-      <c r="F71" s="300"/>
+      <c r="F71" s="308"/>
     </row>
     <row r="72" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A72" s="292"/>
-      <c r="B72" s="290" t="s">
+      <c r="A72" s="300"/>
+      <c r="B72" s="298" t="s">
         <v>10</v>
       </c>
-      <c r="C72" s="291">
+      <c r="C72" s="299">
         <v>1</v>
       </c>
       <c r="D72" s="7">
@@ -5109,14 +5178,14 @@
         <f t="shared" si="4"/>
         <v>20000</v>
       </c>
-      <c r="F72" s="300"/>
+      <c r="F72" s="308"/>
     </row>
     <row r="73" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A73" s="292"/>
-      <c r="B73" s="290" t="s">
+      <c r="A73" s="300"/>
+      <c r="B73" s="298" t="s">
         <v>22</v>
       </c>
-      <c r="C73" s="291">
+      <c r="C73" s="299">
         <v>0.5</v>
       </c>
       <c r="D73" s="7">
@@ -5126,14 +5195,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F73" s="300"/>
+      <c r="F73" s="308"/>
     </row>
     <row r="74" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A74" s="292"/>
-      <c r="B74" s="290" t="s">
+      <c r="A74" s="300"/>
+      <c r="B74" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="C74" s="291">
+      <c r="C74" s="299">
         <v>1</v>
       </c>
       <c r="D74" s="7">
@@ -5143,14 +5212,14 @@
         <f t="shared" si="4"/>
         <v>30000</v>
       </c>
-      <c r="F74" s="300"/>
+      <c r="F74" s="308"/>
     </row>
     <row r="75" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A75" s="292"/>
-      <c r="B75" s="290" t="s">
+      <c r="A75" s="300"/>
+      <c r="B75" s="298" t="s">
         <v>18</v>
       </c>
-      <c r="C75" s="291">
+      <c r="C75" s="299">
         <v>1</v>
       </c>
       <c r="D75" s="7">
@@ -5160,14 +5229,14 @@
         <f t="shared" si="4"/>
         <v>95000</v>
       </c>
-      <c r="F75" s="300"/>
+      <c r="F75" s="308"/>
     </row>
     <row r="76" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A76" s="292"/>
-      <c r="B76" s="290" t="s">
+      <c r="A76" s="300"/>
+      <c r="B76" s="298" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="291">
+      <c r="C76" s="299">
         <v>1</v>
       </c>
       <c r="D76" s="7">
@@ -5177,14 +5246,14 @@
         <f t="shared" si="4"/>
         <v>15000</v>
       </c>
-      <c r="F76" s="300"/>
+      <c r="F76" s="308"/>
     </row>
     <row r="77" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A77" s="292"/>
-      <c r="B77" s="290" t="s">
+      <c r="A77" s="300"/>
+      <c r="B77" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C77" s="291">
+      <c r="C77" s="299">
         <v>2</v>
       </c>
       <c r="D77" s="7">
@@ -5194,14 +5263,14 @@
         <f t="shared" si="4"/>
         <v>48000</v>
       </c>
-      <c r="F77" s="300"/>
+      <c r="F77" s="308"/>
     </row>
     <row r="78" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A78" s="293"/>
-      <c r="B78" s="290" t="s">
+      <c r="A78" s="301"/>
+      <c r="B78" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="C78" s="291">
+      <c r="C78" s="299">
         <v>1</v>
       </c>
       <c r="D78" s="7">
@@ -5211,16 +5280,16 @@
         <f t="shared" si="4"/>
         <v>40000</v>
       </c>
-      <c r="F78" s="301"/>
+      <c r="F78" s="309"/>
     </row>
     <row r="79" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A79" s="289">
+      <c r="A79" s="297">
         <v>46003</v>
       </c>
-      <c r="B79" s="290" t="s">
+      <c r="B79" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="C79" s="291">
+      <c r="C79" s="299">
         <v>3</v>
       </c>
       <c r="D79" s="7">
@@ -5230,17 +5299,17 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F79" s="299">
+      <c r="F79" s="307">
         <f>-SUM(E79:E93)</f>
         <v>-900000</v>
       </c>
     </row>
     <row r="80" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A80" s="292"/>
-      <c r="B80" s="290" t="s">
+      <c r="A80" s="300"/>
+      <c r="B80" s="298" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="291">
+      <c r="C80" s="299">
         <v>2</v>
       </c>
       <c r="D80" s="7">
@@ -5250,14 +5319,14 @@
         <f t="shared" si="4"/>
         <v>140000</v>
       </c>
-      <c r="F80" s="300"/>
+      <c r="F80" s="308"/>
     </row>
     <row r="81" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A81" s="292"/>
-      <c r="B81" s="290" t="s">
+      <c r="A81" s="300"/>
+      <c r="B81" s="298" t="s">
         <v>8</v>
       </c>
-      <c r="C81" s="291">
+      <c r="C81" s="299">
         <v>6</v>
       </c>
       <c r="D81" s="7">
@@ -5267,14 +5336,14 @@
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="F81" s="300"/>
+      <c r="F81" s="308"/>
     </row>
     <row r="82" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A82" s="292"/>
-      <c r="B82" s="290" t="s">
+      <c r="A82" s="300"/>
+      <c r="B82" s="298" t="s">
         <v>35</v>
       </c>
-      <c r="C82" s="291">
+      <c r="C82" s="299">
         <v>2</v>
       </c>
       <c r="D82" s="7">
@@ -5284,14 +5353,14 @@
         <f t="shared" si="4"/>
         <v>96000</v>
       </c>
-      <c r="F82" s="300"/>
+      <c r="F82" s="308"/>
     </row>
     <row r="83" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A83" s="292"/>
-      <c r="B83" s="290" t="s">
+      <c r="A83" s="300"/>
+      <c r="B83" s="298" t="s">
         <v>24</v>
       </c>
-      <c r="C83" s="291">
+      <c r="C83" s="299">
         <v>8.18</v>
       </c>
       <c r="D83" s="7">
@@ -5300,14 +5369,14 @@
       <c r="E83" s="7">
         <v>123000</v>
       </c>
-      <c r="F83" s="300"/>
+      <c r="F83" s="308"/>
     </row>
     <row r="84" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A84" s="292"/>
-      <c r="B84" s="290" t="s">
+      <c r="A84" s="300"/>
+      <c r="B84" s="298" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="291">
+      <c r="C84" s="299">
         <v>0.3</v>
       </c>
       <c r="D84" s="7">
@@ -5317,14 +5386,14 @@
         <f>SUM(C84*D84)</f>
         <v>6000</v>
       </c>
-      <c r="F84" s="300"/>
+      <c r="F84" s="308"/>
     </row>
     <row r="85" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A85" s="292"/>
-      <c r="B85" s="290" t="s">
+      <c r="A85" s="300"/>
+      <c r="B85" s="298" t="s">
         <v>22</v>
       </c>
-      <c r="C85" s="291">
+      <c r="C85" s="299">
         <v>0.5</v>
       </c>
       <c r="D85" s="7">
@@ -5334,14 +5403,14 @@
         <f>SUM(C85*D85)</f>
         <v>15000</v>
       </c>
-      <c r="F85" s="300"/>
+      <c r="F85" s="308"/>
     </row>
     <row r="86" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A86" s="292"/>
-      <c r="B86" s="290" t="s">
+      <c r="A86" s="300"/>
+      <c r="B86" s="298" t="s">
         <v>31</v>
       </c>
-      <c r="C86" s="291">
+      <c r="C86" s="299">
         <v>0.5</v>
       </c>
       <c r="D86" s="7">
@@ -5351,14 +5420,14 @@
         <f>SUM(C86*D86)</f>
         <v>40000</v>
       </c>
-      <c r="F86" s="300"/>
+      <c r="F86" s="308"/>
     </row>
     <row r="87" s="244" customFormat="1" ht="14" customHeight="1" spans="1:8">
-      <c r="A87" s="292"/>
-      <c r="B87" s="290" t="s">
+      <c r="A87" s="300"/>
+      <c r="B87" s="298" t="s">
         <v>18</v>
       </c>
-      <c r="C87" s="291">
+      <c r="C87" s="299">
         <v>0.5</v>
       </c>
       <c r="D87" s="7">
@@ -5367,15 +5436,15 @@
       <c r="E87" s="7">
         <v>48000</v>
       </c>
-      <c r="F87" s="300"/>
-      <c r="H87" s="277"/>
+      <c r="F87" s="308"/>
+      <c r="H87" s="281"/>
     </row>
     <row r="88" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A88" s="292"/>
-      <c r="B88" s="290" t="s">
+      <c r="A88" s="300"/>
+      <c r="B88" s="298" t="s">
         <v>13</v>
       </c>
-      <c r="C88" s="291">
+      <c r="C88" s="299">
         <v>1</v>
       </c>
       <c r="D88" s="7">
@@ -5385,14 +5454,14 @@
         <f t="shared" ref="E88:E94" si="5">SUM(C88*D88)</f>
         <v>15000</v>
       </c>
-      <c r="F88" s="300"/>
+      <c r="F88" s="308"/>
     </row>
     <row r="89" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A89" s="292"/>
-      <c r="B89" s="290" t="s">
+      <c r="A89" s="300"/>
+      <c r="B89" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="C89" s="291">
+      <c r="C89" s="299">
         <v>2</v>
       </c>
       <c r="D89" s="7">
@@ -5402,14 +5471,14 @@
         <f t="shared" si="5"/>
         <v>48000</v>
       </c>
-      <c r="F89" s="300"/>
+      <c r="F89" s="308"/>
     </row>
     <row r="90" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A90" s="292"/>
-      <c r="B90" s="290" t="s">
+      <c r="A90" s="300"/>
+      <c r="B90" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="C90" s="291">
+      <c r="C90" s="299">
         <v>1</v>
       </c>
       <c r="D90" s="7">
@@ -5419,14 +5488,14 @@
         <f t="shared" si="5"/>
         <v>40000</v>
       </c>
-      <c r="F90" s="300"/>
+      <c r="F90" s="308"/>
     </row>
     <row r="91" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A91" s="292"/>
-      <c r="B91" s="290" t="s">
+      <c r="A91" s="300"/>
+      <c r="B91" s="298" t="s">
         <v>32</v>
       </c>
-      <c r="C91" s="291">
+      <c r="C91" s="299">
         <v>1</v>
       </c>
       <c r="D91" s="7">
@@ -5436,14 +5505,14 @@
         <f t="shared" si="5"/>
         <v>49000</v>
       </c>
-      <c r="F91" s="300"/>
+      <c r="F91" s="308"/>
     </row>
     <row r="92" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A92" s="292"/>
-      <c r="B92" s="290" t="s">
+      <c r="A92" s="300"/>
+      <c r="B92" s="298" t="s">
         <v>21</v>
       </c>
-      <c r="C92" s="291">
+      <c r="C92" s="299">
         <v>4</v>
       </c>
       <c r="D92" s="7">
@@ -5453,14 +5522,14 @@
         <f t="shared" si="5"/>
         <v>80000</v>
       </c>
-      <c r="F92" s="300"/>
+      <c r="F92" s="308"/>
     </row>
     <row r="93" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A93" s="293"/>
-      <c r="B93" s="290" t="s">
+      <c r="A93" s="301"/>
+      <c r="B93" s="298" t="s">
         <v>27</v>
       </c>
-      <c r="C93" s="291">
+      <c r="C93" s="299">
         <v>4</v>
       </c>
       <c r="D93" s="7">
@@ -5470,16 +5539,16 @@
         <f t="shared" si="5"/>
         <v>80000</v>
       </c>
-      <c r="F93" s="301"/>
+      <c r="F93" s="309"/>
     </row>
     <row r="94" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A94" s="289">
+      <c r="A94" s="297">
         <v>46004</v>
       </c>
-      <c r="B94" s="296" t="s">
+      <c r="B94" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C94" s="303">
+      <c r="C94" s="311">
         <v>8</v>
       </c>
       <c r="D94" s="7">
@@ -5489,17 +5558,17 @@
         <f t="shared" si="5"/>
         <v>80000</v>
       </c>
-      <c r="F94" s="299">
+      <c r="F94" s="307">
         <f>SUM(E94:E99)</f>
         <v>479000</v>
       </c>
     </row>
     <row r="95" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A95" s="292"/>
-      <c r="B95" s="296" t="s">
+      <c r="A95" s="300"/>
+      <c r="B95" s="304" t="s">
         <v>24</v>
       </c>
-      <c r="C95" s="303">
+      <c r="C95" s="311">
         <v>7.155</v>
       </c>
       <c r="D95" s="7">
@@ -5508,14 +5577,14 @@
       <c r="E95" s="7">
         <v>107000</v>
       </c>
-      <c r="F95" s="300"/>
+      <c r="F95" s="308"/>
     </row>
     <row r="96" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A96" s="292"/>
-      <c r="B96" s="296" t="s">
+      <c r="A96" s="300"/>
+      <c r="B96" s="304" t="s">
         <v>11</v>
       </c>
-      <c r="C96" s="303">
+      <c r="C96" s="311">
         <v>2</v>
       </c>
       <c r="D96" s="7">
@@ -5525,14 +5594,14 @@
         <f>SUM(C96*D96)</f>
         <v>76000</v>
       </c>
-      <c r="F96" s="300"/>
+      <c r="F96" s="308"/>
     </row>
     <row r="97" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A97" s="292"/>
-      <c r="B97" s="296" t="s">
+      <c r="A97" s="300"/>
+      <c r="B97" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C97" s="303">
+      <c r="C97" s="311">
         <v>2</v>
       </c>
       <c r="D97" s="7">
@@ -5542,14 +5611,14 @@
         <f>SUM(C97*D97)</f>
         <v>40000</v>
       </c>
-      <c r="F97" s="300"/>
+      <c r="F97" s="308"/>
     </row>
     <row r="98" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A98" s="292"/>
-      <c r="B98" s="296" t="s">
+      <c r="A98" s="300"/>
+      <c r="B98" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C98" s="303">
+      <c r="C98" s="311">
         <v>4</v>
       </c>
       <c r="D98" s="7">
@@ -5559,14 +5628,14 @@
         <f>SUM(C98*D98)</f>
         <v>96000</v>
       </c>
-      <c r="F98" s="300"/>
+      <c r="F98" s="308"/>
     </row>
     <row r="99" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A99" s="293"/>
-      <c r="B99" s="296" t="s">
+      <c r="A99" s="301"/>
+      <c r="B99" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="C99" s="303">
+      <c r="C99" s="311">
         <v>2</v>
       </c>
       <c r="D99" s="7">
@@ -5576,16 +5645,16 @@
         <f>SUM(C99*D99)</f>
         <v>80000</v>
       </c>
-      <c r="F99" s="301"/>
+      <c r="F99" s="309"/>
     </row>
     <row r="100" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A100" s="292">
+      <c r="A100" s="300">
         <v>46005</v>
       </c>
-      <c r="B100" s="296" t="s">
+      <c r="B100" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C100" s="303">
+      <c r="C100" s="311">
         <v>8</v>
       </c>
       <c r="D100" s="7">
@@ -5595,17 +5664,17 @@
         <f t="shared" ref="E100:E108" si="6">SUM(C100*D100)</f>
         <v>80000</v>
       </c>
-      <c r="F100" s="302">
+      <c r="F100" s="310">
         <f>SUM(E100:E108)</f>
         <v>506000</v>
       </c>
     </row>
     <row r="101" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A101" s="292"/>
-      <c r="B101" s="296" t="s">
+      <c r="A101" s="300"/>
+      <c r="B101" s="304" t="s">
         <v>24</v>
       </c>
-      <c r="C101" s="303">
+      <c r="C101" s="311">
         <v>8.23</v>
       </c>
       <c r="D101" s="7">
@@ -5614,14 +5683,14 @@
       <c r="E101" s="22">
         <v>123000</v>
       </c>
-      <c r="F101" s="303"/>
+      <c r="F101" s="311"/>
     </row>
     <row r="102" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A102" s="292"/>
-      <c r="B102" s="296" t="s">
+      <c r="A102" s="300"/>
+      <c r="B102" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C102" s="303">
+      <c r="C102" s="311">
         <v>2</v>
       </c>
       <c r="D102" s="7">
@@ -5631,14 +5700,14 @@
         <f t="shared" si="6"/>
         <v>40000</v>
       </c>
-      <c r="F102" s="303"/>
+      <c r="F102" s="311"/>
     </row>
     <row r="103" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A103" s="292"/>
-      <c r="B103" s="296" t="s">
+      <c r="A103" s="300"/>
+      <c r="B103" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="C103" s="303">
+      <c r="C103" s="311">
         <v>0.3</v>
       </c>
       <c r="D103" s="7">
@@ -5648,14 +5717,14 @@
         <f t="shared" si="6"/>
         <v>6000</v>
       </c>
-      <c r="F103" s="303"/>
+      <c r="F103" s="311"/>
     </row>
     <row r="104" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A104" s="292"/>
-      <c r="B104" s="296" t="s">
+      <c r="A104" s="300"/>
+      <c r="B104" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="C104" s="303">
+      <c r="C104" s="311">
         <v>1</v>
       </c>
       <c r="D104" s="7">
@@ -5665,14 +5734,14 @@
         <f t="shared" si="6"/>
         <v>15000</v>
       </c>
-      <c r="F104" s="303"/>
+      <c r="F104" s="311"/>
     </row>
     <row r="105" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A105" s="292"/>
-      <c r="B105" s="296" t="s">
+      <c r="A105" s="300"/>
+      <c r="B105" s="304" t="s">
         <v>36</v>
       </c>
-      <c r="C105" s="303">
+      <c r="C105" s="311">
         <v>1</v>
       </c>
       <c r="D105" s="7">
@@ -5682,14 +5751,14 @@
         <f t="shared" si="6"/>
         <v>48000</v>
       </c>
-      <c r="F105" s="303"/>
+      <c r="F105" s="311"/>
     </row>
     <row r="106" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A106" s="292"/>
-      <c r="B106" s="296" t="s">
+      <c r="A106" s="300"/>
+      <c r="B106" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C106" s="303">
+      <c r="C106" s="311">
         <v>5</v>
       </c>
       <c r="D106" s="7">
@@ -5699,14 +5768,14 @@
         <f t="shared" si="6"/>
         <v>120000</v>
       </c>
-      <c r="F106" s="303"/>
+      <c r="F106" s="311"/>
     </row>
     <row r="107" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A107" s="292"/>
-      <c r="B107" s="296" t="s">
+      <c r="A107" s="300"/>
+      <c r="B107" s="304" t="s">
         <v>32</v>
       </c>
-      <c r="C107" s="303">
+      <c r="C107" s="311">
         <v>1</v>
       </c>
       <c r="D107" s="7">
@@ -5716,14 +5785,14 @@
         <f t="shared" si="6"/>
         <v>49000</v>
       </c>
-      <c r="F107" s="303"/>
+      <c r="F107" s="311"/>
     </row>
     <row r="108" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A108" s="292"/>
-      <c r="B108" s="296" t="s">
+      <c r="A108" s="300"/>
+      <c r="B108" s="304" t="s">
         <v>37</v>
       </c>
-      <c r="C108" s="303">
+      <c r="C108" s="311">
         <v>1</v>
       </c>
       <c r="D108" s="7">
@@ -5733,36 +5802,36 @@
         <f t="shared" si="6"/>
         <v>25000</v>
       </c>
-      <c r="F108" s="303"/>
+      <c r="F108" s="311"/>
     </row>
     <row r="109" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A109" s="289">
+      <c r="A109" s="297">
         <v>46006</v>
       </c>
-      <c r="B109" s="296" t="s">
+      <c r="B109" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C109" s="303">
+      <c r="C109" s="311">
         <v>4</v>
       </c>
       <c r="D109" s="7">
         <v>10000</v>
       </c>
       <c r="E109" s="7">
-        <f t="shared" ref="E109:E154" si="7">SUM(C109*D109)</f>
+        <f t="shared" ref="E109:E156" si="7">SUM(C109*D109)</f>
         <v>40000</v>
       </c>
-      <c r="F109" s="299">
+      <c r="F109" s="307">
         <f>SUM(E109:E121)</f>
         <v>630000</v>
       </c>
     </row>
     <row r="110" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A110" s="292"/>
-      <c r="B110" s="296" t="s">
+      <c r="A110" s="300"/>
+      <c r="B110" s="304" t="s">
         <v>24</v>
       </c>
-      <c r="C110" s="303">
+      <c r="C110" s="311">
         <v>3.43</v>
       </c>
       <c r="D110" s="7">
@@ -5771,14 +5840,14 @@
       <c r="E110" s="7">
         <v>51000</v>
       </c>
-      <c r="F110" s="300"/>
+      <c r="F110" s="308"/>
     </row>
     <row r="111" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A111" s="292"/>
-      <c r="B111" s="296" t="s">
+      <c r="A111" s="300"/>
+      <c r="B111" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C111" s="303">
+      <c r="C111" s="311">
         <v>2</v>
       </c>
       <c r="D111" s="7">
@@ -5788,14 +5857,14 @@
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F111" s="300"/>
+      <c r="F111" s="308"/>
     </row>
     <row r="112" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A112" s="292"/>
-      <c r="B112" s="296" t="s">
+      <c r="A112" s="300"/>
+      <c r="B112" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="C112" s="303">
+      <c r="C112" s="311">
         <v>0.3</v>
       </c>
       <c r="D112" s="7">
@@ -5805,14 +5874,14 @@
         <f t="shared" si="7"/>
         <v>6000</v>
       </c>
-      <c r="F112" s="300"/>
+      <c r="F112" s="308"/>
     </row>
     <row r="113" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A113" s="292"/>
-      <c r="B113" s="296" t="s">
+      <c r="A113" s="300"/>
+      <c r="B113" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="C113" s="303">
+      <c r="C113" s="311">
         <v>2</v>
       </c>
       <c r="D113" s="7">
@@ -5822,14 +5891,14 @@
         <f t="shared" si="7"/>
         <v>30000</v>
       </c>
-      <c r="F113" s="300"/>
+      <c r="F113" s="308"/>
     </row>
     <row r="114" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A114" s="292"/>
-      <c r="B114" s="296" t="s">
+      <c r="A114" s="300"/>
+      <c r="B114" s="304" t="s">
         <v>36</v>
       </c>
-      <c r="C114" s="303">
+      <c r="C114" s="311">
         <v>2</v>
       </c>
       <c r="D114" s="7">
@@ -5839,14 +5908,14 @@
         <f t="shared" si="7"/>
         <v>96000</v>
       </c>
-      <c r="F114" s="300"/>
+      <c r="F114" s="308"/>
     </row>
     <row r="115" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A115" s="292"/>
-      <c r="B115" s="296" t="s">
+      <c r="A115" s="300"/>
+      <c r="B115" s="304" t="s">
         <v>38</v>
       </c>
-      <c r="C115" s="303">
+      <c r="C115" s="311">
         <v>1</v>
       </c>
       <c r="D115" s="7">
@@ -5856,14 +5925,14 @@
         <f t="shared" si="7"/>
         <v>45000</v>
       </c>
-      <c r="F115" s="300"/>
+      <c r="F115" s="308"/>
     </row>
     <row r="116" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A116" s="292"/>
-      <c r="B116" s="296" t="s">
+      <c r="A116" s="300"/>
+      <c r="B116" s="304" t="s">
         <v>11</v>
       </c>
-      <c r="C116" s="303">
+      <c r="C116" s="311">
         <v>1.2</v>
       </c>
       <c r="D116" s="7">
@@ -5872,14 +5941,14 @@
       <c r="E116" s="7">
         <v>46000</v>
       </c>
-      <c r="F116" s="300"/>
+      <c r="F116" s="308"/>
     </row>
     <row r="117" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A117" s="292"/>
-      <c r="B117" s="296" t="s">
+      <c r="A117" s="300"/>
+      <c r="B117" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C117" s="303">
+      <c r="C117" s="311">
         <v>0.5</v>
       </c>
       <c r="D117" s="7">
@@ -5889,14 +5958,14 @@
         <f t="shared" si="7"/>
         <v>15000</v>
       </c>
-      <c r="F117" s="300"/>
+      <c r="F117" s="308"/>
     </row>
     <row r="118" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A118" s="292"/>
-      <c r="B118" s="296" t="s">
+      <c r="A118" s="300"/>
+      <c r="B118" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C118" s="303">
+      <c r="C118" s="311">
         <v>3</v>
       </c>
       <c r="D118" s="7">
@@ -5906,14 +5975,14 @@
         <f t="shared" si="7"/>
         <v>72000</v>
       </c>
-      <c r="F118" s="300"/>
+      <c r="F118" s="308"/>
     </row>
     <row r="119" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A119" s="292"/>
-      <c r="B119" s="296" t="s">
+      <c r="A119" s="300"/>
+      <c r="B119" s="304" t="s">
         <v>32</v>
       </c>
-      <c r="C119" s="303">
+      <c r="C119" s="311">
         <v>1</v>
       </c>
       <c r="D119" s="7">
@@ -5923,14 +5992,14 @@
         <f t="shared" si="7"/>
         <v>49000</v>
       </c>
-      <c r="F119" s="300"/>
+      <c r="F119" s="308"/>
     </row>
     <row r="120" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A120" s="292"/>
-      <c r="B120" s="296" t="s">
+      <c r="A120" s="300"/>
+      <c r="B120" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="C120" s="303">
+      <c r="C120" s="311">
         <v>1</v>
       </c>
       <c r="D120" s="7">
@@ -5940,14 +6009,14 @@
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F120" s="300"/>
+      <c r="F120" s="308"/>
     </row>
     <row r="121" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A121" s="293"/>
-      <c r="B121" s="296" t="s">
+      <c r="A121" s="301"/>
+      <c r="B121" s="304" t="s">
         <v>27</v>
       </c>
-      <c r="C121" s="303">
+      <c r="C121" s="311">
         <v>5</v>
       </c>
       <c r="D121" s="7">
@@ -5957,16 +6026,16 @@
         <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="F121" s="301"/>
+      <c r="F121" s="309"/>
     </row>
     <row r="122" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A122" s="289">
+      <c r="A122" s="297">
         <v>46007</v>
       </c>
-      <c r="B122" s="296" t="s">
+      <c r="B122" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C122" s="303">
+      <c r="C122" s="311">
         <v>5</v>
       </c>
       <c r="D122" s="7">
@@ -5976,17 +6045,17 @@
         <f t="shared" si="7"/>
         <v>50000</v>
       </c>
-      <c r="F122" s="299">
+      <c r="F122" s="307">
         <f>SUM(E122:E128)</f>
         <v>412000</v>
       </c>
     </row>
     <row r="123" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A123" s="292"/>
-      <c r="B123" s="296" t="s">
+      <c r="A123" s="300"/>
+      <c r="B123" s="304" t="s">
         <v>24</v>
       </c>
-      <c r="C123" s="303">
+      <c r="C123" s="311">
         <v>6.15</v>
       </c>
       <c r="D123" s="7">
@@ -5995,14 +6064,14 @@
       <c r="E123" s="7">
         <v>92000</v>
       </c>
-      <c r="F123" s="300"/>
+      <c r="F123" s="308"/>
     </row>
     <row r="124" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A124" s="292"/>
-      <c r="B124" s="296" t="s">
+      <c r="A124" s="300"/>
+      <c r="B124" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C124" s="303">
+      <c r="C124" s="311">
         <v>2</v>
       </c>
       <c r="D124" s="7">
@@ -6012,14 +6081,14 @@
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F124" s="300"/>
+      <c r="F124" s="308"/>
     </row>
     <row r="125" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A125" s="292"/>
-      <c r="B125" s="296" t="s">
+      <c r="A125" s="300"/>
+      <c r="B125" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="C125" s="303">
+      <c r="C125" s="311">
         <v>0.3</v>
       </c>
       <c r="D125" s="7">
@@ -6028,14 +6097,14 @@
       <c r="E125" s="7">
         <v>5000</v>
       </c>
-      <c r="F125" s="300"/>
+      <c r="F125" s="308"/>
     </row>
     <row r="126" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A126" s="292"/>
-      <c r="B126" s="296" t="s">
+      <c r="A126" s="300"/>
+      <c r="B126" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C126" s="303">
+      <c r="C126" s="311">
         <v>4</v>
       </c>
       <c r="D126" s="7">
@@ -6045,14 +6114,14 @@
         <f t="shared" si="7"/>
         <v>96000</v>
       </c>
-      <c r="F126" s="300"/>
+      <c r="F126" s="308"/>
     </row>
     <row r="127" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A127" s="292"/>
-      <c r="B127" s="296" t="s">
+      <c r="A127" s="300"/>
+      <c r="B127" s="304" t="s">
         <v>32</v>
       </c>
-      <c r="C127" s="303">
+      <c r="C127" s="311">
         <v>1</v>
       </c>
       <c r="D127" s="7">
@@ -6062,14 +6131,14 @@
         <f t="shared" si="7"/>
         <v>49000</v>
       </c>
-      <c r="F127" s="300"/>
+      <c r="F127" s="308"/>
     </row>
     <row r="128" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A128" s="293"/>
-      <c r="B128" s="296" t="s">
+      <c r="A128" s="301"/>
+      <c r="B128" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="C128" s="303">
+      <c r="C128" s="311">
         <v>2</v>
       </c>
       <c r="D128" s="7">
@@ -6079,16 +6148,16 @@
         <f t="shared" si="7"/>
         <v>80000</v>
       </c>
-      <c r="F128" s="304"/>
+      <c r="F128" s="312"/>
     </row>
     <row r="129" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A129" s="297">
+      <c r="A129" s="305">
         <v>46007</v>
       </c>
-      <c r="B129" s="296" t="s">
+      <c r="B129" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="C129" s="303">
+      <c r="C129" s="311">
         <v>3</v>
       </c>
       <c r="D129" s="7">
@@ -6098,19 +6167,19 @@
         <f t="shared" si="7"/>
         <v>210000</v>
       </c>
-      <c r="F129" s="310">
+      <c r="F129" s="320">
         <f>SUM(E129)</f>
         <v>210000</v>
       </c>
     </row>
     <row r="130" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A130" s="289">
+      <c r="A130" s="297">
         <v>46008</v>
       </c>
-      <c r="B130" s="296" t="s">
+      <c r="B130" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C130" s="303">
+      <c r="C130" s="311">
         <v>3</v>
       </c>
       <c r="D130" s="7">
@@ -6120,17 +6189,17 @@
         <f t="shared" si="7"/>
         <v>60000</v>
       </c>
-      <c r="F130" s="299">
+      <c r="F130" s="307">
         <f>SUM(E130:E138)</f>
         <v>586000</v>
       </c>
     </row>
     <row r="131" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A131" s="292"/>
-      <c r="B131" s="296" t="s">
+      <c r="A131" s="300"/>
+      <c r="B131" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="C131" s="303">
+      <c r="C131" s="311">
         <v>3</v>
       </c>
       <c r="D131" s="7">
@@ -6140,14 +6209,14 @@
         <f t="shared" si="7"/>
         <v>210000</v>
       </c>
-      <c r="F131" s="300"/>
+      <c r="F131" s="308"/>
     </row>
     <row r="132" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A132" s="292"/>
-      <c r="B132" s="296" t="s">
+      <c r="A132" s="300"/>
+      <c r="B132" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C132" s="303">
+      <c r="C132" s="311">
         <v>4</v>
       </c>
       <c r="D132" s="7">
@@ -6157,14 +6226,14 @@
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F132" s="300"/>
+      <c r="F132" s="308"/>
     </row>
     <row r="133" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A133" s="292"/>
-      <c r="B133" s="296" t="s">
+      <c r="A133" s="300"/>
+      <c r="B133" s="304" t="s">
         <v>36</v>
       </c>
-      <c r="C133" s="303">
+      <c r="C133" s="311">
         <v>2</v>
       </c>
       <c r="D133" s="7">
@@ -6174,14 +6243,14 @@
         <f t="shared" si="7"/>
         <v>96000</v>
       </c>
-      <c r="F133" s="300"/>
+      <c r="F133" s="308"/>
     </row>
     <row r="134" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A134" s="292"/>
-      <c r="B134" s="296" t="s">
+      <c r="A134" s="300"/>
+      <c r="B134" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="C134" s="303">
+      <c r="C134" s="311">
         <v>0.3</v>
       </c>
       <c r="D134" s="7">
@@ -6190,14 +6259,14 @@
       <c r="E134" s="7">
         <v>5000</v>
       </c>
-      <c r="F134" s="300"/>
+      <c r="F134" s="308"/>
     </row>
     <row r="135" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A135" s="292"/>
-      <c r="B135" s="296" t="s">
+      <c r="A135" s="300"/>
+      <c r="B135" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C135" s="303">
+      <c r="C135" s="311">
         <v>0.5</v>
       </c>
       <c r="D135" s="7">
@@ -6207,14 +6276,14 @@
         <f t="shared" si="7"/>
         <v>15000</v>
       </c>
-      <c r="F135" s="300"/>
+      <c r="F135" s="308"/>
     </row>
     <row r="136" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A136" s="292"/>
-      <c r="B136" s="296" t="s">
+      <c r="A136" s="300"/>
+      <c r="B136" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="C136" s="303">
+      <c r="C136" s="311">
         <v>1</v>
       </c>
       <c r="D136" s="7">
@@ -6224,14 +6293,14 @@
         <f t="shared" si="7"/>
         <v>15000</v>
       </c>
-      <c r="F136" s="300"/>
+      <c r="F136" s="308"/>
     </row>
     <row r="137" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A137" s="292"/>
-      <c r="B137" s="296" t="s">
+      <c r="A137" s="300"/>
+      <c r="B137" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C137" s="303">
+      <c r="C137" s="311">
         <v>4</v>
       </c>
       <c r="D137" s="7">
@@ -6241,14 +6310,14 @@
         <f t="shared" si="7"/>
         <v>96000</v>
       </c>
-      <c r="F137" s="300"/>
+      <c r="F137" s="308"/>
     </row>
     <row r="138" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A138" s="293"/>
-      <c r="B138" s="296" t="s">
+      <c r="A138" s="301"/>
+      <c r="B138" s="304" t="s">
         <v>32</v>
       </c>
-      <c r="C138" s="303">
+      <c r="C138" s="311">
         <v>1</v>
       </c>
       <c r="D138" s="7">
@@ -6258,16 +6327,16 @@
         <f t="shared" si="7"/>
         <v>49000</v>
       </c>
-      <c r="F138" s="301"/>
+      <c r="F138" s="309"/>
     </row>
     <row r="139" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A139" s="289">
+      <c r="A139" s="297">
         <v>46009</v>
       </c>
-      <c r="B139" s="296" t="s">
+      <c r="B139" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C139" s="303">
+      <c r="C139" s="311">
         <v>5</v>
       </c>
       <c r="D139" s="7">
@@ -6277,17 +6346,17 @@
         <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="F139" s="299">
+      <c r="F139" s="307">
         <f>SUM(E139:E146)</f>
         <v>343000</v>
       </c>
     </row>
     <row r="140" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A140" s="292"/>
-      <c r="B140" s="296" t="s">
+      <c r="A140" s="300"/>
+      <c r="B140" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="C140" s="303">
+      <c r="C140" s="311">
         <v>1</v>
       </c>
       <c r="D140" s="7">
@@ -6297,14 +6366,14 @@
         <f t="shared" si="7"/>
         <v>70000</v>
       </c>
-      <c r="F140" s="300"/>
+      <c r="F140" s="308"/>
     </row>
     <row r="141" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A141" s="292"/>
-      <c r="B141" s="296" t="s">
+      <c r="A141" s="300"/>
+      <c r="B141" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C141" s="303">
+      <c r="C141" s="311">
         <v>4</v>
       </c>
       <c r="D141" s="7">
@@ -6314,14 +6383,14 @@
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="F141" s="300"/>
+      <c r="F141" s="308"/>
     </row>
     <row r="142" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A142" s="292"/>
-      <c r="B142" s="296" t="s">
+      <c r="A142" s="300"/>
+      <c r="B142" s="304" t="s">
         <v>36</v>
       </c>
-      <c r="C142" s="303">
+      <c r="C142" s="311">
         <v>1</v>
       </c>
       <c r="D142" s="7">
@@ -6331,14 +6400,14 @@
         <f t="shared" si="7"/>
         <v>48000</v>
       </c>
-      <c r="F142" s="300"/>
+      <c r="F142" s="308"/>
     </row>
     <row r="143" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A143" s="292"/>
-      <c r="B143" s="296" t="s">
+      <c r="A143" s="300"/>
+      <c r="B143" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="C143" s="303">
+      <c r="C143" s="311">
         <v>0.3</v>
       </c>
       <c r="D143" s="7">
@@ -6347,14 +6416,14 @@
       <c r="E143" s="7">
         <v>5000</v>
       </c>
-      <c r="F143" s="300"/>
+      <c r="F143" s="308"/>
     </row>
     <row r="144" s="244" customFormat="1" ht="14" customHeight="1" spans="1:6">
-      <c r="A144" s="292"/>
-      <c r="B144" s="296" t="s">
+      <c r="A144" s="300"/>
+      <c r="B144" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C144" s="303">
+      <c r="C144" s="311">
         <v>0.5</v>
       </c>
       <c r="D144" s="7">
@@ -6364,14 +6433,14 @@
         <f t="shared" si="7"/>
         <v>15000</v>
       </c>
-      <c r="F144" s="300"/>
+      <c r="F144" s="308"/>
     </row>
     <row r="145" s="244" customFormat="1" ht="14" customHeight="1" spans="1:7">
-      <c r="A145" s="292"/>
-      <c r="B145" s="296" t="s">
+      <c r="A145" s="300"/>
+      <c r="B145" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="C145" s="303">
+      <c r="C145" s="311">
         <v>1.15</v>
       </c>
       <c r="D145" s="7">
@@ -6380,15 +6449,15 @@
       <c r="E145" s="7">
         <v>17000</v>
       </c>
-      <c r="F145" s="300"/>
-      <c r="G145" s="277"/>
+      <c r="F145" s="308"/>
+      <c r="G145" s="281"/>
     </row>
     <row r="146" s="244" customFormat="1" spans="1:6">
-      <c r="A146" s="293"/>
-      <c r="B146" s="296" t="s">
+      <c r="A146" s="301"/>
+      <c r="B146" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C146" s="303">
+      <c r="C146" s="311">
         <v>2</v>
       </c>
       <c r="D146" s="7">
@@ -6398,16 +6467,16 @@
         <f t="shared" si="7"/>
         <v>48000</v>
       </c>
-      <c r="F146" s="301"/>
+      <c r="F146" s="309"/>
     </row>
     <row r="147" s="244" customFormat="1" spans="1:6">
-      <c r="A147" s="289">
+      <c r="A147" s="297">
         <v>46010</v>
       </c>
-      <c r="B147" s="296" t="s">
+      <c r="B147" s="304" t="s">
         <v>8</v>
       </c>
-      <c r="C147" s="303">
+      <c r="C147" s="311">
         <v>5</v>
       </c>
       <c r="D147" s="7">
@@ -6417,17 +6486,17 @@
         <f t="shared" si="7"/>
         <v>50000</v>
       </c>
-      <c r="F147" s="299">
+      <c r="F147" s="307">
         <f>SUM(E147:E156)</f>
         <v>620000</v>
       </c>
     </row>
     <row r="148" s="244" customFormat="1" spans="1:6">
-      <c r="A148" s="292"/>
-      <c r="B148" s="296" t="s">
+      <c r="A148" s="300"/>
+      <c r="B148" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="C148" s="303">
+      <c r="C148" s="311">
         <v>1</v>
       </c>
       <c r="D148" s="7">
@@ -6437,14 +6506,14 @@
         <f t="shared" si="7"/>
         <v>70000</v>
       </c>
-      <c r="F148" s="300"/>
+      <c r="F148" s="308"/>
     </row>
     <row r="149" s="244" customFormat="1" spans="1:6">
-      <c r="A149" s="292"/>
-      <c r="B149" s="296" t="s">
+      <c r="A149" s="300"/>
+      <c r="B149" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="C149" s="303">
+      <c r="C149" s="311">
         <v>3</v>
       </c>
       <c r="D149" s="7">
@@ -6454,14 +6523,14 @@
         <f t="shared" si="7"/>
         <v>60000</v>
       </c>
-      <c r="F149" s="300"/>
+      <c r="F149" s="308"/>
     </row>
     <row r="150" s="244" customFormat="1" spans="1:6">
-      <c r="A150" s="292"/>
-      <c r="B150" s="305" t="s">
+      <c r="A150" s="300"/>
+      <c r="B150" s="313" t="s">
         <v>11</v>
       </c>
-      <c r="C150" s="306">
+      <c r="C150" s="314">
         <v>1</v>
       </c>
       <c r="D150" s="134">
@@ -6471,14 +6540,14 @@
         <f t="shared" si="7"/>
         <v>38000</v>
       </c>
-      <c r="F150" s="300"/>
+      <c r="F150" s="308"/>
     </row>
     <row r="151" s="244" customFormat="1" spans="1:6">
-      <c r="A151" s="292"/>
-      <c r="B151" s="296" t="s">
+      <c r="A151" s="300"/>
+      <c r="B151" s="304" t="s">
         <v>24</v>
       </c>
-      <c r="C151" s="303">
+      <c r="C151" s="311">
         <v>9.26</v>
       </c>
       <c r="D151" s="7">
@@ -6487,14 +6556,14 @@
       <c r="E151" s="7">
         <v>139000</v>
       </c>
-      <c r="F151" s="300"/>
+      <c r="F151" s="308"/>
     </row>
     <row r="152" s="244" customFormat="1" spans="1:6">
-      <c r="A152" s="292"/>
-      <c r="B152" s="296" t="s">
+      <c r="A152" s="300"/>
+      <c r="B152" s="304" t="s">
         <v>26</v>
       </c>
-      <c r="C152" s="303">
+      <c r="C152" s="311">
         <v>0.2</v>
       </c>
       <c r="D152" s="7">
@@ -6504,14 +6573,14 @@
         <f t="shared" si="7"/>
         <v>16000</v>
       </c>
-      <c r="F152" s="300"/>
+      <c r="F152" s="308"/>
     </row>
     <row r="153" s="244" customFormat="1" spans="1:6">
-      <c r="A153" s="292"/>
-      <c r="B153" s="296" t="s">
+      <c r="A153" s="300"/>
+      <c r="B153" s="304" t="s">
         <v>25</v>
       </c>
-      <c r="C153" s="303">
+      <c r="C153" s="311">
         <v>0.3</v>
       </c>
       <c r="D153" s="7">
@@ -6520,14 +6589,14 @@
       <c r="E153" s="7">
         <v>11000</v>
       </c>
-      <c r="F153" s="300"/>
+      <c r="F153" s="308"/>
     </row>
     <row r="154" s="244" customFormat="1" spans="1:6">
-      <c r="A154" s="292"/>
-      <c r="B154" s="296" t="s">
+      <c r="A154" s="300"/>
+      <c r="B154" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C154" s="303">
+      <c r="C154" s="311">
         <v>4</v>
       </c>
       <c r="D154" s="7">
@@ -6537,50 +6606,50 @@
         <f t="shared" si="7"/>
         <v>96000</v>
       </c>
-      <c r="F154" s="300"/>
+      <c r="F154" s="308"/>
     </row>
     <row r="155" s="244" customFormat="1" spans="1:6">
-      <c r="A155" s="292"/>
-      <c r="B155" s="296" t="s">
+      <c r="A155" s="300"/>
+      <c r="B155" s="304" t="s">
         <v>28</v>
       </c>
-      <c r="C155" s="303">
+      <c r="C155" s="311">
         <v>2</v>
       </c>
       <c r="D155" s="7">
         <v>40000</v>
       </c>
       <c r="E155" s="7">
-        <f t="shared" ref="E155:E218" si="8">SUM(C155*D155)</f>
+        <f t="shared" si="7"/>
         <v>80000</v>
       </c>
-      <c r="F155" s="300"/>
+      <c r="F155" s="308"/>
     </row>
     <row r="156" s="244" customFormat="1" spans="1:6">
-      <c r="A156" s="293"/>
-      <c r="B156" s="296" t="s">
+      <c r="A156" s="301"/>
+      <c r="B156" s="304" t="s">
         <v>21</v>
       </c>
-      <c r="C156" s="303">
+      <c r="C156" s="311">
         <v>3</v>
       </c>
       <c r="D156" s="262">
         <v>20000</v>
       </c>
       <c r="E156" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>60000</v>
       </c>
-      <c r="F156" s="301"/>
-    </row>
-    <row r="157" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A157" s="307">
+      <c r="F156" s="309"/>
+    </row>
+    <row r="157" s="244" customFormat="1" spans="1:6">
+      <c r="A157" s="297">
         <v>46011</v>
       </c>
-      <c r="B157" s="296" t="s">
+      <c r="B157" s="304" t="s">
         <v>10</v>
       </c>
-      <c r="C157" s="303">
+      <c r="C157" s="311">
         <v>0.5</v>
       </c>
       <c r="D157" s="7">
@@ -6589,1601 +6658,1662 @@
       <c r="E157" s="7">
         <v>8000</v>
       </c>
-      <c r="F157" s="311">
+      <c r="F157" s="307">
         <f>SUM(E157:E159)</f>
         <v>119000</v>
       </c>
     </row>
-    <row r="158" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A158" s="308"/>
-      <c r="B158" s="296" t="s">
+    <row r="158" s="244" customFormat="1" spans="1:6">
+      <c r="A158" s="300"/>
+      <c r="B158" s="304" t="s">
         <v>22</v>
       </c>
-      <c r="C158" s="303">
+      <c r="C158" s="311">
         <v>0.5</v>
       </c>
       <c r="D158" s="7">
         <v>30000</v>
       </c>
       <c r="E158" s="7">
-        <f t="shared" si="8"/>
+        <f>SUM(C158*D158)</f>
         <v>15000</v>
       </c>
-      <c r="F158" s="312"/>
-    </row>
-    <row r="159" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A159" s="309"/>
-      <c r="B159" s="296" t="s">
+      <c r="F158" s="308"/>
+    </row>
+    <row r="159" s="244" customFormat="1" spans="1:6">
+      <c r="A159" s="301"/>
+      <c r="B159" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="C159" s="303">
+      <c r="C159" s="311">
         <v>4</v>
       </c>
       <c r="D159" s="7">
         <v>24000</v>
       </c>
       <c r="E159" s="7">
+        <f>SUM(C159*D159)</f>
+        <v>96000</v>
+      </c>
+      <c r="F159" s="309"/>
+    </row>
+    <row r="160" s="244" customFormat="1" spans="1:6">
+      <c r="A160" s="315">
+        <v>46012</v>
+      </c>
+      <c r="B160" s="316" t="s">
+        <v>39</v>
+      </c>
+      <c r="C160" s="47">
+        <v>1</v>
+      </c>
+      <c r="D160" s="317">
+        <v>200000</v>
+      </c>
+      <c r="E160" s="317">
+        <f t="shared" ref="E160:E169" si="8">C160*D160</f>
+        <v>200000</v>
+      </c>
+      <c r="F160" s="263">
+        <f>SUM(E160:E169)</f>
+        <v>1105000</v>
+      </c>
+    </row>
+    <row r="161" s="244" customFormat="1" spans="1:6">
+      <c r="A161" s="318"/>
+      <c r="B161" s="316" t="s">
+        <v>8</v>
+      </c>
+      <c r="C161" s="47">
+        <v>8</v>
+      </c>
+      <c r="D161" s="317">
+        <v>10000</v>
+      </c>
+      <c r="E161" s="317">
         <f t="shared" si="8"/>
-        <v>96000</v>
-      </c>
-      <c r="F159" s="313"/>
-    </row>
-    <row r="160" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A160" s="297"/>
-      <c r="B160" s="296"/>
-      <c r="C160" s="303"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="7">
+        <v>80000</v>
+      </c>
+      <c r="F161" s="264"/>
+    </row>
+    <row r="162" s="244" customFormat="1" spans="1:6">
+      <c r="A162" s="318"/>
+      <c r="B162" s="316" t="s">
+        <v>9</v>
+      </c>
+      <c r="C162" s="47">
+        <v>0.63</v>
+      </c>
+      <c r="D162" s="317">
+        <v>38000</v>
+      </c>
+      <c r="E162" s="317">
+        <v>24000</v>
+      </c>
+      <c r="F162" s="264"/>
+    </row>
+    <row r="163" s="244" customFormat="1" spans="1:6">
+      <c r="A163" s="318"/>
+      <c r="B163" s="316" t="s">
+        <v>40</v>
+      </c>
+      <c r="C163" s="47">
+        <v>4</v>
+      </c>
+      <c r="D163" s="317">
+        <v>20000</v>
+      </c>
+      <c r="E163" s="317">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F160" s="310"/>
-    </row>
-    <row r="161" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A161" s="297"/>
-      <c r="B161" s="296"/>
-      <c r="C161" s="303"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="7">
+        <v>80000</v>
+      </c>
+      <c r="F163" s="264"/>
+    </row>
+    <row r="164" s="244" customFormat="1" spans="1:6">
+      <c r="A164" s="318"/>
+      <c r="B164" s="316" t="s">
+        <v>41</v>
+      </c>
+      <c r="C164" s="47">
+        <v>2</v>
+      </c>
+      <c r="D164" s="317">
+        <v>70000</v>
+      </c>
+      <c r="E164" s="317">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F161" s="310"/>
-    </row>
-    <row r="162" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A162" s="297"/>
-      <c r="B162" s="296"/>
-      <c r="C162" s="303"/>
-      <c r="D162" s="7"/>
-      <c r="E162" s="7">
+        <v>140000</v>
+      </c>
+      <c r="F164" s="264"/>
+    </row>
+    <row r="165" s="244" customFormat="1" spans="1:6">
+      <c r="A165" s="318"/>
+      <c r="B165" s="316" t="s">
+        <v>24</v>
+      </c>
+      <c r="C165" s="47">
+        <v>5</v>
+      </c>
+      <c r="D165" s="317">
+        <v>15000</v>
+      </c>
+      <c r="E165" s="317">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F162" s="310"/>
-    </row>
-    <row r="163" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A163" s="297"/>
-      <c r="B163" s="296"/>
-      <c r="C163" s="303"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7">
+        <v>75000</v>
+      </c>
+      <c r="F165" s="264"/>
+    </row>
+    <row r="166" s="244" customFormat="1" spans="1:6">
+      <c r="A166" s="318"/>
+      <c r="B166" s="316" t="s">
+        <v>18</v>
+      </c>
+      <c r="C166" s="47">
+        <v>1</v>
+      </c>
+      <c r="D166" s="317">
+        <v>95000</v>
+      </c>
+      <c r="E166" s="317">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F163" s="310"/>
-    </row>
-    <row r="164" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A164" s="297"/>
-      <c r="B164" s="296"/>
-      <c r="C164" s="303"/>
-      <c r="D164" s="7"/>
-      <c r="E164" s="7">
+        <v>95000</v>
+      </c>
+      <c r="F166" s="264"/>
+    </row>
+    <row r="167" s="244" customFormat="1" spans="1:6">
+      <c r="A167" s="318"/>
+      <c r="B167" s="316" t="s">
+        <v>14</v>
+      </c>
+      <c r="C167" s="47">
+        <v>6</v>
+      </c>
+      <c r="D167" s="317">
+        <v>24000</v>
+      </c>
+      <c r="E167" s="317">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F164" s="310"/>
-    </row>
-    <row r="165" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A165" s="297"/>
-      <c r="B165" s="296"/>
-      <c r="C165" s="303"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7">
+        <v>144000</v>
+      </c>
+      <c r="F167" s="264"/>
+    </row>
+    <row r="168" s="244" customFormat="1" spans="1:6">
+      <c r="A168" s="318"/>
+      <c r="B168" s="316" t="s">
+        <v>19</v>
+      </c>
+      <c r="C168" s="47">
+        <v>3</v>
+      </c>
+      <c r="D168" s="317">
+        <v>40000</v>
+      </c>
+      <c r="E168" s="317">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F165" s="310">
-        <f>SUM(E165:E171)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A166" s="297"/>
-      <c r="B166" s="296"/>
-      <c r="C166" s="303"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7">
+        <v>120000</v>
+      </c>
+      <c r="F168" s="264"/>
+    </row>
+    <row r="169" s="244" customFormat="1" spans="1:6">
+      <c r="A169" s="319"/>
+      <c r="B169" s="316" t="s">
+        <v>32</v>
+      </c>
+      <c r="C169" s="47">
+        <v>3</v>
+      </c>
+      <c r="D169" s="317">
+        <v>49000</v>
+      </c>
+      <c r="E169" s="317">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F166" s="310"/>
-    </row>
-    <row r="167" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A167" s="297"/>
-      <c r="B167" s="296"/>
-      <c r="C167" s="303"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F167" s="310"/>
-    </row>
-    <row r="168" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A168" s="297"/>
-      <c r="B168" s="296"/>
-      <c r="C168" s="303"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F168" s="310"/>
-    </row>
-    <row r="169" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A169" s="297"/>
-      <c r="B169" s="296"/>
-      <c r="C169" s="303"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F169" s="310"/>
+        <v>147000</v>
+      </c>
+      <c r="F169" s="265"/>
     </row>
     <row r="170" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A170" s="297"/>
-      <c r="B170" s="296"/>
-      <c r="C170" s="303"/>
+      <c r="A170" s="305"/>
+      <c r="B170" s="304"/>
+      <c r="C170" s="311"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F170" s="310"/>
+        <f t="shared" ref="E170:E218" si="9">SUM(C170*D170)</f>
+        <v>0</v>
+      </c>
+      <c r="F170" s="320"/>
     </row>
     <row r="171" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A171" s="297"/>
-      <c r="B171" s="296"/>
-      <c r="C171" s="303"/>
+      <c r="A171" s="305"/>
+      <c r="B171" s="304"/>
+      <c r="C171" s="311"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F171" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F171" s="320"/>
     </row>
     <row r="172" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A172" s="297"/>
-      <c r="B172" s="296"/>
-      <c r="C172" s="303"/>
+      <c r="A172" s="305"/>
+      <c r="B172" s="304"/>
+      <c r="C172" s="311"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F172" s="310">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F172" s="320">
         <f>SUM(E172:E181)</f>
         <v>0</v>
       </c>
     </row>
     <row r="173" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A173" s="297"/>
-      <c r="B173" s="296"/>
-      <c r="C173" s="303"/>
+      <c r="A173" s="305"/>
+      <c r="B173" s="304"/>
+      <c r="C173" s="311"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F173" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F173" s="320"/>
     </row>
     <row r="174" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A174" s="297"/>
-      <c r="B174" s="296"/>
-      <c r="C174" s="303"/>
+      <c r="A174" s="305"/>
+      <c r="B174" s="304"/>
+      <c r="C174" s="311"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F174" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F174" s="320"/>
     </row>
     <row r="175" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A175" s="297"/>
-      <c r="B175" s="296"/>
-      <c r="C175" s="303"/>
+      <c r="A175" s="305"/>
+      <c r="B175" s="304"/>
+      <c r="C175" s="311"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F175" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F175" s="320"/>
     </row>
     <row r="176" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A176" s="297"/>
-      <c r="B176" s="296"/>
-      <c r="C176" s="303"/>
+      <c r="A176" s="305"/>
+      <c r="B176" s="304"/>
+      <c r="C176" s="311"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F176" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F176" s="320"/>
     </row>
     <row r="177" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A177" s="297"/>
-      <c r="B177" s="296"/>
-      <c r="C177" s="303"/>
+      <c r="A177" s="305"/>
+      <c r="B177" s="304"/>
+      <c r="C177" s="311"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F177" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F177" s="320"/>
     </row>
     <row r="178" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A178" s="297"/>
-      <c r="B178" s="296"/>
-      <c r="C178" s="303"/>
+      <c r="A178" s="305"/>
+      <c r="B178" s="304"/>
+      <c r="C178" s="311"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F178" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F178" s="320"/>
     </row>
     <row r="179" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A179" s="297"/>
-      <c r="B179" s="296"/>
-      <c r="C179" s="303"/>
+      <c r="A179" s="305"/>
+      <c r="B179" s="304"/>
+      <c r="C179" s="311"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F179" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F179" s="320"/>
     </row>
     <row r="180" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A180" s="297"/>
-      <c r="B180" s="296"/>
-      <c r="C180" s="303"/>
+      <c r="A180" s="305"/>
+      <c r="B180" s="304"/>
+      <c r="C180" s="311"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F180" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F180" s="320"/>
     </row>
     <row r="181" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A181" s="297"/>
-      <c r="B181" s="296"/>
-      <c r="C181" s="303"/>
+      <c r="A181" s="305"/>
+      <c r="B181" s="304"/>
+      <c r="C181" s="311"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F181" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F181" s="320"/>
     </row>
     <row r="182" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A182" s="297"/>
-      <c r="B182" s="296"/>
-      <c r="C182" s="303"/>
+      <c r="A182" s="305"/>
+      <c r="B182" s="304"/>
+      <c r="C182" s="311"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F182" s="310">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F182" s="320">
         <f>SUM(E182:E195)</f>
         <v>0</v>
       </c>
     </row>
     <row r="183" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A183" s="297"/>
-      <c r="B183" s="296"/>
-      <c r="C183" s="303"/>
+      <c r="A183" s="305"/>
+      <c r="B183" s="304"/>
+      <c r="C183" s="311"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F183" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F183" s="320"/>
     </row>
     <row r="184" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A184" s="297"/>
-      <c r="B184" s="296"/>
-      <c r="C184" s="303"/>
+      <c r="A184" s="305"/>
+      <c r="B184" s="304"/>
+      <c r="C184" s="311"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F184" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F184" s="320"/>
     </row>
     <row r="185" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A185" s="297"/>
-      <c r="B185" s="296"/>
-      <c r="C185" s="303"/>
+      <c r="A185" s="305"/>
+      <c r="B185" s="304"/>
+      <c r="C185" s="311"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F185" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F185" s="320"/>
     </row>
     <row r="186" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A186" s="297"/>
-      <c r="B186" s="296"/>
-      <c r="C186" s="303"/>
+      <c r="A186" s="305"/>
+      <c r="B186" s="304"/>
+      <c r="C186" s="311"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F186" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F186" s="320"/>
     </row>
     <row r="187" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A187" s="297"/>
-      <c r="B187" s="296"/>
-      <c r="C187" s="303"/>
+      <c r="A187" s="305"/>
+      <c r="B187" s="304"/>
+      <c r="C187" s="311"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F187" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F187" s="320"/>
     </row>
     <row r="188" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A188" s="297"/>
-      <c r="B188" s="296"/>
-      <c r="C188" s="303"/>
+      <c r="A188" s="305"/>
+      <c r="B188" s="304"/>
+      <c r="C188" s="311"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F188" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F188" s="320"/>
     </row>
     <row r="189" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A189" s="297"/>
-      <c r="B189" s="296"/>
-      <c r="C189" s="303"/>
+      <c r="A189" s="305"/>
+      <c r="B189" s="304"/>
+      <c r="C189" s="311"/>
       <c r="D189" s="7"/>
       <c r="E189" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F189" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F189" s="320"/>
     </row>
     <row r="190" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A190" s="297"/>
-      <c r="B190" s="296"/>
-      <c r="C190" s="303"/>
+      <c r="A190" s="305"/>
+      <c r="B190" s="304"/>
+      <c r="C190" s="311"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F190" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F190" s="320"/>
     </row>
     <row r="191" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A191" s="297"/>
-      <c r="B191" s="296"/>
-      <c r="C191" s="303"/>
+      <c r="A191" s="305"/>
+      <c r="B191" s="304"/>
+      <c r="C191" s="311"/>
       <c r="D191" s="7"/>
       <c r="E191" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F191" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F191" s="320"/>
     </row>
     <row r="192" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A192" s="297"/>
-      <c r="B192" s="296"/>
-      <c r="C192" s="303"/>
+      <c r="A192" s="305"/>
+      <c r="B192" s="304"/>
+      <c r="C192" s="311"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F192" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F192" s="320"/>
     </row>
     <row r="193" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A193" s="297"/>
-      <c r="B193" s="296"/>
-      <c r="C193" s="303"/>
+      <c r="A193" s="305"/>
+      <c r="B193" s="304"/>
+      <c r="C193" s="311"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F193" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F193" s="320"/>
     </row>
     <row r="194" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A194" s="297"/>
-      <c r="B194" s="296"/>
-      <c r="C194" s="303"/>
+      <c r="A194" s="305"/>
+      <c r="B194" s="304"/>
+      <c r="C194" s="311"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F194" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F194" s="320"/>
     </row>
     <row r="195" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A195" s="297"/>
-      <c r="B195" s="296"/>
-      <c r="C195" s="303"/>
+      <c r="A195" s="305"/>
+      <c r="B195" s="304"/>
+      <c r="C195" s="311"/>
       <c r="D195" s="7"/>
       <c r="E195" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F195" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F195" s="320"/>
     </row>
     <row r="196" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A196" s="297"/>
-      <c r="B196" s="296"/>
-      <c r="C196" s="303"/>
+      <c r="A196" s="305"/>
+      <c r="B196" s="304"/>
+      <c r="C196" s="311"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F196" s="310">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F196" s="320">
         <f>SUM(E196)</f>
         <v>0</v>
       </c>
     </row>
     <row r="197" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A197" s="297"/>
-      <c r="B197" s="296"/>
-      <c r="C197" s="303"/>
+      <c r="A197" s="305"/>
+      <c r="B197" s="304"/>
+      <c r="C197" s="311"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F197" s="310">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F197" s="320">
         <f>SUM(E197:E212)</f>
         <v>0</v>
       </c>
     </row>
     <row r="198" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A198" s="297"/>
-      <c r="B198" s="296"/>
-      <c r="C198" s="303"/>
+      <c r="A198" s="305"/>
+      <c r="B198" s="304"/>
+      <c r="C198" s="311"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F198" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F198" s="320"/>
     </row>
     <row r="199" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A199" s="297"/>
-      <c r="B199" s="296"/>
-      <c r="C199" s="303"/>
+      <c r="A199" s="305"/>
+      <c r="B199" s="304"/>
+      <c r="C199" s="311"/>
       <c r="D199" s="7"/>
       <c r="E199" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F199" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F199" s="320"/>
     </row>
     <row r="200" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A200" s="297"/>
-      <c r="B200" s="296"/>
-      <c r="C200" s="303"/>
+      <c r="A200" s="305"/>
+      <c r="B200" s="304"/>
+      <c r="C200" s="311"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F200" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F200" s="320"/>
     </row>
     <row r="201" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A201" s="297"/>
-      <c r="B201" s="296"/>
-      <c r="C201" s="303"/>
+      <c r="A201" s="305"/>
+      <c r="B201" s="304"/>
+      <c r="C201" s="311"/>
       <c r="D201" s="7"/>
       <c r="E201" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F201" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F201" s="320"/>
     </row>
     <row r="202" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A202" s="297"/>
-      <c r="B202" s="296"/>
-      <c r="C202" s="303"/>
+      <c r="A202" s="305"/>
+      <c r="B202" s="304"/>
+      <c r="C202" s="311"/>
       <c r="D202" s="7"/>
       <c r="E202" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F202" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F202" s="320"/>
     </row>
     <row r="203" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A203" s="297"/>
-      <c r="B203" s="296"/>
-      <c r="C203" s="303"/>
+      <c r="A203" s="305"/>
+      <c r="B203" s="304"/>
+      <c r="C203" s="311"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F203" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F203" s="320"/>
     </row>
     <row r="204" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A204" s="297"/>
-      <c r="B204" s="296"/>
-      <c r="C204" s="303"/>
+      <c r="A204" s="305"/>
+      <c r="B204" s="304"/>
+      <c r="C204" s="311"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F204" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F204" s="320"/>
     </row>
     <row r="205" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A205" s="297"/>
-      <c r="B205" s="296"/>
-      <c r="C205" s="303"/>
+      <c r="A205" s="305"/>
+      <c r="B205" s="304"/>
+      <c r="C205" s="311"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F205" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F205" s="320"/>
     </row>
     <row r="206" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A206" s="297"/>
-      <c r="B206" s="296"/>
-      <c r="C206" s="303"/>
+      <c r="A206" s="305"/>
+      <c r="B206" s="304"/>
+      <c r="C206" s="311"/>
       <c r="D206" s="7"/>
       <c r="E206" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F206" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F206" s="320"/>
     </row>
     <row r="207" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A207" s="297"/>
-      <c r="B207" s="296"/>
-      <c r="C207" s="303"/>
+      <c r="A207" s="305"/>
+      <c r="B207" s="304"/>
+      <c r="C207" s="311"/>
       <c r="D207" s="7"/>
       <c r="E207" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F207" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F207" s="320"/>
     </row>
     <row r="208" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A208" s="297"/>
-      <c r="B208" s="296"/>
-      <c r="C208" s="303"/>
+      <c r="A208" s="305"/>
+      <c r="B208" s="304"/>
+      <c r="C208" s="311"/>
       <c r="D208" s="7"/>
       <c r="E208" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F208" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F208" s="320"/>
     </row>
     <row r="209" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A209" s="297"/>
-      <c r="B209" s="296"/>
-      <c r="C209" s="303"/>
+      <c r="A209" s="305"/>
+      <c r="B209" s="304"/>
+      <c r="C209" s="311"/>
       <c r="D209" s="7"/>
       <c r="E209" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F209" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F209" s="320"/>
     </row>
     <row r="210" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A210" s="297"/>
-      <c r="B210" s="296"/>
-      <c r="C210" s="303"/>
+      <c r="A210" s="305"/>
+      <c r="B210" s="304"/>
+      <c r="C210" s="311"/>
       <c r="D210" s="7"/>
       <c r="E210" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F210" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F210" s="320"/>
     </row>
     <row r="211" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A211" s="297"/>
-      <c r="B211" s="305"/>
-      <c r="C211" s="306"/>
+      <c r="A211" s="305"/>
+      <c r="B211" s="313"/>
+      <c r="C211" s="314"/>
       <c r="D211" s="134"/>
       <c r="E211" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F211" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F211" s="320"/>
     </row>
     <row r="212" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A212" s="297"/>
-      <c r="B212" s="296"/>
-      <c r="C212" s="303"/>
+      <c r="A212" s="305"/>
+      <c r="B212" s="304"/>
+      <c r="C212" s="311"/>
       <c r="D212" s="7"/>
       <c r="E212" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F212" s="310"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F212" s="320"/>
     </row>
     <row r="213" s="244" customFormat="1" spans="1:6">
-      <c r="A213" s="289"/>
-      <c r="B213" s="296"/>
-      <c r="C213" s="303"/>
+      <c r="A213" s="297"/>
+      <c r="B213" s="304"/>
+      <c r="C213" s="311"/>
       <c r="D213" s="7"/>
       <c r="E213" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F213" s="299">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F213" s="307">
         <f>SUM(E213:E220)</f>
         <v>0</v>
       </c>
     </row>
     <row r="214" s="244" customFormat="1" spans="1:6">
-      <c r="A214" s="292"/>
-      <c r="B214" s="296"/>
-      <c r="C214" s="303"/>
+      <c r="A214" s="300"/>
+      <c r="B214" s="304"/>
+      <c r="C214" s="311"/>
       <c r="D214" s="7"/>
       <c r="E214" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F214" s="300"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F214" s="308"/>
     </row>
     <row r="215" s="244" customFormat="1" spans="1:6">
-      <c r="A215" s="292"/>
-      <c r="B215" s="296"/>
-      <c r="C215" s="303"/>
+      <c r="A215" s="300"/>
+      <c r="B215" s="304"/>
+      <c r="C215" s="311"/>
       <c r="D215" s="7"/>
       <c r="E215" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F215" s="300"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F215" s="308"/>
     </row>
     <row r="216" s="244" customFormat="1" spans="1:6">
-      <c r="A216" s="292"/>
-      <c r="B216" s="296"/>
-      <c r="C216" s="303"/>
+      <c r="A216" s="300"/>
+      <c r="B216" s="304"/>
+      <c r="C216" s="311"/>
       <c r="D216" s="7"/>
       <c r="E216" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F216" s="300"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F216" s="308"/>
     </row>
     <row r="217" s="244" customFormat="1" spans="1:6">
-      <c r="A217" s="292"/>
-      <c r="B217" s="296"/>
-      <c r="C217" s="303"/>
+      <c r="A217" s="300"/>
+      <c r="B217" s="304"/>
+      <c r="C217" s="311"/>
       <c r="D217" s="7"/>
       <c r="E217" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F217" s="300"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F217" s="308"/>
     </row>
     <row r="218" s="244" customFormat="1" spans="1:6">
-      <c r="A218" s="292"/>
-      <c r="B218" s="296"/>
-      <c r="C218" s="303"/>
+      <c r="A218" s="300"/>
+      <c r="B218" s="304"/>
+      <c r="C218" s="311"/>
       <c r="D218" s="7"/>
       <c r="E218" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F218" s="300"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F218" s="308"/>
     </row>
     <row r="219" s="244" customFormat="1" spans="1:6">
-      <c r="A219" s="292"/>
-      <c r="B219" s="296"/>
-      <c r="C219" s="303"/>
+      <c r="A219" s="300"/>
+      <c r="B219" s="304"/>
+      <c r="C219" s="311"/>
       <c r="D219" s="7"/>
       <c r="E219" s="7">
-        <f t="shared" ref="E219:E282" si="9">SUM(C219*D219)</f>
-        <v>0</v>
-      </c>
-      <c r="F219" s="300"/>
+        <f t="shared" ref="E219:E282" si="10">SUM(C219*D219)</f>
+        <v>0</v>
+      </c>
+      <c r="F219" s="308"/>
     </row>
     <row r="220" s="244" customFormat="1" spans="1:6">
-      <c r="A220" s="293"/>
-      <c r="B220" s="296"/>
-      <c r="C220" s="303"/>
+      <c r="A220" s="301"/>
+      <c r="B220" s="304"/>
+      <c r="C220" s="311"/>
       <c r="D220" s="7"/>
       <c r="E220" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F220" s="301"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F220" s="309"/>
     </row>
     <row r="221" s="244" customFormat="1" spans="1:6">
-      <c r="A221" s="289"/>
-      <c r="B221" s="296"/>
-      <c r="C221" s="303"/>
+      <c r="A221" s="297"/>
+      <c r="B221" s="304"/>
+      <c r="C221" s="311"/>
       <c r="D221" s="7"/>
       <c r="E221" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F221" s="299">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F221" s="307">
         <f>SUM(E221:E232)</f>
         <v>0</v>
       </c>
     </row>
     <row r="222" s="244" customFormat="1" spans="1:6">
-      <c r="A222" s="292"/>
-      <c r="B222" s="296"/>
-      <c r="C222" s="303"/>
+      <c r="A222" s="300"/>
+      <c r="B222" s="304"/>
+      <c r="C222" s="311"/>
       <c r="D222" s="7"/>
       <c r="E222" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F222" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F222" s="308"/>
     </row>
     <row r="223" s="244" customFormat="1" spans="1:6">
-      <c r="A223" s="292"/>
-      <c r="B223" s="296"/>
-      <c r="C223" s="303"/>
+      <c r="A223" s="300"/>
+      <c r="B223" s="304"/>
+      <c r="C223" s="311"/>
       <c r="D223" s="7"/>
       <c r="E223" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F223" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F223" s="308"/>
     </row>
     <row r="224" s="244" customFormat="1" spans="1:6">
-      <c r="A224" s="292"/>
-      <c r="B224" s="296"/>
-      <c r="C224" s="303"/>
+      <c r="A224" s="300"/>
+      <c r="B224" s="304"/>
+      <c r="C224" s="311"/>
       <c r="D224" s="7"/>
       <c r="E224" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F224" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F224" s="308"/>
     </row>
     <row r="225" s="244" customFormat="1" spans="1:6">
-      <c r="A225" s="292"/>
-      <c r="B225" s="296"/>
-      <c r="C225" s="303"/>
+      <c r="A225" s="300"/>
+      <c r="B225" s="304"/>
+      <c r="C225" s="311"/>
       <c r="D225" s="7"/>
       <c r="E225" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F225" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F225" s="308"/>
     </row>
     <row r="226" s="244" customFormat="1" spans="1:6">
-      <c r="A226" s="292"/>
-      <c r="B226" s="296"/>
-      <c r="C226" s="303"/>
+      <c r="A226" s="300"/>
+      <c r="B226" s="304"/>
+      <c r="C226" s="311"/>
       <c r="D226" s="7"/>
       <c r="E226" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F226" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F226" s="308"/>
     </row>
     <row r="227" s="244" customFormat="1" spans="1:6">
-      <c r="A227" s="292"/>
-      <c r="B227" s="296"/>
-      <c r="C227" s="303"/>
+      <c r="A227" s="300"/>
+      <c r="B227" s="304"/>
+      <c r="C227" s="311"/>
       <c r="D227" s="7"/>
       <c r="E227" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F227" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F227" s="308"/>
     </row>
     <row r="228" s="244" customFormat="1" spans="1:6">
-      <c r="A228" s="292"/>
-      <c r="B228" s="296"/>
-      <c r="C228" s="303"/>
+      <c r="A228" s="300"/>
+      <c r="B228" s="304"/>
+      <c r="C228" s="311"/>
       <c r="D228" s="7"/>
       <c r="E228" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F228" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F228" s="308"/>
     </row>
     <row r="229" s="244" customFormat="1" spans="1:6">
-      <c r="A229" s="292"/>
-      <c r="B229" s="296"/>
-      <c r="C229" s="303"/>
+      <c r="A229" s="300"/>
+      <c r="B229" s="304"/>
+      <c r="C229" s="311"/>
       <c r="D229" s="7"/>
       <c r="E229" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F229" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F229" s="308"/>
     </row>
     <row r="230" s="244" customFormat="1" spans="1:6">
-      <c r="A230" s="292"/>
-      <c r="B230" s="296"/>
-      <c r="C230" s="303"/>
+      <c r="A230" s="300"/>
+      <c r="B230" s="304"/>
+      <c r="C230" s="311"/>
       <c r="D230" s="7"/>
       <c r="E230" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F230" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F230" s="308"/>
     </row>
     <row r="231" s="244" customFormat="1" spans="1:6">
-      <c r="A231" s="292"/>
-      <c r="B231" s="296"/>
-      <c r="C231" s="303"/>
+      <c r="A231" s="300"/>
+      <c r="B231" s="304"/>
+      <c r="C231" s="311"/>
       <c r="D231" s="7"/>
       <c r="E231" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F231" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F231" s="308"/>
     </row>
     <row r="232" s="244" customFormat="1" spans="1:6">
-      <c r="A232" s="293"/>
-      <c r="B232" s="296"/>
-      <c r="C232" s="303"/>
+      <c r="A232" s="301"/>
+      <c r="B232" s="304"/>
+      <c r="C232" s="311"/>
       <c r="D232" s="7"/>
       <c r="E232" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F232" s="301"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F232" s="309"/>
     </row>
     <row r="233" s="244" customFormat="1" spans="1:6">
-      <c r="A233" s="289"/>
-      <c r="B233" s="296"/>
-      <c r="C233" s="303"/>
+      <c r="A233" s="297"/>
+      <c r="B233" s="304"/>
+      <c r="C233" s="311"/>
       <c r="D233" s="7"/>
       <c r="E233" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F233" s="299">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F233" s="307">
         <f>SUM(E233:E241)</f>
         <v>0</v>
       </c>
     </row>
     <row r="234" s="244" customFormat="1" spans="1:6">
-      <c r="A234" s="292"/>
-      <c r="B234" s="296"/>
-      <c r="C234" s="303"/>
+      <c r="A234" s="300"/>
+      <c r="B234" s="304"/>
+      <c r="C234" s="311"/>
       <c r="D234" s="7"/>
       <c r="E234" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F234" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F234" s="308"/>
     </row>
     <row r="235" s="244" customFormat="1" spans="1:6">
-      <c r="A235" s="292"/>
-      <c r="B235" s="296"/>
-      <c r="C235" s="303"/>
+      <c r="A235" s="300"/>
+      <c r="B235" s="304"/>
+      <c r="C235" s="311"/>
       <c r="D235" s="7"/>
       <c r="E235" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F235" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F235" s="308"/>
     </row>
     <row r="236" s="244" customFormat="1" spans="1:6">
-      <c r="A236" s="292"/>
-      <c r="B236" s="296"/>
-      <c r="C236" s="303"/>
+      <c r="A236" s="300"/>
+      <c r="B236" s="304"/>
+      <c r="C236" s="311"/>
       <c r="D236" s="7"/>
       <c r="E236" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F236" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F236" s="308"/>
     </row>
     <row r="237" s="244" customFormat="1" spans="1:6">
-      <c r="A237" s="292"/>
-      <c r="B237" s="296"/>
-      <c r="C237" s="303"/>
+      <c r="A237" s="300"/>
+      <c r="B237" s="304"/>
+      <c r="C237" s="311"/>
       <c r="D237" s="7"/>
       <c r="E237" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F237" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F237" s="308"/>
     </row>
     <row r="238" s="244" customFormat="1" spans="1:6">
-      <c r="A238" s="292"/>
-      <c r="B238" s="296"/>
-      <c r="C238" s="303"/>
+      <c r="A238" s="300"/>
+      <c r="B238" s="304"/>
+      <c r="C238" s="311"/>
       <c r="D238" s="7"/>
       <c r="E238" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F238" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F238" s="308"/>
     </row>
     <row r="239" s="244" customFormat="1" spans="1:6">
-      <c r="A239" s="292"/>
-      <c r="B239" s="296"/>
-      <c r="C239" s="303"/>
+      <c r="A239" s="300"/>
+      <c r="B239" s="304"/>
+      <c r="C239" s="311"/>
       <c r="D239" s="7"/>
       <c r="E239" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F239" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F239" s="308"/>
     </row>
     <row r="240" s="244" customFormat="1" spans="1:6">
-      <c r="A240" s="292"/>
-      <c r="B240" s="296"/>
-      <c r="C240" s="303"/>
+      <c r="A240" s="300"/>
+      <c r="B240" s="304"/>
+      <c r="C240" s="311"/>
       <c r="D240" s="7"/>
       <c r="E240" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F240" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F240" s="308"/>
     </row>
     <row r="241" s="244" customFormat="1" spans="1:6">
-      <c r="A241" s="293"/>
-      <c r="B241" s="296"/>
-      <c r="C241" s="303"/>
+      <c r="A241" s="301"/>
+      <c r="B241" s="304"/>
+      <c r="C241" s="311"/>
       <c r="D241" s="7"/>
       <c r="E241" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F241" s="301"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F241" s="309"/>
     </row>
     <row r="242" s="244" customFormat="1" spans="1:6">
-      <c r="A242" s="289"/>
-      <c r="B242" s="296"/>
-      <c r="C242" s="303"/>
+      <c r="A242" s="297"/>
+      <c r="B242" s="304"/>
+      <c r="C242" s="311"/>
       <c r="D242" s="7"/>
       <c r="E242" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F242" s="299">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F242" s="307">
         <f>SUM(E242:E252)</f>
         <v>0</v>
       </c>
     </row>
     <row r="243" s="244" customFormat="1" spans="1:6">
-      <c r="A243" s="292"/>
-      <c r="B243" s="296"/>
-      <c r="C243" s="303"/>
+      <c r="A243" s="300"/>
+      <c r="B243" s="304"/>
+      <c r="C243" s="311"/>
       <c r="D243" s="7"/>
       <c r="E243" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F243" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F243" s="308"/>
     </row>
     <row r="244" s="244" customFormat="1" spans="1:6">
-      <c r="A244" s="292"/>
-      <c r="B244" s="296"/>
-      <c r="C244" s="303"/>
+      <c r="A244" s="300"/>
+      <c r="B244" s="304"/>
+      <c r="C244" s="311"/>
       <c r="D244" s="7"/>
       <c r="E244" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F244" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F244" s="308"/>
     </row>
     <row r="245" s="244" customFormat="1" spans="1:6">
-      <c r="A245" s="292"/>
-      <c r="B245" s="296"/>
-      <c r="C245" s="303"/>
+      <c r="A245" s="300"/>
+      <c r="B245" s="304"/>
+      <c r="C245" s="311"/>
       <c r="D245" s="7"/>
       <c r="E245" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F245" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F245" s="308"/>
     </row>
     <row r="246" s="244" customFormat="1" spans="1:6">
-      <c r="A246" s="292"/>
-      <c r="B246" s="296"/>
-      <c r="C246" s="303"/>
+      <c r="A246" s="300"/>
+      <c r="B246" s="304"/>
+      <c r="C246" s="311"/>
       <c r="D246" s="7"/>
       <c r="E246" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F246" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F246" s="308"/>
     </row>
     <row r="247" s="244" customFormat="1" spans="1:6">
-      <c r="A247" s="292"/>
-      <c r="B247" s="296"/>
-      <c r="C247" s="303"/>
+      <c r="A247" s="300"/>
+      <c r="B247" s="304"/>
+      <c r="C247" s="311"/>
       <c r="D247" s="7"/>
       <c r="E247" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F247" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F247" s="308"/>
     </row>
     <row r="248" s="244" customFormat="1" spans="1:6">
-      <c r="A248" s="292"/>
-      <c r="B248" s="296"/>
-      <c r="C248" s="303"/>
+      <c r="A248" s="300"/>
+      <c r="B248" s="304"/>
+      <c r="C248" s="311"/>
       <c r="D248" s="7"/>
       <c r="E248" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F248" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F248" s="308"/>
     </row>
     <row r="249" s="244" customFormat="1" spans="1:6">
-      <c r="A249" s="292"/>
-      <c r="B249" s="296"/>
-      <c r="C249" s="303"/>
+      <c r="A249" s="300"/>
+      <c r="B249" s="304"/>
+      <c r="C249" s="311"/>
       <c r="D249" s="7"/>
       <c r="E249" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F249" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F249" s="308"/>
     </row>
     <row r="250" s="244" customFormat="1" spans="1:6">
-      <c r="A250" s="292"/>
-      <c r="B250" s="296"/>
-      <c r="C250" s="303"/>
+      <c r="A250" s="300"/>
+      <c r="B250" s="304"/>
+      <c r="C250" s="311"/>
       <c r="D250" s="7"/>
       <c r="E250" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F250" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F250" s="308"/>
     </row>
     <row r="251" s="244" customFormat="1" spans="1:6">
-      <c r="A251" s="292"/>
-      <c r="B251" s="296"/>
-      <c r="C251" s="303"/>
+      <c r="A251" s="300"/>
+      <c r="B251" s="304"/>
+      <c r="C251" s="311"/>
       <c r="D251" s="7"/>
       <c r="E251" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F251" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F251" s="308"/>
     </row>
     <row r="252" s="244" customFormat="1" spans="1:6">
-      <c r="A252" s="293"/>
-      <c r="B252" s="296"/>
-      <c r="C252" s="303"/>
+      <c r="A252" s="301"/>
+      <c r="B252" s="304"/>
+      <c r="C252" s="311"/>
       <c r="D252" s="7"/>
       <c r="E252" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F252" s="301"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F252" s="309"/>
     </row>
     <row r="253" s="244" customFormat="1" spans="1:6">
-      <c r="A253" s="289"/>
-      <c r="B253" s="296"/>
-      <c r="C253" s="303"/>
+      <c r="A253" s="297"/>
+      <c r="B253" s="304"/>
+      <c r="C253" s="311"/>
       <c r="D253" s="7"/>
       <c r="E253" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F253" s="299">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F253" s="307">
         <f>SUM(E253:E263)</f>
         <v>0</v>
       </c>
     </row>
     <row r="254" s="244" customFormat="1" spans="1:6">
-      <c r="A254" s="292"/>
-      <c r="B254" s="296"/>
-      <c r="C254" s="303"/>
+      <c r="A254" s="300"/>
+      <c r="B254" s="304"/>
+      <c r="C254" s="311"/>
       <c r="D254" s="7"/>
       <c r="E254" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F254" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F254" s="308"/>
     </row>
     <row r="255" s="244" customFormat="1" spans="1:6">
-      <c r="A255" s="292"/>
-      <c r="B255" s="296"/>
-      <c r="C255" s="303"/>
+      <c r="A255" s="300"/>
+      <c r="B255" s="304"/>
+      <c r="C255" s="311"/>
       <c r="D255" s="7"/>
       <c r="E255" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F255" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F255" s="308"/>
     </row>
     <row r="256" s="244" customFormat="1" spans="1:6">
-      <c r="A256" s="292"/>
-      <c r="B256" s="296"/>
-      <c r="C256" s="303"/>
+      <c r="A256" s="300"/>
+      <c r="B256" s="304"/>
+      <c r="C256" s="311"/>
       <c r="D256" s="7"/>
       <c r="E256" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F256" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F256" s="308"/>
     </row>
     <row r="257" s="244" customFormat="1" spans="1:6">
-      <c r="A257" s="292"/>
-      <c r="B257" s="296"/>
-      <c r="C257" s="303"/>
+      <c r="A257" s="300"/>
+      <c r="B257" s="304"/>
+      <c r="C257" s="311"/>
       <c r="D257" s="7"/>
       <c r="E257" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F257" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F257" s="308"/>
     </row>
     <row r="258" s="244" customFormat="1" spans="1:6">
-      <c r="A258" s="292"/>
-      <c r="B258" s="296"/>
-      <c r="C258" s="303"/>
+      <c r="A258" s="300"/>
+      <c r="B258" s="304"/>
+      <c r="C258" s="311"/>
       <c r="D258" s="7"/>
       <c r="E258" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F258" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F258" s="308"/>
     </row>
     <row r="259" s="244" customFormat="1" spans="1:6">
-      <c r="A259" s="292"/>
-      <c r="B259" s="296"/>
-      <c r="C259" s="303"/>
+      <c r="A259" s="300"/>
+      <c r="B259" s="304"/>
+      <c r="C259" s="311"/>
       <c r="D259" s="7"/>
       <c r="E259" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F259" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F259" s="308"/>
     </row>
     <row r="260" s="244" customFormat="1" spans="1:6">
-      <c r="A260" s="292"/>
-      <c r="B260" s="296"/>
-      <c r="C260" s="303"/>
+      <c r="A260" s="300"/>
+      <c r="B260" s="304"/>
+      <c r="C260" s="311"/>
       <c r="D260" s="7"/>
       <c r="E260" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F260" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F260" s="308"/>
     </row>
     <row r="261" s="244" customFormat="1" spans="1:6">
-      <c r="A261" s="292"/>
-      <c r="B261" s="296"/>
-      <c r="C261" s="303"/>
+      <c r="A261" s="300"/>
+      <c r="B261" s="304"/>
+      <c r="C261" s="311"/>
       <c r="D261" s="7"/>
       <c r="E261" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F261" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F261" s="308"/>
     </row>
     <row r="262" s="244" customFormat="1" spans="1:6">
-      <c r="A262" s="292"/>
-      <c r="B262" s="296"/>
-      <c r="C262" s="303"/>
+      <c r="A262" s="300"/>
+      <c r="B262" s="304"/>
+      <c r="C262" s="311"/>
       <c r="D262" s="7"/>
       <c r="E262" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F262" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F262" s="308"/>
     </row>
     <row r="263" s="244" customFormat="1" spans="1:6">
-      <c r="A263" s="293"/>
-      <c r="B263" s="296"/>
-      <c r="C263" s="303"/>
+      <c r="A263" s="301"/>
+      <c r="B263" s="304"/>
+      <c r="C263" s="311"/>
       <c r="D263" s="7"/>
       <c r="E263" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F263" s="301"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F263" s="309"/>
     </row>
     <row r="264" s="244" customFormat="1" spans="1:6">
-      <c r="A264" s="289"/>
-      <c r="B264" s="296"/>
-      <c r="C264" s="303"/>
+      <c r="A264" s="297"/>
+      <c r="B264" s="304"/>
+      <c r="C264" s="311"/>
       <c r="D264" s="7"/>
       <c r="E264" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F264" s="299">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F264" s="307">
         <f>SUM(E264:E274)</f>
         <v>0</v>
       </c>
     </row>
     <row r="265" s="244" customFormat="1" spans="1:6">
-      <c r="A265" s="292"/>
-      <c r="B265" s="296"/>
-      <c r="C265" s="303"/>
+      <c r="A265" s="300"/>
+      <c r="B265" s="304"/>
+      <c r="C265" s="311"/>
       <c r="D265" s="7"/>
       <c r="E265" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F265" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F265" s="308"/>
     </row>
     <row r="266" s="244" customFormat="1" spans="1:6">
-      <c r="A266" s="292"/>
-      <c r="B266" s="296"/>
-      <c r="C266" s="303"/>
+      <c r="A266" s="300"/>
+      <c r="B266" s="304"/>
+      <c r="C266" s="311"/>
       <c r="D266" s="7"/>
       <c r="E266" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F266" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F266" s="308"/>
     </row>
     <row r="267" s="244" customFormat="1" spans="1:6">
-      <c r="A267" s="292"/>
-      <c r="B267" s="296"/>
-      <c r="C267" s="303"/>
+      <c r="A267" s="300"/>
+      <c r="B267" s="304"/>
+      <c r="C267" s="311"/>
       <c r="D267" s="7"/>
       <c r="E267" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F267" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F267" s="308"/>
     </row>
     <row r="268" s="244" customFormat="1" spans="1:6">
-      <c r="A268" s="292"/>
-      <c r="B268" s="296"/>
-      <c r="C268" s="303"/>
+      <c r="A268" s="300"/>
+      <c r="B268" s="304"/>
+      <c r="C268" s="311"/>
       <c r="D268" s="7"/>
       <c r="E268" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F268" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F268" s="308"/>
     </row>
     <row r="269" s="244" customFormat="1" spans="1:6">
-      <c r="A269" s="292"/>
-      <c r="B269" s="296"/>
-      <c r="C269" s="303"/>
+      <c r="A269" s="300"/>
+      <c r="B269" s="304"/>
+      <c r="C269" s="311"/>
       <c r="D269" s="7"/>
       <c r="E269" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F269" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F269" s="308"/>
     </row>
     <row r="270" s="244" customFormat="1" spans="1:6">
-      <c r="A270" s="292"/>
-      <c r="B270" s="296"/>
-      <c r="C270" s="303"/>
+      <c r="A270" s="300"/>
+      <c r="B270" s="304"/>
+      <c r="C270" s="311"/>
       <c r="D270" s="7"/>
       <c r="E270" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F270" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F270" s="308"/>
     </row>
     <row r="271" s="244" customFormat="1" spans="1:6">
-      <c r="A271" s="292"/>
-      <c r="B271" s="296"/>
-      <c r="C271" s="303"/>
+      <c r="A271" s="300"/>
+      <c r="B271" s="304"/>
+      <c r="C271" s="311"/>
       <c r="D271" s="7"/>
       <c r="E271" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F271" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F271" s="308"/>
     </row>
     <row r="272" s="244" customFormat="1" spans="1:6">
-      <c r="A272" s="292"/>
-      <c r="B272" s="296"/>
-      <c r="C272" s="303"/>
+      <c r="A272" s="300"/>
+      <c r="B272" s="304"/>
+      <c r="C272" s="311"/>
       <c r="D272" s="7"/>
       <c r="E272" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F272" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F272" s="308"/>
     </row>
     <row r="273" s="244" customFormat="1" spans="1:6">
-      <c r="A273" s="292"/>
-      <c r="B273" s="296"/>
-      <c r="C273" s="303"/>
+      <c r="A273" s="300"/>
+      <c r="B273" s="304"/>
+      <c r="C273" s="311"/>
       <c r="D273" s="7"/>
       <c r="E273" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F273" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F273" s="308"/>
     </row>
     <row r="274" s="244" customFormat="1" spans="1:6">
-      <c r="A274" s="293"/>
-      <c r="B274" s="296"/>
-      <c r="C274" s="303"/>
+      <c r="A274" s="301"/>
+      <c r="B274" s="304"/>
+      <c r="C274" s="311"/>
       <c r="D274" s="7"/>
       <c r="E274" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F274" s="301"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F274" s="309"/>
     </row>
     <row r="275" s="244" customFormat="1" spans="1:6">
-      <c r="A275" s="289"/>
-      <c r="B275" s="296"/>
-      <c r="C275" s="303"/>
+      <c r="A275" s="297"/>
+      <c r="B275" s="304"/>
+      <c r="C275" s="311"/>
       <c r="D275" s="7"/>
       <c r="E275" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F275" s="299">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F275" s="307">
         <f>SUM(E275:E284)</f>
         <v>0</v>
       </c>
     </row>
     <row r="276" s="244" customFormat="1" spans="1:6">
-      <c r="A276" s="292"/>
-      <c r="B276" s="296"/>
-      <c r="C276" s="303"/>
+      <c r="A276" s="300"/>
+      <c r="B276" s="304"/>
+      <c r="C276" s="311"/>
       <c r="D276" s="7"/>
       <c r="E276" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F276" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F276" s="308"/>
     </row>
     <row r="277" s="244" customFormat="1" spans="1:6">
-      <c r="A277" s="292"/>
-      <c r="B277" s="296"/>
-      <c r="C277" s="303"/>
+      <c r="A277" s="300"/>
+      <c r="B277" s="304"/>
+      <c r="C277" s="311"/>
       <c r="D277" s="7"/>
       <c r="E277" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F277" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F277" s="308"/>
     </row>
     <row r="278" s="244" customFormat="1" spans="1:6">
-      <c r="A278" s="292"/>
-      <c r="B278" s="296"/>
-      <c r="C278" s="303"/>
+      <c r="A278" s="300"/>
+      <c r="B278" s="304"/>
+      <c r="C278" s="311"/>
       <c r="D278" s="7"/>
       <c r="E278" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F278" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F278" s="308"/>
     </row>
     <row r="279" s="244" customFormat="1" spans="1:6">
-      <c r="A279" s="292"/>
-      <c r="B279" s="296"/>
-      <c r="C279" s="303"/>
+      <c r="A279" s="300"/>
+      <c r="B279" s="304"/>
+      <c r="C279" s="311"/>
       <c r="D279" s="7"/>
       <c r="E279" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F279" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F279" s="308"/>
     </row>
     <row r="280" s="244" customFormat="1" spans="1:6">
-      <c r="A280" s="292"/>
-      <c r="B280" s="296"/>
-      <c r="C280" s="303"/>
+      <c r="A280" s="300"/>
+      <c r="B280" s="304"/>
+      <c r="C280" s="311"/>
       <c r="D280" s="7"/>
       <c r="E280" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F280" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F280" s="308"/>
     </row>
     <row r="281" s="244" customFormat="1" spans="1:6">
-      <c r="A281" s="292"/>
-      <c r="B281" s="296"/>
-      <c r="C281" s="303"/>
+      <c r="A281" s="300"/>
+      <c r="B281" s="304"/>
+      <c r="C281" s="311"/>
       <c r="D281" s="7"/>
       <c r="E281" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F281" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F281" s="308"/>
     </row>
     <row r="282" s="244" customFormat="1" spans="1:6">
-      <c r="A282" s="292"/>
-      <c r="B282" s="296"/>
-      <c r="C282" s="303"/>
+      <c r="A282" s="300"/>
+      <c r="B282" s="304"/>
+      <c r="C282" s="311"/>
       <c r="D282" s="7"/>
       <c r="E282" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F282" s="300"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F282" s="308"/>
     </row>
     <row r="283" s="244" customFormat="1" spans="1:6">
-      <c r="A283" s="292"/>
-      <c r="B283" s="296"/>
-      <c r="C283" s="303"/>
+      <c r="A283" s="300"/>
+      <c r="B283" s="304"/>
+      <c r="C283" s="311"/>
       <c r="D283" s="7"/>
       <c r="E283" s="7">
-        <f t="shared" ref="E283:E296" si="10">SUM(C283*D283)</f>
-        <v>0</v>
-      </c>
-      <c r="F283" s="300"/>
+        <f t="shared" ref="E283:E296" si="11">SUM(C283*D283)</f>
+        <v>0</v>
+      </c>
+      <c r="F283" s="308"/>
     </row>
     <row r="284" s="244" customFormat="1" spans="1:6">
-      <c r="A284" s="293"/>
-      <c r="B284" s="296"/>
-      <c r="C284" s="303"/>
+      <c r="A284" s="301"/>
+      <c r="B284" s="304"/>
+      <c r="C284" s="311"/>
       <c r="D284" s="7"/>
       <c r="E284" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F284" s="301"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F284" s="309"/>
     </row>
     <row r="285" s="244" customFormat="1" ht="17.6" spans="1:6">
-      <c r="A285" s="297"/>
-      <c r="B285" s="296"/>
-      <c r="C285" s="303"/>
+      <c r="A285" s="305"/>
+      <c r="B285" s="304"/>
+      <c r="C285" s="311"/>
       <c r="D285" s="7"/>
       <c r="E285" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F285" s="310">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F285" s="320">
         <f>SUM(E285)</f>
         <v>0</v>
       </c>
     </row>
     <row r="286" s="244" customFormat="1" spans="1:6">
-      <c r="A286" s="289"/>
-      <c r="B286" s="296"/>
-      <c r="C286" s="303"/>
+      <c r="A286" s="297"/>
+      <c r="B286" s="304"/>
+      <c r="C286" s="311"/>
       <c r="D286" s="7"/>
       <c r="E286" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F286" s="299">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F286" s="307">
         <f>SUM(E286:E296)</f>
         <v>0</v>
       </c>
     </row>
     <row r="287" s="244" customFormat="1" spans="1:6">
-      <c r="A287" s="292"/>
-      <c r="B287" s="296"/>
-      <c r="C287" s="303"/>
+      <c r="A287" s="300"/>
+      <c r="B287" s="304"/>
+      <c r="C287" s="311"/>
       <c r="D287" s="7"/>
       <c r="E287" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F287" s="300"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F287" s="308"/>
     </row>
     <row r="288" s="244" customFormat="1" spans="1:6">
-      <c r="A288" s="292"/>
-      <c r="B288" s="296"/>
-      <c r="C288" s="303"/>
+      <c r="A288" s="300"/>
+      <c r="B288" s="304"/>
+      <c r="C288" s="311"/>
       <c r="D288" s="7"/>
       <c r="E288" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F288" s="300"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F288" s="308"/>
     </row>
     <row r="289" s="244" customFormat="1" spans="1:6">
-      <c r="A289" s="292"/>
-      <c r="B289" s="296"/>
-      <c r="C289" s="303"/>
+      <c r="A289" s="300"/>
+      <c r="B289" s="304"/>
+      <c r="C289" s="311"/>
       <c r="D289" s="7"/>
       <c r="E289" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F289" s="300"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F289" s="308"/>
     </row>
     <row r="290" s="244" customFormat="1" spans="1:6">
-      <c r="A290" s="292"/>
-      <c r="B290" s="296"/>
-      <c r="C290" s="303"/>
+      <c r="A290" s="300"/>
+      <c r="B290" s="304"/>
+      <c r="C290" s="311"/>
       <c r="D290" s="7"/>
       <c r="E290" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F290" s="300"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F290" s="308"/>
     </row>
     <row r="291" s="244" customFormat="1" spans="1:6">
-      <c r="A291" s="292"/>
-      <c r="B291" s="296"/>
-      <c r="C291" s="303"/>
+      <c r="A291" s="300"/>
+      <c r="B291" s="304"/>
+      <c r="C291" s="311"/>
       <c r="D291" s="7"/>
       <c r="E291" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F291" s="300"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F291" s="308"/>
     </row>
     <row r="292" s="244" customFormat="1" spans="1:6">
-      <c r="A292" s="292"/>
-      <c r="B292" s="296"/>
-      <c r="C292" s="303"/>
+      <c r="A292" s="300"/>
+      <c r="B292" s="304"/>
+      <c r="C292" s="311"/>
       <c r="D292" s="7"/>
       <c r="E292" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F292" s="300"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F292" s="308"/>
     </row>
     <row r="293" s="244" customFormat="1" spans="1:6">
-      <c r="A293" s="292"/>
-      <c r="B293" s="296"/>
-      <c r="C293" s="303"/>
+      <c r="A293" s="300"/>
+      <c r="B293" s="304"/>
+      <c r="C293" s="311"/>
       <c r="D293" s="7"/>
       <c r="E293" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F293" s="300"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F293" s="308"/>
     </row>
     <row r="294" s="244" customFormat="1" spans="1:6">
-      <c r="A294" s="292"/>
-      <c r="B294" s="296"/>
-      <c r="C294" s="303"/>
+      <c r="A294" s="300"/>
+      <c r="B294" s="304"/>
+      <c r="C294" s="311"/>
       <c r="D294" s="7"/>
       <c r="E294" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F294" s="300"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F294" s="308"/>
     </row>
     <row r="295" s="244" customFormat="1" spans="1:6">
-      <c r="A295" s="292"/>
-      <c r="B295" s="296"/>
-      <c r="C295" s="303"/>
+      <c r="A295" s="300"/>
+      <c r="B295" s="304"/>
+      <c r="C295" s="311"/>
       <c r="D295" s="7"/>
       <c r="E295" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F295" s="300"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F295" s="308"/>
     </row>
     <row r="296" s="244" customFormat="1" spans="1:6">
-      <c r="A296" s="293"/>
-      <c r="B296" s="296"/>
-      <c r="C296" s="303"/>
+      <c r="A296" s="301"/>
+      <c r="B296" s="304"/>
+      <c r="C296" s="311"/>
       <c r="D296" s="7"/>
       <c r="E296" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F296" s="301"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F296" s="309"/>
     </row>
     <row r="297" s="244" customFormat="1" spans="1:6">
       <c r="A297" s="246"/>
       <c r="C297" s="245"/>
       <c r="E297" s="7"/>
-      <c r="F297" s="310">
+      <c r="F297" s="320">
         <f>SUM(F2:F296)</f>
-        <v>7342000</v>
+        <v>8447000</v>
       </c>
     </row>
     <row r="298" s="244" customFormat="1" spans="1:3">
@@ -8597,10 +8727,10 @@
     <row r="400" s="244" customFormat="1" spans="1:7">
       <c r="A400" s="246"/>
       <c r="C400" s="245"/>
-      <c r="G400" s="277"/>
+      <c r="G400" s="281"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="52">
     <mergeCell ref="A2:A12"/>
     <mergeCell ref="A13:A25"/>
     <mergeCell ref="A26:A34"/>
@@ -8618,6 +8748,7 @@
     <mergeCell ref="A139:A146"/>
     <mergeCell ref="A147:A156"/>
     <mergeCell ref="A157:A159"/>
+    <mergeCell ref="A160:A169"/>
     <mergeCell ref="A213:A220"/>
     <mergeCell ref="A221:A232"/>
     <mergeCell ref="A233:A241"/>
@@ -8643,6 +8774,7 @@
     <mergeCell ref="F139:F146"/>
     <mergeCell ref="F147:F156"/>
     <mergeCell ref="F157:F159"/>
+    <mergeCell ref="F160:F169"/>
     <mergeCell ref="F213:F220"/>
     <mergeCell ref="F221:F232"/>
     <mergeCell ref="F233:F241"/>
@@ -8677,16 +8809,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -8703,7 +8835,7 @@
         <v>38678</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D2" s="27">
         <v>3</v>
@@ -8726,7 +8858,7 @@
       <c r="D3" s="27"/>
       <c r="E3" s="17"/>
       <c r="F3" s="123" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G3" s="53">
         <f>G2*11%</f>
@@ -8768,7 +8900,7 @@
       <c r="D6" s="122"/>
       <c r="E6" s="7"/>
       <c r="F6" s="127" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G6" s="7">
         <f>G5*11%</f>
@@ -8850,7 +8982,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="81" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B14" s="82"/>
       <c r="C14" s="82"/>
@@ -8905,16 +9037,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -9053,7 +9185,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
       <c r="A14" s="81" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B14" s="82"/>
       <c r="C14" s="82"/>
@@ -9107,16 +9239,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -9125,7 +9257,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" ht="147.55" customHeight="1" spans="1:8">
@@ -9133,10 +9265,10 @@
         <v>45999</v>
       </c>
       <c r="B2" s="93" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D2" s="56">
         <v>24</v>
@@ -9163,7 +9295,7 @@
       </c>
       <c r="E3" s="106"/>
       <c r="F3" s="86" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G3" s="107">
         <f>G2*11%</f>
@@ -9211,7 +9343,7 @@
       </c>
       <c r="E6" s="85"/>
       <c r="F6" s="86" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G6" s="107">
         <f>G5*11%</f>
@@ -9256,7 +9388,7 @@
       <c r="D9" s="102"/>
       <c r="E9" s="85"/>
       <c r="F9" s="86" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G9" s="107">
         <f>G8*11%</f>
@@ -9301,7 +9433,7 @@
       <c r="D12" s="102"/>
       <c r="E12" s="85"/>
       <c r="F12" s="86" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G12" s="107">
         <f>G11*11%</f>
@@ -9343,7 +9475,7 @@
       <c r="D15" s="102"/>
       <c r="E15" s="85"/>
       <c r="F15" s="86" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G15" s="107">
         <f>G14*11%</f>
@@ -9368,7 +9500,7 @@
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:8">
       <c r="A17" s="81" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B17" s="82"/>
       <c r="C17" s="82"/>
@@ -9427,19 +9559,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="35" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G1" s="35" t="s">
         <v>5</v>
@@ -9450,10 +9582,10 @@
         <v>46001</v>
       </c>
       <c r="B2" s="93" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D2" s="56">
         <v>10</v>
@@ -9475,10 +9607,10 @@
         <v>46006</v>
       </c>
       <c r="B3" s="93" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D3" s="56">
         <v>10</v>
@@ -9497,7 +9629,7 @@
     </row>
     <row r="4" ht="23" customHeight="1" spans="1:7">
       <c r="A4" s="94" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B4" s="95"/>
       <c r="C4" s="95"/>
@@ -9538,16 +9670,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -9561,10 +9693,10 @@
         <v>45999</v>
       </c>
       <c r="B2" s="77" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D2" s="27">
         <v>3</v>
@@ -9580,7 +9712,7 @@
     </row>
     <row r="3" ht="26" spans="1:7">
       <c r="A3" s="28" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="78"/>
@@ -9590,7 +9722,7 @@
       </c>
       <c r="E3" s="85"/>
       <c r="F3" s="85" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G3" s="86">
         <f>G2*11%</f>
@@ -9645,7 +9777,7 @@
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:7">
       <c r="A8" s="81" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B8" s="82"/>
       <c r="C8" s="82"/>
@@ -9693,19 +9825,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" ht="321" customHeight="1" spans="1:6">
@@ -9768,16 +9900,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -9878,7 +10010,7 @@
     </row>
     <row r="12" ht="27" customHeight="1" spans="1:7">
       <c r="A12" s="49" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B12" s="50"/>
       <c r="C12" s="50"/>
@@ -9931,13 +10063,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>3</v>
@@ -9946,7 +10078,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" ht="324.4" customHeight="1" spans="1:7">
@@ -10005,22 +10137,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" ht="177" customHeight="1" spans="1:7">
@@ -10081,10 +10213,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>5</v>
@@ -10095,11 +10227,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C2" s="5">
         <f>'BUK BUNGA (Groceries)'!F297</f>
-        <v>7342000</v>
+        <v>8447000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -10107,11 +10239,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C3" s="5">
         <f>'WARUNG EKA (Drinks, Etc)'!G117</f>
-        <v>6219000</v>
+        <v>7182000</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -10119,11 +10251,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C4" s="5">
         <f>'DEWATA COCONUT (Coconut)'!E10</f>
-        <v>1680000</v>
+        <v>1940000</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -10131,7 +10263,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C5" s="5">
         <f>'SEDANA JAYA'!F37</f>
@@ -10143,7 +10275,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C6" s="5">
         <f>'PNB (Alcohol)'!H7</f>
@@ -10155,7 +10287,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C7" s="5">
         <f>'DSP (Alcohol)'!F16</f>
@@ -10167,7 +10299,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C8" s="5">
         <f>'DSP ARYA BIMA (Alcohol)'!E3</f>
@@ -10179,7 +10311,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C9" s="5" t="str">
         <f>'SELERA OR STIR UP (Syrup)'!F19</f>
@@ -10191,7 +10323,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C10" s="5">
         <f>'DW BALI (Alcohol)'!E6</f>
@@ -10203,7 +10335,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C11" s="5">
         <f>'DDB (Alcohol)'!E14</f>
@@ -10215,7 +10347,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C12" s="5">
         <f>'NANO DEWATA (Alcohol)'!E14</f>
@@ -10227,7 +10359,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C13" s="5">
         <f>'BALI PERMATA JAYA (Corona Beer)'!E17</f>
@@ -10239,7 +10371,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C14" s="7">
         <f>'BLACK COFFEE ROASTERS (Coffee)'!F4</f>
@@ -10251,7 +10383,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C15" s="5">
         <f>'PT. PRASIDA LANTUR MAJU (Wine)'!E8</f>
@@ -10263,7 +10395,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C16" s="8">
         <f>'PT LOVINA BEACH BREWERY'!D3</f>
@@ -10275,7 +10407,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C17" s="5">
         <f>'CHAI CHITAI (Tea Leaf,etc)'!E12</f>
@@ -10287,7 +10419,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C18" s="5">
         <f>'MULIA JAYA (Passion Fruit)'!D3</f>
@@ -10299,7 +10431,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C19" s="5">
         <f>'Dewata Kencana Distribusi (Vdka'!E3</f>
@@ -10313,7 +10445,7 @@
       <c r="B20" s="9"/>
       <c r="C20" s="10">
         <f>SUM(C2:C13)</f>
-        <v>27199609.94</v>
+        <v>29527609.94</v>
       </c>
     </row>
   </sheetData>
@@ -10349,7 +10481,7 @@
   <sheetData>
     <row r="1" s="244" customFormat="1" ht="21" customHeight="1" spans="1:7">
       <c r="A1" s="250" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B1" s="251" t="s">
         <v>0</v>
@@ -10364,10 +10496,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="252" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G1" s="252" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" s="244" customFormat="1" ht="19" customHeight="1" spans="1:7">
@@ -10378,7 +10510,7 @@
         <v>45992</v>
       </c>
       <c r="C2" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D2" s="115">
         <v>5</v>
@@ -10399,7 +10531,7 @@
       <c r="A3" s="41"/>
       <c r="B3" s="40"/>
       <c r="C3" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D3" s="115">
         <v>1</v>
@@ -10417,7 +10549,7 @@
       <c r="A4" s="255"/>
       <c r="B4" s="131"/>
       <c r="C4" s="254" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D4" s="115">
         <v>1</v>
@@ -10439,7 +10571,7 @@
         <v>45993</v>
       </c>
       <c r="C5" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D5" s="115">
         <v>5</v>
@@ -10460,7 +10592,7 @@
       <c r="A6" s="256"/>
       <c r="B6" s="40"/>
       <c r="C6" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D6" s="115">
         <v>1</v>
@@ -10478,7 +10610,7 @@
       <c r="A7" s="206"/>
       <c r="B7" s="131"/>
       <c r="C7" s="254" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D7" s="115">
         <v>1</v>
@@ -10500,7 +10632,7 @@
         <v>45994</v>
       </c>
       <c r="C8" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D8" s="115">
         <v>6</v>
@@ -10521,7 +10653,7 @@
       <c r="A9" s="256"/>
       <c r="B9" s="40"/>
       <c r="C9" s="254" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9" s="115">
         <v>1</v>
@@ -10539,7 +10671,7 @@
       <c r="A10" s="256"/>
       <c r="B10" s="40"/>
       <c r="C10" s="254" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D10" s="115">
         <v>1</v>
@@ -10557,7 +10689,7 @@
       <c r="A11" s="256"/>
       <c r="B11" s="40"/>
       <c r="C11" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D11" s="115">
         <v>1</v>
@@ -10575,7 +10707,7 @@
       <c r="A12" s="256"/>
       <c r="B12" s="40"/>
       <c r="C12" s="257" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D12" s="115">
         <v>2</v>
@@ -10593,7 +10725,7 @@
       <c r="A13" s="206"/>
       <c r="B13" s="131"/>
       <c r="C13" s="254" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" s="115">
         <v>1</v>
@@ -10615,7 +10747,7 @@
         <v>45995</v>
       </c>
       <c r="C14" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D14" s="115">
         <v>6</v>
@@ -10636,7 +10768,7 @@
       <c r="A15" s="206"/>
       <c r="B15" s="131"/>
       <c r="C15" s="257" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D15" s="115">
         <v>2</v>
@@ -10658,7 +10790,7 @@
         <v>45997</v>
       </c>
       <c r="C16" s="257" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D16" s="115">
         <v>2</v>
@@ -10679,7 +10811,7 @@
       <c r="A17" s="256"/>
       <c r="B17" s="40"/>
       <c r="C17" s="257" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D17" s="115">
         <v>1</v>
@@ -10697,7 +10829,7 @@
       <c r="A18" s="206"/>
       <c r="B18" s="131"/>
       <c r="C18" s="257" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D18" s="115">
         <v>5</v>
@@ -10719,7 +10851,7 @@
         <v>45998</v>
       </c>
       <c r="C19" s="254" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D19" s="115">
         <v>2</v>
@@ -10740,7 +10872,7 @@
       <c r="A20" s="256"/>
       <c r="B20" s="40"/>
       <c r="C20" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D20" s="115">
         <v>1</v>
@@ -10758,7 +10890,7 @@
       <c r="A21" s="256"/>
       <c r="B21" s="40"/>
       <c r="C21" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D21" s="115">
         <v>5</v>
@@ -10776,7 +10908,7 @@
       <c r="A22" s="256"/>
       <c r="B22" s="40"/>
       <c r="C22" s="254" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D22" s="115">
         <v>1</v>
@@ -10794,7 +10926,7 @@
       <c r="A23" s="206"/>
       <c r="B23" s="131"/>
       <c r="C23" s="257" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D23" s="115">
         <v>2</v>
@@ -10816,7 +10948,7 @@
         <v>45999</v>
       </c>
       <c r="C24" s="254" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D24" s="115">
         <v>1</v>
@@ -10837,7 +10969,7 @@
       <c r="A25" s="256"/>
       <c r="B25" s="40"/>
       <c r="C25" s="254" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D25" s="115">
         <v>1</v>
@@ -10855,7 +10987,7 @@
       <c r="A26" s="256"/>
       <c r="B26" s="40"/>
       <c r="C26" s="257" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D26" s="115">
         <v>1</v>
@@ -10873,7 +11005,7 @@
       <c r="A27" s="206"/>
       <c r="B27" s="131"/>
       <c r="C27" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D27" s="115">
         <v>4</v>
@@ -10895,7 +11027,7 @@
         <v>46000</v>
       </c>
       <c r="C28" s="257" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D28" s="115">
         <v>5</v>
@@ -10916,7 +11048,7 @@
       <c r="A29" s="256"/>
       <c r="B29" s="40"/>
       <c r="C29" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D29" s="115">
         <v>1</v>
@@ -10934,7 +11066,7 @@
       <c r="A30" s="206"/>
       <c r="B30" s="131"/>
       <c r="C30" s="254" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D30" s="115">
         <v>1</v>
@@ -10956,7 +11088,7 @@
         <v>46001</v>
       </c>
       <c r="C31" s="258" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D31" s="115">
         <v>6</v>
@@ -10977,7 +11109,7 @@
       <c r="A32" s="56"/>
       <c r="B32" s="25"/>
       <c r="C32" s="259" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D32" s="115">
         <v>1</v>
@@ -10995,7 +11127,7 @@
       <c r="A33" s="56"/>
       <c r="B33" s="25"/>
       <c r="C33" s="258" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D33" s="115">
         <v>1</v>
@@ -11013,7 +11145,7 @@
       <c r="A34" s="56"/>
       <c r="B34" s="25"/>
       <c r="C34" s="258" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D34" s="115">
         <v>1</v>
@@ -11031,7 +11163,7 @@
       <c r="A35" s="56"/>
       <c r="B35" s="25"/>
       <c r="C35" s="258" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D35" s="115">
         <v>1</v>
@@ -11049,7 +11181,7 @@
       <c r="A36" s="56"/>
       <c r="B36" s="25"/>
       <c r="C36" s="258" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D36" s="115">
         <v>1</v>
@@ -11067,7 +11199,7 @@
       <c r="A37" s="56"/>
       <c r="B37" s="25"/>
       <c r="C37" s="258" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D37" s="115">
         <v>2</v>
@@ -11089,7 +11221,7 @@
         <v>46002</v>
       </c>
       <c r="C38" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D38" s="115">
         <v>6</v>
@@ -11110,7 +11242,7 @@
       <c r="A39" s="256"/>
       <c r="B39" s="40"/>
       <c r="C39" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D39" s="115">
         <v>2</v>
@@ -11128,7 +11260,7 @@
       <c r="A40" s="256"/>
       <c r="B40" s="40"/>
       <c r="C40" s="254" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D40" s="115">
         <v>1</v>
@@ -11150,7 +11282,7 @@
         <v>46003</v>
       </c>
       <c r="C41" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D41" s="115">
         <v>6</v>
@@ -11171,7 +11303,7 @@
       <c r="A42" s="256"/>
       <c r="B42" s="40"/>
       <c r="C42" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D42" s="115">
         <v>1</v>
@@ -11189,7 +11321,7 @@
       <c r="A43" s="256"/>
       <c r="B43" s="40"/>
       <c r="C43" s="254" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D43" s="115">
         <v>2</v>
@@ -11207,7 +11339,7 @@
       <c r="A44" s="256"/>
       <c r="B44" s="40"/>
       <c r="C44" s="254" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D44" s="115">
         <v>1</v>
@@ -11225,7 +11357,7 @@
       <c r="A45" s="206"/>
       <c r="B45" s="131"/>
       <c r="C45" s="254" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D45" s="115">
         <v>1</v>
@@ -11247,7 +11379,7 @@
         <v>46004</v>
       </c>
       <c r="C46" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D46" s="115">
         <v>1</v>
@@ -11268,7 +11400,7 @@
       <c r="A47" s="206"/>
       <c r="B47" s="131"/>
       <c r="C47" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D47" s="115">
         <v>6</v>
@@ -11290,7 +11422,7 @@
         <v>46005</v>
       </c>
       <c r="C48" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D48" s="115">
         <v>5</v>
@@ -11311,7 +11443,7 @@
       <c r="A49" s="256"/>
       <c r="B49" s="40"/>
       <c r="C49" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D49" s="115">
         <v>1</v>
@@ -11329,7 +11461,7 @@
       <c r="A50" s="206"/>
       <c r="B50" s="131"/>
       <c r="C50" s="254" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D50" s="115">
         <v>1</v>
@@ -11351,7 +11483,7 @@
         <v>46006</v>
       </c>
       <c r="C51" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D51" s="115">
         <v>6</v>
@@ -11372,7 +11504,7 @@
       <c r="A52" s="256"/>
       <c r="B52" s="40"/>
       <c r="C52" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D52" s="115">
         <v>1</v>
@@ -11390,7 +11522,7 @@
       <c r="A53" s="256"/>
       <c r="B53" s="40"/>
       <c r="C53" s="254" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D53" s="115">
         <v>1</v>
@@ -11408,7 +11540,7 @@
       <c r="A54" s="256"/>
       <c r="B54" s="40"/>
       <c r="C54" s="254" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D54" s="115">
         <v>1</v>
@@ -11426,7 +11558,7 @@
       <c r="A55" s="206"/>
       <c r="B55" s="131"/>
       <c r="C55" s="260" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D55" s="255">
         <v>2</v>
@@ -11448,7 +11580,7 @@
         <v>46007</v>
       </c>
       <c r="C56" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D56" s="115">
         <v>5</v>
@@ -11469,7 +11601,7 @@
       <c r="A57" s="56"/>
       <c r="B57" s="25"/>
       <c r="C57" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D57" s="115">
         <v>1</v>
@@ -11487,7 +11619,7 @@
       <c r="A58" s="56"/>
       <c r="B58" s="25"/>
       <c r="C58" s="254" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D58" s="115">
         <v>2</v>
@@ -11505,7 +11637,7 @@
       <c r="A59" s="56"/>
       <c r="B59" s="25"/>
       <c r="C59" s="254" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D59" s="115">
         <v>1</v>
@@ -11523,7 +11655,7 @@
       <c r="A60" s="56"/>
       <c r="B60" s="25"/>
       <c r="C60" s="254" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D60" s="115">
         <v>1</v>
@@ -11545,7 +11677,7 @@
         <v>46008</v>
       </c>
       <c r="C61" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D61" s="115">
         <v>6</v>
@@ -11566,7 +11698,7 @@
       <c r="A62" s="256"/>
       <c r="B62" s="25"/>
       <c r="C62" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D62" s="115">
         <v>1</v>
@@ -11584,7 +11716,7 @@
       <c r="A63" s="256"/>
       <c r="B63" s="25"/>
       <c r="C63" s="254" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D63" s="115">
         <v>1</v>
@@ -11602,7 +11734,7 @@
       <c r="A64" s="256"/>
       <c r="B64" s="25"/>
       <c r="C64" s="254" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D64" s="115">
         <v>1</v>
@@ -11620,7 +11752,7 @@
       <c r="A65" s="206"/>
       <c r="B65" s="25"/>
       <c r="C65" s="254" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D65" s="115">
         <v>2</v>
@@ -11642,7 +11774,7 @@
         <v>46009</v>
       </c>
       <c r="C66" s="254" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D66" s="115">
         <v>6</v>
@@ -11663,7 +11795,7 @@
       <c r="A67" s="256"/>
       <c r="B67" s="40"/>
       <c r="C67" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D67" s="115">
         <v>1</v>
@@ -11676,13 +11808,13 @@
         <v>20000</v>
       </c>
       <c r="G67" s="264"/>
-      <c r="H67" s="277"/>
+      <c r="H67" s="281"/>
     </row>
     <row r="68" s="244" customFormat="1" ht="17.6" spans="1:14">
       <c r="A68" s="206"/>
       <c r="B68" s="131"/>
       <c r="C68" s="254" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D68" s="115">
         <v>1</v>
@@ -11695,13 +11827,13 @@
         <v>22000</v>
       </c>
       <c r="G68" s="266"/>
-      <c r="H68" s="277"/>
-      <c r="I68" s="283"/>
-      <c r="J68" s="284"/>
-      <c r="K68" s="285"/>
-      <c r="L68" s="286"/>
-      <c r="M68" s="286"/>
-      <c r="N68" s="288"/>
+      <c r="H68" s="281"/>
+      <c r="I68" s="291"/>
+      <c r="J68" s="292"/>
+      <c r="K68" s="293"/>
+      <c r="L68" s="294"/>
+      <c r="M68" s="294"/>
+      <c r="N68" s="296"/>
     </row>
     <row r="69" s="244" customFormat="1" ht="17.6" spans="1:14">
       <c r="A69" s="205">
@@ -11711,7 +11843,7 @@
         <v>46010</v>
       </c>
       <c r="C69" s="254" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D69" s="115">
         <v>1</v>
@@ -11727,18 +11859,18 @@
         <f>SUM(F69:F72)</f>
         <v>209000</v>
       </c>
-      <c r="I69" s="287"/>
-      <c r="J69" s="284"/>
-      <c r="K69" s="285"/>
-      <c r="L69" s="286"/>
-      <c r="M69" s="286"/>
-      <c r="N69" s="286"/>
+      <c r="I69" s="295"/>
+      <c r="J69" s="292"/>
+      <c r="K69" s="293"/>
+      <c r="L69" s="294"/>
+      <c r="M69" s="294"/>
+      <c r="N69" s="294"/>
     </row>
     <row r="70" s="244" customFormat="1" ht="17.6" spans="1:14">
       <c r="A70" s="256"/>
       <c r="B70" s="40"/>
       <c r="C70" s="254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D70" s="115">
         <v>1</v>
@@ -11751,18 +11883,18 @@
         <v>20000</v>
       </c>
       <c r="G70" s="264"/>
-      <c r="I70" s="287"/>
-      <c r="J70" s="284"/>
-      <c r="K70" s="285"/>
-      <c r="L70" s="286"/>
-      <c r="M70" s="286"/>
-      <c r="N70" s="286"/>
+      <c r="I70" s="295"/>
+      <c r="J70" s="292"/>
+      <c r="K70" s="293"/>
+      <c r="L70" s="294"/>
+      <c r="M70" s="294"/>
+      <c r="N70" s="294"/>
     </row>
     <row r="71" s="244" customFormat="1" ht="17.6" spans="1:14">
       <c r="A71" s="256"/>
       <c r="B71" s="40"/>
       <c r="C71" s="254" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D71" s="115">
         <v>1</v>
@@ -11775,18 +11907,18 @@
         <v>22000</v>
       </c>
       <c r="G71" s="264"/>
-      <c r="I71" s="287"/>
-      <c r="J71" s="284"/>
-      <c r="K71" s="285"/>
-      <c r="L71" s="286"/>
-      <c r="M71" s="286"/>
-      <c r="N71" s="286"/>
+      <c r="I71" s="295"/>
+      <c r="J71" s="292"/>
+      <c r="K71" s="293"/>
+      <c r="L71" s="294"/>
+      <c r="M71" s="294"/>
+      <c r="N71" s="294"/>
     </row>
     <row r="72" s="244" customFormat="1" spans="1:7">
       <c r="A72" s="206"/>
       <c r="B72" s="131"/>
       <c r="C72" s="267" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D72" s="115">
         <v>4</v>
@@ -11801,14 +11933,14 @@
       <c r="G72" s="265"/>
     </row>
     <row r="73" s="244" customFormat="1" spans="1:7">
-      <c r="A73" s="268">
+      <c r="A73" s="205">
         <v>75194</v>
       </c>
-      <c r="B73" s="269">
+      <c r="B73" s="36">
         <v>46011</v>
       </c>
       <c r="C73" s="267" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D73" s="115">
         <v>1</v>
@@ -11820,16 +11952,16 @@
         <f t="shared" si="4"/>
         <v>22000</v>
       </c>
-      <c r="G73" s="278">
+      <c r="G73" s="263">
         <f>SUM(F73:F75)</f>
         <v>197000</v>
       </c>
     </row>
     <row r="74" s="244" customFormat="1" spans="1:7">
-      <c r="A74" s="270"/>
-      <c r="B74" s="271"/>
+      <c r="A74" s="256"/>
+      <c r="B74" s="40"/>
       <c r="C74" s="267" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D74" s="115">
         <v>5</v>
@@ -11841,13 +11973,13 @@
         <f t="shared" si="4"/>
         <v>50000</v>
       </c>
-      <c r="G74" s="279"/>
+      <c r="G74" s="264"/>
     </row>
     <row r="75" s="244" customFormat="1" spans="1:7">
-      <c r="A75" s="272"/>
-      <c r="B75" s="273"/>
+      <c r="A75" s="206"/>
+      <c r="B75" s="131"/>
       <c r="C75" s="267" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D75" s="115">
         <v>1</v>
@@ -11859,149 +11991,230 @@
         <f t="shared" si="4"/>
         <v>125000</v>
       </c>
-      <c r="G75" s="280"/>
+      <c r="G75" s="265"/>
     </row>
     <row r="76" s="244" customFormat="1" spans="1:7">
-      <c r="A76" s="203"/>
-      <c r="B76" s="274"/>
-      <c r="C76" s="267"/>
-      <c r="D76" s="115"/>
-      <c r="E76" s="262"/>
+      <c r="A76" s="205">
+        <v>75306</v>
+      </c>
+      <c r="B76" s="268">
+        <v>46012</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76" s="269">
+        <v>5</v>
+      </c>
+      <c r="E76" s="4">
+        <v>8000</v>
+      </c>
       <c r="F76" s="262">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G76" s="281"/>
+        <v>40000</v>
+      </c>
+      <c r="G76" s="282">
+        <f>SUM(F76:F78)</f>
+        <v>540000</v>
+      </c>
     </row>
     <row r="77" s="244" customFormat="1" spans="1:7">
-      <c r="A77" s="203"/>
-      <c r="B77" s="274"/>
-      <c r="C77" s="267"/>
-      <c r="D77" s="115"/>
-      <c r="E77" s="262"/>
+      <c r="A77" s="256"/>
+      <c r="B77" s="270"/>
+      <c r="C77" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D77" s="269">
+        <v>1</v>
+      </c>
+      <c r="E77" s="4">
+        <v>20000</v>
+      </c>
       <c r="F77" s="262">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G77" s="281"/>
+        <v>20000</v>
+      </c>
+      <c r="G77" s="283"/>
     </row>
     <row r="78" s="244" customFormat="1" spans="1:7">
-      <c r="A78" s="203"/>
-      <c r="B78" s="274"/>
-      <c r="C78" s="267"/>
-      <c r="D78" s="115"/>
-      <c r="E78" s="262"/>
+      <c r="A78" s="206"/>
+      <c r="B78" s="271"/>
+      <c r="C78" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D78" s="269">
+        <v>1</v>
+      </c>
+      <c r="E78" s="4">
+        <v>480000</v>
+      </c>
       <c r="F78" s="262">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G78" s="281"/>
+        <v>480000</v>
+      </c>
+      <c r="G78" s="284"/>
     </row>
     <row r="79" s="244" customFormat="1" spans="1:7">
-      <c r="A79" s="203"/>
-      <c r="B79" s="274"/>
-      <c r="C79" s="267"/>
-      <c r="D79" s="115"/>
-      <c r="E79" s="262"/>
+      <c r="A79" s="272">
+        <v>75306</v>
+      </c>
+      <c r="B79" s="273">
+        <v>46013</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79" s="269">
+        <v>6</v>
+      </c>
+      <c r="E79" s="4">
+        <v>8000</v>
+      </c>
       <c r="F79" s="262">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G79" s="281">
+        <v>48000</v>
+      </c>
+      <c r="G79" s="285">
         <f>SUM(F79:F83)</f>
-        <v>0</v>
+        <v>357000</v>
       </c>
     </row>
     <row r="80" s="244" customFormat="1" spans="1:7">
-      <c r="A80" s="203"/>
-      <c r="B80" s="274"/>
-      <c r="C80" s="267"/>
-      <c r="D80" s="115"/>
-      <c r="E80" s="262"/>
+      <c r="A80" s="274"/>
+      <c r="B80" s="275"/>
+      <c r="C80" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D80" s="269">
+        <v>1</v>
+      </c>
+      <c r="E80" s="4">
+        <v>20000</v>
+      </c>
       <c r="F80" s="262">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G80" s="281"/>
+        <v>20000</v>
+      </c>
+      <c r="G80" s="283"/>
     </row>
     <row r="81" s="244" customFormat="1" spans="1:7">
-      <c r="A81" s="203"/>
-      <c r="B81" s="274"/>
-      <c r="C81" s="267"/>
-      <c r="D81" s="115"/>
-      <c r="E81" s="262"/>
+      <c r="A81" s="274"/>
+      <c r="B81" s="275"/>
+      <c r="C81" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D81" s="269">
+        <v>2</v>
+      </c>
+      <c r="E81" s="4">
+        <v>22000</v>
+      </c>
       <c r="F81" s="262">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G81" s="281"/>
+        <v>44000</v>
+      </c>
+      <c r="G81" s="283"/>
     </row>
     <row r="82" s="244" customFormat="1" spans="1:7">
-      <c r="A82" s="203"/>
-      <c r="B82" s="274"/>
-      <c r="C82" s="267"/>
-      <c r="D82" s="115"/>
-      <c r="E82" s="262"/>
+      <c r="A82" s="274"/>
+      <c r="B82" s="275"/>
+      <c r="C82" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D82" s="269">
+        <v>1</v>
+      </c>
+      <c r="E82" s="4">
+        <v>120000</v>
+      </c>
       <c r="F82" s="262">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G82" s="281"/>
+        <v>120000</v>
+      </c>
+      <c r="G82" s="283"/>
     </row>
     <row r="83" s="244" customFormat="1" spans="1:7">
-      <c r="A83" s="203"/>
-      <c r="B83" s="274"/>
-      <c r="C83" s="267"/>
-      <c r="D83" s="115"/>
-      <c r="E83" s="262"/>
+      <c r="A83" s="276"/>
+      <c r="B83" s="277"/>
+      <c r="C83" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D83" s="269">
+        <v>1</v>
+      </c>
+      <c r="E83" s="4">
+        <v>125000</v>
+      </c>
       <c r="F83" s="262">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G83" s="281"/>
+        <v>125000</v>
+      </c>
+      <c r="G83" s="284"/>
     </row>
     <row r="84" s="244" customFormat="1" spans="1:7">
-      <c r="A84" s="203"/>
-      <c r="B84" s="274"/>
-      <c r="C84" s="267"/>
-      <c r="D84" s="115"/>
-      <c r="E84" s="262"/>
+      <c r="A84" s="272">
+        <v>75383</v>
+      </c>
+      <c r="B84" s="273">
+        <v>46014</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" s="269">
+        <v>3</v>
+      </c>
+      <c r="E84" s="4">
+        <v>8000</v>
+      </c>
       <c r="F84" s="262">
-        <f t="shared" ref="F84:F92" si="5">D84*E84</f>
-        <v>0</v>
-      </c>
-      <c r="G84" s="281">
-        <f>SUM(F84:F89)</f>
-        <v>0</v>
+        <f>D84*E84</f>
+        <v>24000</v>
+      </c>
+      <c r="G84" s="286">
+        <f>SUM(F84:F86)</f>
+        <v>66000</v>
       </c>
     </row>
     <row r="85" s="244" customFormat="1" spans="1:7">
-      <c r="A85" s="203"/>
-      <c r="B85" s="274"/>
-      <c r="C85" s="267"/>
-      <c r="D85" s="115"/>
-      <c r="E85" s="262"/>
+      <c r="A85" s="274"/>
+      <c r="B85" s="275"/>
+      <c r="C85" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D85" s="269">
+        <v>1</v>
+      </c>
+      <c r="E85" s="4">
+        <v>20000</v>
+      </c>
       <c r="F85" s="262">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G85" s="281"/>
+        <f>D85*E85</f>
+        <v>20000</v>
+      </c>
+      <c r="G85" s="287"/>
     </row>
     <row r="86" s="244" customFormat="1" spans="1:7">
-      <c r="A86" s="203"/>
-      <c r="B86" s="274"/>
-      <c r="C86" s="267"/>
-      <c r="D86" s="115"/>
-      <c r="E86" s="262"/>
+      <c r="A86" s="276"/>
+      <c r="B86" s="278"/>
+      <c r="C86" s="267" t="s">
+        <v>47</v>
+      </c>
+      <c r="D86" s="115">
+        <v>1</v>
+      </c>
+      <c r="E86" s="262">
+        <v>22000</v>
+      </c>
       <c r="F86" s="262">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G86" s="281"/>
+        <f t="shared" ref="F86:F92" si="5">D86*E86</f>
+        <v>22000</v>
+      </c>
+      <c r="G86" s="288"/>
     </row>
     <row r="87" s="244" customFormat="1" spans="1:7">
-      <c r="A87" s="203"/>
-      <c r="B87" s="274"/>
+      <c r="A87" s="56"/>
+      <c r="B87" s="25"/>
       <c r="C87" s="267"/>
       <c r="D87" s="115"/>
       <c r="E87" s="262"/>
@@ -12009,11 +12222,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G87" s="281"/>
+      <c r="G87" s="289"/>
     </row>
     <row r="88" s="244" customFormat="1" spans="1:7">
-      <c r="A88" s="203"/>
-      <c r="B88" s="274"/>
+      <c r="A88" s="56"/>
+      <c r="B88" s="25"/>
       <c r="C88" s="267"/>
       <c r="D88" s="115"/>
       <c r="E88" s="262"/>
@@ -12021,11 +12234,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G88" s="281"/>
+      <c r="G88" s="289"/>
     </row>
     <row r="89" s="244" customFormat="1" spans="1:7">
-      <c r="A89" s="203"/>
-      <c r="B89" s="274"/>
+      <c r="A89" s="56"/>
+      <c r="B89" s="25"/>
       <c r="C89" s="267"/>
       <c r="D89" s="115"/>
       <c r="E89" s="262"/>
@@ -12033,11 +12246,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G89" s="281"/>
+      <c r="G89" s="289"/>
     </row>
     <row r="90" s="244" customFormat="1" spans="1:7">
-      <c r="A90" s="203"/>
-      <c r="B90" s="274"/>
+      <c r="A90" s="56"/>
+      <c r="B90" s="25"/>
       <c r="C90" s="267"/>
       <c r="D90" s="115"/>
       <c r="E90" s="262"/>
@@ -12045,14 +12258,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G90" s="281">
+      <c r="G90" s="289">
         <f>SUM(F90:F92)</f>
         <v>0</v>
       </c>
     </row>
     <row r="91" s="244" customFormat="1" spans="1:7">
-      <c r="A91" s="203"/>
-      <c r="B91" s="274"/>
+      <c r="A91" s="56"/>
+      <c r="B91" s="25"/>
       <c r="C91" s="267"/>
       <c r="D91" s="115"/>
       <c r="E91" s="262"/>
@@ -12060,11 +12273,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G91" s="281"/>
+      <c r="G91" s="289"/>
     </row>
     <row r="92" s="244" customFormat="1" spans="1:7">
-      <c r="A92" s="203"/>
-      <c r="B92" s="274"/>
+      <c r="A92" s="56"/>
+      <c r="B92" s="25"/>
       <c r="C92" s="267"/>
       <c r="D92" s="115"/>
       <c r="E92" s="262"/>
@@ -12072,11 +12285,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G92" s="281"/>
+      <c r="G92" s="289"/>
     </row>
     <row r="93" s="244" customFormat="1" spans="1:7">
-      <c r="A93" s="203"/>
-      <c r="B93" s="274"/>
+      <c r="A93" s="56"/>
+      <c r="B93" s="25"/>
       <c r="C93" s="267"/>
       <c r="D93" s="115"/>
       <c r="E93" s="262"/>
@@ -12084,14 +12297,14 @@
         <f t="shared" ref="F93:F113" si="6">D93*E93</f>
         <v>0</v>
       </c>
-      <c r="G93" s="281">
+      <c r="G93" s="289">
         <f>SUM(F93:F98)</f>
         <v>0</v>
       </c>
     </row>
     <row r="94" s="244" customFormat="1" spans="1:7">
-      <c r="A94" s="203"/>
-      <c r="B94" s="274"/>
+      <c r="A94" s="56"/>
+      <c r="B94" s="25"/>
       <c r="C94" s="267"/>
       <c r="D94" s="115"/>
       <c r="E94" s="262"/>
@@ -12099,11 +12312,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G94" s="281"/>
+      <c r="G94" s="289"/>
     </row>
     <row r="95" s="244" customFormat="1" spans="1:7">
-      <c r="A95" s="203"/>
-      <c r="B95" s="274"/>
+      <c r="A95" s="56"/>
+      <c r="B95" s="25"/>
       <c r="C95" s="267"/>
       <c r="D95" s="115"/>
       <c r="E95" s="262"/>
@@ -12111,11 +12324,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G95" s="281"/>
+      <c r="G95" s="289"/>
     </row>
     <row r="96" s="244" customFormat="1" spans="1:7">
-      <c r="A96" s="203"/>
-      <c r="B96" s="274"/>
+      <c r="A96" s="56"/>
+      <c r="B96" s="25"/>
       <c r="C96" s="267"/>
       <c r="D96" s="115"/>
       <c r="E96" s="262"/>
@@ -12123,11 +12336,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G96" s="281"/>
+      <c r="G96" s="289"/>
     </row>
     <row r="97" s="244" customFormat="1" spans="1:7">
-      <c r="A97" s="203"/>
-      <c r="B97" s="274"/>
+      <c r="A97" s="56"/>
+      <c r="B97" s="25"/>
       <c r="C97" s="267"/>
       <c r="D97" s="115"/>
       <c r="E97" s="262"/>
@@ -12135,11 +12348,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G97" s="281"/>
+      <c r="G97" s="289"/>
     </row>
     <row r="98" s="244" customFormat="1" spans="1:7">
-      <c r="A98" s="203"/>
-      <c r="B98" s="274"/>
+      <c r="A98" s="56"/>
+      <c r="B98" s="25"/>
       <c r="C98" s="267"/>
       <c r="D98" s="115"/>
       <c r="E98" s="262"/>
@@ -12147,11 +12360,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G98" s="281"/>
+      <c r="G98" s="289"/>
     </row>
     <row r="99" s="244" customFormat="1" spans="1:7">
-      <c r="A99" s="203"/>
-      <c r="B99" s="274"/>
+      <c r="A99" s="56"/>
+      <c r="B99" s="25"/>
       <c r="C99" s="267"/>
       <c r="D99" s="115"/>
       <c r="E99" s="262"/>
@@ -12159,14 +12372,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G99" s="281">
+      <c r="G99" s="289">
         <f>SUM(F99:F103)</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" s="244" customFormat="1" spans="1:7">
-      <c r="A100" s="203"/>
-      <c r="B100" s="274"/>
+      <c r="A100" s="56"/>
+      <c r="B100" s="25"/>
       <c r="C100" s="267"/>
       <c r="D100" s="115"/>
       <c r="E100" s="262"/>
@@ -12174,11 +12387,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G100" s="281"/>
+      <c r="G100" s="289"/>
     </row>
     <row r="101" s="244" customFormat="1" spans="1:7">
-      <c r="A101" s="203"/>
-      <c r="B101" s="274"/>
+      <c r="A101" s="56"/>
+      <c r="B101" s="25"/>
       <c r="C101" s="267"/>
       <c r="D101" s="115"/>
       <c r="E101" s="262"/>
@@ -12186,11 +12399,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G101" s="281"/>
+      <c r="G101" s="289"/>
     </row>
     <row r="102" s="244" customFormat="1" spans="1:7">
-      <c r="A102" s="203"/>
-      <c r="B102" s="274"/>
+      <c r="A102" s="56"/>
+      <c r="B102" s="25"/>
       <c r="C102" s="267"/>
       <c r="D102" s="115"/>
       <c r="E102" s="262"/>
@@ -12198,11 +12411,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G102" s="281"/>
+      <c r="G102" s="289"/>
     </row>
     <row r="103" s="244" customFormat="1" spans="1:7">
-      <c r="A103" s="203"/>
-      <c r="B103" s="274"/>
+      <c r="A103" s="56"/>
+      <c r="B103" s="25"/>
       <c r="C103" s="267"/>
       <c r="D103" s="115"/>
       <c r="E103" s="262"/>
@@ -12210,11 +12423,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G103" s="281"/>
+      <c r="G103" s="289"/>
     </row>
     <row r="104" s="244" customFormat="1" spans="1:7">
-      <c r="A104" s="203"/>
-      <c r="B104" s="274"/>
+      <c r="A104" s="56"/>
+      <c r="B104" s="25"/>
       <c r="C104" s="267"/>
       <c r="D104" s="115"/>
       <c r="E104" s="262"/>
@@ -12222,14 +12435,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G104" s="281">
+      <c r="G104" s="289">
         <f>SUM(F104:F109)</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" s="244" customFormat="1" spans="1:7">
-      <c r="A105" s="203"/>
-      <c r="B105" s="274"/>
+      <c r="A105" s="56"/>
+      <c r="B105" s="25"/>
       <c r="C105" s="267"/>
       <c r="D105" s="115"/>
       <c r="E105" s="262"/>
@@ -12237,11 +12450,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G105" s="281"/>
+      <c r="G105" s="289"/>
     </row>
     <row r="106" s="244" customFormat="1" spans="1:7">
-      <c r="A106" s="203"/>
-      <c r="B106" s="274"/>
+      <c r="A106" s="56"/>
+      <c r="B106" s="25"/>
       <c r="C106" s="267"/>
       <c r="D106" s="115"/>
       <c r="E106" s="262"/>
@@ -12249,11 +12462,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G106" s="281"/>
+      <c r="G106" s="289"/>
     </row>
     <row r="107" s="244" customFormat="1" spans="1:7">
-      <c r="A107" s="203"/>
-      <c r="B107" s="274"/>
+      <c r="A107" s="56"/>
+      <c r="B107" s="25"/>
       <c r="C107" s="267"/>
       <c r="D107" s="115"/>
       <c r="E107" s="262"/>
@@ -12261,11 +12474,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G107" s="281"/>
+      <c r="G107" s="289"/>
     </row>
     <row r="108" s="244" customFormat="1" spans="1:7">
-      <c r="A108" s="203"/>
-      <c r="B108" s="274"/>
+      <c r="A108" s="56"/>
+      <c r="B108" s="25"/>
       <c r="C108" s="267"/>
       <c r="D108" s="115"/>
       <c r="E108" s="262"/>
@@ -12273,11 +12486,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G108" s="281"/>
+      <c r="G108" s="289"/>
     </row>
     <row r="109" s="244" customFormat="1" spans="1:7">
-      <c r="A109" s="203"/>
-      <c r="B109" s="274"/>
+      <c r="A109" s="56"/>
+      <c r="B109" s="25"/>
       <c r="C109" s="267"/>
       <c r="D109" s="115"/>
       <c r="E109" s="262"/>
@@ -12285,11 +12498,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G109" s="281"/>
+      <c r="G109" s="289"/>
     </row>
     <row r="110" s="244" customFormat="1" spans="1:7">
-      <c r="A110" s="203"/>
-      <c r="B110" s="274"/>
+      <c r="A110" s="56"/>
+      <c r="B110" s="25"/>
       <c r="C110" s="267"/>
       <c r="D110" s="115"/>
       <c r="E110" s="262"/>
@@ -12297,14 +12510,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G110" s="281">
+      <c r="G110" s="289">
         <f>SUM(F110:F113)</f>
         <v>0</v>
       </c>
     </row>
     <row r="111" s="244" customFormat="1" spans="1:7">
-      <c r="A111" s="203"/>
-      <c r="B111" s="274"/>
+      <c r="A111" s="56"/>
+      <c r="B111" s="25"/>
       <c r="C111" s="267"/>
       <c r="D111" s="115"/>
       <c r="E111" s="262"/>
@@ -12312,11 +12525,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G111" s="281"/>
+      <c r="G111" s="289"/>
     </row>
     <row r="112" s="244" customFormat="1" spans="1:7">
-      <c r="A112" s="203"/>
-      <c r="B112" s="274"/>
+      <c r="A112" s="56"/>
+      <c r="B112" s="25"/>
       <c r="C112" s="267"/>
       <c r="D112" s="115"/>
       <c r="E112" s="262"/>
@@ -12324,11 +12537,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G112" s="281"/>
+      <c r="G112" s="289"/>
     </row>
     <row r="113" s="244" customFormat="1" spans="1:7">
-      <c r="A113" s="203"/>
-      <c r="B113" s="274"/>
+      <c r="A113" s="56"/>
+      <c r="B113" s="25"/>
       <c r="C113" s="267"/>
       <c r="D113" s="115"/>
       <c r="E113" s="262"/>
@@ -12336,11 +12549,11 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G113" s="281"/>
+      <c r="G113" s="289"/>
     </row>
     <row r="114" s="244" customFormat="1" spans="1:7">
-      <c r="A114" s="203"/>
-      <c r="B114" s="274"/>
+      <c r="A114" s="56"/>
+      <c r="B114" s="25"/>
       <c r="C114" s="267"/>
       <c r="D114" s="115"/>
       <c r="E114" s="262"/>
@@ -12348,14 +12561,14 @@
         <f t="shared" ref="F114:F116" si="7">D114*E114</f>
         <v>0</v>
       </c>
-      <c r="G114" s="281">
+      <c r="G114" s="289">
         <f>SUM(F114:F116)</f>
         <v>0</v>
       </c>
     </row>
     <row r="115" s="244" customFormat="1" spans="1:7">
-      <c r="A115" s="203"/>
-      <c r="B115" s="274"/>
+      <c r="A115" s="56"/>
+      <c r="B115" s="25"/>
       <c r="C115" s="267"/>
       <c r="D115" s="115"/>
       <c r="E115" s="262"/>
@@ -12363,11 +12576,11 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G115" s="281"/>
+      <c r="G115" s="289"/>
     </row>
     <row r="116" s="244" customFormat="1" spans="1:7">
-      <c r="A116" s="203"/>
-      <c r="B116" s="274"/>
+      <c r="A116" s="56"/>
+      <c r="B116" s="25"/>
       <c r="C116" s="267"/>
       <c r="D116" s="115"/>
       <c r="E116" s="262"/>
@@ -12375,20 +12588,20 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G116" s="281"/>
+      <c r="G116" s="289"/>
     </row>
     <row r="117" s="244" customFormat="1" spans="1:7">
-      <c r="A117" s="275" t="s">
-        <v>54</v>
+      <c r="A117" s="279" t="s">
+        <v>57</v>
       </c>
       <c r="B117" s="122"/>
-      <c r="C117" s="276"/>
+      <c r="C117" s="280"/>
       <c r="D117" s="122"/>
       <c r="E117" s="122"/>
-      <c r="F117" s="282"/>
+      <c r="F117" s="290"/>
       <c r="G117" s="63">
         <f>SUM(G2:G116)</f>
-        <v>6219000</v>
+        <v>7182000</v>
       </c>
     </row>
     <row r="118" s="244" customFormat="1" spans="1:7">
@@ -12670,10 +12883,10 @@
       <c r="D152" s="248"/>
       <c r="E152" s="249"/>
       <c r="G152" s="245"/>
-      <c r="H152" s="277"/>
+      <c r="H152" s="281"/>
     </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="68">
     <mergeCell ref="A117:F117"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
@@ -12694,6 +12907,9 @@
     <mergeCell ref="A66:A68"/>
     <mergeCell ref="A69:A72"/>
     <mergeCell ref="A73:A75"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="A84:A86"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B13"/>
@@ -12713,6 +12929,9 @@
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="B69:B72"/>
     <mergeCell ref="B73:B75"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="B84:B86"/>
     <mergeCell ref="G2:G4"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="G8:G13"/>
@@ -12732,6 +12951,9 @@
     <mergeCell ref="G66:G68"/>
     <mergeCell ref="G69:G72"/>
     <mergeCell ref="G73:G75"/>
+    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="G84:G86"/>
     <mergeCell ref="N69:N71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12757,16 +12979,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>3</v>
@@ -12783,7 +13005,7 @@
         <v>12340</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D2" s="16">
         <v>20</v>
@@ -12805,7 +13027,7 @@
         <v>12357</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D3" s="16">
         <v>20</v>
@@ -12827,7 +13049,7 @@
         <v>11374</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D4" s="16">
         <v>20</v>
@@ -12849,7 +13071,7 @@
         <v>13396</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D5" s="16">
         <v>20</v>
@@ -12871,7 +13093,7 @@
         <v>11474</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D6" s="16">
         <v>20</v>
@@ -12893,7 +13115,7 @@
         <v>13509</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D7" s="16">
         <v>20</v>
@@ -12915,7 +13137,7 @@
         <v>8224</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D8" s="16">
         <v>20</v>
@@ -12929,16 +13151,26 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="9" ht="109.9" customHeight="1" spans="1:7">
-      <c r="A9" s="93"/>
-      <c r="B9" s="115"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="16"/>
+    <row r="9" ht="321.8" customHeight="1" spans="1:7">
+      <c r="A9" s="93">
+        <v>46012</v>
+      </c>
+      <c r="B9" s="115">
+        <v>12122</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="16">
+        <v>20</v>
+      </c>
       <c r="E9" s="4"/>
-      <c r="F9" s="242"/>
+      <c r="F9" s="242">
+        <v>13000</v>
+      </c>
       <c r="G9" s="242">
         <f t="shared" ref="G9:G15" si="1">SUM(D9*F9)</f>
-        <v>0</v>
+        <v>260000</v>
       </c>
     </row>
     <row r="10" ht="26" spans="1:7">
@@ -12948,7 +13180,7 @@
       <c r="D10" s="241"/>
       <c r="E10" s="243">
         <f>SUM(G2:G9)</f>
-        <v>1680000</v>
+        <v>1940000</v>
       </c>
       <c r="F10" s="243"/>
       <c r="G10" s="243"/>
@@ -12999,7 +13231,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="224" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F1" s="224" t="s">
         <v>5</v>
@@ -13047,7 +13279,7 @@
     <row r="4" s="217" customFormat="1" spans="1:7">
       <c r="A4" s="229"/>
       <c r="B4" s="226" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C4" s="227">
         <v>0.3</v>
@@ -13065,7 +13297,7 @@
     <row r="5" s="217" customFormat="1" spans="1:6">
       <c r="A5" s="229"/>
       <c r="B5" s="226" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C5" s="227">
         <v>1</v>
@@ -13151,7 +13383,7 @@
     <row r="10" s="217" customFormat="1" spans="1:6">
       <c r="A10" s="230"/>
       <c r="B10" s="226" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C10" s="227">
         <v>2</v>
@@ -13208,7 +13440,7 @@
     <row r="13" s="217" customFormat="1" spans="1:6">
       <c r="A13" s="229"/>
       <c r="B13" s="226" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C13" s="227">
         <v>8</v>
@@ -13293,7 +13525,7 @@
     <row r="18" s="217" customFormat="1" spans="1:6">
       <c r="A18" s="229"/>
       <c r="B18" s="226" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C18" s="227">
         <v>1</v>
@@ -13327,7 +13559,7 @@
     <row r="20" s="217" customFormat="1" spans="1:6">
       <c r="A20" s="230"/>
       <c r="B20" s="226" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C20" s="227">
         <v>1</v>
@@ -15347,19 +15579,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>4</v>
@@ -15373,10 +15605,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="211" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D2" s="16">
         <v>3</v>
@@ -15517,31 +15749,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="182" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="182" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="182" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="182" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="182" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="182" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="182" t="s">
-        <v>68</v>
-      </c>
       <c r="H1" s="182" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I1" s="182" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="182" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" ht="387.45" customHeight="1" spans="1:10">
@@ -15549,10 +15781,10 @@
         <v>46000</v>
       </c>
       <c r="B2" s="184" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C2" s="175" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D2" s="176">
         <v>4</v>
@@ -15583,10 +15815,10 @@
         <v>46002</v>
       </c>
       <c r="B3" s="186" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C3" s="175" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D3" s="176">
         <v>4</v>
@@ -15616,7 +15848,7 @@
       <c r="A4" s="187"/>
       <c r="B4" s="188"/>
       <c r="C4" s="189" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D4" s="190">
         <v>4</v>
@@ -15644,10 +15876,10 @@
         <v>46006</v>
       </c>
       <c r="B5" s="184" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C5" s="175" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D5" s="176">
         <v>3</v>
@@ -15678,10 +15910,10 @@
         <v>46007</v>
       </c>
       <c r="B6" s="184" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C6" s="175" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D6" s="176">
         <v>3</v>
@@ -15712,10 +15944,10 @@
         <v>46010</v>
       </c>
       <c r="B7" s="174" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C7" s="191" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D7" s="176">
         <v>3</v>
@@ -15975,22 +16207,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="172" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="172" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="172" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="172" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="172" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="172" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H1" s="172" t="s">
         <v>5</v>
@@ -16001,10 +16233,10 @@
         <v>46009</v>
       </c>
       <c r="B2" s="174" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C2" s="175" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D2" s="176">
         <v>1</v>
@@ -16073,22 +16305,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="141" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="141" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="141" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="141" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="141" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="141" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H1" s="153" t="s">
         <v>5</v>
@@ -16099,10 +16331,10 @@
         <v>45992</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C2" s="143" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D2" s="144">
         <v>5</v>
@@ -16172,7 +16404,7 @@
       </c>
       <c r="E7" s="161"/>
       <c r="F7" s="162" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G7" s="162"/>
       <c r="H7" s="162">
@@ -16200,10 +16432,10 @@
         <v>45999</v>
       </c>
       <c r="B9" s="142" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C9" s="151" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D9" s="150">
         <v>3</v>
@@ -16225,7 +16457,7 @@
       <c r="A10" s="145"/>
       <c r="B10" s="145"/>
       <c r="C10" s="151" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D10" s="150">
         <v>3</v>
@@ -16244,7 +16476,7 @@
       <c r="A11" s="152"/>
       <c r="B11" s="152"/>
       <c r="C11" s="151" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D11" s="150">
         <v>2</v>
@@ -16271,7 +16503,7 @@
       </c>
       <c r="E12" s="161"/>
       <c r="F12" s="162" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G12" s="162"/>
       <c r="H12" s="162">
@@ -16299,10 +16531,10 @@
         <v>45992</v>
       </c>
       <c r="B14" s="142" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C14" s="143" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D14" s="144">
         <v>5</v>
@@ -16375,7 +16607,7 @@
       </c>
       <c r="E19" s="161"/>
       <c r="F19" s="162" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G19" s="162"/>
       <c r="H19" s="162">
@@ -16481,22 +16713,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H1" s="35" t="s">
         <v>5</v>
@@ -16507,10 +16739,10 @@
         <v>46001</v>
       </c>
       <c r="B2" s="115" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D2" s="115">
         <v>2</v>
@@ -16533,10 +16765,10 @@
         <v>46001</v>
       </c>
       <c r="B3" s="93" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D3" s="115">
         <v>4</v>
@@ -16559,10 +16791,10 @@
         <v>46004</v>
       </c>
       <c r="B4" s="130" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D4" s="115">
         <v>1</v>
@@ -16587,7 +16819,7 @@
       <c r="A5" s="131"/>
       <c r="B5" s="132"/>
       <c r="C5" s="38" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D5" s="115">
         <v>1</v>
@@ -16604,7 +16836,7 @@
     </row>
     <row r="6" ht="26" spans="1:8">
       <c r="A6" s="81" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" s="82"/>
       <c r="C6" s="82"/>
